--- a/data/RETI.MI.xlsx
+++ b/data/RETI.MI.xlsx
@@ -35493,6 +35493,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1528">
+      <c r="A1528" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1528" t="n">
+        <v>31500</v>
+      </c>
+      <c r="C1528" t="n">
+        <v>1.76999998092651</v>
+      </c>
+      <c r="D1528" t="n">
+        <v>1.71000003814697</v>
+      </c>
+      <c r="E1528" t="n">
+        <v>1.71000003814697</v>
+      </c>
+      <c r="F1528" t="n">
+        <v>1.74000000953674</v>
+      </c>
+      <c r="G1528" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RETI.MI.xlsx
+++ b/data/RETI.MI.xlsx
@@ -35516,6 +35516,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1529">
+      <c r="A1529" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1529" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C1529" t="n">
+        <v>1.72000002861023</v>
+      </c>
+      <c r="D1529" t="n">
+        <v>1.6599999666214</v>
+      </c>
+      <c r="E1529" t="n">
+        <v>1.72000002861023</v>
+      </c>
+      <c r="F1529" t="n">
+        <v>1.66999995708466</v>
+      </c>
+      <c r="G1529" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RETI.MI.xlsx
+++ b/data/RETI.MI.xlsx
@@ -35539,6 +35539,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1530">
+      <c r="A1530" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1530" t="n">
+        <v>27000</v>
+      </c>
+      <c r="C1530" t="n">
+        <v>1.6599999666214</v>
+      </c>
+      <c r="D1530" t="n">
+        <v>1.62999999523163</v>
+      </c>
+      <c r="E1530" t="n">
+        <v>1.64999997615814</v>
+      </c>
+      <c r="F1530" t="n">
+        <v>1.6599999666214</v>
+      </c>
+      <c r="G1530" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RETI.MI.xlsx
+++ b/data/RETI.MI.xlsx
@@ -35562,6 +35562,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1531">
+      <c r="A1531" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1531" t="n">
+        <v>10500</v>
+      </c>
+      <c r="C1531" t="n">
+        <v>1.64999997615814</v>
+      </c>
+      <c r="D1531" t="n">
+        <v>1.62000000476837</v>
+      </c>
+      <c r="E1531" t="n">
+        <v>1.64999997615814</v>
+      </c>
+      <c r="F1531" t="n">
+        <v>1.62000000476837</v>
+      </c>
+      <c r="G1531" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RETI.MI.xlsx
+++ b/data/RETI.MI.xlsx
@@ -35403,22 +35403,22 @@
     </row>
     <row r="1524">
       <c r="A1524" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1524" t="n">
-        <v>15000</v>
+        <v>3000</v>
       </c>
       <c r="C1524" t="n">
-        <v>1.72000002861023</v>
+        <v>1.74000000953674</v>
       </c>
       <c r="D1524" t="n">
-        <v>1.6599999666214</v>
+        <v>1.73000001907349</v>
       </c>
       <c r="E1524" t="n">
-        <v>1.72000002861023</v>
+        <v>1.73000001907349</v>
       </c>
       <c r="F1524" t="n">
-        <v>1.71000003814697</v>
+        <v>1.74000000953674</v>
       </c>
       <c r="G1524" t="s">
         <v>7</v>
@@ -35426,19 +35426,19 @@
     </row>
     <row r="1525">
       <c r="A1525" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1525" t="n">
-        <v>4500</v>
+        <v>15000</v>
       </c>
       <c r="C1525" t="n">
-        <v>1.74000000953674</v>
+        <v>1.72000002861023</v>
       </c>
       <c r="D1525" t="n">
-        <v>1.69000005722046</v>
+        <v>1.6599999666214</v>
       </c>
       <c r="E1525" t="n">
-        <v>1.74000000953674</v>
+        <v>1.72000002861023</v>
       </c>
       <c r="F1525" t="n">
         <v>1.71000003814697</v>
@@ -35449,22 +35449,22 @@
     </row>
     <row r="1526">
       <c r="A1526" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1526" t="n">
-        <v>1500</v>
+        <v>4500</v>
       </c>
       <c r="C1526" t="n">
-        <v>1.73000001907349</v>
+        <v>1.74000000953674</v>
       </c>
       <c r="D1526" t="n">
-        <v>1.73000001907349</v>
+        <v>1.69000005722046</v>
       </c>
       <c r="E1526" t="n">
-        <v>1.73000001907349</v>
+        <v>1.74000000953674</v>
       </c>
       <c r="F1526" t="n">
-        <v>1.73000001907349</v>
+        <v>1.71000003814697</v>
       </c>
       <c r="G1526" t="s">
         <v>7</v>
@@ -35472,22 +35472,22 @@
     </row>
     <row r="1527">
       <c r="A1527" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1527" t="n">
-        <v>31500</v>
+        <v>1500</v>
       </c>
       <c r="C1527" t="n">
-        <v>1.69000005722046</v>
+        <v>1.73000001907349</v>
       </c>
       <c r="D1527" t="n">
-        <v>1.64999997615814</v>
+        <v>1.73000001907349</v>
       </c>
       <c r="E1527" t="n">
-        <v>1.69000005722046</v>
+        <v>1.73000001907349</v>
       </c>
       <c r="F1527" t="n">
-        <v>1.67999994754791</v>
+        <v>1.73000001907349</v>
       </c>
       <c r="G1527" t="s">
         <v>7</v>
@@ -35495,22 +35495,22 @@
     </row>
     <row r="1528">
       <c r="A1528" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1528" t="n">
         <v>31500</v>
       </c>
       <c r="C1528" t="n">
-        <v>1.76999998092651</v>
+        <v>1.69000005722046</v>
       </c>
       <c r="D1528" t="n">
-        <v>1.71000003814697</v>
+        <v>1.64999997615814</v>
       </c>
       <c r="E1528" t="n">
-        <v>1.71000003814697</v>
+        <v>1.69000005722046</v>
       </c>
       <c r="F1528" t="n">
-        <v>1.74000000953674</v>
+        <v>1.67999994754791</v>
       </c>
       <c r="G1528" t="s">
         <v>7</v>
@@ -35518,22 +35518,22 @@
     </row>
     <row r="1529">
       <c r="A1529" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1529" t="n">
-        <v>30000</v>
+        <v>31500</v>
       </c>
       <c r="C1529" t="n">
-        <v>1.72000002861023</v>
+        <v>1.76999998092651</v>
       </c>
       <c r="D1529" t="n">
-        <v>1.6599999666214</v>
+        <v>1.71000003814697</v>
       </c>
       <c r="E1529" t="n">
-        <v>1.72000002861023</v>
+        <v>1.71000003814697</v>
       </c>
       <c r="F1529" t="n">
-        <v>1.66999995708466</v>
+        <v>1.74000000953674</v>
       </c>
       <c r="G1529" t="s">
         <v>7</v>
@@ -35541,22 +35541,22 @@
     </row>
     <row r="1530">
       <c r="A1530" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1530" t="n">
-        <v>27000</v>
+        <v>30000</v>
       </c>
       <c r="C1530" t="n">
+        <v>1.72000002861023</v>
+      </c>
+      <c r="D1530" t="n">
         <v>1.6599999666214</v>
       </c>
-      <c r="D1530" t="n">
-        <v>1.62999999523163</v>
-      </c>
       <c r="E1530" t="n">
-        <v>1.64999997615814</v>
+        <v>1.72000002861023</v>
       </c>
       <c r="F1530" t="n">
-        <v>1.6599999666214</v>
+        <v>1.66999995708466</v>
       </c>
       <c r="G1530" t="s">
         <v>7</v>
@@ -35564,24 +35564,47 @@
     </row>
     <row r="1531">
       <c r="A1531" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1531" t="n">
-        <v>10500</v>
+        <v>27000</v>
       </c>
       <c r="C1531" t="n">
-        <v>1.64999997615814</v>
+        <v>1.6599999666214</v>
       </c>
       <c r="D1531" t="n">
-        <v>1.62000000476837</v>
+        <v>1.62999999523163</v>
       </c>
       <c r="E1531" t="n">
         <v>1.64999997615814</v>
       </c>
       <c r="F1531" t="n">
-        <v>1.62000000476837</v>
+        <v>1.6599999666214</v>
       </c>
       <c r="G1531" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1532">
+      <c r="A1532" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1532" t="n">
+        <v>18000</v>
+      </c>
+      <c r="C1532" t="n">
+        <v>1.64999997615814</v>
+      </c>
+      <c r="D1532" t="n">
+        <v>1.61000001430511</v>
+      </c>
+      <c r="E1532" t="n">
+        <v>1.61000001430511</v>
+      </c>
+      <c r="F1532" t="n">
+        <v>1.62999999523163</v>
+      </c>
+      <c r="G1532" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RETI.MI.xlsx
+++ b/data/RETI.MI.xlsx
@@ -421,7 +421,7 @@
         <v>0.889900028705597</v>
       </c>
       <c r="G2" t="n">
-        <v>0.759858548641205</v>
+        <v>0.759858429431915</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>0.879899978637695</v>
       </c>
       <c r="G4" t="n">
-        <v>0.751319646835327</v>
+        <v>0.751319706439972</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G5" t="n">
-        <v>0.765066981315613</v>
+        <v>0.765067040920258</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G6" t="n">
-        <v>0.765066981315613</v>
+        <v>0.765067040920258</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G9" t="n">
-        <v>0.732619941234589</v>
+        <v>0.732620000839233</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G10" t="n">
-        <v>0.722373604774475</v>
+        <v>0.72237354516983</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>0.814000010490417</v>
       </c>
       <c r="G12" t="n">
-        <v>0.695049643516541</v>
+        <v>0.695049703121185</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G13" t="n">
-        <v>0.691634297370911</v>
+        <v>0.691634237766266</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G14" t="n">
-        <v>0.683095574378967</v>
+        <v>0.683095514774323</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G15" t="n">
-        <v>0.683095574378967</v>
+        <v>0.683095514774323</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G16" t="n">
-        <v>0.666018128395081</v>
+        <v>0.666018187999725</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>0.814000010490417</v>
       </c>
       <c r="G19" t="n">
-        <v>0.695049643516541</v>
+        <v>0.695049703121185</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G23" t="n">
-        <v>0.666018128395081</v>
+        <v>0.666018187999725</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G24" t="n">
-        <v>0.652356266975403</v>
+        <v>0.652356207370758</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G28" t="n">
-        <v>0.631863415241241</v>
+        <v>0.631863355636597</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G29" t="n">
-        <v>0.623324751853943</v>
+        <v>0.623324692249298</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G30" t="n">
-        <v>0.607955038547516</v>
+        <v>0.607955098152161</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G31" t="n">
-        <v>0.587462186813354</v>
+        <v>0.58746212720871</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G34" t="n">
-        <v>0.609662771224976</v>
+        <v>0.60966283082962</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G35" t="n">
-        <v>0.580631256103516</v>
+        <v>0.580631196498871</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G37" t="n">
-        <v>0.537937760353088</v>
+        <v>0.537937819957733</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G38" t="n">
-        <v>0.537937760353088</v>
+        <v>0.537937819957733</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G39" t="n">
-        <v>0.525983572006226</v>
+        <v>0.525983512401581</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G41" t="n">
-        <v>0.537937760353088</v>
+        <v>0.537937819957733</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G42" t="n">
-        <v>0.604539513587952</v>
+        <v>0.604539573192596</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G43" t="n">
-        <v>0.623324751853943</v>
+        <v>0.623324692249298</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G44" t="n">
-        <v>0.604539513587952</v>
+        <v>0.604539573192596</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G45" t="n">
-        <v>0.618201494216919</v>
+        <v>0.618201434612274</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G46" t="n">
-        <v>0.631863415241241</v>
+        <v>0.631863355636597</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G47" t="n">
-        <v>0.607955038547516</v>
+        <v>0.607955098152161</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G48" t="n">
-        <v>0.61137056350708</v>
+        <v>0.611370503902435</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G50" t="n">
-        <v>0.631863415241241</v>
+        <v>0.631863355636597</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G52" t="n">
-        <v>0.705296099185944</v>
+        <v>0.705296158790588</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G57" t="n">
-        <v>0.705296099185944</v>
+        <v>0.705296158790588</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G58" t="n">
-        <v>0.703588485717773</v>
+        <v>0.703588426113129</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G59" t="n">
-        <v>0.683095574378967</v>
+        <v>0.683095514774323</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G60" t="n">
-        <v>0.683095574378967</v>
+        <v>0.683095514774323</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G61" t="n">
-        <v>0.683095574378967</v>
+        <v>0.683095514774323</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G64" t="n">
-        <v>0.683095574378967</v>
+        <v>0.683095514774323</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G67" t="n">
-        <v>0.683095574378967</v>
+        <v>0.683095514774323</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G73" t="n">
-        <v>0.705296099185944</v>
+        <v>0.705296158790588</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G74" t="n">
-        <v>0.691634297370911</v>
+        <v>0.691634237766266</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G75" t="n">
-        <v>0.700172901153564</v>
+        <v>0.700172960758209</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G76" t="n">
-        <v>0.707003891468048</v>
+        <v>0.707003951072693</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G77" t="n">
-        <v>0.700172901153564</v>
+        <v>0.700172960758209</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G78" t="n">
-        <v>0.700172901153564</v>
+        <v>0.700172960758209</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G79" t="n">
-        <v>0.705296099185944</v>
+        <v>0.705296158790588</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G81" t="n">
-        <v>0.708711683750153</v>
+        <v>0.708711624145508</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G86" t="n">
-        <v>0.700172901153564</v>
+        <v>0.700172960758209</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G87" t="n">
-        <v>0.688218772411346</v>
+        <v>0.688218712806702</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G88" t="n">
-        <v>0.700172901153564</v>
+        <v>0.700172960758209</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G94" t="n">
-        <v>0.698465287685394</v>
+        <v>0.69846522808075</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G95" t="n">
-        <v>0.683095574378967</v>
+        <v>0.683095514774323</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G98" t="n">
-        <v>0.666018128395081</v>
+        <v>0.666018187999725</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G102" t="n">
-        <v>0.683095574378967</v>
+        <v>0.683095514774323</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G103" t="n">
-        <v>0.707003891468048</v>
+        <v>0.707003951072693</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G104" t="n">
-        <v>0.683095574378967</v>
+        <v>0.683095514774323</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G105" t="n">
-        <v>0.683095574378967</v>
+        <v>0.683095514774323</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G106" t="n">
-        <v>0.683095574378967</v>
+        <v>0.683095514774323</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G107" t="n">
-        <v>0.691634297370911</v>
+        <v>0.691634237766266</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G108" t="n">
-        <v>0.700172901153564</v>
+        <v>0.700172960758209</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G109" t="n">
-        <v>0.683095574378967</v>
+        <v>0.683095514774323</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G110" t="n">
-        <v>0.698465287685394</v>
+        <v>0.69846522808075</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G111" t="n">
-        <v>0.703588485717773</v>
+        <v>0.703588426113129</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G112" t="n">
-        <v>0.686511039733887</v>
+        <v>0.686511099338531</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G113" t="n">
-        <v>0.691634297370911</v>
+        <v>0.691634237766266</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G114" t="n">
-        <v>0.700172901153564</v>
+        <v>0.700172960758209</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G115" t="n">
-        <v>0.703588485717773</v>
+        <v>0.703588426113129</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>0.86599999666214</v>
       </c>
       <c r="G116" t="n">
-        <v>0.739450871944427</v>
+        <v>0.739450991153717</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>0.842000007629395</v>
       </c>
       <c r="G117" t="n">
-        <v>0.718958020210266</v>
+        <v>0.718958079814911</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>0.867999970912933</v>
       </c>
       <c r="G120" t="n">
-        <v>0.741158664226532</v>
+        <v>0.741158604621887</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>0.867999970912933</v>
       </c>
       <c r="G121" t="n">
-        <v>0.741158664226532</v>
+        <v>0.741158604621887</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G124" t="n">
-        <v>0.828253388404846</v>
+        <v>0.828253328800201</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G125" t="n">
-        <v>0.836792051792145</v>
+        <v>0.83679211139679</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G126" t="n">
-        <v>0.836792051792145</v>
+        <v>0.83679211139679</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G128" t="n">
-        <v>0.862408101558685</v>
+        <v>0.86240816116333</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G129" t="n">
-        <v>0.862408101558685</v>
+        <v>0.86240816116333</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G130" t="n">
-        <v>0.862408101558685</v>
+        <v>0.86240816116333</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G132" t="n">
-        <v>0.845330774784088</v>
+        <v>0.845330715179443</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G133" t="n">
-        <v>0.870946764945984</v>
+        <v>0.870946824550629</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G134" t="n">
-        <v>0.875216126441956</v>
+        <v>0.8752161860466</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G135" t="n">
-        <v>0.866677463054657</v>
+        <v>0.866677522659302</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G136" t="n">
-        <v>0.900832235813141</v>
+        <v>0.900832295417786</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G138" t="n">
-        <v>0.892293632030487</v>
+        <v>0.892293512821198</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G139" t="n">
-        <v>0.913640379905701</v>
+        <v>0.913640320301056</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G142" t="n">
-        <v>0.913640379905701</v>
+        <v>0.913640320301056</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G143" t="n">
-        <v>0.930717647075653</v>
+        <v>0.930717766284943</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G146" t="n">
-        <v>1.1356463432312</v>
+        <v>1.13564646244049</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G147" t="n">
-        <v>1.20395588874817</v>
+        <v>1.20395600795746</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G148" t="n">
-        <v>1.20395588874817</v>
+        <v>1.20395600795746</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G149" t="n">
-        <v>1.20395588874817</v>
+        <v>1.20395600795746</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G150" t="n">
-        <v>1.18637990951538</v>
+        <v>1.18637979030609</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G152" t="n">
-        <v>1.22153186798096</v>
+        <v>1.22153174877167</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G153" t="n">
-        <v>1.22153186798096</v>
+        <v>1.22153174877167</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G155" t="n">
-        <v>1.13804578781128</v>
+        <v>1.13804590702057</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>1.25499999523163</v>
       </c>
       <c r="G159" t="n">
-        <v>1.10289394855499</v>
+        <v>1.10289406776428</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G160" t="n">
-        <v>1.05455982685089</v>
+        <v>1.05455994606018</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G161" t="n">
-        <v>1.08971202373505</v>
+        <v>1.08971178531647</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G165" t="n">
-        <v>1.16880393028259</v>
+        <v>1.16880404949188</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G169" t="n">
-        <v>1.12925791740417</v>
+        <v>1.12925779819489</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G171" t="n">
-        <v>1.13804578781128</v>
+        <v>1.13804590702057</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G173" t="n">
-        <v>1.18637990951538</v>
+        <v>1.18637979030609</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G174" t="n">
-        <v>1.18198597431183</v>
+        <v>1.18198585510254</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>1.49500000476837</v>
       </c>
       <c r="G178" t="n">
-        <v>1.31380593776703</v>
+        <v>1.31380581855774</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G183" t="n">
-        <v>1.283047914505</v>
+        <v>1.28304779529572</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G189" t="n">
-        <v>1.45001983642578</v>
+        <v>1.45001995563507</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G190" t="n">
-        <v>1.41486787796021</v>
+        <v>1.41486799716949</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G191" t="n">
-        <v>1.38410985469818</v>
+        <v>1.38410997390747</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G192" t="n">
-        <v>1.37971591949463</v>
+        <v>1.37971580028534</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G194" t="n">
-        <v>1.34016978740692</v>
+        <v>1.34016990661621</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G195" t="n">
-        <v>1.34456372261047</v>
+        <v>1.34456384181976</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>1.49500000476837</v>
       </c>
       <c r="G199" t="n">
-        <v>1.31380593776703</v>
+        <v>1.31380581855774</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G206" t="n">
-        <v>1.34456372261047</v>
+        <v>1.34456384181976</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G207" t="n">
-        <v>1.34456372261047</v>
+        <v>1.34456384181976</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G218" t="n">
-        <v>1.24789583683014</v>
+        <v>1.24789595603943</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G229" t="n">
-        <v>1.27425980567932</v>
+        <v>1.27425992488861</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G231" t="n">
-        <v>1.283047914505</v>
+        <v>1.28304779529572</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G232" t="n">
-        <v>1.34456372261047</v>
+        <v>1.34456384181976</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G233" t="n">
-        <v>1.34016978740692</v>
+        <v>1.34016990661621</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G235" t="n">
-        <v>1.34456372261047</v>
+        <v>1.34456384181976</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>1.49500000476837</v>
       </c>
       <c r="G237" t="n">
-        <v>1.31380593776703</v>
+        <v>1.31380581855774</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G238" t="n">
-        <v>1.36653387546539</v>
+        <v>1.3665337562561</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G239" t="n">
-        <v>1.34016978740692</v>
+        <v>1.34016990661621</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G240" t="n">
-        <v>1.74881184101105</v>
+        <v>1.74881172180176</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G241" t="n">
-        <v>2.24972748756409</v>
+        <v>2.24972772598267</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G244" t="n">
-        <v>2.52215552330017</v>
+        <v>2.52215576171875</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G245" t="n">
-        <v>2.39912366867065</v>
+        <v>2.39912390708923</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G246" t="n">
-        <v>2.27609157562256</v>
+        <v>2.27609181404114</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G247" t="n">
-        <v>2.17063593864441</v>
+        <v>2.17063570022583</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G248" t="n">
-        <v>2.27609157562256</v>
+        <v>2.27609181404114</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G249" t="n">
-        <v>2.20578789710999</v>
+        <v>2.20578813552856</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G253" t="n">
-        <v>2.3288197517395</v>
+        <v>2.32881999015808</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G254" t="n">
-        <v>2.34639573097229</v>
+        <v>2.34639596939087</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G255" t="n">
-        <v>2.33760786056519</v>
+        <v>2.33760809898376</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G256" t="n">
-        <v>2.3288197517395</v>
+        <v>2.32881999015808</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G258" t="n">
-        <v>2.28487992286682</v>
+        <v>2.28487968444824</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G261" t="n">
-        <v>2.21457576751709</v>
+        <v>2.21457600593567</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G262" t="n">
-        <v>2.24972748756409</v>
+        <v>2.24972772598267</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G264" t="n">
-        <v>2.20578789710999</v>
+        <v>2.20578813552856</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G265" t="n">
-        <v>2.34639573097229</v>
+        <v>2.34639596939087</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G267" t="n">
-        <v>2.27609157562256</v>
+        <v>2.27609181404114</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G268" t="n">
-        <v>2.38154768943787</v>
+        <v>2.38154745101929</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G269" t="n">
-        <v>2.31124401092529</v>
+        <v>2.31124377250671</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G272" t="n">
-        <v>2.17063593864441</v>
+        <v>2.17063570022583</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G273" t="n">
-        <v>2.27609157562256</v>
+        <v>2.27609181404114</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G274" t="n">
-        <v>2.24972748756409</v>
+        <v>2.24972772598267</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G275" t="n">
-        <v>2.28487992286682</v>
+        <v>2.28487968444824</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G276" t="n">
-        <v>2.28487992286682</v>
+        <v>2.28487968444824</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G278" t="n">
-        <v>2.3288197517395</v>
+        <v>2.32881999015808</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G280" t="n">
-        <v>2.28487992286682</v>
+        <v>2.28487968444824</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G281" t="n">
-        <v>2.3288197517395</v>
+        <v>2.32881999015808</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G283" t="n">
-        <v>2.25851583480835</v>
+        <v>2.25851559638977</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G285" t="n">
-        <v>2.27609157562256</v>
+        <v>2.27609181404114</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G290" t="n">
-        <v>2.25851583480835</v>
+        <v>2.25851559638977</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G291" t="n">
-        <v>2.27609157562256</v>
+        <v>2.27609181404114</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G292" t="n">
-        <v>2.21457576751709</v>
+        <v>2.21457600593567</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G293" t="n">
-        <v>2.24972748756409</v>
+        <v>2.24972772598267</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G294" t="n">
-        <v>2.28487992286682</v>
+        <v>2.28487968444824</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G297" t="n">
-        <v>2.21457576751709</v>
+        <v>2.21457600593567</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G298" t="n">
-        <v>2.21457576751709</v>
+        <v>2.21457600593567</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G300" t="n">
-        <v>2.20578789710999</v>
+        <v>2.20578813552856</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G304" t="n">
-        <v>2.03881597518921</v>
+        <v>2.03881573677063</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G306" t="n">
-        <v>1.99487555027008</v>
+        <v>1.99487566947937</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G309" t="n">
-        <v>1.9333598613739</v>
+        <v>1.93335962295532</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G310" t="n">
-        <v>1.83669185638428</v>
+        <v>1.83669173717499</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G311" t="n">
-        <v>1.88941991329193</v>
+        <v>1.88941979408264</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G312" t="n">
-        <v>1.82790374755859</v>
+        <v>1.82790386676788</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G313" t="n">
-        <v>1.9333598613739</v>
+        <v>1.93335962295532</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G314" t="n">
-        <v>1.9333598613739</v>
+        <v>1.93335962295532</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G322" t="n">
-        <v>2.10033178329468</v>
+        <v>2.10033202171326</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G323" t="n">
-        <v>2.10033178329468</v>
+        <v>2.10033202171326</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G324" t="n">
-        <v>2.00366377830505</v>
+        <v>2.00366401672363</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G325" t="n">
-        <v>1.94214797019958</v>
+        <v>1.9421478509903</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G327" t="n">
-        <v>1.91578388214111</v>
+        <v>1.9157840013504</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G328" t="n">
-        <v>1.88941991329193</v>
+        <v>1.88941979408264</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G329" t="n">
-        <v>2.00366377830505</v>
+        <v>2.00366401672363</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G330" t="n">
-        <v>2.03002762794495</v>
+        <v>2.03002786636353</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G331" t="n">
-        <v>1.99487555027008</v>
+        <v>1.99487566947937</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G332" t="n">
-        <v>1.99487555027008</v>
+        <v>1.99487566947937</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G333" t="n">
-        <v>1.99487555027008</v>
+        <v>1.99487566947937</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G334" t="n">
-        <v>2.03881597518921</v>
+        <v>2.03881573677063</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G335" t="n">
-        <v>2.00366377830505</v>
+        <v>2.00366401672363</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G337" t="n">
-        <v>2.10911965370178</v>
+        <v>2.10911989212036</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G340" t="n">
-        <v>2.03881597518921</v>
+        <v>2.03881573677063</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G341" t="n">
-        <v>2.0651798248291</v>
+        <v>2.06517958641052</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G342" t="n">
-        <v>2.0651798248291</v>
+        <v>2.06517958641052</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G343" t="n">
-        <v>2.0651798248291</v>
+        <v>2.06517958641052</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G344" t="n">
-        <v>1.95972394943237</v>
+        <v>1.95972383022308</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G345" t="n">
-        <v>2.01245188713074</v>
+        <v>2.01245164871216</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G346" t="n">
-        <v>2.00366377830505</v>
+        <v>2.00366401672363</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G348" t="n">
-        <v>1.9333598613739</v>
+        <v>1.93335962295532</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G351" t="n">
-        <v>1.83669185638428</v>
+        <v>1.83669173717499</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G352" t="n">
-        <v>1.81032752990723</v>
+        <v>1.81032764911652</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G353" t="n">
-        <v>1.88941991329193</v>
+        <v>1.88941979408264</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G354" t="n">
-        <v>1.85426771640778</v>
+        <v>1.85426783561707</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G356" t="n">
-        <v>2.01245188713074</v>
+        <v>2.01245164871216</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G358" t="n">
-        <v>2.03881597518921</v>
+        <v>2.03881573677063</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G359" t="n">
-        <v>2.03002762794495</v>
+        <v>2.03002786636353</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G360" t="n">
-        <v>2.03002762794495</v>
+        <v>2.03002786636353</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G361" t="n">
-        <v>1.99487555027008</v>
+        <v>1.99487566947937</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G362" t="n">
-        <v>1.99487555027008</v>
+        <v>1.99487566947937</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G364" t="n">
-        <v>2.00366377830505</v>
+        <v>2.00366401672363</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G365" t="n">
-        <v>2.00366377830505</v>
+        <v>2.00366401672363</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G366" t="n">
-        <v>1.9333598613739</v>
+        <v>1.93335962295532</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G367" t="n">
-        <v>1.9333598613739</v>
+        <v>1.93335962295532</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G368" t="n">
-        <v>2.01245188713074</v>
+        <v>2.01245164871216</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G370" t="n">
-        <v>1.9333598613739</v>
+        <v>1.93335962295532</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G371" t="n">
-        <v>1.9333598613739</v>
+        <v>1.93335962295532</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G373" t="n">
-        <v>1.95093584060669</v>
+        <v>1.9509357213974</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G375" t="n">
-        <v>1.85426771640778</v>
+        <v>1.85426783561707</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G379" t="n">
-        <v>1.9333598613739</v>
+        <v>1.93335962295532</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G380" t="n">
-        <v>1.62577998638153</v>
+        <v>1.62577974796295</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G381" t="n">
-        <v>1.74002397060394</v>
+        <v>1.74002385139465</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G386" t="n">
-        <v>1.99487555027008</v>
+        <v>1.99487566947937</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G388" t="n">
-        <v>1.99487555027008</v>
+        <v>1.99487566947937</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G390" t="n">
-        <v>1.9333598613739</v>
+        <v>1.93335962295532</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G395" t="n">
-        <v>1.99487555027008</v>
+        <v>1.99487566947937</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G396" t="n">
-        <v>2.01245188713074</v>
+        <v>2.01245164871216</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G397" t="n">
-        <v>2.0651798248291</v>
+        <v>2.06517958641052</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G401" t="n">
-        <v>2.01245188713074</v>
+        <v>2.01245164871216</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G403" t="n">
-        <v>1.9333598613739</v>
+        <v>1.93335962295532</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G409" t="n">
-        <v>1.88941991329193</v>
+        <v>1.88941979408264</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G410" t="n">
-        <v>1.88941991329193</v>
+        <v>1.88941979408264</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G411" t="n">
-        <v>1.87184393405914</v>
+        <v>1.87184369564056</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G414" t="n">
-        <v>1.83669185638428</v>
+        <v>1.83669173717499</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G415" t="n">
-        <v>1.81911587715149</v>
+        <v>1.8191157579422</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G416" t="n">
-        <v>1.81911587715149</v>
+        <v>1.8191157579422</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G418" t="n">
-        <v>1.81032752990723</v>
+        <v>1.81032764911652</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G419" t="n">
-        <v>1.91578388214111</v>
+        <v>1.9157840013504</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G421" t="n">
-        <v>1.91578388214111</v>
+        <v>1.9157840013504</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>2</v>
       </c>
       <c r="G423" t="n">
-        <v>1.75759971141815</v>
+        <v>1.75759983062744</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G425" t="n">
-        <v>1.74002397060394</v>
+        <v>1.74002385139465</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>2</v>
       </c>
       <c r="G426" t="n">
-        <v>1.75759971141815</v>
+        <v>1.75759983062744</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G427" t="n">
-        <v>1.76638793945312</v>
+        <v>1.76638782024384</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G428" t="n">
-        <v>1.76638793945312</v>
+        <v>1.76638782024384</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G429" t="n">
-        <v>1.76638793945312</v>
+        <v>1.76638782024384</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G430" t="n">
-        <v>1.76638793945312</v>
+        <v>1.76638782024384</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G437" t="n">
-        <v>1.85426771640778</v>
+        <v>1.85426783561707</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G438" t="n">
-        <v>1.85426771640778</v>
+        <v>1.85426783561707</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G439" t="n">
-        <v>1.81911587715149</v>
+        <v>1.8191157579422</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G440" t="n">
-        <v>1.81911587715149</v>
+        <v>1.8191157579422</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G443" t="n">
-        <v>1.82790374755859</v>
+        <v>1.82790386676788</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G445" t="n">
-        <v>1.82790374755859</v>
+        <v>1.82790386676788</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G446" t="n">
-        <v>1.82790374755859</v>
+        <v>1.82790386676788</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G447" t="n">
-        <v>1.76638793945312</v>
+        <v>1.76638782024384</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>2</v>
       </c>
       <c r="G450" t="n">
-        <v>1.75759971141815</v>
+        <v>1.75759983062744</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G451" t="n">
-        <v>1.74002397060394</v>
+        <v>1.74002385139465</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G452" t="n">
-        <v>1.72684192657471</v>
+        <v>1.72684180736542</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G453" t="n">
-        <v>1.68729567527771</v>
+        <v>1.687295794487</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G455" t="n">
-        <v>1.70926594734192</v>
+        <v>1.70926582813263</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G456" t="n">
-        <v>1.70926594734192</v>
+        <v>1.70926582813263</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G457" t="n">
-        <v>1.70926594734192</v>
+        <v>1.70926582813263</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G458" t="n">
-        <v>1.70926594734192</v>
+        <v>1.70926582813263</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G459" t="n">
-        <v>1.70926594734192</v>
+        <v>1.70926582813263</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G460" t="n">
-        <v>1.67411363124847</v>
+        <v>1.67411375045776</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G461" t="n">
-        <v>1.67411363124847</v>
+        <v>1.67411375045776</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G462" t="n">
-        <v>1.67411363124847</v>
+        <v>1.67411375045776</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G463" t="n">
-        <v>1.66093170642853</v>
+        <v>1.66093194484711</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G464" t="n">
-        <v>1.66093170642853</v>
+        <v>1.66093194484711</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G467" t="n">
-        <v>1.59502184391022</v>
+        <v>1.59502196311951</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G470" t="n">
-        <v>1.66093170642853</v>
+        <v>1.66093194484711</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G471" t="n">
-        <v>1.59502184391022</v>
+        <v>1.59502196311951</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G472" t="n">
-        <v>1.64335596561432</v>
+        <v>1.64335584640503</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G473" t="n">
-        <v>1.64335596561432</v>
+        <v>1.64335584640503</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G476" t="n">
-        <v>1.66532576084137</v>
+        <v>1.66532588005066</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G477" t="n">
-        <v>1.66532576084137</v>
+        <v>1.66532588005066</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G478" t="n">
-        <v>1.66532576084137</v>
+        <v>1.66532588005066</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G479" t="n">
-        <v>1.65653789043427</v>
+        <v>1.65653777122498</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G480" t="n">
-        <v>1.63017404079437</v>
+        <v>1.63017392158508</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G481" t="n">
-        <v>1.68729567527771</v>
+        <v>1.687295794487</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G482" t="n">
-        <v>1.67411363124847</v>
+        <v>1.67411375045776</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G483" t="n">
-        <v>1.64335596561432</v>
+        <v>1.64335584640503</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G484" t="n">
-        <v>1.74881184101105</v>
+        <v>1.74881172180176</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G485" t="n">
-        <v>1.81032752990723</v>
+        <v>1.81032764911652</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G486" t="n">
-        <v>1.87184393405914</v>
+        <v>1.87184369564056</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G487" t="n">
-        <v>1.9333598613739</v>
+        <v>1.93335962295532</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G489" t="n">
-        <v>2.00366377830505</v>
+        <v>2.00366401672363</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G490" t="n">
-        <v>2.03881597518921</v>
+        <v>2.03881573677063</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G491" t="n">
-        <v>2.03881597518921</v>
+        <v>2.03881573677063</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G492" t="n">
-        <v>1.99487555027008</v>
+        <v>1.99487566947937</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G496" t="n">
-        <v>1.9333598613739</v>
+        <v>1.93335962295532</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G497" t="n">
-        <v>1.82790374755859</v>
+        <v>1.82790386676788</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G499" t="n">
-        <v>1.78396368026733</v>
+        <v>1.78396391868591</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G500" t="n">
-        <v>1.78396368026733</v>
+        <v>1.78396391868591</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G501" t="n">
-        <v>1.78396368026733</v>
+        <v>1.78396391868591</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G502" t="n">
-        <v>1.74881184101105</v>
+        <v>1.74881172180176</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G503" t="n">
-        <v>1.74881184101105</v>
+        <v>1.74881172180176</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G504" t="n">
-        <v>1.74881184101105</v>
+        <v>1.74881172180176</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G507" t="n">
-        <v>1.78396368026733</v>
+        <v>1.78396391868591</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G508" t="n">
-        <v>1.78396368026733</v>
+        <v>1.78396391868591</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G509" t="n">
-        <v>1.78396368026733</v>
+        <v>1.78396391868591</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G512" t="n">
-        <v>1.78396368026733</v>
+        <v>1.78396391868591</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G513" t="n">
-        <v>1.81032752990723</v>
+        <v>1.81032764911652</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G514" t="n">
-        <v>1.78396368026733</v>
+        <v>1.78396391868591</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G515" t="n">
-        <v>1.78396368026733</v>
+        <v>1.78396391868591</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G519" t="n">
-        <v>1.76638793945312</v>
+        <v>1.76638782024384</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G520" t="n">
-        <v>1.79275190830231</v>
+        <v>1.79275178909302</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G521" t="n">
-        <v>1.81032752990723</v>
+        <v>1.81032764911652</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G522" t="n">
-        <v>1.76638793945312</v>
+        <v>1.76638782024384</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G524" t="n">
-        <v>1.70926594734192</v>
+        <v>1.70926582813263</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G525" t="n">
-        <v>1.62577998638153</v>
+        <v>1.62577974796295</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G526" t="n">
-        <v>1.54229378700256</v>
+        <v>1.54229390621185</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G527" t="n">
-        <v>1.50274789333344</v>
+        <v>1.50274777412415</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G528" t="n">
-        <v>1.50274789333344</v>
+        <v>1.50274777412415</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G530" t="n">
-        <v>1.48517179489136</v>
+        <v>1.48517191410065</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G534" t="n">
-        <v>1.48517179489136</v>
+        <v>1.48517191410065</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G535" t="n">
-        <v>1.48517179489136</v>
+        <v>1.48517191410065</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G536" t="n">
-        <v>1.50274789333344</v>
+        <v>1.50274777412415</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G537" t="n">
-        <v>1.50274789333344</v>
+        <v>1.50274777412415</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G538" t="n">
-        <v>1.55108177661896</v>
+        <v>1.55108189582825</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G539" t="n">
-        <v>1.55108177661896</v>
+        <v>1.55108189582825</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G544" t="n">
-        <v>1.52911186218262</v>
+        <v>1.52911174297333</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G551" t="n">
-        <v>1.72684192657471</v>
+        <v>1.72684180736542</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G552" t="n">
-        <v>1.73123586177826</v>
+        <v>1.73123598098755</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>2</v>
       </c>
       <c r="G554" t="n">
-        <v>1.75759971141815</v>
+        <v>1.75759983062744</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>2</v>
       </c>
       <c r="G555" t="n">
-        <v>1.75759971141815</v>
+        <v>1.75759983062744</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G558" t="n">
-        <v>1.72684192657471</v>
+        <v>1.72684180736542</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G559" t="n">
-        <v>1.72684192657471</v>
+        <v>1.72684180736542</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G566" t="n">
-        <v>1.62577998638153</v>
+        <v>1.62577974796295</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G567" t="n">
-        <v>1.62577998638153</v>
+        <v>1.62577974796295</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G568" t="n">
-        <v>1.62577998638153</v>
+        <v>1.62577974796295</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G571" t="n">
-        <v>1.66093170642853</v>
+        <v>1.66093194484711</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G572" t="n">
-        <v>1.67411363124847</v>
+        <v>1.67411375045776</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G581" t="n">
-        <v>1.68729567527771</v>
+        <v>1.687295794487</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G584" t="n">
-        <v>1.62577998638153</v>
+        <v>1.62577974796295</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G585" t="n">
-        <v>1.62577998638153</v>
+        <v>1.62577974796295</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G586" t="n">
-        <v>1.62577998638153</v>
+        <v>1.62577974796295</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G587" t="n">
-        <v>1.62577998638153</v>
+        <v>1.62577974796295</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G588" t="n">
-        <v>1.62577998638153</v>
+        <v>1.62577974796295</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G589" t="n">
-        <v>1.62577998638153</v>
+        <v>1.62577974796295</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G590" t="n">
-        <v>1.65653789043427</v>
+        <v>1.65653777122498</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G610" t="n">
-        <v>1.57744586467743</v>
+        <v>1.57744574546814</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G611" t="n">
-        <v>1.57744586467743</v>
+        <v>1.57744574546814</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G612" t="n">
-        <v>1.60820376873016</v>
+        <v>1.60820388793945</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G613" t="n">
-        <v>1.57744586467743</v>
+        <v>1.57744574546814</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G614" t="n">
-        <v>1.57744586467743</v>
+        <v>1.57744574546814</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G615" t="n">
-        <v>1.57744586467743</v>
+        <v>1.57744574546814</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G616" t="n">
-        <v>1.56865787506104</v>
+        <v>1.56865775585175</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G625" t="n">
-        <v>1.70047771930695</v>
+        <v>1.70047783851624</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G626" t="n">
-        <v>1.70047771930695</v>
+        <v>1.70047783851624</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G627" t="n">
-        <v>2.00366377830505</v>
+        <v>2.00366401672363</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G630" t="n">
-        <v>1.88941991329193</v>
+        <v>1.88941979408264</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G631" t="n">
-        <v>1.81032752990723</v>
+        <v>1.81032764911652</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G633" t="n">
-        <v>1.81911587715149</v>
+        <v>1.8191157579422</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G634" t="n">
-        <v>1.81032752990723</v>
+        <v>1.81032764911652</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G639" t="n">
-        <v>1.64335596561432</v>
+        <v>1.64335584640503</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G640" t="n">
-        <v>1.60820376873016</v>
+        <v>1.60820388793945</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G641" t="n">
-        <v>1.62577998638153</v>
+        <v>1.62577974796295</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G644" t="n">
-        <v>1.66093170642853</v>
+        <v>1.66093194484711</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G645" t="n">
-        <v>1.66093170642853</v>
+        <v>1.66093194484711</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G647" t="n">
-        <v>1.66532576084137</v>
+        <v>1.66532588005066</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>2</v>
       </c>
       <c r="G649" t="n">
-        <v>1.75759971141815</v>
+        <v>1.75759983062744</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G650" t="n">
-        <v>1.74881184101105</v>
+        <v>1.74881172180176</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G654" t="n">
-        <v>1.74002397060394</v>
+        <v>1.74002385139465</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G655" t="n">
-        <v>1.74002397060394</v>
+        <v>1.74002385139465</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>2</v>
       </c>
       <c r="G656" t="n">
-        <v>1.75759971141815</v>
+        <v>1.75759983062744</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G657" t="n">
-        <v>1.70487189292908</v>
+        <v>1.70487177371979</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G658" t="n">
-        <v>1.79275190830231</v>
+        <v>1.79275178909302</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>2</v>
       </c>
       <c r="G659" t="n">
-        <v>1.75759971141815</v>
+        <v>1.75759983062744</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G660" t="n">
-        <v>1.73123586177826</v>
+        <v>1.73123598098755</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G661" t="n">
-        <v>1.78719866275787</v>
+        <v>1.78719854354858</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G662" t="n">
-        <v>1.70596218109131</v>
+        <v>1.7059623003006</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G663" t="n">
-        <v>1.70596218109131</v>
+        <v>1.7059623003006</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G666" t="n">
-        <v>1.73304092884064</v>
+        <v>1.73304104804993</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G667" t="n">
-        <v>1.70596218109131</v>
+        <v>1.7059623003006</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G669" t="n">
-        <v>1.66985738277435</v>
+        <v>1.66985726356506</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G681" t="n">
-        <v>1.62472593784332</v>
+        <v>1.62472605705261</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G682" t="n">
-        <v>1.62472593784332</v>
+        <v>1.62472605705261</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G683" t="n">
-        <v>1.62472593784332</v>
+        <v>1.62472605705261</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G684" t="n">
-        <v>1.59764719009399</v>
+        <v>1.5976470708847</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>1.75</v>
       </c>
       <c r="G689" t="n">
-        <v>1.57959461212158</v>
+        <v>1.57959473133087</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>1.75</v>
       </c>
       <c r="G696" t="n">
-        <v>1.57959461212158</v>
+        <v>1.57959473133087</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G701" t="n">
-        <v>1.59764719009399</v>
+        <v>1.5976470708847</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G702" t="n">
-        <v>1.59764719009399</v>
+        <v>1.5976470708847</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G703" t="n">
-        <v>1.59764719009399</v>
+        <v>1.5976470708847</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G704" t="n">
-        <v>1.59764719009399</v>
+        <v>1.5976470708847</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G706" t="n">
-        <v>1.59764719009399</v>
+        <v>1.5976470708847</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G710" t="n">
-        <v>1.51641082763672</v>
+        <v>1.51641094684601</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>1.75</v>
       </c>
       <c r="G716" t="n">
-        <v>1.57959461212158</v>
+        <v>1.57959473133087</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>1.75</v>
       </c>
       <c r="G717" t="n">
-        <v>1.57959461212158</v>
+        <v>1.57959473133087</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>1.75</v>
       </c>
       <c r="G729" t="n">
-        <v>1.57959461212158</v>
+        <v>1.57959473133087</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>1.75</v>
       </c>
       <c r="G730" t="n">
-        <v>1.57959461212158</v>
+        <v>1.57959473133087</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G738" t="n">
-        <v>1.52543711662292</v>
+        <v>1.52543723583221</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G739" t="n">
-        <v>1.52543711662292</v>
+        <v>1.52543723583221</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G740" t="n">
-        <v>1.52543711662292</v>
+        <v>1.52543723583221</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G753" t="n">
-        <v>1.4983583688736</v>
+        <v>1.49835824966431</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G756" t="n">
-        <v>1.51641082763672</v>
+        <v>1.51641094684601</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G765" t="n">
-        <v>1.51641082763672</v>
+        <v>1.51641094684601</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G766" t="n">
-        <v>1.48030591011047</v>
+        <v>1.48030579090118</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G768" t="n">
-        <v>1.51641082763672</v>
+        <v>1.51641094684601</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>1.75</v>
       </c>
       <c r="G770" t="n">
-        <v>1.57959461212158</v>
+        <v>1.57959473133087</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>1.75</v>
       </c>
       <c r="G771" t="n">
-        <v>1.57959461212158</v>
+        <v>1.57959473133087</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>1.75</v>
       </c>
       <c r="G772" t="n">
-        <v>1.57959461212158</v>
+        <v>1.57959473133087</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G776" t="n">
-        <v>1.51641082763672</v>
+        <v>1.51641094684601</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G777" t="n">
-        <v>1.51641082763672</v>
+        <v>1.51641094684601</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G779" t="n">
-        <v>1.48030591011047</v>
+        <v>1.48030579090118</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G781" t="n">
-        <v>1.41712212562561</v>
+        <v>1.4171222448349</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G784" t="n">
-        <v>1.4983583688736</v>
+        <v>1.49835824966431</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G785" t="n">
-        <v>1.51641082763672</v>
+        <v>1.51641094684601</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G786" t="n">
-        <v>1.51641082763672</v>
+        <v>1.51641094684601</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G787" t="n">
-        <v>1.51641082763672</v>
+        <v>1.51641094684601</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G788" t="n">
-        <v>1.48030591011047</v>
+        <v>1.48030579090118</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G789" t="n">
-        <v>1.48030591011047</v>
+        <v>1.48030579090118</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G794" t="n">
-        <v>1.98577630519867</v>
+        <v>1.98577618598938</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G795" t="n">
-        <v>1.87746107578278</v>
+        <v>1.87746095657349</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G796" t="n">
-        <v>1.66985738277435</v>
+        <v>1.66985726356506</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G799" t="n">
-        <v>1.77817237377167</v>
+        <v>1.77817225456238</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G801" t="n">
-        <v>1.78719866275787</v>
+        <v>1.78719854354858</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G804" t="n">
-        <v>1.87746107578278</v>
+        <v>1.87746095657349</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G805" t="n">
-        <v>1.85940837860107</v>
+        <v>1.85940849781036</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G806" t="n">
-        <v>1.89551365375519</v>
+        <v>1.8955135345459</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G807" t="n">
-        <v>1.85940837860107</v>
+        <v>1.85940849781036</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G808" t="n">
-        <v>1.87746107578278</v>
+        <v>1.87746095657349</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G809" t="n">
-        <v>1.85940837860107</v>
+        <v>1.85940849781036</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G810" t="n">
-        <v>1.85940837860107</v>
+        <v>1.85940849781036</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G812" t="n">
-        <v>1.87746107578278</v>
+        <v>1.87746095657349</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G813" t="n">
-        <v>1.91356611251831</v>
+        <v>1.9135662317276</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G814" t="n">
-        <v>1.87746107578278</v>
+        <v>1.87746095657349</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G818" t="n">
-        <v>1.70596218109131</v>
+        <v>1.7059623003006</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G821" t="n">
-        <v>1.73304092884064</v>
+        <v>1.73304104804993</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G822" t="n">
-        <v>1.77817237377167</v>
+        <v>1.77817225456238</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G827" t="n">
-        <v>1.73304092884064</v>
+        <v>1.73304104804993</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G828" t="n">
-        <v>1.72401475906372</v>
+        <v>1.72401487827301</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G829" t="n">
-        <v>1.72401475906372</v>
+        <v>1.72401487827301</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G832" t="n">
-        <v>1.77817237377167</v>
+        <v>1.77817225456238</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G834" t="n">
-        <v>1.73304092884064</v>
+        <v>1.73304104804993</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G837" t="n">
-        <v>1.77817237377167</v>
+        <v>1.77817225456238</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G840" t="n">
-        <v>1.78719866275787</v>
+        <v>1.78719854354858</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G841" t="n">
-        <v>1.78719866275787</v>
+        <v>1.78719854354858</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G842" t="n">
-        <v>1.72401475906372</v>
+        <v>1.72401487827301</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>2</v>
       </c>
       <c r="G846" t="n">
-        <v>1.80525100231171</v>
+        <v>1.805251121521</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>2</v>
       </c>
       <c r="G847" t="n">
-        <v>1.80525100231171</v>
+        <v>1.805251121521</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>2</v>
       </c>
       <c r="G848" t="n">
-        <v>1.80525100231171</v>
+        <v>1.805251121521</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G850" t="n">
-        <v>1.77817237377167</v>
+        <v>1.77817225456238</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G851" t="n">
-        <v>1.73304092884064</v>
+        <v>1.73304104804993</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G852" t="n">
-        <v>1.77817237377167</v>
+        <v>1.77817225456238</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G853" t="n">
-        <v>1.77817237377167</v>
+        <v>1.77817225456238</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G857" t="n">
-        <v>1.78719866275787</v>
+        <v>1.78719854354858</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G858" t="n">
-        <v>1.78719866275787</v>
+        <v>1.78719854354858</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G860" t="n">
-        <v>1.78719866275787</v>
+        <v>1.78719854354858</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>2</v>
       </c>
       <c r="G861" t="n">
-        <v>1.80525100231171</v>
+        <v>1.805251121521</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G862" t="n">
-        <v>1.78719866275787</v>
+        <v>1.78719854354858</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>2</v>
       </c>
       <c r="G864" t="n">
-        <v>1.80525100231171</v>
+        <v>1.805251121521</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G866" t="n">
-        <v>1.87746107578278</v>
+        <v>1.87746095657349</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G867" t="n">
-        <v>1.91356611251831</v>
+        <v>1.9135662317276</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G868" t="n">
-        <v>1.98577630519867</v>
+        <v>1.98577618598938</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G869" t="n">
-        <v>1.98577630519867</v>
+        <v>1.98577618598938</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G871" t="n">
-        <v>2.07603859901428</v>
+        <v>2.07603883743286</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G874" t="n">
-        <v>1.98577630519867</v>
+        <v>1.98577618598938</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G876" t="n">
-        <v>2.00382876396179</v>
+        <v>2.00382852554321</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G883" t="n">
-        <v>1.98577630519867</v>
+        <v>1.98577618598938</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G884" t="n">
-        <v>2.07603859901428</v>
+        <v>2.07603883743286</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G885" t="n">
-        <v>2.20240640640259</v>
+        <v>2.20240616798401</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G886" t="n">
-        <v>2.16630125045776</v>
+        <v>2.16630148887634</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G887" t="n">
-        <v>2.16630125045776</v>
+        <v>2.16630148887634</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G888" t="n">
-        <v>2.16630125045776</v>
+        <v>2.16630148887634</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>2.5</v>
       </c>
       <c r="G889" t="n">
-        <v>2.25656390190125</v>
+        <v>2.25656414031982</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G890" t="n">
-        <v>2.20240640640259</v>
+        <v>2.20240616798401</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G892" t="n">
-        <v>2.07603859901428</v>
+        <v>2.07603883743286</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G893" t="n">
-        <v>2.07603859901428</v>
+        <v>2.07603883743286</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G895" t="n">
-        <v>1.85940837860107</v>
+        <v>1.85940849781036</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G897" t="n">
-        <v>1.91356611251831</v>
+        <v>1.9135662317276</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G898" t="n">
-        <v>1.87746107578278</v>
+        <v>1.87746095657349</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G899" t="n">
-        <v>1.85940837860107</v>
+        <v>1.85940849781036</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G900" t="n">
-        <v>1.87746107578278</v>
+        <v>1.87746095657349</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G901" t="n">
-        <v>1.85940837860107</v>
+        <v>1.85940849781036</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G903" t="n">
-        <v>1.91356611251831</v>
+        <v>1.9135662317276</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G906" t="n">
-        <v>1.91356611251831</v>
+        <v>1.9135662317276</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G909" t="n">
-        <v>1.85940837860107</v>
+        <v>1.85940849781036</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G911" t="n">
-        <v>1.87746107578278</v>
+        <v>1.87746095657349</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G912" t="n">
-        <v>1.85940837860107</v>
+        <v>1.85940849781036</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G913" t="n">
-        <v>1.85940837860107</v>
+        <v>1.85940849781036</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G914" t="n">
-        <v>1.89551365375519</v>
+        <v>1.8955135345459</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G915" t="n">
-        <v>1.87746107578278</v>
+        <v>1.87746095657349</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G916" t="n">
-        <v>1.87746107578278</v>
+        <v>1.87746095657349</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G917" t="n">
-        <v>1.85940837860107</v>
+        <v>1.85940849781036</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G920" t="n">
-        <v>1.89470195770264</v>
+        <v>1.89470207691193</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G921" t="n">
-        <v>1.89470195770264</v>
+        <v>1.89470207691193</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G922" t="n">
-        <v>1.89470195770264</v>
+        <v>1.89470207691193</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G923" t="n">
-        <v>1.82968783378601</v>
+        <v>1.82968771457672</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G924" t="n">
-        <v>1.773961186409</v>
+        <v>1.77396130561829</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G926" t="n">
-        <v>1.81111240386963</v>
+        <v>1.81111228466034</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G927" t="n">
-        <v>1.81111240386963</v>
+        <v>1.81111228466034</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G928" t="n">
-        <v>1.81111240386963</v>
+        <v>1.81111228466034</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G936" t="n">
-        <v>1.81111240386963</v>
+        <v>1.81111228466034</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G937" t="n">
-        <v>1.81111240386963</v>
+        <v>1.81111228466034</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G940" t="n">
-        <v>1.78324890136719</v>
+        <v>1.78324902057648</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G941" t="n">
-        <v>1.78324890136719</v>
+        <v>1.78324902057648</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G943" t="n">
-        <v>1.81111240386963</v>
+        <v>1.81111228466034</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G944" t="n">
-        <v>1.773961186409</v>
+        <v>1.77396130561829</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G945" t="n">
-        <v>1.773961186409</v>
+        <v>1.77396130561829</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G946" t="n">
-        <v>1.773961186409</v>
+        <v>1.77396130561829</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G947" t="n">
-        <v>1.78324890136719</v>
+        <v>1.78324902057648</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G950" t="n">
-        <v>1.78324890136719</v>
+        <v>1.78324902057648</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G951" t="n">
-        <v>1.78324890136719</v>
+        <v>1.78324902057648</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G957" t="n">
-        <v>1.78324890136719</v>
+        <v>1.78324902057648</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G958" t="n">
-        <v>1.78324890136719</v>
+        <v>1.78324902057648</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G959" t="n">
-        <v>1.78324890136719</v>
+        <v>1.78324902057648</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G960" t="n">
-        <v>1.75538563728333</v>
+        <v>1.75538575649261</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G961" t="n">
-        <v>1.78324890136719</v>
+        <v>1.78324902057648</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G965" t="n">
-        <v>1.78324890136719</v>
+        <v>1.78324902057648</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G966" t="n">
-        <v>1.78324890136719</v>
+        <v>1.78324902057648</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G974" t="n">
-        <v>1.82040011882782</v>
+        <v>1.82039999961853</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G975" t="n">
-        <v>1.82040011882782</v>
+        <v>1.82039999961853</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G976" t="n">
-        <v>1.82040011882782</v>
+        <v>1.82039999961853</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G977" t="n">
-        <v>1.773961186409</v>
+        <v>1.77396130561829</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G981" t="n">
-        <v>1.78324890136719</v>
+        <v>1.78324902057648</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G982" t="n">
-        <v>1.78324890136719</v>
+        <v>1.78324902057648</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G983" t="n">
-        <v>1.78324890136719</v>
+        <v>1.78324902057648</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G985" t="n">
-        <v>1.78324890136719</v>
+        <v>1.78324902057648</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G987" t="n">
-        <v>1.81111240386963</v>
+        <v>1.81111228466034</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G988" t="n">
-        <v>1.82040011882782</v>
+        <v>1.82039999961853</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G989" t="n">
-        <v>1.78324890136719</v>
+        <v>1.78324902057648</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G992" t="n">
-        <v>1.75538563728333</v>
+        <v>1.75538575649261</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G993" t="n">
-        <v>1.75538563728333</v>
+        <v>1.75538575649261</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G994" t="n">
-        <v>1.773961186409</v>
+        <v>1.77396130561829</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G995" t="n">
-        <v>1.773961186409</v>
+        <v>1.77396130561829</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1009" t="n">
-        <v>1.773961186409</v>
+        <v>1.77396130561829</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1010" t="n">
-        <v>1.773961186409</v>
+        <v>1.77396130561829</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.773961186409</v>
+        <v>1.77396130561829</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1013" t="n">
-        <v>1.773961186409</v>
+        <v>1.77396130561829</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1017" t="n">
-        <v>1.773961186409</v>
+        <v>1.77396130561829</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1018" t="n">
-        <v>1.773961186409</v>
+        <v>1.77396130561829</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1019" t="n">
-        <v>1.773961186409</v>
+        <v>1.77396130561829</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1034" t="n">
-        <v>1.75538563728333</v>
+        <v>1.75538575649261</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.81111240386963</v>
+        <v>1.81111228466034</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.78324890136719</v>
+        <v>1.78324902057648</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1044" t="n">
-        <v>1.773961186409</v>
+        <v>1.77396130561829</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1045" t="n">
-        <v>1.75538563728333</v>
+        <v>1.75538575649261</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1046" t="n">
-        <v>1.773961186409</v>
+        <v>1.77396130561829</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1047" t="n">
-        <v>1.773961186409</v>
+        <v>1.77396130561829</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1050" t="n">
-        <v>1.75538563728333</v>
+        <v>1.75538575649261</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1051" t="n">
-        <v>1.773961186409</v>
+        <v>1.77396130561829</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1062" t="n">
-        <v>1.70894706249237</v>
+        <v>1.70894694328308</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1096" t="n">
-        <v>1.60678160190582</v>
+        <v>1.60678172111511</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1098" t="n">
-        <v>1.78324890136719</v>
+        <v>1.78324902057648</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1099" t="n">
-        <v>1.773961186409</v>
+        <v>1.77396130561829</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1100" t="n">
-        <v>1.75538563728333</v>
+        <v>1.75538575649261</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1109" t="n">
-        <v>1.70894706249237</v>
+        <v>1.70894694328308</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1131" t="n">
-        <v>1.70894706249237</v>
+        <v>1.70894694328308</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1134" t="n">
-        <v>1.70894706249237</v>
+        <v>1.70894694328308</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1135" t="n">
-        <v>1.70894706249237</v>
+        <v>1.70894694328308</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1158" t="n">
-        <v>1.65322029590607</v>
+        <v>1.65322041511536</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1166" t="n">
-        <v>1.54176735877991</v>
+        <v>1.54176723957062</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1167" t="n">
-        <v>1.54176735877991</v>
+        <v>1.54176723957062</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1168" t="n">
-        <v>1.54176735877991</v>
+        <v>1.54176723957062</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -40412,6 +40412,32 @@
         <v>1.64999997615814</v>
       </c>
       <c r="H1540" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1541">
+      <c r="A1541" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1541" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C1541" t="n">
+        <v>1.63999998569489</v>
+      </c>
+      <c r="D1541" t="n">
+        <v>1.62000000476837</v>
+      </c>
+      <c r="E1541" t="n">
+        <v>1.62999999523163</v>
+      </c>
+      <c r="F1541" t="n">
+        <v>1.63999998569489</v>
+      </c>
+      <c r="G1541" t="n">
+        <v>1.63999998569489</v>
+      </c>
+      <c r="H1541" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RETI.MI.xlsx
+++ b/data/RETI.MI.xlsx
@@ -35831,7 +35831,9 @@
       <c r="E1542" t="n">
         <v>1.61000001430511</v>
       </c>
-      <c r="F1542"/>
+      <c r="F1542" t="n">
+        <v>1.62999999523163</v>
+      </c>
       <c r="G1542" t="s">
         <v>7</v>
       </c>

--- a/data/RETI.MI.xlsx
+++ b/data/RETI.MI.xlsx
@@ -35838,6 +35838,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1543">
+      <c r="A1543" s="1" t="n">
+        <v>46297.2916666667</v>
+      </c>
+      <c r="B1543" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1543" t="n">
+        <v>1.62999999523163</v>
+      </c>
+      <c r="D1543" t="n">
+        <v>1.62999999523163</v>
+      </c>
+      <c r="E1543" t="n">
+        <v>1.62999999523163</v>
+      </c>
+      <c r="F1543" t="n">
+        <v>1.62999999523163</v>
+      </c>
+      <c r="G1543" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1544">
+      <c r="A1544" s="1" t="n">
+        <v>46300.2916666667</v>
+      </c>
+      <c r="B1544" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C1544" t="n">
+        <v>1.62999999523163</v>
+      </c>
+      <c r="D1544" t="n">
+        <v>1.60000002384186</v>
+      </c>
+      <c r="E1544" t="n">
+        <v>1.60000002384186</v>
+      </c>
+      <c r="F1544"/>
+      <c r="G1544" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RETI.MI.xlsx
+++ b/data/RETI.MI.xlsx
@@ -35877,7 +35877,9 @@
       <c r="E1544" t="n">
         <v>1.60000002384186</v>
       </c>
-      <c r="F1544"/>
+      <c r="F1544" t="n">
+        <v>1.62999999523163</v>
+      </c>
       <c r="G1544" t="s">
         <v>7</v>
       </c>

--- a/data/RETI.MI.xlsx
+++ b/data/RETI.MI.xlsx
@@ -35884,6 +35884,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1545">
+      <c r="A1545" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1545" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1545" t="n">
+        <v>1.62999999523163</v>
+      </c>
+      <c r="D1545" t="n">
+        <v>1.62999999523163</v>
+      </c>
+      <c r="E1545" t="n">
+        <v>1.62999999523163</v>
+      </c>
+      <c r="F1545" t="n">
+        <v>1.62999999523163</v>
+      </c>
+      <c r="G1545" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1546">
+      <c r="A1546" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1546" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C1546" t="n">
+        <v>1.62000000476837</v>
+      </c>
+      <c r="D1546" t="n">
+        <v>1.62000000476837</v>
+      </c>
+      <c r="E1546" t="n">
+        <v>1.62000000476837</v>
+      </c>
+      <c r="F1546"/>
+      <c r="G1546" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RETI.MI.xlsx
+++ b/data/RETI.MI.xlsx
@@ -35923,8 +35923,31 @@
       <c r="E1546" t="n">
         <v>1.62000000476837</v>
       </c>
-      <c r="F1546"/>
+      <c r="F1546" t="n">
+        <v>1.62000000476837</v>
+      </c>
       <c r="G1546" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1547">
+      <c r="A1547" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1547" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C1547" t="n">
+        <v>1.58000004291534</v>
+      </c>
+      <c r="D1547" t="n">
+        <v>1.58000004291534</v>
+      </c>
+      <c r="E1547" t="n">
+        <v>1.58000004291534</v>
+      </c>
+      <c r="F1547"/>
+      <c r="G1547" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RETI.MI.xlsx
+++ b/data/RETI.MI.xlsx
@@ -35946,8 +35946,31 @@
       <c r="E1547" t="n">
         <v>1.58000004291534</v>
       </c>
-      <c r="F1547"/>
+      <c r="F1547" t="n">
+        <v>1.58000004291534</v>
+      </c>
       <c r="G1547" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1548">
+      <c r="A1548" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1548" t="n">
+        <v>9000</v>
+      </c>
+      <c r="C1548" t="n">
+        <v>1.58000004291534</v>
+      </c>
+      <c r="D1548" t="n">
+        <v>1.53999996185303</v>
+      </c>
+      <c r="E1548" t="n">
+        <v>1.54999995231628</v>
+      </c>
+      <c r="F1548"/>
+      <c r="G1548" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RETI.MI.xlsx
+++ b/data/RETI.MI.xlsx
@@ -35976,6 +35976,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1549">
+      <c r="A1549" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1549" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C1549" t="n">
+        <v>1.60000002384186</v>
+      </c>
+      <c r="D1549" t="n">
+        <v>1.54999995231628</v>
+      </c>
+      <c r="E1549" t="n">
+        <v>1.54999995231628</v>
+      </c>
+      <c r="F1549" t="n">
+        <v>1.60000002384186</v>
+      </c>
+      <c r="G1549" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RETI.MI.xlsx
+++ b/data/RETI.MI.xlsx
@@ -421,7 +421,7 @@
         <v>0.889900028705597</v>
       </c>
       <c r="G2" t="n">
-        <v>0.759858369827271</v>
+        <v>0.759858429431915</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>0.899600028991699</v>
       </c>
       <c r="G3" t="n">
-        <v>0.768140971660614</v>
+        <v>0.768140912055969</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G13" t="n">
-        <v>0.691634237766266</v>
+        <v>0.691634178161621</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G16" t="n">
-        <v>0.666018187999725</v>
+        <v>0.666018128395081</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G22" t="n">
-        <v>0.659187197685242</v>
+        <v>0.659187257289886</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G23" t="n">
-        <v>0.666018187999725</v>
+        <v>0.666018128395081</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G29" t="n">
-        <v>0.623324692249298</v>
+        <v>0.623324632644653</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G30" t="n">
-        <v>0.607955038547516</v>
+        <v>0.607955098152161</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G31" t="n">
-        <v>0.587462186813354</v>
+        <v>0.58746212720871</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G36" t="n">
-        <v>0.563553929328918</v>
+        <v>0.563553869724274</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G39" t="n">
-        <v>0.525983572006226</v>
+        <v>0.525983512401581</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G43" t="n">
-        <v>0.623324692249298</v>
+        <v>0.623324632644653</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G45" t="n">
-        <v>0.618201434612274</v>
+        <v>0.618201494216919</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G47" t="n">
-        <v>0.607955038547516</v>
+        <v>0.607955098152161</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G49" t="n">
-        <v>0.614786088466644</v>
+        <v>0.614786028862</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G51" t="n">
-        <v>0.614786088466644</v>
+        <v>0.614786028862</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G63" t="n">
-        <v>0.679680109024048</v>
+        <v>0.679680049419403</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G74" t="n">
-        <v>0.691634237766266</v>
+        <v>0.691634178161621</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G76" t="n">
-        <v>0.707003951072693</v>
+        <v>0.707003891468048</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G98" t="n">
-        <v>0.666018187999725</v>
+        <v>0.666018128395081</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G100" t="n">
-        <v>0.676264584064484</v>
+        <v>0.676264643669128</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G101" t="n">
-        <v>0.676264584064484</v>
+        <v>0.676264643669128</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G103" t="n">
-        <v>0.707003951072693</v>
+        <v>0.707003891468048</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G107" t="n">
-        <v>0.691634237766266</v>
+        <v>0.691634178161621</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G112" t="n">
-        <v>0.686511039733887</v>
+        <v>0.686511099338531</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G113" t="n">
-        <v>0.691634237766266</v>
+        <v>0.691634178161621</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>0.867999970912933</v>
       </c>
       <c r="G120" t="n">
-        <v>0.741158664226532</v>
+        <v>0.741158604621887</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>0.867999970912933</v>
       </c>
       <c r="G121" t="n">
-        <v>0.741158664226532</v>
+        <v>0.741158604621887</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>0.972000002861023</v>
       </c>
       <c r="G123" t="n">
-        <v>0.829961061477661</v>
+        <v>0.829961121082306</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>1</v>
       </c>
       <c r="G127" t="n">
-        <v>0.853869378566742</v>
+        <v>0.853869438171387</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G128" t="n">
-        <v>0.862408101558685</v>
+        <v>0.86240816116333</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G129" t="n">
-        <v>0.862408101558685</v>
+        <v>0.86240816116333</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G130" t="n">
-        <v>0.862408101558685</v>
+        <v>0.86240816116333</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G135" t="n">
-        <v>0.866677522659302</v>
+        <v>0.866677463054657</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G136" t="n">
-        <v>0.900832176208496</v>
+        <v>0.900832235813141</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G138" t="n">
-        <v>0.892293453216553</v>
+        <v>0.892293512821198</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G139" t="n">
-        <v>0.913640439510345</v>
+        <v>0.913640379905701</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G142" t="n">
-        <v>0.913640439510345</v>
+        <v>0.913640379905701</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G143" t="n">
-        <v>0.930717706680298</v>
+        <v>0.930717766284943</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G147" t="n">
-        <v>1.20395588874817</v>
+        <v>1.20395600795746</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G152" t="n">
-        <v>1.22153186798096</v>
+        <v>1.22153174877167</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G153" t="n">
-        <v>1.22153186798096</v>
+        <v>1.22153174877167</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G157" t="n">
-        <v>1.13365185260773</v>
+        <v>1.13365197181702</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>1.25499999523163</v>
       </c>
       <c r="G159" t="n">
-        <v>1.10289394855499</v>
+        <v>1.1028938293457</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G160" t="n">
-        <v>1.05456006526947</v>
+        <v>1.05455994606018</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G163" t="n">
-        <v>1.13365185260773</v>
+        <v>1.13365197181702</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G166" t="n">
-        <v>1.16001605987549</v>
+        <v>1.1600159406662</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G174" t="n">
-        <v>1.18198597431183</v>
+        <v>1.18198585510254</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>1.49500000476837</v>
       </c>
       <c r="G178" t="n">
-        <v>1.31380593776703</v>
+        <v>1.31380581855774</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>1.5</v>
       </c>
       <c r="G182" t="n">
-        <v>1.31819987297058</v>
+        <v>1.31819975376129</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G183" t="n">
-        <v>1.283047914505</v>
+        <v>1.28304779529572</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>1.5</v>
       </c>
       <c r="G185" t="n">
-        <v>1.31819987297058</v>
+        <v>1.31819975376129</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>1.5</v>
       </c>
       <c r="G186" t="n">
-        <v>1.31819987297058</v>
+        <v>1.31819975376129</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G191" t="n">
-        <v>1.38410985469818</v>
+        <v>1.38410997390747</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G195" t="n">
-        <v>1.34456384181976</v>
+        <v>1.34456396102905</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G198" t="n">
-        <v>1.32698786258698</v>
+        <v>1.32698774337769</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>1.49500000476837</v>
       </c>
       <c r="G199" t="n">
-        <v>1.31380593776703</v>
+        <v>1.31380581855774</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>1.5</v>
       </c>
       <c r="G201" t="n">
-        <v>1.31819987297058</v>
+        <v>1.31819975376129</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>1.5</v>
       </c>
       <c r="G202" t="n">
-        <v>1.31819987297058</v>
+        <v>1.31819975376129</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>1.5</v>
       </c>
       <c r="G203" t="n">
-        <v>1.31819987297058</v>
+        <v>1.31819975376129</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G206" t="n">
-        <v>1.34456384181976</v>
+        <v>1.34456396102905</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G207" t="n">
-        <v>1.34456384181976</v>
+        <v>1.34456396102905</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G215" t="n">
-        <v>1.32698786258698</v>
+        <v>1.32698774337769</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>1.5</v>
       </c>
       <c r="G216" t="n">
-        <v>1.31819987297058</v>
+        <v>1.31819975376129</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G220" t="n">
-        <v>1.26547205448151</v>
+        <v>1.26547193527222</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G221" t="n">
-        <v>1.28744196891785</v>
+        <v>1.28744184970856</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>1.5</v>
       </c>
       <c r="G224" t="n">
-        <v>1.31819987297058</v>
+        <v>1.31819975376129</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>1.5</v>
       </c>
       <c r="G225" t="n">
-        <v>1.31819987297058</v>
+        <v>1.31819975376129</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>1.5</v>
       </c>
       <c r="G227" t="n">
-        <v>1.31819987297058</v>
+        <v>1.31819975376129</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G231" t="n">
-        <v>1.283047914505</v>
+        <v>1.28304779529572</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G232" t="n">
-        <v>1.34456384181976</v>
+        <v>1.34456396102905</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G235" t="n">
-        <v>1.34456384181976</v>
+        <v>1.34456396102905</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>1.49500000476837</v>
       </c>
       <c r="G237" t="n">
-        <v>1.31380593776703</v>
+        <v>1.31380581855774</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G238" t="n">
-        <v>1.36653399467468</v>
+        <v>1.3665337562561</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G240" t="n">
-        <v>1.74881184101105</v>
+        <v>1.74881172180176</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G243" t="n">
-        <v>2.23215174674988</v>
+        <v>2.2321515083313</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G244" t="n">
-        <v>2.52215576171875</v>
+        <v>2.52215552330017</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G245" t="n">
-        <v>2.39912366867065</v>
+        <v>2.39912390708923</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G249" t="n">
-        <v>2.20578789710999</v>
+        <v>2.20578765869141</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G250" t="n">
-        <v>2.23215174674988</v>
+        <v>2.2321515083313</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G251" t="n">
-        <v>2.18821167945862</v>
+        <v>2.1882119178772</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G252" t="n">
-        <v>2.18821167945862</v>
+        <v>2.1882119178772</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G254" t="n">
-        <v>2.34639573097229</v>
+        <v>2.34639596939087</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G264" t="n">
-        <v>2.20578789710999</v>
+        <v>2.20578765869141</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G265" t="n">
-        <v>2.34639573097229</v>
+        <v>2.34639596939087</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G269" t="n">
-        <v>2.31124401092529</v>
+        <v>2.31124377250671</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G270" t="n">
-        <v>2.23215174674988</v>
+        <v>2.2321515083313</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G279" t="n">
-        <v>2.32003211975098</v>
+        <v>2.3200318813324</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G284" t="n">
-        <v>2.32003211975098</v>
+        <v>2.3200318813324</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G286" t="n">
-        <v>2.26730370521545</v>
+        <v>2.26730394363403</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G289" t="n">
-        <v>2.32003211975098</v>
+        <v>2.3200318813324</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G295" t="n">
-        <v>2.26730370521545</v>
+        <v>2.26730394363403</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G296" t="n">
-        <v>2.23215174674988</v>
+        <v>2.2321515083313</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G300" t="n">
-        <v>2.20578789710999</v>
+        <v>2.20578765869141</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>2.25</v>
       </c>
       <c r="G305" t="n">
-        <v>1.97729980945587</v>
+        <v>1.97729992866516</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G306" t="n">
-        <v>1.99487602710724</v>
+        <v>1.99487578868866</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>2.25</v>
       </c>
       <c r="G307" t="n">
-        <v>1.97729980945587</v>
+        <v>1.97729992866516</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G310" t="n">
-        <v>1.8366916179657</v>
+        <v>1.83669173717499</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>2.25</v>
       </c>
       <c r="G315" t="n">
-        <v>1.97729980945587</v>
+        <v>1.97729992866516</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G322" t="n">
-        <v>2.10033202171326</v>
+        <v>2.10033178329468</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G323" t="n">
-        <v>2.10033202171326</v>
+        <v>2.10033178329468</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G325" t="n">
-        <v>1.94214797019958</v>
+        <v>1.94214773178101</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>2.25</v>
       </c>
       <c r="G326" t="n">
-        <v>1.97729980945587</v>
+        <v>1.97729992866516</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G327" t="n">
-        <v>1.91578388214111</v>
+        <v>1.9157840013504</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G331" t="n">
-        <v>1.99487602710724</v>
+        <v>1.99487578868866</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G332" t="n">
-        <v>1.99487602710724</v>
+        <v>1.99487578868866</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G333" t="n">
-        <v>1.99487602710724</v>
+        <v>1.99487578868866</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G337" t="n">
-        <v>2.10912013053894</v>
+        <v>2.10911989212036</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G338" t="n">
-        <v>2.05639171600342</v>
+        <v>2.056391954422</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G351" t="n">
-        <v>1.8366916179657</v>
+        <v>1.83669173717499</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G354" t="n">
-        <v>1.85426759719849</v>
+        <v>1.85426771640778</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G355" t="n">
-        <v>1.92457187175751</v>
+        <v>1.9245719909668</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>2.25</v>
       </c>
       <c r="G357" t="n">
-        <v>1.97729980945587</v>
+        <v>1.97729992866516</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G361" t="n">
-        <v>1.99487602710724</v>
+        <v>1.99487578868866</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G362" t="n">
-        <v>1.99487602710724</v>
+        <v>1.99487578868866</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G374" t="n">
-        <v>1.77517580986023</v>
+        <v>1.77517592906952</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G375" t="n">
-        <v>1.85426759719849</v>
+        <v>1.85426771640778</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G376" t="n">
-        <v>1.88063204288483</v>
+        <v>1.88063192367554</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G377" t="n">
-        <v>1.88063204288483</v>
+        <v>1.88063192367554</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>2.25</v>
       </c>
       <c r="G378" t="n">
-        <v>1.97729980945587</v>
+        <v>1.97729992866516</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G385" t="n">
-        <v>1.88063204288483</v>
+        <v>1.88063192367554</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G386" t="n">
-        <v>1.99487602710724</v>
+        <v>1.99487578868866</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G388" t="n">
-        <v>1.99487602710724</v>
+        <v>1.99487578868866</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>2.25</v>
       </c>
       <c r="G389" t="n">
-        <v>1.97729980945587</v>
+        <v>1.97729992866516</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G394" t="n">
-        <v>1.92457187175751</v>
+        <v>1.9245719909668</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G395" t="n">
-        <v>1.99487602710724</v>
+        <v>1.99487578868866</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G398" t="n">
-        <v>2.05639171600342</v>
+        <v>2.056391954422</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G402" t="n">
-        <v>2.05639171600342</v>
+        <v>2.056391954422</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G407" t="n">
-        <v>1.84547972679138</v>
+        <v>1.84547984600067</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G411" t="n">
-        <v>1.87184405326843</v>
+        <v>1.87184393405914</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G412" t="n">
-        <v>1.88063204288483</v>
+        <v>1.88063192367554</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G413" t="n">
-        <v>1.88063204288483</v>
+        <v>1.88063192367554</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G414" t="n">
-        <v>1.8366916179657</v>
+        <v>1.83669173717499</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G419" t="n">
-        <v>1.91578388214111</v>
+        <v>1.9157840013504</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G421" t="n">
-        <v>1.91578388214111</v>
+        <v>1.9157840013504</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>2</v>
       </c>
       <c r="G423" t="n">
-        <v>1.75759971141815</v>
+        <v>1.75759983062744</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G424" t="n">
-        <v>1.77517580986023</v>
+        <v>1.77517592906952</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>2</v>
       </c>
       <c r="G426" t="n">
-        <v>1.75759971141815</v>
+        <v>1.75759983062744</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G431" t="n">
-        <v>1.84547972679138</v>
+        <v>1.84547984600067</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G432" t="n">
-        <v>1.77517580986023</v>
+        <v>1.77517592906952</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G436" t="n">
-        <v>1.88063204288483</v>
+        <v>1.88063192367554</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G437" t="n">
-        <v>1.85426759719849</v>
+        <v>1.85426771640778</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G438" t="n">
-        <v>1.85426759719849</v>
+        <v>1.85426771640778</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G441" t="n">
-        <v>1.88063204288483</v>
+        <v>1.88063192367554</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G442" t="n">
-        <v>1.88063204288483</v>
+        <v>1.88063192367554</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G449" t="n">
-        <v>1.68290185928345</v>
+        <v>1.68290174007416</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>2</v>
       </c>
       <c r="G450" t="n">
-        <v>1.75759971141815</v>
+        <v>1.75759983062744</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G452" t="n">
-        <v>1.72684180736542</v>
+        <v>1.72684192657471</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G454" t="n">
-        <v>1.63896191120148</v>
+        <v>1.63896179199219</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G460" t="n">
-        <v>1.67411375045776</v>
+        <v>1.67411386966705</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G461" t="n">
-        <v>1.67411375045776</v>
+        <v>1.67411386966705</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G462" t="n">
-        <v>1.67411375045776</v>
+        <v>1.67411386966705</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G465" t="n">
-        <v>1.65214371681213</v>
+        <v>1.65214383602142</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G467" t="n">
-        <v>1.59502184391022</v>
+        <v>1.59502196311951</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G468" t="n">
-        <v>1.66971981525421</v>
+        <v>1.6697199344635</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G471" t="n">
-        <v>1.59502184391022</v>
+        <v>1.59502196311951</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G472" t="n">
-        <v>1.64335584640503</v>
+        <v>1.64335572719574</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G473" t="n">
-        <v>1.64335584640503</v>
+        <v>1.64335572719574</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G474" t="n">
-        <v>1.66971981525421</v>
+        <v>1.6697199344635</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G479" t="n">
-        <v>1.65653777122498</v>
+        <v>1.65653789043427</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G482" t="n">
-        <v>1.67411375045776</v>
+        <v>1.67411386966705</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G483" t="n">
-        <v>1.64335584640503</v>
+        <v>1.64335572719574</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G484" t="n">
-        <v>1.74881184101105</v>
+        <v>1.74881172180176</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G486" t="n">
-        <v>1.87184405326843</v>
+        <v>1.87184393405914</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G488" t="n">
-        <v>1.92457187175751</v>
+        <v>1.9245719909668</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G492" t="n">
-        <v>1.99487602710724</v>
+        <v>1.99487578868866</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>2.25</v>
       </c>
       <c r="G494" t="n">
-        <v>1.97729980945587</v>
+        <v>1.97729992866516</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>2.25</v>
       </c>
       <c r="G495" t="n">
-        <v>1.97729980945587</v>
+        <v>1.97729992866516</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G499" t="n">
-        <v>1.78396391868591</v>
+        <v>1.78396379947662</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G500" t="n">
-        <v>1.78396391868591</v>
+        <v>1.78396379947662</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G501" t="n">
-        <v>1.78396391868591</v>
+        <v>1.78396379947662</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G502" t="n">
-        <v>1.74881184101105</v>
+        <v>1.74881172180176</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G503" t="n">
-        <v>1.74881184101105</v>
+        <v>1.74881172180176</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G504" t="n">
-        <v>1.74881184101105</v>
+        <v>1.74881172180176</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G505" t="n">
-        <v>1.77517580986023</v>
+        <v>1.77517592906952</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G506" t="n">
-        <v>1.77517580986023</v>
+        <v>1.77517592906952</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G507" t="n">
-        <v>1.78396391868591</v>
+        <v>1.78396379947662</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G508" t="n">
-        <v>1.78396391868591</v>
+        <v>1.78396379947662</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G509" t="n">
-        <v>1.78396391868591</v>
+        <v>1.78396379947662</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G510" t="n">
-        <v>1.77517580986023</v>
+        <v>1.77517592906952</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G511" t="n">
-        <v>1.7444179058075</v>
+        <v>1.74441778659821</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G512" t="n">
-        <v>1.78396391868591</v>
+        <v>1.78396379947662</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G514" t="n">
-        <v>1.78396391868591</v>
+        <v>1.78396379947662</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G515" t="n">
-        <v>1.78396391868591</v>
+        <v>1.78396379947662</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G531" t="n">
-        <v>1.51592981815338</v>
+        <v>1.51592993736267</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G532" t="n">
-        <v>1.51592981815338</v>
+        <v>1.51592993736267</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G533" t="n">
-        <v>1.51592981815338</v>
+        <v>1.51592993736267</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G545" t="n">
-        <v>1.56426382064819</v>
+        <v>1.56426393985748</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G551" t="n">
-        <v>1.72684180736542</v>
+        <v>1.72684192657471</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G552" t="n">
-        <v>1.73123574256897</v>
+        <v>1.73123586177826</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G553" t="n">
-        <v>1.7444179058075</v>
+        <v>1.74441778659821</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>2</v>
       </c>
       <c r="G554" t="n">
-        <v>1.75759971141815</v>
+        <v>1.75759983062744</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>2</v>
       </c>
       <c r="G555" t="n">
-        <v>1.75759971141815</v>
+        <v>1.75759983062744</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G556" t="n">
-        <v>1.66971981525421</v>
+        <v>1.6697199344635</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G557" t="n">
-        <v>1.66971981525421</v>
+        <v>1.6697199344635</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G558" t="n">
-        <v>1.72684180736542</v>
+        <v>1.72684192657471</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G559" t="n">
-        <v>1.72684180736542</v>
+        <v>1.72684192657471</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G572" t="n">
-        <v>1.67411375045776</v>
+        <v>1.67411386966705</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G573" t="n">
-        <v>1.66971981525421</v>
+        <v>1.6697199344635</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G574" t="n">
-        <v>1.66971981525421</v>
+        <v>1.6697199344635</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G575" t="n">
-        <v>1.66971981525421</v>
+        <v>1.6697199344635</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G576" t="n">
-        <v>1.66971981525421</v>
+        <v>1.6697199344635</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G577" t="n">
-        <v>1.66971981525421</v>
+        <v>1.6697199344635</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G582" t="n">
-        <v>1.65214371681213</v>
+        <v>1.65214383602142</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G583" t="n">
-        <v>1.65214371681213</v>
+        <v>1.65214383602142</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G590" t="n">
-        <v>1.65653777122498</v>
+        <v>1.65653789043427</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G598" t="n">
-        <v>1.63896191120148</v>
+        <v>1.63896179199219</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G599" t="n">
-        <v>1.63896191120148</v>
+        <v>1.63896179199219</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G606" t="n">
-        <v>1.63896191120148</v>
+        <v>1.63896179199219</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G610" t="n">
-        <v>1.57744586467743</v>
+        <v>1.57744574546814</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G611" t="n">
-        <v>1.57744586467743</v>
+        <v>1.57744574546814</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G613" t="n">
-        <v>1.57744586467743</v>
+        <v>1.57744574546814</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G614" t="n">
-        <v>1.57744586467743</v>
+        <v>1.57744574546814</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G615" t="n">
-        <v>1.57744586467743</v>
+        <v>1.57744574546814</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G616" t="n">
-        <v>1.56865775585175</v>
+        <v>1.56865787506104</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G621" t="n">
-        <v>1.66971981525421</v>
+        <v>1.6697199344635</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G622" t="n">
-        <v>1.68290185928345</v>
+        <v>1.68290174007416</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G624" t="n">
-        <v>1.66971981525421</v>
+        <v>1.6697199344635</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>2.25</v>
       </c>
       <c r="G628" t="n">
-        <v>1.97729980945587</v>
+        <v>1.97729992866516</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G629" t="n">
-        <v>1.88063204288483</v>
+        <v>1.88063192367554</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G635" t="n">
-        <v>1.7444179058075</v>
+        <v>1.74441778659821</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G639" t="n">
-        <v>1.64335584640503</v>
+        <v>1.64335572719574</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G642" t="n">
-        <v>1.65214371681213</v>
+        <v>1.65214383602142</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G643" t="n">
-        <v>1.65214371681213</v>
+        <v>1.65214383602142</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G646" t="n">
-        <v>1.6213858127594</v>
+        <v>1.62138593196869</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>2</v>
       </c>
       <c r="G649" t="n">
-        <v>1.75759971141815</v>
+        <v>1.75759983062744</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G650" t="n">
-        <v>1.74881184101105</v>
+        <v>1.74881172180176</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>2</v>
       </c>
       <c r="G656" t="n">
-        <v>1.75759971141815</v>
+        <v>1.75759983062744</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>2</v>
       </c>
       <c r="G659" t="n">
-        <v>1.75759971141815</v>
+        <v>1.75759983062744</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G660" t="n">
-        <v>1.73123574256897</v>
+        <v>1.73123586177826</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G670" t="n">
-        <v>1.66083109378815</v>
+        <v>1.66083097457886</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G684" t="n">
-        <v>1.59764719009399</v>
+        <v>1.5976470708847</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G697" t="n">
-        <v>1.53446352481842</v>
+        <v>1.53446340560913</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G701" t="n">
-        <v>1.59764719009399</v>
+        <v>1.5976470708847</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G702" t="n">
-        <v>1.59764719009399</v>
+        <v>1.5976470708847</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G703" t="n">
-        <v>1.59764719009399</v>
+        <v>1.5976470708847</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G704" t="n">
-        <v>1.59764719009399</v>
+        <v>1.5976470708847</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G706" t="n">
-        <v>1.59764719009399</v>
+        <v>1.5976470708847</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G714" t="n">
-        <v>1.53446352481842</v>
+        <v>1.53446340560913</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G715" t="n">
-        <v>1.53446352481842</v>
+        <v>1.53446340560913</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G719" t="n">
-        <v>1.53446352481842</v>
+        <v>1.53446340560913</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G733" t="n">
-        <v>1.55251586437225</v>
+        <v>1.55251598358154</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G734" t="n">
-        <v>1.55251586437225</v>
+        <v>1.55251598358154</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G735" t="n">
-        <v>1.55251586437225</v>
+        <v>1.55251598358154</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G736" t="n">
-        <v>1.55251586437225</v>
+        <v>1.55251598358154</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G737" t="n">
-        <v>1.53446352481842</v>
+        <v>1.53446340560913</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G747" t="n">
-        <v>1.53446352481842</v>
+        <v>1.53446340560913</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G748" t="n">
-        <v>1.53446352481842</v>
+        <v>1.53446340560913</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G749" t="n">
-        <v>1.53446352481842</v>
+        <v>1.53446340560913</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G750" t="n">
-        <v>1.53446352481842</v>
+        <v>1.53446340560913</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G753" t="n">
-        <v>1.4983583688736</v>
+        <v>1.49835848808289</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G755" t="n">
-        <v>1.44420075416565</v>
+        <v>1.44420087337494</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G767" t="n">
-        <v>1.48933219909668</v>
+        <v>1.48933207988739</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G775" t="n">
-        <v>1.48933219909668</v>
+        <v>1.48933207988739</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G778" t="n">
-        <v>1.48933219909668</v>
+        <v>1.48933207988739</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G782" t="n">
-        <v>1.53446352481842</v>
+        <v>1.53446340560913</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G784" t="n">
-        <v>1.4983583688736</v>
+        <v>1.49835848808289</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G794" t="n">
-        <v>1.98577618598938</v>
+        <v>1.98577630519867</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G795" t="n">
-        <v>1.87746107578278</v>
+        <v>1.87746119499207</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G799" t="n">
-        <v>1.77817225456238</v>
+        <v>1.77817237377167</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G804" t="n">
-        <v>1.87746107578278</v>
+        <v>1.87746119499207</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G805" t="n">
-        <v>1.85940861701965</v>
+        <v>1.85940849781036</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G806" t="n">
-        <v>1.8955135345459</v>
+        <v>1.89551365375519</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G807" t="n">
-        <v>1.85940861701965</v>
+        <v>1.85940849781036</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G808" t="n">
-        <v>1.87746107578278</v>
+        <v>1.87746119499207</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G809" t="n">
-        <v>1.85940861701965</v>
+        <v>1.85940849781036</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G810" t="n">
-        <v>1.85940861701965</v>
+        <v>1.85940849781036</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G812" t="n">
-        <v>1.87746107578278</v>
+        <v>1.87746119499207</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G813" t="n">
-        <v>1.91356611251831</v>
+        <v>1.91356599330902</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G814" t="n">
-        <v>1.87746107578278</v>
+        <v>1.87746119499207</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G822" t="n">
-        <v>1.77817225456238</v>
+        <v>1.77817237377167</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G832" t="n">
-        <v>1.77817225456238</v>
+        <v>1.77817237377167</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G837" t="n">
-        <v>1.77817225456238</v>
+        <v>1.77817237377167</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G850" t="n">
-        <v>1.77817225456238</v>
+        <v>1.77817237377167</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G852" t="n">
-        <v>1.77817225456238</v>
+        <v>1.77817237377167</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G853" t="n">
-        <v>1.77817225456238</v>
+        <v>1.77817237377167</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G866" t="n">
-        <v>1.87746107578278</v>
+        <v>1.87746119499207</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G867" t="n">
-        <v>1.91356611251831</v>
+        <v>1.91356599330902</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G868" t="n">
-        <v>1.98577618598938</v>
+        <v>1.98577630519867</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G869" t="n">
-        <v>1.98577618598938</v>
+        <v>1.98577630519867</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G874" t="n">
-        <v>1.98577618598938</v>
+        <v>1.98577630519867</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G883" t="n">
-        <v>1.98577618598938</v>
+        <v>1.98577630519867</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G885" t="n">
-        <v>2.20240616798401</v>
+        <v>2.20240640640259</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G886" t="n">
-        <v>2.16630148887634</v>
+        <v>2.16630125045776</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G887" t="n">
-        <v>2.16630148887634</v>
+        <v>2.16630125045776</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G888" t="n">
-        <v>2.16630148887634</v>
+        <v>2.16630125045776</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>2.5</v>
       </c>
       <c r="G889" t="n">
-        <v>2.25656414031982</v>
+        <v>2.25656390190125</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G890" t="n">
-        <v>2.20240616798401</v>
+        <v>2.20240640640259</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G894" t="n">
-        <v>2.02188110351562</v>
+        <v>2.0218813419342</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G895" t="n">
-        <v>1.85940861701965</v>
+        <v>1.85940849781036</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G897" t="n">
-        <v>1.91356611251831</v>
+        <v>1.91356599330902</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G898" t="n">
-        <v>1.87746107578278</v>
+        <v>1.87746119499207</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G899" t="n">
-        <v>1.85940861701965</v>
+        <v>1.85940849781036</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G900" t="n">
-        <v>1.87746107578278</v>
+        <v>1.87746119499207</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G901" t="n">
-        <v>1.85940861701965</v>
+        <v>1.85940849781036</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G903" t="n">
-        <v>1.91356611251831</v>
+        <v>1.91356599330902</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G906" t="n">
-        <v>1.91356611251831</v>
+        <v>1.91356599330902</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G909" t="n">
-        <v>1.85940861701965</v>
+        <v>1.85940849781036</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G911" t="n">
-        <v>1.87746107578278</v>
+        <v>1.87746119499207</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G912" t="n">
-        <v>1.85940861701965</v>
+        <v>1.85940849781036</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G913" t="n">
-        <v>1.85940861701965</v>
+        <v>1.85940849781036</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G914" t="n">
-        <v>1.8955135345459</v>
+        <v>1.89551365375519</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G915" t="n">
-        <v>1.87746107578278</v>
+        <v>1.87746119499207</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G916" t="n">
-        <v>1.87746107578278</v>
+        <v>1.87746119499207</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G917" t="n">
-        <v>1.85940861701965</v>
+        <v>1.85940849781036</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -40698,6 +40698,32 @@
         <v>1.61000001430511</v>
       </c>
       <c r="H1551" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1552">
+      <c r="A1552" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1552" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C1552" t="n">
+        <v>1.57000005245209</v>
+      </c>
+      <c r="D1552" t="n">
+        <v>1.57000005245209</v>
+      </c>
+      <c r="E1552" t="n">
+        <v>1.57000005245209</v>
+      </c>
+      <c r="F1552" t="n">
+        <v>1.57000005245209</v>
+      </c>
+      <c r="G1552" t="n">
+        <v>1.57000005245209</v>
+      </c>
+      <c r="H1552" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RETI.MI.xlsx
+++ b/data/RETI.MI.xlsx
@@ -447,7 +447,7 @@
         <v>0.899600028991699</v>
       </c>
       <c r="G3" t="n">
-        <v>0.768140912055969</v>
+        <v>0.768140971660614</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>0.879899978637695</v>
       </c>
       <c r="G4" t="n">
-        <v>0.751319766044617</v>
+        <v>0.751319706439972</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G5" t="n">
-        <v>0.765067040920258</v>
+        <v>0.765067100524902</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G6" t="n">
-        <v>0.765067040920258</v>
+        <v>0.765067100524902</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G10" t="n">
-        <v>0.722373604774475</v>
+        <v>0.72237354516983</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>0.84799998998642</v>
       </c>
       <c r="G11" t="n">
-        <v>0.724081218242645</v>
+        <v>0.72408127784729</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>0.814000010490417</v>
       </c>
       <c r="G12" t="n">
-        <v>0.695049703121185</v>
+        <v>0.69504976272583</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G13" t="n">
-        <v>0.691634178161621</v>
+        <v>0.691634237766266</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G14" t="n">
-        <v>0.683095514774323</v>
+        <v>0.683095574378967</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G15" t="n">
-        <v>0.683095514774323</v>
+        <v>0.683095574378967</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G16" t="n">
-        <v>0.666018128395081</v>
+        <v>0.666018187999725</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G17" t="n">
-        <v>0.654063999652863</v>
+        <v>0.654063940048218</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>0.833999991416931</v>
       </c>
       <c r="G18" t="n">
-        <v>0.712127149105072</v>
+        <v>0.712127089500427</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>0.814000010490417</v>
       </c>
       <c r="G19" t="n">
-        <v>0.695049703121185</v>
+        <v>0.69504976272583</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G21" t="n">
-        <v>0.654063999652863</v>
+        <v>0.654063940048218</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G22" t="n">
-        <v>0.659187257289886</v>
+        <v>0.659187197685242</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G23" t="n">
-        <v>0.666018128395081</v>
+        <v>0.666018187999725</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G24" t="n">
-        <v>0.652356266975403</v>
+        <v>0.652356207370758</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G25" t="n">
-        <v>0.660894989967346</v>
+        <v>0.660894930362701</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G26" t="n">
-        <v>0.654063999652863</v>
+        <v>0.654063940048218</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G27" t="n">
-        <v>0.633571088314056</v>
+        <v>0.633571147918701</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G29" t="n">
-        <v>0.623324632644653</v>
+        <v>0.623324692249298</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>0.73199999332428</v>
       </c>
       <c r="G32" t="n">
-        <v>0.625032484531403</v>
+        <v>0.625032365322113</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G34" t="n">
-        <v>0.60966283082962</v>
+        <v>0.609662771224976</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G36" t="n">
-        <v>0.563553869724274</v>
+        <v>0.563553929328918</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G39" t="n">
-        <v>0.525983512401581</v>
+        <v>0.525983572006226</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G43" t="n">
-        <v>0.623324632644653</v>
+        <v>0.623324692249298</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G45" t="n">
-        <v>0.618201494216919</v>
+        <v>0.618201434612274</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G48" t="n">
-        <v>0.611370503902435</v>
+        <v>0.611370623111725</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G55" t="n">
-        <v>0.677972316741943</v>
+        <v>0.677972376346588</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G59" t="n">
-        <v>0.683095514774323</v>
+        <v>0.683095574378967</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G60" t="n">
-        <v>0.683095514774323</v>
+        <v>0.683095574378967</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G61" t="n">
-        <v>0.683095514774323</v>
+        <v>0.683095574378967</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G63" t="n">
-        <v>0.679680049419403</v>
+        <v>0.679680109024048</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G64" t="n">
-        <v>0.683095514774323</v>
+        <v>0.683095574378967</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G67" t="n">
-        <v>0.683095514774323</v>
+        <v>0.683095574378967</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G70" t="n">
-        <v>0.677972316741943</v>
+        <v>0.677972376346588</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G71" t="n">
-        <v>0.677972316741943</v>
+        <v>0.677972376346588</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G74" t="n">
-        <v>0.691634178161621</v>
+        <v>0.691634237766266</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G80" t="n">
-        <v>0.717250347137451</v>
+        <v>0.717250287532806</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G81" t="n">
-        <v>0.708711624145508</v>
+        <v>0.708711564540863</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>0.833999991416931</v>
       </c>
       <c r="G82" t="n">
-        <v>0.712127149105072</v>
+        <v>0.712127089500427</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G84" t="n">
-        <v>0.717250347137451</v>
+        <v>0.717250287532806</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G87" t="n">
-        <v>0.688218712806702</v>
+        <v>0.688218772411346</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G94" t="n">
-        <v>0.698465168476105</v>
+        <v>0.698465287685394</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G95" t="n">
-        <v>0.683095514774323</v>
+        <v>0.683095574378967</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G98" t="n">
-        <v>0.666018128395081</v>
+        <v>0.666018187999725</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G99" t="n">
-        <v>0.677972316741943</v>
+        <v>0.677972376346588</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G100" t="n">
-        <v>0.676264643669128</v>
+        <v>0.676264584064484</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G101" t="n">
-        <v>0.676264643669128</v>
+        <v>0.676264584064484</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G102" t="n">
-        <v>0.683095514774323</v>
+        <v>0.683095574378967</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G104" t="n">
-        <v>0.683095514774323</v>
+        <v>0.683095574378967</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G105" t="n">
-        <v>0.683095514774323</v>
+        <v>0.683095574378967</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G106" t="n">
-        <v>0.683095514774323</v>
+        <v>0.683095574378967</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G107" t="n">
-        <v>0.691634178161621</v>
+        <v>0.691634237766266</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G109" t="n">
-        <v>0.683095514774323</v>
+        <v>0.683095574378967</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G110" t="n">
-        <v>0.698465168476105</v>
+        <v>0.698465287685394</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G112" t="n">
-        <v>0.686511099338531</v>
+        <v>0.686511039733887</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G113" t="n">
-        <v>0.691634178161621</v>
+        <v>0.691634237766266</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>0.86599999666214</v>
       </c>
       <c r="G116" t="n">
-        <v>0.739450871944427</v>
+        <v>0.739450931549072</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G118" t="n">
-        <v>0.717250347137451</v>
+        <v>0.717250287532806</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G122" t="n">
-        <v>0.858138859272003</v>
+        <v>0.858138740062714</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G124" t="n">
-        <v>0.828253388404846</v>
+        <v>0.828253328800201</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G125" t="n">
-        <v>0.836792051792145</v>
+        <v>0.83679211139679</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G126" t="n">
-        <v>0.836792051792145</v>
+        <v>0.83679211139679</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G132" t="n">
-        <v>0.845330774784088</v>
+        <v>0.845330715179443</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G133" t="n">
-        <v>0.870946884155273</v>
+        <v>0.870946824550629</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G134" t="n">
-        <v>0.875216126441956</v>
+        <v>0.8752161860466</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G135" t="n">
-        <v>0.866677463054657</v>
+        <v>0.866677522659302</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G139" t="n">
-        <v>0.913640379905701</v>
+        <v>0.913640320301056</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G140" t="n">
-        <v>0.922179043292999</v>
+        <v>0.922179102897644</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G141" t="n">
-        <v>0.922179043292999</v>
+        <v>0.922179102897644</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G142" t="n">
-        <v>0.913640379905701</v>
+        <v>0.913640320301056</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G143" t="n">
-        <v>0.930717766284943</v>
+        <v>0.930717706680298</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G144" t="n">
-        <v>1.17833983898163</v>
+        <v>1.17833971977234</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G146" t="n">
-        <v>1.1356463432312</v>
+        <v>1.13564646244049</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G148" t="n">
-        <v>1.20395588874817</v>
+        <v>1.20395600795746</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G149" t="n">
-        <v>1.20395588874817</v>
+        <v>1.20395600795746</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G150" t="n">
-        <v>1.18637990951538</v>
+        <v>1.18637979030609</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G152" t="n">
-        <v>1.22153174877167</v>
+        <v>1.22153186798096</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G153" t="n">
-        <v>1.22153174877167</v>
+        <v>1.22153186798096</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G154" t="n">
-        <v>1.1775918006897</v>
+        <v>1.17759191989899</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G155" t="n">
-        <v>1.13804590702057</v>
+        <v>1.13804578781128</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G157" t="n">
-        <v>1.13365197181702</v>
+        <v>1.13365185260773</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>1.25499999523163</v>
       </c>
       <c r="G159" t="n">
-        <v>1.1028938293457</v>
+        <v>1.10289406776428</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G163" t="n">
-        <v>1.13365197181702</v>
+        <v>1.13365185260773</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G167" t="n">
-        <v>1.1775918006897</v>
+        <v>1.17759191989899</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G169" t="n">
-        <v>1.12925791740417</v>
+        <v>1.12925779819489</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G171" t="n">
-        <v>1.13804590702057</v>
+        <v>1.13804578781128</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G173" t="n">
-        <v>1.18637990951538</v>
+        <v>1.18637979030609</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G176" t="n">
-        <v>1.32259380817413</v>
+        <v>1.32259392738342</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G177" t="n">
-        <v>1.32259380817413</v>
+        <v>1.32259392738342</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G179" t="n">
-        <v>1.33577585220337</v>
+        <v>1.33577573299408</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G181" t="n">
-        <v>1.33577585220337</v>
+        <v>1.33577573299408</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>1.5</v>
       </c>
       <c r="G182" t="n">
-        <v>1.31819975376129</v>
+        <v>1.31819987297058</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G184" t="n">
-        <v>1.32259380817413</v>
+        <v>1.32259392738342</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>1.5</v>
       </c>
       <c r="G185" t="n">
-        <v>1.31819975376129</v>
+        <v>1.31819987297058</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>1.5</v>
       </c>
       <c r="G186" t="n">
-        <v>1.31819975376129</v>
+        <v>1.31819987297058</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G187" t="n">
-        <v>1.3006237745285</v>
+        <v>1.30062389373779</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G189" t="n">
-        <v>1.45001995563507</v>
+        <v>1.45001983642578</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G190" t="n">
-        <v>1.41486787796021</v>
+        <v>1.41486799716949</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G191" t="n">
-        <v>1.38410997390747</v>
+        <v>1.38410985469818</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G192" t="n">
-        <v>1.37971591949463</v>
+        <v>1.37971580028534</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G195" t="n">
-        <v>1.34456396102905</v>
+        <v>1.34456384181976</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G197" t="n">
-        <v>1.32259380817413</v>
+        <v>1.32259392738342</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G198" t="n">
-        <v>1.32698774337769</v>
+        <v>1.32698786258698</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>1.5</v>
       </c>
       <c r="G201" t="n">
-        <v>1.31819975376129</v>
+        <v>1.31819987297058</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>1.5</v>
       </c>
       <c r="G202" t="n">
-        <v>1.31819975376129</v>
+        <v>1.31819987297058</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>1.5</v>
       </c>
       <c r="G203" t="n">
-        <v>1.31819975376129</v>
+        <v>1.31819987297058</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G205" t="n">
-        <v>1.33577585220337</v>
+        <v>1.33577573299408</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G206" t="n">
-        <v>1.34456396102905</v>
+        <v>1.34456384181976</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G207" t="n">
-        <v>1.34456396102905</v>
+        <v>1.34456384181976</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G211" t="n">
-        <v>1.2918359041214</v>
+        <v>1.29183602333069</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G213" t="n">
-        <v>1.3006237745285</v>
+        <v>1.30062389373779</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G215" t="n">
-        <v>1.32698774337769</v>
+        <v>1.32698786258698</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>1.5</v>
       </c>
       <c r="G216" t="n">
-        <v>1.31819975376129</v>
+        <v>1.31819987297058</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G222" t="n">
-        <v>1.2918359041214</v>
+        <v>1.29183602333069</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>1.5</v>
       </c>
       <c r="G224" t="n">
-        <v>1.31819975376129</v>
+        <v>1.31819987297058</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>1.5</v>
       </c>
       <c r="G225" t="n">
-        <v>1.31819975376129</v>
+        <v>1.31819987297058</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G226" t="n">
-        <v>1.3006237745285</v>
+        <v>1.30062389373779</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>1.5</v>
       </c>
       <c r="G227" t="n">
-        <v>1.31819975376129</v>
+        <v>1.31819987297058</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G228" t="n">
-        <v>1.2918359041214</v>
+        <v>1.29183602333069</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G230" t="n">
-        <v>1.25668382644653</v>
+        <v>1.25668394565582</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G232" t="n">
-        <v>1.34456396102905</v>
+        <v>1.34456384181976</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G235" t="n">
-        <v>1.34456396102905</v>
+        <v>1.34456384181976</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G238" t="n">
-        <v>1.3665337562561</v>
+        <v>1.36653387546539</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G240" t="n">
-        <v>1.74881172180176</v>
+        <v>1.74881184101105</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G241" t="n">
-        <v>2.24972772598267</v>
+        <v>2.24972748756409</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G243" t="n">
-        <v>2.2321515083313</v>
+        <v>2.23215174674988</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G244" t="n">
-        <v>2.52215552330017</v>
+        <v>2.52215576171875</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G245" t="n">
-        <v>2.39912390708923</v>
+        <v>2.39912414550781</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G246" t="n">
-        <v>2.27609181404114</v>
+        <v>2.27609157562256</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G248" t="n">
-        <v>2.27609181404114</v>
+        <v>2.27609157562256</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G249" t="n">
-        <v>2.20578765869141</v>
+        <v>2.20578813552856</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G250" t="n">
-        <v>2.2321515083313</v>
+        <v>2.23215174674988</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G251" t="n">
-        <v>2.1882119178772</v>
+        <v>2.18821167945862</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G252" t="n">
-        <v>2.1882119178772</v>
+        <v>2.18821167945862</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G257" t="n">
-        <v>2.35518360137939</v>
+        <v>2.35518383979797</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G259" t="n">
-        <v>2.22336363792419</v>
+        <v>2.22336387634277</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G261" t="n">
-        <v>2.21457576751709</v>
+        <v>2.21457600593567</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G262" t="n">
-        <v>2.24972772598267</v>
+        <v>2.24972748756409</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G264" t="n">
-        <v>2.20578765869141</v>
+        <v>2.20578813552856</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G266" t="n">
-        <v>2.35518360137939</v>
+        <v>2.35518383979797</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G267" t="n">
-        <v>2.27609181404114</v>
+        <v>2.27609157562256</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G268" t="n">
-        <v>2.38154768943787</v>
+        <v>2.38154745101929</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G269" t="n">
-        <v>2.31124377250671</v>
+        <v>2.31124401092529</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G270" t="n">
-        <v>2.2321515083313</v>
+        <v>2.23215174674988</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G273" t="n">
-        <v>2.27609181404114</v>
+        <v>2.27609157562256</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G274" t="n">
-        <v>2.24972772598267</v>
+        <v>2.24972748756409</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G277" t="n">
-        <v>2.30245566368103</v>
+        <v>2.30245590209961</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G282" t="n">
-        <v>2.30245566368103</v>
+        <v>2.30245590209961</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G283" t="n">
-        <v>2.25851583480835</v>
+        <v>2.25851559638977</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G285" t="n">
-        <v>2.27609181404114</v>
+        <v>2.27609157562256</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G286" t="n">
-        <v>2.26730394363403</v>
+        <v>2.26730370521545</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G290" t="n">
-        <v>2.25851583480835</v>
+        <v>2.25851559638977</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G291" t="n">
-        <v>2.27609181404114</v>
+        <v>2.27609157562256</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G292" t="n">
-        <v>2.21457576751709</v>
+        <v>2.21457600593567</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G293" t="n">
-        <v>2.24972772598267</v>
+        <v>2.24972748756409</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G295" t="n">
-        <v>2.26730394363403</v>
+        <v>2.26730370521545</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G296" t="n">
-        <v>2.2321515083313</v>
+        <v>2.23215174674988</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G297" t="n">
-        <v>2.21457576751709</v>
+        <v>2.21457600593567</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G298" t="n">
-        <v>2.21457576751709</v>
+        <v>2.21457600593567</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G299" t="n">
-        <v>2.22336363792419</v>
+        <v>2.22336387634277</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G300" t="n">
-        <v>2.20578765869141</v>
+        <v>2.20578813552856</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G302" t="n">
-        <v>2.14427161216736</v>
+        <v>2.14427185058594</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G303" t="n">
-        <v>2.07396769523621</v>
+        <v>2.07396745681763</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G306" t="n">
-        <v>1.99487578868866</v>
+        <v>1.99487566947937</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G308" t="n">
-        <v>2.02123951911926</v>
+        <v>2.02123999595642</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G309" t="n">
-        <v>1.93335962295532</v>
+        <v>1.9333598613739</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G311" t="n">
-        <v>1.88941991329193</v>
+        <v>1.88942003250122</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G313" t="n">
-        <v>1.93335962295532</v>
+        <v>1.9333598613739</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G314" t="n">
-        <v>1.93335962295532</v>
+        <v>1.9333598613739</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G317" t="n">
-        <v>2.07396769523621</v>
+        <v>2.07396745681763</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G320" t="n">
-        <v>2.14427161216736</v>
+        <v>2.14427185058594</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G321" t="n">
-        <v>2.14427161216736</v>
+        <v>2.14427185058594</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G322" t="n">
-        <v>2.10033178329468</v>
+        <v>2.10033202171326</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G323" t="n">
-        <v>2.10033178329468</v>
+        <v>2.10033202171326</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G325" t="n">
-        <v>1.94214773178101</v>
+        <v>1.9421478509903</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G327" t="n">
-        <v>1.9157840013504</v>
+        <v>1.91578376293182</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G328" t="n">
-        <v>1.88941991329193</v>
+        <v>1.88942003250122</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G331" t="n">
-        <v>1.99487578868866</v>
+        <v>1.99487566947937</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G332" t="n">
-        <v>1.99487578868866</v>
+        <v>1.99487566947937</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G333" t="n">
-        <v>1.99487578868866</v>
+        <v>1.99487566947937</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G336" t="n">
-        <v>2.02123951911926</v>
+        <v>2.02123999595642</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G338" t="n">
-        <v>2.056391954422</v>
+        <v>2.05639147758484</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G341" t="n">
-        <v>2.0651798248291</v>
+        <v>2.06517958641052</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G342" t="n">
-        <v>2.0651798248291</v>
+        <v>2.06517958641052</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G343" t="n">
-        <v>2.0651798248291</v>
+        <v>2.06517958641052</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G344" t="n">
-        <v>1.95972371101379</v>
+        <v>1.9597235918045</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G347" t="n">
-        <v>1.9685115814209</v>
+        <v>1.96851170063019</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G348" t="n">
-        <v>1.93335962295532</v>
+        <v>1.9333598613739</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G349" t="n">
-        <v>1.90699601173401</v>
+        <v>1.90699577331543</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G350" t="n">
-        <v>1.90699601173401</v>
+        <v>1.90699577331543</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G352" t="n">
-        <v>1.81032776832581</v>
+        <v>1.81032764911652</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G353" t="n">
-        <v>1.88941991329193</v>
+        <v>1.88942003250122</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G354" t="n">
-        <v>1.85426771640778</v>
+        <v>1.85426759719849</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G361" t="n">
-        <v>1.99487578868866</v>
+        <v>1.99487566947937</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G362" t="n">
-        <v>1.99487578868866</v>
+        <v>1.99487566947937</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G363" t="n">
-        <v>1.9685115814209</v>
+        <v>1.96851170063019</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G366" t="n">
-        <v>1.93335962295532</v>
+        <v>1.9333598613739</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G367" t="n">
-        <v>1.93335962295532</v>
+        <v>1.9333598613739</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G369" t="n">
-        <v>1.98608791828156</v>
+        <v>1.98608779907227</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G370" t="n">
-        <v>1.93335962295532</v>
+        <v>1.9333598613739</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G371" t="n">
-        <v>1.93335962295532</v>
+        <v>1.9333598613739</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G372" t="n">
-        <v>1.98608791828156</v>
+        <v>1.98608779907227</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G373" t="n">
-        <v>1.95093584060669</v>
+        <v>1.9509357213974</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G374" t="n">
-        <v>1.77517592906952</v>
+        <v>1.77517569065094</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G375" t="n">
-        <v>1.85426771640778</v>
+        <v>1.85426759719849</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G376" t="n">
-        <v>1.88063192367554</v>
+        <v>1.88063216209412</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G377" t="n">
-        <v>1.88063192367554</v>
+        <v>1.88063216209412</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G379" t="n">
-        <v>1.93335962295532</v>
+        <v>1.9333598613739</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G383" t="n">
-        <v>1.86305570602417</v>
+        <v>1.86305582523346</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G384" t="n">
-        <v>1.86305570602417</v>
+        <v>1.86305582523346</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G385" t="n">
-        <v>1.88063192367554</v>
+        <v>1.88063216209412</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G386" t="n">
-        <v>1.99487578868866</v>
+        <v>1.99487566947937</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G388" t="n">
-        <v>1.99487578868866</v>
+        <v>1.99487566947937</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G390" t="n">
-        <v>1.93335962295532</v>
+        <v>1.9333598613739</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G391" t="n">
-        <v>1.9685115814209</v>
+        <v>1.96851170063019</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G392" t="n">
-        <v>1.98608791828156</v>
+        <v>1.98608779907227</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G393" t="n">
-        <v>1.98608791828156</v>
+        <v>1.98608779907227</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G395" t="n">
-        <v>1.99487578868866</v>
+        <v>1.99487566947937</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G397" t="n">
-        <v>2.0651798248291</v>
+        <v>2.06517958641052</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G398" t="n">
-        <v>2.056391954422</v>
+        <v>2.05639147758484</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G399" t="n">
-        <v>1.98608791828156</v>
+        <v>1.98608779907227</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G400" t="n">
-        <v>2.02123951911926</v>
+        <v>2.02123999595642</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G402" t="n">
-        <v>2.056391954422</v>
+        <v>2.05639147758484</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G403" t="n">
-        <v>1.93335962295532</v>
+        <v>1.9333598613739</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G404" t="n">
-        <v>1.9685115814209</v>
+        <v>1.96851170063019</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G405" t="n">
-        <v>1.98608791828156</v>
+        <v>1.98608779907227</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G406" t="n">
-        <v>1.98608791828156</v>
+        <v>1.98608779907227</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G407" t="n">
-        <v>1.84547984600067</v>
+        <v>1.84547972679138</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G409" t="n">
-        <v>1.88941991329193</v>
+        <v>1.88942003250122</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G410" t="n">
-        <v>1.88941991329193</v>
+        <v>1.88942003250122</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G412" t="n">
-        <v>1.88063192367554</v>
+        <v>1.88063216209412</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G413" t="n">
-        <v>1.88063192367554</v>
+        <v>1.88063216209412</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G417" t="n">
-        <v>1.86305570602417</v>
+        <v>1.86305582523346</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G418" t="n">
-        <v>1.81032776832581</v>
+        <v>1.81032764911652</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G419" t="n">
-        <v>1.9157840013504</v>
+        <v>1.91578376293182</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G421" t="n">
-        <v>1.9157840013504</v>
+        <v>1.91578376293182</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G424" t="n">
-        <v>1.77517592906952</v>
+        <v>1.77517569065094</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G427" t="n">
-        <v>1.76638793945312</v>
+        <v>1.76638782024384</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G428" t="n">
-        <v>1.76638793945312</v>
+        <v>1.76638782024384</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G429" t="n">
-        <v>1.76638793945312</v>
+        <v>1.76638782024384</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G430" t="n">
-        <v>1.76638793945312</v>
+        <v>1.76638782024384</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G431" t="n">
-        <v>1.84547984600067</v>
+        <v>1.84547972679138</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G432" t="n">
-        <v>1.77517592906952</v>
+        <v>1.77517569065094</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G433" t="n">
-        <v>1.86305570602417</v>
+        <v>1.86305582523346</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G434" t="n">
-        <v>1.86305570602417</v>
+        <v>1.86305582523346</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G435" t="n">
-        <v>1.86305570602417</v>
+        <v>1.86305582523346</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G436" t="n">
-        <v>1.88063192367554</v>
+        <v>1.88063216209412</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G437" t="n">
-        <v>1.85426771640778</v>
+        <v>1.85426759719849</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G438" t="n">
-        <v>1.85426771640778</v>
+        <v>1.85426759719849</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G441" t="n">
-        <v>1.88063192367554</v>
+        <v>1.88063216209412</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G442" t="n">
-        <v>1.88063192367554</v>
+        <v>1.88063216209412</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G444" t="n">
-        <v>1.86305570602417</v>
+        <v>1.86305582523346</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G447" t="n">
-        <v>1.76638793945312</v>
+        <v>1.76638782024384</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G448" t="n">
-        <v>1.73562979698181</v>
+        <v>1.7356299161911</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G449" t="n">
-        <v>1.68290174007416</v>
+        <v>1.68290185928345</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G452" t="n">
-        <v>1.72684192657471</v>
+        <v>1.72684180736542</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G453" t="n">
-        <v>1.68729591369629</v>
+        <v>1.687295794487</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G454" t="n">
-        <v>1.63896179199219</v>
+        <v>1.63896191120148</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G460" t="n">
-        <v>1.67411386966705</v>
+        <v>1.67411375045776</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G461" t="n">
-        <v>1.67411386966705</v>
+        <v>1.67411375045776</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G462" t="n">
-        <v>1.67411386966705</v>
+        <v>1.67411375045776</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G463" t="n">
-        <v>1.66093194484711</v>
+        <v>1.66093182563782</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G464" t="n">
-        <v>1.66093194484711</v>
+        <v>1.66093182563782</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G466" t="n">
-        <v>1.59941589832306</v>
+        <v>1.59941601753235</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G467" t="n">
-        <v>1.59502196311951</v>
+        <v>1.59502184391022</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G468" t="n">
-        <v>1.6697199344635</v>
+        <v>1.66971969604492</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>1.875</v>
       </c>
       <c r="G469" t="n">
-        <v>1.64774978160858</v>
+        <v>1.64774990081787</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G470" t="n">
-        <v>1.66093194484711</v>
+        <v>1.66093182563782</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G471" t="n">
-        <v>1.59502196311951</v>
+        <v>1.59502184391022</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G472" t="n">
-        <v>1.64335572719574</v>
+        <v>1.64335584640503</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G473" t="n">
-        <v>1.64335572719574</v>
+        <v>1.64335584640503</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G474" t="n">
-        <v>1.6697199344635</v>
+        <v>1.66971969604492</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G475" t="n">
-        <v>1.63456785678864</v>
+        <v>1.63456797599792</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G476" t="n">
-        <v>1.66532588005066</v>
+        <v>1.66532576084137</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G477" t="n">
-        <v>1.66532588005066</v>
+        <v>1.66532576084137</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G478" t="n">
-        <v>1.66532588005066</v>
+        <v>1.66532576084137</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G479" t="n">
-        <v>1.65653789043427</v>
+        <v>1.65653777122498</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G480" t="n">
-        <v>1.63017380237579</v>
+        <v>1.63017392158508</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G481" t="n">
-        <v>1.68729591369629</v>
+        <v>1.687295794487</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G482" t="n">
-        <v>1.67411386966705</v>
+        <v>1.67411375045776</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G483" t="n">
-        <v>1.64335572719574</v>
+        <v>1.64335584640503</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G484" t="n">
-        <v>1.74881172180176</v>
+        <v>1.74881184101105</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G485" t="n">
-        <v>1.81032776832581</v>
+        <v>1.81032764911652</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G487" t="n">
-        <v>1.93335962295532</v>
+        <v>1.9333598613739</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G492" t="n">
-        <v>1.99487578868866</v>
+        <v>1.99487566947937</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G493" t="n">
-        <v>2.02123951911926</v>
+        <v>2.02123999595642</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G496" t="n">
-        <v>1.93335962295532</v>
+        <v>1.9333598613739</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G498" t="n">
-        <v>1.73562979698181</v>
+        <v>1.7356299161911</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G499" t="n">
-        <v>1.78396379947662</v>
+        <v>1.78396391868591</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G500" t="n">
-        <v>1.78396379947662</v>
+        <v>1.78396391868591</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G501" t="n">
-        <v>1.78396379947662</v>
+        <v>1.78396391868591</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G502" t="n">
-        <v>1.74881172180176</v>
+        <v>1.74881184101105</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G503" t="n">
-        <v>1.74881172180176</v>
+        <v>1.74881184101105</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G504" t="n">
-        <v>1.74881172180176</v>
+        <v>1.74881184101105</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G505" t="n">
-        <v>1.77517592906952</v>
+        <v>1.77517569065094</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G506" t="n">
-        <v>1.77517592906952</v>
+        <v>1.77517569065094</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G507" t="n">
-        <v>1.78396379947662</v>
+        <v>1.78396391868591</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G508" t="n">
-        <v>1.78396379947662</v>
+        <v>1.78396391868591</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G509" t="n">
-        <v>1.78396379947662</v>
+        <v>1.78396391868591</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G510" t="n">
-        <v>1.77517592906952</v>
+        <v>1.77517569065094</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G511" t="n">
-        <v>1.74441778659821</v>
+        <v>1.7444179058075</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G512" t="n">
-        <v>1.78396379947662</v>
+        <v>1.78396391868591</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G513" t="n">
-        <v>1.81032776832581</v>
+        <v>1.81032764911652</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G514" t="n">
-        <v>1.78396379947662</v>
+        <v>1.78396391868591</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G515" t="n">
-        <v>1.78396379947662</v>
+        <v>1.78396391868591</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G516" t="n">
-        <v>1.71365988254547</v>
+        <v>1.71365976333618</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G517" t="n">
-        <v>1.71365988254547</v>
+        <v>1.71365976333618</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G518" t="n">
-        <v>1.71365988254547</v>
+        <v>1.71365976333618</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G519" t="n">
-        <v>1.76638793945312</v>
+        <v>1.76638782024384</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G521" t="n">
-        <v>1.81032776832581</v>
+        <v>1.81032764911652</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G522" t="n">
-        <v>1.76638793945312</v>
+        <v>1.76638782024384</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G526" t="n">
-        <v>1.54229378700256</v>
+        <v>1.54229390621185</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G527" t="n">
-        <v>1.50274789333344</v>
+        <v>1.50274777412415</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G528" t="n">
-        <v>1.50274789333344</v>
+        <v>1.50274777412415</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G531" t="n">
-        <v>1.51592993736267</v>
+        <v>1.51592981815338</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G532" t="n">
-        <v>1.51592993736267</v>
+        <v>1.51592981815338</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G533" t="n">
-        <v>1.51592993736267</v>
+        <v>1.51592981815338</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G536" t="n">
-        <v>1.50274789333344</v>
+        <v>1.50274777412415</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G537" t="n">
-        <v>1.50274789333344</v>
+        <v>1.50274777412415</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G538" t="n">
-        <v>1.55108189582825</v>
+        <v>1.55108177661896</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G539" t="n">
-        <v>1.55108189582825</v>
+        <v>1.55108177661896</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G540" t="n">
-        <v>1.51153576374054</v>
+        <v>1.51153588294983</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G541" t="n">
-        <v>1.51153576374054</v>
+        <v>1.51153588294983</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G542" t="n">
-        <v>1.51153576374054</v>
+        <v>1.51153588294983</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G545" t="n">
-        <v>1.56426393985748</v>
+        <v>1.5642637014389</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>1.875</v>
       </c>
       <c r="G546" t="n">
-        <v>1.64774978160858</v>
+        <v>1.64774990081787</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>1.875</v>
       </c>
       <c r="G547" t="n">
-        <v>1.64774978160858</v>
+        <v>1.64774990081787</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G551" t="n">
-        <v>1.72684192657471</v>
+        <v>1.72684180736542</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G553" t="n">
-        <v>1.74441778659821</v>
+        <v>1.7444179058075</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G556" t="n">
-        <v>1.6697199344635</v>
+        <v>1.66971969604492</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G557" t="n">
-        <v>1.6697199344635</v>
+        <v>1.66971969604492</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G558" t="n">
-        <v>1.72684192657471</v>
+        <v>1.72684180736542</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G559" t="n">
-        <v>1.72684192657471</v>
+        <v>1.72684180736542</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G569" t="n">
-        <v>1.60380983352661</v>
+        <v>1.6038099527359</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G570" t="n">
-        <v>1.60380983352661</v>
+        <v>1.6038099527359</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G571" t="n">
-        <v>1.66093194484711</v>
+        <v>1.66093182563782</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G572" t="n">
-        <v>1.67411386966705</v>
+        <v>1.67411375045776</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G573" t="n">
-        <v>1.6697199344635</v>
+        <v>1.66971969604492</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G574" t="n">
-        <v>1.6697199344635</v>
+        <v>1.66971969604492</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G575" t="n">
-        <v>1.6697199344635</v>
+        <v>1.66971969604492</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G576" t="n">
-        <v>1.6697199344635</v>
+        <v>1.66971969604492</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G577" t="n">
-        <v>1.6697199344635</v>
+        <v>1.66971969604492</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G581" t="n">
-        <v>1.68729591369629</v>
+        <v>1.687295794487</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G590" t="n">
-        <v>1.65653789043427</v>
+        <v>1.65653777122498</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G592" t="n">
-        <v>1.61699187755585</v>
+        <v>1.61699175834656</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G593" t="n">
-        <v>1.55547595024109</v>
+        <v>1.5554758310318</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G594" t="n">
-        <v>1.55986988544464</v>
+        <v>1.55986976623535</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>1.875</v>
       </c>
       <c r="G595" t="n">
-        <v>1.64774978160858</v>
+        <v>1.64774990081787</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>1.875</v>
       </c>
       <c r="G596" t="n">
-        <v>1.64774978160858</v>
+        <v>1.64774990081787</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G597" t="n">
-        <v>1.61699187755585</v>
+        <v>1.61699175834656</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G598" t="n">
-        <v>1.63896179199219</v>
+        <v>1.63896191120148</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G599" t="n">
-        <v>1.63896179199219</v>
+        <v>1.63896191120148</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G600" t="n">
-        <v>1.59941589832306</v>
+        <v>1.59941601753235</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G601" t="n">
-        <v>1.59941589832306</v>
+        <v>1.59941601753235</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G602" t="n">
-        <v>1.59941589832306</v>
+        <v>1.59941601753235</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G604" t="n">
-        <v>1.60380983352661</v>
+        <v>1.6038099527359</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G605" t="n">
-        <v>1.60380983352661</v>
+        <v>1.6038099527359</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G606" t="n">
-        <v>1.63896179199219</v>
+        <v>1.63896191120148</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G607" t="n">
-        <v>1.61699187755585</v>
+        <v>1.61699175834656</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G608" t="n">
-        <v>1.58183991909027</v>
+        <v>1.58183979988098</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G610" t="n">
-        <v>1.57744574546814</v>
+        <v>1.57744586467743</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G611" t="n">
-        <v>1.57744574546814</v>
+        <v>1.57744586467743</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G613" t="n">
-        <v>1.57744574546814</v>
+        <v>1.57744586467743</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G614" t="n">
-        <v>1.57744574546814</v>
+        <v>1.57744586467743</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G615" t="n">
-        <v>1.57744574546814</v>
+        <v>1.57744586467743</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G616" t="n">
-        <v>1.56865787506104</v>
+        <v>1.56865775585175</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G617" t="n">
-        <v>1.7532057762146</v>
+        <v>1.75320589542389</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G621" t="n">
-        <v>1.6697199344635</v>
+        <v>1.66971969604492</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G622" t="n">
-        <v>1.68290174007416</v>
+        <v>1.68290185928345</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G623" t="n">
-        <v>1.69608378410339</v>
+        <v>1.69608390331268</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G624" t="n">
-        <v>1.6697199344635</v>
+        <v>1.66971969604492</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G629" t="n">
-        <v>1.88063192367554</v>
+        <v>1.88063216209412</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G630" t="n">
-        <v>1.88941991329193</v>
+        <v>1.88942003250122</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G631" t="n">
-        <v>1.81032776832581</v>
+        <v>1.81032764911652</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G632" t="n">
-        <v>1.86305570602417</v>
+        <v>1.86305582523346</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G634" t="n">
-        <v>1.81032776832581</v>
+        <v>1.81032764911652</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G635" t="n">
-        <v>1.74441778659821</v>
+        <v>1.7444179058075</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G637" t="n">
-        <v>1.71365988254547</v>
+        <v>1.71365976333618</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G639" t="n">
-        <v>1.64335572719574</v>
+        <v>1.64335584640503</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G644" t="n">
-        <v>1.66093194484711</v>
+        <v>1.66093182563782</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G645" t="n">
-        <v>1.66093194484711</v>
+        <v>1.66093182563782</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G646" t="n">
-        <v>1.62138593196869</v>
+        <v>1.62138569355011</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G647" t="n">
-        <v>1.66532588005066</v>
+        <v>1.66532576084137</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G648" t="n">
-        <v>1.69608378410339</v>
+        <v>1.69608390331268</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G650" t="n">
-        <v>1.74881172180176</v>
+        <v>1.74881184101105</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G651" t="n">
-        <v>1.71365988254547</v>
+        <v>1.71365976333618</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G669" t="n">
-        <v>1.66985738277435</v>
+        <v>1.66985726356506</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G671" t="n">
-        <v>1.63375210762024</v>
+        <v>1.63375222682953</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G672" t="n">
-        <v>1.63375210762024</v>
+        <v>1.63375222682953</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G677" t="n">
-        <v>1.60667335987091</v>
+        <v>1.6066734790802</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G678" t="n">
-        <v>1.60667335987091</v>
+        <v>1.6066734790802</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G679" t="n">
-        <v>1.63375210762024</v>
+        <v>1.63375222682953</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G680" t="n">
-        <v>1.63375210762024</v>
+        <v>1.63375222682953</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G681" t="n">
-        <v>1.62472593784332</v>
+        <v>1.62472605705261</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G682" t="n">
-        <v>1.62472593784332</v>
+        <v>1.62472605705261</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G683" t="n">
-        <v>1.62472593784332</v>
+        <v>1.62472605705261</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G685" t="n">
-        <v>1.60667335987091</v>
+        <v>1.6066734790802</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G686" t="n">
-        <v>1.60667335987091</v>
+        <v>1.6066734790802</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G687" t="n">
-        <v>1.60667335987091</v>
+        <v>1.6066734790802</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G688" t="n">
-        <v>1.60667335987091</v>
+        <v>1.6066734790802</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G690" t="n">
-        <v>1.60667335987091</v>
+        <v>1.6066734790802</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G691" t="n">
-        <v>1.60667335987091</v>
+        <v>1.6066734790802</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G692" t="n">
-        <v>1.61569964885712</v>
+        <v>1.61569976806641</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G693" t="n">
-        <v>1.61569964885712</v>
+        <v>1.61569976806641</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G694" t="n">
-        <v>1.61569964885712</v>
+        <v>1.61569976806641</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G697" t="n">
-        <v>1.53446340560913</v>
+        <v>1.53446352481842</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G714" t="n">
-        <v>1.53446340560913</v>
+        <v>1.53446352481842</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G715" t="n">
-        <v>1.53446340560913</v>
+        <v>1.53446352481842</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G719" t="n">
-        <v>1.53446340560913</v>
+        <v>1.53446352481842</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G737" t="n">
-        <v>1.53446340560913</v>
+        <v>1.53446352481842</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G747" t="n">
-        <v>1.53446340560913</v>
+        <v>1.53446352481842</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G748" t="n">
-        <v>1.53446340560913</v>
+        <v>1.53446352481842</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G749" t="n">
-        <v>1.53446340560913</v>
+        <v>1.53446352481842</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G750" t="n">
-        <v>1.53446340560913</v>
+        <v>1.53446352481842</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G753" t="n">
-        <v>1.49835848808289</v>
+        <v>1.49835824966431</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G754" t="n">
-        <v>1.46225333213806</v>
+        <v>1.46225345134735</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G766" t="n">
-        <v>1.48030591011047</v>
+        <v>1.48030579090118</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G779" t="n">
-        <v>1.48030591011047</v>
+        <v>1.48030579090118</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G781" t="n">
-        <v>1.41712212562561</v>
+        <v>1.4171222448349</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G782" t="n">
-        <v>1.53446340560913</v>
+        <v>1.53446352481842</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G783" t="n">
-        <v>1.46225333213806</v>
+        <v>1.46225345134735</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G784" t="n">
-        <v>1.49835848808289</v>
+        <v>1.49835824966431</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G788" t="n">
-        <v>1.48030591011047</v>
+        <v>1.48030579090118</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G789" t="n">
-        <v>1.48030591011047</v>
+        <v>1.48030579090118</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G794" t="n">
-        <v>1.98577630519867</v>
+        <v>1.98577618598938</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G795" t="n">
-        <v>1.87746119499207</v>
+        <v>1.87746095657349</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G796" t="n">
-        <v>1.66985738277435</v>
+        <v>1.66985726356506</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G799" t="n">
-        <v>1.77817237377167</v>
+        <v>1.77817225456238</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G804" t="n">
-        <v>1.87746119499207</v>
+        <v>1.87746095657349</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G806" t="n">
-        <v>1.89551365375519</v>
+        <v>1.8955135345459</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G808" t="n">
-        <v>1.87746119499207</v>
+        <v>1.87746095657349</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G812" t="n">
-        <v>1.87746119499207</v>
+        <v>1.87746095657349</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G813" t="n">
-        <v>1.91356599330902</v>
+        <v>1.9135662317276</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G814" t="n">
-        <v>1.87746119499207</v>
+        <v>1.87746095657349</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G822" t="n">
-        <v>1.77817237377167</v>
+        <v>1.77817225456238</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G828" t="n">
-        <v>1.72401475906372</v>
+        <v>1.72401487827301</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G829" t="n">
-        <v>1.72401475906372</v>
+        <v>1.72401487827301</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G832" t="n">
-        <v>1.77817237377167</v>
+        <v>1.77817225456238</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G833" t="n">
-        <v>1.74206721782684</v>
+        <v>1.74206733703613</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G837" t="n">
-        <v>1.77817237377167</v>
+        <v>1.77817225456238</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G838" t="n">
-        <v>1.74206721782684</v>
+        <v>1.74206733703613</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G839" t="n">
-        <v>1.74206721782684</v>
+        <v>1.74206733703613</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G842" t="n">
-        <v>1.72401475906372</v>
+        <v>1.72401487827301</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>2</v>
       </c>
       <c r="G846" t="n">
-        <v>1.80525100231171</v>
+        <v>1.805251121521</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>2</v>
       </c>
       <c r="G847" t="n">
-        <v>1.80525100231171</v>
+        <v>1.805251121521</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>2</v>
       </c>
       <c r="G848" t="n">
-        <v>1.80525100231171</v>
+        <v>1.805251121521</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G850" t="n">
-        <v>1.77817237377167</v>
+        <v>1.77817225456238</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G852" t="n">
-        <v>1.77817237377167</v>
+        <v>1.77817225456238</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G853" t="n">
-        <v>1.77817237377167</v>
+        <v>1.77817225456238</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>2</v>
       </c>
       <c r="G861" t="n">
-        <v>1.80525100231171</v>
+        <v>1.805251121521</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>2</v>
       </c>
       <c r="G864" t="n">
-        <v>1.80525100231171</v>
+        <v>1.805251121521</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G866" t="n">
-        <v>1.87746119499207</v>
+        <v>1.87746095657349</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G867" t="n">
-        <v>1.91356599330902</v>
+        <v>1.9135662317276</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G868" t="n">
-        <v>1.98577630519867</v>
+        <v>1.98577618598938</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G869" t="n">
-        <v>1.98577630519867</v>
+        <v>1.98577618598938</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G871" t="n">
-        <v>2.07603859901428</v>
+        <v>2.07603883743286</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G874" t="n">
-        <v>1.98577630519867</v>
+        <v>1.98577618598938</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G876" t="n">
-        <v>2.00382876396179</v>
+        <v>2.00382852554321</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G877" t="n">
-        <v>1.94967114925385</v>
+        <v>1.94967126846313</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G879" t="n">
-        <v>1.94967114925385</v>
+        <v>1.94967126846313</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G880" t="n">
-        <v>1.94967114925385</v>
+        <v>1.94967126846313</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G881" t="n">
-        <v>1.94967114925385</v>
+        <v>1.94967126846313</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G882" t="n">
-        <v>1.94967114925385</v>
+        <v>1.94967126846313</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G883" t="n">
-        <v>1.98577630519867</v>
+        <v>1.98577618598938</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G884" t="n">
-        <v>2.07603859901428</v>
+        <v>2.07603883743286</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G885" t="n">
-        <v>2.20240640640259</v>
+        <v>2.20240616798401</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G886" t="n">
-        <v>2.16630125045776</v>
+        <v>2.16630148887634</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G887" t="n">
-        <v>2.16630125045776</v>
+        <v>2.16630148887634</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G888" t="n">
-        <v>2.16630125045776</v>
+        <v>2.16630148887634</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>2.5</v>
       </c>
       <c r="G889" t="n">
-        <v>2.25656390190125</v>
+        <v>2.25656414031982</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G890" t="n">
-        <v>2.20240640640259</v>
+        <v>2.20240616798401</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G892" t="n">
-        <v>2.07603859901428</v>
+        <v>2.07603883743286</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G893" t="n">
-        <v>2.07603859901428</v>
+        <v>2.07603883743286</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G894" t="n">
-        <v>2.0218813419342</v>
+        <v>2.02188110351562</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G896" t="n">
-        <v>1.94967114925385</v>
+        <v>1.94967126846313</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G897" t="n">
-        <v>1.91356599330902</v>
+        <v>1.9135662317276</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G898" t="n">
-        <v>1.87746119499207</v>
+        <v>1.87746095657349</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G900" t="n">
-        <v>1.87746119499207</v>
+        <v>1.87746095657349</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G903" t="n">
-        <v>1.91356599330902</v>
+        <v>1.9135662317276</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G905" t="n">
-        <v>1.94967114925385</v>
+        <v>1.94967126846313</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G906" t="n">
-        <v>1.91356599330902</v>
+        <v>1.9135662317276</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G911" t="n">
-        <v>1.87746119499207</v>
+        <v>1.87746095657349</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G914" t="n">
-        <v>1.89551365375519</v>
+        <v>1.8955135345459</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G915" t="n">
-        <v>1.87746119499207</v>
+        <v>1.87746095657349</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G916" t="n">
-        <v>1.87746119499207</v>
+        <v>1.87746095657349</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -40724,6 +40724,32 @@
         <v>1.57000005245209</v>
       </c>
       <c r="H1552" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1553">
+      <c r="A1553" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B1553" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C1553" t="n">
+        <v>1.54999995231628</v>
+      </c>
+      <c r="D1553" t="n">
+        <v>1.54999995231628</v>
+      </c>
+      <c r="E1553" t="n">
+        <v>1.54999995231628</v>
+      </c>
+      <c r="F1553" t="n">
+        <v>1.55999994277954</v>
+      </c>
+      <c r="G1553" t="n">
+        <v>1.55999994277954</v>
+      </c>
+      <c r="H1553" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RETI.MI.xlsx
+++ b/data/RETI.MI.xlsx
@@ -456,7 +456,7 @@
         <v>0.899600028991699</v>
       </c>
       <c r="G3" t="n">
-        <v>0.768140971660614</v>
+        <v>0.768141031265259</v>
       </c>
       <c r="H3" t="n">
         <v>472500</v>
@@ -630,7 +630,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G9" t="n">
-        <v>0.732620000839233</v>
+        <v>0.732619941234589</v>
       </c>
       <c r="H9" t="n">
         <v>118500</v>
@@ -659,7 +659,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G10" t="n">
-        <v>0.722373604774475</v>
+        <v>0.72237354516983</v>
       </c>
       <c r="H10" t="n">
         <v>48000</v>
@@ -688,7 +688,7 @@
         <v>0.84799998998642</v>
       </c>
       <c r="G11" t="n">
-        <v>0.724081218242645</v>
+        <v>0.72408127784729</v>
       </c>
       <c r="H11" t="n">
         <v>39000</v>
@@ -775,7 +775,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G14" t="n">
-        <v>0.683095574378967</v>
+        <v>0.683095633983612</v>
       </c>
       <c r="H14" t="n">
         <v>18000</v>
@@ -804,7 +804,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G15" t="n">
-        <v>0.683095574378967</v>
+        <v>0.683095633983612</v>
       </c>
       <c r="H15" t="n">
         <v>42000</v>
@@ -862,7 +862,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G17" t="n">
-        <v>0.654063999652863</v>
+        <v>0.654063940048218</v>
       </c>
       <c r="H17" t="n">
         <v>25500</v>
@@ -891,7 +891,7 @@
         <v>0.833999991416931</v>
       </c>
       <c r="G18" t="n">
-        <v>0.712127029895782</v>
+        <v>0.712127089500427</v>
       </c>
       <c r="H18" t="n">
         <v>579000</v>
@@ -978,7 +978,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G21" t="n">
-        <v>0.654063999652863</v>
+        <v>0.654063940048218</v>
       </c>
       <c r="H21" t="n">
         <v>132000</v>
@@ -1065,7 +1065,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G24" t="n">
-        <v>0.652356207370758</v>
+        <v>0.652356326580048</v>
       </c>
       <c r="H24" t="n">
         <v>10500</v>
@@ -1094,7 +1094,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G25" t="n">
-        <v>0.660894989967346</v>
+        <v>0.660894930362701</v>
       </c>
       <c r="H25" t="n">
         <v>12000</v>
@@ -1123,7 +1123,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G26" t="n">
-        <v>0.654063999652863</v>
+        <v>0.654063940048218</v>
       </c>
       <c r="H26" t="n">
         <v>27000</v>
@@ -1152,7 +1152,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G27" t="n">
-        <v>0.633571147918701</v>
+        <v>0.633571088314056</v>
       </c>
       <c r="H27" t="n">
         <v>43500</v>
@@ -1181,7 +1181,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G28" t="n">
-        <v>0.631863355636597</v>
+        <v>0.631863415241241</v>
       </c>
       <c r="H28" t="n">
         <v>33000</v>
@@ -1210,7 +1210,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G29" t="n">
-        <v>0.623324751853943</v>
+        <v>0.623324632644653</v>
       </c>
       <c r="H29" t="n">
         <v>46500</v>
@@ -1239,7 +1239,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G30" t="n">
-        <v>0.607955038547516</v>
+        <v>0.607955098152161</v>
       </c>
       <c r="H30" t="n">
         <v>19500</v>
@@ -1268,7 +1268,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G31" t="n">
-        <v>0.58746212720871</v>
+        <v>0.587462246417999</v>
       </c>
       <c r="H31" t="n">
         <v>78000</v>
@@ -1297,7 +1297,7 @@
         <v>0.73199999332428</v>
       </c>
       <c r="G32" t="n">
-        <v>0.625032424926758</v>
+        <v>0.625032484531403</v>
       </c>
       <c r="H32" t="n">
         <v>27000</v>
@@ -1326,7 +1326,7 @@
         <v>0.722000002861023</v>
       </c>
       <c r="G33" t="n">
-        <v>0.616493761539459</v>
+        <v>0.616493701934814</v>
       </c>
       <c r="H33" t="n">
         <v>3000</v>
@@ -1384,7 +1384,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G35" t="n">
-        <v>0.58063131570816</v>
+        <v>0.580631256103516</v>
       </c>
       <c r="H35" t="n">
         <v>12000</v>
@@ -1413,7 +1413,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G36" t="n">
-        <v>0.563553869724274</v>
+        <v>0.563553810119629</v>
       </c>
       <c r="H36" t="n">
         <v>66000</v>
@@ -1442,7 +1442,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G37" t="n">
-        <v>0.537937760353088</v>
+        <v>0.537937700748444</v>
       </c>
       <c r="H37" t="n">
         <v>27000</v>
@@ -1471,7 +1471,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G38" t="n">
-        <v>0.537937760353088</v>
+        <v>0.537937700748444</v>
       </c>
       <c r="H38" t="n">
         <v>13500</v>
@@ -1500,7 +1500,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G39" t="n">
-        <v>0.52598363161087</v>
+        <v>0.525983512401581</v>
       </c>
       <c r="H39" t="n">
         <v>10500</v>
@@ -1529,7 +1529,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G40" t="n">
-        <v>0.546476483345032</v>
+        <v>0.546476423740387</v>
       </c>
       <c r="H40" t="n">
         <v>15000</v>
@@ -1558,7 +1558,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G41" t="n">
-        <v>0.537937760353088</v>
+        <v>0.537937700748444</v>
       </c>
       <c r="H41" t="n">
         <v>16500</v>
@@ -1587,7 +1587,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G42" t="n">
-        <v>0.604539573192596</v>
+        <v>0.604539513587952</v>
       </c>
       <c r="H42" t="n">
         <v>127500</v>
@@ -1616,7 +1616,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G43" t="n">
-        <v>0.623324751853943</v>
+        <v>0.623324632644653</v>
       </c>
       <c r="H43" t="n">
         <v>138000</v>
@@ -1645,7 +1645,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G44" t="n">
-        <v>0.604539573192596</v>
+        <v>0.604539513587952</v>
       </c>
       <c r="H44" t="n">
         <v>64500</v>
@@ -1703,7 +1703,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G46" t="n">
-        <v>0.631863355636597</v>
+        <v>0.631863415241241</v>
       </c>
       <c r="H46" t="n">
         <v>6000</v>
@@ -1732,7 +1732,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G47" t="n">
-        <v>0.607955038547516</v>
+        <v>0.607955098152161</v>
       </c>
       <c r="H47" t="n">
         <v>7500</v>
@@ -1761,7 +1761,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G48" t="n">
-        <v>0.611370503902435</v>
+        <v>0.61137056350708</v>
       </c>
       <c r="H48" t="n">
         <v>21000</v>
@@ -1819,7 +1819,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G50" t="n">
-        <v>0.631863355636597</v>
+        <v>0.631863415241241</v>
       </c>
       <c r="H50" t="n">
         <v>12000</v>
@@ -1906,7 +1906,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G53" t="n">
-        <v>0.701880693435669</v>
+        <v>0.701880633831024</v>
       </c>
       <c r="H53" t="n">
         <v>70500</v>
@@ -1935,7 +1935,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G54" t="n">
-        <v>0.674556851387024</v>
+        <v>0.674556910991669</v>
       </c>
       <c r="H54" t="n">
         <v>115500</v>
@@ -1993,7 +1993,7 @@
         <v>0.815999984741211</v>
       </c>
       <c r="G56" t="n">
-        <v>0.696757435798645</v>
+        <v>0.69675749540329</v>
       </c>
       <c r="H56" t="n">
         <v>28500</v>
@@ -2051,7 +2051,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G58" t="n">
-        <v>0.703588426113129</v>
+        <v>0.703588485717773</v>
       </c>
       <c r="H58" t="n">
         <v>12000</v>
@@ -2080,7 +2080,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G59" t="n">
-        <v>0.683095574378967</v>
+        <v>0.683095633983612</v>
       </c>
       <c r="H59" t="n">
         <v>6000</v>
@@ -2109,7 +2109,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G60" t="n">
-        <v>0.683095574378967</v>
+        <v>0.683095633983612</v>
       </c>
       <c r="H60" t="n">
         <v>1500</v>
@@ -2138,7 +2138,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G61" t="n">
-        <v>0.683095574378967</v>
+        <v>0.683095633983612</v>
       </c>
       <c r="H61" t="n">
         <v>102000</v>
@@ -2196,7 +2196,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G63" t="n">
-        <v>0.679679989814758</v>
+        <v>0.679680049419403</v>
       </c>
       <c r="H63" t="n">
         <v>42000</v>
@@ -2225,7 +2225,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G64" t="n">
-        <v>0.683095574378967</v>
+        <v>0.683095633983612</v>
       </c>
       <c r="H64" t="n">
         <v>7500</v>
@@ -2283,7 +2283,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G66" t="n">
-        <v>0.674556851387024</v>
+        <v>0.674556910991669</v>
       </c>
       <c r="H66" t="n">
         <v>10500</v>
@@ -2312,7 +2312,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G67" t="n">
-        <v>0.683095574378967</v>
+        <v>0.683095633983612</v>
       </c>
       <c r="H67" t="n">
         <v>7500</v>
@@ -2341,7 +2341,7 @@
         <v>0.815999984741211</v>
       </c>
       <c r="G68" t="n">
-        <v>0.696757435798645</v>
+        <v>0.69675749540329</v>
       </c>
       <c r="H68" t="n">
         <v>7500</v>
@@ -2370,7 +2370,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G69" t="n">
-        <v>0.69334203004837</v>
+        <v>0.693341970443726</v>
       </c>
       <c r="H69" t="n">
         <v>15000</v>
@@ -2457,7 +2457,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G72" t="n">
-        <v>0.69334203004837</v>
+        <v>0.693341970443726</v>
       </c>
       <c r="H72" t="n">
         <v>3000</v>
@@ -2573,7 +2573,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G76" t="n">
-        <v>0.707003891468048</v>
+        <v>0.707003831863403</v>
       </c>
       <c r="H76" t="n">
         <v>7500</v>
@@ -2689,7 +2689,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G80" t="n">
-        <v>0.717250287532806</v>
+        <v>0.717250347137451</v>
       </c>
       <c r="H80" t="n">
         <v>28500</v>
@@ -2747,7 +2747,7 @@
         <v>0.833999991416931</v>
       </c>
       <c r="G82" t="n">
-        <v>0.712127029895782</v>
+        <v>0.712127089500427</v>
       </c>
       <c r="H82" t="n">
         <v>4500</v>
@@ -2776,7 +2776,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G83" t="n">
-        <v>0.715542554855347</v>
+        <v>0.715542614459991</v>
       </c>
       <c r="H83" t="n">
         <v>1500</v>
@@ -2805,7 +2805,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G84" t="n">
-        <v>0.717250287532806</v>
+        <v>0.717250347137451</v>
       </c>
       <c r="H84" t="n">
         <v>1500</v>
@@ -2834,7 +2834,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G85" t="n">
-        <v>0.715542554855347</v>
+        <v>0.715542614459991</v>
       </c>
       <c r="H85" t="n">
         <v>9000</v>
@@ -3008,7 +3008,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G91" t="n">
-        <v>0.701880693435669</v>
+        <v>0.701880633831024</v>
       </c>
       <c r="H91" t="n">
         <v>10500</v>
@@ -3037,7 +3037,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G92" t="n">
-        <v>0.701880693435669</v>
+        <v>0.701880633831024</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
@@ -3066,7 +3066,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G93" t="n">
-        <v>0.701880693435669</v>
+        <v>0.701880633831024</v>
       </c>
       <c r="H93" t="n">
         <v>1500</v>
@@ -3095,7 +3095,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G94" t="n">
-        <v>0.698465287685394</v>
+        <v>0.69846522808075</v>
       </c>
       <c r="H94" t="n">
         <v>19500</v>
@@ -3124,7 +3124,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G95" t="n">
-        <v>0.683095574378967</v>
+        <v>0.683095633983612</v>
       </c>
       <c r="H95" t="n">
         <v>3000</v>
@@ -3153,7 +3153,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G96" t="n">
-        <v>0.674556851387024</v>
+        <v>0.674556910991669</v>
       </c>
       <c r="H96" t="n">
         <v>12000</v>
@@ -3327,7 +3327,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G102" t="n">
-        <v>0.683095574378967</v>
+        <v>0.683095633983612</v>
       </c>
       <c r="H102" t="n">
         <v>10500</v>
@@ -3356,7 +3356,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G103" t="n">
-        <v>0.707003891468048</v>
+        <v>0.707003831863403</v>
       </c>
       <c r="H103" t="n">
         <v>22500</v>
@@ -3385,7 +3385,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G104" t="n">
-        <v>0.683095574378967</v>
+        <v>0.683095633983612</v>
       </c>
       <c r="H104" t="n">
         <v>49500</v>
@@ -3414,7 +3414,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G105" t="n">
-        <v>0.683095574378967</v>
+        <v>0.683095633983612</v>
       </c>
       <c r="H105" t="n">
         <v>13500</v>
@@ -3443,7 +3443,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G106" t="n">
-        <v>0.683095574378967</v>
+        <v>0.683095633983612</v>
       </c>
       <c r="H106" t="n">
         <v>1500</v>
@@ -3530,7 +3530,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G109" t="n">
-        <v>0.683095574378967</v>
+        <v>0.683095633983612</v>
       </c>
       <c r="H109" t="n">
         <v>13500</v>
@@ -3559,7 +3559,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G110" t="n">
-        <v>0.698465287685394</v>
+        <v>0.69846522808075</v>
       </c>
       <c r="H110" t="n">
         <v>6000</v>
@@ -3588,7 +3588,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G111" t="n">
-        <v>0.703588426113129</v>
+        <v>0.703588485717773</v>
       </c>
       <c r="H111" t="n">
         <v>24000</v>
@@ -3704,7 +3704,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G115" t="n">
-        <v>0.703588426113129</v>
+        <v>0.703588485717773</v>
       </c>
       <c r="H115" t="n">
         <v>7500</v>
@@ -3733,7 +3733,7 @@
         <v>0.86599999666214</v>
       </c>
       <c r="G116" t="n">
-        <v>0.739450871944427</v>
+        <v>0.739450931549072</v>
       </c>
       <c r="H116" t="n">
         <v>108000</v>
@@ -3791,7 +3791,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G118" t="n">
-        <v>0.717250287532806</v>
+        <v>0.717250347137451</v>
       </c>
       <c r="H118" t="n">
         <v>69000</v>
@@ -3820,7 +3820,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G119" t="n">
-        <v>0.715542554855347</v>
+        <v>0.715542614459991</v>
       </c>
       <c r="H119" t="n">
         <v>16500</v>
@@ -3936,7 +3936,7 @@
         <v>0.972000002861023</v>
       </c>
       <c r="G123" t="n">
-        <v>0.829961121082306</v>
+        <v>0.829961061477661</v>
       </c>
       <c r="H123" t="n">
         <v>922500</v>
@@ -3994,7 +3994,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G125" t="n">
-        <v>0.83679211139679</v>
+        <v>0.836792051792145</v>
       </c>
       <c r="H125" t="n">
         <v>196500</v>
@@ -4023,7 +4023,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G126" t="n">
-        <v>0.83679211139679</v>
+        <v>0.836792051792145</v>
       </c>
       <c r="H126" t="n">
         <v>76500</v>
@@ -4081,7 +4081,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G128" t="n">
-        <v>0.862408101558685</v>
+        <v>0.86240816116333</v>
       </c>
       <c r="H128" t="n">
         <v>60000</v>
@@ -4110,7 +4110,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G129" t="n">
-        <v>0.862408101558685</v>
+        <v>0.86240816116333</v>
       </c>
       <c r="H129" t="n">
         <v>25500</v>
@@ -4139,7 +4139,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G130" t="n">
-        <v>0.862408101558685</v>
+        <v>0.86240816116333</v>
       </c>
       <c r="H130" t="n">
         <v>72000</v>
@@ -4197,7 +4197,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G132" t="n">
-        <v>0.845330774784088</v>
+        <v>0.845330715179443</v>
       </c>
       <c r="H132" t="n">
         <v>25500</v>
@@ -4226,7 +4226,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G133" t="n">
-        <v>0.870946705341339</v>
+        <v>0.870946824550629</v>
       </c>
       <c r="H133" t="n">
         <v>19500</v>
@@ -4255,7 +4255,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G134" t="n">
-        <v>0.875216126441956</v>
+        <v>0.8752161860466</v>
       </c>
       <c r="H134" t="n">
         <v>19500</v>
@@ -4400,7 +4400,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G139" t="n">
-        <v>0.913640260696411</v>
+        <v>0.913640320301056</v>
       </c>
       <c r="H139" t="n">
         <v>4500</v>
@@ -4429,7 +4429,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G140" t="n">
-        <v>0.922179043292999</v>
+        <v>0.922178983688354</v>
       </c>
       <c r="H140" t="n">
         <v>22500</v>
@@ -4458,7 +4458,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G141" t="n">
-        <v>0.922179043292999</v>
+        <v>0.922178983688354</v>
       </c>
       <c r="H141" t="n">
         <v>67500</v>
@@ -4487,7 +4487,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G142" t="n">
-        <v>0.913640260696411</v>
+        <v>0.913640320301056</v>
       </c>
       <c r="H142" t="n">
         <v>42000</v>
@@ -4516,7 +4516,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G143" t="n">
-        <v>0.930717766284943</v>
+        <v>0.930717647075653</v>
       </c>
       <c r="H143" t="n">
         <v>45000</v>
@@ -4719,7 +4719,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G150" t="n">
-        <v>1.18637979030609</v>
+        <v>1.18638002872467</v>
       </c>
       <c r="H150" t="n">
         <v>103500</v>
@@ -4864,7 +4864,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G155" t="n">
-        <v>1.13804590702057</v>
+        <v>1.13804578781128</v>
       </c>
       <c r="H155" t="n">
         <v>30000</v>
@@ -4893,7 +4893,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G156" t="n">
-        <v>1.14683389663696</v>
+        <v>1.14683377742767</v>
       </c>
       <c r="H156" t="n">
         <v>15000</v>
@@ -4980,7 +4980,7 @@
         <v>1.25499999523163</v>
       </c>
       <c r="G159" t="n">
-        <v>1.10289394855499</v>
+        <v>1.1028938293457</v>
       </c>
       <c r="H159" t="n">
         <v>19500</v>
@@ -5009,7 +5009,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G160" t="n">
-        <v>1.05455982685089</v>
+        <v>1.05455994606018</v>
       </c>
       <c r="H160" t="n">
         <v>49500</v>
@@ -5038,7 +5038,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G161" t="n">
-        <v>1.08971202373505</v>
+        <v>1.08971190452576</v>
       </c>
       <c r="H161" t="n">
         <v>136500</v>
@@ -5154,7 +5154,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G165" t="n">
-        <v>1.16880393028259</v>
+        <v>1.1688038110733</v>
       </c>
       <c r="H165" t="n">
         <v>52500</v>
@@ -5183,7 +5183,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G166" t="n">
-        <v>1.1600159406662</v>
+        <v>1.16001582145691</v>
       </c>
       <c r="H166" t="n">
         <v>49500</v>
@@ -5241,7 +5241,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G168" t="n">
-        <v>1.14683389663696</v>
+        <v>1.14683377742767</v>
       </c>
       <c r="H168" t="n">
         <v>49500</v>
@@ -5299,7 +5299,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G170" t="n">
-        <v>1.14683389663696</v>
+        <v>1.14683377742767</v>
       </c>
       <c r="H170" t="n">
         <v>9000</v>
@@ -5328,7 +5328,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G171" t="n">
-        <v>1.13804590702057</v>
+        <v>1.13804578781128</v>
       </c>
       <c r="H171" t="n">
         <v>9000</v>
@@ -5386,7 +5386,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G173" t="n">
-        <v>1.18637979030609</v>
+        <v>1.18638002872467</v>
       </c>
       <c r="H173" t="n">
         <v>85500</v>
@@ -5415,7 +5415,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G174" t="n">
-        <v>1.18198597431183</v>
+        <v>1.18198585510254</v>
       </c>
       <c r="H174" t="n">
         <v>24000</v>
@@ -5444,7 +5444,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G175" t="n">
-        <v>1.23031985759735</v>
+        <v>1.23031973838806</v>
       </c>
       <c r="H175" t="n">
         <v>234000</v>
@@ -5589,7 +5589,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G180" t="n">
-        <v>1.34895777702332</v>
+        <v>1.3489578962326</v>
       </c>
       <c r="H180" t="n">
         <v>9000</v>
@@ -5792,7 +5792,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G187" t="n">
-        <v>1.3006237745285</v>
+        <v>1.30062401294708</v>
       </c>
       <c r="H187" t="n">
         <v>25500</v>
@@ -5821,7 +5821,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G188" t="n">
-        <v>1.34895777702332</v>
+        <v>1.3489578962326</v>
       </c>
       <c r="H188" t="n">
         <v>36000</v>
@@ -5850,7 +5850,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G189" t="n">
-        <v>1.45001995563507</v>
+        <v>1.45001983642578</v>
       </c>
       <c r="H189" t="n">
         <v>148500</v>
@@ -5879,7 +5879,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G190" t="n">
-        <v>1.41486787796021</v>
+        <v>1.41486799716949</v>
       </c>
       <c r="H190" t="n">
         <v>154500</v>
@@ -5966,7 +5966,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G193" t="n">
-        <v>1.34895777702332</v>
+        <v>1.3489578962326</v>
       </c>
       <c r="H193" t="n">
         <v>34500</v>
@@ -5995,7 +5995,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G194" t="n">
-        <v>1.34016990661621</v>
+        <v>1.34016978740692</v>
       </c>
       <c r="H194" t="n">
         <v>85500</v>
@@ -6024,7 +6024,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G195" t="n">
-        <v>1.34456384181976</v>
+        <v>1.34456372261047</v>
       </c>
       <c r="H195" t="n">
         <v>18000</v>
@@ -6111,7 +6111,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G198" t="n">
-        <v>1.32698798179626</v>
+        <v>1.32698786258698</v>
       </c>
       <c r="H198" t="n">
         <v>13500</v>
@@ -6169,7 +6169,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G200" t="n">
-        <v>1.34895777702332</v>
+        <v>1.3489578962326</v>
       </c>
       <c r="H200" t="n">
         <v>22500</v>
@@ -6343,7 +6343,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G206" t="n">
-        <v>1.34456384181976</v>
+        <v>1.34456372261047</v>
       </c>
       <c r="H206" t="n">
         <v>18000</v>
@@ -6372,7 +6372,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G207" t="n">
-        <v>1.34456384181976</v>
+        <v>1.34456372261047</v>
       </c>
       <c r="H207" t="n">
         <v>4500</v>
@@ -6488,7 +6488,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G211" t="n">
-        <v>1.2918359041214</v>
+        <v>1.29183602333069</v>
       </c>
       <c r="H211" t="n">
         <v>45000</v>
@@ -6517,7 +6517,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G212" t="n">
-        <v>1.3094117641449</v>
+        <v>1.30941188335419</v>
       </c>
       <c r="H212" t="n">
         <v>4500</v>
@@ -6546,7 +6546,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G213" t="n">
-        <v>1.3006237745285</v>
+        <v>1.30062401294708</v>
       </c>
       <c r="H213" t="n">
         <v>6000</v>
@@ -6575,7 +6575,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G214" t="n">
-        <v>1.34895777702332</v>
+        <v>1.3489578962326</v>
       </c>
       <c r="H214" t="n">
         <v>28500</v>
@@ -6604,7 +6604,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G215" t="n">
-        <v>1.32698798179626</v>
+        <v>1.32698786258698</v>
       </c>
       <c r="H215" t="n">
         <v>13500</v>
@@ -6662,7 +6662,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G217" t="n">
-        <v>1.3094117641449</v>
+        <v>1.30941188335419</v>
       </c>
       <c r="H217" t="n">
         <v>10500</v>
@@ -6720,7 +6720,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G219" t="n">
-        <v>1.23031985759735</v>
+        <v>1.23031973838806</v>
       </c>
       <c r="H219" t="n">
         <v>70500</v>
@@ -6807,7 +6807,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G222" t="n">
-        <v>1.2918359041214</v>
+        <v>1.29183602333069</v>
       </c>
       <c r="H222" t="n">
         <v>9000</v>
@@ -6836,7 +6836,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G223" t="n">
-        <v>1.3094117641449</v>
+        <v>1.30941188335419</v>
       </c>
       <c r="H223" t="n">
         <v>6000</v>
@@ -6923,7 +6923,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G226" t="n">
-        <v>1.3006237745285</v>
+        <v>1.30062401294708</v>
       </c>
       <c r="H226" t="n">
         <v>4500</v>
@@ -6981,7 +6981,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G228" t="n">
-        <v>1.2918359041214</v>
+        <v>1.29183602333069</v>
       </c>
       <c r="H228" t="n">
         <v>27000</v>
@@ -7097,7 +7097,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G232" t="n">
-        <v>1.34456384181976</v>
+        <v>1.34456372261047</v>
       </c>
       <c r="H232" t="n">
         <v>45000</v>
@@ -7126,7 +7126,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G233" t="n">
-        <v>1.34016990661621</v>
+        <v>1.34016978740692</v>
       </c>
       <c r="H233" t="n">
         <v>61500</v>
@@ -7184,7 +7184,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G235" t="n">
-        <v>1.34456384181976</v>
+        <v>1.34456372261047</v>
       </c>
       <c r="H235" t="n">
         <v>13500</v>
@@ -7213,7 +7213,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G236" t="n">
-        <v>1.34895777702332</v>
+        <v>1.3489578962326</v>
       </c>
       <c r="H236" t="n">
         <v>13500</v>
@@ -7300,7 +7300,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G239" t="n">
-        <v>1.34016990661621</v>
+        <v>1.34016978740692</v>
       </c>
       <c r="H239" t="n">
         <v>69000</v>
@@ -7358,7 +7358,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G241" t="n">
-        <v>2.24972772598267</v>
+        <v>2.24972748756409</v>
       </c>
       <c r="H241" t="n">
         <v>774000</v>
@@ -7387,7 +7387,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G242" t="n">
-        <v>2.08275556564331</v>
+        <v>2.08275580406189</v>
       </c>
       <c r="H242" t="n">
         <v>1374000</v>
@@ -7416,7 +7416,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G243" t="n">
-        <v>2.23215198516846</v>
+        <v>2.2321515083313</v>
       </c>
       <c r="H243" t="n">
         <v>702000</v>
@@ -7445,7 +7445,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G244" t="n">
-        <v>2.52215576171875</v>
+        <v>2.52215552330017</v>
       </c>
       <c r="H244" t="n">
         <v>1464000</v>
@@ -7474,7 +7474,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G245" t="n">
-        <v>2.39912366867065</v>
+        <v>2.39912390708923</v>
       </c>
       <c r="H245" t="n">
         <v>546000</v>
@@ -7503,7 +7503,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G246" t="n">
-        <v>2.27609181404114</v>
+        <v>2.27609157562256</v>
       </c>
       <c r="H246" t="n">
         <v>229500</v>
@@ -7561,7 +7561,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G248" t="n">
-        <v>2.27609181404114</v>
+        <v>2.27609157562256</v>
       </c>
       <c r="H248" t="n">
         <v>240000</v>
@@ -7590,7 +7590,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G249" t="n">
-        <v>2.20578789710999</v>
+        <v>2.20578765869141</v>
       </c>
       <c r="H249" t="n">
         <v>195000</v>
@@ -7619,7 +7619,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G250" t="n">
-        <v>2.23215198516846</v>
+        <v>2.2321515083313</v>
       </c>
       <c r="H250" t="n">
         <v>102000</v>
@@ -7648,7 +7648,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G251" t="n">
-        <v>2.18821167945862</v>
+        <v>2.1882119178772</v>
       </c>
       <c r="H251" t="n">
         <v>40500</v>
@@ -7677,7 +7677,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G252" t="n">
-        <v>2.18821167945862</v>
+        <v>2.1882119178772</v>
       </c>
       <c r="H252" t="n">
         <v>36000</v>
@@ -7735,7 +7735,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G254" t="n">
-        <v>2.34639573097229</v>
+        <v>2.34639549255371</v>
       </c>
       <c r="H254" t="n">
         <v>139500</v>
@@ -7764,7 +7764,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G255" t="n">
-        <v>2.33760786056519</v>
+        <v>2.33760762214661</v>
       </c>
       <c r="H255" t="n">
         <v>108000</v>
@@ -7967,7 +7967,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G262" t="n">
-        <v>2.24972772598267</v>
+        <v>2.24972748756409</v>
       </c>
       <c r="H262" t="n">
         <v>33000</v>
@@ -8025,7 +8025,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G264" t="n">
-        <v>2.20578789710999</v>
+        <v>2.20578765869141</v>
       </c>
       <c r="H264" t="n">
         <v>37500</v>
@@ -8054,7 +8054,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G265" t="n">
-        <v>2.34639573097229</v>
+        <v>2.34639549255371</v>
       </c>
       <c r="H265" t="n">
         <v>46500</v>
@@ -8112,7 +8112,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G267" t="n">
-        <v>2.27609181404114</v>
+        <v>2.27609157562256</v>
       </c>
       <c r="H267" t="n">
         <v>61500</v>
@@ -8141,7 +8141,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G268" t="n">
-        <v>2.38154768943787</v>
+        <v>2.38154792785645</v>
       </c>
       <c r="H268" t="n">
         <v>88500</v>
@@ -8170,7 +8170,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G269" t="n">
-        <v>2.31124401092529</v>
+        <v>2.31124377250671</v>
       </c>
       <c r="H269" t="n">
         <v>54000</v>
@@ -8199,7 +8199,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G270" t="n">
-        <v>2.23215198516846</v>
+        <v>2.2321515083313</v>
       </c>
       <c r="H270" t="n">
         <v>97500</v>
@@ -8286,7 +8286,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G273" t="n">
-        <v>2.27609181404114</v>
+        <v>2.27609157562256</v>
       </c>
       <c r="H273" t="n">
         <v>94500</v>
@@ -8315,7 +8315,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G274" t="n">
-        <v>2.24972772598267</v>
+        <v>2.24972748756409</v>
       </c>
       <c r="H274" t="n">
         <v>45000</v>
@@ -8402,7 +8402,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G277" t="n">
-        <v>2.30245542526245</v>
+        <v>2.30245566368103</v>
       </c>
       <c r="H277" t="n">
         <v>18000</v>
@@ -8460,7 +8460,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G279" t="n">
-        <v>2.3200318813324</v>
+        <v>2.32003164291382</v>
       </c>
       <c r="H279" t="n">
         <v>10500</v>
@@ -8547,7 +8547,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G282" t="n">
-        <v>2.30245542526245</v>
+        <v>2.30245566368103</v>
       </c>
       <c r="H282" t="n">
         <v>4500</v>
@@ -8605,7 +8605,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G284" t="n">
-        <v>2.3200318813324</v>
+        <v>2.32003164291382</v>
       </c>
       <c r="H284" t="n">
         <v>18000</v>
@@ -8634,7 +8634,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G285" t="n">
-        <v>2.27609181404114</v>
+        <v>2.27609157562256</v>
       </c>
       <c r="H285" t="n">
         <v>24000</v>
@@ -8750,7 +8750,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G289" t="n">
-        <v>2.3200318813324</v>
+        <v>2.32003164291382</v>
       </c>
       <c r="H289" t="n">
         <v>87000</v>
@@ -8808,7 +8808,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G291" t="n">
-        <v>2.27609181404114</v>
+        <v>2.27609157562256</v>
       </c>
       <c r="H291" t="n">
         <v>18000</v>
@@ -8866,7 +8866,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G293" t="n">
-        <v>2.24972772598267</v>
+        <v>2.24972748756409</v>
       </c>
       <c r="H293" t="n">
         <v>1500</v>
@@ -8953,7 +8953,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G296" t="n">
-        <v>2.23215198516846</v>
+        <v>2.2321515083313</v>
       </c>
       <c r="H296" t="n">
         <v>7500</v>
@@ -9069,7 +9069,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G300" t="n">
-        <v>2.20578789710999</v>
+        <v>2.20578765869141</v>
       </c>
       <c r="H300" t="n">
         <v>24000</v>
@@ -9127,7 +9127,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G302" t="n">
-        <v>2.14427185058594</v>
+        <v>2.14427208900452</v>
       </c>
       <c r="H302" t="n">
         <v>31500</v>
@@ -9156,7 +9156,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G303" t="n">
-        <v>2.07396769523621</v>
+        <v>2.07396793365479</v>
       </c>
       <c r="H303" t="n">
         <v>58500</v>
@@ -9185,7 +9185,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G304" t="n">
-        <v>2.03881573677063</v>
+        <v>2.03881597518921</v>
       </c>
       <c r="H304" t="n">
         <v>51000</v>
@@ -9214,7 +9214,7 @@
         <v>2.25</v>
       </c>
       <c r="G305" t="n">
-        <v>1.97729969024658</v>
+        <v>1.97729980945587</v>
       </c>
       <c r="H305" t="n">
         <v>51000</v>
@@ -9243,7 +9243,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G306" t="n">
-        <v>1.99487555027008</v>
+        <v>1.99487590789795</v>
       </c>
       <c r="H306" t="n">
         <v>13500</v>
@@ -9272,7 +9272,7 @@
         <v>2.25</v>
       </c>
       <c r="G307" t="n">
-        <v>1.97729969024658</v>
+        <v>1.97729980945587</v>
       </c>
       <c r="H307" t="n">
         <v>13500</v>
@@ -9330,7 +9330,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G309" t="n">
-        <v>1.9333598613739</v>
+        <v>1.93335998058319</v>
       </c>
       <c r="H309" t="n">
         <v>18000</v>
@@ -9417,7 +9417,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G312" t="n">
-        <v>1.8279036283493</v>
+        <v>1.82790386676788</v>
       </c>
       <c r="H312" t="n">
         <v>37500</v>
@@ -9446,7 +9446,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G313" t="n">
-        <v>1.9333598613739</v>
+        <v>1.93335998058319</v>
       </c>
       <c r="H313" t="n">
         <v>18000</v>
@@ -9475,7 +9475,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G314" t="n">
-        <v>1.9333598613739</v>
+        <v>1.93335998058319</v>
       </c>
       <c r="H314" t="n">
         <v>6000</v>
@@ -9504,7 +9504,7 @@
         <v>2.25</v>
       </c>
       <c r="G315" t="n">
-        <v>1.97729969024658</v>
+        <v>1.97729980945587</v>
       </c>
       <c r="H315" t="n">
         <v>25500</v>
@@ -9533,7 +9533,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G316" t="n">
-        <v>2.08275556564331</v>
+        <v>2.08275580406189</v>
       </c>
       <c r="H316" t="n">
         <v>48000</v>
@@ -9562,7 +9562,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G317" t="n">
-        <v>2.07396769523621</v>
+        <v>2.07396793365479</v>
       </c>
       <c r="H317" t="n">
         <v>12000</v>
@@ -9649,7 +9649,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G320" t="n">
-        <v>2.14427185058594</v>
+        <v>2.14427208900452</v>
       </c>
       <c r="H320" t="n">
         <v>9000</v>
@@ -9678,7 +9678,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G321" t="n">
-        <v>2.14427185058594</v>
+        <v>2.14427208900452</v>
       </c>
       <c r="H321" t="n">
         <v>3000</v>
@@ -9707,7 +9707,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G322" t="n">
-        <v>2.10033178329468</v>
+        <v>2.10033202171326</v>
       </c>
       <c r="H322" t="n">
         <v>3000</v>
@@ -9736,7 +9736,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G323" t="n">
-        <v>2.10033178329468</v>
+        <v>2.10033202171326</v>
       </c>
       <c r="H323" t="n">
         <v>0</v>
@@ -9823,7 +9823,7 @@
         <v>2.25</v>
       </c>
       <c r="G326" t="n">
-        <v>1.97729969024658</v>
+        <v>1.97729980945587</v>
       </c>
       <c r="H326" t="n">
         <v>48000</v>
@@ -9852,7 +9852,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G327" t="n">
-        <v>1.91578412055969</v>
+        <v>1.91578376293182</v>
       </c>
       <c r="H327" t="n">
         <v>24000</v>
@@ -9968,7 +9968,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G331" t="n">
-        <v>1.99487555027008</v>
+        <v>1.99487590789795</v>
       </c>
       <c r="H331" t="n">
         <v>12000</v>
@@ -9997,7 +9997,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G332" t="n">
-        <v>1.99487555027008</v>
+        <v>1.99487590789795</v>
       </c>
       <c r="H332" t="n">
         <v>7500</v>
@@ -10026,7 +10026,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G333" t="n">
-        <v>1.99487555027008</v>
+        <v>1.99487590789795</v>
       </c>
       <c r="H333" t="n">
         <v>6000</v>
@@ -10055,7 +10055,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G334" t="n">
-        <v>2.03881573677063</v>
+        <v>2.03881597518921</v>
       </c>
       <c r="H334" t="n">
         <v>7500</v>
@@ -10142,7 +10142,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G337" t="n">
-        <v>2.10911965370178</v>
+        <v>2.10911989212036</v>
       </c>
       <c r="H337" t="n">
         <v>9000</v>
@@ -10171,7 +10171,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G338" t="n">
-        <v>2.05639147758484</v>
+        <v>2.056391954422</v>
       </c>
       <c r="H338" t="n">
         <v>3000</v>
@@ -10200,7 +10200,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G339" t="n">
-        <v>2.08275556564331</v>
+        <v>2.08275580406189</v>
       </c>
       <c r="H339" t="n">
         <v>3000</v>
@@ -10229,7 +10229,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G340" t="n">
-        <v>2.03881573677063</v>
+        <v>2.03881597518921</v>
       </c>
       <c r="H340" t="n">
         <v>3000</v>
@@ -10345,7 +10345,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G344" t="n">
-        <v>1.95972394943237</v>
+        <v>1.95972383022308</v>
       </c>
       <c r="H344" t="n">
         <v>27000</v>
@@ -10432,7 +10432,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G347" t="n">
-        <v>1.96851170063019</v>
+        <v>1.96851181983948</v>
       </c>
       <c r="H347" t="n">
         <v>15000</v>
@@ -10461,7 +10461,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G348" t="n">
-        <v>1.9333598613739</v>
+        <v>1.93335998058319</v>
       </c>
       <c r="H348" t="n">
         <v>1500</v>
@@ -10490,7 +10490,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G349" t="n">
-        <v>1.90699577331543</v>
+        <v>1.90699589252472</v>
       </c>
       <c r="H349" t="n">
         <v>7500</v>
@@ -10519,7 +10519,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G350" t="n">
-        <v>1.90699577331543</v>
+        <v>1.90699589252472</v>
       </c>
       <c r="H350" t="n">
         <v>4500</v>
@@ -10635,7 +10635,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G354" t="n">
-        <v>1.85426771640778</v>
+        <v>1.85426783561707</v>
       </c>
       <c r="H354" t="n">
         <v>13500</v>
@@ -10664,7 +10664,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G355" t="n">
-        <v>1.92457175254822</v>
+        <v>1.9245719909668</v>
       </c>
       <c r="H355" t="n">
         <v>13500</v>
@@ -10722,7 +10722,7 @@
         <v>2.25</v>
       </c>
       <c r="G357" t="n">
-        <v>1.97729969024658</v>
+        <v>1.97729980945587</v>
       </c>
       <c r="H357" t="n">
         <v>7500</v>
@@ -10751,7 +10751,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G358" t="n">
-        <v>2.03881573677063</v>
+        <v>2.03881597518921</v>
       </c>
       <c r="H358" t="n">
         <v>10500</v>
@@ -10838,7 +10838,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G361" t="n">
-        <v>1.99487555027008</v>
+        <v>1.99487590789795</v>
       </c>
       <c r="H361" t="n">
         <v>15000</v>
@@ -10867,7 +10867,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G362" t="n">
-        <v>1.99487555027008</v>
+        <v>1.99487590789795</v>
       </c>
       <c r="H362" t="n">
         <v>6000</v>
@@ -10896,7 +10896,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G363" t="n">
-        <v>1.96851170063019</v>
+        <v>1.96851181983948</v>
       </c>
       <c r="H363" t="n">
         <v>3000</v>
@@ -10983,7 +10983,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G366" t="n">
-        <v>1.9333598613739</v>
+        <v>1.93335998058319</v>
       </c>
       <c r="H366" t="n">
         <v>13500</v>
@@ -11012,7 +11012,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G367" t="n">
-        <v>1.9333598613739</v>
+        <v>1.93335998058319</v>
       </c>
       <c r="H367" t="n">
         <v>1500</v>
@@ -11070,7 +11070,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G369" t="n">
-        <v>1.98608803749084</v>
+        <v>1.98608791828156</v>
       </c>
       <c r="H369" t="n">
         <v>25500</v>
@@ -11099,7 +11099,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G370" t="n">
-        <v>1.9333598613739</v>
+        <v>1.93335998058319</v>
       </c>
       <c r="H370" t="n">
         <v>6000</v>
@@ -11128,7 +11128,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G371" t="n">
-        <v>1.9333598613739</v>
+        <v>1.93335998058319</v>
       </c>
       <c r="H371" t="n">
         <v>1500</v>
@@ -11157,7 +11157,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G372" t="n">
-        <v>1.98608803749084</v>
+        <v>1.98608791828156</v>
       </c>
       <c r="H372" t="n">
         <v>7500</v>
@@ -11244,7 +11244,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G375" t="n">
-        <v>1.85426771640778</v>
+        <v>1.85426783561707</v>
       </c>
       <c r="H375" t="n">
         <v>15000</v>
@@ -11273,7 +11273,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G376" t="n">
-        <v>1.88063168525696</v>
+        <v>1.88063192367554</v>
       </c>
       <c r="H376" t="n">
         <v>9000</v>
@@ -11302,7 +11302,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G377" t="n">
-        <v>1.88063168525696</v>
+        <v>1.88063192367554</v>
       </c>
       <c r="H377" t="n">
         <v>3000</v>
@@ -11331,7 +11331,7 @@
         <v>2.25</v>
       </c>
       <c r="G378" t="n">
-        <v>1.97729969024658</v>
+        <v>1.97729980945587</v>
       </c>
       <c r="H378" t="n">
         <v>16500</v>
@@ -11360,7 +11360,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G379" t="n">
-        <v>1.9333598613739</v>
+        <v>1.93335998058319</v>
       </c>
       <c r="H379" t="n">
         <v>3000</v>
@@ -11418,7 +11418,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G381" t="n">
-        <v>1.74002397060394</v>
+        <v>1.74002385139465</v>
       </c>
       <c r="H381" t="n">
         <v>34500</v>
@@ -11476,7 +11476,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G383" t="n">
-        <v>1.86305570602417</v>
+        <v>1.86305582523346</v>
       </c>
       <c r="H383" t="n">
         <v>21000</v>
@@ -11505,7 +11505,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G384" t="n">
-        <v>1.86305570602417</v>
+        <v>1.86305582523346</v>
       </c>
       <c r="H384" t="n">
         <v>1500</v>
@@ -11534,7 +11534,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G385" t="n">
-        <v>1.88063168525696</v>
+        <v>1.88063192367554</v>
       </c>
       <c r="H385" t="n">
         <v>13500</v>
@@ -11563,7 +11563,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G386" t="n">
-        <v>1.99487555027008</v>
+        <v>1.99487590789795</v>
       </c>
       <c r="H386" t="n">
         <v>15000</v>
@@ -11621,7 +11621,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G388" t="n">
-        <v>1.99487555027008</v>
+        <v>1.99487590789795</v>
       </c>
       <c r="H388" t="n">
         <v>9000</v>
@@ -11650,7 +11650,7 @@
         <v>2.25</v>
       </c>
       <c r="G389" t="n">
-        <v>1.97729969024658</v>
+        <v>1.97729980945587</v>
       </c>
       <c r="H389" t="n">
         <v>6000</v>
@@ -11679,7 +11679,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G390" t="n">
-        <v>1.9333598613739</v>
+        <v>1.93335998058319</v>
       </c>
       <c r="H390" t="n">
         <v>1500</v>
@@ -11708,7 +11708,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G391" t="n">
-        <v>1.96851170063019</v>
+        <v>1.96851181983948</v>
       </c>
       <c r="H391" t="n">
         <v>9000</v>
@@ -11737,7 +11737,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G392" t="n">
-        <v>1.98608803749084</v>
+        <v>1.98608791828156</v>
       </c>
       <c r="H392" t="n">
         <v>6000</v>
@@ -11766,7 +11766,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G393" t="n">
-        <v>1.98608803749084</v>
+        <v>1.98608791828156</v>
       </c>
       <c r="H393" t="n">
         <v>0</v>
@@ -11795,7 +11795,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G394" t="n">
-        <v>1.92457175254822</v>
+        <v>1.9245719909668</v>
       </c>
       <c r="H394" t="n">
         <v>12000</v>
@@ -11824,7 +11824,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G395" t="n">
-        <v>1.99487555027008</v>
+        <v>1.99487590789795</v>
       </c>
       <c r="H395" t="n">
         <v>31500</v>
@@ -11911,7 +11911,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G398" t="n">
-        <v>2.05639147758484</v>
+        <v>2.056391954422</v>
       </c>
       <c r="H398" t="n">
         <v>10500</v>
@@ -11940,7 +11940,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G399" t="n">
-        <v>1.98608803749084</v>
+        <v>1.98608791828156</v>
       </c>
       <c r="H399" t="n">
         <v>6000</v>
@@ -12027,7 +12027,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G402" t="n">
-        <v>2.05639147758484</v>
+        <v>2.056391954422</v>
       </c>
       <c r="H402" t="n">
         <v>36000</v>
@@ -12056,7 +12056,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G403" t="n">
-        <v>1.9333598613739</v>
+        <v>1.93335998058319</v>
       </c>
       <c r="H403" t="n">
         <v>7500</v>
@@ -12085,7 +12085,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G404" t="n">
-        <v>1.96851170063019</v>
+        <v>1.96851181983948</v>
       </c>
       <c r="H404" t="n">
         <v>22500</v>
@@ -12114,7 +12114,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G405" t="n">
-        <v>1.98608803749084</v>
+        <v>1.98608791828156</v>
       </c>
       <c r="H405" t="n">
         <v>16500</v>
@@ -12143,7 +12143,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G406" t="n">
-        <v>1.98608803749084</v>
+        <v>1.98608791828156</v>
       </c>
       <c r="H406" t="n">
         <v>0</v>
@@ -12172,7 +12172,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G407" t="n">
-        <v>1.84547972679138</v>
+        <v>1.84547984600067</v>
       </c>
       <c r="H407" t="n">
         <v>64500</v>
@@ -12317,7 +12317,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G412" t="n">
-        <v>1.88063168525696</v>
+        <v>1.88063192367554</v>
       </c>
       <c r="H412" t="n">
         <v>9000</v>
@@ -12346,7 +12346,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G413" t="n">
-        <v>1.88063168525696</v>
+        <v>1.88063192367554</v>
       </c>
       <c r="H413" t="n">
         <v>0</v>
@@ -12462,7 +12462,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G417" t="n">
-        <v>1.86305570602417</v>
+        <v>1.86305582523346</v>
       </c>
       <c r="H417" t="n">
         <v>6000</v>
@@ -12520,7 +12520,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G419" t="n">
-        <v>1.91578412055969</v>
+        <v>1.91578376293182</v>
       </c>
       <c r="H419" t="n">
         <v>18000</v>
@@ -12578,7 +12578,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G421" t="n">
-        <v>1.91578412055969</v>
+        <v>1.91578376293182</v>
       </c>
       <c r="H421" t="n">
         <v>1500</v>
@@ -12636,7 +12636,7 @@
         <v>2</v>
       </c>
       <c r="G423" t="n">
-        <v>1.75759971141815</v>
+        <v>1.75759983062744</v>
       </c>
       <c r="H423" t="n">
         <v>25500</v>
@@ -12694,7 +12694,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G425" t="n">
-        <v>1.74002397060394</v>
+        <v>1.74002385139465</v>
       </c>
       <c r="H425" t="n">
         <v>3000</v>
@@ -12723,7 +12723,7 @@
         <v>2</v>
       </c>
       <c r="G426" t="n">
-        <v>1.75759971141815</v>
+        <v>1.75759983062744</v>
       </c>
       <c r="H426" t="n">
         <v>4500</v>
@@ -12752,7 +12752,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G427" t="n">
-        <v>1.76638793945312</v>
+        <v>1.76638782024384</v>
       </c>
       <c r="H427" t="n">
         <v>4500</v>
@@ -12781,7 +12781,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G428" t="n">
-        <v>1.76638793945312</v>
+        <v>1.76638782024384</v>
       </c>
       <c r="H428" t="n">
         <v>3000</v>
@@ -12810,7 +12810,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G429" t="n">
-        <v>1.76638793945312</v>
+        <v>1.76638782024384</v>
       </c>
       <c r="H429" t="n">
         <v>3000</v>
@@ -12839,7 +12839,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G430" t="n">
-        <v>1.76638793945312</v>
+        <v>1.76638782024384</v>
       </c>
       <c r="H430" t="n">
         <v>4500</v>
@@ -12868,7 +12868,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G431" t="n">
-        <v>1.84547972679138</v>
+        <v>1.84547984600067</v>
       </c>
       <c r="H431" t="n">
         <v>6000</v>
@@ -12926,7 +12926,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G433" t="n">
-        <v>1.86305570602417</v>
+        <v>1.86305582523346</v>
       </c>
       <c r="H433" t="n">
         <v>7500</v>
@@ -12955,7 +12955,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G434" t="n">
-        <v>1.86305570602417</v>
+        <v>1.86305582523346</v>
       </c>
       <c r="H434" t="n">
         <v>0</v>
@@ -12984,7 +12984,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G435" t="n">
-        <v>1.86305570602417</v>
+        <v>1.86305582523346</v>
       </c>
       <c r="H435" t="n">
         <v>3000</v>
@@ -13013,7 +13013,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G436" t="n">
-        <v>1.88063168525696</v>
+        <v>1.88063192367554</v>
       </c>
       <c r="H436" t="n">
         <v>3000</v>
@@ -13042,7 +13042,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G437" t="n">
-        <v>1.85426771640778</v>
+        <v>1.85426783561707</v>
       </c>
       <c r="H437" t="n">
         <v>4500</v>
@@ -13071,7 +13071,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G438" t="n">
-        <v>1.85426771640778</v>
+        <v>1.85426783561707</v>
       </c>
       <c r="H438" t="n">
         <v>0</v>
@@ -13158,7 +13158,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G441" t="n">
-        <v>1.88063168525696</v>
+        <v>1.88063192367554</v>
       </c>
       <c r="H441" t="n">
         <v>3000</v>
@@ -13187,7 +13187,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G442" t="n">
-        <v>1.88063168525696</v>
+        <v>1.88063192367554</v>
       </c>
       <c r="H442" t="n">
         <v>0</v>
@@ -13216,7 +13216,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G443" t="n">
-        <v>1.8279036283493</v>
+        <v>1.82790386676788</v>
       </c>
       <c r="H443" t="n">
         <v>4500</v>
@@ -13245,7 +13245,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G444" t="n">
-        <v>1.86305570602417</v>
+        <v>1.86305582523346</v>
       </c>
       <c r="H444" t="n">
         <v>1500</v>
@@ -13274,7 +13274,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G445" t="n">
-        <v>1.8279036283493</v>
+        <v>1.82790386676788</v>
       </c>
       <c r="H445" t="n">
         <v>1500</v>
@@ -13303,7 +13303,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G446" t="n">
-        <v>1.8279036283493</v>
+        <v>1.82790386676788</v>
       </c>
       <c r="H446" t="n">
         <v>0</v>
@@ -13332,7 +13332,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G447" t="n">
-        <v>1.76638793945312</v>
+        <v>1.76638782024384</v>
       </c>
       <c r="H447" t="n">
         <v>15000</v>
@@ -13361,7 +13361,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G448" t="n">
-        <v>1.73562979698181</v>
+        <v>1.7356299161911</v>
       </c>
       <c r="H448" t="n">
         <v>3000</v>
@@ -13419,7 +13419,7 @@
         <v>2</v>
       </c>
       <c r="G450" t="n">
-        <v>1.75759971141815</v>
+        <v>1.75759983062744</v>
       </c>
       <c r="H450" t="n">
         <v>10500</v>
@@ -13448,7 +13448,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G451" t="n">
-        <v>1.74002397060394</v>
+        <v>1.74002385139465</v>
       </c>
       <c r="H451" t="n">
         <v>4500</v>
@@ -13477,7 +13477,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G452" t="n">
-        <v>1.72684192657471</v>
+        <v>1.72684180736542</v>
       </c>
       <c r="H452" t="n">
         <v>3000</v>
@@ -13506,7 +13506,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G453" t="n">
-        <v>1.68729567527771</v>
+        <v>1.687295794487</v>
       </c>
       <c r="H453" t="n">
         <v>7500</v>
@@ -13535,7 +13535,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G454" t="n">
-        <v>1.63896191120148</v>
+        <v>1.63896179199219</v>
       </c>
       <c r="H454" t="n">
         <v>6000</v>
@@ -13564,7 +13564,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G455" t="n">
-        <v>1.70926594734192</v>
+        <v>1.70926582813263</v>
       </c>
       <c r="H455" t="n">
         <v>9000</v>
@@ -13593,7 +13593,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G456" t="n">
-        <v>1.70926594734192</v>
+        <v>1.70926582813263</v>
       </c>
       <c r="H456" t="n">
         <v>0</v>
@@ -13622,7 +13622,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G457" t="n">
-        <v>1.70926594734192</v>
+        <v>1.70926582813263</v>
       </c>
       <c r="H457" t="n">
         <v>0</v>
@@ -13651,7 +13651,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G458" t="n">
-        <v>1.70926594734192</v>
+        <v>1.70926582813263</v>
       </c>
       <c r="H458" t="n">
         <v>0</v>
@@ -13680,7 +13680,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G459" t="n">
-        <v>1.70926594734192</v>
+        <v>1.70926582813263</v>
       </c>
       <c r="H459" t="n">
         <v>0</v>
@@ -13796,7 +13796,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G463" t="n">
-        <v>1.66093170642853</v>
+        <v>1.66093182563782</v>
       </c>
       <c r="H463" t="n">
         <v>1500</v>
@@ -13825,7 +13825,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G464" t="n">
-        <v>1.66093170642853</v>
+        <v>1.66093182563782</v>
       </c>
       <c r="H464" t="n">
         <v>0</v>
@@ -13854,7 +13854,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G465" t="n">
-        <v>1.65214383602142</v>
+        <v>1.65214371681213</v>
       </c>
       <c r="H465" t="n">
         <v>9000</v>
@@ -13883,7 +13883,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G466" t="n">
-        <v>1.59941601753235</v>
+        <v>1.59941589832306</v>
       </c>
       <c r="H466" t="n">
         <v>6000</v>
@@ -13999,7 +13999,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G470" t="n">
-        <v>1.66093170642853</v>
+        <v>1.66093182563782</v>
       </c>
       <c r="H470" t="n">
         <v>3000</v>
@@ -14057,7 +14057,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G472" t="n">
-        <v>1.64335596561432</v>
+        <v>1.64335584640503</v>
       </c>
       <c r="H472" t="n">
         <v>4500</v>
@@ -14086,7 +14086,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G473" t="n">
-        <v>1.64335596561432</v>
+        <v>1.64335584640503</v>
       </c>
       <c r="H473" t="n">
         <v>0</v>
@@ -14144,7 +14144,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G475" t="n">
-        <v>1.63456773757935</v>
+        <v>1.63456785678864</v>
       </c>
       <c r="H475" t="n">
         <v>3000</v>
@@ -14173,7 +14173,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G476" t="n">
-        <v>1.66532588005066</v>
+        <v>1.66532576084137</v>
       </c>
       <c r="H476" t="n">
         <v>1500</v>
@@ -14202,7 +14202,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G477" t="n">
-        <v>1.66532588005066</v>
+        <v>1.66532576084137</v>
       </c>
       <c r="H477" t="n">
         <v>0</v>
@@ -14231,7 +14231,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G478" t="n">
-        <v>1.66532588005066</v>
+        <v>1.66532576084137</v>
       </c>
       <c r="H478" t="n">
         <v>0</v>
@@ -14289,7 +14289,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G480" t="n">
-        <v>1.63017392158508</v>
+        <v>1.63017380237579</v>
       </c>
       <c r="H480" t="n">
         <v>3000</v>
@@ -14318,7 +14318,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G481" t="n">
-        <v>1.68729567527771</v>
+        <v>1.687295794487</v>
       </c>
       <c r="H481" t="n">
         <v>3000</v>
@@ -14376,7 +14376,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G483" t="n">
-        <v>1.64335596561432</v>
+        <v>1.64335584640503</v>
       </c>
       <c r="H483" t="n">
         <v>3000</v>
@@ -14492,7 +14492,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G487" t="n">
-        <v>1.9333598613739</v>
+        <v>1.93335998058319</v>
       </c>
       <c r="H487" t="n">
         <v>33000</v>
@@ -14521,7 +14521,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G488" t="n">
-        <v>1.92457175254822</v>
+        <v>1.9245719909668</v>
       </c>
       <c r="H488" t="n">
         <v>34500</v>
@@ -14579,7 +14579,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G490" t="n">
-        <v>2.03881573677063</v>
+        <v>2.03881597518921</v>
       </c>
       <c r="H490" t="n">
         <v>28500</v>
@@ -14608,7 +14608,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G491" t="n">
-        <v>2.03881573677063</v>
+        <v>2.03881597518921</v>
       </c>
       <c r="H491" t="n">
         <v>0</v>
@@ -14637,7 +14637,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G492" t="n">
-        <v>1.99487555027008</v>
+        <v>1.99487590789795</v>
       </c>
       <c r="H492" t="n">
         <v>3000</v>
@@ -14695,7 +14695,7 @@
         <v>2.25</v>
       </c>
       <c r="G494" t="n">
-        <v>1.97729969024658</v>
+        <v>1.97729980945587</v>
       </c>
       <c r="H494" t="n">
         <v>4500</v>
@@ -14724,7 +14724,7 @@
         <v>2.25</v>
       </c>
       <c r="G495" t="n">
-        <v>1.97729969024658</v>
+        <v>1.97729980945587</v>
       </c>
       <c r="H495" t="n">
         <v>0</v>
@@ -14753,7 +14753,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G496" t="n">
-        <v>1.9333598613739</v>
+        <v>1.93335998058319</v>
       </c>
       <c r="H496" t="n">
         <v>6000</v>
@@ -14782,7 +14782,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G497" t="n">
-        <v>1.8279036283493</v>
+        <v>1.82790386676788</v>
       </c>
       <c r="H497" t="n">
         <v>21000</v>
@@ -14811,7 +14811,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G498" t="n">
-        <v>1.73562979698181</v>
+        <v>1.7356299161911</v>
       </c>
       <c r="H498" t="n">
         <v>40500</v>
@@ -14840,7 +14840,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G499" t="n">
-        <v>1.78396368026733</v>
+        <v>1.78396379947662</v>
       </c>
       <c r="H499" t="n">
         <v>12000</v>
@@ -14869,7 +14869,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G500" t="n">
-        <v>1.78396368026733</v>
+        <v>1.78396379947662</v>
       </c>
       <c r="H500" t="n">
         <v>3000</v>
@@ -14898,7 +14898,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G501" t="n">
-        <v>1.78396368026733</v>
+        <v>1.78396379947662</v>
       </c>
       <c r="H501" t="n">
         <v>0</v>
@@ -15072,7 +15072,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G507" t="n">
-        <v>1.78396368026733</v>
+        <v>1.78396379947662</v>
       </c>
       <c r="H507" t="n">
         <v>3000</v>
@@ -15101,7 +15101,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G508" t="n">
-        <v>1.78396368026733</v>
+        <v>1.78396379947662</v>
       </c>
       <c r="H508" t="n">
         <v>1500</v>
@@ -15130,7 +15130,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G509" t="n">
-        <v>1.78396368026733</v>
+        <v>1.78396379947662</v>
       </c>
       <c r="H509" t="n">
         <v>1500</v>
@@ -15217,7 +15217,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G512" t="n">
-        <v>1.78396368026733</v>
+        <v>1.78396379947662</v>
       </c>
       <c r="H512" t="n">
         <v>6000</v>
@@ -15275,7 +15275,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G514" t="n">
-        <v>1.78396368026733</v>
+        <v>1.78396379947662</v>
       </c>
       <c r="H514" t="n">
         <v>4500</v>
@@ -15304,7 +15304,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G515" t="n">
-        <v>1.78396368026733</v>
+        <v>1.78396379947662</v>
       </c>
       <c r="H515" t="n">
         <v>1500</v>
@@ -15333,7 +15333,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G516" t="n">
-        <v>1.71365976333618</v>
+        <v>1.71365988254547</v>
       </c>
       <c r="H516" t="n">
         <v>6000</v>
@@ -15362,7 +15362,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G517" t="n">
-        <v>1.71365976333618</v>
+        <v>1.71365988254547</v>
       </c>
       <c r="H517" t="n">
         <v>1500</v>
@@ -15391,7 +15391,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G518" t="n">
-        <v>1.71365976333618</v>
+        <v>1.71365988254547</v>
       </c>
       <c r="H518" t="n">
         <v>0</v>
@@ -15420,7 +15420,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G519" t="n">
-        <v>1.76638793945312</v>
+        <v>1.76638782024384</v>
       </c>
       <c r="H519" t="n">
         <v>3000</v>
@@ -15449,7 +15449,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G520" t="n">
-        <v>1.79275178909302</v>
+        <v>1.79275190830231</v>
       </c>
       <c r="H520" t="n">
         <v>4500</v>
@@ -15507,7 +15507,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G522" t="n">
-        <v>1.76638793945312</v>
+        <v>1.76638782024384</v>
       </c>
       <c r="H522" t="n">
         <v>9000</v>
@@ -15536,7 +15536,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G523" t="n">
-        <v>1.67850780487061</v>
+        <v>1.6785079240799</v>
       </c>
       <c r="H523" t="n">
         <v>9000</v>
@@ -15565,7 +15565,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G524" t="n">
-        <v>1.70926594734192</v>
+        <v>1.70926582813263</v>
       </c>
       <c r="H524" t="n">
         <v>1500</v>
@@ -15623,7 +15623,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G526" t="n">
-        <v>1.54229390621185</v>
+        <v>1.54229378700256</v>
       </c>
       <c r="H526" t="n">
         <v>19500</v>
@@ -15739,7 +15739,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G530" t="n">
-        <v>1.48517191410065</v>
+        <v>1.48517203330994</v>
       </c>
       <c r="H530" t="n">
         <v>7500</v>
@@ -15768,7 +15768,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G531" t="n">
-        <v>1.51592993736267</v>
+        <v>1.51592981815338</v>
       </c>
       <c r="H531" t="n">
         <v>1500</v>
@@ -15797,7 +15797,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G532" t="n">
-        <v>1.51592993736267</v>
+        <v>1.51592981815338</v>
       </c>
       <c r="H532" t="n">
         <v>0</v>
@@ -15826,7 +15826,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G533" t="n">
-        <v>1.51592993736267</v>
+        <v>1.51592981815338</v>
       </c>
       <c r="H533" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G534" t="n">
-        <v>1.48517191410065</v>
+        <v>1.48517203330994</v>
       </c>
       <c r="H534" t="n">
         <v>1500</v>
@@ -15884,7 +15884,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G535" t="n">
-        <v>1.48517191410065</v>
+        <v>1.48517203330994</v>
       </c>
       <c r="H535" t="n">
         <v>0</v>
@@ -15971,7 +15971,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G538" t="n">
-        <v>1.55108189582825</v>
+        <v>1.55108165740967</v>
       </c>
       <c r="H538" t="n">
         <v>1500</v>
@@ -16000,7 +16000,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G539" t="n">
-        <v>1.55108189582825</v>
+        <v>1.55108165740967</v>
       </c>
       <c r="H539" t="n">
         <v>0</v>
@@ -16029,7 +16029,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G540" t="n">
-        <v>1.51153576374054</v>
+        <v>1.51153588294983</v>
       </c>
       <c r="H540" t="n">
         <v>7500</v>
@@ -16058,7 +16058,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G541" t="n">
-        <v>1.51153576374054</v>
+        <v>1.51153588294983</v>
       </c>
       <c r="H541" t="n">
         <v>0</v>
@@ -16087,7 +16087,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G542" t="n">
-        <v>1.51153576374054</v>
+        <v>1.51153588294983</v>
       </c>
       <c r="H542" t="n">
         <v>0</v>
@@ -16261,7 +16261,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G548" t="n">
-        <v>1.67850780487061</v>
+        <v>1.6785079240799</v>
       </c>
       <c r="H548" t="n">
         <v>3000</v>
@@ -16290,7 +16290,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G549" t="n">
-        <v>1.67850780487061</v>
+        <v>1.6785079240799</v>
       </c>
       <c r="H549" t="n">
         <v>0</v>
@@ -16319,7 +16319,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G550" t="n">
-        <v>1.67850780487061</v>
+        <v>1.6785079240799</v>
       </c>
       <c r="H550" t="n">
         <v>0</v>
@@ -16348,7 +16348,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G551" t="n">
-        <v>1.72684192657471</v>
+        <v>1.72684180736542</v>
       </c>
       <c r="H551" t="n">
         <v>1500</v>
@@ -16435,7 +16435,7 @@
         <v>2</v>
       </c>
       <c r="G554" t="n">
-        <v>1.75759971141815</v>
+        <v>1.75759983062744</v>
       </c>
       <c r="H554" t="n">
         <v>1500</v>
@@ -16464,7 +16464,7 @@
         <v>2</v>
       </c>
       <c r="G555" t="n">
-        <v>1.75759971141815</v>
+        <v>1.75759983062744</v>
       </c>
       <c r="H555" t="n">
         <v>0</v>
@@ -16551,7 +16551,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G558" t="n">
-        <v>1.72684192657471</v>
+        <v>1.72684180736542</v>
       </c>
       <c r="H558" t="n">
         <v>13500</v>
@@ -16580,7 +16580,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G559" t="n">
-        <v>1.72684192657471</v>
+        <v>1.72684180736542</v>
       </c>
       <c r="H559" t="n">
         <v>0</v>
@@ -16609,7 +16609,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G560" t="n">
-        <v>1.67850780487061</v>
+        <v>1.6785079240799</v>
       </c>
       <c r="H560" t="n">
         <v>9000</v>
@@ -16638,7 +16638,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G561" t="n">
-        <v>1.67850780487061</v>
+        <v>1.6785079240799</v>
       </c>
       <c r="H561" t="n">
         <v>0</v>
@@ -16667,7 +16667,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G562" t="n">
-        <v>1.67850780487061</v>
+        <v>1.6785079240799</v>
       </c>
       <c r="H562" t="n">
         <v>0</v>
@@ -16696,7 +16696,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G563" t="n">
-        <v>1.67850780487061</v>
+        <v>1.6785079240799</v>
       </c>
       <c r="H563" t="n">
         <v>0</v>
@@ -16725,7 +16725,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G564" t="n">
-        <v>1.67850780487061</v>
+        <v>1.6785079240799</v>
       </c>
       <c r="H564" t="n">
         <v>0</v>
@@ -16754,7 +16754,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G565" t="n">
-        <v>1.67850780487061</v>
+        <v>1.6785079240799</v>
       </c>
       <c r="H565" t="n">
         <v>0</v>
@@ -16928,7 +16928,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G571" t="n">
-        <v>1.66093170642853</v>
+        <v>1.66093182563782</v>
       </c>
       <c r="H571" t="n">
         <v>1500</v>
@@ -17131,7 +17131,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G578" t="n">
-        <v>1.67850780487061</v>
+        <v>1.6785079240799</v>
       </c>
       <c r="H578" t="n">
         <v>1500</v>
@@ -17160,7 +17160,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G579" t="n">
-        <v>1.67850780487061</v>
+        <v>1.6785079240799</v>
       </c>
       <c r="H579" t="n">
         <v>0</v>
@@ -17189,7 +17189,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G580" t="n">
-        <v>1.67850780487061</v>
+        <v>1.6785079240799</v>
       </c>
       <c r="H580" t="n">
         <v>0</v>
@@ -17218,7 +17218,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G581" t="n">
-        <v>1.68729567527771</v>
+        <v>1.687295794487</v>
       </c>
       <c r="H581" t="n">
         <v>1500</v>
@@ -17247,7 +17247,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G582" t="n">
-        <v>1.65214383602142</v>
+        <v>1.65214371681213</v>
       </c>
       <c r="H582" t="n">
         <v>1500</v>
@@ -17276,7 +17276,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G583" t="n">
-        <v>1.65214383602142</v>
+        <v>1.65214371681213</v>
       </c>
       <c r="H583" t="n">
         <v>0</v>
@@ -17537,7 +17537,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G592" t="n">
-        <v>1.61699187755585</v>
+        <v>1.61699175834656</v>
       </c>
       <c r="H592" t="n">
         <v>6000</v>
@@ -17595,7 +17595,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G594" t="n">
-        <v>1.55986988544464</v>
+        <v>1.55986976623535</v>
       </c>
       <c r="H594" t="n">
         <v>15000</v>
@@ -17682,7 +17682,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G597" t="n">
-        <v>1.61699187755585</v>
+        <v>1.61699175834656</v>
       </c>
       <c r="H597" t="n">
         <v>15000</v>
@@ -17711,7 +17711,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G598" t="n">
-        <v>1.63896191120148</v>
+        <v>1.63896179199219</v>
       </c>
       <c r="H598" t="n">
         <v>1500</v>
@@ -17740,7 +17740,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G599" t="n">
-        <v>1.63896191120148</v>
+        <v>1.63896179199219</v>
       </c>
       <c r="H599" t="n">
         <v>0</v>
@@ -17769,7 +17769,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G600" t="n">
-        <v>1.59941601753235</v>
+        <v>1.59941589832306</v>
       </c>
       <c r="H600" t="n">
         <v>3000</v>
@@ -17798,7 +17798,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G601" t="n">
-        <v>1.59941601753235</v>
+        <v>1.59941589832306</v>
       </c>
       <c r="H601" t="n">
         <v>0</v>
@@ -17827,7 +17827,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G602" t="n">
-        <v>1.59941601753235</v>
+        <v>1.59941589832306</v>
       </c>
       <c r="H602" t="n">
         <v>0</v>
@@ -17943,7 +17943,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G606" t="n">
-        <v>1.63896191120148</v>
+        <v>1.63896179199219</v>
       </c>
       <c r="H606" t="n">
         <v>3000</v>
@@ -17972,7 +17972,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G607" t="n">
-        <v>1.61699187755585</v>
+        <v>1.61699175834656</v>
       </c>
       <c r="H607" t="n">
         <v>3000</v>
@@ -18117,7 +18117,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G612" t="n">
-        <v>1.60820388793945</v>
+        <v>1.60820376873016</v>
       </c>
       <c r="H612" t="n">
         <v>1500</v>
@@ -18233,7 +18233,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G616" t="n">
-        <v>1.56865775585175</v>
+        <v>1.56865787506104</v>
       </c>
       <c r="H616" t="n">
         <v>7500</v>
@@ -18291,7 +18291,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G618" t="n">
-        <v>1.67850780487061</v>
+        <v>1.6785079240799</v>
       </c>
       <c r="H618" t="n">
         <v>45000</v>
@@ -18320,7 +18320,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G619" t="n">
-        <v>1.72244799137115</v>
+        <v>1.72244775295258</v>
       </c>
       <c r="H619" t="n">
         <v>10500</v>
@@ -18436,7 +18436,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G623" t="n">
-        <v>1.69608390331268</v>
+        <v>1.69608378410339</v>
       </c>
       <c r="H623" t="n">
         <v>1500</v>
@@ -18494,7 +18494,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G625" t="n">
-        <v>1.70047771930695</v>
+        <v>1.70047783851624</v>
       </c>
       <c r="H625" t="n">
         <v>6000</v>
@@ -18523,7 +18523,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G626" t="n">
-        <v>1.70047771930695</v>
+        <v>1.70047783851624</v>
       </c>
       <c r="H626" t="n">
         <v>7500</v>
@@ -18581,7 +18581,7 @@
         <v>2.25</v>
       </c>
       <c r="G628" t="n">
-        <v>1.97729969024658</v>
+        <v>1.97729980945587</v>
       </c>
       <c r="H628" t="n">
         <v>303000</v>
@@ -18610,7 +18610,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G629" t="n">
-        <v>1.88063168525696</v>
+        <v>1.88063192367554</v>
       </c>
       <c r="H629" t="n">
         <v>39000</v>
@@ -18697,7 +18697,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G632" t="n">
-        <v>1.86305570602417</v>
+        <v>1.86305582523346</v>
       </c>
       <c r="H632" t="n">
         <v>33000</v>
@@ -18842,7 +18842,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G637" t="n">
-        <v>1.71365976333618</v>
+        <v>1.71365988254547</v>
       </c>
       <c r="H637" t="n">
         <v>24000</v>
@@ -18871,7 +18871,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G638" t="n">
-        <v>1.67850780487061</v>
+        <v>1.6785079240799</v>
       </c>
       <c r="H638" t="n">
         <v>12000</v>
@@ -18900,7 +18900,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G639" t="n">
-        <v>1.64335596561432</v>
+        <v>1.64335584640503</v>
       </c>
       <c r="H639" t="n">
         <v>19500</v>
@@ -18929,7 +18929,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G640" t="n">
-        <v>1.60820388793945</v>
+        <v>1.60820376873016</v>
       </c>
       <c r="H640" t="n">
         <v>33000</v>
@@ -18987,7 +18987,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G642" t="n">
-        <v>1.65214383602142</v>
+        <v>1.65214371681213</v>
       </c>
       <c r="H642" t="n">
         <v>18000</v>
@@ -19016,7 +19016,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G643" t="n">
-        <v>1.65214383602142</v>
+        <v>1.65214371681213</v>
       </c>
       <c r="H643" t="n">
         <v>9000</v>
@@ -19045,7 +19045,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G644" t="n">
-        <v>1.66093170642853</v>
+        <v>1.66093182563782</v>
       </c>
       <c r="H644" t="n">
         <v>9000</v>
@@ -19074,7 +19074,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G645" t="n">
-        <v>1.66093170642853</v>
+        <v>1.66093182563782</v>
       </c>
       <c r="H645" t="n">
         <v>0</v>
@@ -19103,7 +19103,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G646" t="n">
-        <v>1.6213858127594</v>
+        <v>1.62138593196869</v>
       </c>
       <c r="H646" t="n">
         <v>6000</v>
@@ -19132,7 +19132,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G647" t="n">
-        <v>1.66532588005066</v>
+        <v>1.66532576084137</v>
       </c>
       <c r="H647" t="n">
         <v>7500</v>
@@ -19161,7 +19161,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G648" t="n">
-        <v>1.69608390331268</v>
+        <v>1.69608378410339</v>
       </c>
       <c r="H648" t="n">
         <v>1500</v>
@@ -19190,7 +19190,7 @@
         <v>2</v>
       </c>
       <c r="G649" t="n">
-        <v>1.75759971141815</v>
+        <v>1.75759983062744</v>
       </c>
       <c r="H649" t="n">
         <v>6000</v>
@@ -19248,7 +19248,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G651" t="n">
-        <v>1.71365976333618</v>
+        <v>1.71365988254547</v>
       </c>
       <c r="H651" t="n">
         <v>1500</v>
@@ -19277,7 +19277,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G652" t="n">
-        <v>1.67850780487061</v>
+        <v>1.6785079240799</v>
       </c>
       <c r="H652" t="n">
         <v>6000</v>
@@ -19306,7 +19306,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G653" t="n">
-        <v>1.67850780487061</v>
+        <v>1.6785079240799</v>
       </c>
       <c r="H653" t="n">
         <v>0</v>
@@ -19335,7 +19335,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G654" t="n">
-        <v>1.74002397060394</v>
+        <v>1.74002385139465</v>
       </c>
       <c r="H654" t="n">
         <v>1500</v>
@@ -19364,7 +19364,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G655" t="n">
-        <v>1.74002397060394</v>
+        <v>1.74002385139465</v>
       </c>
       <c r="H655" t="n">
         <v>0</v>
@@ -19393,7 +19393,7 @@
         <v>2</v>
       </c>
       <c r="G656" t="n">
-        <v>1.75759971141815</v>
+        <v>1.75759983062744</v>
       </c>
       <c r="H656" t="n">
         <v>1500</v>
@@ -19451,7 +19451,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G658" t="n">
-        <v>1.79275178909302</v>
+        <v>1.79275190830231</v>
       </c>
       <c r="H658" t="n">
         <v>108000</v>
@@ -19480,7 +19480,7 @@
         <v>2</v>
       </c>
       <c r="G659" t="n">
-        <v>1.75759971141815</v>
+        <v>1.75759983062744</v>
       </c>
       <c r="H659" t="n">
         <v>102000</v>
@@ -19654,7 +19654,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G665" t="n">
-        <v>1.67888343334198</v>
+        <v>1.67888355255127</v>
       </c>
       <c r="H665" t="n">
         <v>13500</v>
@@ -19741,7 +19741,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G668" t="n">
-        <v>1.67888343334198</v>
+        <v>1.67888355255127</v>
       </c>
       <c r="H668" t="n">
         <v>4500</v>
@@ -19770,7 +19770,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G669" t="n">
-        <v>1.66985726356506</v>
+        <v>1.66985738277435</v>
       </c>
       <c r="H669" t="n">
         <v>3000</v>
@@ -19799,7 +19799,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G670" t="n">
-        <v>1.66083109378815</v>
+        <v>1.66083097457886</v>
       </c>
       <c r="H670" t="n">
         <v>30000</v>
@@ -19886,7 +19886,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G673" t="n">
-        <v>1.64277863502502</v>
+        <v>1.64277851581573</v>
       </c>
       <c r="H673" t="n">
         <v>4500</v>
@@ -19915,7 +19915,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G674" t="n">
-        <v>1.64277863502502</v>
+        <v>1.64277851581573</v>
       </c>
       <c r="H674" t="n">
         <v>0</v>
@@ -19944,7 +19944,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G675" t="n">
-        <v>1.64277863502502</v>
+        <v>1.64277851581573</v>
       </c>
       <c r="H675" t="n">
         <v>0</v>
@@ -19973,7 +19973,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G676" t="n">
-        <v>1.64277863502502</v>
+        <v>1.64277851581573</v>
       </c>
       <c r="H676" t="n">
         <v>0</v>
@@ -20205,7 +20205,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G684" t="n">
-        <v>1.5976470708847</v>
+        <v>1.59764719009399</v>
       </c>
       <c r="H684" t="n">
         <v>1500</v>
@@ -20698,7 +20698,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G701" t="n">
-        <v>1.5976470708847</v>
+        <v>1.59764719009399</v>
       </c>
       <c r="H701" t="n">
         <v>1500</v>
@@ -20727,7 +20727,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G702" t="n">
-        <v>1.5976470708847</v>
+        <v>1.59764719009399</v>
       </c>
       <c r="H702" t="n">
         <v>3000</v>
@@ -20756,7 +20756,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G703" t="n">
-        <v>1.5976470708847</v>
+        <v>1.59764719009399</v>
       </c>
       <c r="H703" t="n">
         <v>4500</v>
@@ -20785,7 +20785,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G704" t="n">
-        <v>1.5976470708847</v>
+        <v>1.59764719009399</v>
       </c>
       <c r="H704" t="n">
         <v>0</v>
@@ -20843,7 +20843,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G706" t="n">
-        <v>1.5976470708847</v>
+        <v>1.59764719009399</v>
       </c>
       <c r="H706" t="n">
         <v>7500</v>
@@ -21626,7 +21626,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G733" t="n">
-        <v>1.55251586437225</v>
+        <v>1.55251598358154</v>
       </c>
       <c r="H733" t="n">
         <v>1500</v>
@@ -21655,7 +21655,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G734" t="n">
-        <v>1.55251586437225</v>
+        <v>1.55251598358154</v>
       </c>
       <c r="H734" t="n">
         <v>6000</v>
@@ -21684,7 +21684,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G735" t="n">
-        <v>1.55251586437225</v>
+        <v>1.55251598358154</v>
       </c>
       <c r="H735" t="n">
         <v>0</v>
@@ -21713,7 +21713,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G736" t="n">
-        <v>1.55251586437225</v>
+        <v>1.55251598358154</v>
       </c>
       <c r="H736" t="n">
         <v>0</v>
@@ -21771,7 +21771,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G738" t="n">
-        <v>1.52543723583221</v>
+        <v>1.52543711662292</v>
       </c>
       <c r="H738" t="n">
         <v>7500</v>
@@ -21800,7 +21800,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G739" t="n">
-        <v>1.52543723583221</v>
+        <v>1.52543711662292</v>
       </c>
       <c r="H739" t="n">
         <v>0</v>
@@ -21829,7 +21829,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G740" t="n">
-        <v>1.52543723583221</v>
+        <v>1.52543711662292</v>
       </c>
       <c r="H740" t="n">
         <v>0</v>
@@ -22235,7 +22235,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G754" t="n">
-        <v>1.46225333213806</v>
+        <v>1.46225345134735</v>
       </c>
       <c r="H754" t="n">
         <v>15000</v>
@@ -22612,7 +22612,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G767" t="n">
-        <v>1.48933219909668</v>
+        <v>1.48933207988739</v>
       </c>
       <c r="H767" t="n">
         <v>15000</v>
@@ -22844,7 +22844,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G775" t="n">
-        <v>1.48933219909668</v>
+        <v>1.48933207988739</v>
       </c>
       <c r="H775" t="n">
         <v>3000</v>
@@ -22931,7 +22931,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G778" t="n">
-        <v>1.48933219909668</v>
+        <v>1.48933207988739</v>
       </c>
       <c r="H778" t="n">
         <v>4500</v>
@@ -23076,7 +23076,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G783" t="n">
-        <v>1.46225333213806</v>
+        <v>1.46225345134735</v>
       </c>
       <c r="H783" t="n">
         <v>15000</v>
@@ -23424,7 +23424,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G795" t="n">
-        <v>1.87746095657349</v>
+        <v>1.87746107578278</v>
       </c>
       <c r="H795" t="n">
         <v>319500</v>
@@ -23453,7 +23453,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G796" t="n">
-        <v>1.66985726356506</v>
+        <v>1.66985738277435</v>
       </c>
       <c r="H796" t="n">
         <v>94500</v>
@@ -23627,7 +23627,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G802" t="n">
-        <v>1.84135603904724</v>
+        <v>1.84135615825653</v>
       </c>
       <c r="H802" t="n">
         <v>37500</v>
@@ -23656,7 +23656,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G803" t="n">
-        <v>1.93161857128143</v>
+        <v>1.93161880970001</v>
       </c>
       <c r="H803" t="n">
         <v>73500</v>
@@ -23685,7 +23685,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G804" t="n">
-        <v>1.87746095657349</v>
+        <v>1.87746107578278</v>
       </c>
       <c r="H804" t="n">
         <v>46500</v>
@@ -23714,7 +23714,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G805" t="n">
-        <v>1.85940849781036</v>
+        <v>1.85940837860107</v>
       </c>
       <c r="H805" t="n">
         <v>4500</v>
@@ -23743,7 +23743,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G806" t="n">
-        <v>1.8955135345459</v>
+        <v>1.89551365375519</v>
       </c>
       <c r="H806" t="n">
         <v>9000</v>
@@ -23772,7 +23772,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G807" t="n">
-        <v>1.85940849781036</v>
+        <v>1.85940837860107</v>
       </c>
       <c r="H807" t="n">
         <v>7500</v>
@@ -23801,7 +23801,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G808" t="n">
-        <v>1.87746095657349</v>
+        <v>1.87746107578278</v>
       </c>
       <c r="H808" t="n">
         <v>10500</v>
@@ -23830,7 +23830,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G809" t="n">
-        <v>1.85940849781036</v>
+        <v>1.85940837860107</v>
       </c>
       <c r="H809" t="n">
         <v>1500</v>
@@ -23859,7 +23859,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G810" t="n">
-        <v>1.85940849781036</v>
+        <v>1.85940837860107</v>
       </c>
       <c r="H810" t="n">
         <v>1500</v>
@@ -23888,7 +23888,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G811" t="n">
-        <v>1.84135603904724</v>
+        <v>1.84135615825653</v>
       </c>
       <c r="H811" t="n">
         <v>6000</v>
@@ -23917,7 +23917,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G812" t="n">
-        <v>1.87746095657349</v>
+        <v>1.87746107578278</v>
       </c>
       <c r="H812" t="n">
         <v>6000</v>
@@ -23946,7 +23946,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G813" t="n">
-        <v>1.91356599330902</v>
+        <v>1.91356611251831</v>
       </c>
       <c r="H813" t="n">
         <v>3000</v>
@@ -23975,7 +23975,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G814" t="n">
-        <v>1.87746095657349</v>
+        <v>1.87746107578278</v>
       </c>
       <c r="H814" t="n">
         <v>7500</v>
@@ -24120,7 +24120,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G819" t="n">
-        <v>1.76914620399475</v>
+        <v>1.76914608478546</v>
       </c>
       <c r="H819" t="n">
         <v>12000</v>
@@ -24149,7 +24149,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G820" t="n">
-        <v>1.76914620399475</v>
+        <v>1.76914608478546</v>
       </c>
       <c r="H820" t="n">
         <v>0</v>
@@ -24236,7 +24236,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G823" t="n">
-        <v>1.84135603904724</v>
+        <v>1.84135615825653</v>
       </c>
       <c r="H823" t="n">
         <v>15000</v>
@@ -24584,7 +24584,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G835" t="n">
-        <v>1.76914620399475</v>
+        <v>1.76914608478546</v>
       </c>
       <c r="H835" t="n">
         <v>7500</v>
@@ -25135,7 +25135,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G854" t="n">
-        <v>1.76914620399475</v>
+        <v>1.76914608478546</v>
       </c>
       <c r="H854" t="n">
         <v>1500</v>
@@ -25454,7 +25454,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G865" t="n">
-        <v>1.84135603904724</v>
+        <v>1.84135615825653</v>
       </c>
       <c r="H865" t="n">
         <v>48000</v>
@@ -25483,7 +25483,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G866" t="n">
-        <v>1.87746095657349</v>
+        <v>1.87746107578278</v>
       </c>
       <c r="H866" t="n">
         <v>7500</v>
@@ -25512,7 +25512,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G867" t="n">
-        <v>1.91356599330902</v>
+        <v>1.91356611251831</v>
       </c>
       <c r="H867" t="n">
         <v>21000</v>
@@ -25831,7 +25831,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G878" t="n">
-        <v>1.93161857128143</v>
+        <v>1.93161880970001</v>
       </c>
       <c r="H878" t="n">
         <v>12000</v>
@@ -26324,7 +26324,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G895" t="n">
-        <v>1.85940849781036</v>
+        <v>1.85940837860107</v>
       </c>
       <c r="H895" t="n">
         <v>126000</v>
@@ -26382,7 +26382,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G897" t="n">
-        <v>1.91356599330902</v>
+        <v>1.91356611251831</v>
       </c>
       <c r="H897" t="n">
         <v>54000</v>
@@ -26411,7 +26411,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G898" t="n">
-        <v>1.87746095657349</v>
+        <v>1.87746107578278</v>
       </c>
       <c r="H898" t="n">
         <v>15000</v>
@@ -26440,7 +26440,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G899" t="n">
-        <v>1.85940849781036</v>
+        <v>1.85940837860107</v>
       </c>
       <c r="H899" t="n">
         <v>16500</v>
@@ -26469,7 +26469,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G900" t="n">
-        <v>1.87746095657349</v>
+        <v>1.87746107578278</v>
       </c>
       <c r="H900" t="n">
         <v>12000</v>
@@ -26498,7 +26498,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G901" t="n">
-        <v>1.85940849781036</v>
+        <v>1.85940837860107</v>
       </c>
       <c r="H901" t="n">
         <v>4500</v>
@@ -26527,7 +26527,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G902" t="n">
-        <v>1.93161857128143</v>
+        <v>1.93161880970001</v>
       </c>
       <c r="H902" t="n">
         <v>9000</v>
@@ -26556,7 +26556,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G903" t="n">
-        <v>1.91356599330902</v>
+        <v>1.91356611251831</v>
       </c>
       <c r="H903" t="n">
         <v>4500</v>
@@ -26585,7 +26585,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G904" t="n">
-        <v>1.93161857128143</v>
+        <v>1.93161880970001</v>
       </c>
       <c r="H904" t="n">
         <v>9000</v>
@@ -26643,7 +26643,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G906" t="n">
-        <v>1.91356599330902</v>
+        <v>1.91356611251831</v>
       </c>
       <c r="H906" t="n">
         <v>7500</v>
@@ -26672,7 +26672,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G907" t="n">
-        <v>1.93161857128143</v>
+        <v>1.93161880970001</v>
       </c>
       <c r="H907" t="n">
         <v>1500</v>
@@ -26701,7 +26701,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G908" t="n">
-        <v>1.93161857128143</v>
+        <v>1.93161880970001</v>
       </c>
       <c r="H908" t="n">
         <v>0</v>
@@ -26730,7 +26730,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G909" t="n">
-        <v>1.85940849781036</v>
+        <v>1.85940837860107</v>
       </c>
       <c r="H909" t="n">
         <v>111000</v>
@@ -26759,7 +26759,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G910" t="n">
-        <v>1.84135603904724</v>
+        <v>1.84135615825653</v>
       </c>
       <c r="H910" t="n">
         <v>21000</v>
@@ -26788,7 +26788,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G911" t="n">
-        <v>1.87746095657349</v>
+        <v>1.87746107578278</v>
       </c>
       <c r="H911" t="n">
         <v>9000</v>
@@ -26817,7 +26817,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G912" t="n">
-        <v>1.85940849781036</v>
+        <v>1.85940837860107</v>
       </c>
       <c r="H912" t="n">
         <v>15000</v>
@@ -26846,7 +26846,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G913" t="n">
-        <v>1.85940849781036</v>
+        <v>1.85940837860107</v>
       </c>
       <c r="H913" t="n">
         <v>6000</v>
@@ -26875,7 +26875,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G914" t="n">
-        <v>1.8955135345459</v>
+        <v>1.89551365375519</v>
       </c>
       <c r="H914" t="n">
         <v>7500</v>
@@ -26904,7 +26904,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G915" t="n">
-        <v>1.87746095657349</v>
+        <v>1.87746107578278</v>
       </c>
       <c r="H915" t="n">
         <v>10500</v>
@@ -26933,7 +26933,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G916" t="n">
-        <v>1.87746095657349</v>
+        <v>1.87746107578278</v>
       </c>
       <c r="H916" t="n">
         <v>1500</v>
@@ -26962,7 +26962,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G917" t="n">
-        <v>1.85940849781036</v>
+        <v>1.85940837860107</v>
       </c>
       <c r="H917" t="n">
         <v>13500</v>
@@ -45412,6 +45412,35 @@
         <v>3000</v>
       </c>
       <c r="I1553" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1554">
+      <c r="A1554" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1554" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C1554" t="n">
+        <v>1.51999998092651</v>
+      </c>
+      <c r="D1554" t="n">
+        <v>1.52999997138977</v>
+      </c>
+      <c r="E1554" t="n">
+        <v>1.51999998092651</v>
+      </c>
+      <c r="F1554" t="n">
+        <v>1.52999997138977</v>
+      </c>
+      <c r="G1554" t="n">
+        <v>1.52999997138977</v>
+      </c>
+      <c r="H1554" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I1554" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RETI.MI.xlsx
+++ b/data/RETI.MI.xlsx
@@ -427,7 +427,7 @@
         <v>0.889900028705597</v>
       </c>
       <c r="G2" t="n">
-        <v>0.75985848903656</v>
+        <v>0.759858429431915</v>
       </c>
       <c r="H2" t="n">
         <v>856500</v>
@@ -456,7 +456,7 @@
         <v>0.899600028991699</v>
       </c>
       <c r="G3" t="n">
-        <v>0.768141031265259</v>
+        <v>0.768140912055969</v>
       </c>
       <c r="H3" t="n">
         <v>472500</v>
@@ -485,7 +485,7 @@
         <v>0.879899978637695</v>
       </c>
       <c r="G4" t="n">
-        <v>0.751319646835327</v>
+        <v>0.751319706439972</v>
       </c>
       <c r="H4" t="n">
         <v>75000</v>
@@ -601,7 +601,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G8" t="n">
-        <v>0.756528317928314</v>
+        <v>0.756528258323669</v>
       </c>
       <c r="H8" t="n">
         <v>63000</v>
@@ -630,7 +630,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G9" t="n">
-        <v>0.732619941234589</v>
+        <v>0.732620060443878</v>
       </c>
       <c r="H9" t="n">
         <v>118500</v>
@@ -659,7 +659,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G10" t="n">
-        <v>0.72237354516983</v>
+        <v>0.722373604774475</v>
       </c>
       <c r="H10" t="n">
         <v>48000</v>
@@ -717,7 +717,7 @@
         <v>0.814000010490417</v>
       </c>
       <c r="G12" t="n">
-        <v>0.695049703121185</v>
+        <v>0.69504976272583</v>
       </c>
       <c r="H12" t="n">
         <v>63000</v>
@@ -746,7 +746,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G13" t="n">
-        <v>0.691634237766266</v>
+        <v>0.691634178161621</v>
       </c>
       <c r="H13" t="n">
         <v>49500</v>
@@ -775,7 +775,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G14" t="n">
-        <v>0.683095633983612</v>
+        <v>0.683095574378967</v>
       </c>
       <c r="H14" t="n">
         <v>18000</v>
@@ -804,7 +804,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G15" t="n">
-        <v>0.683095633983612</v>
+        <v>0.683095574378967</v>
       </c>
       <c r="H15" t="n">
         <v>42000</v>
@@ -833,7 +833,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G16" t="n">
-        <v>0.666018128395081</v>
+        <v>0.666018187999725</v>
       </c>
       <c r="H16" t="n">
         <v>67500</v>
@@ -862,7 +862,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G17" t="n">
-        <v>0.654063940048218</v>
+        <v>0.654063999652863</v>
       </c>
       <c r="H17" t="n">
         <v>25500</v>
@@ -920,7 +920,7 @@
         <v>0.814000010490417</v>
       </c>
       <c r="G19" t="n">
-        <v>0.695049703121185</v>
+        <v>0.69504976272583</v>
       </c>
       <c r="H19" t="n">
         <v>265500</v>
@@ -978,7 +978,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G21" t="n">
-        <v>0.654063940048218</v>
+        <v>0.654063999652863</v>
       </c>
       <c r="H21" t="n">
         <v>132000</v>
@@ -1007,7 +1007,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G22" t="n">
-        <v>0.659187257289886</v>
+        <v>0.659187197685242</v>
       </c>
       <c r="H22" t="n">
         <v>24000</v>
@@ -1036,7 +1036,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G23" t="n">
-        <v>0.666018128395081</v>
+        <v>0.666018187999725</v>
       </c>
       <c r="H23" t="n">
         <v>39000</v>
@@ -1065,7 +1065,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G24" t="n">
-        <v>0.652356326580048</v>
+        <v>0.652356207370758</v>
       </c>
       <c r="H24" t="n">
         <v>10500</v>
@@ -1123,7 +1123,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G26" t="n">
-        <v>0.654063940048218</v>
+        <v>0.654063999652863</v>
       </c>
       <c r="H26" t="n">
         <v>27000</v>
@@ -1239,7 +1239,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G30" t="n">
-        <v>0.607955098152161</v>
+        <v>0.607955038547516</v>
       </c>
       <c r="H30" t="n">
         <v>19500</v>
@@ -1268,7 +1268,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G31" t="n">
-        <v>0.587462246417999</v>
+        <v>0.587462186813354</v>
       </c>
       <c r="H31" t="n">
         <v>78000</v>
@@ -1297,7 +1297,7 @@
         <v>0.73199999332428</v>
       </c>
       <c r="G32" t="n">
-        <v>0.625032484531403</v>
+        <v>0.625032424926758</v>
       </c>
       <c r="H32" t="n">
         <v>27000</v>
@@ -1384,7 +1384,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G35" t="n">
-        <v>0.580631256103516</v>
+        <v>0.580631196498871</v>
       </c>
       <c r="H35" t="n">
         <v>12000</v>
@@ -1413,7 +1413,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G36" t="n">
-        <v>0.563553810119629</v>
+        <v>0.563553869724274</v>
       </c>
       <c r="H36" t="n">
         <v>66000</v>
@@ -1442,7 +1442,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G37" t="n">
-        <v>0.537937700748444</v>
+        <v>0.537937819957733</v>
       </c>
       <c r="H37" t="n">
         <v>27000</v>
@@ -1471,7 +1471,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G38" t="n">
-        <v>0.537937700748444</v>
+        <v>0.537937819957733</v>
       </c>
       <c r="H38" t="n">
         <v>13500</v>
@@ -1500,7 +1500,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G39" t="n">
-        <v>0.525983512401581</v>
+        <v>0.525983572006226</v>
       </c>
       <c r="H39" t="n">
         <v>10500</v>
@@ -1558,7 +1558,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G41" t="n">
-        <v>0.537937700748444</v>
+        <v>0.537937819957733</v>
       </c>
       <c r="H41" t="n">
         <v>16500</v>
@@ -1587,7 +1587,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G42" t="n">
-        <v>0.604539513587952</v>
+        <v>0.604539573192596</v>
       </c>
       <c r="H42" t="n">
         <v>127500</v>
@@ -1645,7 +1645,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G44" t="n">
-        <v>0.604539513587952</v>
+        <v>0.604539573192596</v>
       </c>
       <c r="H44" t="n">
         <v>64500</v>
@@ -1732,7 +1732,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G47" t="n">
-        <v>0.607955098152161</v>
+        <v>0.607955038547516</v>
       </c>
       <c r="H47" t="n">
         <v>7500</v>
@@ -1761,7 +1761,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G48" t="n">
-        <v>0.61137056350708</v>
+        <v>0.611370503902435</v>
       </c>
       <c r="H48" t="n">
         <v>21000</v>
@@ -1906,7 +1906,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G53" t="n">
-        <v>0.701880633831024</v>
+        <v>0.701880693435669</v>
       </c>
       <c r="H53" t="n">
         <v>70500</v>
@@ -1935,7 +1935,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G54" t="n">
-        <v>0.674556910991669</v>
+        <v>0.674556851387024</v>
       </c>
       <c r="H54" t="n">
         <v>115500</v>
@@ -1964,7 +1964,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G55" t="n">
-        <v>0.677972376346588</v>
+        <v>0.677972316741943</v>
       </c>
       <c r="H55" t="n">
         <v>36000</v>
@@ -1993,7 +1993,7 @@
         <v>0.815999984741211</v>
       </c>
       <c r="G56" t="n">
-        <v>0.69675749540329</v>
+        <v>0.696757435798645</v>
       </c>
       <c r="H56" t="n">
         <v>28500</v>
@@ -2051,7 +2051,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G58" t="n">
-        <v>0.703588485717773</v>
+        <v>0.703588426113129</v>
       </c>
       <c r="H58" t="n">
         <v>12000</v>
@@ -2080,7 +2080,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G59" t="n">
-        <v>0.683095633983612</v>
+        <v>0.683095574378967</v>
       </c>
       <c r="H59" t="n">
         <v>6000</v>
@@ -2109,7 +2109,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G60" t="n">
-        <v>0.683095633983612</v>
+        <v>0.683095574378967</v>
       </c>
       <c r="H60" t="n">
         <v>1500</v>
@@ -2138,7 +2138,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G61" t="n">
-        <v>0.683095633983612</v>
+        <v>0.683095574378967</v>
       </c>
       <c r="H61" t="n">
         <v>102000</v>
@@ -2225,7 +2225,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G64" t="n">
-        <v>0.683095633983612</v>
+        <v>0.683095574378967</v>
       </c>
       <c r="H64" t="n">
         <v>7500</v>
@@ -2283,7 +2283,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G66" t="n">
-        <v>0.674556910991669</v>
+        <v>0.674556851387024</v>
       </c>
       <c r="H66" t="n">
         <v>10500</v>
@@ -2312,7 +2312,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G67" t="n">
-        <v>0.683095633983612</v>
+        <v>0.683095574378967</v>
       </c>
       <c r="H67" t="n">
         <v>7500</v>
@@ -2341,7 +2341,7 @@
         <v>0.815999984741211</v>
       </c>
       <c r="G68" t="n">
-        <v>0.69675749540329</v>
+        <v>0.696757435798645</v>
       </c>
       <c r="H68" t="n">
         <v>7500</v>
@@ -2370,7 +2370,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G69" t="n">
-        <v>0.693341970443726</v>
+        <v>0.69334203004837</v>
       </c>
       <c r="H69" t="n">
         <v>15000</v>
@@ -2399,7 +2399,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G70" t="n">
-        <v>0.677972376346588</v>
+        <v>0.677972316741943</v>
       </c>
       <c r="H70" t="n">
         <v>3000</v>
@@ -2428,7 +2428,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G71" t="n">
-        <v>0.677972376346588</v>
+        <v>0.677972316741943</v>
       </c>
       <c r="H71" t="n">
         <v>3000</v>
@@ -2457,7 +2457,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G72" t="n">
-        <v>0.693341970443726</v>
+        <v>0.69334203004837</v>
       </c>
       <c r="H72" t="n">
         <v>3000</v>
@@ -2515,7 +2515,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G74" t="n">
-        <v>0.691634237766266</v>
+        <v>0.691634178161621</v>
       </c>
       <c r="H74" t="n">
         <v>43500</v>
@@ -2544,7 +2544,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G75" t="n">
-        <v>0.700172901153564</v>
+        <v>0.700172960758209</v>
       </c>
       <c r="H75" t="n">
         <v>73500</v>
@@ -2602,7 +2602,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G77" t="n">
-        <v>0.700172901153564</v>
+        <v>0.700172960758209</v>
       </c>
       <c r="H77" t="n">
         <v>22500</v>
@@ -2631,7 +2631,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G78" t="n">
-        <v>0.700172901153564</v>
+        <v>0.700172960758209</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
@@ -2689,7 +2689,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G80" t="n">
-        <v>0.717250347137451</v>
+        <v>0.717250287532806</v>
       </c>
       <c r="H80" t="n">
         <v>28500</v>
@@ -2718,7 +2718,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G81" t="n">
-        <v>0.708711683750153</v>
+        <v>0.708711624145508</v>
       </c>
       <c r="H81" t="n">
         <v>22500</v>
@@ -2776,7 +2776,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G83" t="n">
-        <v>0.715542614459991</v>
+        <v>0.715542674064636</v>
       </c>
       <c r="H83" t="n">
         <v>1500</v>
@@ -2805,7 +2805,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G84" t="n">
-        <v>0.717250347137451</v>
+        <v>0.717250287532806</v>
       </c>
       <c r="H84" t="n">
         <v>1500</v>
@@ -2834,7 +2834,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G85" t="n">
-        <v>0.715542614459991</v>
+        <v>0.715542674064636</v>
       </c>
       <c r="H85" t="n">
         <v>9000</v>
@@ -2863,7 +2863,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G86" t="n">
-        <v>0.700172901153564</v>
+        <v>0.700172960758209</v>
       </c>
       <c r="H86" t="n">
         <v>1500</v>
@@ -2921,7 +2921,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G88" t="n">
-        <v>0.700172901153564</v>
+        <v>0.700172960758209</v>
       </c>
       <c r="H88" t="n">
         <v>16500</v>
@@ -3008,7 +3008,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G91" t="n">
-        <v>0.701880633831024</v>
+        <v>0.701880693435669</v>
       </c>
       <c r="H91" t="n">
         <v>10500</v>
@@ -3037,7 +3037,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G92" t="n">
-        <v>0.701880633831024</v>
+        <v>0.701880693435669</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
@@ -3066,7 +3066,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G93" t="n">
-        <v>0.701880633831024</v>
+        <v>0.701880693435669</v>
       </c>
       <c r="H93" t="n">
         <v>1500</v>
@@ -3124,7 +3124,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G95" t="n">
-        <v>0.683095633983612</v>
+        <v>0.683095574378967</v>
       </c>
       <c r="H95" t="n">
         <v>3000</v>
@@ -3153,7 +3153,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G96" t="n">
-        <v>0.674556910991669</v>
+        <v>0.674556851387024</v>
       </c>
       <c r="H96" t="n">
         <v>12000</v>
@@ -3211,7 +3211,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G98" t="n">
-        <v>0.666018128395081</v>
+        <v>0.666018187999725</v>
       </c>
       <c r="H98" t="n">
         <v>18000</v>
@@ -3240,7 +3240,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G99" t="n">
-        <v>0.677972376346588</v>
+        <v>0.677972316741943</v>
       </c>
       <c r="H99" t="n">
         <v>7500</v>
@@ -3269,7 +3269,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G100" t="n">
-        <v>0.676264584064484</v>
+        <v>0.676264643669128</v>
       </c>
       <c r="H100" t="n">
         <v>7500</v>
@@ -3298,7 +3298,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G101" t="n">
-        <v>0.676264584064484</v>
+        <v>0.676264643669128</v>
       </c>
       <c r="H101" t="n">
         <v>0</v>
@@ -3327,7 +3327,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G102" t="n">
-        <v>0.683095633983612</v>
+        <v>0.683095574378967</v>
       </c>
       <c r="H102" t="n">
         <v>10500</v>
@@ -3385,7 +3385,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G104" t="n">
-        <v>0.683095633983612</v>
+        <v>0.683095574378967</v>
       </c>
       <c r="H104" t="n">
         <v>49500</v>
@@ -3414,7 +3414,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G105" t="n">
-        <v>0.683095633983612</v>
+        <v>0.683095574378967</v>
       </c>
       <c r="H105" t="n">
         <v>13500</v>
@@ -3443,7 +3443,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G106" t="n">
-        <v>0.683095633983612</v>
+        <v>0.683095574378967</v>
       </c>
       <c r="H106" t="n">
         <v>1500</v>
@@ -3472,7 +3472,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G107" t="n">
-        <v>0.691634237766266</v>
+        <v>0.691634178161621</v>
       </c>
       <c r="H107" t="n">
         <v>42000</v>
@@ -3501,7 +3501,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G108" t="n">
-        <v>0.700172901153564</v>
+        <v>0.700172960758209</v>
       </c>
       <c r="H108" t="n">
         <v>55500</v>
@@ -3530,7 +3530,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G109" t="n">
-        <v>0.683095633983612</v>
+        <v>0.683095574378967</v>
       </c>
       <c r="H109" t="n">
         <v>13500</v>
@@ -3588,7 +3588,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G111" t="n">
-        <v>0.703588485717773</v>
+        <v>0.703588426113129</v>
       </c>
       <c r="H111" t="n">
         <v>24000</v>
@@ -3617,7 +3617,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G112" t="n">
-        <v>0.686511039733887</v>
+        <v>0.686511099338531</v>
       </c>
       <c r="H112" t="n">
         <v>40500</v>
@@ -3646,7 +3646,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G113" t="n">
-        <v>0.691634237766266</v>
+        <v>0.691634178161621</v>
       </c>
       <c r="H113" t="n">
         <v>4500</v>
@@ -3675,7 +3675,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G114" t="n">
-        <v>0.700172901153564</v>
+        <v>0.700172960758209</v>
       </c>
       <c r="H114" t="n">
         <v>21000</v>
@@ -3704,7 +3704,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G115" t="n">
-        <v>0.703588485717773</v>
+        <v>0.703588426113129</v>
       </c>
       <c r="H115" t="n">
         <v>7500</v>
@@ -3791,7 +3791,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G118" t="n">
-        <v>0.717250347137451</v>
+        <v>0.717250287532806</v>
       </c>
       <c r="H118" t="n">
         <v>69000</v>
@@ -3820,7 +3820,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G119" t="n">
-        <v>0.715542614459991</v>
+        <v>0.715542674064636</v>
       </c>
       <c r="H119" t="n">
         <v>16500</v>
@@ -3849,7 +3849,7 @@
         <v>0.867999970912933</v>
       </c>
       <c r="G120" t="n">
-        <v>0.741158664226532</v>
+        <v>0.741158604621887</v>
       </c>
       <c r="H120" t="n">
         <v>139500</v>
@@ -3878,7 +3878,7 @@
         <v>0.867999970912933</v>
       </c>
       <c r="G121" t="n">
-        <v>0.741158664226532</v>
+        <v>0.741158604621887</v>
       </c>
       <c r="H121" t="n">
         <v>151500</v>
@@ -3994,7 +3994,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G125" t="n">
-        <v>0.836792051792145</v>
+        <v>0.8367919921875</v>
       </c>
       <c r="H125" t="n">
         <v>196500</v>
@@ -4023,7 +4023,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G126" t="n">
-        <v>0.836792051792145</v>
+        <v>0.8367919921875</v>
       </c>
       <c r="H126" t="n">
         <v>76500</v>
@@ -4052,7 +4052,7 @@
         <v>1</v>
       </c>
       <c r="G127" t="n">
-        <v>0.853869438171387</v>
+        <v>0.853869378566742</v>
       </c>
       <c r="H127" t="n">
         <v>66000</v>
@@ -4168,7 +4168,7 @@
         <v>0.994000017642975</v>
       </c>
       <c r="G131" t="n">
-        <v>0.848746240139008</v>
+        <v>0.848746299743652</v>
       </c>
       <c r="H131" t="n">
         <v>60000</v>
@@ -4226,7 +4226,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G133" t="n">
-        <v>0.870946824550629</v>
+        <v>0.870946884155273</v>
       </c>
       <c r="H133" t="n">
         <v>19500</v>
@@ -4255,7 +4255,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G134" t="n">
-        <v>0.8752161860466</v>
+        <v>0.875216126441956</v>
       </c>
       <c r="H134" t="n">
         <v>19500</v>
@@ -4313,7 +4313,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G136" t="n">
-        <v>0.900832235813141</v>
+        <v>0.900832295417786</v>
       </c>
       <c r="H136" t="n">
         <v>127500</v>
@@ -4342,7 +4342,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G137" t="n">
-        <v>0.888024151325226</v>
+        <v>0.888024210929871</v>
       </c>
       <c r="H137" t="n">
         <v>33000</v>
@@ -4371,7 +4371,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G138" t="n">
-        <v>0.892293572425842</v>
+        <v>0.892293512821198</v>
       </c>
       <c r="H138" t="n">
         <v>82500</v>
@@ -4400,7 +4400,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G139" t="n">
-        <v>0.913640320301056</v>
+        <v>0.913640379905701</v>
       </c>
       <c r="H139" t="n">
         <v>4500</v>
@@ -4429,7 +4429,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G140" t="n">
-        <v>0.922178983688354</v>
+        <v>0.922179102897644</v>
       </c>
       <c r="H140" t="n">
         <v>22500</v>
@@ -4458,7 +4458,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G141" t="n">
-        <v>0.922178983688354</v>
+        <v>0.922179102897644</v>
       </c>
       <c r="H141" t="n">
         <v>67500</v>
@@ -4487,7 +4487,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G142" t="n">
-        <v>0.913640320301056</v>
+        <v>0.913640379905701</v>
       </c>
       <c r="H142" t="n">
         <v>42000</v>
@@ -4516,7 +4516,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G143" t="n">
-        <v>0.930717647075653</v>
+        <v>0.930717766284943</v>
       </c>
       <c r="H143" t="n">
         <v>45000</v>
@@ -4545,7 +4545,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G144" t="n">
-        <v>1.17833983898163</v>
+        <v>1.17833995819092</v>
       </c>
       <c r="H144" t="n">
         <v>451500</v>
@@ -4574,7 +4574,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G145" t="n">
-        <v>1.11429965496063</v>
+        <v>1.11429953575134</v>
       </c>
       <c r="H145" t="n">
         <v>834000</v>
@@ -4719,7 +4719,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G150" t="n">
-        <v>1.18638002872467</v>
+        <v>1.18637990951538</v>
       </c>
       <c r="H150" t="n">
         <v>103500</v>
@@ -4748,7 +4748,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G151" t="n">
-        <v>1.21274387836456</v>
+        <v>1.21274399757385</v>
       </c>
       <c r="H151" t="n">
         <v>76500</v>
@@ -4864,7 +4864,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G155" t="n">
-        <v>1.13804578781128</v>
+        <v>1.13804590702057</v>
       </c>
       <c r="H155" t="n">
         <v>30000</v>
@@ -5009,7 +5009,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G160" t="n">
-        <v>1.05455994606018</v>
+        <v>1.05455982685089</v>
       </c>
       <c r="H160" t="n">
         <v>49500</v>
@@ -5067,7 +5067,7 @@
         <v>1.25</v>
       </c>
       <c r="G162" t="n">
-        <v>1.09849989414215</v>
+        <v>1.09850001335144</v>
       </c>
       <c r="H162" t="n">
         <v>39000</v>
@@ -5154,7 +5154,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G165" t="n">
-        <v>1.1688038110733</v>
+        <v>1.16880393028259</v>
       </c>
       <c r="H165" t="n">
         <v>52500</v>
@@ -5183,7 +5183,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G166" t="n">
-        <v>1.16001582145691</v>
+        <v>1.1600159406662</v>
       </c>
       <c r="H166" t="n">
         <v>49500</v>
@@ -5328,7 +5328,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G171" t="n">
-        <v>1.13804578781128</v>
+        <v>1.13804590702057</v>
       </c>
       <c r="H171" t="n">
         <v>9000</v>
@@ -5386,7 +5386,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G173" t="n">
-        <v>1.18638002872467</v>
+        <v>1.18637990951538</v>
       </c>
       <c r="H173" t="n">
         <v>85500</v>
@@ -5444,7 +5444,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G175" t="n">
-        <v>1.23031973838806</v>
+        <v>1.23031985759735</v>
       </c>
       <c r="H175" t="n">
         <v>234000</v>
@@ -5647,7 +5647,7 @@
         <v>1.5</v>
       </c>
       <c r="G182" t="n">
-        <v>1.31819987297058</v>
+        <v>1.31819975376129</v>
       </c>
       <c r="H182" t="n">
         <v>39000</v>
@@ -5676,7 +5676,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G183" t="n">
-        <v>1.283047914505</v>
+        <v>1.28304779529572</v>
       </c>
       <c r="H183" t="n">
         <v>180000</v>
@@ -5734,7 +5734,7 @@
         <v>1.5</v>
       </c>
       <c r="G185" t="n">
-        <v>1.31819987297058</v>
+        <v>1.31819975376129</v>
       </c>
       <c r="H185" t="n">
         <v>19500</v>
@@ -5763,7 +5763,7 @@
         <v>1.5</v>
       </c>
       <c r="G186" t="n">
-        <v>1.31819987297058</v>
+        <v>1.31819975376129</v>
       </c>
       <c r="H186" t="n">
         <v>31500</v>
@@ -5792,7 +5792,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G187" t="n">
-        <v>1.30062401294708</v>
+        <v>1.30062389373779</v>
       </c>
       <c r="H187" t="n">
         <v>25500</v>
@@ -5995,7 +5995,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G194" t="n">
-        <v>1.34016978740692</v>
+        <v>1.34016990661621</v>
       </c>
       <c r="H194" t="n">
         <v>85500</v>
@@ -6198,7 +6198,7 @@
         <v>1.5</v>
       </c>
       <c r="G201" t="n">
-        <v>1.31819987297058</v>
+        <v>1.31819975376129</v>
       </c>
       <c r="H201" t="n">
         <v>16500</v>
@@ -6227,7 +6227,7 @@
         <v>1.5</v>
       </c>
       <c r="G202" t="n">
-        <v>1.31819987297058</v>
+        <v>1.31819975376129</v>
       </c>
       <c r="H202" t="n">
         <v>3000</v>
@@ -6256,7 +6256,7 @@
         <v>1.5</v>
       </c>
       <c r="G203" t="n">
-        <v>1.31819987297058</v>
+        <v>1.31819975376129</v>
       </c>
       <c r="H203" t="n">
         <v>12000</v>
@@ -6401,7 +6401,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G208" t="n">
-        <v>1.35335183143616</v>
+        <v>1.35335195064545</v>
       </c>
       <c r="H208" t="n">
         <v>1500</v>
@@ -6430,7 +6430,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G209" t="n">
-        <v>1.35335183143616</v>
+        <v>1.35335195064545</v>
       </c>
       <c r="H209" t="n">
         <v>0</v>
@@ -6459,7 +6459,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G210" t="n">
-        <v>1.35335183143616</v>
+        <v>1.35335195064545</v>
       </c>
       <c r="H210" t="n">
         <v>0</v>
@@ -6488,7 +6488,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G211" t="n">
-        <v>1.29183602333069</v>
+        <v>1.2918359041214</v>
       </c>
       <c r="H211" t="n">
         <v>45000</v>
@@ -6546,7 +6546,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G213" t="n">
-        <v>1.30062401294708</v>
+        <v>1.30062389373779</v>
       </c>
       <c r="H213" t="n">
         <v>6000</v>
@@ -6633,7 +6633,7 @@
         <v>1.5</v>
       </c>
       <c r="G216" t="n">
-        <v>1.31819987297058</v>
+        <v>1.31819975376129</v>
       </c>
       <c r="H216" t="n">
         <v>15000</v>
@@ -6691,7 +6691,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G218" t="n">
-        <v>1.24789583683014</v>
+        <v>1.24789595603943</v>
       </c>
       <c r="H218" t="n">
         <v>33000</v>
@@ -6720,7 +6720,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G219" t="n">
-        <v>1.23031973838806</v>
+        <v>1.23031985759735</v>
       </c>
       <c r="H219" t="n">
         <v>70500</v>
@@ -6807,7 +6807,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G222" t="n">
-        <v>1.29183602333069</v>
+        <v>1.2918359041214</v>
       </c>
       <c r="H222" t="n">
         <v>9000</v>
@@ -6865,7 +6865,7 @@
         <v>1.5</v>
       </c>
       <c r="G224" t="n">
-        <v>1.31819987297058</v>
+        <v>1.31819975376129</v>
       </c>
       <c r="H224" t="n">
         <v>13500</v>
@@ -6894,7 +6894,7 @@
         <v>1.5</v>
       </c>
       <c r="G225" t="n">
-        <v>1.31819987297058</v>
+        <v>1.31819975376129</v>
       </c>
       <c r="H225" t="n">
         <v>0</v>
@@ -6923,7 +6923,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G226" t="n">
-        <v>1.30062401294708</v>
+        <v>1.30062389373779</v>
       </c>
       <c r="H226" t="n">
         <v>4500</v>
@@ -6952,7 +6952,7 @@
         <v>1.5</v>
       </c>
       <c r="G227" t="n">
-        <v>1.31819987297058</v>
+        <v>1.31819975376129</v>
       </c>
       <c r="H227" t="n">
         <v>13500</v>
@@ -6981,7 +6981,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G228" t="n">
-        <v>1.29183602333069</v>
+        <v>1.2918359041214</v>
       </c>
       <c r="H228" t="n">
         <v>27000</v>
@@ -7010,7 +7010,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G229" t="n">
-        <v>1.27425980567932</v>
+        <v>1.27425992488861</v>
       </c>
       <c r="H229" t="n">
         <v>6000</v>
@@ -7068,7 +7068,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G231" t="n">
-        <v>1.283047914505</v>
+        <v>1.28304779529572</v>
       </c>
       <c r="H231" t="n">
         <v>4500</v>
@@ -7126,7 +7126,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G233" t="n">
-        <v>1.34016978740692</v>
+        <v>1.34016990661621</v>
       </c>
       <c r="H233" t="n">
         <v>61500</v>
@@ -7300,7 +7300,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G239" t="n">
-        <v>1.34016978740692</v>
+        <v>1.34016990661621</v>
       </c>
       <c r="H239" t="n">
         <v>69000</v>
@@ -7358,7 +7358,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G241" t="n">
-        <v>2.24972748756409</v>
+        <v>2.24972772598267</v>
       </c>
       <c r="H241" t="n">
         <v>774000</v>
@@ -7387,7 +7387,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G242" t="n">
-        <v>2.08275580406189</v>
+        <v>2.08275556564331</v>
       </c>
       <c r="H242" t="n">
         <v>1374000</v>
@@ -7503,7 +7503,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G246" t="n">
-        <v>2.27609157562256</v>
+        <v>2.27609181404114</v>
       </c>
       <c r="H246" t="n">
         <v>229500</v>
@@ -7561,7 +7561,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G248" t="n">
-        <v>2.27609157562256</v>
+        <v>2.27609181404114</v>
       </c>
       <c r="H248" t="n">
         <v>240000</v>
@@ -7706,7 +7706,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G253" t="n">
-        <v>2.3288197517395</v>
+        <v>2.32881999015808</v>
       </c>
       <c r="H253" t="n">
         <v>237000</v>
@@ -7735,7 +7735,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G254" t="n">
-        <v>2.34639549255371</v>
+        <v>2.34639596939087</v>
       </c>
       <c r="H254" t="n">
         <v>139500</v>
@@ -7764,7 +7764,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G255" t="n">
-        <v>2.33760762214661</v>
+        <v>2.33760786056519</v>
       </c>
       <c r="H255" t="n">
         <v>108000</v>
@@ -7793,7 +7793,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G256" t="n">
-        <v>2.3288197517395</v>
+        <v>2.32881999015808</v>
       </c>
       <c r="H256" t="n">
         <v>75000</v>
@@ -7851,7 +7851,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G258" t="n">
-        <v>2.28487968444824</v>
+        <v>2.28487992286682</v>
       </c>
       <c r="H258" t="n">
         <v>138000</v>
@@ -7909,7 +7909,7 @@
         <v>2.5</v>
       </c>
       <c r="G260" t="n">
-        <v>2.1969997882843</v>
+        <v>2.19700002670288</v>
       </c>
       <c r="H260" t="n">
         <v>85500</v>
@@ -7938,7 +7938,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G261" t="n">
-        <v>2.21457576751709</v>
+        <v>2.21457600593567</v>
       </c>
       <c r="H261" t="n">
         <v>55500</v>
@@ -7967,7 +7967,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G262" t="n">
-        <v>2.24972748756409</v>
+        <v>2.24972772598267</v>
       </c>
       <c r="H262" t="n">
         <v>33000</v>
@@ -7996,7 +7996,7 @@
         <v>2.5</v>
       </c>
       <c r="G263" t="n">
-        <v>2.1969997882843</v>
+        <v>2.19700002670288</v>
       </c>
       <c r="H263" t="n">
         <v>13500</v>
@@ -8054,7 +8054,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G265" t="n">
-        <v>2.34639549255371</v>
+        <v>2.34639596939087</v>
       </c>
       <c r="H265" t="n">
         <v>46500</v>
@@ -8112,7 +8112,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G267" t="n">
-        <v>2.27609157562256</v>
+        <v>2.27609181404114</v>
       </c>
       <c r="H267" t="n">
         <v>61500</v>
@@ -8141,7 +8141,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G268" t="n">
-        <v>2.38154792785645</v>
+        <v>2.38154768943787</v>
       </c>
       <c r="H268" t="n">
         <v>88500</v>
@@ -8170,7 +8170,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G269" t="n">
-        <v>2.31124377250671</v>
+        <v>2.31124401092529</v>
       </c>
       <c r="H269" t="n">
         <v>54000</v>
@@ -8228,7 +8228,7 @@
         <v>2.5</v>
       </c>
       <c r="G271" t="n">
-        <v>2.1969997882843</v>
+        <v>2.19700002670288</v>
       </c>
       <c r="H271" t="n">
         <v>36000</v>
@@ -8286,7 +8286,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G273" t="n">
-        <v>2.27609157562256</v>
+        <v>2.27609181404114</v>
       </c>
       <c r="H273" t="n">
         <v>94500</v>
@@ -8315,7 +8315,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G274" t="n">
-        <v>2.24972748756409</v>
+        <v>2.24972772598267</v>
       </c>
       <c r="H274" t="n">
         <v>45000</v>
@@ -8344,7 +8344,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G275" t="n">
-        <v>2.28487968444824</v>
+        <v>2.28487992286682</v>
       </c>
       <c r="H275" t="n">
         <v>18000</v>
@@ -8373,7 +8373,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G276" t="n">
-        <v>2.28487968444824</v>
+        <v>2.28487992286682</v>
       </c>
       <c r="H276" t="n">
         <v>6000</v>
@@ -8431,7 +8431,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G278" t="n">
-        <v>2.3288197517395</v>
+        <v>2.32881999015808</v>
       </c>
       <c r="H278" t="n">
         <v>33000</v>
@@ -8460,7 +8460,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G279" t="n">
-        <v>2.32003164291382</v>
+        <v>2.3200318813324</v>
       </c>
       <c r="H279" t="n">
         <v>10500</v>
@@ -8489,7 +8489,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G280" t="n">
-        <v>2.28487968444824</v>
+        <v>2.28487992286682</v>
       </c>
       <c r="H280" t="n">
         <v>16500</v>
@@ -8518,7 +8518,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G281" t="n">
-        <v>2.3288197517395</v>
+        <v>2.32881999015808</v>
       </c>
       <c r="H281" t="n">
         <v>25500</v>
@@ -8605,7 +8605,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G284" t="n">
-        <v>2.32003164291382</v>
+        <v>2.3200318813324</v>
       </c>
       <c r="H284" t="n">
         <v>18000</v>
@@ -8634,7 +8634,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G285" t="n">
-        <v>2.27609157562256</v>
+        <v>2.27609181404114</v>
       </c>
       <c r="H285" t="n">
         <v>24000</v>
@@ -8750,7 +8750,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G289" t="n">
-        <v>2.32003164291382</v>
+        <v>2.3200318813324</v>
       </c>
       <c r="H289" t="n">
         <v>87000</v>
@@ -8808,7 +8808,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G291" t="n">
-        <v>2.27609157562256</v>
+        <v>2.27609181404114</v>
       </c>
       <c r="H291" t="n">
         <v>18000</v>
@@ -8837,7 +8837,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G292" t="n">
-        <v>2.21457576751709</v>
+        <v>2.21457600593567</v>
       </c>
       <c r="H292" t="n">
         <v>16500</v>
@@ -8866,7 +8866,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G293" t="n">
-        <v>2.24972748756409</v>
+        <v>2.24972772598267</v>
       </c>
       <c r="H293" t="n">
         <v>1500</v>
@@ -8895,7 +8895,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G294" t="n">
-        <v>2.28487968444824</v>
+        <v>2.28487992286682</v>
       </c>
       <c r="H294" t="n">
         <v>1500</v>
@@ -8982,7 +8982,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G297" t="n">
-        <v>2.21457576751709</v>
+        <v>2.21457600593567</v>
       </c>
       <c r="H297" t="n">
         <v>12000</v>
@@ -9011,7 +9011,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G298" t="n">
-        <v>2.21457576751709</v>
+        <v>2.21457600593567</v>
       </c>
       <c r="H298" t="n">
         <v>21000</v>
@@ -9098,7 +9098,7 @@
         <v>2.5</v>
       </c>
       <c r="G301" t="n">
-        <v>2.1969997882843</v>
+        <v>2.19700002670288</v>
       </c>
       <c r="H301" t="n">
         <v>21000</v>
@@ -9127,7 +9127,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G302" t="n">
-        <v>2.14427208900452</v>
+        <v>2.14427185058594</v>
       </c>
       <c r="H302" t="n">
         <v>31500</v>
@@ -9185,7 +9185,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G304" t="n">
-        <v>2.03881597518921</v>
+        <v>2.03881573677063</v>
       </c>
       <c r="H304" t="n">
         <v>51000</v>
@@ -9301,7 +9301,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G308" t="n">
-        <v>2.02123975753784</v>
+        <v>2.02123951911926</v>
       </c>
       <c r="H308" t="n">
         <v>12000</v>
@@ -9330,7 +9330,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G309" t="n">
-        <v>1.93335998058319</v>
+        <v>1.93335974216461</v>
       </c>
       <c r="H309" t="n">
         <v>18000</v>
@@ -9388,7 +9388,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G311" t="n">
-        <v>1.88941991329193</v>
+        <v>1.88941979408264</v>
       </c>
       <c r="H311" t="n">
         <v>34500</v>
@@ -9417,7 +9417,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G312" t="n">
-        <v>1.82790386676788</v>
+        <v>1.82790374755859</v>
       </c>
       <c r="H312" t="n">
         <v>37500</v>
@@ -9446,7 +9446,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G313" t="n">
-        <v>1.93335998058319</v>
+        <v>1.93335974216461</v>
       </c>
       <c r="H313" t="n">
         <v>18000</v>
@@ -9475,7 +9475,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G314" t="n">
-        <v>1.93335998058319</v>
+        <v>1.93335974216461</v>
       </c>
       <c r="H314" t="n">
         <v>6000</v>
@@ -9533,7 +9533,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G316" t="n">
-        <v>2.08275580406189</v>
+        <v>2.08275556564331</v>
       </c>
       <c r="H316" t="n">
         <v>48000</v>
@@ -9591,7 +9591,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G318" t="n">
-        <v>2.09154391288757</v>
+        <v>2.09154367446899</v>
       </c>
       <c r="H318" t="n">
         <v>12000</v>
@@ -9649,7 +9649,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G320" t="n">
-        <v>2.14427208900452</v>
+        <v>2.14427185058594</v>
       </c>
       <c r="H320" t="n">
         <v>9000</v>
@@ -9678,7 +9678,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G321" t="n">
-        <v>2.14427208900452</v>
+        <v>2.14427185058594</v>
       </c>
       <c r="H321" t="n">
         <v>3000</v>
@@ -9794,7 +9794,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G325" t="n">
-        <v>1.94214797019958</v>
+        <v>1.94214773178101</v>
       </c>
       <c r="H325" t="n">
         <v>7500</v>
@@ -9852,7 +9852,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G327" t="n">
-        <v>1.91578376293182</v>
+        <v>1.9157840013504</v>
       </c>
       <c r="H327" t="n">
         <v>24000</v>
@@ -9881,7 +9881,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G328" t="n">
-        <v>1.88941991329193</v>
+        <v>1.88941979408264</v>
       </c>
       <c r="H328" t="n">
         <v>31500</v>
@@ -10055,7 +10055,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G334" t="n">
-        <v>2.03881597518921</v>
+        <v>2.03881573677063</v>
       </c>
       <c r="H334" t="n">
         <v>7500</v>
@@ -10113,7 +10113,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G336" t="n">
-        <v>2.02123975753784</v>
+        <v>2.02123951911926</v>
       </c>
       <c r="H336" t="n">
         <v>10500</v>
@@ -10142,7 +10142,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G337" t="n">
-        <v>2.10911989212036</v>
+        <v>2.10911965370178</v>
       </c>
       <c r="H337" t="n">
         <v>9000</v>
@@ -10171,7 +10171,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G338" t="n">
-        <v>2.056391954422</v>
+        <v>2.05639171600342</v>
       </c>
       <c r="H338" t="n">
         <v>3000</v>
@@ -10200,7 +10200,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G339" t="n">
-        <v>2.08275580406189</v>
+        <v>2.08275556564331</v>
       </c>
       <c r="H339" t="n">
         <v>3000</v>
@@ -10229,7 +10229,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G340" t="n">
-        <v>2.03881597518921</v>
+        <v>2.03881573677063</v>
       </c>
       <c r="H340" t="n">
         <v>3000</v>
@@ -10345,7 +10345,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G344" t="n">
-        <v>1.95972383022308</v>
+        <v>1.9597235918045</v>
       </c>
       <c r="H344" t="n">
         <v>27000</v>
@@ -10461,7 +10461,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G348" t="n">
-        <v>1.93335998058319</v>
+        <v>1.93335974216461</v>
       </c>
       <c r="H348" t="n">
         <v>1500</v>
@@ -10577,7 +10577,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G352" t="n">
-        <v>1.81032764911652</v>
+        <v>1.81032776832581</v>
       </c>
       <c r="H352" t="n">
         <v>10500</v>
@@ -10606,7 +10606,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G353" t="n">
-        <v>1.88941991329193</v>
+        <v>1.88941979408264</v>
       </c>
       <c r="H353" t="n">
         <v>7500</v>
@@ -10751,7 +10751,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G358" t="n">
-        <v>2.03881597518921</v>
+        <v>2.03881573677063</v>
       </c>
       <c r="H358" t="n">
         <v>10500</v>
@@ -10983,7 +10983,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G366" t="n">
-        <v>1.93335998058319</v>
+        <v>1.93335974216461</v>
       </c>
       <c r="H366" t="n">
         <v>13500</v>
@@ -11012,7 +11012,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G367" t="n">
-        <v>1.93335998058319</v>
+        <v>1.93335974216461</v>
       </c>
       <c r="H367" t="n">
         <v>1500</v>
@@ -11099,7 +11099,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G370" t="n">
-        <v>1.93335998058319</v>
+        <v>1.93335974216461</v>
       </c>
       <c r="H370" t="n">
         <v>6000</v>
@@ -11128,7 +11128,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G371" t="n">
-        <v>1.93335998058319</v>
+        <v>1.93335974216461</v>
       </c>
       <c r="H371" t="n">
         <v>1500</v>
@@ -11215,7 +11215,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G374" t="n">
-        <v>1.77517580986023</v>
+        <v>1.77517592906952</v>
       </c>
       <c r="H374" t="n">
         <v>52500</v>
@@ -11360,7 +11360,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G379" t="n">
-        <v>1.93335998058319</v>
+        <v>1.93335974216461</v>
       </c>
       <c r="H379" t="n">
         <v>3000</v>
@@ -11418,7 +11418,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G381" t="n">
-        <v>1.74002385139465</v>
+        <v>1.74002373218536</v>
       </c>
       <c r="H381" t="n">
         <v>34500</v>
@@ -11592,7 +11592,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G387" t="n">
-        <v>1.89820790290833</v>
+        <v>1.89820802211761</v>
       </c>
       <c r="H387" t="n">
         <v>28500</v>
@@ -11679,7 +11679,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G390" t="n">
-        <v>1.93335998058319</v>
+        <v>1.93335974216461</v>
       </c>
       <c r="H390" t="n">
         <v>1500</v>
@@ -11911,7 +11911,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G398" t="n">
-        <v>2.056391954422</v>
+        <v>2.05639171600342</v>
       </c>
       <c r="H398" t="n">
         <v>10500</v>
@@ -11969,7 +11969,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G400" t="n">
-        <v>2.02123975753784</v>
+        <v>2.02123951911926</v>
       </c>
       <c r="H400" t="n">
         <v>10500</v>
@@ -12027,7 +12027,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G402" t="n">
-        <v>2.056391954422</v>
+        <v>2.05639171600342</v>
       </c>
       <c r="H402" t="n">
         <v>36000</v>
@@ -12056,7 +12056,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G403" t="n">
-        <v>1.93335998058319</v>
+        <v>1.93335974216461</v>
       </c>
       <c r="H403" t="n">
         <v>7500</v>
@@ -12172,7 +12172,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G407" t="n">
-        <v>1.84547984600067</v>
+        <v>1.84547972679138</v>
       </c>
       <c r="H407" t="n">
         <v>64500</v>
@@ -12201,7 +12201,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G408" t="n">
-        <v>1.89820790290833</v>
+        <v>1.89820802211761</v>
       </c>
       <c r="H408" t="n">
         <v>6000</v>
@@ -12230,7 +12230,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G409" t="n">
-        <v>1.88941991329193</v>
+        <v>1.88941979408264</v>
       </c>
       <c r="H409" t="n">
         <v>6000</v>
@@ -12259,7 +12259,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G410" t="n">
-        <v>1.88941991329193</v>
+        <v>1.88941979408264</v>
       </c>
       <c r="H410" t="n">
         <v>0</v>
@@ -12288,7 +12288,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G411" t="n">
-        <v>1.87184393405914</v>
+        <v>1.87184381484985</v>
       </c>
       <c r="H411" t="n">
         <v>4500</v>
@@ -12404,7 +12404,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G415" t="n">
-        <v>1.81911587715149</v>
+        <v>1.8191157579422</v>
       </c>
       <c r="H415" t="n">
         <v>4500</v>
@@ -12433,7 +12433,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G416" t="n">
-        <v>1.81911587715149</v>
+        <v>1.8191157579422</v>
       </c>
       <c r="H416" t="n">
         <v>0</v>
@@ -12491,7 +12491,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G418" t="n">
-        <v>1.81032764911652</v>
+        <v>1.81032776832581</v>
       </c>
       <c r="H418" t="n">
         <v>6000</v>
@@ -12520,7 +12520,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G419" t="n">
-        <v>1.91578376293182</v>
+        <v>1.9157840013504</v>
       </c>
       <c r="H419" t="n">
         <v>18000</v>
@@ -12549,7 +12549,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G420" t="n">
-        <v>1.89820790290833</v>
+        <v>1.89820802211761</v>
       </c>
       <c r="H420" t="n">
         <v>6000</v>
@@ -12578,7 +12578,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G421" t="n">
-        <v>1.91578376293182</v>
+        <v>1.9157840013504</v>
       </c>
       <c r="H421" t="n">
         <v>1500</v>
@@ -12636,7 +12636,7 @@
         <v>2</v>
       </c>
       <c r="G423" t="n">
-        <v>1.75759983062744</v>
+        <v>1.75759971141815</v>
       </c>
       <c r="H423" t="n">
         <v>25500</v>
@@ -12665,7 +12665,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G424" t="n">
-        <v>1.77517580986023</v>
+        <v>1.77517592906952</v>
       </c>
       <c r="H424" t="n">
         <v>7500</v>
@@ -12694,7 +12694,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G425" t="n">
-        <v>1.74002385139465</v>
+        <v>1.74002373218536</v>
       </c>
       <c r="H425" t="n">
         <v>3000</v>
@@ -12723,7 +12723,7 @@
         <v>2</v>
       </c>
       <c r="G426" t="n">
-        <v>1.75759983062744</v>
+        <v>1.75759971141815</v>
       </c>
       <c r="H426" t="n">
         <v>4500</v>
@@ -12868,7 +12868,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G431" t="n">
-        <v>1.84547984600067</v>
+        <v>1.84547972679138</v>
       </c>
       <c r="H431" t="n">
         <v>6000</v>
@@ -12897,7 +12897,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G432" t="n">
-        <v>1.77517580986023</v>
+        <v>1.77517592906952</v>
       </c>
       <c r="H432" t="n">
         <v>3000</v>
@@ -13100,7 +13100,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G439" t="n">
-        <v>1.81911587715149</v>
+        <v>1.8191157579422</v>
       </c>
       <c r="H439" t="n">
         <v>6000</v>
@@ -13129,7 +13129,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G440" t="n">
-        <v>1.81911587715149</v>
+        <v>1.8191157579422</v>
       </c>
       <c r="H440" t="n">
         <v>0</v>
@@ -13216,7 +13216,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G443" t="n">
-        <v>1.82790386676788</v>
+        <v>1.82790374755859</v>
       </c>
       <c r="H443" t="n">
         <v>4500</v>
@@ -13274,7 +13274,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G445" t="n">
-        <v>1.82790386676788</v>
+        <v>1.82790374755859</v>
       </c>
       <c r="H445" t="n">
         <v>1500</v>
@@ -13303,7 +13303,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G446" t="n">
-        <v>1.82790386676788</v>
+        <v>1.82790374755859</v>
       </c>
       <c r="H446" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G448" t="n">
-        <v>1.7356299161911</v>
+        <v>1.73563003540039</v>
       </c>
       <c r="H448" t="n">
         <v>3000</v>
@@ -13390,7 +13390,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G449" t="n">
-        <v>1.68290185928345</v>
+        <v>1.68290174007416</v>
       </c>
       <c r="H449" t="n">
         <v>6000</v>
@@ -13419,7 +13419,7 @@
         <v>2</v>
       </c>
       <c r="G450" t="n">
-        <v>1.75759983062744</v>
+        <v>1.75759971141815</v>
       </c>
       <c r="H450" t="n">
         <v>10500</v>
@@ -13448,7 +13448,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G451" t="n">
-        <v>1.74002385139465</v>
+        <v>1.74002373218536</v>
       </c>
       <c r="H451" t="n">
         <v>4500</v>
@@ -13477,7 +13477,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G452" t="n">
-        <v>1.72684180736542</v>
+        <v>1.72684192657471</v>
       </c>
       <c r="H452" t="n">
         <v>3000</v>
@@ -13854,7 +13854,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G465" t="n">
-        <v>1.65214371681213</v>
+        <v>1.65214383602142</v>
       </c>
       <c r="H465" t="n">
         <v>9000</v>
@@ -13912,7 +13912,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G467" t="n">
-        <v>1.59502184391022</v>
+        <v>1.59502196311951</v>
       </c>
       <c r="H467" t="n">
         <v>3000</v>
@@ -13941,7 +13941,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G468" t="n">
-        <v>1.66971981525421</v>
+        <v>1.6697199344635</v>
       </c>
       <c r="H468" t="n">
         <v>4500</v>
@@ -14028,7 +14028,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G471" t="n">
-        <v>1.59502184391022</v>
+        <v>1.59502196311951</v>
       </c>
       <c r="H471" t="n">
         <v>15000</v>
@@ -14115,7 +14115,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G474" t="n">
-        <v>1.66971981525421</v>
+        <v>1.6697199344635</v>
       </c>
       <c r="H474" t="n">
         <v>3000</v>
@@ -14289,7 +14289,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G480" t="n">
-        <v>1.63017380237579</v>
+        <v>1.63017392158508</v>
       </c>
       <c r="H480" t="n">
         <v>3000</v>
@@ -14434,7 +14434,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G485" t="n">
-        <v>1.81032764911652</v>
+        <v>1.81032776832581</v>
       </c>
       <c r="H485" t="n">
         <v>6000</v>
@@ -14463,7 +14463,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G486" t="n">
-        <v>1.87184393405914</v>
+        <v>1.87184381484985</v>
       </c>
       <c r="H486" t="n">
         <v>25500</v>
@@ -14492,7 +14492,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G487" t="n">
-        <v>1.93335998058319</v>
+        <v>1.93335974216461</v>
       </c>
       <c r="H487" t="n">
         <v>33000</v>
@@ -14579,7 +14579,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G490" t="n">
-        <v>2.03881597518921</v>
+        <v>2.03881573677063</v>
       </c>
       <c r="H490" t="n">
         <v>28500</v>
@@ -14608,7 +14608,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G491" t="n">
-        <v>2.03881597518921</v>
+        <v>2.03881573677063</v>
       </c>
       <c r="H491" t="n">
         <v>0</v>
@@ -14666,7 +14666,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G493" t="n">
-        <v>2.02123975753784</v>
+        <v>2.02123951911926</v>
       </c>
       <c r="H493" t="n">
         <v>42000</v>
@@ -14753,7 +14753,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G496" t="n">
-        <v>1.93335998058319</v>
+        <v>1.93335974216461</v>
       </c>
       <c r="H496" t="n">
         <v>6000</v>
@@ -14782,7 +14782,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G497" t="n">
-        <v>1.82790386676788</v>
+        <v>1.82790374755859</v>
       </c>
       <c r="H497" t="n">
         <v>21000</v>
@@ -14811,7 +14811,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G498" t="n">
-        <v>1.7356299161911</v>
+        <v>1.73563003540039</v>
       </c>
       <c r="H498" t="n">
         <v>40500</v>
@@ -15014,7 +15014,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G505" t="n">
-        <v>1.77517580986023</v>
+        <v>1.77517592906952</v>
       </c>
       <c r="H505" t="n">
         <v>3000</v>
@@ -15043,7 +15043,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G506" t="n">
-        <v>1.77517580986023</v>
+        <v>1.77517592906952</v>
       </c>
       <c r="H506" t="n">
         <v>3000</v>
@@ -15159,7 +15159,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G510" t="n">
-        <v>1.77517580986023</v>
+        <v>1.77517592906952</v>
       </c>
       <c r="H510" t="n">
         <v>4500</v>
@@ -15246,7 +15246,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G513" t="n">
-        <v>1.81032764911652</v>
+        <v>1.81032776832581</v>
       </c>
       <c r="H513" t="n">
         <v>3000</v>
@@ -15478,7 +15478,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G521" t="n">
-        <v>1.81032764911652</v>
+        <v>1.81032776832581</v>
       </c>
       <c r="H521" t="n">
         <v>4500</v>
@@ -15536,7 +15536,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G523" t="n">
-        <v>1.6785079240799</v>
+        <v>1.67850780487061</v>
       </c>
       <c r="H523" t="n">
         <v>9000</v>
@@ -15739,7 +15739,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G530" t="n">
-        <v>1.48517203330994</v>
+        <v>1.48517191410065</v>
       </c>
       <c r="H530" t="n">
         <v>7500</v>
@@ -15855,7 +15855,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G534" t="n">
-        <v>1.48517203330994</v>
+        <v>1.48517191410065</v>
       </c>
       <c r="H534" t="n">
         <v>1500</v>
@@ -15884,7 +15884,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G535" t="n">
-        <v>1.48517203330994</v>
+        <v>1.48517191410065</v>
       </c>
       <c r="H535" t="n">
         <v>0</v>
@@ -15971,7 +15971,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G538" t="n">
-        <v>1.55108165740967</v>
+        <v>1.55108177661896</v>
       </c>
       <c r="H538" t="n">
         <v>1500</v>
@@ -16000,7 +16000,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G539" t="n">
-        <v>1.55108165740967</v>
+        <v>1.55108177661896</v>
       </c>
       <c r="H539" t="n">
         <v>0</v>
@@ -16116,7 +16116,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G543" t="n">
-        <v>1.49395990371704</v>
+        <v>1.49395978450775</v>
       </c>
       <c r="H543" t="n">
         <v>1500</v>
@@ -16174,7 +16174,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G545" t="n">
-        <v>1.56426382064819</v>
+        <v>1.56426393985748</v>
       </c>
       <c r="H545" t="n">
         <v>4500</v>
@@ -16261,7 +16261,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G548" t="n">
-        <v>1.6785079240799</v>
+        <v>1.67850780487061</v>
       </c>
       <c r="H548" t="n">
         <v>3000</v>
@@ -16290,7 +16290,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G549" t="n">
-        <v>1.6785079240799</v>
+        <v>1.67850780487061</v>
       </c>
       <c r="H549" t="n">
         <v>0</v>
@@ -16319,7 +16319,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G550" t="n">
-        <v>1.6785079240799</v>
+        <v>1.67850780487061</v>
       </c>
       <c r="H550" t="n">
         <v>0</v>
@@ -16348,7 +16348,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G551" t="n">
-        <v>1.72684180736542</v>
+        <v>1.72684192657471</v>
       </c>
       <c r="H551" t="n">
         <v>1500</v>
@@ -16435,7 +16435,7 @@
         <v>2</v>
       </c>
       <c r="G554" t="n">
-        <v>1.75759983062744</v>
+        <v>1.75759971141815</v>
       </c>
       <c r="H554" t="n">
         <v>1500</v>
@@ -16464,7 +16464,7 @@
         <v>2</v>
       </c>
       <c r="G555" t="n">
-        <v>1.75759983062744</v>
+        <v>1.75759971141815</v>
       </c>
       <c r="H555" t="n">
         <v>0</v>
@@ -16493,7 +16493,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G556" t="n">
-        <v>1.66971981525421</v>
+        <v>1.6697199344635</v>
       </c>
       <c r="H556" t="n">
         <v>6000</v>
@@ -16522,7 +16522,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G557" t="n">
-        <v>1.66971981525421</v>
+        <v>1.6697199344635</v>
       </c>
       <c r="H557" t="n">
         <v>3000</v>
@@ -16551,7 +16551,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G558" t="n">
-        <v>1.72684180736542</v>
+        <v>1.72684192657471</v>
       </c>
       <c r="H558" t="n">
         <v>13500</v>
@@ -16580,7 +16580,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G559" t="n">
-        <v>1.72684180736542</v>
+        <v>1.72684192657471</v>
       </c>
       <c r="H559" t="n">
         <v>0</v>
@@ -16609,7 +16609,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G560" t="n">
-        <v>1.6785079240799</v>
+        <v>1.67850780487061</v>
       </c>
       <c r="H560" t="n">
         <v>9000</v>
@@ -16638,7 +16638,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G561" t="n">
-        <v>1.6785079240799</v>
+        <v>1.67850780487061</v>
       </c>
       <c r="H561" t="n">
         <v>0</v>
@@ -16667,7 +16667,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G562" t="n">
-        <v>1.6785079240799</v>
+        <v>1.67850780487061</v>
       </c>
       <c r="H562" t="n">
         <v>0</v>
@@ -16696,7 +16696,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G563" t="n">
-        <v>1.6785079240799</v>
+        <v>1.67850780487061</v>
       </c>
       <c r="H563" t="n">
         <v>0</v>
@@ -16725,7 +16725,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G564" t="n">
-        <v>1.6785079240799</v>
+        <v>1.67850780487061</v>
       </c>
       <c r="H564" t="n">
         <v>0</v>
@@ -16754,7 +16754,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G565" t="n">
-        <v>1.6785079240799</v>
+        <v>1.67850780487061</v>
       </c>
       <c r="H565" t="n">
         <v>0</v>
@@ -16986,7 +16986,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G573" t="n">
-        <v>1.66971981525421</v>
+        <v>1.6697199344635</v>
       </c>
       <c r="H573" t="n">
         <v>1500</v>
@@ -17015,7 +17015,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G574" t="n">
-        <v>1.66971981525421</v>
+        <v>1.6697199344635</v>
       </c>
       <c r="H574" t="n">
         <v>0</v>
@@ -17044,7 +17044,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G575" t="n">
-        <v>1.66971981525421</v>
+        <v>1.6697199344635</v>
       </c>
       <c r="H575" t="n">
         <v>0</v>
@@ -17073,7 +17073,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G576" t="n">
-        <v>1.66971981525421</v>
+        <v>1.6697199344635</v>
       </c>
       <c r="H576" t="n">
         <v>0</v>
@@ -17102,7 +17102,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G577" t="n">
-        <v>1.66971981525421</v>
+        <v>1.6697199344635</v>
       </c>
       <c r="H577" t="n">
         <v>0</v>
@@ -17131,7 +17131,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G578" t="n">
-        <v>1.6785079240799</v>
+        <v>1.67850780487061</v>
       </c>
       <c r="H578" t="n">
         <v>1500</v>
@@ -17160,7 +17160,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G579" t="n">
-        <v>1.6785079240799</v>
+        <v>1.67850780487061</v>
       </c>
       <c r="H579" t="n">
         <v>0</v>
@@ -17189,7 +17189,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G580" t="n">
-        <v>1.6785079240799</v>
+        <v>1.67850780487061</v>
       </c>
       <c r="H580" t="n">
         <v>0</v>
@@ -17247,7 +17247,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G582" t="n">
-        <v>1.65214371681213</v>
+        <v>1.65214383602142</v>
       </c>
       <c r="H582" t="n">
         <v>1500</v>
@@ -17276,7 +17276,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G583" t="n">
-        <v>1.65214371681213</v>
+        <v>1.65214383602142</v>
       </c>
       <c r="H583" t="n">
         <v>0</v>
@@ -17566,7 +17566,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G593" t="n">
-        <v>1.55547571182251</v>
+        <v>1.5554758310318</v>
       </c>
       <c r="H593" t="n">
         <v>13500</v>
@@ -18030,7 +18030,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G609" t="n">
-        <v>1.61259782314301</v>
+        <v>1.61259794235229</v>
       </c>
       <c r="H609" t="n">
         <v>1500</v>
@@ -18262,7 +18262,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G617" t="n">
-        <v>1.75320589542389</v>
+        <v>1.7532057762146</v>
       </c>
       <c r="H617" t="n">
         <v>114000</v>
@@ -18291,7 +18291,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G618" t="n">
-        <v>1.6785079240799</v>
+        <v>1.67850780487061</v>
       </c>
       <c r="H618" t="n">
         <v>45000</v>
@@ -18349,7 +18349,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G620" t="n">
-        <v>1.71805381774902</v>
+        <v>1.71805393695831</v>
       </c>
       <c r="H620" t="n">
         <v>1500</v>
@@ -18378,7 +18378,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G621" t="n">
-        <v>1.66971981525421</v>
+        <v>1.6697199344635</v>
       </c>
       <c r="H621" t="n">
         <v>7500</v>
@@ -18407,7 +18407,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G622" t="n">
-        <v>1.68290185928345</v>
+        <v>1.68290174007416</v>
       </c>
       <c r="H622" t="n">
         <v>13500</v>
@@ -18465,7 +18465,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G624" t="n">
-        <v>1.66971981525421</v>
+        <v>1.6697199344635</v>
       </c>
       <c r="H624" t="n">
         <v>4500</v>
@@ -18639,7 +18639,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G630" t="n">
-        <v>1.88941991329193</v>
+        <v>1.88941979408264</v>
       </c>
       <c r="H630" t="n">
         <v>19500</v>
@@ -18668,7 +18668,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G631" t="n">
-        <v>1.81032764911652</v>
+        <v>1.81032776832581</v>
       </c>
       <c r="H631" t="n">
         <v>24000</v>
@@ -18726,7 +18726,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G633" t="n">
-        <v>1.81911587715149</v>
+        <v>1.8191157579422</v>
       </c>
       <c r="H633" t="n">
         <v>4500</v>
@@ -18755,7 +18755,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G634" t="n">
-        <v>1.81032764911652</v>
+        <v>1.81032776832581</v>
       </c>
       <c r="H634" t="n">
         <v>21000</v>
@@ -18813,7 +18813,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G636" t="n">
-        <v>1.71805381774902</v>
+        <v>1.71805393695831</v>
       </c>
       <c r="H636" t="n">
         <v>30000</v>
@@ -18871,7 +18871,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G638" t="n">
-        <v>1.6785079240799</v>
+        <v>1.67850780487061</v>
       </c>
       <c r="H638" t="n">
         <v>12000</v>
@@ -18987,7 +18987,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G642" t="n">
-        <v>1.65214371681213</v>
+        <v>1.65214383602142</v>
       </c>
       <c r="H642" t="n">
         <v>18000</v>
@@ -19016,7 +19016,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G643" t="n">
-        <v>1.65214371681213</v>
+        <v>1.65214383602142</v>
       </c>
       <c r="H643" t="n">
         <v>9000</v>
@@ -19190,7 +19190,7 @@
         <v>2</v>
       </c>
       <c r="G649" t="n">
-        <v>1.75759983062744</v>
+        <v>1.75759971141815</v>
       </c>
       <c r="H649" t="n">
         <v>6000</v>
@@ -19277,7 +19277,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G652" t="n">
-        <v>1.6785079240799</v>
+        <v>1.67850780487061</v>
       </c>
       <c r="H652" t="n">
         <v>6000</v>
@@ -19306,7 +19306,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G653" t="n">
-        <v>1.6785079240799</v>
+        <v>1.67850780487061</v>
       </c>
       <c r="H653" t="n">
         <v>0</v>
@@ -19335,7 +19335,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G654" t="n">
-        <v>1.74002385139465</v>
+        <v>1.74002373218536</v>
       </c>
       <c r="H654" t="n">
         <v>1500</v>
@@ -19364,7 +19364,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G655" t="n">
-        <v>1.74002385139465</v>
+        <v>1.74002373218536</v>
       </c>
       <c r="H655" t="n">
         <v>0</v>
@@ -19393,7 +19393,7 @@
         <v>2</v>
       </c>
       <c r="G656" t="n">
-        <v>1.75759983062744</v>
+        <v>1.75759971141815</v>
       </c>
       <c r="H656" t="n">
         <v>1500</v>
@@ -19480,7 +19480,7 @@
         <v>2</v>
       </c>
       <c r="G659" t="n">
-        <v>1.75759983062744</v>
+        <v>1.75759971141815</v>
       </c>
       <c r="H659" t="n">
         <v>102000</v>
@@ -19654,7 +19654,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G665" t="n">
-        <v>1.67888355255127</v>
+        <v>1.67888343334198</v>
       </c>
       <c r="H665" t="n">
         <v>13500</v>
@@ -19741,7 +19741,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G668" t="n">
-        <v>1.67888355255127</v>
+        <v>1.67888343334198</v>
       </c>
       <c r="H668" t="n">
         <v>4500</v>
@@ -19770,7 +19770,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G669" t="n">
-        <v>1.66985738277435</v>
+        <v>1.66985726356506</v>
       </c>
       <c r="H669" t="n">
         <v>3000</v>
@@ -19799,7 +19799,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G670" t="n">
-        <v>1.66083097457886</v>
+        <v>1.66083109378815</v>
       </c>
       <c r="H670" t="n">
         <v>30000</v>
@@ -19886,7 +19886,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G673" t="n">
-        <v>1.64277851581573</v>
+        <v>1.64277863502502</v>
       </c>
       <c r="H673" t="n">
         <v>4500</v>
@@ -19915,7 +19915,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G674" t="n">
-        <v>1.64277851581573</v>
+        <v>1.64277863502502</v>
       </c>
       <c r="H674" t="n">
         <v>0</v>
@@ -19944,7 +19944,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G675" t="n">
-        <v>1.64277851581573</v>
+        <v>1.64277863502502</v>
       </c>
       <c r="H675" t="n">
         <v>0</v>
@@ -19973,7 +19973,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G676" t="n">
-        <v>1.64277851581573</v>
+        <v>1.64277863502502</v>
       </c>
       <c r="H676" t="n">
         <v>0</v>
@@ -20205,7 +20205,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G684" t="n">
-        <v>1.59764719009399</v>
+        <v>1.5976470708847</v>
       </c>
       <c r="H684" t="n">
         <v>1500</v>
@@ -20698,7 +20698,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G701" t="n">
-        <v>1.59764719009399</v>
+        <v>1.5976470708847</v>
       </c>
       <c r="H701" t="n">
         <v>1500</v>
@@ -20727,7 +20727,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G702" t="n">
-        <v>1.59764719009399</v>
+        <v>1.5976470708847</v>
       </c>
       <c r="H702" t="n">
         <v>3000</v>
@@ -20756,7 +20756,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G703" t="n">
-        <v>1.59764719009399</v>
+        <v>1.5976470708847</v>
       </c>
       <c r="H703" t="n">
         <v>4500</v>
@@ -20785,7 +20785,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G704" t="n">
-        <v>1.59764719009399</v>
+        <v>1.5976470708847</v>
       </c>
       <c r="H704" t="n">
         <v>0</v>
@@ -20843,7 +20843,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G706" t="n">
-        <v>1.59764719009399</v>
+        <v>1.5976470708847</v>
       </c>
       <c r="H706" t="n">
         <v>7500</v>
@@ -21626,7 +21626,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G733" t="n">
-        <v>1.55251598358154</v>
+        <v>1.55251586437225</v>
       </c>
       <c r="H733" t="n">
         <v>1500</v>
@@ -21655,7 +21655,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G734" t="n">
-        <v>1.55251598358154</v>
+        <v>1.55251586437225</v>
       </c>
       <c r="H734" t="n">
         <v>6000</v>
@@ -21684,7 +21684,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G735" t="n">
-        <v>1.55251598358154</v>
+        <v>1.55251586437225</v>
       </c>
       <c r="H735" t="n">
         <v>0</v>
@@ -21713,7 +21713,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G736" t="n">
-        <v>1.55251598358154</v>
+        <v>1.55251586437225</v>
       </c>
       <c r="H736" t="n">
         <v>0</v>
@@ -21771,7 +21771,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G738" t="n">
-        <v>1.52543711662292</v>
+        <v>1.52543723583221</v>
       </c>
       <c r="H738" t="n">
         <v>7500</v>
@@ -21800,7 +21800,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G739" t="n">
-        <v>1.52543711662292</v>
+        <v>1.52543723583221</v>
       </c>
       <c r="H739" t="n">
         <v>0</v>
@@ -21829,7 +21829,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G740" t="n">
-        <v>1.52543711662292</v>
+        <v>1.52543723583221</v>
       </c>
       <c r="H740" t="n">
         <v>0</v>
@@ -22235,7 +22235,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G754" t="n">
-        <v>1.46225345134735</v>
+        <v>1.46225333213806</v>
       </c>
       <c r="H754" t="n">
         <v>15000</v>
@@ -22612,7 +22612,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G767" t="n">
-        <v>1.48933207988739</v>
+        <v>1.48933219909668</v>
       </c>
       <c r="H767" t="n">
         <v>15000</v>
@@ -22844,7 +22844,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G775" t="n">
-        <v>1.48933207988739</v>
+        <v>1.48933219909668</v>
       </c>
       <c r="H775" t="n">
         <v>3000</v>
@@ -22931,7 +22931,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G778" t="n">
-        <v>1.48933207988739</v>
+        <v>1.48933219909668</v>
       </c>
       <c r="H778" t="n">
         <v>4500</v>
@@ -23076,7 +23076,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G783" t="n">
-        <v>1.46225345134735</v>
+        <v>1.46225333213806</v>
       </c>
       <c r="H783" t="n">
         <v>15000</v>
@@ -23424,7 +23424,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G795" t="n">
-        <v>1.87746107578278</v>
+        <v>1.87746095657349</v>
       </c>
       <c r="H795" t="n">
         <v>319500</v>
@@ -23453,7 +23453,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G796" t="n">
-        <v>1.66985738277435</v>
+        <v>1.66985726356506</v>
       </c>
       <c r="H796" t="n">
         <v>94500</v>
@@ -23627,7 +23627,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G802" t="n">
-        <v>1.84135615825653</v>
+        <v>1.84135603904724</v>
       </c>
       <c r="H802" t="n">
         <v>37500</v>
@@ -23656,7 +23656,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G803" t="n">
-        <v>1.93161880970001</v>
+        <v>1.93161857128143</v>
       </c>
       <c r="H803" t="n">
         <v>73500</v>
@@ -23685,7 +23685,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G804" t="n">
-        <v>1.87746107578278</v>
+        <v>1.87746095657349</v>
       </c>
       <c r="H804" t="n">
         <v>46500</v>
@@ -23714,7 +23714,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G805" t="n">
-        <v>1.85940837860107</v>
+        <v>1.85940849781036</v>
       </c>
       <c r="H805" t="n">
         <v>4500</v>
@@ -23743,7 +23743,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G806" t="n">
-        <v>1.89551365375519</v>
+        <v>1.8955135345459</v>
       </c>
       <c r="H806" t="n">
         <v>9000</v>
@@ -23772,7 +23772,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G807" t="n">
-        <v>1.85940837860107</v>
+        <v>1.85940849781036</v>
       </c>
       <c r="H807" t="n">
         <v>7500</v>
@@ -23801,7 +23801,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G808" t="n">
-        <v>1.87746107578278</v>
+        <v>1.87746095657349</v>
       </c>
       <c r="H808" t="n">
         <v>10500</v>
@@ -23830,7 +23830,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G809" t="n">
-        <v>1.85940837860107</v>
+        <v>1.85940849781036</v>
       </c>
       <c r="H809" t="n">
         <v>1500</v>
@@ -23859,7 +23859,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G810" t="n">
-        <v>1.85940837860107</v>
+        <v>1.85940849781036</v>
       </c>
       <c r="H810" t="n">
         <v>1500</v>
@@ -23888,7 +23888,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G811" t="n">
-        <v>1.84135615825653</v>
+        <v>1.84135603904724</v>
       </c>
       <c r="H811" t="n">
         <v>6000</v>
@@ -23917,7 +23917,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G812" t="n">
-        <v>1.87746107578278</v>
+        <v>1.87746095657349</v>
       </c>
       <c r="H812" t="n">
         <v>6000</v>
@@ -23946,7 +23946,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G813" t="n">
-        <v>1.91356611251831</v>
+        <v>1.91356599330902</v>
       </c>
       <c r="H813" t="n">
         <v>3000</v>
@@ -23975,7 +23975,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G814" t="n">
-        <v>1.87746107578278</v>
+        <v>1.87746095657349</v>
       </c>
       <c r="H814" t="n">
         <v>7500</v>
@@ -24120,7 +24120,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G819" t="n">
-        <v>1.76914608478546</v>
+        <v>1.76914620399475</v>
       </c>
       <c r="H819" t="n">
         <v>12000</v>
@@ -24149,7 +24149,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G820" t="n">
-        <v>1.76914608478546</v>
+        <v>1.76914620399475</v>
       </c>
       <c r="H820" t="n">
         <v>0</v>
@@ -24236,7 +24236,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G823" t="n">
-        <v>1.84135615825653</v>
+        <v>1.84135603904724</v>
       </c>
       <c r="H823" t="n">
         <v>15000</v>
@@ -24584,7 +24584,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G835" t="n">
-        <v>1.76914608478546</v>
+        <v>1.76914620399475</v>
       </c>
       <c r="H835" t="n">
         <v>7500</v>
@@ -25135,7 +25135,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G854" t="n">
-        <v>1.76914608478546</v>
+        <v>1.76914620399475</v>
       </c>
       <c r="H854" t="n">
         <v>1500</v>
@@ -25454,7 +25454,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G865" t="n">
-        <v>1.84135615825653</v>
+        <v>1.84135603904724</v>
       </c>
       <c r="H865" t="n">
         <v>48000</v>
@@ -25483,7 +25483,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G866" t="n">
-        <v>1.87746107578278</v>
+        <v>1.87746095657349</v>
       </c>
       <c r="H866" t="n">
         <v>7500</v>
@@ -25512,7 +25512,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G867" t="n">
-        <v>1.91356611251831</v>
+        <v>1.91356599330902</v>
       </c>
       <c r="H867" t="n">
         <v>21000</v>
@@ -25831,7 +25831,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G878" t="n">
-        <v>1.93161880970001</v>
+        <v>1.93161857128143</v>
       </c>
       <c r="H878" t="n">
         <v>12000</v>
@@ -26324,7 +26324,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G895" t="n">
-        <v>1.85940837860107</v>
+        <v>1.85940849781036</v>
       </c>
       <c r="H895" t="n">
         <v>126000</v>
@@ -26382,7 +26382,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G897" t="n">
-        <v>1.91356611251831</v>
+        <v>1.91356599330902</v>
       </c>
       <c r="H897" t="n">
         <v>54000</v>
@@ -26411,7 +26411,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G898" t="n">
-        <v>1.87746107578278</v>
+        <v>1.87746095657349</v>
       </c>
       <c r="H898" t="n">
         <v>15000</v>
@@ -26440,7 +26440,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G899" t="n">
-        <v>1.85940837860107</v>
+        <v>1.85940849781036</v>
       </c>
       <c r="H899" t="n">
         <v>16500</v>
@@ -26469,7 +26469,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G900" t="n">
-        <v>1.87746107578278</v>
+        <v>1.87746095657349</v>
       </c>
       <c r="H900" t="n">
         <v>12000</v>
@@ -26498,7 +26498,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G901" t="n">
-        <v>1.85940837860107</v>
+        <v>1.85940849781036</v>
       </c>
       <c r="H901" t="n">
         <v>4500</v>
@@ -26527,7 +26527,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G902" t="n">
-        <v>1.93161880970001</v>
+        <v>1.93161857128143</v>
       </c>
       <c r="H902" t="n">
         <v>9000</v>
@@ -26556,7 +26556,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G903" t="n">
-        <v>1.91356611251831</v>
+        <v>1.91356599330902</v>
       </c>
       <c r="H903" t="n">
         <v>4500</v>
@@ -26585,7 +26585,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G904" t="n">
-        <v>1.93161880970001</v>
+        <v>1.93161857128143</v>
       </c>
       <c r="H904" t="n">
         <v>9000</v>
@@ -26643,7 +26643,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G906" t="n">
-        <v>1.91356611251831</v>
+        <v>1.91356599330902</v>
       </c>
       <c r="H906" t="n">
         <v>7500</v>
@@ -26672,7 +26672,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G907" t="n">
-        <v>1.93161880970001</v>
+        <v>1.93161857128143</v>
       </c>
       <c r="H907" t="n">
         <v>1500</v>
@@ -26701,7 +26701,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G908" t="n">
-        <v>1.93161880970001</v>
+        <v>1.93161857128143</v>
       </c>
       <c r="H908" t="n">
         <v>0</v>
@@ -26730,7 +26730,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G909" t="n">
-        <v>1.85940837860107</v>
+        <v>1.85940849781036</v>
       </c>
       <c r="H909" t="n">
         <v>111000</v>
@@ -26759,7 +26759,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G910" t="n">
-        <v>1.84135615825653</v>
+        <v>1.84135603904724</v>
       </c>
       <c r="H910" t="n">
         <v>21000</v>
@@ -26788,7 +26788,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G911" t="n">
-        <v>1.87746107578278</v>
+        <v>1.87746095657349</v>
       </c>
       <c r="H911" t="n">
         <v>9000</v>
@@ -26817,7 +26817,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G912" t="n">
-        <v>1.85940837860107</v>
+        <v>1.85940849781036</v>
       </c>
       <c r="H912" t="n">
         <v>15000</v>
@@ -26846,7 +26846,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G913" t="n">
-        <v>1.85940837860107</v>
+        <v>1.85940849781036</v>
       </c>
       <c r="H913" t="n">
         <v>6000</v>
@@ -26875,7 +26875,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G914" t="n">
-        <v>1.89551365375519</v>
+        <v>1.8955135345459</v>
       </c>
       <c r="H914" t="n">
         <v>7500</v>
@@ -26904,7 +26904,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G915" t="n">
-        <v>1.87746107578278</v>
+        <v>1.87746095657349</v>
       </c>
       <c r="H915" t="n">
         <v>10500</v>
@@ -26933,7 +26933,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G916" t="n">
-        <v>1.87746107578278</v>
+        <v>1.87746095657349</v>
       </c>
       <c r="H916" t="n">
         <v>1500</v>
@@ -26962,7 +26962,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G917" t="n">
-        <v>1.85940837860107</v>
+        <v>1.85940849781036</v>
       </c>
       <c r="H917" t="n">
         <v>13500</v>
@@ -45441,6 +45441,35 @@
         <v>3000</v>
       </c>
       <c r="I1554" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1555">
+      <c r="A1555" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1555" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1555" t="n">
+        <v>1.52999997138977</v>
+      </c>
+      <c r="D1555" t="n">
+        <v>1.52999997138977</v>
+      </c>
+      <c r="E1555" t="n">
+        <v>1.52999997138977</v>
+      </c>
+      <c r="F1555" t="n">
+        <v>1.52999997138977</v>
+      </c>
+      <c r="G1555" t="n">
+        <v>1.52999997138977</v>
+      </c>
+      <c r="H1555" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1555" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RETI.MI.xlsx
+++ b/data/RETI.MI.xlsx
@@ -456,7 +456,7 @@
         <v>0.899600028991699</v>
       </c>
       <c r="G3" t="n">
-        <v>0.768140912055969</v>
+        <v>0.768140971660614</v>
       </c>
       <c r="H3" t="n">
         <v>472500</v>
@@ -485,7 +485,7 @@
         <v>0.879899978637695</v>
       </c>
       <c r="G4" t="n">
-        <v>0.751319706439972</v>
+        <v>0.751319646835327</v>
       </c>
       <c r="H4" t="n">
         <v>75000</v>
@@ -601,7 +601,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G8" t="n">
-        <v>0.756528258323669</v>
+        <v>0.756528317928314</v>
       </c>
       <c r="H8" t="n">
         <v>63000</v>
@@ -630,7 +630,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G9" t="n">
-        <v>0.732620060443878</v>
+        <v>0.732619941234589</v>
       </c>
       <c r="H9" t="n">
         <v>118500</v>
@@ -659,7 +659,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G10" t="n">
-        <v>0.722373604774475</v>
+        <v>0.72237354516983</v>
       </c>
       <c r="H10" t="n">
         <v>48000</v>
@@ -717,7 +717,7 @@
         <v>0.814000010490417</v>
       </c>
       <c r="G12" t="n">
-        <v>0.69504976272583</v>
+        <v>0.695049703121185</v>
       </c>
       <c r="H12" t="n">
         <v>63000</v>
@@ -775,7 +775,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G14" t="n">
-        <v>0.683095574378967</v>
+        <v>0.683095633983612</v>
       </c>
       <c r="H14" t="n">
         <v>18000</v>
@@ -804,7 +804,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G15" t="n">
-        <v>0.683095574378967</v>
+        <v>0.683095633983612</v>
       </c>
       <c r="H15" t="n">
         <v>42000</v>
@@ -862,7 +862,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G17" t="n">
-        <v>0.654063999652863</v>
+        <v>0.654063940048218</v>
       </c>
       <c r="H17" t="n">
         <v>25500</v>
@@ -891,7 +891,7 @@
         <v>0.833999991416931</v>
       </c>
       <c r="G18" t="n">
-        <v>0.712127089500427</v>
+        <v>0.712127149105072</v>
       </c>
       <c r="H18" t="n">
         <v>579000</v>
@@ -920,7 +920,7 @@
         <v>0.814000010490417</v>
       </c>
       <c r="G19" t="n">
-        <v>0.69504976272583</v>
+        <v>0.695049703121185</v>
       </c>
       <c r="H19" t="n">
         <v>265500</v>
@@ -978,7 +978,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G21" t="n">
-        <v>0.654063999652863</v>
+        <v>0.654063940048218</v>
       </c>
       <c r="H21" t="n">
         <v>132000</v>
@@ -1065,7 +1065,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G24" t="n">
-        <v>0.652356207370758</v>
+        <v>0.652356266975403</v>
       </c>
       <c r="H24" t="n">
         <v>10500</v>
@@ -1123,7 +1123,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G26" t="n">
-        <v>0.654063999652863</v>
+        <v>0.654063940048218</v>
       </c>
       <c r="H26" t="n">
         <v>27000</v>
@@ -1152,7 +1152,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G27" t="n">
-        <v>0.633571088314056</v>
+        <v>0.633571147918701</v>
       </c>
       <c r="H27" t="n">
         <v>43500</v>
@@ -1268,7 +1268,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G31" t="n">
-        <v>0.587462186813354</v>
+        <v>0.58746212720871</v>
       </c>
       <c r="H31" t="n">
         <v>78000</v>
@@ -1297,7 +1297,7 @@
         <v>0.73199999332428</v>
       </c>
       <c r="G32" t="n">
-        <v>0.625032424926758</v>
+        <v>0.625032365322113</v>
       </c>
       <c r="H32" t="n">
         <v>27000</v>
@@ -1326,7 +1326,7 @@
         <v>0.722000002861023</v>
       </c>
       <c r="G33" t="n">
-        <v>0.616493701934814</v>
+        <v>0.616493761539459</v>
       </c>
       <c r="H33" t="n">
         <v>3000</v>
@@ -1384,7 +1384,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G35" t="n">
-        <v>0.580631196498871</v>
+        <v>0.580631256103516</v>
       </c>
       <c r="H35" t="n">
         <v>12000</v>
@@ -1413,7 +1413,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G36" t="n">
-        <v>0.563553869724274</v>
+        <v>0.563553810119629</v>
       </c>
       <c r="H36" t="n">
         <v>66000</v>
@@ -1442,7 +1442,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G37" t="n">
-        <v>0.537937819957733</v>
+        <v>0.537937700748444</v>
       </c>
       <c r="H37" t="n">
         <v>27000</v>
@@ -1471,7 +1471,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G38" t="n">
-        <v>0.537937819957733</v>
+        <v>0.537937700748444</v>
       </c>
       <c r="H38" t="n">
         <v>13500</v>
@@ -1529,7 +1529,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G40" t="n">
-        <v>0.546476423740387</v>
+        <v>0.546476483345032</v>
       </c>
       <c r="H40" t="n">
         <v>15000</v>
@@ -1558,7 +1558,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G41" t="n">
-        <v>0.537937819957733</v>
+        <v>0.537937700748444</v>
       </c>
       <c r="H41" t="n">
         <v>16500</v>
@@ -1587,7 +1587,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G42" t="n">
-        <v>0.604539573192596</v>
+        <v>0.604539513587952</v>
       </c>
       <c r="H42" t="n">
         <v>127500</v>
@@ -1645,7 +1645,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G44" t="n">
-        <v>0.604539573192596</v>
+        <v>0.604539513587952</v>
       </c>
       <c r="H44" t="n">
         <v>64500</v>
@@ -1761,7 +1761,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G48" t="n">
-        <v>0.611370503902435</v>
+        <v>0.61137056350708</v>
       </c>
       <c r="H48" t="n">
         <v>21000</v>
@@ -2080,7 +2080,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G59" t="n">
-        <v>0.683095574378967</v>
+        <v>0.683095633983612</v>
       </c>
       <c r="H59" t="n">
         <v>6000</v>
@@ -2109,7 +2109,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G60" t="n">
-        <v>0.683095574378967</v>
+        <v>0.683095633983612</v>
       </c>
       <c r="H60" t="n">
         <v>1500</v>
@@ -2138,7 +2138,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G61" t="n">
-        <v>0.683095574378967</v>
+        <v>0.683095633983612</v>
       </c>
       <c r="H61" t="n">
         <v>102000</v>
@@ -2167,7 +2167,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G62" t="n">
-        <v>0.681387782096863</v>
+        <v>0.681387841701508</v>
       </c>
       <c r="H62" t="n">
         <v>16500</v>
@@ -2225,7 +2225,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G64" t="n">
-        <v>0.683095574378967</v>
+        <v>0.683095633983612</v>
       </c>
       <c r="H64" t="n">
         <v>7500</v>
@@ -2312,7 +2312,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G67" t="n">
-        <v>0.683095574378967</v>
+        <v>0.683095633983612</v>
       </c>
       <c r="H67" t="n">
         <v>7500</v>
@@ -2370,7 +2370,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G69" t="n">
-        <v>0.69334203004837</v>
+        <v>0.693341970443726</v>
       </c>
       <c r="H69" t="n">
         <v>15000</v>
@@ -2457,7 +2457,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G72" t="n">
-        <v>0.69334203004837</v>
+        <v>0.693341970443726</v>
       </c>
       <c r="H72" t="n">
         <v>3000</v>
@@ -2573,7 +2573,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G76" t="n">
-        <v>0.707003831863403</v>
+        <v>0.707003891468048</v>
       </c>
       <c r="H76" t="n">
         <v>7500</v>
@@ -2689,7 +2689,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G80" t="n">
-        <v>0.717250287532806</v>
+        <v>0.717250347137451</v>
       </c>
       <c r="H80" t="n">
         <v>28500</v>
@@ -2747,7 +2747,7 @@
         <v>0.833999991416931</v>
       </c>
       <c r="G82" t="n">
-        <v>0.712127089500427</v>
+        <v>0.712127149105072</v>
       </c>
       <c r="H82" t="n">
         <v>4500</v>
@@ -2776,7 +2776,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G83" t="n">
-        <v>0.715542674064636</v>
+        <v>0.715542614459991</v>
       </c>
       <c r="H83" t="n">
         <v>1500</v>
@@ -2805,7 +2805,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G84" t="n">
-        <v>0.717250287532806</v>
+        <v>0.717250347137451</v>
       </c>
       <c r="H84" t="n">
         <v>1500</v>
@@ -2834,7 +2834,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G85" t="n">
-        <v>0.715542674064636</v>
+        <v>0.715542614459991</v>
       </c>
       <c r="H85" t="n">
         <v>9000</v>
@@ -2950,7 +2950,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G89" t="n">
-        <v>0.684803247451782</v>
+        <v>0.684803307056427</v>
       </c>
       <c r="H89" t="n">
         <v>22500</v>
@@ -2979,7 +2979,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G90" t="n">
-        <v>0.684803247451782</v>
+        <v>0.684803307056427</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -3124,7 +3124,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G95" t="n">
-        <v>0.683095574378967</v>
+        <v>0.683095633983612</v>
       </c>
       <c r="H95" t="n">
         <v>3000</v>
@@ -3269,7 +3269,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G100" t="n">
-        <v>0.676264643669128</v>
+        <v>0.676264524459839</v>
       </c>
       <c r="H100" t="n">
         <v>7500</v>
@@ -3298,7 +3298,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G101" t="n">
-        <v>0.676264643669128</v>
+        <v>0.676264524459839</v>
       </c>
       <c r="H101" t="n">
         <v>0</v>
@@ -3327,7 +3327,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G102" t="n">
-        <v>0.683095574378967</v>
+        <v>0.683095633983612</v>
       </c>
       <c r="H102" t="n">
         <v>10500</v>
@@ -3356,7 +3356,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G103" t="n">
-        <v>0.707003831863403</v>
+        <v>0.707003891468048</v>
       </c>
       <c r="H103" t="n">
         <v>22500</v>
@@ -3385,7 +3385,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G104" t="n">
-        <v>0.683095574378967</v>
+        <v>0.683095633983612</v>
       </c>
       <c r="H104" t="n">
         <v>49500</v>
@@ -3414,7 +3414,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G105" t="n">
-        <v>0.683095574378967</v>
+        <v>0.683095633983612</v>
       </c>
       <c r="H105" t="n">
         <v>13500</v>
@@ -3443,7 +3443,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G106" t="n">
-        <v>0.683095574378967</v>
+        <v>0.683095633983612</v>
       </c>
       <c r="H106" t="n">
         <v>1500</v>
@@ -3530,7 +3530,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G109" t="n">
-        <v>0.683095574378967</v>
+        <v>0.683095633983612</v>
       </c>
       <c r="H109" t="n">
         <v>13500</v>
@@ -3617,7 +3617,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G112" t="n">
-        <v>0.686511099338531</v>
+        <v>0.686511039733887</v>
       </c>
       <c r="H112" t="n">
         <v>40500</v>
@@ -3762,7 +3762,7 @@
         <v>0.842000007629395</v>
       </c>
       <c r="G117" t="n">
-        <v>0.718958020210266</v>
+        <v>0.718958079814911</v>
       </c>
       <c r="H117" t="n">
         <v>102000</v>
@@ -3791,7 +3791,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G118" t="n">
-        <v>0.717250287532806</v>
+        <v>0.717250347137451</v>
       </c>
       <c r="H118" t="n">
         <v>69000</v>
@@ -3820,7 +3820,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G119" t="n">
-        <v>0.715542674064636</v>
+        <v>0.715542614459991</v>
       </c>
       <c r="H119" t="n">
         <v>16500</v>
@@ -3849,7 +3849,7 @@
         <v>0.867999970912933</v>
       </c>
       <c r="G120" t="n">
-        <v>0.741158604621887</v>
+        <v>0.741158664226532</v>
       </c>
       <c r="H120" t="n">
         <v>139500</v>
@@ -3878,7 +3878,7 @@
         <v>0.867999970912933</v>
       </c>
       <c r="G121" t="n">
-        <v>0.741158604621887</v>
+        <v>0.741158664226532</v>
       </c>
       <c r="H121" t="n">
         <v>151500</v>
@@ -3907,7 +3907,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G122" t="n">
-        <v>0.858138799667358</v>
+        <v>0.858138740062714</v>
       </c>
       <c r="H122" t="n">
         <v>660000</v>
@@ -3936,7 +3936,7 @@
         <v>0.972000002861023</v>
       </c>
       <c r="G123" t="n">
-        <v>0.829961061477661</v>
+        <v>0.829961121082306</v>
       </c>
       <c r="H123" t="n">
         <v>922500</v>
@@ -3994,7 +3994,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G125" t="n">
-        <v>0.8367919921875</v>
+        <v>0.836792051792145</v>
       </c>
       <c r="H125" t="n">
         <v>196500</v>
@@ -4023,7 +4023,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G126" t="n">
-        <v>0.8367919921875</v>
+        <v>0.836792051792145</v>
       </c>
       <c r="H126" t="n">
         <v>76500</v>
@@ -4168,7 +4168,7 @@
         <v>0.994000017642975</v>
       </c>
       <c r="G131" t="n">
-        <v>0.848746299743652</v>
+        <v>0.848746240139008</v>
       </c>
       <c r="H131" t="n">
         <v>60000</v>
@@ -4226,7 +4226,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G133" t="n">
-        <v>0.870946884155273</v>
+        <v>0.870946824550629</v>
       </c>
       <c r="H133" t="n">
         <v>19500</v>
@@ -4255,7 +4255,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G134" t="n">
-        <v>0.875216126441956</v>
+        <v>0.8752161860466</v>
       </c>
       <c r="H134" t="n">
         <v>19500</v>
@@ -4284,7 +4284,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G135" t="n">
-        <v>0.866677463054657</v>
+        <v>0.866677522659302</v>
       </c>
       <c r="H135" t="n">
         <v>15000</v>
@@ -4313,7 +4313,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G136" t="n">
-        <v>0.900832295417786</v>
+        <v>0.900832235813141</v>
       </c>
       <c r="H136" t="n">
         <v>127500</v>
@@ -4371,7 +4371,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G138" t="n">
-        <v>0.892293512821198</v>
+        <v>0.892293572425842</v>
       </c>
       <c r="H138" t="n">
         <v>82500</v>
@@ -4400,7 +4400,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G139" t="n">
-        <v>0.913640379905701</v>
+        <v>0.913640260696411</v>
       </c>
       <c r="H139" t="n">
         <v>4500</v>
@@ -4487,7 +4487,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G142" t="n">
-        <v>0.913640379905701</v>
+        <v>0.913640260696411</v>
       </c>
       <c r="H142" t="n">
         <v>42000</v>
@@ -4516,7 +4516,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G143" t="n">
-        <v>0.930717766284943</v>
+        <v>0.930717825889587</v>
       </c>
       <c r="H143" t="n">
         <v>45000</v>
@@ -4545,7 +4545,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G144" t="n">
-        <v>1.17833995819092</v>
+        <v>1.17833983898163</v>
       </c>
       <c r="H144" t="n">
         <v>451500</v>
@@ -4574,7 +4574,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G145" t="n">
-        <v>1.11429953575134</v>
+        <v>1.11429965496063</v>
       </c>
       <c r="H145" t="n">
         <v>834000</v>
@@ -4748,7 +4748,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G151" t="n">
-        <v>1.21274399757385</v>
+        <v>1.21274387836456</v>
       </c>
       <c r="H151" t="n">
         <v>76500</v>
@@ -4835,7 +4835,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G154" t="n">
-        <v>1.1775918006897</v>
+        <v>1.17759191989899</v>
       </c>
       <c r="H154" t="n">
         <v>31500</v>
@@ -4893,7 +4893,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G156" t="n">
-        <v>1.14683377742767</v>
+        <v>1.14683389663696</v>
       </c>
       <c r="H156" t="n">
         <v>15000</v>
@@ -5067,7 +5067,7 @@
         <v>1.25</v>
       </c>
       <c r="G162" t="n">
-        <v>1.09850001335144</v>
+        <v>1.09849989414215</v>
       </c>
       <c r="H162" t="n">
         <v>39000</v>
@@ -5212,7 +5212,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G167" t="n">
-        <v>1.1775918006897</v>
+        <v>1.17759191989899</v>
       </c>
       <c r="H167" t="n">
         <v>12000</v>
@@ -5241,7 +5241,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G168" t="n">
-        <v>1.14683377742767</v>
+        <v>1.14683389663696</v>
       </c>
       <c r="H168" t="n">
         <v>49500</v>
@@ -5299,7 +5299,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G170" t="n">
-        <v>1.14683377742767</v>
+        <v>1.14683389663696</v>
       </c>
       <c r="H170" t="n">
         <v>9000</v>
@@ -5415,7 +5415,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G174" t="n">
-        <v>1.18198585510254</v>
+        <v>1.18198597431183</v>
       </c>
       <c r="H174" t="n">
         <v>24000</v>
@@ -5444,7 +5444,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G175" t="n">
-        <v>1.23031985759735</v>
+        <v>1.23031973838806</v>
       </c>
       <c r="H175" t="n">
         <v>234000</v>
@@ -5560,7 +5560,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G179" t="n">
-        <v>1.33577585220337</v>
+        <v>1.33577597141266</v>
       </c>
       <c r="H179" t="n">
         <v>48000</v>
@@ -5618,7 +5618,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G181" t="n">
-        <v>1.33577585220337</v>
+        <v>1.33577597141266</v>
       </c>
       <c r="H181" t="n">
         <v>24000</v>
@@ -5647,7 +5647,7 @@
         <v>1.5</v>
       </c>
       <c r="G182" t="n">
-        <v>1.31819975376129</v>
+        <v>1.31819987297058</v>
       </c>
       <c r="H182" t="n">
         <v>39000</v>
@@ -5676,7 +5676,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G183" t="n">
-        <v>1.28304779529572</v>
+        <v>1.283047914505</v>
       </c>
       <c r="H183" t="n">
         <v>180000</v>
@@ -5734,7 +5734,7 @@
         <v>1.5</v>
       </c>
       <c r="G185" t="n">
-        <v>1.31819975376129</v>
+        <v>1.31819987297058</v>
       </c>
       <c r="H185" t="n">
         <v>19500</v>
@@ -5763,7 +5763,7 @@
         <v>1.5</v>
       </c>
       <c r="G186" t="n">
-        <v>1.31819975376129</v>
+        <v>1.31819987297058</v>
       </c>
       <c r="H186" t="n">
         <v>31500</v>
@@ -5850,7 +5850,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G189" t="n">
-        <v>1.45001983642578</v>
+        <v>1.45001995563507</v>
       </c>
       <c r="H189" t="n">
         <v>148500</v>
@@ -5879,7 +5879,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G190" t="n">
-        <v>1.41486799716949</v>
+        <v>1.41486787796021</v>
       </c>
       <c r="H190" t="n">
         <v>154500</v>
@@ -5937,7 +5937,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G192" t="n">
-        <v>1.37971591949463</v>
+        <v>1.37971580028534</v>
       </c>
       <c r="H192" t="n">
         <v>87000</v>
@@ -6024,7 +6024,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G195" t="n">
-        <v>1.34456372261047</v>
+        <v>1.34456384181976</v>
       </c>
       <c r="H195" t="n">
         <v>18000</v>
@@ -6111,7 +6111,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G198" t="n">
-        <v>1.32698786258698</v>
+        <v>1.32698798179626</v>
       </c>
       <c r="H198" t="n">
         <v>13500</v>
@@ -6198,7 +6198,7 @@
         <v>1.5</v>
       </c>
       <c r="G201" t="n">
-        <v>1.31819975376129</v>
+        <v>1.31819987297058</v>
       </c>
       <c r="H201" t="n">
         <v>16500</v>
@@ -6227,7 +6227,7 @@
         <v>1.5</v>
       </c>
       <c r="G202" t="n">
-        <v>1.31819975376129</v>
+        <v>1.31819987297058</v>
       </c>
       <c r="H202" t="n">
         <v>3000</v>
@@ -6256,7 +6256,7 @@
         <v>1.5</v>
       </c>
       <c r="G203" t="n">
-        <v>1.31819975376129</v>
+        <v>1.31819987297058</v>
       </c>
       <c r="H203" t="n">
         <v>12000</v>
@@ -6314,7 +6314,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G205" t="n">
-        <v>1.33577585220337</v>
+        <v>1.33577597141266</v>
       </c>
       <c r="H205" t="n">
         <v>4500</v>
@@ -6343,7 +6343,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G206" t="n">
-        <v>1.34456372261047</v>
+        <v>1.34456384181976</v>
       </c>
       <c r="H206" t="n">
         <v>18000</v>
@@ -6372,7 +6372,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G207" t="n">
-        <v>1.34456372261047</v>
+        <v>1.34456384181976</v>
       </c>
       <c r="H207" t="n">
         <v>4500</v>
@@ -6401,7 +6401,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G208" t="n">
-        <v>1.35335195064545</v>
+        <v>1.35335183143616</v>
       </c>
       <c r="H208" t="n">
         <v>1500</v>
@@ -6430,7 +6430,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G209" t="n">
-        <v>1.35335195064545</v>
+        <v>1.35335183143616</v>
       </c>
       <c r="H209" t="n">
         <v>0</v>
@@ -6459,7 +6459,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G210" t="n">
-        <v>1.35335195064545</v>
+        <v>1.35335183143616</v>
       </c>
       <c r="H210" t="n">
         <v>0</v>
@@ -6517,7 +6517,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G212" t="n">
-        <v>1.30941188335419</v>
+        <v>1.3094117641449</v>
       </c>
       <c r="H212" t="n">
         <v>4500</v>
@@ -6604,7 +6604,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G215" t="n">
-        <v>1.32698786258698</v>
+        <v>1.32698798179626</v>
       </c>
       <c r="H215" t="n">
         <v>13500</v>
@@ -6633,7 +6633,7 @@
         <v>1.5</v>
       </c>
       <c r="G216" t="n">
-        <v>1.31819975376129</v>
+        <v>1.31819987297058</v>
       </c>
       <c r="H216" t="n">
         <v>15000</v>
@@ -6662,7 +6662,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G217" t="n">
-        <v>1.30941188335419</v>
+        <v>1.3094117641449</v>
       </c>
       <c r="H217" t="n">
         <v>10500</v>
@@ -6691,7 +6691,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G218" t="n">
-        <v>1.24789595603943</v>
+        <v>1.24789583683014</v>
       </c>
       <c r="H218" t="n">
         <v>33000</v>
@@ -6720,7 +6720,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G219" t="n">
-        <v>1.23031985759735</v>
+        <v>1.23031973838806</v>
       </c>
       <c r="H219" t="n">
         <v>70500</v>
@@ -6836,7 +6836,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G223" t="n">
-        <v>1.30941188335419</v>
+        <v>1.3094117641449</v>
       </c>
       <c r="H223" t="n">
         <v>6000</v>
@@ -6865,7 +6865,7 @@
         <v>1.5</v>
       </c>
       <c r="G224" t="n">
-        <v>1.31819975376129</v>
+        <v>1.31819987297058</v>
       </c>
       <c r="H224" t="n">
         <v>13500</v>
@@ -6894,7 +6894,7 @@
         <v>1.5</v>
       </c>
       <c r="G225" t="n">
-        <v>1.31819975376129</v>
+        <v>1.31819987297058</v>
       </c>
       <c r="H225" t="n">
         <v>0</v>
@@ -6952,7 +6952,7 @@
         <v>1.5</v>
       </c>
       <c r="G227" t="n">
-        <v>1.31819975376129</v>
+        <v>1.31819987297058</v>
       </c>
       <c r="H227" t="n">
         <v>13500</v>
@@ -7010,7 +7010,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G229" t="n">
-        <v>1.27425992488861</v>
+        <v>1.27425980567932</v>
       </c>
       <c r="H229" t="n">
         <v>6000</v>
@@ -7068,7 +7068,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G231" t="n">
-        <v>1.28304779529572</v>
+        <v>1.283047914505</v>
       </c>
       <c r="H231" t="n">
         <v>4500</v>
@@ -7097,7 +7097,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G232" t="n">
-        <v>1.34456372261047</v>
+        <v>1.34456384181976</v>
       </c>
       <c r="H232" t="n">
         <v>45000</v>
@@ -7155,7 +7155,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G234" t="n">
-        <v>1.36213982105255</v>
+        <v>1.36213994026184</v>
       </c>
       <c r="H234" t="n">
         <v>22500</v>
@@ -7184,7 +7184,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G235" t="n">
-        <v>1.34456372261047</v>
+        <v>1.34456384181976</v>
       </c>
       <c r="H235" t="n">
         <v>13500</v>
@@ -7387,7 +7387,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G242" t="n">
-        <v>2.08275556564331</v>
+        <v>2.08275580406189</v>
       </c>
       <c r="H242" t="n">
         <v>1374000</v>
@@ -7416,7 +7416,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G243" t="n">
-        <v>2.2321515083313</v>
+        <v>2.23215174674988</v>
       </c>
       <c r="H243" t="n">
         <v>702000</v>
@@ -7445,7 +7445,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G244" t="n">
-        <v>2.52215552330017</v>
+        <v>2.52215576171875</v>
       </c>
       <c r="H244" t="n">
         <v>1464000</v>
@@ -7619,7 +7619,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G250" t="n">
-        <v>2.2321515083313</v>
+        <v>2.23215174674988</v>
       </c>
       <c r="H250" t="n">
         <v>102000</v>
@@ -7735,7 +7735,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G254" t="n">
-        <v>2.34639596939087</v>
+        <v>2.34639573097229</v>
       </c>
       <c r="H254" t="n">
         <v>139500</v>
@@ -7822,7 +7822,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G257" t="n">
-        <v>2.35518360137939</v>
+        <v>2.35518383979797</v>
       </c>
       <c r="H257" t="n">
         <v>30000</v>
@@ -7851,7 +7851,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G258" t="n">
-        <v>2.28487992286682</v>
+        <v>2.28487968444824</v>
       </c>
       <c r="H258" t="n">
         <v>138000</v>
@@ -7909,7 +7909,7 @@
         <v>2.5</v>
       </c>
       <c r="G260" t="n">
-        <v>2.19700002670288</v>
+        <v>2.1969997882843</v>
       </c>
       <c r="H260" t="n">
         <v>85500</v>
@@ -7938,7 +7938,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G261" t="n">
-        <v>2.21457600593567</v>
+        <v>2.21457576751709</v>
       </c>
       <c r="H261" t="n">
         <v>55500</v>
@@ -7996,7 +7996,7 @@
         <v>2.5</v>
       </c>
       <c r="G263" t="n">
-        <v>2.19700002670288</v>
+        <v>2.1969997882843</v>
       </c>
       <c r="H263" t="n">
         <v>13500</v>
@@ -8054,7 +8054,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G265" t="n">
-        <v>2.34639596939087</v>
+        <v>2.34639573097229</v>
       </c>
       <c r="H265" t="n">
         <v>46500</v>
@@ -8083,7 +8083,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G266" t="n">
-        <v>2.35518360137939</v>
+        <v>2.35518383979797</v>
       </c>
       <c r="H266" t="n">
         <v>60000</v>
@@ -8141,7 +8141,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G268" t="n">
-        <v>2.38154768943787</v>
+        <v>2.38154792785645</v>
       </c>
       <c r="H268" t="n">
         <v>88500</v>
@@ -8199,7 +8199,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G270" t="n">
-        <v>2.2321515083313</v>
+        <v>2.23215174674988</v>
       </c>
       <c r="H270" t="n">
         <v>97500</v>
@@ -8228,7 +8228,7 @@
         <v>2.5</v>
       </c>
       <c r="G271" t="n">
-        <v>2.19700002670288</v>
+        <v>2.1969997882843</v>
       </c>
       <c r="H271" t="n">
         <v>36000</v>
@@ -8344,7 +8344,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G275" t="n">
-        <v>2.28487992286682</v>
+        <v>2.28487968444824</v>
       </c>
       <c r="H275" t="n">
         <v>18000</v>
@@ -8373,7 +8373,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G276" t="n">
-        <v>2.28487992286682</v>
+        <v>2.28487968444824</v>
       </c>
       <c r="H276" t="n">
         <v>6000</v>
@@ -8489,7 +8489,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G280" t="n">
-        <v>2.28487992286682</v>
+        <v>2.28487968444824</v>
       </c>
       <c r="H280" t="n">
         <v>16500</v>
@@ -8837,7 +8837,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G292" t="n">
-        <v>2.21457600593567</v>
+        <v>2.21457576751709</v>
       </c>
       <c r="H292" t="n">
         <v>16500</v>
@@ -8895,7 +8895,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G294" t="n">
-        <v>2.28487992286682</v>
+        <v>2.28487968444824</v>
       </c>
       <c r="H294" t="n">
         <v>1500</v>
@@ -8953,7 +8953,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G296" t="n">
-        <v>2.2321515083313</v>
+        <v>2.23215174674988</v>
       </c>
       <c r="H296" t="n">
         <v>7500</v>
@@ -8982,7 +8982,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G297" t="n">
-        <v>2.21457600593567</v>
+        <v>2.21457576751709</v>
       </c>
       <c r="H297" t="n">
         <v>12000</v>
@@ -9011,7 +9011,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G298" t="n">
-        <v>2.21457600593567</v>
+        <v>2.21457576751709</v>
       </c>
       <c r="H298" t="n">
         <v>21000</v>
@@ -9098,7 +9098,7 @@
         <v>2.5</v>
       </c>
       <c r="G301" t="n">
-        <v>2.19700002670288</v>
+        <v>2.1969997882843</v>
       </c>
       <c r="H301" t="n">
         <v>21000</v>
@@ -9243,7 +9243,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G306" t="n">
-        <v>1.99487590789795</v>
+        <v>1.99487566947937</v>
       </c>
       <c r="H306" t="n">
         <v>13500</v>
@@ -9301,7 +9301,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G308" t="n">
-        <v>2.02123951911926</v>
+        <v>2.02123975753784</v>
       </c>
       <c r="H308" t="n">
         <v>12000</v>
@@ -9330,7 +9330,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G309" t="n">
-        <v>1.93335974216461</v>
+        <v>1.93335998058319</v>
       </c>
       <c r="H309" t="n">
         <v>18000</v>
@@ -9388,7 +9388,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G311" t="n">
-        <v>1.88941979408264</v>
+        <v>1.88941991329193</v>
       </c>
       <c r="H311" t="n">
         <v>34500</v>
@@ -9446,7 +9446,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G313" t="n">
-        <v>1.93335974216461</v>
+        <v>1.93335998058319</v>
       </c>
       <c r="H313" t="n">
         <v>18000</v>
@@ -9475,7 +9475,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G314" t="n">
-        <v>1.93335974216461</v>
+        <v>1.93335998058319</v>
       </c>
       <c r="H314" t="n">
         <v>6000</v>
@@ -9533,7 +9533,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G316" t="n">
-        <v>2.08275556564331</v>
+        <v>2.08275580406189</v>
       </c>
       <c r="H316" t="n">
         <v>48000</v>
@@ -9620,7 +9620,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G319" t="n">
-        <v>2.12669587135315</v>
+        <v>2.12669563293457</v>
       </c>
       <c r="H319" t="n">
         <v>15000</v>
@@ -9707,7 +9707,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G322" t="n">
-        <v>2.10033202171326</v>
+        <v>2.10033178329468</v>
       </c>
       <c r="H322" t="n">
         <v>3000</v>
@@ -9736,7 +9736,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G323" t="n">
-        <v>2.10033202171326</v>
+        <v>2.10033178329468</v>
       </c>
       <c r="H323" t="n">
         <v>0</v>
@@ -9794,7 +9794,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G325" t="n">
-        <v>1.94214773178101</v>
+        <v>1.94214797019958</v>
       </c>
       <c r="H325" t="n">
         <v>7500</v>
@@ -9881,7 +9881,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G328" t="n">
-        <v>1.88941979408264</v>
+        <v>1.88941991329193</v>
       </c>
       <c r="H328" t="n">
         <v>31500</v>
@@ -9939,7 +9939,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G330" t="n">
-        <v>2.03002786636353</v>
+        <v>2.0300281047821</v>
       </c>
       <c r="H330" t="n">
         <v>4500</v>
@@ -9968,7 +9968,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G331" t="n">
-        <v>1.99487590789795</v>
+        <v>1.99487566947937</v>
       </c>
       <c r="H331" t="n">
         <v>12000</v>
@@ -9997,7 +9997,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G332" t="n">
-        <v>1.99487590789795</v>
+        <v>1.99487566947937</v>
       </c>
       <c r="H332" t="n">
         <v>7500</v>
@@ -10026,7 +10026,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G333" t="n">
-        <v>1.99487590789795</v>
+        <v>1.99487566947937</v>
       </c>
       <c r="H333" t="n">
         <v>6000</v>
@@ -10113,7 +10113,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G336" t="n">
-        <v>2.02123951911926</v>
+        <v>2.02123975753784</v>
       </c>
       <c r="H336" t="n">
         <v>10500</v>
@@ -10200,7 +10200,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G339" t="n">
-        <v>2.08275556564331</v>
+        <v>2.08275580406189</v>
       </c>
       <c r="H339" t="n">
         <v>3000</v>
@@ -10345,7 +10345,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G344" t="n">
-        <v>1.9597235918045</v>
+        <v>1.95972383022308</v>
       </c>
       <c r="H344" t="n">
         <v>27000</v>
@@ -10461,7 +10461,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G348" t="n">
-        <v>1.93335974216461</v>
+        <v>1.93335998058319</v>
       </c>
       <c r="H348" t="n">
         <v>1500</v>
@@ -10606,7 +10606,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G353" t="n">
-        <v>1.88941979408264</v>
+        <v>1.88941991329193</v>
       </c>
       <c r="H353" t="n">
         <v>7500</v>
@@ -10635,7 +10635,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G354" t="n">
-        <v>1.85426783561707</v>
+        <v>1.85426771640778</v>
       </c>
       <c r="H354" t="n">
         <v>13500</v>
@@ -10664,7 +10664,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G355" t="n">
-        <v>1.9245719909668</v>
+        <v>1.92457175254822</v>
       </c>
       <c r="H355" t="n">
         <v>13500</v>
@@ -10780,7 +10780,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G359" t="n">
-        <v>2.03002786636353</v>
+        <v>2.0300281047821</v>
       </c>
       <c r="H359" t="n">
         <v>7500</v>
@@ -10809,7 +10809,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G360" t="n">
-        <v>2.03002786636353</v>
+        <v>2.0300281047821</v>
       </c>
       <c r="H360" t="n">
         <v>0</v>
@@ -10838,7 +10838,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G361" t="n">
-        <v>1.99487590789795</v>
+        <v>1.99487566947937</v>
       </c>
       <c r="H361" t="n">
         <v>15000</v>
@@ -10867,7 +10867,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G362" t="n">
-        <v>1.99487590789795</v>
+        <v>1.99487566947937</v>
       </c>
       <c r="H362" t="n">
         <v>6000</v>
@@ -10983,7 +10983,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G366" t="n">
-        <v>1.93335974216461</v>
+        <v>1.93335998058319</v>
       </c>
       <c r="H366" t="n">
         <v>13500</v>
@@ -11012,7 +11012,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G367" t="n">
-        <v>1.93335974216461</v>
+        <v>1.93335998058319</v>
       </c>
       <c r="H367" t="n">
         <v>1500</v>
@@ -11099,7 +11099,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G370" t="n">
-        <v>1.93335974216461</v>
+        <v>1.93335998058319</v>
       </c>
       <c r="H370" t="n">
         <v>6000</v>
@@ -11128,7 +11128,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G371" t="n">
-        <v>1.93335974216461</v>
+        <v>1.93335998058319</v>
       </c>
       <c r="H371" t="n">
         <v>1500</v>
@@ -11215,7 +11215,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G374" t="n">
-        <v>1.77517592906952</v>
+        <v>1.77517580986023</v>
       </c>
       <c r="H374" t="n">
         <v>52500</v>
@@ -11244,7 +11244,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G375" t="n">
-        <v>1.85426783561707</v>
+        <v>1.85426771640778</v>
       </c>
       <c r="H375" t="n">
         <v>15000</v>
@@ -11273,7 +11273,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G376" t="n">
-        <v>1.88063192367554</v>
+        <v>1.88063168525696</v>
       </c>
       <c r="H376" t="n">
         <v>9000</v>
@@ -11302,7 +11302,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G377" t="n">
-        <v>1.88063192367554</v>
+        <v>1.88063168525696</v>
       </c>
       <c r="H377" t="n">
         <v>3000</v>
@@ -11360,7 +11360,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G379" t="n">
-        <v>1.93335974216461</v>
+        <v>1.93335998058319</v>
       </c>
       <c r="H379" t="n">
         <v>3000</v>
@@ -11418,7 +11418,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G381" t="n">
-        <v>1.74002373218536</v>
+        <v>1.74002385139465</v>
       </c>
       <c r="H381" t="n">
         <v>34500</v>
@@ -11476,7 +11476,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G383" t="n">
-        <v>1.86305582523346</v>
+        <v>1.86305558681488</v>
       </c>
       <c r="H383" t="n">
         <v>21000</v>
@@ -11505,7 +11505,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G384" t="n">
-        <v>1.86305582523346</v>
+        <v>1.86305558681488</v>
       </c>
       <c r="H384" t="n">
         <v>1500</v>
@@ -11534,7 +11534,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G385" t="n">
-        <v>1.88063192367554</v>
+        <v>1.88063168525696</v>
       </c>
       <c r="H385" t="n">
         <v>13500</v>
@@ -11563,7 +11563,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G386" t="n">
-        <v>1.99487590789795</v>
+        <v>1.99487566947937</v>
       </c>
       <c r="H386" t="n">
         <v>15000</v>
@@ -11592,7 +11592,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G387" t="n">
-        <v>1.89820802211761</v>
+        <v>1.89820790290833</v>
       </c>
       <c r="H387" t="n">
         <v>28500</v>
@@ -11621,7 +11621,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G388" t="n">
-        <v>1.99487590789795</v>
+        <v>1.99487566947937</v>
       </c>
       <c r="H388" t="n">
         <v>9000</v>
@@ -11679,7 +11679,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G390" t="n">
-        <v>1.93335974216461</v>
+        <v>1.93335998058319</v>
       </c>
       <c r="H390" t="n">
         <v>1500</v>
@@ -11795,7 +11795,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G394" t="n">
-        <v>1.9245719909668</v>
+        <v>1.92457175254822</v>
       </c>
       <c r="H394" t="n">
         <v>12000</v>
@@ -11824,7 +11824,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G395" t="n">
-        <v>1.99487590789795</v>
+        <v>1.99487566947937</v>
       </c>
       <c r="H395" t="n">
         <v>31500</v>
@@ -11969,7 +11969,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G400" t="n">
-        <v>2.02123951911926</v>
+        <v>2.02123975753784</v>
       </c>
       <c r="H400" t="n">
         <v>10500</v>
@@ -12056,7 +12056,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G403" t="n">
-        <v>1.93335974216461</v>
+        <v>1.93335998058319</v>
       </c>
       <c r="H403" t="n">
         <v>7500</v>
@@ -12201,7 +12201,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G408" t="n">
-        <v>1.89820802211761</v>
+        <v>1.89820790290833</v>
       </c>
       <c r="H408" t="n">
         <v>6000</v>
@@ -12230,7 +12230,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G409" t="n">
-        <v>1.88941979408264</v>
+        <v>1.88941991329193</v>
       </c>
       <c r="H409" t="n">
         <v>6000</v>
@@ -12259,7 +12259,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G410" t="n">
-        <v>1.88941979408264</v>
+        <v>1.88941991329193</v>
       </c>
       <c r="H410" t="n">
         <v>0</v>
@@ -12317,7 +12317,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G412" t="n">
-        <v>1.88063192367554</v>
+        <v>1.88063168525696</v>
       </c>
       <c r="H412" t="n">
         <v>9000</v>
@@ -12346,7 +12346,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G413" t="n">
-        <v>1.88063192367554</v>
+        <v>1.88063168525696</v>
       </c>
       <c r="H413" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G415" t="n">
-        <v>1.8191157579422</v>
+        <v>1.81911587715149</v>
       </c>
       <c r="H415" t="n">
         <v>4500</v>
@@ -12433,7 +12433,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G416" t="n">
-        <v>1.8191157579422</v>
+        <v>1.81911587715149</v>
       </c>
       <c r="H416" t="n">
         <v>0</v>
@@ -12462,7 +12462,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G417" t="n">
-        <v>1.86305582523346</v>
+        <v>1.86305558681488</v>
       </c>
       <c r="H417" t="n">
         <v>6000</v>
@@ -12549,7 +12549,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G420" t="n">
-        <v>1.89820802211761</v>
+        <v>1.89820790290833</v>
       </c>
       <c r="H420" t="n">
         <v>6000</v>
@@ -12665,7 +12665,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G424" t="n">
-        <v>1.77517592906952</v>
+        <v>1.77517580986023</v>
       </c>
       <c r="H424" t="n">
         <v>7500</v>
@@ -12694,7 +12694,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G425" t="n">
-        <v>1.74002373218536</v>
+        <v>1.74002385139465</v>
       </c>
       <c r="H425" t="n">
         <v>3000</v>
@@ -12897,7 +12897,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G432" t="n">
-        <v>1.77517592906952</v>
+        <v>1.77517580986023</v>
       </c>
       <c r="H432" t="n">
         <v>3000</v>
@@ -12926,7 +12926,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G433" t="n">
-        <v>1.86305582523346</v>
+        <v>1.86305558681488</v>
       </c>
       <c r="H433" t="n">
         <v>7500</v>
@@ -12955,7 +12955,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G434" t="n">
-        <v>1.86305582523346</v>
+        <v>1.86305558681488</v>
       </c>
       <c r="H434" t="n">
         <v>0</v>
@@ -12984,7 +12984,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G435" t="n">
-        <v>1.86305582523346</v>
+        <v>1.86305558681488</v>
       </c>
       <c r="H435" t="n">
         <v>3000</v>
@@ -13013,7 +13013,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G436" t="n">
-        <v>1.88063192367554</v>
+        <v>1.88063168525696</v>
       </c>
       <c r="H436" t="n">
         <v>3000</v>
@@ -13042,7 +13042,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G437" t="n">
-        <v>1.85426783561707</v>
+        <v>1.85426771640778</v>
       </c>
       <c r="H437" t="n">
         <v>4500</v>
@@ -13071,7 +13071,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G438" t="n">
-        <v>1.85426783561707</v>
+        <v>1.85426771640778</v>
       </c>
       <c r="H438" t="n">
         <v>0</v>
@@ -13100,7 +13100,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G439" t="n">
-        <v>1.8191157579422</v>
+        <v>1.81911587715149</v>
       </c>
       <c r="H439" t="n">
         <v>6000</v>
@@ -13129,7 +13129,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G440" t="n">
-        <v>1.8191157579422</v>
+        <v>1.81911587715149</v>
       </c>
       <c r="H440" t="n">
         <v>0</v>
@@ -13158,7 +13158,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G441" t="n">
-        <v>1.88063192367554</v>
+        <v>1.88063168525696</v>
       </c>
       <c r="H441" t="n">
         <v>3000</v>
@@ -13187,7 +13187,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G442" t="n">
-        <v>1.88063192367554</v>
+        <v>1.88063168525696</v>
       </c>
       <c r="H442" t="n">
         <v>0</v>
@@ -13245,7 +13245,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G444" t="n">
-        <v>1.86305582523346</v>
+        <v>1.86305558681488</v>
       </c>
       <c r="H444" t="n">
         <v>1500</v>
@@ -13361,7 +13361,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G448" t="n">
-        <v>1.73563003540039</v>
+        <v>1.73562979698181</v>
       </c>
       <c r="H448" t="n">
         <v>3000</v>
@@ -13390,7 +13390,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G449" t="n">
-        <v>1.68290174007416</v>
+        <v>1.68290185928345</v>
       </c>
       <c r="H449" t="n">
         <v>6000</v>
@@ -13448,7 +13448,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G451" t="n">
-        <v>1.74002373218536</v>
+        <v>1.74002385139465</v>
       </c>
       <c r="H451" t="n">
         <v>4500</v>
@@ -13477,7 +13477,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G452" t="n">
-        <v>1.72684192657471</v>
+        <v>1.72684180736542</v>
       </c>
       <c r="H452" t="n">
         <v>3000</v>
@@ -13535,7 +13535,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G454" t="n">
-        <v>1.63896179199219</v>
+        <v>1.63896191120148</v>
       </c>
       <c r="H454" t="n">
         <v>6000</v>
@@ -13709,7 +13709,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G460" t="n">
-        <v>1.67411375045776</v>
+        <v>1.67411386966705</v>
       </c>
       <c r="H460" t="n">
         <v>1500</v>
@@ -13738,7 +13738,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G461" t="n">
-        <v>1.67411375045776</v>
+        <v>1.67411386966705</v>
       </c>
       <c r="H461" t="n">
         <v>6000</v>
@@ -13767,7 +13767,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G462" t="n">
-        <v>1.67411375045776</v>
+        <v>1.67411386966705</v>
       </c>
       <c r="H462" t="n">
         <v>1500</v>
@@ -13883,7 +13883,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G466" t="n">
-        <v>1.59941589832306</v>
+        <v>1.59941601753235</v>
       </c>
       <c r="H466" t="n">
         <v>6000</v>
@@ -13912,7 +13912,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G467" t="n">
-        <v>1.59502196311951</v>
+        <v>1.59502184391022</v>
       </c>
       <c r="H467" t="n">
         <v>3000</v>
@@ -13941,7 +13941,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G468" t="n">
-        <v>1.6697199344635</v>
+        <v>1.66971981525421</v>
       </c>
       <c r="H468" t="n">
         <v>4500</v>
@@ -13970,7 +13970,7 @@
         <v>1.875</v>
       </c>
       <c r="G469" t="n">
-        <v>1.64774978160858</v>
+        <v>1.64774990081787</v>
       </c>
       <c r="H469" t="n">
         <v>3000</v>
@@ -14028,7 +14028,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G471" t="n">
-        <v>1.59502196311951</v>
+        <v>1.59502184391022</v>
       </c>
       <c r="H471" t="n">
         <v>15000</v>
@@ -14115,7 +14115,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G474" t="n">
-        <v>1.6697199344635</v>
+        <v>1.66971981525421</v>
       </c>
       <c r="H474" t="n">
         <v>3000</v>
@@ -14173,7 +14173,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G476" t="n">
-        <v>1.66532576084137</v>
+        <v>1.66532588005066</v>
       </c>
       <c r="H476" t="n">
         <v>1500</v>
@@ -14202,7 +14202,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G477" t="n">
-        <v>1.66532576084137</v>
+        <v>1.66532588005066</v>
       </c>
       <c r="H477" t="n">
         <v>0</v>
@@ -14231,7 +14231,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G478" t="n">
-        <v>1.66532576084137</v>
+        <v>1.66532588005066</v>
       </c>
       <c r="H478" t="n">
         <v>0</v>
@@ -14289,7 +14289,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G480" t="n">
-        <v>1.63017392158508</v>
+        <v>1.63017380237579</v>
       </c>
       <c r="H480" t="n">
         <v>3000</v>
@@ -14347,7 +14347,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G482" t="n">
-        <v>1.67411375045776</v>
+        <v>1.67411386966705</v>
       </c>
       <c r="H482" t="n">
         <v>4500</v>
@@ -14492,7 +14492,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G487" t="n">
-        <v>1.93335974216461</v>
+        <v>1.93335998058319</v>
       </c>
       <c r="H487" t="n">
         <v>33000</v>
@@ -14521,7 +14521,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G488" t="n">
-        <v>1.9245719909668</v>
+        <v>1.92457175254822</v>
       </c>
       <c r="H488" t="n">
         <v>34500</v>
@@ -14637,7 +14637,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G492" t="n">
-        <v>1.99487590789795</v>
+        <v>1.99487566947937</v>
       </c>
       <c r="H492" t="n">
         <v>3000</v>
@@ -14666,7 +14666,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G493" t="n">
-        <v>2.02123951911926</v>
+        <v>2.02123975753784</v>
       </c>
       <c r="H493" t="n">
         <v>42000</v>
@@ -14753,7 +14753,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G496" t="n">
-        <v>1.93335974216461</v>
+        <v>1.93335998058319</v>
       </c>
       <c r="H496" t="n">
         <v>6000</v>
@@ -14811,7 +14811,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G498" t="n">
-        <v>1.73563003540039</v>
+        <v>1.73562979698181</v>
       </c>
       <c r="H498" t="n">
         <v>40500</v>
@@ -15014,7 +15014,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G505" t="n">
-        <v>1.77517592906952</v>
+        <v>1.77517580986023</v>
       </c>
       <c r="H505" t="n">
         <v>3000</v>
@@ -15043,7 +15043,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G506" t="n">
-        <v>1.77517592906952</v>
+        <v>1.77517580986023</v>
       </c>
       <c r="H506" t="n">
         <v>3000</v>
@@ -15159,7 +15159,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G510" t="n">
-        <v>1.77517592906952</v>
+        <v>1.77517580986023</v>
       </c>
       <c r="H510" t="n">
         <v>4500</v>
@@ -15449,7 +15449,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G520" t="n">
-        <v>1.79275190830231</v>
+        <v>1.79275178909302</v>
       </c>
       <c r="H520" t="n">
         <v>4500</v>
@@ -15536,7 +15536,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G523" t="n">
-        <v>1.67850780487061</v>
+        <v>1.6785079240799</v>
       </c>
       <c r="H523" t="n">
         <v>9000</v>
@@ -15623,7 +15623,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G526" t="n">
-        <v>1.54229378700256</v>
+        <v>1.54229390621185</v>
       </c>
       <c r="H526" t="n">
         <v>19500</v>
@@ -15710,7 +15710,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G529" t="n">
-        <v>1.52471780776978</v>
+        <v>1.52471792697906</v>
       </c>
       <c r="H529" t="n">
         <v>6000</v>
@@ -15739,7 +15739,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G530" t="n">
-        <v>1.48517191410065</v>
+        <v>1.48517203330994</v>
       </c>
       <c r="H530" t="n">
         <v>7500</v>
@@ -15768,7 +15768,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G531" t="n">
-        <v>1.51592981815338</v>
+        <v>1.51592993736267</v>
       </c>
       <c r="H531" t="n">
         <v>1500</v>
@@ -15797,7 +15797,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G532" t="n">
-        <v>1.51592981815338</v>
+        <v>1.51592993736267</v>
       </c>
       <c r="H532" t="n">
         <v>0</v>
@@ -15826,7 +15826,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G533" t="n">
-        <v>1.51592981815338</v>
+        <v>1.51592993736267</v>
       </c>
       <c r="H533" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G534" t="n">
-        <v>1.48517191410065</v>
+        <v>1.48517203330994</v>
       </c>
       <c r="H534" t="n">
         <v>1500</v>
@@ -15884,7 +15884,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G535" t="n">
-        <v>1.48517191410065</v>
+        <v>1.48517203330994</v>
       </c>
       <c r="H535" t="n">
         <v>0</v>
@@ -16116,7 +16116,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G543" t="n">
-        <v>1.49395978450775</v>
+        <v>1.49395990371704</v>
       </c>
       <c r="H543" t="n">
         <v>1500</v>
@@ -16174,7 +16174,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G545" t="n">
-        <v>1.56426393985748</v>
+        <v>1.56426382064819</v>
       </c>
       <c r="H545" t="n">
         <v>4500</v>
@@ -16203,7 +16203,7 @@
         <v>1.875</v>
       </c>
       <c r="G546" t="n">
-        <v>1.64774978160858</v>
+        <v>1.64774990081787</v>
       </c>
       <c r="H546" t="n">
         <v>18000</v>
@@ -16232,7 +16232,7 @@
         <v>1.875</v>
       </c>
       <c r="G547" t="n">
-        <v>1.64774978160858</v>
+        <v>1.64774990081787</v>
       </c>
       <c r="H547" t="n">
         <v>0</v>
@@ -16261,7 +16261,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G548" t="n">
-        <v>1.67850780487061</v>
+        <v>1.6785079240799</v>
       </c>
       <c r="H548" t="n">
         <v>3000</v>
@@ -16290,7 +16290,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G549" t="n">
-        <v>1.67850780487061</v>
+        <v>1.6785079240799</v>
       </c>
       <c r="H549" t="n">
         <v>0</v>
@@ -16319,7 +16319,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G550" t="n">
-        <v>1.67850780487061</v>
+        <v>1.6785079240799</v>
       </c>
       <c r="H550" t="n">
         <v>0</v>
@@ -16348,7 +16348,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G551" t="n">
-        <v>1.72684192657471</v>
+        <v>1.72684180736542</v>
       </c>
       <c r="H551" t="n">
         <v>1500</v>
@@ -16493,7 +16493,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G556" t="n">
-        <v>1.6697199344635</v>
+        <v>1.66971981525421</v>
       </c>
       <c r="H556" t="n">
         <v>6000</v>
@@ -16522,7 +16522,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G557" t="n">
-        <v>1.6697199344635</v>
+        <v>1.66971981525421</v>
       </c>
       <c r="H557" t="n">
         <v>3000</v>
@@ -16551,7 +16551,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G558" t="n">
-        <v>1.72684192657471</v>
+        <v>1.72684180736542</v>
       </c>
       <c r="H558" t="n">
         <v>13500</v>
@@ -16580,7 +16580,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G559" t="n">
-        <v>1.72684192657471</v>
+        <v>1.72684180736542</v>
       </c>
       <c r="H559" t="n">
         <v>0</v>
@@ -16609,7 +16609,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G560" t="n">
-        <v>1.67850780487061</v>
+        <v>1.6785079240799</v>
       </c>
       <c r="H560" t="n">
         <v>9000</v>
@@ -16638,7 +16638,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G561" t="n">
-        <v>1.67850780487061</v>
+        <v>1.6785079240799</v>
       </c>
       <c r="H561" t="n">
         <v>0</v>
@@ -16667,7 +16667,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G562" t="n">
-        <v>1.67850780487061</v>
+        <v>1.6785079240799</v>
       </c>
       <c r="H562" t="n">
         <v>0</v>
@@ -16696,7 +16696,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G563" t="n">
-        <v>1.67850780487061</v>
+        <v>1.6785079240799</v>
       </c>
       <c r="H563" t="n">
         <v>0</v>
@@ -16725,7 +16725,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G564" t="n">
-        <v>1.67850780487061</v>
+        <v>1.6785079240799</v>
       </c>
       <c r="H564" t="n">
         <v>0</v>
@@ -16754,7 +16754,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G565" t="n">
-        <v>1.67850780487061</v>
+        <v>1.6785079240799</v>
       </c>
       <c r="H565" t="n">
         <v>0</v>
@@ -16957,7 +16957,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G572" t="n">
-        <v>1.67411375045776</v>
+        <v>1.67411386966705</v>
       </c>
       <c r="H572" t="n">
         <v>1500</v>
@@ -16986,7 +16986,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G573" t="n">
-        <v>1.6697199344635</v>
+        <v>1.66971981525421</v>
       </c>
       <c r="H573" t="n">
         <v>1500</v>
@@ -17015,7 +17015,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G574" t="n">
-        <v>1.6697199344635</v>
+        <v>1.66971981525421</v>
       </c>
       <c r="H574" t="n">
         <v>0</v>
@@ -17044,7 +17044,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G575" t="n">
-        <v>1.6697199344635</v>
+        <v>1.66971981525421</v>
       </c>
       <c r="H575" t="n">
         <v>0</v>
@@ -17073,7 +17073,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G576" t="n">
-        <v>1.6697199344635</v>
+        <v>1.66971981525421</v>
       </c>
       <c r="H576" t="n">
         <v>0</v>
@@ -17102,7 +17102,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G577" t="n">
-        <v>1.6697199344635</v>
+        <v>1.66971981525421</v>
       </c>
       <c r="H577" t="n">
         <v>0</v>
@@ -17131,7 +17131,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G578" t="n">
-        <v>1.67850780487061</v>
+        <v>1.6785079240799</v>
       </c>
       <c r="H578" t="n">
         <v>1500</v>
@@ -17160,7 +17160,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G579" t="n">
-        <v>1.67850780487061</v>
+        <v>1.6785079240799</v>
       </c>
       <c r="H579" t="n">
         <v>0</v>
@@ -17189,7 +17189,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G580" t="n">
-        <v>1.67850780487061</v>
+        <v>1.6785079240799</v>
       </c>
       <c r="H580" t="n">
         <v>0</v>
@@ -17537,7 +17537,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G592" t="n">
-        <v>1.61699175834656</v>
+        <v>1.61699187755585</v>
       </c>
       <c r="H592" t="n">
         <v>6000</v>
@@ -17566,7 +17566,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G593" t="n">
-        <v>1.5554758310318</v>
+        <v>1.55547571182251</v>
       </c>
       <c r="H593" t="n">
         <v>13500</v>
@@ -17624,7 +17624,7 @@
         <v>1.875</v>
       </c>
       <c r="G595" t="n">
-        <v>1.64774978160858</v>
+        <v>1.64774990081787</v>
       </c>
       <c r="H595" t="n">
         <v>7500</v>
@@ -17653,7 +17653,7 @@
         <v>1.875</v>
       </c>
       <c r="G596" t="n">
-        <v>1.64774978160858</v>
+        <v>1.64774990081787</v>
       </c>
       <c r="H596" t="n">
         <v>0</v>
@@ -17682,7 +17682,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G597" t="n">
-        <v>1.61699175834656</v>
+        <v>1.61699187755585</v>
       </c>
       <c r="H597" t="n">
         <v>15000</v>
@@ -17711,7 +17711,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G598" t="n">
-        <v>1.63896179199219</v>
+        <v>1.63896191120148</v>
       </c>
       <c r="H598" t="n">
         <v>1500</v>
@@ -17740,7 +17740,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G599" t="n">
-        <v>1.63896179199219</v>
+        <v>1.63896191120148</v>
       </c>
       <c r="H599" t="n">
         <v>0</v>
@@ -17769,7 +17769,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G600" t="n">
-        <v>1.59941589832306</v>
+        <v>1.59941601753235</v>
       </c>
       <c r="H600" t="n">
         <v>3000</v>
@@ -17798,7 +17798,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G601" t="n">
-        <v>1.59941589832306</v>
+        <v>1.59941601753235</v>
       </c>
       <c r="H601" t="n">
         <v>0</v>
@@ -17827,7 +17827,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G602" t="n">
-        <v>1.59941589832306</v>
+        <v>1.59941601753235</v>
       </c>
       <c r="H602" t="n">
         <v>0</v>
@@ -17943,7 +17943,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G606" t="n">
-        <v>1.63896179199219</v>
+        <v>1.63896191120148</v>
       </c>
       <c r="H606" t="n">
         <v>3000</v>
@@ -17972,7 +17972,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G607" t="n">
-        <v>1.61699175834656</v>
+        <v>1.61699187755585</v>
       </c>
       <c r="H607" t="n">
         <v>3000</v>
@@ -18030,7 +18030,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G609" t="n">
-        <v>1.61259794235229</v>
+        <v>1.61259782314301</v>
       </c>
       <c r="H609" t="n">
         <v>1500</v>
@@ -18117,7 +18117,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G612" t="n">
-        <v>1.60820376873016</v>
+        <v>1.60820388793945</v>
       </c>
       <c r="H612" t="n">
         <v>1500</v>
@@ -18233,7 +18233,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G616" t="n">
-        <v>1.56865787506104</v>
+        <v>1.56865775585175</v>
       </c>
       <c r="H616" t="n">
         <v>7500</v>
@@ -18291,7 +18291,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G618" t="n">
-        <v>1.67850780487061</v>
+        <v>1.6785079240799</v>
       </c>
       <c r="H618" t="n">
         <v>45000</v>
@@ -18320,7 +18320,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G619" t="n">
-        <v>1.72244775295258</v>
+        <v>1.72244787216187</v>
       </c>
       <c r="H619" t="n">
         <v>10500</v>
@@ -18349,7 +18349,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G620" t="n">
-        <v>1.71805393695831</v>
+        <v>1.71805381774902</v>
       </c>
       <c r="H620" t="n">
         <v>1500</v>
@@ -18378,7 +18378,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G621" t="n">
-        <v>1.6697199344635</v>
+        <v>1.66971981525421</v>
       </c>
       <c r="H621" t="n">
         <v>7500</v>
@@ -18407,7 +18407,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G622" t="n">
-        <v>1.68290174007416</v>
+        <v>1.68290185928345</v>
       </c>
       <c r="H622" t="n">
         <v>13500</v>
@@ -18465,7 +18465,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G624" t="n">
-        <v>1.6697199344635</v>
+        <v>1.66971981525421</v>
       </c>
       <c r="H624" t="n">
         <v>4500</v>
@@ -18610,7 +18610,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G629" t="n">
-        <v>1.88063192367554</v>
+        <v>1.88063168525696</v>
       </c>
       <c r="H629" t="n">
         <v>39000</v>
@@ -18639,7 +18639,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G630" t="n">
-        <v>1.88941979408264</v>
+        <v>1.88941991329193</v>
       </c>
       <c r="H630" t="n">
         <v>19500</v>
@@ -18697,7 +18697,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G632" t="n">
-        <v>1.86305582523346</v>
+        <v>1.86305558681488</v>
       </c>
       <c r="H632" t="n">
         <v>33000</v>
@@ -18726,7 +18726,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G633" t="n">
-        <v>1.8191157579422</v>
+        <v>1.81911587715149</v>
       </c>
       <c r="H633" t="n">
         <v>4500</v>
@@ -18813,7 +18813,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G636" t="n">
-        <v>1.71805393695831</v>
+        <v>1.71805381774902</v>
       </c>
       <c r="H636" t="n">
         <v>30000</v>
@@ -18871,7 +18871,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G638" t="n">
-        <v>1.67850780487061</v>
+        <v>1.6785079240799</v>
       </c>
       <c r="H638" t="n">
         <v>12000</v>
@@ -18929,7 +18929,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G640" t="n">
-        <v>1.60820376873016</v>
+        <v>1.60820388793945</v>
       </c>
       <c r="H640" t="n">
         <v>33000</v>
@@ -19132,7 +19132,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G647" t="n">
-        <v>1.66532576084137</v>
+        <v>1.66532588005066</v>
       </c>
       <c r="H647" t="n">
         <v>7500</v>
@@ -19277,7 +19277,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G652" t="n">
-        <v>1.67850780487061</v>
+        <v>1.6785079240799</v>
       </c>
       <c r="H652" t="n">
         <v>6000</v>
@@ -19306,7 +19306,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G653" t="n">
-        <v>1.67850780487061</v>
+        <v>1.6785079240799</v>
       </c>
       <c r="H653" t="n">
         <v>0</v>
@@ -19335,7 +19335,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G654" t="n">
-        <v>1.74002373218536</v>
+        <v>1.74002385139465</v>
       </c>
       <c r="H654" t="n">
         <v>1500</v>
@@ -19364,7 +19364,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G655" t="n">
-        <v>1.74002373218536</v>
+        <v>1.74002385139465</v>
       </c>
       <c r="H655" t="n">
         <v>0</v>
@@ -19451,7 +19451,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G658" t="n">
-        <v>1.79275190830231</v>
+        <v>1.79275178909302</v>
       </c>
       <c r="H658" t="n">
         <v>108000</v>
@@ -45470,6 +45470,64 @@
         <v>0</v>
       </c>
       <c r="I1555" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1556">
+      <c r="A1556" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1556" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1556" t="n">
+        <v>1.52999997138977</v>
+      </c>
+      <c r="D1556" t="n">
+        <v>1.52999997138977</v>
+      </c>
+      <c r="E1556" t="n">
+        <v>1.52999997138977</v>
+      </c>
+      <c r="F1556" t="n">
+        <v>1.52999997138977</v>
+      </c>
+      <c r="G1556" t="n">
+        <v>1.52999997138977</v>
+      </c>
+      <c r="H1556" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1556" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1557">
+      <c r="A1557" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1557" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1557" t="n">
+        <v>1.50999999046326</v>
+      </c>
+      <c r="D1557" t="n">
+        <v>1.50999999046326</v>
+      </c>
+      <c r="E1557" t="n">
+        <v>1.50999999046326</v>
+      </c>
+      <c r="F1557" t="n">
+        <v>1.50999999046326</v>
+      </c>
+      <c r="G1557" t="n">
+        <v>1.50999999046326</v>
+      </c>
+      <c r="H1557" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I1557" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RETI.MI.xlsx
+++ b/data/RETI.MI.xlsx
@@ -427,7 +427,7 @@
         <v>0.889900028705597</v>
       </c>
       <c r="G2" t="n">
-        <v>0.759858429431915</v>
+        <v>0.75985848903656</v>
       </c>
       <c r="H2" t="n">
         <v>856500</v>
@@ -456,7 +456,7 @@
         <v>0.899600028991699</v>
       </c>
       <c r="G3" t="n">
-        <v>0.768140971660614</v>
+        <v>0.768141031265259</v>
       </c>
       <c r="H3" t="n">
         <v>472500</v>
@@ -572,7 +572,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G7" t="n">
-        <v>0.749697387218475</v>
+        <v>0.74969744682312</v>
       </c>
       <c r="H7" t="n">
         <v>139500</v>
@@ -659,7 +659,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G10" t="n">
-        <v>0.72237354516983</v>
+        <v>0.722373604774475</v>
       </c>
       <c r="H10" t="n">
         <v>48000</v>
@@ -717,7 +717,7 @@
         <v>0.814000010490417</v>
       </c>
       <c r="G12" t="n">
-        <v>0.695049703121185</v>
+        <v>0.695049643516541</v>
       </c>
       <c r="H12" t="n">
         <v>63000</v>
@@ -746,7 +746,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G13" t="n">
-        <v>0.691634178161621</v>
+        <v>0.691634237766266</v>
       </c>
       <c r="H13" t="n">
         <v>49500</v>
@@ -833,7 +833,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G16" t="n">
-        <v>0.666018187999725</v>
+        <v>0.666018128395081</v>
       </c>
       <c r="H16" t="n">
         <v>67500</v>
@@ -920,7 +920,7 @@
         <v>0.814000010490417</v>
       </c>
       <c r="G19" t="n">
-        <v>0.695049703121185</v>
+        <v>0.695049643516541</v>
       </c>
       <c r="H19" t="n">
         <v>265500</v>
@@ -1007,7 +1007,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G22" t="n">
-        <v>0.659187197685242</v>
+        <v>0.659187257289886</v>
       </c>
       <c r="H22" t="n">
         <v>24000</v>
@@ -1036,7 +1036,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G23" t="n">
-        <v>0.666018187999725</v>
+        <v>0.666018128395081</v>
       </c>
       <c r="H23" t="n">
         <v>39000</v>
@@ -1210,7 +1210,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G29" t="n">
-        <v>0.623324632644653</v>
+        <v>0.623324692249298</v>
       </c>
       <c r="H29" t="n">
         <v>46500</v>
@@ -1239,7 +1239,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G30" t="n">
-        <v>0.607955038547516</v>
+        <v>0.607955098152161</v>
       </c>
       <c r="H30" t="n">
         <v>19500</v>
@@ -1268,7 +1268,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G31" t="n">
-        <v>0.58746212720871</v>
+        <v>0.587462186813354</v>
       </c>
       <c r="H31" t="n">
         <v>78000</v>
@@ -1297,7 +1297,7 @@
         <v>0.73199999332428</v>
       </c>
       <c r="G32" t="n">
-        <v>0.625032365322113</v>
+        <v>0.625032424926758</v>
       </c>
       <c r="H32" t="n">
         <v>27000</v>
@@ -1326,7 +1326,7 @@
         <v>0.722000002861023</v>
       </c>
       <c r="G33" t="n">
-        <v>0.616493761539459</v>
+        <v>0.616493701934814</v>
       </c>
       <c r="H33" t="n">
         <v>3000</v>
@@ -1529,7 +1529,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G40" t="n">
-        <v>0.546476483345032</v>
+        <v>0.546476423740387</v>
       </c>
       <c r="H40" t="n">
         <v>15000</v>
@@ -1616,7 +1616,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G43" t="n">
-        <v>0.623324632644653</v>
+        <v>0.623324692249298</v>
       </c>
       <c r="H43" t="n">
         <v>138000</v>
@@ -1732,7 +1732,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G47" t="n">
-        <v>0.607955038547516</v>
+        <v>0.607955098152161</v>
       </c>
       <c r="H47" t="n">
         <v>7500</v>
@@ -1877,7 +1877,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G52" t="n">
-        <v>0.705296158790588</v>
+        <v>0.705296099185944</v>
       </c>
       <c r="H52" t="n">
         <v>157500</v>
@@ -1964,7 +1964,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G55" t="n">
-        <v>0.677972316741943</v>
+        <v>0.677972376346588</v>
       </c>
       <c r="H55" t="n">
         <v>36000</v>
@@ -2022,7 +2022,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G57" t="n">
-        <v>0.705296158790588</v>
+        <v>0.705296099185944</v>
       </c>
       <c r="H57" t="n">
         <v>25500</v>
@@ -2051,7 +2051,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G58" t="n">
-        <v>0.703588426113129</v>
+        <v>0.703588485717773</v>
       </c>
       <c r="H58" t="n">
         <v>12000</v>
@@ -2167,7 +2167,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G62" t="n">
-        <v>0.681387841701508</v>
+        <v>0.681387782096863</v>
       </c>
       <c r="H62" t="n">
         <v>16500</v>
@@ -2399,7 +2399,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G70" t="n">
-        <v>0.677972316741943</v>
+        <v>0.677972376346588</v>
       </c>
       <c r="H70" t="n">
         <v>3000</v>
@@ -2428,7 +2428,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G71" t="n">
-        <v>0.677972316741943</v>
+        <v>0.677972376346588</v>
       </c>
       <c r="H71" t="n">
         <v>3000</v>
@@ -2486,7 +2486,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G73" t="n">
-        <v>0.705296158790588</v>
+        <v>0.705296099185944</v>
       </c>
       <c r="H73" t="n">
         <v>19500</v>
@@ -2515,7 +2515,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G74" t="n">
-        <v>0.691634178161621</v>
+        <v>0.691634237766266</v>
       </c>
       <c r="H74" t="n">
         <v>43500</v>
@@ -2544,7 +2544,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G75" t="n">
-        <v>0.700172960758209</v>
+        <v>0.700172901153564</v>
       </c>
       <c r="H75" t="n">
         <v>73500</v>
@@ -2602,7 +2602,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G77" t="n">
-        <v>0.700172960758209</v>
+        <v>0.700172901153564</v>
       </c>
       <c r="H77" t="n">
         <v>22500</v>
@@ -2631,7 +2631,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G78" t="n">
-        <v>0.700172960758209</v>
+        <v>0.700172901153564</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
@@ -2660,7 +2660,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G79" t="n">
-        <v>0.705296158790588</v>
+        <v>0.705296099185944</v>
       </c>
       <c r="H79" t="n">
         <v>3000</v>
@@ -2718,7 +2718,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G81" t="n">
-        <v>0.708711624145508</v>
+        <v>0.708711683750153</v>
       </c>
       <c r="H81" t="n">
         <v>22500</v>
@@ -2863,7 +2863,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G86" t="n">
-        <v>0.700172960758209</v>
+        <v>0.700172901153564</v>
       </c>
       <c r="H86" t="n">
         <v>1500</v>
@@ -2921,7 +2921,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G88" t="n">
-        <v>0.700172960758209</v>
+        <v>0.700172901153564</v>
       </c>
       <c r="H88" t="n">
         <v>16500</v>
@@ -2950,7 +2950,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G89" t="n">
-        <v>0.684803307056427</v>
+        <v>0.684803247451782</v>
       </c>
       <c r="H89" t="n">
         <v>22500</v>
@@ -2979,7 +2979,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G90" t="n">
-        <v>0.684803307056427</v>
+        <v>0.684803247451782</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -3211,7 +3211,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G98" t="n">
-        <v>0.666018187999725</v>
+        <v>0.666018128395081</v>
       </c>
       <c r="H98" t="n">
         <v>18000</v>
@@ -3240,7 +3240,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G99" t="n">
-        <v>0.677972316741943</v>
+        <v>0.677972376346588</v>
       </c>
       <c r="H99" t="n">
         <v>7500</v>
@@ -3269,7 +3269,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G100" t="n">
-        <v>0.676264524459839</v>
+        <v>0.676264584064484</v>
       </c>
       <c r="H100" t="n">
         <v>7500</v>
@@ -3298,7 +3298,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G101" t="n">
-        <v>0.676264524459839</v>
+        <v>0.676264584064484</v>
       </c>
       <c r="H101" t="n">
         <v>0</v>
@@ -3472,7 +3472,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G107" t="n">
-        <v>0.691634178161621</v>
+        <v>0.691634237766266</v>
       </c>
       <c r="H107" t="n">
         <v>42000</v>
@@ -3501,7 +3501,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G108" t="n">
-        <v>0.700172960758209</v>
+        <v>0.700172901153564</v>
       </c>
       <c r="H108" t="n">
         <v>55500</v>
@@ -3588,7 +3588,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G111" t="n">
-        <v>0.703588426113129</v>
+        <v>0.703588485717773</v>
       </c>
       <c r="H111" t="n">
         <v>24000</v>
@@ -3646,7 +3646,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G113" t="n">
-        <v>0.691634178161621</v>
+        <v>0.691634237766266</v>
       </c>
       <c r="H113" t="n">
         <v>4500</v>
@@ -3675,7 +3675,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G114" t="n">
-        <v>0.700172960758209</v>
+        <v>0.700172901153564</v>
       </c>
       <c r="H114" t="n">
         <v>21000</v>
@@ -3704,7 +3704,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G115" t="n">
-        <v>0.703588426113129</v>
+        <v>0.703588485717773</v>
       </c>
       <c r="H115" t="n">
         <v>7500</v>
@@ -3733,7 +3733,7 @@
         <v>0.86599999666214</v>
       </c>
       <c r="G116" t="n">
-        <v>0.739450931549072</v>
+        <v>0.739450871944427</v>
       </c>
       <c r="H116" t="n">
         <v>108000</v>
@@ -3762,7 +3762,7 @@
         <v>0.842000007629395</v>
       </c>
       <c r="G117" t="n">
-        <v>0.718958079814911</v>
+        <v>0.718958020210266</v>
       </c>
       <c r="H117" t="n">
         <v>102000</v>
@@ -3907,7 +3907,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G122" t="n">
-        <v>0.858138740062714</v>
+        <v>0.858138799667358</v>
       </c>
       <c r="H122" t="n">
         <v>660000</v>
@@ -4081,7 +4081,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G128" t="n">
-        <v>0.86240816116333</v>
+        <v>0.862408101558685</v>
       </c>
       <c r="H128" t="n">
         <v>60000</v>
@@ -4110,7 +4110,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G129" t="n">
-        <v>0.86240816116333</v>
+        <v>0.862408101558685</v>
       </c>
       <c r="H129" t="n">
         <v>25500</v>
@@ -4139,7 +4139,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G130" t="n">
-        <v>0.86240816116333</v>
+        <v>0.862408101558685</v>
       </c>
       <c r="H130" t="n">
         <v>72000</v>
@@ -4197,7 +4197,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G132" t="n">
-        <v>0.845330715179443</v>
+        <v>0.845330774784088</v>
       </c>
       <c r="H132" t="n">
         <v>25500</v>
@@ -4284,7 +4284,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G135" t="n">
-        <v>0.866677522659302</v>
+        <v>0.866677463054657</v>
       </c>
       <c r="H135" t="n">
         <v>15000</v>
@@ -4400,7 +4400,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G139" t="n">
-        <v>0.913640260696411</v>
+        <v>0.913640379905701</v>
       </c>
       <c r="H139" t="n">
         <v>4500</v>
@@ -4429,7 +4429,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G140" t="n">
-        <v>0.922179102897644</v>
+        <v>0.922179043292999</v>
       </c>
       <c r="H140" t="n">
         <v>22500</v>
@@ -4458,7 +4458,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G141" t="n">
-        <v>0.922179102897644</v>
+        <v>0.922179043292999</v>
       </c>
       <c r="H141" t="n">
         <v>67500</v>
@@ -4487,7 +4487,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G142" t="n">
-        <v>0.913640260696411</v>
+        <v>0.913640379905701</v>
       </c>
       <c r="H142" t="n">
         <v>42000</v>
@@ -4516,7 +4516,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G143" t="n">
-        <v>0.930717825889587</v>
+        <v>0.930717706680298</v>
       </c>
       <c r="H143" t="n">
         <v>45000</v>
@@ -4719,7 +4719,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G150" t="n">
-        <v>1.18637990951538</v>
+        <v>1.18638002872467</v>
       </c>
       <c r="H150" t="n">
         <v>103500</v>
@@ -4864,7 +4864,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G155" t="n">
-        <v>1.13804590702057</v>
+        <v>1.13804578781128</v>
       </c>
       <c r="H155" t="n">
         <v>30000</v>
@@ -5328,7 +5328,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G171" t="n">
-        <v>1.13804590702057</v>
+        <v>1.13804578781128</v>
       </c>
       <c r="H171" t="n">
         <v>9000</v>
@@ -5386,7 +5386,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G173" t="n">
-        <v>1.18637990951538</v>
+        <v>1.18638002872467</v>
       </c>
       <c r="H173" t="n">
         <v>85500</v>
@@ -5560,7 +5560,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G179" t="n">
-        <v>1.33577597141266</v>
+        <v>1.33577585220337</v>
       </c>
       <c r="H179" t="n">
         <v>48000</v>
@@ -5589,7 +5589,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G180" t="n">
-        <v>1.3489578962326</v>
+        <v>1.34895801544189</v>
       </c>
       <c r="H180" t="n">
         <v>9000</v>
@@ -5618,7 +5618,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G181" t="n">
-        <v>1.33577597141266</v>
+        <v>1.33577585220337</v>
       </c>
       <c r="H181" t="n">
         <v>24000</v>
@@ -5792,7 +5792,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G187" t="n">
-        <v>1.30062389373779</v>
+        <v>1.30062401294708</v>
       </c>
       <c r="H187" t="n">
         <v>25500</v>
@@ -5821,7 +5821,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G188" t="n">
-        <v>1.3489578962326</v>
+        <v>1.34895801544189</v>
       </c>
       <c r="H188" t="n">
         <v>36000</v>
@@ -5850,7 +5850,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G189" t="n">
-        <v>1.45001995563507</v>
+        <v>1.45001983642578</v>
       </c>
       <c r="H189" t="n">
         <v>148500</v>
@@ -5908,7 +5908,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G191" t="n">
-        <v>1.38410997390747</v>
+        <v>1.38410985469818</v>
       </c>
       <c r="H191" t="n">
         <v>34500</v>
@@ -5966,7 +5966,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G193" t="n">
-        <v>1.3489578962326</v>
+        <v>1.34895801544189</v>
       </c>
       <c r="H193" t="n">
         <v>34500</v>
@@ -5995,7 +5995,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G194" t="n">
-        <v>1.34016990661621</v>
+        <v>1.34016978740692</v>
       </c>
       <c r="H194" t="n">
         <v>85500</v>
@@ -6024,7 +6024,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G195" t="n">
-        <v>1.34456384181976</v>
+        <v>1.34456372261047</v>
       </c>
       <c r="H195" t="n">
         <v>18000</v>
@@ -6111,7 +6111,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G198" t="n">
-        <v>1.32698798179626</v>
+        <v>1.32698786258698</v>
       </c>
       <c r="H198" t="n">
         <v>13500</v>
@@ -6169,7 +6169,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G200" t="n">
-        <v>1.3489578962326</v>
+        <v>1.34895801544189</v>
       </c>
       <c r="H200" t="n">
         <v>22500</v>
@@ -6314,7 +6314,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G205" t="n">
-        <v>1.33577597141266</v>
+        <v>1.33577585220337</v>
       </c>
       <c r="H205" t="n">
         <v>4500</v>
@@ -6343,7 +6343,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G206" t="n">
-        <v>1.34456384181976</v>
+        <v>1.34456372261047</v>
       </c>
       <c r="H206" t="n">
         <v>18000</v>
@@ -6372,7 +6372,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G207" t="n">
-        <v>1.34456384181976</v>
+        <v>1.34456372261047</v>
       </c>
       <c r="H207" t="n">
         <v>4500</v>
@@ -6401,7 +6401,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G208" t="n">
-        <v>1.35335183143616</v>
+        <v>1.35335195064545</v>
       </c>
       <c r="H208" t="n">
         <v>1500</v>
@@ -6430,7 +6430,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G209" t="n">
-        <v>1.35335183143616</v>
+        <v>1.35335195064545</v>
       </c>
       <c r="H209" t="n">
         <v>0</v>
@@ -6459,7 +6459,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G210" t="n">
-        <v>1.35335183143616</v>
+        <v>1.35335195064545</v>
       </c>
       <c r="H210" t="n">
         <v>0</v>
@@ -6488,7 +6488,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G211" t="n">
-        <v>1.2918359041214</v>
+        <v>1.29183602333069</v>
       </c>
       <c r="H211" t="n">
         <v>45000</v>
@@ -6517,7 +6517,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G212" t="n">
-        <v>1.3094117641449</v>
+        <v>1.30941188335419</v>
       </c>
       <c r="H212" t="n">
         <v>4500</v>
@@ -6546,7 +6546,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G213" t="n">
-        <v>1.30062389373779</v>
+        <v>1.30062401294708</v>
       </c>
       <c r="H213" t="n">
         <v>6000</v>
@@ -6575,7 +6575,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G214" t="n">
-        <v>1.3489578962326</v>
+        <v>1.34895801544189</v>
       </c>
       <c r="H214" t="n">
         <v>28500</v>
@@ -6604,7 +6604,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G215" t="n">
-        <v>1.32698798179626</v>
+        <v>1.32698786258698</v>
       </c>
       <c r="H215" t="n">
         <v>13500</v>
@@ -6662,7 +6662,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G217" t="n">
-        <v>1.3094117641449</v>
+        <v>1.30941188335419</v>
       </c>
       <c r="H217" t="n">
         <v>10500</v>
@@ -6807,7 +6807,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G222" t="n">
-        <v>1.2918359041214</v>
+        <v>1.29183602333069</v>
       </c>
       <c r="H222" t="n">
         <v>9000</v>
@@ -6836,7 +6836,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G223" t="n">
-        <v>1.3094117641449</v>
+        <v>1.30941188335419</v>
       </c>
       <c r="H223" t="n">
         <v>6000</v>
@@ -6923,7 +6923,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G226" t="n">
-        <v>1.30062389373779</v>
+        <v>1.30062401294708</v>
       </c>
       <c r="H226" t="n">
         <v>4500</v>
@@ -6981,7 +6981,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G228" t="n">
-        <v>1.2918359041214</v>
+        <v>1.29183602333069</v>
       </c>
       <c r="H228" t="n">
         <v>27000</v>
@@ -7097,7 +7097,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G232" t="n">
-        <v>1.34456384181976</v>
+        <v>1.34456372261047</v>
       </c>
       <c r="H232" t="n">
         <v>45000</v>
@@ -7126,7 +7126,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G233" t="n">
-        <v>1.34016990661621</v>
+        <v>1.34016978740692</v>
       </c>
       <c r="H233" t="n">
         <v>61500</v>
@@ -7184,7 +7184,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G235" t="n">
-        <v>1.34456384181976</v>
+        <v>1.34456372261047</v>
       </c>
       <c r="H235" t="n">
         <v>13500</v>
@@ -7213,7 +7213,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G236" t="n">
-        <v>1.3489578962326</v>
+        <v>1.34895801544189</v>
       </c>
       <c r="H236" t="n">
         <v>13500</v>
@@ -7271,7 +7271,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G238" t="n">
-        <v>1.3665337562561</v>
+        <v>1.36653387546539</v>
       </c>
       <c r="H238" t="n">
         <v>34500</v>
@@ -7300,7 +7300,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G239" t="n">
-        <v>1.34016990661621</v>
+        <v>1.34016978740692</v>
       </c>
       <c r="H239" t="n">
         <v>69000</v>
@@ -7358,7 +7358,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G241" t="n">
-        <v>2.24972772598267</v>
+        <v>2.24972748756409</v>
       </c>
       <c r="H241" t="n">
         <v>774000</v>
@@ -7416,7 +7416,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G243" t="n">
-        <v>2.23215174674988</v>
+        <v>2.2321515083313</v>
       </c>
       <c r="H243" t="n">
         <v>702000</v>
@@ -7445,7 +7445,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G244" t="n">
-        <v>2.52215576171875</v>
+        <v>2.52215552330017</v>
       </c>
       <c r="H244" t="n">
         <v>1464000</v>
@@ -7503,7 +7503,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G246" t="n">
-        <v>2.27609181404114</v>
+        <v>2.27609157562256</v>
       </c>
       <c r="H246" t="n">
         <v>229500</v>
@@ -7532,7 +7532,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G247" t="n">
-        <v>2.17063570022583</v>
+        <v>2.17063593864441</v>
       </c>
       <c r="H247" t="n">
         <v>265500</v>
@@ -7561,7 +7561,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G248" t="n">
-        <v>2.27609181404114</v>
+        <v>2.27609157562256</v>
       </c>
       <c r="H248" t="n">
         <v>240000</v>
@@ -7619,7 +7619,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G250" t="n">
-        <v>2.23215174674988</v>
+        <v>2.2321515083313</v>
       </c>
       <c r="H250" t="n">
         <v>102000</v>
@@ -7851,7 +7851,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G258" t="n">
-        <v>2.28487968444824</v>
+        <v>2.28487992286682</v>
       </c>
       <c r="H258" t="n">
         <v>138000</v>
@@ -7967,7 +7967,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G262" t="n">
-        <v>2.24972772598267</v>
+        <v>2.24972748756409</v>
       </c>
       <c r="H262" t="n">
         <v>33000</v>
@@ -8112,7 +8112,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G267" t="n">
-        <v>2.27609181404114</v>
+        <v>2.27609157562256</v>
       </c>
       <c r="H267" t="n">
         <v>61500</v>
@@ -8199,7 +8199,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G270" t="n">
-        <v>2.23215174674988</v>
+        <v>2.2321515083313</v>
       </c>
       <c r="H270" t="n">
         <v>97500</v>
@@ -8257,7 +8257,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G272" t="n">
-        <v>2.17063570022583</v>
+        <v>2.17063593864441</v>
       </c>
       <c r="H272" t="n">
         <v>42000</v>
@@ -8286,7 +8286,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G273" t="n">
-        <v>2.27609181404114</v>
+        <v>2.27609157562256</v>
       </c>
       <c r="H273" t="n">
         <v>94500</v>
@@ -8315,7 +8315,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G274" t="n">
-        <v>2.24972772598267</v>
+        <v>2.24972748756409</v>
       </c>
       <c r="H274" t="n">
         <v>45000</v>
@@ -8344,7 +8344,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G275" t="n">
-        <v>2.28487968444824</v>
+        <v>2.28487992286682</v>
       </c>
       <c r="H275" t="n">
         <v>18000</v>
@@ -8373,7 +8373,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G276" t="n">
-        <v>2.28487968444824</v>
+        <v>2.28487992286682</v>
       </c>
       <c r="H276" t="n">
         <v>6000</v>
@@ -8402,7 +8402,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G277" t="n">
-        <v>2.30245566368103</v>
+        <v>2.30245590209961</v>
       </c>
       <c r="H277" t="n">
         <v>18000</v>
@@ -8489,7 +8489,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G280" t="n">
-        <v>2.28487968444824</v>
+        <v>2.28487992286682</v>
       </c>
       <c r="H280" t="n">
         <v>16500</v>
@@ -8547,7 +8547,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G282" t="n">
-        <v>2.30245566368103</v>
+        <v>2.30245590209961</v>
       </c>
       <c r="H282" t="n">
         <v>4500</v>
@@ -8634,7 +8634,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G285" t="n">
-        <v>2.27609181404114</v>
+        <v>2.27609157562256</v>
       </c>
       <c r="H285" t="n">
         <v>24000</v>
@@ -8808,7 +8808,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G291" t="n">
-        <v>2.27609181404114</v>
+        <v>2.27609157562256</v>
       </c>
       <c r="H291" t="n">
         <v>18000</v>
@@ -8866,7 +8866,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G293" t="n">
-        <v>2.24972772598267</v>
+        <v>2.24972748756409</v>
       </c>
       <c r="H293" t="n">
         <v>1500</v>
@@ -8895,7 +8895,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G294" t="n">
-        <v>2.28487968444824</v>
+        <v>2.28487992286682</v>
       </c>
       <c r="H294" t="n">
         <v>1500</v>
@@ -8953,7 +8953,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G296" t="n">
-        <v>2.23215174674988</v>
+        <v>2.2321515083313</v>
       </c>
       <c r="H296" t="n">
         <v>7500</v>
@@ -9185,7 +9185,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G304" t="n">
-        <v>2.03881573677063</v>
+        <v>2.03881597518921</v>
       </c>
       <c r="H304" t="n">
         <v>51000</v>
@@ -9359,7 +9359,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G310" t="n">
-        <v>1.83669173717499</v>
+        <v>1.83669185638428</v>
       </c>
       <c r="H310" t="n">
         <v>82500</v>
@@ -9417,7 +9417,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G312" t="n">
-        <v>1.82790374755859</v>
+        <v>1.82790386676788</v>
       </c>
       <c r="H312" t="n">
         <v>37500</v>
@@ -9852,7 +9852,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G327" t="n">
-        <v>1.9157840013504</v>
+        <v>1.91578376293182</v>
       </c>
       <c r="H327" t="n">
         <v>24000</v>
@@ -9939,7 +9939,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G330" t="n">
-        <v>2.0300281047821</v>
+        <v>2.03002786636353</v>
       </c>
       <c r="H330" t="n">
         <v>4500</v>
@@ -10055,7 +10055,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G334" t="n">
-        <v>2.03881573677063</v>
+        <v>2.03881597518921</v>
       </c>
       <c r="H334" t="n">
         <v>7500</v>
@@ -10171,7 +10171,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G338" t="n">
-        <v>2.05639171600342</v>
+        <v>2.056391954422</v>
       </c>
       <c r="H338" t="n">
         <v>3000</v>
@@ -10229,7 +10229,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G340" t="n">
-        <v>2.03881573677063</v>
+        <v>2.03881597518921</v>
       </c>
       <c r="H340" t="n">
         <v>3000</v>
@@ -10548,7 +10548,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G351" t="n">
-        <v>1.83669173717499</v>
+        <v>1.83669185638428</v>
       </c>
       <c r="H351" t="n">
         <v>10500</v>
@@ -10577,7 +10577,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G352" t="n">
-        <v>1.81032776832581</v>
+        <v>1.81032764911652</v>
       </c>
       <c r="H352" t="n">
         <v>10500</v>
@@ -10664,7 +10664,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G355" t="n">
-        <v>1.92457175254822</v>
+        <v>1.9245719909668</v>
       </c>
       <c r="H355" t="n">
         <v>13500</v>
@@ -10751,7 +10751,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G358" t="n">
-        <v>2.03881573677063</v>
+        <v>2.03881597518921</v>
       </c>
       <c r="H358" t="n">
         <v>10500</v>
@@ -10780,7 +10780,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G359" t="n">
-        <v>2.0300281047821</v>
+        <v>2.03002786636353</v>
       </c>
       <c r="H359" t="n">
         <v>7500</v>
@@ -10809,7 +10809,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G360" t="n">
-        <v>2.0300281047821</v>
+        <v>2.03002786636353</v>
       </c>
       <c r="H360" t="n">
         <v>0</v>
@@ -11070,7 +11070,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G369" t="n">
-        <v>1.98608791828156</v>
+        <v>1.98608767986298</v>
       </c>
       <c r="H369" t="n">
         <v>25500</v>
@@ -11157,7 +11157,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G372" t="n">
-        <v>1.98608791828156</v>
+        <v>1.98608767986298</v>
       </c>
       <c r="H372" t="n">
         <v>7500</v>
@@ -11273,7 +11273,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G376" t="n">
-        <v>1.88063168525696</v>
+        <v>1.88063192367554</v>
       </c>
       <c r="H376" t="n">
         <v>9000</v>
@@ -11302,7 +11302,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G377" t="n">
-        <v>1.88063168525696</v>
+        <v>1.88063192367554</v>
       </c>
       <c r="H377" t="n">
         <v>3000</v>
@@ -11389,7 +11389,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G380" t="n">
-        <v>1.62577986717224</v>
+        <v>1.62577998638153</v>
       </c>
       <c r="H380" t="n">
         <v>43500</v>
@@ -11476,7 +11476,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G383" t="n">
-        <v>1.86305558681488</v>
+        <v>1.86305570602417</v>
       </c>
       <c r="H383" t="n">
         <v>21000</v>
@@ -11505,7 +11505,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G384" t="n">
-        <v>1.86305558681488</v>
+        <v>1.86305570602417</v>
       </c>
       <c r="H384" t="n">
         <v>1500</v>
@@ -11534,7 +11534,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G385" t="n">
-        <v>1.88063168525696</v>
+        <v>1.88063192367554</v>
       </c>
       <c r="H385" t="n">
         <v>13500</v>
@@ -11737,7 +11737,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G392" t="n">
-        <v>1.98608791828156</v>
+        <v>1.98608767986298</v>
       </c>
       <c r="H392" t="n">
         <v>6000</v>
@@ -11766,7 +11766,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G393" t="n">
-        <v>1.98608791828156</v>
+        <v>1.98608767986298</v>
       </c>
       <c r="H393" t="n">
         <v>0</v>
@@ -11795,7 +11795,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G394" t="n">
-        <v>1.92457175254822</v>
+        <v>1.9245719909668</v>
       </c>
       <c r="H394" t="n">
         <v>12000</v>
@@ -11911,7 +11911,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G398" t="n">
-        <v>2.05639171600342</v>
+        <v>2.056391954422</v>
       </c>
       <c r="H398" t="n">
         <v>10500</v>
@@ -11940,7 +11940,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G399" t="n">
-        <v>1.98608791828156</v>
+        <v>1.98608767986298</v>
       </c>
       <c r="H399" t="n">
         <v>6000</v>
@@ -12027,7 +12027,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G402" t="n">
-        <v>2.05639171600342</v>
+        <v>2.056391954422</v>
       </c>
       <c r="H402" t="n">
         <v>36000</v>
@@ -12114,7 +12114,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G405" t="n">
-        <v>1.98608791828156</v>
+        <v>1.98608767986298</v>
       </c>
       <c r="H405" t="n">
         <v>16500</v>
@@ -12143,7 +12143,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G406" t="n">
-        <v>1.98608791828156</v>
+        <v>1.98608767986298</v>
       </c>
       <c r="H406" t="n">
         <v>0</v>
@@ -12172,7 +12172,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G407" t="n">
-        <v>1.84547972679138</v>
+        <v>1.84547984600067</v>
       </c>
       <c r="H407" t="n">
         <v>64500</v>
@@ -12317,7 +12317,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G412" t="n">
-        <v>1.88063168525696</v>
+        <v>1.88063192367554</v>
       </c>
       <c r="H412" t="n">
         <v>9000</v>
@@ -12346,7 +12346,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G413" t="n">
-        <v>1.88063168525696</v>
+        <v>1.88063192367554</v>
       </c>
       <c r="H413" t="n">
         <v>0</v>
@@ -12375,7 +12375,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G414" t="n">
-        <v>1.83669173717499</v>
+        <v>1.83669185638428</v>
       </c>
       <c r="H414" t="n">
         <v>1500</v>
@@ -12462,7 +12462,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G417" t="n">
-        <v>1.86305558681488</v>
+        <v>1.86305570602417</v>
       </c>
       <c r="H417" t="n">
         <v>6000</v>
@@ -12491,7 +12491,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G418" t="n">
-        <v>1.81032776832581</v>
+        <v>1.81032764911652</v>
       </c>
       <c r="H418" t="n">
         <v>6000</v>
@@ -12520,7 +12520,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G419" t="n">
-        <v>1.9157840013504</v>
+        <v>1.91578376293182</v>
       </c>
       <c r="H419" t="n">
         <v>18000</v>
@@ -12578,7 +12578,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G421" t="n">
-        <v>1.9157840013504</v>
+        <v>1.91578376293182</v>
       </c>
       <c r="H421" t="n">
         <v>1500</v>
@@ -12868,7 +12868,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G431" t="n">
-        <v>1.84547972679138</v>
+        <v>1.84547984600067</v>
       </c>
       <c r="H431" t="n">
         <v>6000</v>
@@ -12926,7 +12926,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G433" t="n">
-        <v>1.86305558681488</v>
+        <v>1.86305570602417</v>
       </c>
       <c r="H433" t="n">
         <v>7500</v>
@@ -12955,7 +12955,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G434" t="n">
-        <v>1.86305558681488</v>
+        <v>1.86305570602417</v>
       </c>
       <c r="H434" t="n">
         <v>0</v>
@@ -12984,7 +12984,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G435" t="n">
-        <v>1.86305558681488</v>
+        <v>1.86305570602417</v>
       </c>
       <c r="H435" t="n">
         <v>3000</v>
@@ -13013,7 +13013,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G436" t="n">
-        <v>1.88063168525696</v>
+        <v>1.88063192367554</v>
       </c>
       <c r="H436" t="n">
         <v>3000</v>
@@ -13158,7 +13158,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G441" t="n">
-        <v>1.88063168525696</v>
+        <v>1.88063192367554</v>
       </c>
       <c r="H441" t="n">
         <v>3000</v>
@@ -13187,7 +13187,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G442" t="n">
-        <v>1.88063168525696</v>
+        <v>1.88063192367554</v>
       </c>
       <c r="H442" t="n">
         <v>0</v>
@@ -13216,7 +13216,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G443" t="n">
-        <v>1.82790374755859</v>
+        <v>1.82790386676788</v>
       </c>
       <c r="H443" t="n">
         <v>4500</v>
@@ -13245,7 +13245,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G444" t="n">
-        <v>1.86305558681488</v>
+        <v>1.86305570602417</v>
       </c>
       <c r="H444" t="n">
         <v>1500</v>
@@ -13274,7 +13274,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G445" t="n">
-        <v>1.82790374755859</v>
+        <v>1.82790386676788</v>
       </c>
       <c r="H445" t="n">
         <v>1500</v>
@@ -13303,7 +13303,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G446" t="n">
-        <v>1.82790374755859</v>
+        <v>1.82790386676788</v>
       </c>
       <c r="H446" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G448" t="n">
-        <v>1.73562979698181</v>
+        <v>1.7356299161911</v>
       </c>
       <c r="H448" t="n">
         <v>3000</v>
@@ -13709,7 +13709,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G460" t="n">
-        <v>1.67411386966705</v>
+        <v>1.67411375045776</v>
       </c>
       <c r="H460" t="n">
         <v>1500</v>
@@ -13738,7 +13738,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G461" t="n">
-        <v>1.67411386966705</v>
+        <v>1.67411375045776</v>
       </c>
       <c r="H461" t="n">
         <v>6000</v>
@@ -13767,7 +13767,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G462" t="n">
-        <v>1.67411386966705</v>
+        <v>1.67411375045776</v>
       </c>
       <c r="H462" t="n">
         <v>1500</v>
@@ -13883,7 +13883,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G466" t="n">
-        <v>1.59941601753235</v>
+        <v>1.59941589832306</v>
       </c>
       <c r="H466" t="n">
         <v>6000</v>
@@ -14144,7 +14144,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G475" t="n">
-        <v>1.63456785678864</v>
+        <v>1.63456797599792</v>
       </c>
       <c r="H475" t="n">
         <v>3000</v>
@@ -14173,7 +14173,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G476" t="n">
-        <v>1.66532588005066</v>
+        <v>1.66532576084137</v>
       </c>
       <c r="H476" t="n">
         <v>1500</v>
@@ -14202,7 +14202,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G477" t="n">
-        <v>1.66532588005066</v>
+        <v>1.66532576084137</v>
       </c>
       <c r="H477" t="n">
         <v>0</v>
@@ -14231,7 +14231,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G478" t="n">
-        <v>1.66532588005066</v>
+        <v>1.66532576084137</v>
       </c>
       <c r="H478" t="n">
         <v>0</v>
@@ -14289,7 +14289,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G480" t="n">
-        <v>1.63017380237579</v>
+        <v>1.63017392158508</v>
       </c>
       <c r="H480" t="n">
         <v>3000</v>
@@ -14347,7 +14347,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G482" t="n">
-        <v>1.67411386966705</v>
+        <v>1.67411375045776</v>
       </c>
       <c r="H482" t="n">
         <v>4500</v>
@@ -14434,7 +14434,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G485" t="n">
-        <v>1.81032776832581</v>
+        <v>1.81032764911652</v>
       </c>
       <c r="H485" t="n">
         <v>6000</v>
@@ -14521,7 +14521,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G488" t="n">
-        <v>1.92457175254822</v>
+        <v>1.9245719909668</v>
       </c>
       <c r="H488" t="n">
         <v>34500</v>
@@ -14579,7 +14579,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G490" t="n">
-        <v>2.03881573677063</v>
+        <v>2.03881597518921</v>
       </c>
       <c r="H490" t="n">
         <v>28500</v>
@@ -14608,7 +14608,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G491" t="n">
-        <v>2.03881573677063</v>
+        <v>2.03881597518921</v>
       </c>
       <c r="H491" t="n">
         <v>0</v>
@@ -14782,7 +14782,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G497" t="n">
-        <v>1.82790374755859</v>
+        <v>1.82790386676788</v>
       </c>
       <c r="H497" t="n">
         <v>21000</v>
@@ -14811,7 +14811,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G498" t="n">
-        <v>1.73562979698181</v>
+        <v>1.7356299161911</v>
       </c>
       <c r="H498" t="n">
         <v>40500</v>
@@ -15246,7 +15246,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G513" t="n">
-        <v>1.81032776832581</v>
+        <v>1.81032764911652</v>
       </c>
       <c r="H513" t="n">
         <v>3000</v>
@@ -15449,7 +15449,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G520" t="n">
-        <v>1.79275178909302</v>
+        <v>1.79275190830231</v>
       </c>
       <c r="H520" t="n">
         <v>4500</v>
@@ -15478,7 +15478,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G521" t="n">
-        <v>1.81032776832581</v>
+        <v>1.81032764911652</v>
       </c>
       <c r="H521" t="n">
         <v>4500</v>
@@ -15594,7 +15594,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G525" t="n">
-        <v>1.62577986717224</v>
+        <v>1.62577998638153</v>
       </c>
       <c r="H525" t="n">
         <v>6000</v>
@@ -15623,7 +15623,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G526" t="n">
-        <v>1.54229390621185</v>
+        <v>1.54229378700256</v>
       </c>
       <c r="H526" t="n">
         <v>19500</v>
@@ -15739,7 +15739,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G530" t="n">
-        <v>1.48517203330994</v>
+        <v>1.48517191410065</v>
       </c>
       <c r="H530" t="n">
         <v>7500</v>
@@ -15855,7 +15855,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G534" t="n">
-        <v>1.48517203330994</v>
+        <v>1.48517191410065</v>
       </c>
       <c r="H534" t="n">
         <v>1500</v>
@@ -15884,7 +15884,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G535" t="n">
-        <v>1.48517203330994</v>
+        <v>1.48517191410065</v>
       </c>
       <c r="H535" t="n">
         <v>0</v>
@@ -15971,7 +15971,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G538" t="n">
-        <v>1.55108177661896</v>
+        <v>1.55108165740967</v>
       </c>
       <c r="H538" t="n">
         <v>1500</v>
@@ -16000,7 +16000,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G539" t="n">
-        <v>1.55108177661896</v>
+        <v>1.55108165740967</v>
       </c>
       <c r="H539" t="n">
         <v>0</v>
@@ -16029,7 +16029,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G540" t="n">
-        <v>1.51153588294983</v>
+        <v>1.51153600215912</v>
       </c>
       <c r="H540" t="n">
         <v>7500</v>
@@ -16058,7 +16058,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G541" t="n">
-        <v>1.51153588294983</v>
+        <v>1.51153600215912</v>
       </c>
       <c r="H541" t="n">
         <v>0</v>
@@ -16087,7 +16087,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G542" t="n">
-        <v>1.51153588294983</v>
+        <v>1.51153600215912</v>
       </c>
       <c r="H542" t="n">
         <v>0</v>
@@ -16783,7 +16783,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G566" t="n">
-        <v>1.62577986717224</v>
+        <v>1.62577998638153</v>
       </c>
       <c r="H566" t="n">
         <v>4500</v>
@@ -16812,7 +16812,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G567" t="n">
-        <v>1.62577986717224</v>
+        <v>1.62577998638153</v>
       </c>
       <c r="H567" t="n">
         <v>0</v>
@@ -16841,7 +16841,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G568" t="n">
-        <v>1.62577986717224</v>
+        <v>1.62577998638153</v>
       </c>
       <c r="H568" t="n">
         <v>0</v>
@@ -16957,7 +16957,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G572" t="n">
-        <v>1.67411386966705</v>
+        <v>1.67411375045776</v>
       </c>
       <c r="H572" t="n">
         <v>1500</v>
@@ -17305,7 +17305,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G584" t="n">
-        <v>1.62577986717224</v>
+        <v>1.62577998638153</v>
       </c>
       <c r="H584" t="n">
         <v>1500</v>
@@ -17334,7 +17334,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G585" t="n">
-        <v>1.62577986717224</v>
+        <v>1.62577998638153</v>
       </c>
       <c r="H585" t="n">
         <v>0</v>
@@ -17363,7 +17363,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G586" t="n">
-        <v>1.62577986717224</v>
+        <v>1.62577998638153</v>
       </c>
       <c r="H586" t="n">
         <v>0</v>
@@ -17392,7 +17392,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G587" t="n">
-        <v>1.62577986717224</v>
+        <v>1.62577998638153</v>
       </c>
       <c r="H587" t="n">
         <v>1500</v>
@@ -17421,7 +17421,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G588" t="n">
-        <v>1.62577986717224</v>
+        <v>1.62577998638153</v>
       </c>
       <c r="H588" t="n">
         <v>0</v>
@@ -17450,7 +17450,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G589" t="n">
-        <v>1.62577986717224</v>
+        <v>1.62577998638153</v>
       </c>
       <c r="H589" t="n">
         <v>1500</v>
@@ -17537,7 +17537,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G592" t="n">
-        <v>1.61699187755585</v>
+        <v>1.61699175834656</v>
       </c>
       <c r="H592" t="n">
         <v>6000</v>
@@ -17566,7 +17566,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G593" t="n">
-        <v>1.55547571182251</v>
+        <v>1.5554758310318</v>
       </c>
       <c r="H593" t="n">
         <v>13500</v>
@@ -17682,7 +17682,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G597" t="n">
-        <v>1.61699187755585</v>
+        <v>1.61699175834656</v>
       </c>
       <c r="H597" t="n">
         <v>15000</v>
@@ -17769,7 +17769,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G600" t="n">
-        <v>1.59941601753235</v>
+        <v>1.59941589832306</v>
       </c>
       <c r="H600" t="n">
         <v>3000</v>
@@ -17798,7 +17798,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G601" t="n">
-        <v>1.59941601753235</v>
+        <v>1.59941589832306</v>
       </c>
       <c r="H601" t="n">
         <v>0</v>
@@ -17827,7 +17827,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G602" t="n">
-        <v>1.59941601753235</v>
+        <v>1.59941589832306</v>
       </c>
       <c r="H602" t="n">
         <v>0</v>
@@ -17972,7 +17972,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G607" t="n">
-        <v>1.61699187755585</v>
+        <v>1.61699175834656</v>
       </c>
       <c r="H607" t="n">
         <v>3000</v>
@@ -18117,7 +18117,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G612" t="n">
-        <v>1.60820388793945</v>
+        <v>1.60820376873016</v>
       </c>
       <c r="H612" t="n">
         <v>1500</v>
@@ -18233,7 +18233,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G616" t="n">
-        <v>1.56865775585175</v>
+        <v>1.56865787506104</v>
       </c>
       <c r="H616" t="n">
         <v>7500</v>
@@ -18320,7 +18320,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G619" t="n">
-        <v>1.72244787216187</v>
+        <v>1.72244775295258</v>
       </c>
       <c r="H619" t="n">
         <v>10500</v>
@@ -18610,7 +18610,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G629" t="n">
-        <v>1.88063168525696</v>
+        <v>1.88063192367554</v>
       </c>
       <c r="H629" t="n">
         <v>39000</v>
@@ -18668,7 +18668,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G631" t="n">
-        <v>1.81032776832581</v>
+        <v>1.81032764911652</v>
       </c>
       <c r="H631" t="n">
         <v>24000</v>
@@ -18697,7 +18697,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G632" t="n">
-        <v>1.86305558681488</v>
+        <v>1.86305570602417</v>
       </c>
       <c r="H632" t="n">
         <v>33000</v>
@@ -18755,7 +18755,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G634" t="n">
-        <v>1.81032776832581</v>
+        <v>1.81032764911652</v>
       </c>
       <c r="H634" t="n">
         <v>21000</v>
@@ -18929,7 +18929,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G640" t="n">
-        <v>1.60820388793945</v>
+        <v>1.60820376873016</v>
       </c>
       <c r="H640" t="n">
         <v>33000</v>
@@ -18958,7 +18958,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G641" t="n">
-        <v>1.62577986717224</v>
+        <v>1.62577998638153</v>
       </c>
       <c r="H641" t="n">
         <v>1500</v>
@@ -19132,7 +19132,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G647" t="n">
-        <v>1.66532588005066</v>
+        <v>1.66532576084137</v>
       </c>
       <c r="H647" t="n">
         <v>7500</v>
@@ -19451,7 +19451,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G658" t="n">
-        <v>1.79275178909302</v>
+        <v>1.79275190830231</v>
       </c>
       <c r="H658" t="n">
         <v>108000</v>
@@ -19654,7 +19654,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G665" t="n">
-        <v>1.67888343334198</v>
+        <v>1.67888355255127</v>
       </c>
       <c r="H665" t="n">
         <v>13500</v>
@@ -19741,7 +19741,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G668" t="n">
-        <v>1.67888343334198</v>
+        <v>1.67888355255127</v>
       </c>
       <c r="H668" t="n">
         <v>4500</v>
@@ -19770,7 +19770,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G669" t="n">
-        <v>1.66985726356506</v>
+        <v>1.66985738277435</v>
       </c>
       <c r="H669" t="n">
         <v>3000</v>
@@ -19799,7 +19799,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G670" t="n">
-        <v>1.66083109378815</v>
+        <v>1.66083097457886</v>
       </c>
       <c r="H670" t="n">
         <v>30000</v>
@@ -19886,7 +19886,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G673" t="n">
-        <v>1.64277863502502</v>
+        <v>1.64277851581573</v>
       </c>
       <c r="H673" t="n">
         <v>4500</v>
@@ -19915,7 +19915,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G674" t="n">
-        <v>1.64277863502502</v>
+        <v>1.64277851581573</v>
       </c>
       <c r="H674" t="n">
         <v>0</v>
@@ -19944,7 +19944,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G675" t="n">
-        <v>1.64277863502502</v>
+        <v>1.64277851581573</v>
       </c>
       <c r="H675" t="n">
         <v>0</v>
@@ -19973,7 +19973,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G676" t="n">
-        <v>1.64277863502502</v>
+        <v>1.64277851581573</v>
       </c>
       <c r="H676" t="n">
         <v>0</v>
@@ -20205,7 +20205,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G684" t="n">
-        <v>1.5976470708847</v>
+        <v>1.59764719009399</v>
       </c>
       <c r="H684" t="n">
         <v>1500</v>
@@ -20698,7 +20698,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G701" t="n">
-        <v>1.5976470708847</v>
+        <v>1.59764719009399</v>
       </c>
       <c r="H701" t="n">
         <v>1500</v>
@@ -20727,7 +20727,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G702" t="n">
-        <v>1.5976470708847</v>
+        <v>1.59764719009399</v>
       </c>
       <c r="H702" t="n">
         <v>3000</v>
@@ -20756,7 +20756,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G703" t="n">
-        <v>1.5976470708847</v>
+        <v>1.59764719009399</v>
       </c>
       <c r="H703" t="n">
         <v>4500</v>
@@ -20785,7 +20785,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G704" t="n">
-        <v>1.5976470708847</v>
+        <v>1.59764719009399</v>
       </c>
       <c r="H704" t="n">
         <v>0</v>
@@ -20843,7 +20843,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G706" t="n">
-        <v>1.5976470708847</v>
+        <v>1.59764719009399</v>
       </c>
       <c r="H706" t="n">
         <v>7500</v>
@@ -21626,7 +21626,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G733" t="n">
-        <v>1.55251586437225</v>
+        <v>1.55251598358154</v>
       </c>
       <c r="H733" t="n">
         <v>1500</v>
@@ -21655,7 +21655,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G734" t="n">
-        <v>1.55251586437225</v>
+        <v>1.55251598358154</v>
       </c>
       <c r="H734" t="n">
         <v>6000</v>
@@ -21684,7 +21684,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G735" t="n">
-        <v>1.55251586437225</v>
+        <v>1.55251598358154</v>
       </c>
       <c r="H735" t="n">
         <v>0</v>
@@ -21713,7 +21713,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G736" t="n">
-        <v>1.55251586437225</v>
+        <v>1.55251598358154</v>
       </c>
       <c r="H736" t="n">
         <v>0</v>
@@ -21771,7 +21771,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G738" t="n">
-        <v>1.52543723583221</v>
+        <v>1.52543711662292</v>
       </c>
       <c r="H738" t="n">
         <v>7500</v>
@@ -21800,7 +21800,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G739" t="n">
-        <v>1.52543723583221</v>
+        <v>1.52543711662292</v>
       </c>
       <c r="H739" t="n">
         <v>0</v>
@@ -21829,7 +21829,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G740" t="n">
-        <v>1.52543723583221</v>
+        <v>1.52543711662292</v>
       </c>
       <c r="H740" t="n">
         <v>0</v>
@@ -22235,7 +22235,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G754" t="n">
-        <v>1.46225333213806</v>
+        <v>1.46225345134735</v>
       </c>
       <c r="H754" t="n">
         <v>15000</v>
@@ -22612,7 +22612,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G767" t="n">
-        <v>1.48933219909668</v>
+        <v>1.48933207988739</v>
       </c>
       <c r="H767" t="n">
         <v>15000</v>
@@ -22844,7 +22844,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G775" t="n">
-        <v>1.48933219909668</v>
+        <v>1.48933207988739</v>
       </c>
       <c r="H775" t="n">
         <v>3000</v>
@@ -22931,7 +22931,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G778" t="n">
-        <v>1.48933219909668</v>
+        <v>1.48933207988739</v>
       </c>
       <c r="H778" t="n">
         <v>4500</v>
@@ -23076,7 +23076,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G783" t="n">
-        <v>1.46225333213806</v>
+        <v>1.46225345134735</v>
       </c>
       <c r="H783" t="n">
         <v>15000</v>
@@ -23424,7 +23424,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G795" t="n">
-        <v>1.87746095657349</v>
+        <v>1.87746107578278</v>
       </c>
       <c r="H795" t="n">
         <v>319500</v>
@@ -23453,7 +23453,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G796" t="n">
-        <v>1.66985726356506</v>
+        <v>1.66985738277435</v>
       </c>
       <c r="H796" t="n">
         <v>94500</v>
@@ -23627,7 +23627,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G802" t="n">
-        <v>1.84135603904724</v>
+        <v>1.84135615825653</v>
       </c>
       <c r="H802" t="n">
         <v>37500</v>
@@ -23656,7 +23656,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G803" t="n">
-        <v>1.93161857128143</v>
+        <v>1.93161880970001</v>
       </c>
       <c r="H803" t="n">
         <v>73500</v>
@@ -23685,7 +23685,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G804" t="n">
-        <v>1.87746095657349</v>
+        <v>1.87746107578278</v>
       </c>
       <c r="H804" t="n">
         <v>46500</v>
@@ -23714,7 +23714,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G805" t="n">
-        <v>1.85940849781036</v>
+        <v>1.85940837860107</v>
       </c>
       <c r="H805" t="n">
         <v>4500</v>
@@ -23743,7 +23743,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G806" t="n">
-        <v>1.8955135345459</v>
+        <v>1.89551365375519</v>
       </c>
       <c r="H806" t="n">
         <v>9000</v>
@@ -23772,7 +23772,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G807" t="n">
-        <v>1.85940849781036</v>
+        <v>1.85940837860107</v>
       </c>
       <c r="H807" t="n">
         <v>7500</v>
@@ -23801,7 +23801,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G808" t="n">
-        <v>1.87746095657349</v>
+        <v>1.87746107578278</v>
       </c>
       <c r="H808" t="n">
         <v>10500</v>
@@ -23830,7 +23830,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G809" t="n">
-        <v>1.85940849781036</v>
+        <v>1.85940837860107</v>
       </c>
       <c r="H809" t="n">
         <v>1500</v>
@@ -23859,7 +23859,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G810" t="n">
-        <v>1.85940849781036</v>
+        <v>1.85940837860107</v>
       </c>
       <c r="H810" t="n">
         <v>1500</v>
@@ -23888,7 +23888,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G811" t="n">
-        <v>1.84135603904724</v>
+        <v>1.84135615825653</v>
       </c>
       <c r="H811" t="n">
         <v>6000</v>
@@ -23917,7 +23917,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G812" t="n">
-        <v>1.87746095657349</v>
+        <v>1.87746107578278</v>
       </c>
       <c r="H812" t="n">
         <v>6000</v>
@@ -23946,7 +23946,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G813" t="n">
-        <v>1.91356599330902</v>
+        <v>1.91356611251831</v>
       </c>
       <c r="H813" t="n">
         <v>3000</v>
@@ -23975,7 +23975,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G814" t="n">
-        <v>1.87746095657349</v>
+        <v>1.87746107578278</v>
       </c>
       <c r="H814" t="n">
         <v>7500</v>
@@ -24120,7 +24120,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G819" t="n">
-        <v>1.76914620399475</v>
+        <v>1.76914608478546</v>
       </c>
       <c r="H819" t="n">
         <v>12000</v>
@@ -24149,7 +24149,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G820" t="n">
-        <v>1.76914620399475</v>
+        <v>1.76914608478546</v>
       </c>
       <c r="H820" t="n">
         <v>0</v>
@@ -24236,7 +24236,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G823" t="n">
-        <v>1.84135603904724</v>
+        <v>1.84135615825653</v>
       </c>
       <c r="H823" t="n">
         <v>15000</v>
@@ -24584,7 +24584,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G835" t="n">
-        <v>1.76914620399475</v>
+        <v>1.76914608478546</v>
       </c>
       <c r="H835" t="n">
         <v>7500</v>
@@ -25135,7 +25135,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G854" t="n">
-        <v>1.76914620399475</v>
+        <v>1.76914608478546</v>
       </c>
       <c r="H854" t="n">
         <v>1500</v>
@@ -25454,7 +25454,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G865" t="n">
-        <v>1.84135603904724</v>
+        <v>1.84135615825653</v>
       </c>
       <c r="H865" t="n">
         <v>48000</v>
@@ -25483,7 +25483,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G866" t="n">
-        <v>1.87746095657349</v>
+        <v>1.87746107578278</v>
       </c>
       <c r="H866" t="n">
         <v>7500</v>
@@ -25512,7 +25512,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G867" t="n">
-        <v>1.91356599330902</v>
+        <v>1.91356611251831</v>
       </c>
       <c r="H867" t="n">
         <v>21000</v>
@@ -25831,7 +25831,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G878" t="n">
-        <v>1.93161857128143</v>
+        <v>1.93161880970001</v>
       </c>
       <c r="H878" t="n">
         <v>12000</v>
@@ -26324,7 +26324,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G895" t="n">
-        <v>1.85940849781036</v>
+        <v>1.85940837860107</v>
       </c>
       <c r="H895" t="n">
         <v>126000</v>
@@ -26382,7 +26382,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G897" t="n">
-        <v>1.91356599330902</v>
+        <v>1.91356611251831</v>
       </c>
       <c r="H897" t="n">
         <v>54000</v>
@@ -26411,7 +26411,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G898" t="n">
-        <v>1.87746095657349</v>
+        <v>1.87746107578278</v>
       </c>
       <c r="H898" t="n">
         <v>15000</v>
@@ -26440,7 +26440,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G899" t="n">
-        <v>1.85940849781036</v>
+        <v>1.85940837860107</v>
       </c>
       <c r="H899" t="n">
         <v>16500</v>
@@ -26469,7 +26469,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G900" t="n">
-        <v>1.87746095657349</v>
+        <v>1.87746107578278</v>
       </c>
       <c r="H900" t="n">
         <v>12000</v>
@@ -26498,7 +26498,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G901" t="n">
-        <v>1.85940849781036</v>
+        <v>1.85940837860107</v>
       </c>
       <c r="H901" t="n">
         <v>4500</v>
@@ -26527,7 +26527,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G902" t="n">
-        <v>1.93161857128143</v>
+        <v>1.93161880970001</v>
       </c>
       <c r="H902" t="n">
         <v>9000</v>
@@ -26556,7 +26556,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G903" t="n">
-        <v>1.91356599330902</v>
+        <v>1.91356611251831</v>
       </c>
       <c r="H903" t="n">
         <v>4500</v>
@@ -26585,7 +26585,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G904" t="n">
-        <v>1.93161857128143</v>
+        <v>1.93161880970001</v>
       </c>
       <c r="H904" t="n">
         <v>9000</v>
@@ -26643,7 +26643,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G906" t="n">
-        <v>1.91356599330902</v>
+        <v>1.91356611251831</v>
       </c>
       <c r="H906" t="n">
         <v>7500</v>
@@ -26672,7 +26672,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G907" t="n">
-        <v>1.93161857128143</v>
+        <v>1.93161880970001</v>
       </c>
       <c r="H907" t="n">
         <v>1500</v>
@@ -26701,7 +26701,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G908" t="n">
-        <v>1.93161857128143</v>
+        <v>1.93161880970001</v>
       </c>
       <c r="H908" t="n">
         <v>0</v>
@@ -26730,7 +26730,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G909" t="n">
-        <v>1.85940849781036</v>
+        <v>1.85940837860107</v>
       </c>
       <c r="H909" t="n">
         <v>111000</v>
@@ -26759,7 +26759,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G910" t="n">
-        <v>1.84135603904724</v>
+        <v>1.84135615825653</v>
       </c>
       <c r="H910" t="n">
         <v>21000</v>
@@ -26788,7 +26788,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G911" t="n">
-        <v>1.87746095657349</v>
+        <v>1.87746107578278</v>
       </c>
       <c r="H911" t="n">
         <v>9000</v>
@@ -26817,7 +26817,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G912" t="n">
-        <v>1.85940849781036</v>
+        <v>1.85940837860107</v>
       </c>
       <c r="H912" t="n">
         <v>15000</v>
@@ -26846,7 +26846,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G913" t="n">
-        <v>1.85940849781036</v>
+        <v>1.85940837860107</v>
       </c>
       <c r="H913" t="n">
         <v>6000</v>
@@ -26875,7 +26875,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G914" t="n">
-        <v>1.8955135345459</v>
+        <v>1.89551365375519</v>
       </c>
       <c r="H914" t="n">
         <v>7500</v>
@@ -26904,7 +26904,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G915" t="n">
-        <v>1.87746095657349</v>
+        <v>1.87746107578278</v>
       </c>
       <c r="H915" t="n">
         <v>10500</v>
@@ -26933,7 +26933,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G916" t="n">
-        <v>1.87746095657349</v>
+        <v>1.87746107578278</v>
       </c>
       <c r="H916" t="n">
         <v>1500</v>
@@ -26962,7 +26962,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G917" t="n">
-        <v>1.85940849781036</v>
+        <v>1.85940837860107</v>
       </c>
       <c r="H917" t="n">
         <v>13500</v>
@@ -45528,6 +45528,35 @@
         <v>3000</v>
       </c>
       <c r="I1557" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1558">
+      <c r="A1558" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1558" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1558" t="n">
+        <v>1.52999997138977</v>
+      </c>
+      <c r="D1558" t="n">
+        <v>1.52999997138977</v>
+      </c>
+      <c r="E1558" t="n">
+        <v>1.50999999046326</v>
+      </c>
+      <c r="F1558" t="n">
+        <v>1.50999999046326</v>
+      </c>
+      <c r="G1558" t="n">
+        <v>1.50999999046326</v>
+      </c>
+      <c r="H1558" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I1558" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RETI.MI.xlsx
+++ b/data/RETI.MI.xlsx
@@ -427,7 +427,7 @@
         <v>0.889900028705597</v>
       </c>
       <c r="G2" t="n">
-        <v>0.75985848903656</v>
+        <v>0.759858429431915</v>
       </c>
       <c r="H2" t="n">
         <v>856500</v>
@@ -572,7 +572,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G7" t="n">
-        <v>0.74969744682312</v>
+        <v>0.749697387218475</v>
       </c>
       <c r="H7" t="n">
         <v>139500</v>
@@ -659,7 +659,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G10" t="n">
-        <v>0.722373604774475</v>
+        <v>0.72237354516983</v>
       </c>
       <c r="H10" t="n">
         <v>48000</v>
@@ -717,7 +717,7 @@
         <v>0.814000010490417</v>
       </c>
       <c r="G12" t="n">
-        <v>0.695049643516541</v>
+        <v>0.695049703121185</v>
       </c>
       <c r="H12" t="n">
         <v>63000</v>
@@ -891,7 +891,7 @@
         <v>0.833999991416931</v>
       </c>
       <c r="G18" t="n">
-        <v>0.712127149105072</v>
+        <v>0.712127089500427</v>
       </c>
       <c r="H18" t="n">
         <v>579000</v>
@@ -920,7 +920,7 @@
         <v>0.814000010490417</v>
       </c>
       <c r="G19" t="n">
-        <v>0.695049643516541</v>
+        <v>0.695049703121185</v>
       </c>
       <c r="H19" t="n">
         <v>265500</v>
@@ -1007,7 +1007,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G22" t="n">
-        <v>0.659187257289886</v>
+        <v>0.659187197685242</v>
       </c>
       <c r="H22" t="n">
         <v>24000</v>
@@ -1094,7 +1094,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G25" t="n">
-        <v>0.660894930362701</v>
+        <v>0.660894989967346</v>
       </c>
       <c r="H25" t="n">
         <v>12000</v>
@@ -1152,7 +1152,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G27" t="n">
-        <v>0.633571147918701</v>
+        <v>0.633571088314056</v>
       </c>
       <c r="H27" t="n">
         <v>43500</v>
@@ -1239,7 +1239,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G30" t="n">
-        <v>0.607955098152161</v>
+        <v>0.607955038547516</v>
       </c>
       <c r="H30" t="n">
         <v>19500</v>
@@ -1268,7 +1268,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G31" t="n">
-        <v>0.587462186813354</v>
+        <v>0.587462246417999</v>
       </c>
       <c r="H31" t="n">
         <v>78000</v>
@@ -1297,7 +1297,7 @@
         <v>0.73199999332428</v>
       </c>
       <c r="G32" t="n">
-        <v>0.625032424926758</v>
+        <v>0.625032484531403</v>
       </c>
       <c r="H32" t="n">
         <v>27000</v>
@@ -1384,7 +1384,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G35" t="n">
-        <v>0.580631256103516</v>
+        <v>0.580631196498871</v>
       </c>
       <c r="H35" t="n">
         <v>12000</v>
@@ -1413,7 +1413,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G36" t="n">
-        <v>0.563553810119629</v>
+        <v>0.563553869724274</v>
       </c>
       <c r="H36" t="n">
         <v>66000</v>
@@ -1587,7 +1587,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G42" t="n">
-        <v>0.604539513587952</v>
+        <v>0.604539573192596</v>
       </c>
       <c r="H42" t="n">
         <v>127500</v>
@@ -1645,7 +1645,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G44" t="n">
-        <v>0.604539513587952</v>
+        <v>0.604539573192596</v>
       </c>
       <c r="H44" t="n">
         <v>64500</v>
@@ -1674,7 +1674,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G45" t="n">
-        <v>0.618201494216919</v>
+        <v>0.618201434612274</v>
       </c>
       <c r="H45" t="n">
         <v>18000</v>
@@ -1732,7 +1732,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G47" t="n">
-        <v>0.607955098152161</v>
+        <v>0.607955038547516</v>
       </c>
       <c r="H47" t="n">
         <v>7500</v>
@@ -1790,7 +1790,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G49" t="n">
-        <v>0.614786028862</v>
+        <v>0.614785969257355</v>
       </c>
       <c r="H49" t="n">
         <v>18000</v>
@@ -1848,7 +1848,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G51" t="n">
-        <v>0.614786028862</v>
+        <v>0.614785969257355</v>
       </c>
       <c r="H51" t="n">
         <v>22500</v>
@@ -1877,7 +1877,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G52" t="n">
-        <v>0.705296099185944</v>
+        <v>0.705296158790588</v>
       </c>
       <c r="H52" t="n">
         <v>157500</v>
@@ -1906,7 +1906,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G53" t="n">
-        <v>0.701880693435669</v>
+        <v>0.701880633831024</v>
       </c>
       <c r="H53" t="n">
         <v>70500</v>
@@ -2022,7 +2022,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G57" t="n">
-        <v>0.705296099185944</v>
+        <v>0.705296158790588</v>
       </c>
       <c r="H57" t="n">
         <v>25500</v>
@@ -2486,7 +2486,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G73" t="n">
-        <v>0.705296099185944</v>
+        <v>0.705296158790588</v>
       </c>
       <c r="H73" t="n">
         <v>19500</v>
@@ -2544,7 +2544,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G75" t="n">
-        <v>0.700172901153564</v>
+        <v>0.700172960758209</v>
       </c>
       <c r="H75" t="n">
         <v>73500</v>
@@ -2602,7 +2602,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G77" t="n">
-        <v>0.700172901153564</v>
+        <v>0.700172960758209</v>
       </c>
       <c r="H77" t="n">
         <v>22500</v>
@@ -2631,7 +2631,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G78" t="n">
-        <v>0.700172901153564</v>
+        <v>0.700172960758209</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
@@ -2660,7 +2660,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G79" t="n">
-        <v>0.705296099185944</v>
+        <v>0.705296158790588</v>
       </c>
       <c r="H79" t="n">
         <v>3000</v>
@@ -2689,7 +2689,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G80" t="n">
-        <v>0.717250347137451</v>
+        <v>0.717250287532806</v>
       </c>
       <c r="H80" t="n">
         <v>28500</v>
@@ -2718,7 +2718,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G81" t="n">
-        <v>0.708711683750153</v>
+        <v>0.708711624145508</v>
       </c>
       <c r="H81" t="n">
         <v>22500</v>
@@ -2747,7 +2747,7 @@
         <v>0.833999991416931</v>
       </c>
       <c r="G82" t="n">
-        <v>0.712127149105072</v>
+        <v>0.712127089500427</v>
       </c>
       <c r="H82" t="n">
         <v>4500</v>
@@ -2776,7 +2776,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G83" t="n">
-        <v>0.715542614459991</v>
+        <v>0.715542554855347</v>
       </c>
       <c r="H83" t="n">
         <v>1500</v>
@@ -2805,7 +2805,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G84" t="n">
-        <v>0.717250347137451</v>
+        <v>0.717250287532806</v>
       </c>
       <c r="H84" t="n">
         <v>1500</v>
@@ -2834,7 +2834,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G85" t="n">
-        <v>0.715542614459991</v>
+        <v>0.715542554855347</v>
       </c>
       <c r="H85" t="n">
         <v>9000</v>
@@ -2863,7 +2863,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G86" t="n">
-        <v>0.700172901153564</v>
+        <v>0.700172960758209</v>
       </c>
       <c r="H86" t="n">
         <v>1500</v>
@@ -2921,7 +2921,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G88" t="n">
-        <v>0.700172901153564</v>
+        <v>0.700172960758209</v>
       </c>
       <c r="H88" t="n">
         <v>16500</v>
@@ -2950,7 +2950,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G89" t="n">
-        <v>0.684803247451782</v>
+        <v>0.684803307056427</v>
       </c>
       <c r="H89" t="n">
         <v>22500</v>
@@ -2979,7 +2979,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G90" t="n">
-        <v>0.684803247451782</v>
+        <v>0.684803307056427</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -3008,7 +3008,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G91" t="n">
-        <v>0.701880693435669</v>
+        <v>0.701880633831024</v>
       </c>
       <c r="H91" t="n">
         <v>10500</v>
@@ -3037,7 +3037,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G92" t="n">
-        <v>0.701880693435669</v>
+        <v>0.701880633831024</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
@@ -3066,7 +3066,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G93" t="n">
-        <v>0.701880693435669</v>
+        <v>0.701880633831024</v>
       </c>
       <c r="H93" t="n">
         <v>1500</v>
@@ -3501,7 +3501,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G108" t="n">
-        <v>0.700172901153564</v>
+        <v>0.700172960758209</v>
       </c>
       <c r="H108" t="n">
         <v>55500</v>
@@ -3675,7 +3675,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G114" t="n">
-        <v>0.700172901153564</v>
+        <v>0.700172960758209</v>
       </c>
       <c r="H114" t="n">
         <v>21000</v>
@@ -3733,7 +3733,7 @@
         <v>0.86599999666214</v>
       </c>
       <c r="G116" t="n">
-        <v>0.739450871944427</v>
+        <v>0.739450931549072</v>
       </c>
       <c r="H116" t="n">
         <v>108000</v>
@@ -3762,7 +3762,7 @@
         <v>0.842000007629395</v>
       </c>
       <c r="G117" t="n">
-        <v>0.718958020210266</v>
+        <v>0.718958079814911</v>
       </c>
       <c r="H117" t="n">
         <v>102000</v>
@@ -3791,7 +3791,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G118" t="n">
-        <v>0.717250347137451</v>
+        <v>0.717250287532806</v>
       </c>
       <c r="H118" t="n">
         <v>69000</v>
@@ -3820,7 +3820,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G119" t="n">
-        <v>0.715542614459991</v>
+        <v>0.715542554855347</v>
       </c>
       <c r="H119" t="n">
         <v>16500</v>
@@ -3849,7 +3849,7 @@
         <v>0.867999970912933</v>
       </c>
       <c r="G120" t="n">
-        <v>0.741158664226532</v>
+        <v>0.741158723831177</v>
       </c>
       <c r="H120" t="n">
         <v>139500</v>
@@ -3878,7 +3878,7 @@
         <v>0.867999970912933</v>
       </c>
       <c r="G121" t="n">
-        <v>0.741158664226532</v>
+        <v>0.741158723831177</v>
       </c>
       <c r="H121" t="n">
         <v>151500</v>
@@ -3936,7 +3936,7 @@
         <v>0.972000002861023</v>
       </c>
       <c r="G123" t="n">
-        <v>0.829961121082306</v>
+        <v>0.829961061477661</v>
       </c>
       <c r="H123" t="n">
         <v>922500</v>
@@ -4052,7 +4052,7 @@
         <v>1</v>
       </c>
       <c r="G127" t="n">
-        <v>0.853869378566742</v>
+        <v>0.853869438171387</v>
       </c>
       <c r="H127" t="n">
         <v>66000</v>
@@ -4081,7 +4081,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G128" t="n">
-        <v>0.862408101558685</v>
+        <v>0.86240816116333</v>
       </c>
       <c r="H128" t="n">
         <v>60000</v>
@@ -4110,7 +4110,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G129" t="n">
-        <v>0.862408101558685</v>
+        <v>0.86240816116333</v>
       </c>
       <c r="H129" t="n">
         <v>25500</v>
@@ -4139,7 +4139,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G130" t="n">
-        <v>0.862408101558685</v>
+        <v>0.86240816116333</v>
       </c>
       <c r="H130" t="n">
         <v>72000</v>
@@ -4197,7 +4197,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G132" t="n">
-        <v>0.845330774784088</v>
+        <v>0.845330715179443</v>
       </c>
       <c r="H132" t="n">
         <v>25500</v>
@@ -4255,7 +4255,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G134" t="n">
-        <v>0.8752161860466</v>
+        <v>0.875216126441956</v>
       </c>
       <c r="H134" t="n">
         <v>19500</v>
@@ -4342,7 +4342,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G137" t="n">
-        <v>0.888024210929871</v>
+        <v>0.888024151325226</v>
       </c>
       <c r="H137" t="n">
         <v>33000</v>
@@ -4400,7 +4400,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G139" t="n">
-        <v>0.913640379905701</v>
+        <v>0.913640320301056</v>
       </c>
       <c r="H139" t="n">
         <v>4500</v>
@@ -4487,7 +4487,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G142" t="n">
-        <v>0.913640379905701</v>
+        <v>0.913640320301056</v>
       </c>
       <c r="H142" t="n">
         <v>42000</v>
@@ -4516,7 +4516,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G143" t="n">
-        <v>0.930717706680298</v>
+        <v>0.930717647075653</v>
       </c>
       <c r="H143" t="n">
         <v>45000</v>
@@ -4777,7 +4777,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G152" t="n">
-        <v>1.22153186798096</v>
+        <v>1.22153174877167</v>
       </c>
       <c r="H152" t="n">
         <v>57000</v>
@@ -4806,7 +4806,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G153" t="n">
-        <v>1.22153186798096</v>
+        <v>1.22153174877167</v>
       </c>
       <c r="H153" t="n">
         <v>157500</v>
@@ -4835,7 +4835,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G154" t="n">
-        <v>1.17759191989899</v>
+        <v>1.1775918006897</v>
       </c>
       <c r="H154" t="n">
         <v>31500</v>
@@ -4864,7 +4864,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G155" t="n">
-        <v>1.13804578781128</v>
+        <v>1.13804590702057</v>
       </c>
       <c r="H155" t="n">
         <v>30000</v>
@@ -4922,7 +4922,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G157" t="n">
-        <v>1.13365185260773</v>
+        <v>1.13365197181702</v>
       </c>
       <c r="H157" t="n">
         <v>46500</v>
@@ -5009,7 +5009,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G160" t="n">
-        <v>1.05455982685089</v>
+        <v>1.05455994606018</v>
       </c>
       <c r="H160" t="n">
         <v>49500</v>
@@ -5096,7 +5096,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G163" t="n">
-        <v>1.13365185260773</v>
+        <v>1.13365197181702</v>
       </c>
       <c r="H163" t="n">
         <v>21000</v>
@@ -5154,7 +5154,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G165" t="n">
-        <v>1.16880393028259</v>
+        <v>1.1688038110733</v>
       </c>
       <c r="H165" t="n">
         <v>52500</v>
@@ -5212,7 +5212,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G167" t="n">
-        <v>1.17759191989899</v>
+        <v>1.1775918006897</v>
       </c>
       <c r="H167" t="n">
         <v>12000</v>
@@ -5328,7 +5328,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G171" t="n">
-        <v>1.13804578781128</v>
+        <v>1.13804590702057</v>
       </c>
       <c r="H171" t="n">
         <v>9000</v>
@@ -5415,7 +5415,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G174" t="n">
-        <v>1.18198597431183</v>
+        <v>1.18198585510254</v>
       </c>
       <c r="H174" t="n">
         <v>24000</v>
@@ -5444,7 +5444,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G175" t="n">
-        <v>1.23031973838806</v>
+        <v>1.23031985759735</v>
       </c>
       <c r="H175" t="n">
         <v>234000</v>
@@ -5531,7 +5531,7 @@
         <v>1.49500000476837</v>
       </c>
       <c r="G178" t="n">
-        <v>1.31380593776703</v>
+        <v>1.31380581855774</v>
       </c>
       <c r="H178" t="n">
         <v>75000</v>
@@ -5589,7 +5589,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G180" t="n">
-        <v>1.34895801544189</v>
+        <v>1.3489578962326</v>
       </c>
       <c r="H180" t="n">
         <v>9000</v>
@@ -5792,7 +5792,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G187" t="n">
-        <v>1.30062401294708</v>
+        <v>1.30062389373779</v>
       </c>
       <c r="H187" t="n">
         <v>25500</v>
@@ -5821,7 +5821,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G188" t="n">
-        <v>1.34895801544189</v>
+        <v>1.3489578962326</v>
       </c>
       <c r="H188" t="n">
         <v>36000</v>
@@ -5908,7 +5908,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G191" t="n">
-        <v>1.38410985469818</v>
+        <v>1.38410997390747</v>
       </c>
       <c r="H191" t="n">
         <v>34500</v>
@@ -5937,7 +5937,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G192" t="n">
-        <v>1.37971580028534</v>
+        <v>1.37971591949463</v>
       </c>
       <c r="H192" t="n">
         <v>87000</v>
@@ -5966,7 +5966,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G193" t="n">
-        <v>1.34895801544189</v>
+        <v>1.3489578962326</v>
       </c>
       <c r="H193" t="n">
         <v>34500</v>
@@ -6024,7 +6024,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G195" t="n">
-        <v>1.34456372261047</v>
+        <v>1.34456384181976</v>
       </c>
       <c r="H195" t="n">
         <v>18000</v>
@@ -6111,7 +6111,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G198" t="n">
-        <v>1.32698786258698</v>
+        <v>1.32698774337769</v>
       </c>
       <c r="H198" t="n">
         <v>13500</v>
@@ -6140,7 +6140,7 @@
         <v>1.49500000476837</v>
       </c>
       <c r="G199" t="n">
-        <v>1.31380593776703</v>
+        <v>1.31380581855774</v>
       </c>
       <c r="H199" t="n">
         <v>18000</v>
@@ -6169,7 +6169,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G200" t="n">
-        <v>1.34895801544189</v>
+        <v>1.3489578962326</v>
       </c>
       <c r="H200" t="n">
         <v>22500</v>
@@ -6343,7 +6343,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G206" t="n">
-        <v>1.34456372261047</v>
+        <v>1.34456384181976</v>
       </c>
       <c r="H206" t="n">
         <v>18000</v>
@@ -6372,7 +6372,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G207" t="n">
-        <v>1.34456372261047</v>
+        <v>1.34456384181976</v>
       </c>
       <c r="H207" t="n">
         <v>4500</v>
@@ -6401,7 +6401,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G208" t="n">
-        <v>1.35335195064545</v>
+        <v>1.35335183143616</v>
       </c>
       <c r="H208" t="n">
         <v>1500</v>
@@ -6430,7 +6430,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G209" t="n">
-        <v>1.35335195064545</v>
+        <v>1.35335183143616</v>
       </c>
       <c r="H209" t="n">
         <v>0</v>
@@ -6459,7 +6459,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G210" t="n">
-        <v>1.35335195064545</v>
+        <v>1.35335183143616</v>
       </c>
       <c r="H210" t="n">
         <v>0</v>
@@ -6546,7 +6546,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G213" t="n">
-        <v>1.30062401294708</v>
+        <v>1.30062389373779</v>
       </c>
       <c r="H213" t="n">
         <v>6000</v>
@@ -6575,7 +6575,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G214" t="n">
-        <v>1.34895801544189</v>
+        <v>1.3489578962326</v>
       </c>
       <c r="H214" t="n">
         <v>28500</v>
@@ -6604,7 +6604,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G215" t="n">
-        <v>1.32698786258698</v>
+        <v>1.32698774337769</v>
       </c>
       <c r="H215" t="n">
         <v>13500</v>
@@ -6720,7 +6720,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G219" t="n">
-        <v>1.23031973838806</v>
+        <v>1.23031985759735</v>
       </c>
       <c r="H219" t="n">
         <v>70500</v>
@@ -6923,7 +6923,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G226" t="n">
-        <v>1.30062401294708</v>
+        <v>1.30062389373779</v>
       </c>
       <c r="H226" t="n">
         <v>4500</v>
@@ -7097,7 +7097,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G232" t="n">
-        <v>1.34456372261047</v>
+        <v>1.34456384181976</v>
       </c>
       <c r="H232" t="n">
         <v>45000</v>
@@ -7155,7 +7155,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G234" t="n">
-        <v>1.36213994026184</v>
+        <v>1.36213982105255</v>
       </c>
       <c r="H234" t="n">
         <v>22500</v>
@@ -7184,7 +7184,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G235" t="n">
-        <v>1.34456372261047</v>
+        <v>1.34456384181976</v>
       </c>
       <c r="H235" t="n">
         <v>13500</v>
@@ -7213,7 +7213,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G236" t="n">
-        <v>1.34895801544189</v>
+        <v>1.3489578962326</v>
       </c>
       <c r="H236" t="n">
         <v>13500</v>
@@ -7242,7 +7242,7 @@
         <v>1.49500000476837</v>
       </c>
       <c r="G237" t="n">
-        <v>1.31380593776703</v>
+        <v>1.31380581855774</v>
       </c>
       <c r="H237" t="n">
         <v>28500</v>
@@ -7271,7 +7271,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G238" t="n">
-        <v>1.36653387546539</v>
+        <v>1.3665337562561</v>
       </c>
       <c r="H238" t="n">
         <v>34500</v>
@@ -7329,7 +7329,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G240" t="n">
-        <v>1.74881184101105</v>
+        <v>1.74881172180176</v>
       </c>
       <c r="H240" t="n">
         <v>333000</v>
@@ -7358,7 +7358,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G241" t="n">
-        <v>2.24972748756409</v>
+        <v>2.24972772598267</v>
       </c>
       <c r="H241" t="n">
         <v>774000</v>
@@ -7503,7 +7503,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G246" t="n">
-        <v>2.27609157562256</v>
+        <v>2.27609181404114</v>
       </c>
       <c r="H246" t="n">
         <v>229500</v>
@@ -7532,7 +7532,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G247" t="n">
-        <v>2.17063593864441</v>
+        <v>2.17063570022583</v>
       </c>
       <c r="H247" t="n">
         <v>265500</v>
@@ -7561,7 +7561,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G248" t="n">
-        <v>2.27609157562256</v>
+        <v>2.27609181404114</v>
       </c>
       <c r="H248" t="n">
         <v>240000</v>
@@ -7706,7 +7706,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G253" t="n">
-        <v>2.32881999015808</v>
+        <v>2.3288197517395</v>
       </c>
       <c r="H253" t="n">
         <v>237000</v>
@@ -7764,7 +7764,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G255" t="n">
-        <v>2.33760786056519</v>
+        <v>2.33760762214661</v>
       </c>
       <c r="H255" t="n">
         <v>108000</v>
@@ -7793,7 +7793,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G256" t="n">
-        <v>2.32881999015808</v>
+        <v>2.3288197517395</v>
       </c>
       <c r="H256" t="n">
         <v>75000</v>
@@ -7822,7 +7822,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G257" t="n">
-        <v>2.35518383979797</v>
+        <v>2.35518360137939</v>
       </c>
       <c r="H257" t="n">
         <v>30000</v>
@@ -7851,7 +7851,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G258" t="n">
-        <v>2.28487992286682</v>
+        <v>2.28487968444824</v>
       </c>
       <c r="H258" t="n">
         <v>138000</v>
@@ -7967,7 +7967,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G262" t="n">
-        <v>2.24972748756409</v>
+        <v>2.24972772598267</v>
       </c>
       <c r="H262" t="n">
         <v>33000</v>
@@ -8083,7 +8083,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G266" t="n">
-        <v>2.35518383979797</v>
+        <v>2.35518360137939</v>
       </c>
       <c r="H266" t="n">
         <v>60000</v>
@@ -8112,7 +8112,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G267" t="n">
-        <v>2.27609157562256</v>
+        <v>2.27609181404114</v>
       </c>
       <c r="H267" t="n">
         <v>61500</v>
@@ -8170,7 +8170,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G269" t="n">
-        <v>2.31124401092529</v>
+        <v>2.31124377250671</v>
       </c>
       <c r="H269" t="n">
         <v>54000</v>
@@ -8257,7 +8257,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G272" t="n">
-        <v>2.17063593864441</v>
+        <v>2.17063570022583</v>
       </c>
       <c r="H272" t="n">
         <v>42000</v>
@@ -8286,7 +8286,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G273" t="n">
-        <v>2.27609157562256</v>
+        <v>2.27609181404114</v>
       </c>
       <c r="H273" t="n">
         <v>94500</v>
@@ -8315,7 +8315,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G274" t="n">
-        <v>2.24972748756409</v>
+        <v>2.24972772598267</v>
       </c>
       <c r="H274" t="n">
         <v>45000</v>
@@ -8344,7 +8344,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G275" t="n">
-        <v>2.28487992286682</v>
+        <v>2.28487968444824</v>
       </c>
       <c r="H275" t="n">
         <v>18000</v>
@@ -8373,7 +8373,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G276" t="n">
-        <v>2.28487992286682</v>
+        <v>2.28487968444824</v>
       </c>
       <c r="H276" t="n">
         <v>6000</v>
@@ -8402,7 +8402,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G277" t="n">
-        <v>2.30245590209961</v>
+        <v>2.30245566368103</v>
       </c>
       <c r="H277" t="n">
         <v>18000</v>
@@ -8431,7 +8431,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G278" t="n">
-        <v>2.32881999015808</v>
+        <v>2.3288197517395</v>
       </c>
       <c r="H278" t="n">
         <v>33000</v>
@@ -8489,7 +8489,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G280" t="n">
-        <v>2.28487992286682</v>
+        <v>2.28487968444824</v>
       </c>
       <c r="H280" t="n">
         <v>16500</v>
@@ -8518,7 +8518,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G281" t="n">
-        <v>2.32881999015808</v>
+        <v>2.3288197517395</v>
       </c>
       <c r="H281" t="n">
         <v>25500</v>
@@ -8547,7 +8547,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G282" t="n">
-        <v>2.30245590209961</v>
+        <v>2.30245566368103</v>
       </c>
       <c r="H282" t="n">
         <v>4500</v>
@@ -8634,7 +8634,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G285" t="n">
-        <v>2.27609157562256</v>
+        <v>2.27609181404114</v>
       </c>
       <c r="H285" t="n">
         <v>24000</v>
@@ -8663,7 +8663,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G286" t="n">
-        <v>2.26730370521545</v>
+        <v>2.26730394363403</v>
       </c>
       <c r="H286" t="n">
         <v>28500</v>
@@ -8808,7 +8808,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G291" t="n">
-        <v>2.27609157562256</v>
+        <v>2.27609181404114</v>
       </c>
       <c r="H291" t="n">
         <v>18000</v>
@@ -8866,7 +8866,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G293" t="n">
-        <v>2.24972748756409</v>
+        <v>2.24972772598267</v>
       </c>
       <c r="H293" t="n">
         <v>1500</v>
@@ -8895,7 +8895,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G294" t="n">
-        <v>2.28487992286682</v>
+        <v>2.28487968444824</v>
       </c>
       <c r="H294" t="n">
         <v>1500</v>
@@ -8924,7 +8924,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G295" t="n">
-        <v>2.26730370521545</v>
+        <v>2.26730394363403</v>
       </c>
       <c r="H295" t="n">
         <v>30000</v>
@@ -9156,7 +9156,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G303" t="n">
-        <v>2.07396793365479</v>
+        <v>2.07396769523621</v>
       </c>
       <c r="H303" t="n">
         <v>58500</v>
@@ -9243,7 +9243,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G306" t="n">
-        <v>1.99487566947937</v>
+        <v>1.99487578868866</v>
       </c>
       <c r="H306" t="n">
         <v>13500</v>
@@ -9301,7 +9301,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G308" t="n">
-        <v>2.02123975753784</v>
+        <v>2.02123951911926</v>
       </c>
       <c r="H308" t="n">
         <v>12000</v>
@@ -9330,7 +9330,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G309" t="n">
-        <v>1.93335998058319</v>
+        <v>1.9333598613739</v>
       </c>
       <c r="H309" t="n">
         <v>18000</v>
@@ -9359,7 +9359,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G310" t="n">
-        <v>1.83669185638428</v>
+        <v>1.83669173717499</v>
       </c>
       <c r="H310" t="n">
         <v>82500</v>
@@ -9417,7 +9417,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G312" t="n">
-        <v>1.82790386676788</v>
+        <v>1.82790374755859</v>
       </c>
       <c r="H312" t="n">
         <v>37500</v>
@@ -9446,7 +9446,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G313" t="n">
-        <v>1.93335998058319</v>
+        <v>1.9333598613739</v>
       </c>
       <c r="H313" t="n">
         <v>18000</v>
@@ -9475,7 +9475,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G314" t="n">
-        <v>1.93335998058319</v>
+        <v>1.9333598613739</v>
       </c>
       <c r="H314" t="n">
         <v>6000</v>
@@ -9562,7 +9562,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G317" t="n">
-        <v>2.07396793365479</v>
+        <v>2.07396769523621</v>
       </c>
       <c r="H317" t="n">
         <v>12000</v>
@@ -9591,7 +9591,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G318" t="n">
-        <v>2.09154367446899</v>
+        <v>2.09154391288757</v>
       </c>
       <c r="H318" t="n">
         <v>12000</v>
@@ -9794,7 +9794,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G325" t="n">
-        <v>1.94214797019958</v>
+        <v>1.94214773178101</v>
       </c>
       <c r="H325" t="n">
         <v>7500</v>
@@ -9968,7 +9968,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G331" t="n">
-        <v>1.99487566947937</v>
+        <v>1.99487578868866</v>
       </c>
       <c r="H331" t="n">
         <v>12000</v>
@@ -9997,7 +9997,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G332" t="n">
-        <v>1.99487566947937</v>
+        <v>1.99487578868866</v>
       </c>
       <c r="H332" t="n">
         <v>7500</v>
@@ -10026,7 +10026,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G333" t="n">
-        <v>1.99487566947937</v>
+        <v>1.99487578868866</v>
       </c>
       <c r="H333" t="n">
         <v>6000</v>
@@ -10113,7 +10113,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G336" t="n">
-        <v>2.02123975753784</v>
+        <v>2.02123951911926</v>
       </c>
       <c r="H336" t="n">
         <v>10500</v>
@@ -10142,7 +10142,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G337" t="n">
-        <v>2.10911965370178</v>
+        <v>2.10911989212036</v>
       </c>
       <c r="H337" t="n">
         <v>9000</v>
@@ -10345,7 +10345,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G344" t="n">
-        <v>1.95972383022308</v>
+        <v>1.95972371101379</v>
       </c>
       <c r="H344" t="n">
         <v>27000</v>
@@ -10374,7 +10374,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G345" t="n">
-        <v>2.01245188713074</v>
+        <v>2.01245164871216</v>
       </c>
       <c r="H345" t="n">
         <v>4500</v>
@@ -10432,7 +10432,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G347" t="n">
-        <v>1.96851181983948</v>
+        <v>1.9685115814209</v>
       </c>
       <c r="H347" t="n">
         <v>15000</v>
@@ -10461,7 +10461,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G348" t="n">
-        <v>1.93335998058319</v>
+        <v>1.9333598613739</v>
       </c>
       <c r="H348" t="n">
         <v>1500</v>
@@ -10490,7 +10490,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G349" t="n">
-        <v>1.90699589252472</v>
+        <v>1.90699577331543</v>
       </c>
       <c r="H349" t="n">
         <v>7500</v>
@@ -10519,7 +10519,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G350" t="n">
-        <v>1.90699589252472</v>
+        <v>1.90699577331543</v>
       </c>
       <c r="H350" t="n">
         <v>4500</v>
@@ -10548,7 +10548,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G351" t="n">
-        <v>1.83669185638428</v>
+        <v>1.83669173717499</v>
       </c>
       <c r="H351" t="n">
         <v>10500</v>
@@ -10693,7 +10693,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G356" t="n">
-        <v>2.01245188713074</v>
+        <v>2.01245164871216</v>
       </c>
       <c r="H356" t="n">
         <v>19500</v>
@@ -10838,7 +10838,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G361" t="n">
-        <v>1.99487566947937</v>
+        <v>1.99487578868866</v>
       </c>
       <c r="H361" t="n">
         <v>15000</v>
@@ -10867,7 +10867,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G362" t="n">
-        <v>1.99487566947937</v>
+        <v>1.99487578868866</v>
       </c>
       <c r="H362" t="n">
         <v>6000</v>
@@ -10896,7 +10896,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G363" t="n">
-        <v>1.96851181983948</v>
+        <v>1.9685115814209</v>
       </c>
       <c r="H363" t="n">
         <v>3000</v>
@@ -10983,7 +10983,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G366" t="n">
-        <v>1.93335998058319</v>
+        <v>1.9333598613739</v>
       </c>
       <c r="H366" t="n">
         <v>13500</v>
@@ -11012,7 +11012,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G367" t="n">
-        <v>1.93335998058319</v>
+        <v>1.9333598613739</v>
       </c>
       <c r="H367" t="n">
         <v>1500</v>
@@ -11041,7 +11041,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G368" t="n">
-        <v>2.01245188713074</v>
+        <v>2.01245164871216</v>
       </c>
       <c r="H368" t="n">
         <v>4500</v>
@@ -11070,7 +11070,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G369" t="n">
-        <v>1.98608767986298</v>
+        <v>1.98608791828156</v>
       </c>
       <c r="H369" t="n">
         <v>25500</v>
@@ -11099,7 +11099,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G370" t="n">
-        <v>1.93335998058319</v>
+        <v>1.9333598613739</v>
       </c>
       <c r="H370" t="n">
         <v>6000</v>
@@ -11128,7 +11128,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G371" t="n">
-        <v>1.93335998058319</v>
+        <v>1.9333598613739</v>
       </c>
       <c r="H371" t="n">
         <v>1500</v>
@@ -11157,7 +11157,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G372" t="n">
-        <v>1.98608767986298</v>
+        <v>1.98608791828156</v>
       </c>
       <c r="H372" t="n">
         <v>7500</v>
@@ -11360,7 +11360,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G379" t="n">
-        <v>1.93335998058319</v>
+        <v>1.9333598613739</v>
       </c>
       <c r="H379" t="n">
         <v>3000</v>
@@ -11389,7 +11389,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G380" t="n">
-        <v>1.62577998638153</v>
+        <v>1.62577986717224</v>
       </c>
       <c r="H380" t="n">
         <v>43500</v>
@@ -11563,7 +11563,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G386" t="n">
-        <v>1.99487566947937</v>
+        <v>1.99487578868866</v>
       </c>
       <c r="H386" t="n">
         <v>15000</v>
@@ -11621,7 +11621,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G388" t="n">
-        <v>1.99487566947937</v>
+        <v>1.99487578868866</v>
       </c>
       <c r="H388" t="n">
         <v>9000</v>
@@ -11679,7 +11679,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G390" t="n">
-        <v>1.93335998058319</v>
+        <v>1.9333598613739</v>
       </c>
       <c r="H390" t="n">
         <v>1500</v>
@@ -11708,7 +11708,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G391" t="n">
-        <v>1.96851181983948</v>
+        <v>1.9685115814209</v>
       </c>
       <c r="H391" t="n">
         <v>9000</v>
@@ -11737,7 +11737,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G392" t="n">
-        <v>1.98608767986298</v>
+        <v>1.98608791828156</v>
       </c>
       <c r="H392" t="n">
         <v>6000</v>
@@ -11766,7 +11766,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G393" t="n">
-        <v>1.98608767986298</v>
+        <v>1.98608791828156</v>
       </c>
       <c r="H393" t="n">
         <v>0</v>
@@ -11824,7 +11824,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G395" t="n">
-        <v>1.99487566947937</v>
+        <v>1.99487578868866</v>
       </c>
       <c r="H395" t="n">
         <v>31500</v>
@@ -11853,7 +11853,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G396" t="n">
-        <v>2.01245188713074</v>
+        <v>2.01245164871216</v>
       </c>
       <c r="H396" t="n">
         <v>12000</v>
@@ -11940,7 +11940,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G399" t="n">
-        <v>1.98608767986298</v>
+        <v>1.98608791828156</v>
       </c>
       <c r="H399" t="n">
         <v>6000</v>
@@ -11969,7 +11969,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G400" t="n">
-        <v>2.02123975753784</v>
+        <v>2.02123951911926</v>
       </c>
       <c r="H400" t="n">
         <v>10500</v>
@@ -11998,7 +11998,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G401" t="n">
-        <v>2.01245188713074</v>
+        <v>2.01245164871216</v>
       </c>
       <c r="H401" t="n">
         <v>15000</v>
@@ -12056,7 +12056,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G403" t="n">
-        <v>1.93335998058319</v>
+        <v>1.9333598613739</v>
       </c>
       <c r="H403" t="n">
         <v>7500</v>
@@ -12085,7 +12085,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G404" t="n">
-        <v>1.96851181983948</v>
+        <v>1.9685115814209</v>
       </c>
       <c r="H404" t="n">
         <v>22500</v>
@@ -12114,7 +12114,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G405" t="n">
-        <v>1.98608767986298</v>
+        <v>1.98608791828156</v>
       </c>
       <c r="H405" t="n">
         <v>16500</v>
@@ -12143,7 +12143,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G406" t="n">
-        <v>1.98608767986298</v>
+        <v>1.98608791828156</v>
       </c>
       <c r="H406" t="n">
         <v>0</v>
@@ -12288,7 +12288,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G411" t="n">
-        <v>1.87184381484985</v>
+        <v>1.87184393405914</v>
       </c>
       <c r="H411" t="n">
         <v>4500</v>
@@ -12375,7 +12375,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G414" t="n">
-        <v>1.83669185638428</v>
+        <v>1.83669173717499</v>
       </c>
       <c r="H414" t="n">
         <v>1500</v>
@@ -12636,7 +12636,7 @@
         <v>2</v>
       </c>
       <c r="G423" t="n">
-        <v>1.75759971141815</v>
+        <v>1.75759983062744</v>
       </c>
       <c r="H423" t="n">
         <v>25500</v>
@@ -12723,7 +12723,7 @@
         <v>2</v>
       </c>
       <c r="G426" t="n">
-        <v>1.75759971141815</v>
+        <v>1.75759983062744</v>
       </c>
       <c r="H426" t="n">
         <v>4500</v>
@@ -12752,7 +12752,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G427" t="n">
-        <v>1.76638782024384</v>
+        <v>1.76638793945312</v>
       </c>
       <c r="H427" t="n">
         <v>4500</v>
@@ -12781,7 +12781,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G428" t="n">
-        <v>1.76638782024384</v>
+        <v>1.76638793945312</v>
       </c>
       <c r="H428" t="n">
         <v>3000</v>
@@ -12810,7 +12810,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G429" t="n">
-        <v>1.76638782024384</v>
+        <v>1.76638793945312</v>
       </c>
       <c r="H429" t="n">
         <v>3000</v>
@@ -12839,7 +12839,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G430" t="n">
-        <v>1.76638782024384</v>
+        <v>1.76638793945312</v>
       </c>
       <c r="H430" t="n">
         <v>4500</v>
@@ -13216,7 +13216,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G443" t="n">
-        <v>1.82790386676788</v>
+        <v>1.82790374755859</v>
       </c>
       <c r="H443" t="n">
         <v>4500</v>
@@ -13274,7 +13274,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G445" t="n">
-        <v>1.82790386676788</v>
+        <v>1.82790374755859</v>
       </c>
       <c r="H445" t="n">
         <v>1500</v>
@@ -13303,7 +13303,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G446" t="n">
-        <v>1.82790386676788</v>
+        <v>1.82790374755859</v>
       </c>
       <c r="H446" t="n">
         <v>0</v>
@@ -13332,7 +13332,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G447" t="n">
-        <v>1.76638782024384</v>
+        <v>1.76638793945312</v>
       </c>
       <c r="H447" t="n">
         <v>15000</v>
@@ -13361,7 +13361,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G448" t="n">
-        <v>1.7356299161911</v>
+        <v>1.73562979698181</v>
       </c>
       <c r="H448" t="n">
         <v>3000</v>
@@ -13419,7 +13419,7 @@
         <v>2</v>
       </c>
       <c r="G450" t="n">
-        <v>1.75759971141815</v>
+        <v>1.75759983062744</v>
       </c>
       <c r="H450" t="n">
         <v>10500</v>
@@ -13506,7 +13506,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G453" t="n">
-        <v>1.687295794487</v>
+        <v>1.68729591369629</v>
       </c>
       <c r="H453" t="n">
         <v>7500</v>
@@ -13535,7 +13535,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G454" t="n">
-        <v>1.63896191120148</v>
+        <v>1.63896179199219</v>
       </c>
       <c r="H454" t="n">
         <v>6000</v>
@@ -13709,7 +13709,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G460" t="n">
-        <v>1.67411375045776</v>
+        <v>1.67411386966705</v>
       </c>
       <c r="H460" t="n">
         <v>1500</v>
@@ -13738,7 +13738,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G461" t="n">
-        <v>1.67411375045776</v>
+        <v>1.67411386966705</v>
       </c>
       <c r="H461" t="n">
         <v>6000</v>
@@ -13767,7 +13767,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G462" t="n">
-        <v>1.67411375045776</v>
+        <v>1.67411386966705</v>
       </c>
       <c r="H462" t="n">
         <v>1500</v>
@@ -13796,7 +13796,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G463" t="n">
-        <v>1.66093182563782</v>
+        <v>1.66093194484711</v>
       </c>
       <c r="H463" t="n">
         <v>1500</v>
@@ -13825,7 +13825,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G464" t="n">
-        <v>1.66093182563782</v>
+        <v>1.66093194484711</v>
       </c>
       <c r="H464" t="n">
         <v>0</v>
@@ -13854,7 +13854,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G465" t="n">
-        <v>1.65214383602142</v>
+        <v>1.65214371681213</v>
       </c>
       <c r="H465" t="n">
         <v>9000</v>
@@ -13912,7 +13912,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G467" t="n">
-        <v>1.59502184391022</v>
+        <v>1.59502196311951</v>
       </c>
       <c r="H467" t="n">
         <v>3000</v>
@@ -13970,7 +13970,7 @@
         <v>1.875</v>
       </c>
       <c r="G469" t="n">
-        <v>1.64774990081787</v>
+        <v>1.64774978160858</v>
       </c>
       <c r="H469" t="n">
         <v>3000</v>
@@ -13999,7 +13999,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G470" t="n">
-        <v>1.66093182563782</v>
+        <v>1.66093194484711</v>
       </c>
       <c r="H470" t="n">
         <v>3000</v>
@@ -14028,7 +14028,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G471" t="n">
-        <v>1.59502184391022</v>
+        <v>1.59502196311951</v>
       </c>
       <c r="H471" t="n">
         <v>15000</v>
@@ -14057,7 +14057,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G472" t="n">
-        <v>1.64335584640503</v>
+        <v>1.64335572719574</v>
       </c>
       <c r="H472" t="n">
         <v>4500</v>
@@ -14086,7 +14086,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G473" t="n">
-        <v>1.64335584640503</v>
+        <v>1.64335572719574</v>
       </c>
       <c r="H473" t="n">
         <v>0</v>
@@ -14144,7 +14144,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G475" t="n">
-        <v>1.63456797599792</v>
+        <v>1.63456785678864</v>
       </c>
       <c r="H475" t="n">
         <v>3000</v>
@@ -14173,7 +14173,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G476" t="n">
-        <v>1.66532576084137</v>
+        <v>1.66532588005066</v>
       </c>
       <c r="H476" t="n">
         <v>1500</v>
@@ -14202,7 +14202,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G477" t="n">
-        <v>1.66532576084137</v>
+        <v>1.66532588005066</v>
       </c>
       <c r="H477" t="n">
         <v>0</v>
@@ -14231,7 +14231,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G478" t="n">
-        <v>1.66532576084137</v>
+        <v>1.66532588005066</v>
       </c>
       <c r="H478" t="n">
         <v>0</v>
@@ -14289,7 +14289,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G480" t="n">
-        <v>1.63017392158508</v>
+        <v>1.63017380237579</v>
       </c>
       <c r="H480" t="n">
         <v>3000</v>
@@ -14318,7 +14318,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G481" t="n">
-        <v>1.687295794487</v>
+        <v>1.68729591369629</v>
       </c>
       <c r="H481" t="n">
         <v>3000</v>
@@ -14347,7 +14347,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G482" t="n">
-        <v>1.67411375045776</v>
+        <v>1.67411386966705</v>
       </c>
       <c r="H482" t="n">
         <v>4500</v>
@@ -14376,7 +14376,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G483" t="n">
-        <v>1.64335584640503</v>
+        <v>1.64335572719574</v>
       </c>
       <c r="H483" t="n">
         <v>3000</v>
@@ -14405,7 +14405,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G484" t="n">
-        <v>1.74881184101105</v>
+        <v>1.74881172180176</v>
       </c>
       <c r="H484" t="n">
         <v>19500</v>
@@ -14463,7 +14463,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G486" t="n">
-        <v>1.87184381484985</v>
+        <v>1.87184393405914</v>
       </c>
       <c r="H486" t="n">
         <v>25500</v>
@@ -14492,7 +14492,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G487" t="n">
-        <v>1.93335998058319</v>
+        <v>1.9333598613739</v>
       </c>
       <c r="H487" t="n">
         <v>33000</v>
@@ -14637,7 +14637,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G492" t="n">
-        <v>1.99487566947937</v>
+        <v>1.99487578868866</v>
       </c>
       <c r="H492" t="n">
         <v>3000</v>
@@ -14666,7 +14666,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G493" t="n">
-        <v>2.02123975753784</v>
+        <v>2.02123951911926</v>
       </c>
       <c r="H493" t="n">
         <v>42000</v>
@@ -14753,7 +14753,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G496" t="n">
-        <v>1.93335998058319</v>
+        <v>1.9333598613739</v>
       </c>
       <c r="H496" t="n">
         <v>6000</v>
@@ -14782,7 +14782,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G497" t="n">
-        <v>1.82790386676788</v>
+        <v>1.82790374755859</v>
       </c>
       <c r="H497" t="n">
         <v>21000</v>
@@ -14811,7 +14811,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G498" t="n">
-        <v>1.7356299161911</v>
+        <v>1.73562979698181</v>
       </c>
       <c r="H498" t="n">
         <v>40500</v>
@@ -14927,7 +14927,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G502" t="n">
-        <v>1.74881184101105</v>
+        <v>1.74881172180176</v>
       </c>
       <c r="H502" t="n">
         <v>4500</v>
@@ -14956,7 +14956,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G503" t="n">
-        <v>1.74881184101105</v>
+        <v>1.74881172180176</v>
       </c>
       <c r="H503" t="n">
         <v>1500</v>
@@ -14985,7 +14985,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G504" t="n">
-        <v>1.74881184101105</v>
+        <v>1.74881172180176</v>
       </c>
       <c r="H504" t="n">
         <v>1500</v>
@@ -15420,7 +15420,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G519" t="n">
-        <v>1.76638782024384</v>
+        <v>1.76638793945312</v>
       </c>
       <c r="H519" t="n">
         <v>3000</v>
@@ -15507,7 +15507,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G522" t="n">
-        <v>1.76638782024384</v>
+        <v>1.76638793945312</v>
       </c>
       <c r="H522" t="n">
         <v>9000</v>
@@ -15594,7 +15594,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G525" t="n">
-        <v>1.62577998638153</v>
+        <v>1.62577986717224</v>
       </c>
       <c r="H525" t="n">
         <v>6000</v>
@@ -15710,7 +15710,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G529" t="n">
-        <v>1.52471792697906</v>
+        <v>1.52471780776978</v>
       </c>
       <c r="H529" t="n">
         <v>6000</v>
@@ -15971,7 +15971,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G538" t="n">
-        <v>1.55108165740967</v>
+        <v>1.55108177661896</v>
       </c>
       <c r="H538" t="n">
         <v>1500</v>
@@ -16000,7 +16000,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G539" t="n">
-        <v>1.55108165740967</v>
+        <v>1.55108177661896</v>
       </c>
       <c r="H539" t="n">
         <v>0</v>
@@ -16029,7 +16029,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G540" t="n">
-        <v>1.51153600215912</v>
+        <v>1.51153588294983</v>
       </c>
       <c r="H540" t="n">
         <v>7500</v>
@@ -16058,7 +16058,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G541" t="n">
-        <v>1.51153600215912</v>
+        <v>1.51153588294983</v>
       </c>
       <c r="H541" t="n">
         <v>0</v>
@@ -16087,7 +16087,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G542" t="n">
-        <v>1.51153600215912</v>
+        <v>1.51153588294983</v>
       </c>
       <c r="H542" t="n">
         <v>0</v>
@@ -16203,7 +16203,7 @@
         <v>1.875</v>
       </c>
       <c r="G546" t="n">
-        <v>1.64774990081787</v>
+        <v>1.64774978160858</v>
       </c>
       <c r="H546" t="n">
         <v>18000</v>
@@ -16232,7 +16232,7 @@
         <v>1.875</v>
       </c>
       <c r="G547" t="n">
-        <v>1.64774990081787</v>
+        <v>1.64774978160858</v>
       </c>
       <c r="H547" t="n">
         <v>0</v>
@@ -16435,7 +16435,7 @@
         <v>2</v>
       </c>
       <c r="G554" t="n">
-        <v>1.75759971141815</v>
+        <v>1.75759983062744</v>
       </c>
       <c r="H554" t="n">
         <v>1500</v>
@@ -16464,7 +16464,7 @@
         <v>2</v>
       </c>
       <c r="G555" t="n">
-        <v>1.75759971141815</v>
+        <v>1.75759983062744</v>
       </c>
       <c r="H555" t="n">
         <v>0</v>
@@ -16783,7 +16783,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G566" t="n">
-        <v>1.62577998638153</v>
+        <v>1.62577986717224</v>
       </c>
       <c r="H566" t="n">
         <v>4500</v>
@@ -16812,7 +16812,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G567" t="n">
-        <v>1.62577998638153</v>
+        <v>1.62577986717224</v>
       </c>
       <c r="H567" t="n">
         <v>0</v>
@@ -16841,7 +16841,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G568" t="n">
-        <v>1.62577998638153</v>
+        <v>1.62577986717224</v>
       </c>
       <c r="H568" t="n">
         <v>0</v>
@@ -16928,7 +16928,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G571" t="n">
-        <v>1.66093182563782</v>
+        <v>1.66093194484711</v>
       </c>
       <c r="H571" t="n">
         <v>1500</v>
@@ -16957,7 +16957,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G572" t="n">
-        <v>1.67411375045776</v>
+        <v>1.67411386966705</v>
       </c>
       <c r="H572" t="n">
         <v>1500</v>
@@ -17218,7 +17218,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G581" t="n">
-        <v>1.687295794487</v>
+        <v>1.68729591369629</v>
       </c>
       <c r="H581" t="n">
         <v>1500</v>
@@ -17247,7 +17247,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G582" t="n">
-        <v>1.65214383602142</v>
+        <v>1.65214371681213</v>
       </c>
       <c r="H582" t="n">
         <v>1500</v>
@@ -17276,7 +17276,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G583" t="n">
-        <v>1.65214383602142</v>
+        <v>1.65214371681213</v>
       </c>
       <c r="H583" t="n">
         <v>0</v>
@@ -17305,7 +17305,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G584" t="n">
-        <v>1.62577998638153</v>
+        <v>1.62577986717224</v>
       </c>
       <c r="H584" t="n">
         <v>1500</v>
@@ -17334,7 +17334,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G585" t="n">
-        <v>1.62577998638153</v>
+        <v>1.62577986717224</v>
       </c>
       <c r="H585" t="n">
         <v>0</v>
@@ -17363,7 +17363,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G586" t="n">
-        <v>1.62577998638153</v>
+        <v>1.62577986717224</v>
       </c>
       <c r="H586" t="n">
         <v>0</v>
@@ -17392,7 +17392,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G587" t="n">
-        <v>1.62577998638153</v>
+        <v>1.62577986717224</v>
       </c>
       <c r="H587" t="n">
         <v>1500</v>
@@ -17421,7 +17421,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G588" t="n">
-        <v>1.62577998638153</v>
+        <v>1.62577986717224</v>
       </c>
       <c r="H588" t="n">
         <v>0</v>
@@ -17450,7 +17450,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G589" t="n">
-        <v>1.62577998638153</v>
+        <v>1.62577986717224</v>
       </c>
       <c r="H589" t="n">
         <v>1500</v>
@@ -17595,7 +17595,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G594" t="n">
-        <v>1.55986976623535</v>
+        <v>1.55986988544464</v>
       </c>
       <c r="H594" t="n">
         <v>15000</v>
@@ -17624,7 +17624,7 @@
         <v>1.875</v>
       </c>
       <c r="G595" t="n">
-        <v>1.64774990081787</v>
+        <v>1.64774978160858</v>
       </c>
       <c r="H595" t="n">
         <v>7500</v>
@@ -17653,7 +17653,7 @@
         <v>1.875</v>
       </c>
       <c r="G596" t="n">
-        <v>1.64774990081787</v>
+        <v>1.64774978160858</v>
       </c>
       <c r="H596" t="n">
         <v>0</v>
@@ -17711,7 +17711,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G598" t="n">
-        <v>1.63896191120148</v>
+        <v>1.63896179199219</v>
       </c>
       <c r="H598" t="n">
         <v>1500</v>
@@ -17740,7 +17740,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G599" t="n">
-        <v>1.63896191120148</v>
+        <v>1.63896179199219</v>
       </c>
       <c r="H599" t="n">
         <v>0</v>
@@ -17943,7 +17943,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G606" t="n">
-        <v>1.63896191120148</v>
+        <v>1.63896179199219</v>
       </c>
       <c r="H606" t="n">
         <v>3000</v>
@@ -18001,7 +18001,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G608" t="n">
-        <v>1.58183979988098</v>
+        <v>1.58183991909027</v>
       </c>
       <c r="H608" t="n">
         <v>12000</v>
@@ -18117,7 +18117,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G612" t="n">
-        <v>1.60820376873016</v>
+        <v>1.60820388793945</v>
       </c>
       <c r="H612" t="n">
         <v>1500</v>
@@ -18233,7 +18233,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G616" t="n">
-        <v>1.56865787506104</v>
+        <v>1.56865799427032</v>
       </c>
       <c r="H616" t="n">
         <v>7500</v>
@@ -18262,7 +18262,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G617" t="n">
-        <v>1.7532057762146</v>
+        <v>1.75320589542389</v>
       </c>
       <c r="H617" t="n">
         <v>114000</v>
@@ -18900,7 +18900,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G639" t="n">
-        <v>1.64335584640503</v>
+        <v>1.64335572719574</v>
       </c>
       <c r="H639" t="n">
         <v>19500</v>
@@ -18929,7 +18929,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G640" t="n">
-        <v>1.60820376873016</v>
+        <v>1.60820388793945</v>
       </c>
       <c r="H640" t="n">
         <v>33000</v>
@@ -18958,7 +18958,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G641" t="n">
-        <v>1.62577998638153</v>
+        <v>1.62577986717224</v>
       </c>
       <c r="H641" t="n">
         <v>1500</v>
@@ -18987,7 +18987,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G642" t="n">
-        <v>1.65214383602142</v>
+        <v>1.65214371681213</v>
       </c>
       <c r="H642" t="n">
         <v>18000</v>
@@ -19016,7 +19016,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G643" t="n">
-        <v>1.65214383602142</v>
+        <v>1.65214371681213</v>
       </c>
       <c r="H643" t="n">
         <v>9000</v>
@@ -19045,7 +19045,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G644" t="n">
-        <v>1.66093182563782</v>
+        <v>1.66093194484711</v>
       </c>
       <c r="H644" t="n">
         <v>9000</v>
@@ -19074,7 +19074,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G645" t="n">
-        <v>1.66093182563782</v>
+        <v>1.66093194484711</v>
       </c>
       <c r="H645" t="n">
         <v>0</v>
@@ -19132,7 +19132,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G647" t="n">
-        <v>1.66532576084137</v>
+        <v>1.66532588005066</v>
       </c>
       <c r="H647" t="n">
         <v>7500</v>
@@ -19190,7 +19190,7 @@
         <v>2</v>
       </c>
       <c r="G649" t="n">
-        <v>1.75759971141815</v>
+        <v>1.75759983062744</v>
       </c>
       <c r="H649" t="n">
         <v>6000</v>
@@ -19219,7 +19219,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G650" t="n">
-        <v>1.74881184101105</v>
+        <v>1.74881172180176</v>
       </c>
       <c r="H650" t="n">
         <v>3000</v>
@@ -19393,7 +19393,7 @@
         <v>2</v>
       </c>
       <c r="G656" t="n">
-        <v>1.75759971141815</v>
+        <v>1.75759983062744</v>
       </c>
       <c r="H656" t="n">
         <v>1500</v>
@@ -19480,7 +19480,7 @@
         <v>2</v>
       </c>
       <c r="G659" t="n">
-        <v>1.75759971141815</v>
+        <v>1.75759983062744</v>
       </c>
       <c r="H659" t="n">
         <v>102000</v>
@@ -19538,7 +19538,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G661" t="n">
-        <v>1.78719866275787</v>
+        <v>1.78719854354858</v>
       </c>
       <c r="H661" t="n">
         <v>3000</v>
@@ -19567,7 +19567,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G662" t="n">
-        <v>1.70596218109131</v>
+        <v>1.7059623003006</v>
       </c>
       <c r="H662" t="n">
         <v>54000</v>
@@ -19596,7 +19596,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G663" t="n">
-        <v>1.70596218109131</v>
+        <v>1.7059623003006</v>
       </c>
       <c r="H663" t="n">
         <v>6000</v>
@@ -19683,7 +19683,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G666" t="n">
-        <v>1.73304092884064</v>
+        <v>1.73304104804993</v>
       </c>
       <c r="H666" t="n">
         <v>9000</v>
@@ -19712,7 +19712,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G667" t="n">
-        <v>1.70596218109131</v>
+        <v>1.7059623003006</v>
       </c>
       <c r="H667" t="n">
         <v>7500</v>
@@ -19828,7 +19828,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G671" t="n">
-        <v>1.63375222682953</v>
+        <v>1.63375210762024</v>
       </c>
       <c r="H671" t="n">
         <v>1500</v>
@@ -19857,7 +19857,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G672" t="n">
-        <v>1.63375222682953</v>
+        <v>1.63375210762024</v>
       </c>
       <c r="H672" t="n">
         <v>0</v>
@@ -20002,7 +20002,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G677" t="n">
-        <v>1.6066734790802</v>
+        <v>1.60667335987091</v>
       </c>
       <c r="H677" t="n">
         <v>4500</v>
@@ -20031,7 +20031,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G678" t="n">
-        <v>1.6066734790802</v>
+        <v>1.60667335987091</v>
       </c>
       <c r="H678" t="n">
         <v>1500</v>
@@ -20060,7 +20060,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G679" t="n">
-        <v>1.63375222682953</v>
+        <v>1.63375210762024</v>
       </c>
       <c r="H679" t="n">
         <v>1500</v>
@@ -20089,7 +20089,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G680" t="n">
-        <v>1.63375222682953</v>
+        <v>1.63375210762024</v>
       </c>
       <c r="H680" t="n">
         <v>0</v>
@@ -20205,7 +20205,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G684" t="n">
-        <v>1.59764719009399</v>
+        <v>1.5976470708847</v>
       </c>
       <c r="H684" t="n">
         <v>1500</v>
@@ -20234,7 +20234,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G685" t="n">
-        <v>1.6066734790802</v>
+        <v>1.60667335987091</v>
       </c>
       <c r="H685" t="n">
         <v>7500</v>
@@ -20263,7 +20263,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G686" t="n">
-        <v>1.6066734790802</v>
+        <v>1.60667335987091</v>
       </c>
       <c r="H686" t="n">
         <v>0</v>
@@ -20292,7 +20292,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G687" t="n">
-        <v>1.6066734790802</v>
+        <v>1.60667335987091</v>
       </c>
       <c r="H687" t="n">
         <v>0</v>
@@ -20321,7 +20321,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G688" t="n">
-        <v>1.6066734790802</v>
+        <v>1.60667335987091</v>
       </c>
       <c r="H688" t="n">
         <v>4500</v>
@@ -20350,7 +20350,7 @@
         <v>1.75</v>
       </c>
       <c r="G689" t="n">
-        <v>1.57959461212158</v>
+        <v>1.57959473133087</v>
       </c>
       <c r="H689" t="n">
         <v>4500</v>
@@ -20379,7 +20379,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G690" t="n">
-        <v>1.6066734790802</v>
+        <v>1.60667335987091</v>
       </c>
       <c r="H690" t="n">
         <v>3000</v>
@@ -20408,7 +20408,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G691" t="n">
-        <v>1.6066734790802</v>
+        <v>1.60667335987091</v>
       </c>
       <c r="H691" t="n">
         <v>0</v>
@@ -20437,7 +20437,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G692" t="n">
-        <v>1.61569976806641</v>
+        <v>1.61569964885712</v>
       </c>
       <c r="H692" t="n">
         <v>4500</v>
@@ -20466,7 +20466,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G693" t="n">
-        <v>1.61569976806641</v>
+        <v>1.61569964885712</v>
       </c>
       <c r="H693" t="n">
         <v>0</v>
@@ -20495,7 +20495,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G694" t="n">
-        <v>1.61569976806641</v>
+        <v>1.61569964885712</v>
       </c>
       <c r="H694" t="n">
         <v>0</v>
@@ -20553,7 +20553,7 @@
         <v>1.75</v>
       </c>
       <c r="G696" t="n">
-        <v>1.57959461212158</v>
+        <v>1.57959473133087</v>
       </c>
       <c r="H696" t="n">
         <v>6000</v>
@@ -20582,7 +20582,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G697" t="n">
-        <v>1.53446352481842</v>
+        <v>1.53446340560913</v>
       </c>
       <c r="H697" t="n">
         <v>12000</v>
@@ -20698,7 +20698,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G701" t="n">
-        <v>1.59764719009399</v>
+        <v>1.5976470708847</v>
       </c>
       <c r="H701" t="n">
         <v>1500</v>
@@ -20727,7 +20727,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G702" t="n">
-        <v>1.59764719009399</v>
+        <v>1.5976470708847</v>
       </c>
       <c r="H702" t="n">
         <v>3000</v>
@@ -20756,7 +20756,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G703" t="n">
-        <v>1.59764719009399</v>
+        <v>1.5976470708847</v>
       </c>
       <c r="H703" t="n">
         <v>4500</v>
@@ -20785,7 +20785,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G704" t="n">
-        <v>1.59764719009399</v>
+        <v>1.5976470708847</v>
       </c>
       <c r="H704" t="n">
         <v>0</v>
@@ -20843,7 +20843,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G706" t="n">
-        <v>1.59764719009399</v>
+        <v>1.5976470708847</v>
       </c>
       <c r="H706" t="n">
         <v>7500</v>
@@ -20959,7 +20959,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G710" t="n">
-        <v>1.51641082763672</v>
+        <v>1.51641094684601</v>
       </c>
       <c r="H710" t="n">
         <v>13500</v>
@@ -21075,7 +21075,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G714" t="n">
-        <v>1.53446352481842</v>
+        <v>1.53446340560913</v>
       </c>
       <c r="H714" t="n">
         <v>1500</v>
@@ -21104,7 +21104,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G715" t="n">
-        <v>1.53446352481842</v>
+        <v>1.53446340560913</v>
       </c>
       <c r="H715" t="n">
         <v>6000</v>
@@ -21133,7 +21133,7 @@
         <v>1.75</v>
       </c>
       <c r="G716" t="n">
-        <v>1.57959461212158</v>
+        <v>1.57959473133087</v>
       </c>
       <c r="H716" t="n">
         <v>4500</v>
@@ -21162,7 +21162,7 @@
         <v>1.75</v>
       </c>
       <c r="G717" t="n">
-        <v>1.57959461212158</v>
+        <v>1.57959473133087</v>
       </c>
       <c r="H717" t="n">
         <v>0</v>
@@ -21220,7 +21220,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G719" t="n">
-        <v>1.53446352481842</v>
+        <v>1.53446340560913</v>
       </c>
       <c r="H719" t="n">
         <v>10500</v>
@@ -21510,7 +21510,7 @@
         <v>1.75</v>
       </c>
       <c r="G729" t="n">
-        <v>1.57959461212158</v>
+        <v>1.57959473133087</v>
       </c>
       <c r="H729" t="n">
         <v>1500</v>
@@ -21539,7 +21539,7 @@
         <v>1.75</v>
       </c>
       <c r="G730" t="n">
-        <v>1.57959461212158</v>
+        <v>1.57959473133087</v>
       </c>
       <c r="H730" t="n">
         <v>7500</v>
@@ -21742,7 +21742,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G737" t="n">
-        <v>1.53446352481842</v>
+        <v>1.53446340560913</v>
       </c>
       <c r="H737" t="n">
         <v>1500</v>
@@ -21771,7 +21771,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G738" t="n">
-        <v>1.52543711662292</v>
+        <v>1.52543723583221</v>
       </c>
       <c r="H738" t="n">
         <v>7500</v>
@@ -21800,7 +21800,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G739" t="n">
-        <v>1.52543711662292</v>
+        <v>1.52543723583221</v>
       </c>
       <c r="H739" t="n">
         <v>0</v>
@@ -21829,7 +21829,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G740" t="n">
-        <v>1.52543711662292</v>
+        <v>1.52543723583221</v>
       </c>
       <c r="H740" t="n">
         <v>0</v>
@@ -22032,7 +22032,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G747" t="n">
-        <v>1.53446352481842</v>
+        <v>1.53446340560913</v>
       </c>
       <c r="H747" t="n">
         <v>1500</v>
@@ -22061,7 +22061,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G748" t="n">
-        <v>1.53446352481842</v>
+        <v>1.53446340560913</v>
       </c>
       <c r="H748" t="n">
         <v>0</v>
@@ -22090,7 +22090,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G749" t="n">
-        <v>1.53446352481842</v>
+        <v>1.53446340560913</v>
       </c>
       <c r="H749" t="n">
         <v>1500</v>
@@ -22119,7 +22119,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G750" t="n">
-        <v>1.53446352481842</v>
+        <v>1.53446340560913</v>
       </c>
       <c r="H750" t="n">
         <v>0</v>
@@ -22206,7 +22206,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G753" t="n">
-        <v>1.4983583688736</v>
+        <v>1.49835848808289</v>
       </c>
       <c r="H753" t="n">
         <v>4500</v>
@@ -22235,7 +22235,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G754" t="n">
-        <v>1.46225345134735</v>
+        <v>1.46225333213806</v>
       </c>
       <c r="H754" t="n">
         <v>15000</v>
@@ -22293,7 +22293,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G756" t="n">
-        <v>1.51641082763672</v>
+        <v>1.51641094684601</v>
       </c>
       <c r="H756" t="n">
         <v>4500</v>
@@ -22554,7 +22554,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G765" t="n">
-        <v>1.51641082763672</v>
+        <v>1.51641094684601</v>
       </c>
       <c r="H765" t="n">
         <v>1500</v>
@@ -22641,7 +22641,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G768" t="n">
-        <v>1.51641082763672</v>
+        <v>1.51641094684601</v>
       </c>
       <c r="H768" t="n">
         <v>3000</v>
@@ -22699,7 +22699,7 @@
         <v>1.75</v>
       </c>
       <c r="G770" t="n">
-        <v>1.57959461212158</v>
+        <v>1.57959473133087</v>
       </c>
       <c r="H770" t="n">
         <v>6000</v>
@@ -22728,7 +22728,7 @@
         <v>1.75</v>
       </c>
       <c r="G771" t="n">
-        <v>1.57959461212158</v>
+        <v>1.57959473133087</v>
       </c>
       <c r="H771" t="n">
         <v>0</v>
@@ -22757,7 +22757,7 @@
         <v>1.75</v>
       </c>
       <c r="G772" t="n">
-        <v>1.57959461212158</v>
+        <v>1.57959473133087</v>
       </c>
       <c r="H772" t="n">
         <v>0</v>
@@ -22873,7 +22873,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G776" t="n">
-        <v>1.51641082763672</v>
+        <v>1.51641094684601</v>
       </c>
       <c r="H776" t="n">
         <v>3000</v>
@@ -22902,7 +22902,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G777" t="n">
-        <v>1.51641082763672</v>
+        <v>1.51641094684601</v>
       </c>
       <c r="H777" t="n">
         <v>0</v>
@@ -23047,7 +23047,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G782" t="n">
-        <v>1.53446352481842</v>
+        <v>1.53446340560913</v>
       </c>
       <c r="H782" t="n">
         <v>27000</v>
@@ -23076,7 +23076,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G783" t="n">
-        <v>1.46225345134735</v>
+        <v>1.46225333213806</v>
       </c>
       <c r="H783" t="n">
         <v>15000</v>
@@ -23105,7 +23105,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G784" t="n">
-        <v>1.4983583688736</v>
+        <v>1.49835848808289</v>
       </c>
       <c r="H784" t="n">
         <v>18000</v>
@@ -23134,7 +23134,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G785" t="n">
-        <v>1.51641082763672</v>
+        <v>1.51641094684601</v>
       </c>
       <c r="H785" t="n">
         <v>1500</v>
@@ -23163,7 +23163,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G786" t="n">
-        <v>1.51641082763672</v>
+        <v>1.51641094684601</v>
       </c>
       <c r="H786" t="n">
         <v>3000</v>
@@ -23192,7 +23192,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G787" t="n">
-        <v>1.51641082763672</v>
+        <v>1.51641094684601</v>
       </c>
       <c r="H787" t="n">
         <v>0</v>
@@ -23424,7 +23424,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G795" t="n">
-        <v>1.87746107578278</v>
+        <v>1.87746119499207</v>
       </c>
       <c r="H795" t="n">
         <v>319500</v>
@@ -23598,7 +23598,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G801" t="n">
-        <v>1.78719866275787</v>
+        <v>1.78719854354858</v>
       </c>
       <c r="H801" t="n">
         <v>30000</v>
@@ -23685,7 +23685,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G804" t="n">
-        <v>1.87746107578278</v>
+        <v>1.87746119499207</v>
       </c>
       <c r="H804" t="n">
         <v>46500</v>
@@ -23714,7 +23714,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G805" t="n">
-        <v>1.85940837860107</v>
+        <v>1.85940849781036</v>
       </c>
       <c r="H805" t="n">
         <v>4500</v>
@@ -23772,7 +23772,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G807" t="n">
-        <v>1.85940837860107</v>
+        <v>1.85940849781036</v>
       </c>
       <c r="H807" t="n">
         <v>7500</v>
@@ -23801,7 +23801,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G808" t="n">
-        <v>1.87746107578278</v>
+        <v>1.87746119499207</v>
       </c>
       <c r="H808" t="n">
         <v>10500</v>
@@ -23830,7 +23830,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G809" t="n">
-        <v>1.85940837860107</v>
+        <v>1.85940849781036</v>
       </c>
       <c r="H809" t="n">
         <v>1500</v>
@@ -23859,7 +23859,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G810" t="n">
-        <v>1.85940837860107</v>
+        <v>1.85940849781036</v>
       </c>
       <c r="H810" t="n">
         <v>1500</v>
@@ -23917,7 +23917,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G812" t="n">
-        <v>1.87746107578278</v>
+        <v>1.87746119499207</v>
       </c>
       <c r="H812" t="n">
         <v>6000</v>
@@ -23946,7 +23946,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G813" t="n">
-        <v>1.91356611251831</v>
+        <v>1.91356599330902</v>
       </c>
       <c r="H813" t="n">
         <v>3000</v>
@@ -23975,7 +23975,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G814" t="n">
-        <v>1.87746107578278</v>
+        <v>1.87746119499207</v>
       </c>
       <c r="H814" t="n">
         <v>7500</v>
@@ -24091,7 +24091,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G818" t="n">
-        <v>1.70596218109131</v>
+        <v>1.7059623003006</v>
       </c>
       <c r="H818" t="n">
         <v>55500</v>
@@ -24178,7 +24178,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G821" t="n">
-        <v>1.73304092884064</v>
+        <v>1.73304104804993</v>
       </c>
       <c r="H821" t="n">
         <v>7500</v>
@@ -24352,7 +24352,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G827" t="n">
-        <v>1.73304092884064</v>
+        <v>1.73304104804993</v>
       </c>
       <c r="H827" t="n">
         <v>10500</v>
@@ -24526,7 +24526,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G833" t="n">
-        <v>1.74206733703613</v>
+        <v>1.74206721782684</v>
       </c>
       <c r="H833" t="n">
         <v>6000</v>
@@ -24555,7 +24555,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G834" t="n">
-        <v>1.73304092884064</v>
+        <v>1.73304104804993</v>
       </c>
       <c r="H834" t="n">
         <v>1500</v>
@@ -24671,7 +24671,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G838" t="n">
-        <v>1.74206733703613</v>
+        <v>1.74206721782684</v>
       </c>
       <c r="H838" t="n">
         <v>10500</v>
@@ -24700,7 +24700,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G839" t="n">
-        <v>1.74206733703613</v>
+        <v>1.74206721782684</v>
       </c>
       <c r="H839" t="n">
         <v>0</v>
@@ -24729,7 +24729,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G840" t="n">
-        <v>1.78719866275787</v>
+        <v>1.78719854354858</v>
       </c>
       <c r="H840" t="n">
         <v>15000</v>
@@ -24758,7 +24758,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G841" t="n">
-        <v>1.78719866275787</v>
+        <v>1.78719854354858</v>
       </c>
       <c r="H841" t="n">
         <v>1500</v>
@@ -25048,7 +25048,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G851" t="n">
-        <v>1.73304092884064</v>
+        <v>1.73304104804993</v>
       </c>
       <c r="H851" t="n">
         <v>16500</v>
@@ -25222,7 +25222,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G857" t="n">
-        <v>1.78719866275787</v>
+        <v>1.78719854354858</v>
       </c>
       <c r="H857" t="n">
         <v>6000</v>
@@ -25251,7 +25251,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G858" t="n">
-        <v>1.78719866275787</v>
+        <v>1.78719854354858</v>
       </c>
       <c r="H858" t="n">
         <v>0</v>
@@ -25309,7 +25309,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G860" t="n">
-        <v>1.78719866275787</v>
+        <v>1.78719854354858</v>
       </c>
       <c r="H860" t="n">
         <v>6000</v>
@@ -25367,7 +25367,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G862" t="n">
-        <v>1.78719866275787</v>
+        <v>1.78719854354858</v>
       </c>
       <c r="H862" t="n">
         <v>4500</v>
@@ -25483,7 +25483,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G866" t="n">
-        <v>1.87746107578278</v>
+        <v>1.87746119499207</v>
       </c>
       <c r="H866" t="n">
         <v>7500</v>
@@ -25512,7 +25512,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G867" t="n">
-        <v>1.91356611251831</v>
+        <v>1.91356599330902</v>
       </c>
       <c r="H867" t="n">
         <v>21000</v>
@@ -25802,7 +25802,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G877" t="n">
-        <v>1.94967126846313</v>
+        <v>1.94967114925385</v>
       </c>
       <c r="H877" t="n">
         <v>10500</v>
@@ -25860,7 +25860,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G879" t="n">
-        <v>1.94967126846313</v>
+        <v>1.94967114925385</v>
       </c>
       <c r="H879" t="n">
         <v>22500</v>
@@ -25889,7 +25889,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G880" t="n">
-        <v>1.94967126846313</v>
+        <v>1.94967114925385</v>
       </c>
       <c r="H880" t="n">
         <v>1500</v>
@@ -25918,7 +25918,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G881" t="n">
-        <v>1.94967126846313</v>
+        <v>1.94967114925385</v>
       </c>
       <c r="H881" t="n">
         <v>9000</v>
@@ -25947,7 +25947,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G882" t="n">
-        <v>1.94967126846313</v>
+        <v>1.94967114925385</v>
       </c>
       <c r="H882" t="n">
         <v>7500</v>
@@ -26295,7 +26295,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G894" t="n">
-        <v>2.02188110351562</v>
+        <v>2.0218813419342</v>
       </c>
       <c r="H894" t="n">
         <v>42000</v>
@@ -26324,7 +26324,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G895" t="n">
-        <v>1.85940837860107</v>
+        <v>1.85940849781036</v>
       </c>
       <c r="H895" t="n">
         <v>126000</v>
@@ -26353,7 +26353,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G896" t="n">
-        <v>1.94967126846313</v>
+        <v>1.94967114925385</v>
       </c>
       <c r="H896" t="n">
         <v>33000</v>
@@ -26382,7 +26382,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G897" t="n">
-        <v>1.91356611251831</v>
+        <v>1.91356599330902</v>
       </c>
       <c r="H897" t="n">
         <v>54000</v>
@@ -26411,7 +26411,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G898" t="n">
-        <v>1.87746107578278</v>
+        <v>1.87746119499207</v>
       </c>
       <c r="H898" t="n">
         <v>15000</v>
@@ -26440,7 +26440,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G899" t="n">
-        <v>1.85940837860107</v>
+        <v>1.85940849781036</v>
       </c>
       <c r="H899" t="n">
         <v>16500</v>
@@ -26469,7 +26469,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G900" t="n">
-        <v>1.87746107578278</v>
+        <v>1.87746119499207</v>
       </c>
       <c r="H900" t="n">
         <v>12000</v>
@@ -26498,7 +26498,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G901" t="n">
-        <v>1.85940837860107</v>
+        <v>1.85940849781036</v>
       </c>
       <c r="H901" t="n">
         <v>4500</v>
@@ -26556,7 +26556,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G903" t="n">
-        <v>1.91356611251831</v>
+        <v>1.91356599330902</v>
       </c>
       <c r="H903" t="n">
         <v>4500</v>
@@ -26614,7 +26614,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G905" t="n">
-        <v>1.94967126846313</v>
+        <v>1.94967114925385</v>
       </c>
       <c r="H905" t="n">
         <v>15000</v>
@@ -26643,7 +26643,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G906" t="n">
-        <v>1.91356611251831</v>
+        <v>1.91356599330902</v>
       </c>
       <c r="H906" t="n">
         <v>7500</v>
@@ -26730,7 +26730,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G909" t="n">
-        <v>1.85940837860107</v>
+        <v>1.85940849781036</v>
       </c>
       <c r="H909" t="n">
         <v>111000</v>
@@ -26788,7 +26788,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G911" t="n">
-        <v>1.87746107578278</v>
+        <v>1.87746119499207</v>
       </c>
       <c r="H911" t="n">
         <v>9000</v>
@@ -26817,7 +26817,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G912" t="n">
-        <v>1.85940837860107</v>
+        <v>1.85940849781036</v>
       </c>
       <c r="H912" t="n">
         <v>15000</v>
@@ -26846,7 +26846,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G913" t="n">
-        <v>1.85940837860107</v>
+        <v>1.85940849781036</v>
       </c>
       <c r="H913" t="n">
         <v>6000</v>
@@ -26904,7 +26904,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G915" t="n">
-        <v>1.87746107578278</v>
+        <v>1.87746119499207</v>
       </c>
       <c r="H915" t="n">
         <v>10500</v>
@@ -26933,7 +26933,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G916" t="n">
-        <v>1.87746107578278</v>
+        <v>1.87746119499207</v>
       </c>
       <c r="H916" t="n">
         <v>1500</v>
@@ -26962,7 +26962,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G917" t="n">
-        <v>1.85940837860107</v>
+        <v>1.85940849781036</v>
       </c>
       <c r="H917" t="n">
         <v>13500</v>
@@ -27049,7 +27049,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G920" t="n">
-        <v>1.89470195770264</v>
+        <v>1.89470207691193</v>
       </c>
       <c r="H920" t="n">
         <v>4500</v>
@@ -27078,7 +27078,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G921" t="n">
-        <v>1.89470195770264</v>
+        <v>1.89470207691193</v>
       </c>
       <c r="H921" t="n">
         <v>0</v>
@@ -27107,7 +27107,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G922" t="n">
-        <v>1.89470195770264</v>
+        <v>1.89470207691193</v>
       </c>
       <c r="H922" t="n">
         <v>15000</v>
@@ -27136,7 +27136,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G923" t="n">
-        <v>1.82968783378601</v>
+        <v>1.82968771457672</v>
       </c>
       <c r="H923" t="n">
         <v>28500</v>
@@ -27165,7 +27165,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G924" t="n">
-        <v>1.773961186409</v>
+        <v>1.77396130561829</v>
       </c>
       <c r="H924" t="n">
         <v>147000</v>
@@ -27223,7 +27223,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G926" t="n">
-        <v>1.81111240386963</v>
+        <v>1.81111228466034</v>
       </c>
       <c r="H926" t="n">
         <v>6000</v>
@@ -27252,7 +27252,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G927" t="n">
-        <v>1.81111240386963</v>
+        <v>1.81111228466034</v>
       </c>
       <c r="H927" t="n">
         <v>4500</v>
@@ -27281,7 +27281,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G928" t="n">
-        <v>1.81111240386963</v>
+        <v>1.81111228466034</v>
       </c>
       <c r="H928" t="n">
         <v>1500</v>
@@ -27513,7 +27513,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G936" t="n">
-        <v>1.81111240386963</v>
+        <v>1.81111228466034</v>
       </c>
       <c r="H936" t="n">
         <v>7500</v>
@@ -27542,7 +27542,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G937" t="n">
-        <v>1.81111240386963</v>
+        <v>1.81111228466034</v>
       </c>
       <c r="H937" t="n">
         <v>1500</v>
@@ -27629,7 +27629,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G940" t="n">
-        <v>1.78324890136719</v>
+        <v>1.78324902057648</v>
       </c>
       <c r="H940" t="n">
         <v>3000</v>
@@ -27658,7 +27658,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G941" t="n">
-        <v>1.78324890136719</v>
+        <v>1.78324902057648</v>
       </c>
       <c r="H941" t="n">
         <v>6000</v>
@@ -27716,7 +27716,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G943" t="n">
-        <v>1.81111240386963</v>
+        <v>1.81111228466034</v>
       </c>
       <c r="H943" t="n">
         <v>3000</v>
@@ -27745,7 +27745,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G944" t="n">
-        <v>1.773961186409</v>
+        <v>1.77396130561829</v>
       </c>
       <c r="H944" t="n">
         <v>27000</v>
@@ -27774,7 +27774,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G945" t="n">
-        <v>1.773961186409</v>
+        <v>1.77396130561829</v>
       </c>
       <c r="H945" t="n">
         <v>3000</v>
@@ -27803,7 +27803,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G946" t="n">
-        <v>1.773961186409</v>
+        <v>1.77396130561829</v>
       </c>
       <c r="H946" t="n">
         <v>0</v>
@@ -27832,7 +27832,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G947" t="n">
-        <v>1.78324890136719</v>
+        <v>1.78324902057648</v>
       </c>
       <c r="H947" t="n">
         <v>4500</v>
@@ -27919,7 +27919,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G950" t="n">
-        <v>1.78324890136719</v>
+        <v>1.78324902057648</v>
       </c>
       <c r="H950" t="n">
         <v>6000</v>
@@ -27948,7 +27948,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G951" t="n">
-        <v>1.78324890136719</v>
+        <v>1.78324902057648</v>
       </c>
       <c r="H951" t="n">
         <v>1500</v>
@@ -28122,7 +28122,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G957" t="n">
-        <v>1.78324890136719</v>
+        <v>1.78324902057648</v>
       </c>
       <c r="H957" t="n">
         <v>3000</v>
@@ -28151,7 +28151,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G958" t="n">
-        <v>1.78324890136719</v>
+        <v>1.78324902057648</v>
       </c>
       <c r="H958" t="n">
         <v>1500</v>
@@ -28180,7 +28180,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G959" t="n">
-        <v>1.78324890136719</v>
+        <v>1.78324902057648</v>
       </c>
       <c r="H959" t="n">
         <v>1500</v>
@@ -28209,7 +28209,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G960" t="n">
-        <v>1.75538563728333</v>
+        <v>1.75538575649261</v>
       </c>
       <c r="H960" t="n">
         <v>9000</v>
@@ -28238,7 +28238,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G961" t="n">
-        <v>1.78324890136719</v>
+        <v>1.78324902057648</v>
       </c>
       <c r="H961" t="n">
         <v>4500</v>
@@ -28354,7 +28354,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G965" t="n">
-        <v>1.78324890136719</v>
+        <v>1.78324902057648</v>
       </c>
       <c r="H965" t="n">
         <v>13500</v>
@@ -28383,7 +28383,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G966" t="n">
-        <v>1.78324890136719</v>
+        <v>1.78324902057648</v>
       </c>
       <c r="H966" t="n">
         <v>4500</v>
@@ -28615,7 +28615,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G974" t="n">
-        <v>1.82040011882782</v>
+        <v>1.82039999961853</v>
       </c>
       <c r="H974" t="n">
         <v>13500</v>
@@ -28644,7 +28644,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G975" t="n">
-        <v>1.82040011882782</v>
+        <v>1.82039999961853</v>
       </c>
       <c r="H975" t="n">
         <v>0</v>
@@ -28673,7 +28673,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G976" t="n">
-        <v>1.82040011882782</v>
+        <v>1.82039999961853</v>
       </c>
       <c r="H976" t="n">
         <v>0</v>
@@ -28702,7 +28702,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G977" t="n">
-        <v>1.773961186409</v>
+        <v>1.77396130561829</v>
       </c>
       <c r="H977" t="n">
         <v>16500</v>
@@ -28818,7 +28818,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G981" t="n">
-        <v>1.78324890136719</v>
+        <v>1.78324902057648</v>
       </c>
       <c r="H981" t="n">
         <v>1500</v>
@@ -28847,7 +28847,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G982" t="n">
-        <v>1.78324890136719</v>
+        <v>1.78324902057648</v>
       </c>
       <c r="H982" t="n">
         <v>0</v>
@@ -28876,7 +28876,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G983" t="n">
-        <v>1.78324890136719</v>
+        <v>1.78324902057648</v>
       </c>
       <c r="H983" t="n">
         <v>0</v>
@@ -28934,7 +28934,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G985" t="n">
-        <v>1.78324890136719</v>
+        <v>1.78324902057648</v>
       </c>
       <c r="H985" t="n">
         <v>15000</v>
@@ -28992,7 +28992,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G987" t="n">
-        <v>1.81111240386963</v>
+        <v>1.81111228466034</v>
       </c>
       <c r="H987" t="n">
         <v>40500</v>
@@ -29021,7 +29021,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G988" t="n">
-        <v>1.82040011882782</v>
+        <v>1.82039999961853</v>
       </c>
       <c r="H988" t="n">
         <v>3000</v>
@@ -29050,7 +29050,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G989" t="n">
-        <v>1.78324890136719</v>
+        <v>1.78324902057648</v>
       </c>
       <c r="H989" t="n">
         <v>1500</v>
@@ -29137,7 +29137,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G992" t="n">
-        <v>1.75538563728333</v>
+        <v>1.75538575649261</v>
       </c>
       <c r="H992" t="n">
         <v>9000</v>
@@ -29166,7 +29166,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G993" t="n">
-        <v>1.75538563728333</v>
+        <v>1.75538575649261</v>
       </c>
       <c r="H993" t="n">
         <v>0</v>
@@ -29195,7 +29195,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G994" t="n">
-        <v>1.773961186409</v>
+        <v>1.77396130561829</v>
       </c>
       <c r="H994" t="n">
         <v>3000</v>
@@ -29224,7 +29224,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G995" t="n">
-        <v>1.773961186409</v>
+        <v>1.77396130561829</v>
       </c>
       <c r="H995" t="n">
         <v>0</v>
@@ -29630,7 +29630,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1009" t="n">
-        <v>1.773961186409</v>
+        <v>1.77396130561829</v>
       </c>
       <c r="H1009" t="n">
         <v>6000</v>
@@ -29659,7 +29659,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1010" t="n">
-        <v>1.773961186409</v>
+        <v>1.77396130561829</v>
       </c>
       <c r="H1010" t="n">
         <v>0</v>
@@ -29688,7 +29688,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.773961186409</v>
+        <v>1.77396130561829</v>
       </c>
       <c r="H1011" t="n">
         <v>0</v>
@@ -29746,7 +29746,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1013" t="n">
-        <v>1.773961186409</v>
+        <v>1.77396130561829</v>
       </c>
       <c r="H1013" t="n">
         <v>3000</v>
@@ -29862,7 +29862,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1017" t="n">
-        <v>1.773961186409</v>
+        <v>1.77396130561829</v>
       </c>
       <c r="H1017" t="n">
         <v>1500</v>
@@ -29891,7 +29891,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1018" t="n">
-        <v>1.773961186409</v>
+        <v>1.77396130561829</v>
       </c>
       <c r="H1018" t="n">
         <v>0</v>
@@ -29920,7 +29920,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1019" t="n">
-        <v>1.773961186409</v>
+        <v>1.77396130561829</v>
       </c>
       <c r="H1019" t="n">
         <v>0</v>
@@ -30355,7 +30355,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1034" t="n">
-        <v>1.75538563728333</v>
+        <v>1.75538575649261</v>
       </c>
       <c r="H1034" t="n">
         <v>13500</v>
@@ -30384,7 +30384,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.81111240386963</v>
+        <v>1.81111228466034</v>
       </c>
       <c r="H1035" t="n">
         <v>1500</v>
@@ -30616,7 +30616,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.78324890136719</v>
+        <v>1.78324902057648</v>
       </c>
       <c r="H1043" t="n">
         <v>4500</v>
@@ -30645,7 +30645,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1044" t="n">
-        <v>1.773961186409</v>
+        <v>1.77396130561829</v>
       </c>
       <c r="H1044" t="n">
         <v>3000</v>
@@ -30674,7 +30674,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1045" t="n">
-        <v>1.75538563728333</v>
+        <v>1.75538575649261</v>
       </c>
       <c r="H1045" t="n">
         <v>4500</v>
@@ -30703,7 +30703,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1046" t="n">
-        <v>1.773961186409</v>
+        <v>1.77396130561829</v>
       </c>
       <c r="H1046" t="n">
         <v>9000</v>
@@ -30732,7 +30732,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1047" t="n">
-        <v>1.773961186409</v>
+        <v>1.77396130561829</v>
       </c>
       <c r="H1047" t="n">
         <v>1500</v>
@@ -30819,7 +30819,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1050" t="n">
-        <v>1.75538563728333</v>
+        <v>1.75538575649261</v>
       </c>
       <c r="H1050" t="n">
         <v>1500</v>
@@ -30848,7 +30848,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1051" t="n">
-        <v>1.773961186409</v>
+        <v>1.77396130561829</v>
       </c>
       <c r="H1051" t="n">
         <v>4500</v>
@@ -31167,7 +31167,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1062" t="n">
-        <v>1.70894706249237</v>
+        <v>1.70894694328308</v>
       </c>
       <c r="H1062" t="n">
         <v>4500</v>
@@ -32153,7 +32153,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1096" t="n">
-        <v>1.60678160190582</v>
+        <v>1.60678172111511</v>
       </c>
       <c r="H1096" t="n">
         <v>10500</v>
@@ -32211,7 +32211,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1098" t="n">
-        <v>1.78324890136719</v>
+        <v>1.78324902057648</v>
       </c>
       <c r="H1098" t="n">
         <v>25500</v>
@@ -32240,7 +32240,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1099" t="n">
-        <v>1.773961186409</v>
+        <v>1.77396130561829</v>
       </c>
       <c r="H1099" t="n">
         <v>7500</v>
@@ -32269,7 +32269,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1100" t="n">
-        <v>1.75538563728333</v>
+        <v>1.75538575649261</v>
       </c>
       <c r="H1100" t="n">
         <v>6000</v>
@@ -32530,7 +32530,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1109" t="n">
-        <v>1.70894706249237</v>
+        <v>1.70894694328308</v>
       </c>
       <c r="H1109" t="n">
         <v>4500</v>
@@ -33168,7 +33168,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1131" t="n">
-        <v>1.70894706249237</v>
+        <v>1.70894694328308</v>
       </c>
       <c r="H1131" t="n">
         <v>1500</v>
@@ -33255,7 +33255,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1134" t="n">
-        <v>1.70894706249237</v>
+        <v>1.70894694328308</v>
       </c>
       <c r="H1134" t="n">
         <v>6000</v>
@@ -33284,7 +33284,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1135" t="n">
-        <v>1.70894706249237</v>
+        <v>1.70894694328308</v>
       </c>
       <c r="H1135" t="n">
         <v>0</v>
@@ -33951,7 +33951,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1158" t="n">
-        <v>1.65322029590607</v>
+        <v>1.65322041511536</v>
       </c>
       <c r="H1158" t="n">
         <v>3000</v>
@@ -34183,7 +34183,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1166" t="n">
-        <v>1.54176735877991</v>
+        <v>1.54176723957062</v>
       </c>
       <c r="H1166" t="n">
         <v>13500</v>
@@ -34212,7 +34212,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1167" t="n">
-        <v>1.54176735877991</v>
+        <v>1.54176723957062</v>
       </c>
       <c r="H1167" t="n">
         <v>0</v>
@@ -34241,7 +34241,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1168" t="n">
-        <v>1.54176735877991</v>
+        <v>1.54176723957062</v>
       </c>
       <c r="H1168" t="n">
         <v>0</v>
@@ -45557,6 +45557,35 @@
         <v>4500</v>
       </c>
       <c r="I1558" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1559">
+      <c r="A1559" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1559" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1559" t="n">
+        <v>1.50999999046326</v>
+      </c>
+      <c r="D1559" t="n">
+        <v>1.52999997138977</v>
+      </c>
+      <c r="E1559" t="n">
+        <v>1.50999999046326</v>
+      </c>
+      <c r="F1559" t="n">
+        <v>1.52999997138977</v>
+      </c>
+      <c r="G1559" t="n">
+        <v>1.52999997138977</v>
+      </c>
+      <c r="H1559" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I1559" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RETI.MI.xlsx
+++ b/data/RETI.MI.xlsx
@@ -485,7 +485,7 @@
         <v>0.879899978637695</v>
       </c>
       <c r="G4" t="n">
-        <v>0.751319646835327</v>
+        <v>0.751319766044617</v>
       </c>
       <c r="H4" t="n">
         <v>75000</v>
@@ -630,7 +630,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G9" t="n">
-        <v>0.732619941234589</v>
+        <v>0.732620000839233</v>
       </c>
       <c r="H9" t="n">
         <v>118500</v>
@@ -659,7 +659,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G10" t="n">
-        <v>0.72237354516983</v>
+        <v>0.722373604774475</v>
       </c>
       <c r="H10" t="n">
         <v>48000</v>
@@ -688,7 +688,7 @@
         <v>0.84799998998642</v>
       </c>
       <c r="G11" t="n">
-        <v>0.72408127784729</v>
+        <v>0.724081218242645</v>
       </c>
       <c r="H11" t="n">
         <v>39000</v>
@@ -775,7 +775,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G14" t="n">
-        <v>0.683095633983612</v>
+        <v>0.683095574378967</v>
       </c>
       <c r="H14" t="n">
         <v>18000</v>
@@ -804,7 +804,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G15" t="n">
-        <v>0.683095633983612</v>
+        <v>0.683095574378967</v>
       </c>
       <c r="H15" t="n">
         <v>42000</v>
@@ -862,7 +862,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G17" t="n">
-        <v>0.654063940048218</v>
+        <v>0.654063999652863</v>
       </c>
       <c r="H17" t="n">
         <v>25500</v>
@@ -949,7 +949,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G20" t="n">
-        <v>0.667725920677185</v>
+        <v>0.66772586107254</v>
       </c>
       <c r="H20" t="n">
         <v>72000</v>
@@ -978,7 +978,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G21" t="n">
-        <v>0.654063940048218</v>
+        <v>0.654063999652863</v>
       </c>
       <c r="H21" t="n">
         <v>132000</v>
@@ -1065,7 +1065,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G24" t="n">
-        <v>0.652356266975403</v>
+        <v>0.652356207370758</v>
       </c>
       <c r="H24" t="n">
         <v>10500</v>
@@ -1123,7 +1123,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G26" t="n">
-        <v>0.654063940048218</v>
+        <v>0.654063999652863</v>
       </c>
       <c r="H26" t="n">
         <v>27000</v>
@@ -1152,7 +1152,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G27" t="n">
-        <v>0.633571088314056</v>
+        <v>0.633571147918701</v>
       </c>
       <c r="H27" t="n">
         <v>43500</v>
@@ -1210,7 +1210,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G29" t="n">
-        <v>0.623324692249298</v>
+        <v>0.623324632644653</v>
       </c>
       <c r="H29" t="n">
         <v>46500</v>
@@ -1268,7 +1268,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G31" t="n">
-        <v>0.587462246417999</v>
+        <v>0.58746212720871</v>
       </c>
       <c r="H31" t="n">
         <v>78000</v>
@@ -1297,7 +1297,7 @@
         <v>0.73199999332428</v>
       </c>
       <c r="G32" t="n">
-        <v>0.625032484531403</v>
+        <v>0.625032424926758</v>
       </c>
       <c r="H32" t="n">
         <v>27000</v>
@@ -1326,7 +1326,7 @@
         <v>0.722000002861023</v>
       </c>
       <c r="G33" t="n">
-        <v>0.616493701934814</v>
+        <v>0.616493761539459</v>
       </c>
       <c r="H33" t="n">
         <v>3000</v>
@@ -1355,7 +1355,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G34" t="n">
-        <v>0.609662771224976</v>
+        <v>0.60966283082962</v>
       </c>
       <c r="H34" t="n">
         <v>13500</v>
@@ -1384,7 +1384,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G35" t="n">
-        <v>0.580631196498871</v>
+        <v>0.580631256103516</v>
       </c>
       <c r="H35" t="n">
         <v>12000</v>
@@ -1413,7 +1413,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G36" t="n">
-        <v>0.563553869724274</v>
+        <v>0.563553810119629</v>
       </c>
       <c r="H36" t="n">
         <v>66000</v>
@@ -1442,7 +1442,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G37" t="n">
-        <v>0.537937700748444</v>
+        <v>0.537937760353088</v>
       </c>
       <c r="H37" t="n">
         <v>27000</v>
@@ -1471,7 +1471,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G38" t="n">
-        <v>0.537937700748444</v>
+        <v>0.537937760353088</v>
       </c>
       <c r="H38" t="n">
         <v>13500</v>
@@ -1558,7 +1558,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G41" t="n">
-        <v>0.537937700748444</v>
+        <v>0.537937760353088</v>
       </c>
       <c r="H41" t="n">
         <v>16500</v>
@@ -1587,7 +1587,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G42" t="n">
-        <v>0.604539573192596</v>
+        <v>0.604539632797241</v>
       </c>
       <c r="H42" t="n">
         <v>127500</v>
@@ -1616,7 +1616,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G43" t="n">
-        <v>0.623324692249298</v>
+        <v>0.623324632644653</v>
       </c>
       <c r="H43" t="n">
         <v>138000</v>
@@ -1645,7 +1645,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G44" t="n">
-        <v>0.604539573192596</v>
+        <v>0.604539632797241</v>
       </c>
       <c r="H44" t="n">
         <v>64500</v>
@@ -1761,7 +1761,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G48" t="n">
-        <v>0.61137056350708</v>
+        <v>0.611370503902435</v>
       </c>
       <c r="H48" t="n">
         <v>21000</v>
@@ -1790,7 +1790,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G49" t="n">
-        <v>0.614785969257355</v>
+        <v>0.614786028862</v>
       </c>
       <c r="H49" t="n">
         <v>18000</v>
@@ -1848,7 +1848,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G51" t="n">
-        <v>0.614785969257355</v>
+        <v>0.614786028862</v>
       </c>
       <c r="H51" t="n">
         <v>22500</v>
@@ -1906,7 +1906,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G53" t="n">
-        <v>0.701880633831024</v>
+        <v>0.701880693435669</v>
       </c>
       <c r="H53" t="n">
         <v>70500</v>
@@ -1993,7 +1993,7 @@
         <v>0.815999984741211</v>
       </c>
       <c r="G56" t="n">
-        <v>0.696757435798645</v>
+        <v>0.69675749540329</v>
       </c>
       <c r="H56" t="n">
         <v>28500</v>
@@ -2051,7 +2051,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G58" t="n">
-        <v>0.703588485717773</v>
+        <v>0.703588426113129</v>
       </c>
       <c r="H58" t="n">
         <v>12000</v>
@@ -2080,7 +2080,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G59" t="n">
-        <v>0.683095633983612</v>
+        <v>0.683095574378967</v>
       </c>
       <c r="H59" t="n">
         <v>6000</v>
@@ -2109,7 +2109,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G60" t="n">
-        <v>0.683095633983612</v>
+        <v>0.683095574378967</v>
       </c>
       <c r="H60" t="n">
         <v>1500</v>
@@ -2138,7 +2138,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G61" t="n">
-        <v>0.683095633983612</v>
+        <v>0.683095574378967</v>
       </c>
       <c r="H61" t="n">
         <v>102000</v>
@@ -2225,7 +2225,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G64" t="n">
-        <v>0.683095633983612</v>
+        <v>0.683095574378967</v>
       </c>
       <c r="H64" t="n">
         <v>7500</v>
@@ -2254,7 +2254,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G65" t="n">
-        <v>0.667725920677185</v>
+        <v>0.66772586107254</v>
       </c>
       <c r="H65" t="n">
         <v>10500</v>
@@ -2312,7 +2312,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G67" t="n">
-        <v>0.683095633983612</v>
+        <v>0.683095574378967</v>
       </c>
       <c r="H67" t="n">
         <v>7500</v>
@@ -2341,7 +2341,7 @@
         <v>0.815999984741211</v>
       </c>
       <c r="G68" t="n">
-        <v>0.696757435798645</v>
+        <v>0.69675749540329</v>
       </c>
       <c r="H68" t="n">
         <v>7500</v>
@@ -2370,7 +2370,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G69" t="n">
-        <v>0.693341970443726</v>
+        <v>0.69334203004837</v>
       </c>
       <c r="H69" t="n">
         <v>15000</v>
@@ -2457,7 +2457,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G72" t="n">
-        <v>0.693341970443726</v>
+        <v>0.69334203004837</v>
       </c>
       <c r="H72" t="n">
         <v>3000</v>
@@ -2544,7 +2544,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G75" t="n">
-        <v>0.700172960758209</v>
+        <v>0.700172901153564</v>
       </c>
       <c r="H75" t="n">
         <v>73500</v>
@@ -2573,7 +2573,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G76" t="n">
-        <v>0.707003891468048</v>
+        <v>0.707003831863403</v>
       </c>
       <c r="H76" t="n">
         <v>7500</v>
@@ -2602,7 +2602,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G77" t="n">
-        <v>0.700172960758209</v>
+        <v>0.700172901153564</v>
       </c>
       <c r="H77" t="n">
         <v>22500</v>
@@ -2631,7 +2631,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G78" t="n">
-        <v>0.700172960758209</v>
+        <v>0.700172901153564</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
@@ -2689,7 +2689,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G80" t="n">
-        <v>0.717250287532806</v>
+        <v>0.717250347137451</v>
       </c>
       <c r="H80" t="n">
         <v>28500</v>
@@ -2776,7 +2776,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G83" t="n">
-        <v>0.715542554855347</v>
+        <v>0.715542614459991</v>
       </c>
       <c r="H83" t="n">
         <v>1500</v>
@@ -2805,7 +2805,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G84" t="n">
-        <v>0.717250287532806</v>
+        <v>0.717250347137451</v>
       </c>
       <c r="H84" t="n">
         <v>1500</v>
@@ -2834,7 +2834,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G85" t="n">
-        <v>0.715542554855347</v>
+        <v>0.715542614459991</v>
       </c>
       <c r="H85" t="n">
         <v>9000</v>
@@ -2863,7 +2863,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G86" t="n">
-        <v>0.700172960758209</v>
+        <v>0.700172901153564</v>
       </c>
       <c r="H86" t="n">
         <v>1500</v>
@@ -2892,7 +2892,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G87" t="n">
-        <v>0.688218772411346</v>
+        <v>0.688218712806702</v>
       </c>
       <c r="H87" t="n">
         <v>1500</v>
@@ -2921,7 +2921,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G88" t="n">
-        <v>0.700172960758209</v>
+        <v>0.700172901153564</v>
       </c>
       <c r="H88" t="n">
         <v>16500</v>
@@ -2950,7 +2950,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G89" t="n">
-        <v>0.684803307056427</v>
+        <v>0.684803247451782</v>
       </c>
       <c r="H89" t="n">
         <v>22500</v>
@@ -2979,7 +2979,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G90" t="n">
-        <v>0.684803307056427</v>
+        <v>0.684803247451782</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -3008,7 +3008,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G91" t="n">
-        <v>0.701880633831024</v>
+        <v>0.701880693435669</v>
       </c>
       <c r="H91" t="n">
         <v>10500</v>
@@ -3037,7 +3037,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G92" t="n">
-        <v>0.701880633831024</v>
+        <v>0.701880693435669</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
@@ -3066,7 +3066,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G93" t="n">
-        <v>0.701880633831024</v>
+        <v>0.701880693435669</v>
       </c>
       <c r="H93" t="n">
         <v>1500</v>
@@ -3124,7 +3124,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G95" t="n">
-        <v>0.683095633983612</v>
+        <v>0.683095574378967</v>
       </c>
       <c r="H95" t="n">
         <v>3000</v>
@@ -3182,7 +3182,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G97" t="n">
-        <v>0.667725920677185</v>
+        <v>0.66772586107254</v>
       </c>
       <c r="H97" t="n">
         <v>9000</v>
@@ -3327,7 +3327,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G102" t="n">
-        <v>0.683095633983612</v>
+        <v>0.683095574378967</v>
       </c>
       <c r="H102" t="n">
         <v>10500</v>
@@ -3356,7 +3356,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G103" t="n">
-        <v>0.707003891468048</v>
+        <v>0.707003831863403</v>
       </c>
       <c r="H103" t="n">
         <v>22500</v>
@@ -3385,7 +3385,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G104" t="n">
-        <v>0.683095633983612</v>
+        <v>0.683095574378967</v>
       </c>
       <c r="H104" t="n">
         <v>49500</v>
@@ -3414,7 +3414,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G105" t="n">
-        <v>0.683095633983612</v>
+        <v>0.683095574378967</v>
       </c>
       <c r="H105" t="n">
         <v>13500</v>
@@ -3443,7 +3443,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G106" t="n">
-        <v>0.683095633983612</v>
+        <v>0.683095574378967</v>
       </c>
       <c r="H106" t="n">
         <v>1500</v>
@@ -3501,7 +3501,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G108" t="n">
-        <v>0.700172960758209</v>
+        <v>0.700172901153564</v>
       </c>
       <c r="H108" t="n">
         <v>55500</v>
@@ -3530,7 +3530,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G109" t="n">
-        <v>0.683095633983612</v>
+        <v>0.683095574378967</v>
       </c>
       <c r="H109" t="n">
         <v>13500</v>
@@ -3588,7 +3588,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G111" t="n">
-        <v>0.703588485717773</v>
+        <v>0.703588426113129</v>
       </c>
       <c r="H111" t="n">
         <v>24000</v>
@@ -3675,7 +3675,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G114" t="n">
-        <v>0.700172960758209</v>
+        <v>0.700172901153564</v>
       </c>
       <c r="H114" t="n">
         <v>21000</v>
@@ -3704,7 +3704,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G115" t="n">
-        <v>0.703588485717773</v>
+        <v>0.703588426113129</v>
       </c>
       <c r="H115" t="n">
         <v>7500</v>
@@ -3762,7 +3762,7 @@
         <v>0.842000007629395</v>
       </c>
       <c r="G117" t="n">
-        <v>0.718958079814911</v>
+        <v>0.718958020210266</v>
       </c>
       <c r="H117" t="n">
         <v>102000</v>
@@ -3791,7 +3791,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G118" t="n">
-        <v>0.717250287532806</v>
+        <v>0.717250347137451</v>
       </c>
       <c r="H118" t="n">
         <v>69000</v>
@@ -3820,7 +3820,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G119" t="n">
-        <v>0.715542554855347</v>
+        <v>0.715542614459991</v>
       </c>
       <c r="H119" t="n">
         <v>16500</v>
@@ -3849,7 +3849,7 @@
         <v>0.867999970912933</v>
       </c>
       <c r="G120" t="n">
-        <v>0.741158723831177</v>
+        <v>0.741158664226532</v>
       </c>
       <c r="H120" t="n">
         <v>139500</v>
@@ -3878,7 +3878,7 @@
         <v>0.867999970912933</v>
       </c>
       <c r="G121" t="n">
-        <v>0.741158723831177</v>
+        <v>0.741158664226532</v>
       </c>
       <c r="H121" t="n">
         <v>151500</v>
@@ -3936,7 +3936,7 @@
         <v>0.972000002861023</v>
       </c>
       <c r="G123" t="n">
-        <v>0.829961061477661</v>
+        <v>0.829961121082306</v>
       </c>
       <c r="H123" t="n">
         <v>922500</v>
@@ -4081,7 +4081,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G128" t="n">
-        <v>0.86240816116333</v>
+        <v>0.862408101558685</v>
       </c>
       <c r="H128" t="n">
         <v>60000</v>
@@ -4110,7 +4110,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G129" t="n">
-        <v>0.86240816116333</v>
+        <v>0.862408101558685</v>
       </c>
       <c r="H129" t="n">
         <v>25500</v>
@@ -4139,7 +4139,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G130" t="n">
-        <v>0.86240816116333</v>
+        <v>0.862408101558685</v>
       </c>
       <c r="H130" t="n">
         <v>72000</v>
@@ -4168,7 +4168,7 @@
         <v>0.994000017642975</v>
       </c>
       <c r="G131" t="n">
-        <v>0.848746240139008</v>
+        <v>0.848746299743652</v>
       </c>
       <c r="H131" t="n">
         <v>60000</v>
@@ -4197,7 +4197,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G132" t="n">
-        <v>0.845330715179443</v>
+        <v>0.845330774784088</v>
       </c>
       <c r="H132" t="n">
         <v>25500</v>
@@ -4284,7 +4284,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G135" t="n">
-        <v>0.866677463054657</v>
+        <v>0.866677522659302</v>
       </c>
       <c r="H135" t="n">
         <v>15000</v>
@@ -4313,7 +4313,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G136" t="n">
-        <v>0.900832235813141</v>
+        <v>0.900832295417786</v>
       </c>
       <c r="H136" t="n">
         <v>127500</v>
@@ -4371,7 +4371,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G138" t="n">
-        <v>0.892293572425842</v>
+        <v>0.892293512821198</v>
       </c>
       <c r="H138" t="n">
         <v>82500</v>
@@ -4516,7 +4516,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G143" t="n">
-        <v>0.930717647075653</v>
+        <v>0.930717766284943</v>
       </c>
       <c r="H143" t="n">
         <v>45000</v>
@@ -4632,7 +4632,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G147" t="n">
-        <v>1.20395588874817</v>
+        <v>1.20395600795746</v>
       </c>
       <c r="H147" t="n">
         <v>510000</v>
@@ -4661,7 +4661,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G148" t="n">
-        <v>1.20395588874817</v>
+        <v>1.20395600795746</v>
       </c>
       <c r="H148" t="n">
         <v>210000</v>
@@ -4690,7 +4690,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G149" t="n">
-        <v>1.20395588874817</v>
+        <v>1.20395600795746</v>
       </c>
       <c r="H149" t="n">
         <v>172500</v>
@@ -4719,7 +4719,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G150" t="n">
-        <v>1.18638002872467</v>
+        <v>1.18637979030609</v>
       </c>
       <c r="H150" t="n">
         <v>103500</v>
@@ -4777,7 +4777,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G152" t="n">
-        <v>1.22153174877167</v>
+        <v>1.22153186798096</v>
       </c>
       <c r="H152" t="n">
         <v>57000</v>
@@ -4806,7 +4806,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G153" t="n">
-        <v>1.22153174877167</v>
+        <v>1.22153186798096</v>
       </c>
       <c r="H153" t="n">
         <v>157500</v>
@@ -4864,7 +4864,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G155" t="n">
-        <v>1.13804590702057</v>
+        <v>1.13804602622986</v>
       </c>
       <c r="H155" t="n">
         <v>30000</v>
@@ -4980,7 +4980,7 @@
         <v>1.25499999523163</v>
       </c>
       <c r="G159" t="n">
-        <v>1.1028938293457</v>
+        <v>1.10289394855499</v>
       </c>
       <c r="H159" t="n">
         <v>19500</v>
@@ -5154,7 +5154,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G165" t="n">
-        <v>1.1688038110733</v>
+        <v>1.16880393028259</v>
       </c>
       <c r="H165" t="n">
         <v>52500</v>
@@ -5183,7 +5183,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G166" t="n">
-        <v>1.1600159406662</v>
+        <v>1.16001582145691</v>
       </c>
       <c r="H166" t="n">
         <v>49500</v>
@@ -5328,7 +5328,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G171" t="n">
-        <v>1.13804590702057</v>
+        <v>1.13804602622986</v>
       </c>
       <c r="H171" t="n">
         <v>9000</v>
@@ -5386,7 +5386,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G173" t="n">
-        <v>1.18638002872467</v>
+        <v>1.18637979030609</v>
       </c>
       <c r="H173" t="n">
         <v>85500</v>
@@ -5444,7 +5444,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G175" t="n">
-        <v>1.23031985759735</v>
+        <v>1.23031997680664</v>
       </c>
       <c r="H175" t="n">
         <v>234000</v>
@@ -5473,7 +5473,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G176" t="n">
-        <v>1.32259380817413</v>
+        <v>1.32259392738342</v>
       </c>
       <c r="H176" t="n">
         <v>226500</v>
@@ -5502,7 +5502,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G177" t="n">
-        <v>1.32259380817413</v>
+        <v>1.32259392738342</v>
       </c>
       <c r="H177" t="n">
         <v>208500</v>
@@ -5589,7 +5589,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G180" t="n">
-        <v>1.3489578962326</v>
+        <v>1.34895777702332</v>
       </c>
       <c r="H180" t="n">
         <v>9000</v>
@@ -5676,7 +5676,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G183" t="n">
-        <v>1.283047914505</v>
+        <v>1.28304779529572</v>
       </c>
       <c r="H183" t="n">
         <v>180000</v>
@@ -5705,7 +5705,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G184" t="n">
-        <v>1.32259380817413</v>
+        <v>1.32259392738342</v>
       </c>
       <c r="H184" t="n">
         <v>30000</v>
@@ -5821,7 +5821,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G188" t="n">
-        <v>1.3489578962326</v>
+        <v>1.34895777702332</v>
       </c>
       <c r="H188" t="n">
         <v>36000</v>
@@ -5937,7 +5937,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G192" t="n">
-        <v>1.37971591949463</v>
+        <v>1.37971580028534</v>
       </c>
       <c r="H192" t="n">
         <v>87000</v>
@@ -5966,7 +5966,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G193" t="n">
-        <v>1.3489578962326</v>
+        <v>1.34895777702332</v>
       </c>
       <c r="H193" t="n">
         <v>34500</v>
@@ -6053,7 +6053,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G196" t="n">
-        <v>1.33138179779053</v>
+        <v>1.33138191699982</v>
       </c>
       <c r="H196" t="n">
         <v>66000</v>
@@ -6082,7 +6082,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G197" t="n">
-        <v>1.32259380817413</v>
+        <v>1.32259392738342</v>
       </c>
       <c r="H197" t="n">
         <v>43500</v>
@@ -6111,7 +6111,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G198" t="n">
-        <v>1.32698774337769</v>
+        <v>1.32698798179626</v>
       </c>
       <c r="H198" t="n">
         <v>13500</v>
@@ -6169,7 +6169,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G200" t="n">
-        <v>1.3489578962326</v>
+        <v>1.34895777702332</v>
       </c>
       <c r="H200" t="n">
         <v>22500</v>
@@ -6285,7 +6285,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G204" t="n">
-        <v>1.33138179779053</v>
+        <v>1.33138191699982</v>
       </c>
       <c r="H204" t="n">
         <v>6000</v>
@@ -6488,7 +6488,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G211" t="n">
-        <v>1.29183602333069</v>
+        <v>1.2918359041214</v>
       </c>
       <c r="H211" t="n">
         <v>45000</v>
@@ -6575,7 +6575,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G214" t="n">
-        <v>1.3489578962326</v>
+        <v>1.34895777702332</v>
       </c>
       <c r="H214" t="n">
         <v>28500</v>
@@ -6604,7 +6604,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G215" t="n">
-        <v>1.32698774337769</v>
+        <v>1.32698798179626</v>
       </c>
       <c r="H215" t="n">
         <v>13500</v>
@@ -6691,7 +6691,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G218" t="n">
-        <v>1.24789583683014</v>
+        <v>1.24789571762085</v>
       </c>
       <c r="H218" t="n">
         <v>33000</v>
@@ -6720,7 +6720,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G219" t="n">
-        <v>1.23031985759735</v>
+        <v>1.23031997680664</v>
       </c>
       <c r="H219" t="n">
         <v>70500</v>
@@ -6778,7 +6778,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G221" t="n">
-        <v>1.28744184970856</v>
+        <v>1.28744196891785</v>
       </c>
       <c r="H221" t="n">
         <v>15000</v>
@@ -6807,7 +6807,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G222" t="n">
-        <v>1.29183602333069</v>
+        <v>1.2918359041214</v>
       </c>
       <c r="H222" t="n">
         <v>9000</v>
@@ -6981,7 +6981,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G228" t="n">
-        <v>1.29183602333069</v>
+        <v>1.2918359041214</v>
       </c>
       <c r="H228" t="n">
         <v>27000</v>
@@ -7010,7 +7010,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G229" t="n">
-        <v>1.27425980567932</v>
+        <v>1.27425992488861</v>
       </c>
       <c r="H229" t="n">
         <v>6000</v>
@@ -7068,7 +7068,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G231" t="n">
-        <v>1.283047914505</v>
+        <v>1.28304779529572</v>
       </c>
       <c r="H231" t="n">
         <v>4500</v>
@@ -7213,7 +7213,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G236" t="n">
-        <v>1.3489578962326</v>
+        <v>1.34895777702332</v>
       </c>
       <c r="H236" t="n">
         <v>13500</v>
@@ -7329,7 +7329,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G240" t="n">
-        <v>1.74881172180176</v>
+        <v>1.74881184101105</v>
       </c>
       <c r="H240" t="n">
         <v>333000</v>
@@ -7416,7 +7416,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G243" t="n">
-        <v>2.2321515083313</v>
+        <v>2.23215174674988</v>
       </c>
       <c r="H243" t="n">
         <v>702000</v>
@@ -7445,7 +7445,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G244" t="n">
-        <v>2.52215552330017</v>
+        <v>2.52215576171875</v>
       </c>
       <c r="H244" t="n">
         <v>1464000</v>
@@ -7503,7 +7503,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G246" t="n">
-        <v>2.27609181404114</v>
+        <v>2.27609205245972</v>
       </c>
       <c r="H246" t="n">
         <v>229500</v>
@@ -7561,7 +7561,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G248" t="n">
-        <v>2.27609181404114</v>
+        <v>2.27609205245972</v>
       </c>
       <c r="H248" t="n">
         <v>240000</v>
@@ -7590,7 +7590,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G249" t="n">
-        <v>2.20578765869141</v>
+        <v>2.20578789710999</v>
       </c>
       <c r="H249" t="n">
         <v>195000</v>
@@ -7619,7 +7619,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G250" t="n">
-        <v>2.2321515083313</v>
+        <v>2.23215174674988</v>
       </c>
       <c r="H250" t="n">
         <v>102000</v>
@@ -7648,7 +7648,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G251" t="n">
-        <v>2.1882119178772</v>
+        <v>2.18821167945862</v>
       </c>
       <c r="H251" t="n">
         <v>40500</v>
@@ -7677,7 +7677,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G252" t="n">
-        <v>2.1882119178772</v>
+        <v>2.18821167945862</v>
       </c>
       <c r="H252" t="n">
         <v>36000</v>
@@ -7706,7 +7706,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G253" t="n">
-        <v>2.3288197517395</v>
+        <v>2.32881999015808</v>
       </c>
       <c r="H253" t="n">
         <v>237000</v>
@@ -7735,7 +7735,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G254" t="n">
-        <v>2.34639573097229</v>
+        <v>2.34639596939087</v>
       </c>
       <c r="H254" t="n">
         <v>139500</v>
@@ -7764,7 +7764,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G255" t="n">
-        <v>2.33760762214661</v>
+        <v>2.33760786056519</v>
       </c>
       <c r="H255" t="n">
         <v>108000</v>
@@ -7793,7 +7793,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G256" t="n">
-        <v>2.3288197517395</v>
+        <v>2.32881999015808</v>
       </c>
       <c r="H256" t="n">
         <v>75000</v>
@@ -8025,7 +8025,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G264" t="n">
-        <v>2.20578765869141</v>
+        <v>2.20578789710999</v>
       </c>
       <c r="H264" t="n">
         <v>37500</v>
@@ -8054,7 +8054,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G265" t="n">
-        <v>2.34639573097229</v>
+        <v>2.34639596939087</v>
       </c>
       <c r="H265" t="n">
         <v>46500</v>
@@ -8112,7 +8112,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G267" t="n">
-        <v>2.27609181404114</v>
+        <v>2.27609205245972</v>
       </c>
       <c r="H267" t="n">
         <v>61500</v>
@@ -8141,7 +8141,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G268" t="n">
-        <v>2.38154792785645</v>
+        <v>2.38154768943787</v>
       </c>
       <c r="H268" t="n">
         <v>88500</v>
@@ -8199,7 +8199,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G270" t="n">
-        <v>2.2321515083313</v>
+        <v>2.23215174674988</v>
       </c>
       <c r="H270" t="n">
         <v>97500</v>
@@ -8286,7 +8286,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G273" t="n">
-        <v>2.27609181404114</v>
+        <v>2.27609205245972</v>
       </c>
       <c r="H273" t="n">
         <v>94500</v>
@@ -8431,7 +8431,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G278" t="n">
-        <v>2.3288197517395</v>
+        <v>2.32881999015808</v>
       </c>
       <c r="H278" t="n">
         <v>33000</v>
@@ -8460,7 +8460,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G279" t="n">
-        <v>2.3200318813324</v>
+        <v>2.32003164291382</v>
       </c>
       <c r="H279" t="n">
         <v>10500</v>
@@ -8518,7 +8518,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G281" t="n">
-        <v>2.3288197517395</v>
+        <v>2.32881999015808</v>
       </c>
       <c r="H281" t="n">
         <v>25500</v>
@@ -8605,7 +8605,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G284" t="n">
-        <v>2.3200318813324</v>
+        <v>2.32003164291382</v>
       </c>
       <c r="H284" t="n">
         <v>18000</v>
@@ -8634,7 +8634,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G285" t="n">
-        <v>2.27609181404114</v>
+        <v>2.27609205245972</v>
       </c>
       <c r="H285" t="n">
         <v>24000</v>
@@ -8750,7 +8750,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G289" t="n">
-        <v>2.3200318813324</v>
+        <v>2.32003164291382</v>
       </c>
       <c r="H289" t="n">
         <v>87000</v>
@@ -8808,7 +8808,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G291" t="n">
-        <v>2.27609181404114</v>
+        <v>2.27609205245972</v>
       </c>
       <c r="H291" t="n">
         <v>18000</v>
@@ -8953,7 +8953,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G296" t="n">
-        <v>2.2321515083313</v>
+        <v>2.23215174674988</v>
       </c>
       <c r="H296" t="n">
         <v>7500</v>
@@ -9069,7 +9069,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G300" t="n">
-        <v>2.20578765869141</v>
+        <v>2.20578789710999</v>
       </c>
       <c r="H300" t="n">
         <v>24000</v>
@@ -9127,7 +9127,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G302" t="n">
-        <v>2.14427185058594</v>
+        <v>2.14427208900452</v>
       </c>
       <c r="H302" t="n">
         <v>31500</v>
@@ -9185,7 +9185,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G304" t="n">
-        <v>2.03881597518921</v>
+        <v>2.03881573677063</v>
       </c>
       <c r="H304" t="n">
         <v>51000</v>
@@ -9214,7 +9214,7 @@
         <v>2.25</v>
       </c>
       <c r="G305" t="n">
-        <v>1.97729980945587</v>
+        <v>1.97729969024658</v>
       </c>
       <c r="H305" t="n">
         <v>51000</v>
@@ -9243,7 +9243,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G306" t="n">
-        <v>1.99487578868866</v>
+        <v>1.99487566947937</v>
       </c>
       <c r="H306" t="n">
         <v>13500</v>
@@ -9272,7 +9272,7 @@
         <v>2.25</v>
       </c>
       <c r="G307" t="n">
-        <v>1.97729980945587</v>
+        <v>1.97729969024658</v>
       </c>
       <c r="H307" t="n">
         <v>13500</v>
@@ -9301,7 +9301,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G308" t="n">
-        <v>2.02123951911926</v>
+        <v>2.02123975753784</v>
       </c>
       <c r="H308" t="n">
         <v>12000</v>
@@ -9330,7 +9330,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G309" t="n">
-        <v>1.9333598613739</v>
+        <v>1.93335998058319</v>
       </c>
       <c r="H309" t="n">
         <v>18000</v>
@@ -9388,7 +9388,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G311" t="n">
-        <v>1.88941991329193</v>
+        <v>1.88941979408264</v>
       </c>
       <c r="H311" t="n">
         <v>34500</v>
@@ -9417,7 +9417,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G312" t="n">
-        <v>1.82790374755859</v>
+        <v>1.8279036283493</v>
       </c>
       <c r="H312" t="n">
         <v>37500</v>
@@ -9446,7 +9446,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G313" t="n">
-        <v>1.9333598613739</v>
+        <v>1.93335998058319</v>
       </c>
       <c r="H313" t="n">
         <v>18000</v>
@@ -9475,7 +9475,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G314" t="n">
-        <v>1.9333598613739</v>
+        <v>1.93335998058319</v>
       </c>
       <c r="H314" t="n">
         <v>6000</v>
@@ -9504,7 +9504,7 @@
         <v>2.25</v>
       </c>
       <c r="G315" t="n">
-        <v>1.97729980945587</v>
+        <v>1.97729969024658</v>
       </c>
       <c r="H315" t="n">
         <v>25500</v>
@@ -9649,7 +9649,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G320" t="n">
-        <v>2.14427185058594</v>
+        <v>2.14427208900452</v>
       </c>
       <c r="H320" t="n">
         <v>9000</v>
@@ -9678,7 +9678,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G321" t="n">
-        <v>2.14427185058594</v>
+        <v>2.14427208900452</v>
       </c>
       <c r="H321" t="n">
         <v>3000</v>
@@ -9707,7 +9707,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G322" t="n">
-        <v>2.10033178329468</v>
+        <v>2.10033202171326</v>
       </c>
       <c r="H322" t="n">
         <v>3000</v>
@@ -9736,7 +9736,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G323" t="n">
-        <v>2.10033178329468</v>
+        <v>2.10033202171326</v>
       </c>
       <c r="H323" t="n">
         <v>0</v>
@@ -9823,7 +9823,7 @@
         <v>2.25</v>
       </c>
       <c r="G326" t="n">
-        <v>1.97729980945587</v>
+        <v>1.97729969024658</v>
       </c>
       <c r="H326" t="n">
         <v>48000</v>
@@ -9852,7 +9852,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G327" t="n">
-        <v>1.91578376293182</v>
+        <v>1.9157840013504</v>
       </c>
       <c r="H327" t="n">
         <v>24000</v>
@@ -9881,7 +9881,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G328" t="n">
-        <v>1.88941991329193</v>
+        <v>1.88941979408264</v>
       </c>
       <c r="H328" t="n">
         <v>31500</v>
@@ -9968,7 +9968,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G331" t="n">
-        <v>1.99487578868866</v>
+        <v>1.99487566947937</v>
       </c>
       <c r="H331" t="n">
         <v>12000</v>
@@ -9997,7 +9997,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G332" t="n">
-        <v>1.99487578868866</v>
+        <v>1.99487566947937</v>
       </c>
       <c r="H332" t="n">
         <v>7500</v>
@@ -10026,7 +10026,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G333" t="n">
-        <v>1.99487578868866</v>
+        <v>1.99487566947937</v>
       </c>
       <c r="H333" t="n">
         <v>6000</v>
@@ -10055,7 +10055,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G334" t="n">
-        <v>2.03881597518921</v>
+        <v>2.03881573677063</v>
       </c>
       <c r="H334" t="n">
         <v>7500</v>
@@ -10113,7 +10113,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G336" t="n">
-        <v>2.02123951911926</v>
+        <v>2.02123975753784</v>
       </c>
       <c r="H336" t="n">
         <v>10500</v>
@@ -10171,7 +10171,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G338" t="n">
-        <v>2.056391954422</v>
+        <v>2.05639171600342</v>
       </c>
       <c r="H338" t="n">
         <v>3000</v>
@@ -10229,7 +10229,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G340" t="n">
-        <v>2.03881597518921</v>
+        <v>2.03881573677063</v>
       </c>
       <c r="H340" t="n">
         <v>3000</v>
@@ -10345,7 +10345,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G344" t="n">
-        <v>1.95972371101379</v>
+        <v>1.9597235918045</v>
       </c>
       <c r="H344" t="n">
         <v>27000</v>
@@ -10432,7 +10432,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G347" t="n">
-        <v>1.9685115814209</v>
+        <v>1.96851170063019</v>
       </c>
       <c r="H347" t="n">
         <v>15000</v>
@@ -10461,7 +10461,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G348" t="n">
-        <v>1.9333598613739</v>
+        <v>1.93335998058319</v>
       </c>
       <c r="H348" t="n">
         <v>1500</v>
@@ -10606,7 +10606,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G353" t="n">
-        <v>1.88941991329193</v>
+        <v>1.88941979408264</v>
       </c>
       <c r="H353" t="n">
         <v>7500</v>
@@ -10635,7 +10635,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G354" t="n">
-        <v>1.85426771640778</v>
+        <v>1.85426783561707</v>
       </c>
       <c r="H354" t="n">
         <v>13500</v>
@@ -10664,7 +10664,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G355" t="n">
-        <v>1.9245719909668</v>
+        <v>1.92457187175751</v>
       </c>
       <c r="H355" t="n">
         <v>13500</v>
@@ -10722,7 +10722,7 @@
         <v>2.25</v>
       </c>
       <c r="G357" t="n">
-        <v>1.97729980945587</v>
+        <v>1.97729969024658</v>
       </c>
       <c r="H357" t="n">
         <v>7500</v>
@@ -10751,7 +10751,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G358" t="n">
-        <v>2.03881597518921</v>
+        <v>2.03881573677063</v>
       </c>
       <c r="H358" t="n">
         <v>10500</v>
@@ -10838,7 +10838,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G361" t="n">
-        <v>1.99487578868866</v>
+        <v>1.99487566947937</v>
       </c>
       <c r="H361" t="n">
         <v>15000</v>
@@ -10867,7 +10867,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G362" t="n">
-        <v>1.99487578868866</v>
+        <v>1.99487566947937</v>
       </c>
       <c r="H362" t="n">
         <v>6000</v>
@@ -10896,7 +10896,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G363" t="n">
-        <v>1.9685115814209</v>
+        <v>1.96851170063019</v>
       </c>
       <c r="H363" t="n">
         <v>3000</v>
@@ -10983,7 +10983,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G366" t="n">
-        <v>1.9333598613739</v>
+        <v>1.93335998058319</v>
       </c>
       <c r="H366" t="n">
         <v>13500</v>
@@ -11012,7 +11012,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G367" t="n">
-        <v>1.9333598613739</v>
+        <v>1.93335998058319</v>
       </c>
       <c r="H367" t="n">
         <v>1500</v>
@@ -11070,7 +11070,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G369" t="n">
-        <v>1.98608791828156</v>
+        <v>1.98608779907227</v>
       </c>
       <c r="H369" t="n">
         <v>25500</v>
@@ -11099,7 +11099,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G370" t="n">
-        <v>1.9333598613739</v>
+        <v>1.93335998058319</v>
       </c>
       <c r="H370" t="n">
         <v>6000</v>
@@ -11128,7 +11128,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G371" t="n">
-        <v>1.9333598613739</v>
+        <v>1.93335998058319</v>
       </c>
       <c r="H371" t="n">
         <v>1500</v>
@@ -11157,7 +11157,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G372" t="n">
-        <v>1.98608791828156</v>
+        <v>1.98608779907227</v>
       </c>
       <c r="H372" t="n">
         <v>7500</v>
@@ -11186,7 +11186,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G373" t="n">
-        <v>1.95093584060669</v>
+        <v>1.9509357213974</v>
       </c>
       <c r="H373" t="n">
         <v>3000</v>
@@ -11244,7 +11244,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G375" t="n">
-        <v>1.85426771640778</v>
+        <v>1.85426783561707</v>
       </c>
       <c r="H375" t="n">
         <v>15000</v>
@@ -11273,7 +11273,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G376" t="n">
-        <v>1.88063192367554</v>
+        <v>1.88063180446625</v>
       </c>
       <c r="H376" t="n">
         <v>9000</v>
@@ -11302,7 +11302,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G377" t="n">
-        <v>1.88063192367554</v>
+        <v>1.88063180446625</v>
       </c>
       <c r="H377" t="n">
         <v>3000</v>
@@ -11331,7 +11331,7 @@
         <v>2.25</v>
       </c>
       <c r="G378" t="n">
-        <v>1.97729980945587</v>
+        <v>1.97729969024658</v>
       </c>
       <c r="H378" t="n">
         <v>16500</v>
@@ -11360,7 +11360,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G379" t="n">
-        <v>1.9333598613739</v>
+        <v>1.93335998058319</v>
       </c>
       <c r="H379" t="n">
         <v>3000</v>
@@ -11389,7 +11389,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G380" t="n">
-        <v>1.62577986717224</v>
+        <v>1.62577974796295</v>
       </c>
       <c r="H380" t="n">
         <v>43500</v>
@@ -11447,7 +11447,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G382" t="n">
-        <v>1.80153977870941</v>
+        <v>1.80153965950012</v>
       </c>
       <c r="H382" t="n">
         <v>21000</v>
@@ -11476,7 +11476,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G383" t="n">
-        <v>1.86305570602417</v>
+        <v>1.86305558681488</v>
       </c>
       <c r="H383" t="n">
         <v>21000</v>
@@ -11505,7 +11505,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G384" t="n">
-        <v>1.86305570602417</v>
+        <v>1.86305558681488</v>
       </c>
       <c r="H384" t="n">
         <v>1500</v>
@@ -11534,7 +11534,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G385" t="n">
-        <v>1.88063192367554</v>
+        <v>1.88063180446625</v>
       </c>
       <c r="H385" t="n">
         <v>13500</v>
@@ -11563,7 +11563,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G386" t="n">
-        <v>1.99487578868866</v>
+        <v>1.99487566947937</v>
       </c>
       <c r="H386" t="n">
         <v>15000</v>
@@ -11621,7 +11621,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G388" t="n">
-        <v>1.99487578868866</v>
+        <v>1.99487566947937</v>
       </c>
       <c r="H388" t="n">
         <v>9000</v>
@@ -11650,7 +11650,7 @@
         <v>2.25</v>
       </c>
       <c r="G389" t="n">
-        <v>1.97729980945587</v>
+        <v>1.97729969024658</v>
       </c>
       <c r="H389" t="n">
         <v>6000</v>
@@ -11679,7 +11679,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G390" t="n">
-        <v>1.9333598613739</v>
+        <v>1.93335998058319</v>
       </c>
       <c r="H390" t="n">
         <v>1500</v>
@@ -11708,7 +11708,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G391" t="n">
-        <v>1.9685115814209</v>
+        <v>1.96851170063019</v>
       </c>
       <c r="H391" t="n">
         <v>9000</v>
@@ -11737,7 +11737,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G392" t="n">
-        <v>1.98608791828156</v>
+        <v>1.98608779907227</v>
       </c>
       <c r="H392" t="n">
         <v>6000</v>
@@ -11766,7 +11766,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G393" t="n">
-        <v>1.98608791828156</v>
+        <v>1.98608779907227</v>
       </c>
       <c r="H393" t="n">
         <v>0</v>
@@ -11795,7 +11795,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G394" t="n">
-        <v>1.9245719909668</v>
+        <v>1.92457187175751</v>
       </c>
       <c r="H394" t="n">
         <v>12000</v>
@@ -11824,7 +11824,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G395" t="n">
-        <v>1.99487578868866</v>
+        <v>1.99487566947937</v>
       </c>
       <c r="H395" t="n">
         <v>31500</v>
@@ -11911,7 +11911,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G398" t="n">
-        <v>2.056391954422</v>
+        <v>2.05639171600342</v>
       </c>
       <c r="H398" t="n">
         <v>10500</v>
@@ -11940,7 +11940,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G399" t="n">
-        <v>1.98608791828156</v>
+        <v>1.98608779907227</v>
       </c>
       <c r="H399" t="n">
         <v>6000</v>
@@ -11969,7 +11969,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G400" t="n">
-        <v>2.02123951911926</v>
+        <v>2.02123975753784</v>
       </c>
       <c r="H400" t="n">
         <v>10500</v>
@@ -12027,7 +12027,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G402" t="n">
-        <v>2.056391954422</v>
+        <v>2.05639171600342</v>
       </c>
       <c r="H402" t="n">
         <v>36000</v>
@@ -12056,7 +12056,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G403" t="n">
-        <v>1.9333598613739</v>
+        <v>1.93335998058319</v>
       </c>
       <c r="H403" t="n">
         <v>7500</v>
@@ -12085,7 +12085,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G404" t="n">
-        <v>1.9685115814209</v>
+        <v>1.96851170063019</v>
       </c>
       <c r="H404" t="n">
         <v>22500</v>
@@ -12114,7 +12114,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G405" t="n">
-        <v>1.98608791828156</v>
+        <v>1.98608779907227</v>
       </c>
       <c r="H405" t="n">
         <v>16500</v>
@@ -12143,7 +12143,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G406" t="n">
-        <v>1.98608791828156</v>
+        <v>1.98608779907227</v>
       </c>
       <c r="H406" t="n">
         <v>0</v>
@@ -12172,7 +12172,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G407" t="n">
-        <v>1.84547984600067</v>
+        <v>1.84547972679138</v>
       </c>
       <c r="H407" t="n">
         <v>64500</v>
@@ -12230,7 +12230,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G409" t="n">
-        <v>1.88941991329193</v>
+        <v>1.88941979408264</v>
       </c>
       <c r="H409" t="n">
         <v>6000</v>
@@ -12259,7 +12259,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G410" t="n">
-        <v>1.88941991329193</v>
+        <v>1.88941979408264</v>
       </c>
       <c r="H410" t="n">
         <v>0</v>
@@ -12288,7 +12288,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G411" t="n">
-        <v>1.87184393405914</v>
+        <v>1.87184405326843</v>
       </c>
       <c r="H411" t="n">
         <v>4500</v>
@@ -12317,7 +12317,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G412" t="n">
-        <v>1.88063192367554</v>
+        <v>1.88063180446625</v>
       </c>
       <c r="H412" t="n">
         <v>9000</v>
@@ -12346,7 +12346,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G413" t="n">
-        <v>1.88063192367554</v>
+        <v>1.88063180446625</v>
       </c>
       <c r="H413" t="n">
         <v>0</v>
@@ -12462,7 +12462,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G417" t="n">
-        <v>1.86305570602417</v>
+        <v>1.86305558681488</v>
       </c>
       <c r="H417" t="n">
         <v>6000</v>
@@ -12520,7 +12520,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G419" t="n">
-        <v>1.91578376293182</v>
+        <v>1.9157840013504</v>
       </c>
       <c r="H419" t="n">
         <v>18000</v>
@@ -12578,7 +12578,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G421" t="n">
-        <v>1.91578376293182</v>
+        <v>1.9157840013504</v>
       </c>
       <c r="H421" t="n">
         <v>1500</v>
@@ -12607,7 +12607,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G422" t="n">
-        <v>1.80153977870941</v>
+        <v>1.80153965950012</v>
       </c>
       <c r="H422" t="n">
         <v>25500</v>
@@ -12752,7 +12752,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G427" t="n">
-        <v>1.76638793945312</v>
+        <v>1.76638782024384</v>
       </c>
       <c r="H427" t="n">
         <v>4500</v>
@@ -12781,7 +12781,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G428" t="n">
-        <v>1.76638793945312</v>
+        <v>1.76638782024384</v>
       </c>
       <c r="H428" t="n">
         <v>3000</v>
@@ -12810,7 +12810,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G429" t="n">
-        <v>1.76638793945312</v>
+        <v>1.76638782024384</v>
       </c>
       <c r="H429" t="n">
         <v>3000</v>
@@ -12839,7 +12839,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G430" t="n">
-        <v>1.76638793945312</v>
+        <v>1.76638782024384</v>
       </c>
       <c r="H430" t="n">
         <v>4500</v>
@@ -12868,7 +12868,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G431" t="n">
-        <v>1.84547984600067</v>
+        <v>1.84547972679138</v>
       </c>
       <c r="H431" t="n">
         <v>6000</v>
@@ -12926,7 +12926,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G433" t="n">
-        <v>1.86305570602417</v>
+        <v>1.86305558681488</v>
       </c>
       <c r="H433" t="n">
         <v>7500</v>
@@ -12955,7 +12955,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G434" t="n">
-        <v>1.86305570602417</v>
+        <v>1.86305558681488</v>
       </c>
       <c r="H434" t="n">
         <v>0</v>
@@ -12984,7 +12984,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G435" t="n">
-        <v>1.86305570602417</v>
+        <v>1.86305558681488</v>
       </c>
       <c r="H435" t="n">
         <v>3000</v>
@@ -13013,7 +13013,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G436" t="n">
-        <v>1.88063192367554</v>
+        <v>1.88063180446625</v>
       </c>
       <c r="H436" t="n">
         <v>3000</v>
@@ -13042,7 +13042,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G437" t="n">
-        <v>1.85426771640778</v>
+        <v>1.85426783561707</v>
       </c>
       <c r="H437" t="n">
         <v>4500</v>
@@ -13071,7 +13071,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G438" t="n">
-        <v>1.85426771640778</v>
+        <v>1.85426783561707</v>
       </c>
       <c r="H438" t="n">
         <v>0</v>
@@ -13158,7 +13158,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G441" t="n">
-        <v>1.88063192367554</v>
+        <v>1.88063180446625</v>
       </c>
       <c r="H441" t="n">
         <v>3000</v>
@@ -13187,7 +13187,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G442" t="n">
-        <v>1.88063192367554</v>
+        <v>1.88063180446625</v>
       </c>
       <c r="H442" t="n">
         <v>0</v>
@@ -13216,7 +13216,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G443" t="n">
-        <v>1.82790374755859</v>
+        <v>1.8279036283493</v>
       </c>
       <c r="H443" t="n">
         <v>4500</v>
@@ -13245,7 +13245,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G444" t="n">
-        <v>1.86305570602417</v>
+        <v>1.86305558681488</v>
       </c>
       <c r="H444" t="n">
         <v>1500</v>
@@ -13274,7 +13274,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G445" t="n">
-        <v>1.82790374755859</v>
+        <v>1.8279036283493</v>
       </c>
       <c r="H445" t="n">
         <v>1500</v>
@@ -13303,7 +13303,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G446" t="n">
-        <v>1.82790374755859</v>
+        <v>1.8279036283493</v>
       </c>
       <c r="H446" t="n">
         <v>0</v>
@@ -13332,7 +13332,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G447" t="n">
-        <v>1.76638793945312</v>
+        <v>1.76638782024384</v>
       </c>
       <c r="H447" t="n">
         <v>15000</v>
@@ -13506,7 +13506,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G453" t="n">
-        <v>1.68729591369629</v>
+        <v>1.68729567527771</v>
       </c>
       <c r="H453" t="n">
         <v>7500</v>
@@ -13535,7 +13535,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G454" t="n">
-        <v>1.63896179199219</v>
+        <v>1.63896191120148</v>
       </c>
       <c r="H454" t="n">
         <v>6000</v>
@@ -13796,7 +13796,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G463" t="n">
-        <v>1.66093194484711</v>
+        <v>1.66093182563782</v>
       </c>
       <c r="H463" t="n">
         <v>1500</v>
@@ -13825,7 +13825,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G464" t="n">
-        <v>1.66093194484711</v>
+        <v>1.66093182563782</v>
       </c>
       <c r="H464" t="n">
         <v>0</v>
@@ -13854,7 +13854,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G465" t="n">
-        <v>1.65214371681213</v>
+        <v>1.65214383602142</v>
       </c>
       <c r="H465" t="n">
         <v>9000</v>
@@ -13883,7 +13883,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G466" t="n">
-        <v>1.59941589832306</v>
+        <v>1.59941601753235</v>
       </c>
       <c r="H466" t="n">
         <v>6000</v>
@@ -13912,7 +13912,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G467" t="n">
-        <v>1.59502196311951</v>
+        <v>1.59502184391022</v>
       </c>
       <c r="H467" t="n">
         <v>3000</v>
@@ -13970,7 +13970,7 @@
         <v>1.875</v>
       </c>
       <c r="G469" t="n">
-        <v>1.64774978160858</v>
+        <v>1.64774990081787</v>
       </c>
       <c r="H469" t="n">
         <v>3000</v>
@@ -13999,7 +13999,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G470" t="n">
-        <v>1.66093194484711</v>
+        <v>1.66093182563782</v>
       </c>
       <c r="H470" t="n">
         <v>3000</v>
@@ -14028,7 +14028,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G471" t="n">
-        <v>1.59502196311951</v>
+        <v>1.59502184391022</v>
       </c>
       <c r="H471" t="n">
         <v>15000</v>
@@ -14057,7 +14057,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G472" t="n">
-        <v>1.64335572719574</v>
+        <v>1.64335584640503</v>
       </c>
       <c r="H472" t="n">
         <v>4500</v>
@@ -14086,7 +14086,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G473" t="n">
-        <v>1.64335572719574</v>
+        <v>1.64335584640503</v>
       </c>
       <c r="H473" t="n">
         <v>0</v>
@@ -14260,7 +14260,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G479" t="n">
-        <v>1.65653789043427</v>
+        <v>1.65653777122498</v>
       </c>
       <c r="H479" t="n">
         <v>4500</v>
@@ -14318,7 +14318,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G481" t="n">
-        <v>1.68729591369629</v>
+        <v>1.68729567527771</v>
       </c>
       <c r="H481" t="n">
         <v>3000</v>
@@ -14376,7 +14376,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G483" t="n">
-        <v>1.64335572719574</v>
+        <v>1.64335584640503</v>
       </c>
       <c r="H483" t="n">
         <v>3000</v>
@@ -14405,7 +14405,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G484" t="n">
-        <v>1.74881172180176</v>
+        <v>1.74881184101105</v>
       </c>
       <c r="H484" t="n">
         <v>19500</v>
@@ -14463,7 +14463,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G486" t="n">
-        <v>1.87184393405914</v>
+        <v>1.87184405326843</v>
       </c>
       <c r="H486" t="n">
         <v>25500</v>
@@ -14492,7 +14492,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G487" t="n">
-        <v>1.9333598613739</v>
+        <v>1.93335998058319</v>
       </c>
       <c r="H487" t="n">
         <v>33000</v>
@@ -14521,7 +14521,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G488" t="n">
-        <v>1.9245719909668</v>
+        <v>1.92457187175751</v>
       </c>
       <c r="H488" t="n">
         <v>34500</v>
@@ -14579,7 +14579,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G490" t="n">
-        <v>2.03881597518921</v>
+        <v>2.03881573677063</v>
       </c>
       <c r="H490" t="n">
         <v>28500</v>
@@ -14608,7 +14608,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G491" t="n">
-        <v>2.03881597518921</v>
+        <v>2.03881573677063</v>
       </c>
       <c r="H491" t="n">
         <v>0</v>
@@ -14637,7 +14637,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G492" t="n">
-        <v>1.99487578868866</v>
+        <v>1.99487566947937</v>
       </c>
       <c r="H492" t="n">
         <v>3000</v>
@@ -14666,7 +14666,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G493" t="n">
-        <v>2.02123951911926</v>
+        <v>2.02123975753784</v>
       </c>
       <c r="H493" t="n">
         <v>42000</v>
@@ -14695,7 +14695,7 @@
         <v>2.25</v>
       </c>
       <c r="G494" t="n">
-        <v>1.97729980945587</v>
+        <v>1.97729969024658</v>
       </c>
       <c r="H494" t="n">
         <v>4500</v>
@@ -14724,7 +14724,7 @@
         <v>2.25</v>
       </c>
       <c r="G495" t="n">
-        <v>1.97729980945587</v>
+        <v>1.97729969024658</v>
       </c>
       <c r="H495" t="n">
         <v>0</v>
@@ -14753,7 +14753,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G496" t="n">
-        <v>1.9333598613739</v>
+        <v>1.93335998058319</v>
       </c>
       <c r="H496" t="n">
         <v>6000</v>
@@ -14782,7 +14782,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G497" t="n">
-        <v>1.82790374755859</v>
+        <v>1.8279036283493</v>
       </c>
       <c r="H497" t="n">
         <v>21000</v>
@@ -14840,7 +14840,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G499" t="n">
-        <v>1.78396379947662</v>
+        <v>1.78396391868591</v>
       </c>
       <c r="H499" t="n">
         <v>12000</v>
@@ -14869,7 +14869,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G500" t="n">
-        <v>1.78396379947662</v>
+        <v>1.78396391868591</v>
       </c>
       <c r="H500" t="n">
         <v>3000</v>
@@ -14898,7 +14898,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G501" t="n">
-        <v>1.78396379947662</v>
+        <v>1.78396391868591</v>
       </c>
       <c r="H501" t="n">
         <v>0</v>
@@ -14927,7 +14927,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G502" t="n">
-        <v>1.74881172180176</v>
+        <v>1.74881184101105</v>
       </c>
       <c r="H502" t="n">
         <v>4500</v>
@@ -14956,7 +14956,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G503" t="n">
-        <v>1.74881172180176</v>
+        <v>1.74881184101105</v>
       </c>
       <c r="H503" t="n">
         <v>1500</v>
@@ -14985,7 +14985,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G504" t="n">
-        <v>1.74881172180176</v>
+        <v>1.74881184101105</v>
       </c>
       <c r="H504" t="n">
         <v>1500</v>
@@ -15072,7 +15072,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G507" t="n">
-        <v>1.78396379947662</v>
+        <v>1.78396391868591</v>
       </c>
       <c r="H507" t="n">
         <v>3000</v>
@@ -15101,7 +15101,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G508" t="n">
-        <v>1.78396379947662</v>
+        <v>1.78396391868591</v>
       </c>
       <c r="H508" t="n">
         <v>1500</v>
@@ -15130,7 +15130,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G509" t="n">
-        <v>1.78396379947662</v>
+        <v>1.78396391868591</v>
       </c>
       <c r="H509" t="n">
         <v>1500</v>
@@ -15217,7 +15217,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G512" t="n">
-        <v>1.78396379947662</v>
+        <v>1.78396391868591</v>
       </c>
       <c r="H512" t="n">
         <v>6000</v>
@@ -15275,7 +15275,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G514" t="n">
-        <v>1.78396379947662</v>
+        <v>1.78396391868591</v>
       </c>
       <c r="H514" t="n">
         <v>4500</v>
@@ -15304,7 +15304,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G515" t="n">
-        <v>1.78396379947662</v>
+        <v>1.78396391868591</v>
       </c>
       <c r="H515" t="n">
         <v>1500</v>
@@ -15420,7 +15420,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G519" t="n">
-        <v>1.76638793945312</v>
+        <v>1.76638782024384</v>
       </c>
       <c r="H519" t="n">
         <v>3000</v>
@@ -15449,7 +15449,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G520" t="n">
-        <v>1.79275190830231</v>
+        <v>1.79275178909302</v>
       </c>
       <c r="H520" t="n">
         <v>4500</v>
@@ -15507,7 +15507,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G522" t="n">
-        <v>1.76638793945312</v>
+        <v>1.76638782024384</v>
       </c>
       <c r="H522" t="n">
         <v>9000</v>
@@ -15536,7 +15536,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G523" t="n">
-        <v>1.6785079240799</v>
+        <v>1.67850780487061</v>
       </c>
       <c r="H523" t="n">
         <v>9000</v>
@@ -15594,7 +15594,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G525" t="n">
-        <v>1.62577986717224</v>
+        <v>1.62577974796295</v>
       </c>
       <c r="H525" t="n">
         <v>6000</v>
@@ -15623,7 +15623,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G526" t="n">
-        <v>1.54229378700256</v>
+        <v>1.54229390621185</v>
       </c>
       <c r="H526" t="n">
         <v>19500</v>
@@ -16029,7 +16029,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G540" t="n">
-        <v>1.51153588294983</v>
+        <v>1.51153600215912</v>
       </c>
       <c r="H540" t="n">
         <v>7500</v>
@@ -16058,7 +16058,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G541" t="n">
-        <v>1.51153588294983</v>
+        <v>1.51153600215912</v>
       </c>
       <c r="H541" t="n">
         <v>0</v>
@@ -16087,7 +16087,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G542" t="n">
-        <v>1.51153588294983</v>
+        <v>1.51153600215912</v>
       </c>
       <c r="H542" t="n">
         <v>0</v>
@@ -16145,7 +16145,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G544" t="n">
-        <v>1.52911186218262</v>
+        <v>1.52911174297333</v>
       </c>
       <c r="H544" t="n">
         <v>1500</v>
@@ -16174,7 +16174,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G545" t="n">
-        <v>1.56426382064819</v>
+        <v>1.5642637014389</v>
       </c>
       <c r="H545" t="n">
         <v>4500</v>
@@ -16203,7 +16203,7 @@
         <v>1.875</v>
       </c>
       <c r="G546" t="n">
-        <v>1.64774978160858</v>
+        <v>1.64774990081787</v>
       </c>
       <c r="H546" t="n">
         <v>18000</v>
@@ -16232,7 +16232,7 @@
         <v>1.875</v>
       </c>
       <c r="G547" t="n">
-        <v>1.64774978160858</v>
+        <v>1.64774990081787</v>
       </c>
       <c r="H547" t="n">
         <v>0</v>
@@ -16261,7 +16261,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G548" t="n">
-        <v>1.6785079240799</v>
+        <v>1.67850780487061</v>
       </c>
       <c r="H548" t="n">
         <v>3000</v>
@@ -16290,7 +16290,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G549" t="n">
-        <v>1.6785079240799</v>
+        <v>1.67850780487061</v>
       </c>
       <c r="H549" t="n">
         <v>0</v>
@@ -16319,7 +16319,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G550" t="n">
-        <v>1.6785079240799</v>
+        <v>1.67850780487061</v>
       </c>
       <c r="H550" t="n">
         <v>0</v>
@@ -16609,7 +16609,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G560" t="n">
-        <v>1.6785079240799</v>
+        <v>1.67850780487061</v>
       </c>
       <c r="H560" t="n">
         <v>9000</v>
@@ -16638,7 +16638,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G561" t="n">
-        <v>1.6785079240799</v>
+        <v>1.67850780487061</v>
       </c>
       <c r="H561" t="n">
         <v>0</v>
@@ -16667,7 +16667,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G562" t="n">
-        <v>1.6785079240799</v>
+        <v>1.67850780487061</v>
       </c>
       <c r="H562" t="n">
         <v>0</v>
@@ -16696,7 +16696,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G563" t="n">
-        <v>1.6785079240799</v>
+        <v>1.67850780487061</v>
       </c>
       <c r="H563" t="n">
         <v>0</v>
@@ -16725,7 +16725,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G564" t="n">
-        <v>1.6785079240799</v>
+        <v>1.67850780487061</v>
       </c>
       <c r="H564" t="n">
         <v>0</v>
@@ -16754,7 +16754,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G565" t="n">
-        <v>1.6785079240799</v>
+        <v>1.67850780487061</v>
       </c>
       <c r="H565" t="n">
         <v>0</v>
@@ -16783,7 +16783,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G566" t="n">
-        <v>1.62577986717224</v>
+        <v>1.62577974796295</v>
       </c>
       <c r="H566" t="n">
         <v>4500</v>
@@ -16812,7 +16812,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G567" t="n">
-        <v>1.62577986717224</v>
+        <v>1.62577974796295</v>
       </c>
       <c r="H567" t="n">
         <v>0</v>
@@ -16841,7 +16841,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G568" t="n">
-        <v>1.62577986717224</v>
+        <v>1.62577974796295</v>
       </c>
       <c r="H568" t="n">
         <v>0</v>
@@ -16870,7 +16870,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G569" t="n">
-        <v>1.60380983352661</v>
+        <v>1.6038099527359</v>
       </c>
       <c r="H569" t="n">
         <v>4500</v>
@@ -16899,7 +16899,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G570" t="n">
-        <v>1.60380983352661</v>
+        <v>1.6038099527359</v>
       </c>
       <c r="H570" t="n">
         <v>0</v>
@@ -16928,7 +16928,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G571" t="n">
-        <v>1.66093194484711</v>
+        <v>1.66093182563782</v>
       </c>
       <c r="H571" t="n">
         <v>1500</v>
@@ -17131,7 +17131,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G578" t="n">
-        <v>1.6785079240799</v>
+        <v>1.67850780487061</v>
       </c>
       <c r="H578" t="n">
         <v>1500</v>
@@ -17160,7 +17160,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G579" t="n">
-        <v>1.6785079240799</v>
+        <v>1.67850780487061</v>
       </c>
       <c r="H579" t="n">
         <v>0</v>
@@ -17189,7 +17189,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G580" t="n">
-        <v>1.6785079240799</v>
+        <v>1.67850780487061</v>
       </c>
       <c r="H580" t="n">
         <v>0</v>
@@ -17218,7 +17218,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G581" t="n">
-        <v>1.68729591369629</v>
+        <v>1.68729567527771</v>
       </c>
       <c r="H581" t="n">
         <v>1500</v>
@@ -17247,7 +17247,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G582" t="n">
-        <v>1.65214371681213</v>
+        <v>1.65214383602142</v>
       </c>
       <c r="H582" t="n">
         <v>1500</v>
@@ -17276,7 +17276,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G583" t="n">
-        <v>1.65214371681213</v>
+        <v>1.65214383602142</v>
       </c>
       <c r="H583" t="n">
         <v>0</v>
@@ -17305,7 +17305,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G584" t="n">
-        <v>1.62577986717224</v>
+        <v>1.62577974796295</v>
       </c>
       <c r="H584" t="n">
         <v>1500</v>
@@ -17334,7 +17334,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G585" t="n">
-        <v>1.62577986717224</v>
+        <v>1.62577974796295</v>
       </c>
       <c r="H585" t="n">
         <v>0</v>
@@ -17363,7 +17363,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G586" t="n">
-        <v>1.62577986717224</v>
+        <v>1.62577974796295</v>
       </c>
       <c r="H586" t="n">
         <v>0</v>
@@ -17392,7 +17392,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G587" t="n">
-        <v>1.62577986717224</v>
+        <v>1.62577974796295</v>
       </c>
       <c r="H587" t="n">
         <v>1500</v>
@@ -17421,7 +17421,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G588" t="n">
-        <v>1.62577986717224</v>
+        <v>1.62577974796295</v>
       </c>
       <c r="H588" t="n">
         <v>0</v>
@@ -17450,7 +17450,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G589" t="n">
-        <v>1.62577986717224</v>
+        <v>1.62577974796295</v>
       </c>
       <c r="H589" t="n">
         <v>1500</v>
@@ -17479,7 +17479,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G590" t="n">
-        <v>1.65653789043427</v>
+        <v>1.65653777122498</v>
       </c>
       <c r="H590" t="n">
         <v>3000</v>
@@ -17508,7 +17508,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G591" t="n">
-        <v>1.58623385429382</v>
+        <v>1.58623373508453</v>
       </c>
       <c r="H591" t="n">
         <v>9000</v>
@@ -17537,7 +17537,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G592" t="n">
-        <v>1.61699175834656</v>
+        <v>1.61699187755585</v>
       </c>
       <c r="H592" t="n">
         <v>6000</v>
@@ -17566,7 +17566,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G593" t="n">
-        <v>1.5554758310318</v>
+        <v>1.55547571182251</v>
       </c>
       <c r="H593" t="n">
         <v>13500</v>
@@ -17595,7 +17595,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G594" t="n">
-        <v>1.55986988544464</v>
+        <v>1.55986976623535</v>
       </c>
       <c r="H594" t="n">
         <v>15000</v>
@@ -17624,7 +17624,7 @@
         <v>1.875</v>
       </c>
       <c r="G595" t="n">
-        <v>1.64774978160858</v>
+        <v>1.64774990081787</v>
       </c>
       <c r="H595" t="n">
         <v>7500</v>
@@ -17653,7 +17653,7 @@
         <v>1.875</v>
       </c>
       <c r="G596" t="n">
-        <v>1.64774978160858</v>
+        <v>1.64774990081787</v>
       </c>
       <c r="H596" t="n">
         <v>0</v>
@@ -17682,7 +17682,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G597" t="n">
-        <v>1.61699175834656</v>
+        <v>1.61699187755585</v>
       </c>
       <c r="H597" t="n">
         <v>15000</v>
@@ -17711,7 +17711,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G598" t="n">
-        <v>1.63896179199219</v>
+        <v>1.63896191120148</v>
       </c>
       <c r="H598" t="n">
         <v>1500</v>
@@ -17740,7 +17740,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G599" t="n">
-        <v>1.63896179199219</v>
+        <v>1.63896191120148</v>
       </c>
       <c r="H599" t="n">
         <v>0</v>
@@ -17769,7 +17769,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G600" t="n">
-        <v>1.59941589832306</v>
+        <v>1.59941601753235</v>
       </c>
       <c r="H600" t="n">
         <v>3000</v>
@@ -17798,7 +17798,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G601" t="n">
-        <v>1.59941589832306</v>
+        <v>1.59941601753235</v>
       </c>
       <c r="H601" t="n">
         <v>0</v>
@@ -17827,7 +17827,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G602" t="n">
-        <v>1.59941589832306</v>
+        <v>1.59941601753235</v>
       </c>
       <c r="H602" t="n">
         <v>0</v>
@@ -17885,7 +17885,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G604" t="n">
-        <v>1.60380983352661</v>
+        <v>1.6038099527359</v>
       </c>
       <c r="H604" t="n">
         <v>18000</v>
@@ -17914,7 +17914,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G605" t="n">
-        <v>1.60380983352661</v>
+        <v>1.6038099527359</v>
       </c>
       <c r="H605" t="n">
         <v>0</v>
@@ -17943,7 +17943,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G606" t="n">
-        <v>1.63896179199219</v>
+        <v>1.63896191120148</v>
       </c>
       <c r="H606" t="n">
         <v>3000</v>
@@ -17972,7 +17972,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G607" t="n">
-        <v>1.61699175834656</v>
+        <v>1.61699187755585</v>
       </c>
       <c r="H607" t="n">
         <v>3000</v>
@@ -18233,7 +18233,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G616" t="n">
-        <v>1.56865799427032</v>
+        <v>1.56865787506104</v>
       </c>
       <c r="H616" t="n">
         <v>7500</v>
@@ -18291,7 +18291,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G618" t="n">
-        <v>1.6785079240799</v>
+        <v>1.67850780487061</v>
       </c>
       <c r="H618" t="n">
         <v>45000</v>
@@ -18320,7 +18320,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G619" t="n">
-        <v>1.72244775295258</v>
+        <v>1.72244787216187</v>
       </c>
       <c r="H619" t="n">
         <v>10500</v>
@@ -18436,7 +18436,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G623" t="n">
-        <v>1.69608378410339</v>
+        <v>1.69608390331268</v>
       </c>
       <c r="H623" t="n">
         <v>1500</v>
@@ -18581,7 +18581,7 @@
         <v>2.25</v>
       </c>
       <c r="G628" t="n">
-        <v>1.97729980945587</v>
+        <v>1.97729969024658</v>
       </c>
       <c r="H628" t="n">
         <v>303000</v>
@@ -18610,7 +18610,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G629" t="n">
-        <v>1.88063192367554</v>
+        <v>1.88063180446625</v>
       </c>
       <c r="H629" t="n">
         <v>39000</v>
@@ -18639,7 +18639,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G630" t="n">
-        <v>1.88941991329193</v>
+        <v>1.88941979408264</v>
       </c>
       <c r="H630" t="n">
         <v>19500</v>
@@ -18697,7 +18697,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G632" t="n">
-        <v>1.86305570602417</v>
+        <v>1.86305558681488</v>
       </c>
       <c r="H632" t="n">
         <v>33000</v>
@@ -18871,7 +18871,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G638" t="n">
-        <v>1.6785079240799</v>
+        <v>1.67850780487061</v>
       </c>
       <c r="H638" t="n">
         <v>12000</v>
@@ -18900,7 +18900,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G639" t="n">
-        <v>1.64335572719574</v>
+        <v>1.64335584640503</v>
       </c>
       <c r="H639" t="n">
         <v>19500</v>
@@ -18958,7 +18958,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G641" t="n">
-        <v>1.62577986717224</v>
+        <v>1.62577974796295</v>
       </c>
       <c r="H641" t="n">
         <v>1500</v>
@@ -18987,7 +18987,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G642" t="n">
-        <v>1.65214371681213</v>
+        <v>1.65214383602142</v>
       </c>
       <c r="H642" t="n">
         <v>18000</v>
@@ -19016,7 +19016,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G643" t="n">
-        <v>1.65214371681213</v>
+        <v>1.65214383602142</v>
       </c>
       <c r="H643" t="n">
         <v>9000</v>
@@ -19045,7 +19045,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G644" t="n">
-        <v>1.66093194484711</v>
+        <v>1.66093182563782</v>
       </c>
       <c r="H644" t="n">
         <v>9000</v>
@@ -19074,7 +19074,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G645" t="n">
-        <v>1.66093194484711</v>
+        <v>1.66093182563782</v>
       </c>
       <c r="H645" t="n">
         <v>0</v>
@@ -19103,7 +19103,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G646" t="n">
-        <v>1.62138593196869</v>
+        <v>1.62138569355011</v>
       </c>
       <c r="H646" t="n">
         <v>6000</v>
@@ -19161,7 +19161,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G648" t="n">
-        <v>1.69608378410339</v>
+        <v>1.69608390331268</v>
       </c>
       <c r="H648" t="n">
         <v>1500</v>
@@ -19219,7 +19219,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G650" t="n">
-        <v>1.74881172180176</v>
+        <v>1.74881184101105</v>
       </c>
       <c r="H650" t="n">
         <v>3000</v>
@@ -19277,7 +19277,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G652" t="n">
-        <v>1.6785079240799</v>
+        <v>1.67850780487061</v>
       </c>
       <c r="H652" t="n">
         <v>6000</v>
@@ -19306,7 +19306,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G653" t="n">
-        <v>1.6785079240799</v>
+        <v>1.67850780487061</v>
       </c>
       <c r="H653" t="n">
         <v>0</v>
@@ -19451,7 +19451,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G658" t="n">
-        <v>1.79275190830231</v>
+        <v>1.79275178909302</v>
       </c>
       <c r="H658" t="n">
         <v>108000</v>
@@ -19567,7 +19567,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G662" t="n">
-        <v>1.7059623003006</v>
+        <v>1.70596218109131</v>
       </c>
       <c r="H662" t="n">
         <v>54000</v>
@@ -19596,7 +19596,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G663" t="n">
-        <v>1.7059623003006</v>
+        <v>1.70596218109131</v>
       </c>
       <c r="H663" t="n">
         <v>6000</v>
@@ -19683,7 +19683,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G666" t="n">
-        <v>1.73304104804993</v>
+        <v>1.73304092884064</v>
       </c>
       <c r="H666" t="n">
         <v>9000</v>
@@ -19712,7 +19712,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G667" t="n">
-        <v>1.7059623003006</v>
+        <v>1.70596218109131</v>
       </c>
       <c r="H667" t="n">
         <v>7500</v>
@@ -19770,7 +19770,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G669" t="n">
-        <v>1.66985738277435</v>
+        <v>1.66985726356506</v>
       </c>
       <c r="H669" t="n">
         <v>3000</v>
@@ -19799,7 +19799,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G670" t="n">
-        <v>1.66083097457886</v>
+        <v>1.66083109378815</v>
       </c>
       <c r="H670" t="n">
         <v>30000</v>
@@ -19828,7 +19828,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G671" t="n">
-        <v>1.63375210762024</v>
+        <v>1.63375222682953</v>
       </c>
       <c r="H671" t="n">
         <v>1500</v>
@@ -19857,7 +19857,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G672" t="n">
-        <v>1.63375210762024</v>
+        <v>1.63375222682953</v>
       </c>
       <c r="H672" t="n">
         <v>0</v>
@@ -20060,7 +20060,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G679" t="n">
-        <v>1.63375210762024</v>
+        <v>1.63375222682953</v>
       </c>
       <c r="H679" t="n">
         <v>1500</v>
@@ -20089,7 +20089,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G680" t="n">
-        <v>1.63375210762024</v>
+        <v>1.63375222682953</v>
       </c>
       <c r="H680" t="n">
         <v>0</v>
@@ -20118,7 +20118,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G681" t="n">
-        <v>1.62472593784332</v>
+        <v>1.62472605705261</v>
       </c>
       <c r="H681" t="n">
         <v>10500</v>
@@ -20147,7 +20147,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G682" t="n">
-        <v>1.62472593784332</v>
+        <v>1.62472605705261</v>
       </c>
       <c r="H682" t="n">
         <v>0</v>
@@ -20176,7 +20176,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G683" t="n">
-        <v>1.62472593784332</v>
+        <v>1.62472605705261</v>
       </c>
       <c r="H683" t="n">
         <v>0</v>
@@ -20437,7 +20437,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G692" t="n">
-        <v>1.61569964885712</v>
+        <v>1.61569976806641</v>
       </c>
       <c r="H692" t="n">
         <v>4500</v>
@@ -20466,7 +20466,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G693" t="n">
-        <v>1.61569964885712</v>
+        <v>1.61569976806641</v>
       </c>
       <c r="H693" t="n">
         <v>0</v>
@@ -20495,7 +20495,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G694" t="n">
-        <v>1.61569964885712</v>
+        <v>1.61569976806641</v>
       </c>
       <c r="H694" t="n">
         <v>0</v>
@@ -20524,7 +20524,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G695" t="n">
-        <v>1.56154227256775</v>
+        <v>1.56154215335846</v>
       </c>
       <c r="H695" t="n">
         <v>9000</v>
@@ -20582,7 +20582,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G697" t="n">
-        <v>1.53446340560913</v>
+        <v>1.53446352481842</v>
       </c>
       <c r="H697" t="n">
         <v>12000</v>
@@ -20611,7 +20611,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G698" t="n">
-        <v>1.56154227256775</v>
+        <v>1.56154215335846</v>
       </c>
       <c r="H698" t="n">
         <v>3000</v>
@@ -20988,7 +20988,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G711" t="n">
-        <v>1.56154227256775</v>
+        <v>1.56154215335846</v>
       </c>
       <c r="H711" t="n">
         <v>4500</v>
@@ -21017,7 +21017,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G712" t="n">
-        <v>1.56154227256775</v>
+        <v>1.56154215335846</v>
       </c>
       <c r="H712" t="n">
         <v>0</v>
@@ -21046,7 +21046,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G713" t="n">
-        <v>1.56154227256775</v>
+        <v>1.56154215335846</v>
       </c>
       <c r="H713" t="n">
         <v>0</v>
@@ -21075,7 +21075,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G714" t="n">
-        <v>1.53446340560913</v>
+        <v>1.53446352481842</v>
       </c>
       <c r="H714" t="n">
         <v>1500</v>
@@ -21104,7 +21104,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G715" t="n">
-        <v>1.53446340560913</v>
+        <v>1.53446352481842</v>
       </c>
       <c r="H715" t="n">
         <v>6000</v>
@@ -21220,7 +21220,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G719" t="n">
-        <v>1.53446340560913</v>
+        <v>1.53446352481842</v>
       </c>
       <c r="H719" t="n">
         <v>10500</v>
@@ -21249,7 +21249,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G720" t="n">
-        <v>1.56154227256775</v>
+        <v>1.56154215335846</v>
       </c>
       <c r="H720" t="n">
         <v>1500</v>
@@ -21278,7 +21278,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G721" t="n">
-        <v>1.56154227256775</v>
+        <v>1.56154215335846</v>
       </c>
       <c r="H721" t="n">
         <v>0</v>
@@ -21307,7 +21307,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G722" t="n">
-        <v>1.56154227256775</v>
+        <v>1.56154215335846</v>
       </c>
       <c r="H722" t="n">
         <v>1500</v>
@@ -21336,7 +21336,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G723" t="n">
-        <v>1.56154227256775</v>
+        <v>1.56154215335846</v>
       </c>
       <c r="H723" t="n">
         <v>0</v>
@@ -21365,7 +21365,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G724" t="n">
-        <v>1.56154227256775</v>
+        <v>1.56154215335846</v>
       </c>
       <c r="H724" t="n">
         <v>0</v>
@@ -21742,7 +21742,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G737" t="n">
-        <v>1.53446340560913</v>
+        <v>1.53446352481842</v>
       </c>
       <c r="H737" t="n">
         <v>1500</v>
@@ -22032,7 +22032,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G747" t="n">
-        <v>1.53446340560913</v>
+        <v>1.53446352481842</v>
       </c>
       <c r="H747" t="n">
         <v>1500</v>
@@ -22061,7 +22061,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G748" t="n">
-        <v>1.53446340560913</v>
+        <v>1.53446352481842</v>
       </c>
       <c r="H748" t="n">
         <v>0</v>
@@ -22090,7 +22090,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G749" t="n">
-        <v>1.53446340560913</v>
+        <v>1.53446352481842</v>
       </c>
       <c r="H749" t="n">
         <v>1500</v>
@@ -22119,7 +22119,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G750" t="n">
-        <v>1.53446340560913</v>
+        <v>1.53446352481842</v>
       </c>
       <c r="H750" t="n">
         <v>0</v>
@@ -22206,7 +22206,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G753" t="n">
-        <v>1.49835848808289</v>
+        <v>1.4983583688736</v>
       </c>
       <c r="H753" t="n">
         <v>4500</v>
@@ -22322,7 +22322,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G757" t="n">
-        <v>1.56154227256775</v>
+        <v>1.56154215335846</v>
       </c>
       <c r="H757" t="n">
         <v>6000</v>
@@ -22351,7 +22351,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G758" t="n">
-        <v>1.56154227256775</v>
+        <v>1.56154215335846</v>
       </c>
       <c r="H758" t="n">
         <v>6000</v>
@@ -22583,7 +22583,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G766" t="n">
-        <v>1.48030591011047</v>
+        <v>1.48030579090118</v>
       </c>
       <c r="H766" t="n">
         <v>3000</v>
@@ -22612,7 +22612,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G767" t="n">
-        <v>1.48933207988739</v>
+        <v>1.48933219909668</v>
       </c>
       <c r="H767" t="n">
         <v>15000</v>
@@ -22844,7 +22844,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G775" t="n">
-        <v>1.48933207988739</v>
+        <v>1.48933219909668</v>
       </c>
       <c r="H775" t="n">
         <v>3000</v>
@@ -22931,7 +22931,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G778" t="n">
-        <v>1.48933207988739</v>
+        <v>1.48933219909668</v>
       </c>
       <c r="H778" t="n">
         <v>4500</v>
@@ -22960,7 +22960,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G779" t="n">
-        <v>1.48030591011047</v>
+        <v>1.48030579090118</v>
       </c>
       <c r="H779" t="n">
         <v>6000</v>
@@ -22989,7 +22989,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G780" t="n">
-        <v>1.45322716236115</v>
+        <v>1.45322704315186</v>
       </c>
       <c r="H780" t="n">
         <v>10500</v>
@@ -23047,7 +23047,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G782" t="n">
-        <v>1.53446340560913</v>
+        <v>1.53446352481842</v>
       </c>
       <c r="H782" t="n">
         <v>27000</v>
@@ -23105,7 +23105,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G784" t="n">
-        <v>1.49835848808289</v>
+        <v>1.4983583688736</v>
       </c>
       <c r="H784" t="n">
         <v>18000</v>
@@ -23221,7 +23221,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G788" t="n">
-        <v>1.48030591011047</v>
+        <v>1.48030579090118</v>
       </c>
       <c r="H788" t="n">
         <v>1500</v>
@@ -23250,7 +23250,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G789" t="n">
-        <v>1.48030591011047</v>
+        <v>1.48030579090118</v>
       </c>
       <c r="H789" t="n">
         <v>0</v>
@@ -23395,7 +23395,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G794" t="n">
-        <v>1.98577630519867</v>
+        <v>1.98577642440796</v>
       </c>
       <c r="H794" t="n">
         <v>370500</v>
@@ -23424,7 +23424,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G795" t="n">
-        <v>1.87746119499207</v>
+        <v>1.87746095657349</v>
       </c>
       <c r="H795" t="n">
         <v>319500</v>
@@ -23453,7 +23453,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G796" t="n">
-        <v>1.66985738277435</v>
+        <v>1.66985726356506</v>
       </c>
       <c r="H796" t="n">
         <v>94500</v>
@@ -23627,7 +23627,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G802" t="n">
-        <v>1.84135615825653</v>
+        <v>1.84135603904724</v>
       </c>
       <c r="H802" t="n">
         <v>37500</v>
@@ -23656,7 +23656,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G803" t="n">
-        <v>1.93161880970001</v>
+        <v>1.93161869049072</v>
       </c>
       <c r="H803" t="n">
         <v>73500</v>
@@ -23685,7 +23685,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G804" t="n">
-        <v>1.87746119499207</v>
+        <v>1.87746095657349</v>
       </c>
       <c r="H804" t="n">
         <v>46500</v>
@@ -23743,7 +23743,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G806" t="n">
-        <v>1.89551365375519</v>
+        <v>1.89551341533661</v>
       </c>
       <c r="H806" t="n">
         <v>9000</v>
@@ -23801,7 +23801,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G808" t="n">
-        <v>1.87746119499207</v>
+        <v>1.87746095657349</v>
       </c>
       <c r="H808" t="n">
         <v>10500</v>
@@ -23888,7 +23888,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G811" t="n">
-        <v>1.84135615825653</v>
+        <v>1.84135603904724</v>
       </c>
       <c r="H811" t="n">
         <v>6000</v>
@@ -23917,7 +23917,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G812" t="n">
-        <v>1.87746119499207</v>
+        <v>1.87746095657349</v>
       </c>
       <c r="H812" t="n">
         <v>6000</v>
@@ -23975,7 +23975,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G814" t="n">
-        <v>1.87746119499207</v>
+        <v>1.87746095657349</v>
       </c>
       <c r="H814" t="n">
         <v>7500</v>
@@ -24004,7 +24004,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G815" t="n">
-        <v>1.76011979579926</v>
+        <v>1.76011991500854</v>
       </c>
       <c r="H815" t="n">
         <v>79500</v>
@@ -24091,7 +24091,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G818" t="n">
-        <v>1.7059623003006</v>
+        <v>1.70596218109131</v>
       </c>
       <c r="H818" t="n">
         <v>55500</v>
@@ -24120,7 +24120,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G819" t="n">
-        <v>1.76914608478546</v>
+        <v>1.76914620399475</v>
       </c>
       <c r="H819" t="n">
         <v>12000</v>
@@ -24149,7 +24149,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G820" t="n">
-        <v>1.76914608478546</v>
+        <v>1.76914620399475</v>
       </c>
       <c r="H820" t="n">
         <v>0</v>
@@ -24178,7 +24178,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G821" t="n">
-        <v>1.73304104804993</v>
+        <v>1.73304092884064</v>
       </c>
       <c r="H821" t="n">
         <v>7500</v>
@@ -24236,7 +24236,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G823" t="n">
-        <v>1.84135615825653</v>
+        <v>1.84135603904724</v>
       </c>
       <c r="H823" t="n">
         <v>15000</v>
@@ -24294,7 +24294,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G825" t="n">
-        <v>1.76011979579926</v>
+        <v>1.76011991500854</v>
       </c>
       <c r="H825" t="n">
         <v>15000</v>
@@ -24352,7 +24352,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G827" t="n">
-        <v>1.73304104804993</v>
+        <v>1.73304092884064</v>
       </c>
       <c r="H827" t="n">
         <v>10500</v>
@@ -24526,7 +24526,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G833" t="n">
-        <v>1.74206721782684</v>
+        <v>1.74206733703613</v>
       </c>
       <c r="H833" t="n">
         <v>6000</v>
@@ -24555,7 +24555,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G834" t="n">
-        <v>1.73304104804993</v>
+        <v>1.73304092884064</v>
       </c>
       <c r="H834" t="n">
         <v>1500</v>
@@ -24584,7 +24584,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G835" t="n">
-        <v>1.76914608478546</v>
+        <v>1.76914620399475</v>
       </c>
       <c r="H835" t="n">
         <v>7500</v>
@@ -24613,7 +24613,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G836" t="n">
-        <v>1.76011979579926</v>
+        <v>1.76011991500854</v>
       </c>
       <c r="H836" t="n">
         <v>1500</v>
@@ -24671,7 +24671,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G838" t="n">
-        <v>1.74206721782684</v>
+        <v>1.74206733703613</v>
       </c>
       <c r="H838" t="n">
         <v>10500</v>
@@ -24700,7 +24700,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G839" t="n">
-        <v>1.74206721782684</v>
+        <v>1.74206733703613</v>
       </c>
       <c r="H839" t="n">
         <v>0</v>
@@ -24903,7 +24903,7 @@
         <v>2</v>
       </c>
       <c r="G846" t="n">
-        <v>1.80525100231171</v>
+        <v>1.805251121521</v>
       </c>
       <c r="H846" t="n">
         <v>24000</v>
@@ -24932,7 +24932,7 @@
         <v>2</v>
       </c>
       <c r="G847" t="n">
-        <v>1.80525100231171</v>
+        <v>1.805251121521</v>
       </c>
       <c r="H847" t="n">
         <v>0</v>
@@ -24961,7 +24961,7 @@
         <v>2</v>
       </c>
       <c r="G848" t="n">
-        <v>1.80525100231171</v>
+        <v>1.805251121521</v>
       </c>
       <c r="H848" t="n">
         <v>0</v>
@@ -25048,7 +25048,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G851" t="n">
-        <v>1.73304104804993</v>
+        <v>1.73304092884064</v>
       </c>
       <c r="H851" t="n">
         <v>16500</v>
@@ -25135,7 +25135,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G854" t="n">
-        <v>1.76914608478546</v>
+        <v>1.76914620399475</v>
       </c>
       <c r="H854" t="n">
         <v>1500</v>
@@ -25164,7 +25164,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G855" t="n">
-        <v>1.76011979579926</v>
+        <v>1.76011991500854</v>
       </c>
       <c r="H855" t="n">
         <v>10500</v>
@@ -25193,7 +25193,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G856" t="n">
-        <v>1.76011979579926</v>
+        <v>1.76011991500854</v>
       </c>
       <c r="H856" t="n">
         <v>1500</v>
@@ -25280,7 +25280,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G859" t="n">
-        <v>1.76011979579926</v>
+        <v>1.76011991500854</v>
       </c>
       <c r="H859" t="n">
         <v>1500</v>
@@ -25338,7 +25338,7 @@
         <v>2</v>
       </c>
       <c r="G861" t="n">
-        <v>1.80525100231171</v>
+        <v>1.805251121521</v>
       </c>
       <c r="H861" t="n">
         <v>4500</v>
@@ -25425,7 +25425,7 @@
         <v>2</v>
       </c>
       <c r="G864" t="n">
-        <v>1.80525100231171</v>
+        <v>1.805251121521</v>
       </c>
       <c r="H864" t="n">
         <v>9000</v>
@@ -25454,7 +25454,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G865" t="n">
-        <v>1.84135615825653</v>
+        <v>1.84135603904724</v>
       </c>
       <c r="H865" t="n">
         <v>48000</v>
@@ -25483,7 +25483,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G866" t="n">
-        <v>1.87746119499207</v>
+        <v>1.87746095657349</v>
       </c>
       <c r="H866" t="n">
         <v>7500</v>
@@ -25541,7 +25541,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G868" t="n">
-        <v>1.98577630519867</v>
+        <v>1.98577642440796</v>
       </c>
       <c r="H868" t="n">
         <v>57000</v>
@@ -25570,7 +25570,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G869" t="n">
-        <v>1.98577630519867</v>
+        <v>1.98577642440796</v>
       </c>
       <c r="H869" t="n">
         <v>42000</v>
@@ -25599,7 +25599,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G870" t="n">
-        <v>2.05798625946045</v>
+        <v>2.05798602104187</v>
       </c>
       <c r="H870" t="n">
         <v>60000</v>
@@ -25628,7 +25628,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G871" t="n">
-        <v>2.07603859901428</v>
+        <v>2.07603883743286</v>
       </c>
       <c r="H871" t="n">
         <v>30000</v>
@@ -25657,7 +25657,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G872" t="n">
-        <v>2.05798625946045</v>
+        <v>2.05798602104187</v>
       </c>
       <c r="H872" t="n">
         <v>43500</v>
@@ -25686,7 +25686,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G873" t="n">
-        <v>2.05798625946045</v>
+        <v>2.05798602104187</v>
       </c>
       <c r="H873" t="n">
         <v>30000</v>
@@ -25715,7 +25715,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G874" t="n">
-        <v>1.98577630519867</v>
+        <v>1.98577642440796</v>
       </c>
       <c r="H874" t="n">
         <v>33000</v>
@@ -25744,7 +25744,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G875" t="n">
-        <v>2.05798625946045</v>
+        <v>2.05798602104187</v>
       </c>
       <c r="H875" t="n">
         <v>10500</v>
@@ -25802,7 +25802,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G877" t="n">
-        <v>1.94967114925385</v>
+        <v>1.94967126846313</v>
       </c>
       <c r="H877" t="n">
         <v>10500</v>
@@ -25831,7 +25831,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G878" t="n">
-        <v>1.93161880970001</v>
+        <v>1.93161869049072</v>
       </c>
       <c r="H878" t="n">
         <v>12000</v>
@@ -25860,7 +25860,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G879" t="n">
-        <v>1.94967114925385</v>
+        <v>1.94967126846313</v>
       </c>
       <c r="H879" t="n">
         <v>22500</v>
@@ -25889,7 +25889,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G880" t="n">
-        <v>1.94967114925385</v>
+        <v>1.94967126846313</v>
       </c>
       <c r="H880" t="n">
         <v>1500</v>
@@ -25918,7 +25918,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G881" t="n">
-        <v>1.94967114925385</v>
+        <v>1.94967126846313</v>
       </c>
       <c r="H881" t="n">
         <v>9000</v>
@@ -25947,7 +25947,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G882" t="n">
-        <v>1.94967114925385</v>
+        <v>1.94967126846313</v>
       </c>
       <c r="H882" t="n">
         <v>7500</v>
@@ -25976,7 +25976,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G883" t="n">
-        <v>1.98577630519867</v>
+        <v>1.98577642440796</v>
       </c>
       <c r="H883" t="n">
         <v>13500</v>
@@ -26005,7 +26005,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G884" t="n">
-        <v>2.07603859901428</v>
+        <v>2.07603883743286</v>
       </c>
       <c r="H884" t="n">
         <v>45000</v>
@@ -26063,7 +26063,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G886" t="n">
-        <v>2.16630125045776</v>
+        <v>2.16630148887634</v>
       </c>
       <c r="H886" t="n">
         <v>43500</v>
@@ -26092,7 +26092,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G887" t="n">
-        <v>2.16630125045776</v>
+        <v>2.16630148887634</v>
       </c>
       <c r="H887" t="n">
         <v>31500</v>
@@ -26121,7 +26121,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G888" t="n">
-        <v>2.16630125045776</v>
+        <v>2.16630148887634</v>
       </c>
       <c r="H888" t="n">
         <v>51000</v>
@@ -26237,7 +26237,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G892" t="n">
-        <v>2.07603859901428</v>
+        <v>2.07603883743286</v>
       </c>
       <c r="H892" t="n">
         <v>67500</v>
@@ -26266,7 +26266,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G893" t="n">
-        <v>2.07603859901428</v>
+        <v>2.07603883743286</v>
       </c>
       <c r="H893" t="n">
         <v>15000</v>
@@ -26353,7 +26353,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G896" t="n">
-        <v>1.94967114925385</v>
+        <v>1.94967126846313</v>
       </c>
       <c r="H896" t="n">
         <v>33000</v>
@@ -26411,7 +26411,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G898" t="n">
-        <v>1.87746119499207</v>
+        <v>1.87746095657349</v>
       </c>
       <c r="H898" t="n">
         <v>15000</v>
@@ -26469,7 +26469,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G900" t="n">
-        <v>1.87746119499207</v>
+        <v>1.87746095657349</v>
       </c>
       <c r="H900" t="n">
         <v>12000</v>
@@ -26527,7 +26527,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G902" t="n">
-        <v>1.93161880970001</v>
+        <v>1.93161869049072</v>
       </c>
       <c r="H902" t="n">
         <v>9000</v>
@@ -26585,7 +26585,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G904" t="n">
-        <v>1.93161880970001</v>
+        <v>1.93161869049072</v>
       </c>
       <c r="H904" t="n">
         <v>9000</v>
@@ -26614,7 +26614,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G905" t="n">
-        <v>1.94967114925385</v>
+        <v>1.94967126846313</v>
       </c>
       <c r="H905" t="n">
         <v>15000</v>
@@ -26672,7 +26672,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G907" t="n">
-        <v>1.93161880970001</v>
+        <v>1.93161869049072</v>
       </c>
       <c r="H907" t="n">
         <v>1500</v>
@@ -26701,7 +26701,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G908" t="n">
-        <v>1.93161880970001</v>
+        <v>1.93161869049072</v>
       </c>
       <c r="H908" t="n">
         <v>0</v>
@@ -26759,7 +26759,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G910" t="n">
-        <v>1.84135615825653</v>
+        <v>1.84135603904724</v>
       </c>
       <c r="H910" t="n">
         <v>21000</v>
@@ -26788,7 +26788,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G911" t="n">
-        <v>1.87746119499207</v>
+        <v>1.87746095657349</v>
       </c>
       <c r="H911" t="n">
         <v>9000</v>
@@ -26875,7 +26875,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G914" t="n">
-        <v>1.89551365375519</v>
+        <v>1.89551341533661</v>
       </c>
       <c r="H914" t="n">
         <v>7500</v>
@@ -26904,7 +26904,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G915" t="n">
-        <v>1.87746119499207</v>
+        <v>1.87746095657349</v>
       </c>
       <c r="H915" t="n">
         <v>10500</v>
@@ -26933,7 +26933,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G916" t="n">
-        <v>1.87746119499207</v>
+        <v>1.87746095657349</v>
       </c>
       <c r="H916" t="n">
         <v>1500</v>
@@ -27049,7 +27049,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G920" t="n">
-        <v>1.89470207691193</v>
+        <v>1.89470195770264</v>
       </c>
       <c r="H920" t="n">
         <v>4500</v>
@@ -27078,7 +27078,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G921" t="n">
-        <v>1.89470207691193</v>
+        <v>1.89470195770264</v>
       </c>
       <c r="H921" t="n">
         <v>0</v>
@@ -27107,7 +27107,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G922" t="n">
-        <v>1.89470207691193</v>
+        <v>1.89470195770264</v>
       </c>
       <c r="H922" t="n">
         <v>15000</v>
@@ -27136,7 +27136,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G923" t="n">
-        <v>1.82968771457672</v>
+        <v>1.82968783378601</v>
       </c>
       <c r="H923" t="n">
         <v>28500</v>
@@ -27165,7 +27165,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G924" t="n">
-        <v>1.77396130561829</v>
+        <v>1.773961186409</v>
       </c>
       <c r="H924" t="n">
         <v>147000</v>
@@ -27223,7 +27223,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G926" t="n">
-        <v>1.81111228466034</v>
+        <v>1.81111240386963</v>
       </c>
       <c r="H926" t="n">
         <v>6000</v>
@@ -27252,7 +27252,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G927" t="n">
-        <v>1.81111228466034</v>
+        <v>1.81111240386963</v>
       </c>
       <c r="H927" t="n">
         <v>4500</v>
@@ -27281,7 +27281,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G928" t="n">
-        <v>1.81111228466034</v>
+        <v>1.81111240386963</v>
       </c>
       <c r="H928" t="n">
         <v>1500</v>
@@ -27513,7 +27513,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G936" t="n">
-        <v>1.81111228466034</v>
+        <v>1.81111240386963</v>
       </c>
       <c r="H936" t="n">
         <v>7500</v>
@@ -27542,7 +27542,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G937" t="n">
-        <v>1.81111228466034</v>
+        <v>1.81111240386963</v>
       </c>
       <c r="H937" t="n">
         <v>1500</v>
@@ -27629,7 +27629,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G940" t="n">
-        <v>1.78324902057648</v>
+        <v>1.78324890136719</v>
       </c>
       <c r="H940" t="n">
         <v>3000</v>
@@ -27658,7 +27658,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G941" t="n">
-        <v>1.78324902057648</v>
+        <v>1.78324890136719</v>
       </c>
       <c r="H941" t="n">
         <v>6000</v>
@@ -27716,7 +27716,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G943" t="n">
-        <v>1.81111228466034</v>
+        <v>1.81111240386963</v>
       </c>
       <c r="H943" t="n">
         <v>3000</v>
@@ -27745,7 +27745,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G944" t="n">
-        <v>1.77396130561829</v>
+        <v>1.773961186409</v>
       </c>
       <c r="H944" t="n">
         <v>27000</v>
@@ -27774,7 +27774,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G945" t="n">
-        <v>1.77396130561829</v>
+        <v>1.773961186409</v>
       </c>
       <c r="H945" t="n">
         <v>3000</v>
@@ -27803,7 +27803,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G946" t="n">
-        <v>1.77396130561829</v>
+        <v>1.773961186409</v>
       </c>
       <c r="H946" t="n">
         <v>0</v>
@@ -27832,7 +27832,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G947" t="n">
-        <v>1.78324902057648</v>
+        <v>1.78324890136719</v>
       </c>
       <c r="H947" t="n">
         <v>4500</v>
@@ -27919,7 +27919,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G950" t="n">
-        <v>1.78324902057648</v>
+        <v>1.78324890136719</v>
       </c>
       <c r="H950" t="n">
         <v>6000</v>
@@ -27948,7 +27948,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G951" t="n">
-        <v>1.78324902057648</v>
+        <v>1.78324890136719</v>
       </c>
       <c r="H951" t="n">
         <v>1500</v>
@@ -28122,7 +28122,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G957" t="n">
-        <v>1.78324902057648</v>
+        <v>1.78324890136719</v>
       </c>
       <c r="H957" t="n">
         <v>3000</v>
@@ -28151,7 +28151,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G958" t="n">
-        <v>1.78324902057648</v>
+        <v>1.78324890136719</v>
       </c>
       <c r="H958" t="n">
         <v>1500</v>
@@ -28180,7 +28180,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G959" t="n">
-        <v>1.78324902057648</v>
+        <v>1.78324890136719</v>
       </c>
       <c r="H959" t="n">
         <v>1500</v>
@@ -28209,7 +28209,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G960" t="n">
-        <v>1.75538575649261</v>
+        <v>1.75538563728333</v>
       </c>
       <c r="H960" t="n">
         <v>9000</v>
@@ -28238,7 +28238,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G961" t="n">
-        <v>1.78324902057648</v>
+        <v>1.78324890136719</v>
       </c>
       <c r="H961" t="n">
         <v>4500</v>
@@ -28354,7 +28354,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G965" t="n">
-        <v>1.78324902057648</v>
+        <v>1.78324890136719</v>
       </c>
       <c r="H965" t="n">
         <v>13500</v>
@@ -28383,7 +28383,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G966" t="n">
-        <v>1.78324902057648</v>
+        <v>1.78324890136719</v>
       </c>
       <c r="H966" t="n">
         <v>4500</v>
@@ -28615,7 +28615,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G974" t="n">
-        <v>1.82039999961853</v>
+        <v>1.82040011882782</v>
       </c>
       <c r="H974" t="n">
         <v>13500</v>
@@ -28644,7 +28644,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G975" t="n">
-        <v>1.82039999961853</v>
+        <v>1.82040011882782</v>
       </c>
       <c r="H975" t="n">
         <v>0</v>
@@ -28673,7 +28673,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G976" t="n">
-        <v>1.82039999961853</v>
+        <v>1.82040011882782</v>
       </c>
       <c r="H976" t="n">
         <v>0</v>
@@ -28702,7 +28702,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G977" t="n">
-        <v>1.77396130561829</v>
+        <v>1.773961186409</v>
       </c>
       <c r="H977" t="n">
         <v>16500</v>
@@ -28818,7 +28818,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G981" t="n">
-        <v>1.78324902057648</v>
+        <v>1.78324890136719</v>
       </c>
       <c r="H981" t="n">
         <v>1500</v>
@@ -28847,7 +28847,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G982" t="n">
-        <v>1.78324902057648</v>
+        <v>1.78324890136719</v>
       </c>
       <c r="H982" t="n">
         <v>0</v>
@@ -28876,7 +28876,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G983" t="n">
-        <v>1.78324902057648</v>
+        <v>1.78324890136719</v>
       </c>
       <c r="H983" t="n">
         <v>0</v>
@@ -28934,7 +28934,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G985" t="n">
-        <v>1.78324902057648</v>
+        <v>1.78324890136719</v>
       </c>
       <c r="H985" t="n">
         <v>15000</v>
@@ -28992,7 +28992,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G987" t="n">
-        <v>1.81111228466034</v>
+        <v>1.81111240386963</v>
       </c>
       <c r="H987" t="n">
         <v>40500</v>
@@ -29021,7 +29021,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G988" t="n">
-        <v>1.82039999961853</v>
+        <v>1.82040011882782</v>
       </c>
       <c r="H988" t="n">
         <v>3000</v>
@@ -29050,7 +29050,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G989" t="n">
-        <v>1.78324902057648</v>
+        <v>1.78324890136719</v>
       </c>
       <c r="H989" t="n">
         <v>1500</v>
@@ -29137,7 +29137,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G992" t="n">
-        <v>1.75538575649261</v>
+        <v>1.75538563728333</v>
       </c>
       <c r="H992" t="n">
         <v>9000</v>
@@ -29166,7 +29166,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G993" t="n">
-        <v>1.75538575649261</v>
+        <v>1.75538563728333</v>
       </c>
       <c r="H993" t="n">
         <v>0</v>
@@ -29195,7 +29195,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G994" t="n">
-        <v>1.77396130561829</v>
+        <v>1.773961186409</v>
       </c>
       <c r="H994" t="n">
         <v>3000</v>
@@ -29224,7 +29224,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G995" t="n">
-        <v>1.77396130561829</v>
+        <v>1.773961186409</v>
       </c>
       <c r="H995" t="n">
         <v>0</v>
@@ -29630,7 +29630,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1009" t="n">
-        <v>1.77396130561829</v>
+        <v>1.773961186409</v>
       </c>
       <c r="H1009" t="n">
         <v>6000</v>
@@ -29659,7 +29659,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1010" t="n">
-        <v>1.77396130561829</v>
+        <v>1.773961186409</v>
       </c>
       <c r="H1010" t="n">
         <v>0</v>
@@ -29688,7 +29688,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.77396130561829</v>
+        <v>1.773961186409</v>
       </c>
       <c r="H1011" t="n">
         <v>0</v>
@@ -29746,7 +29746,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1013" t="n">
-        <v>1.77396130561829</v>
+        <v>1.773961186409</v>
       </c>
       <c r="H1013" t="n">
         <v>3000</v>
@@ -29862,7 +29862,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1017" t="n">
-        <v>1.77396130561829</v>
+        <v>1.773961186409</v>
       </c>
       <c r="H1017" t="n">
         <v>1500</v>
@@ -29891,7 +29891,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1018" t="n">
-        <v>1.77396130561829</v>
+        <v>1.773961186409</v>
       </c>
       <c r="H1018" t="n">
         <v>0</v>
@@ -29920,7 +29920,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1019" t="n">
-        <v>1.77396130561829</v>
+        <v>1.773961186409</v>
       </c>
       <c r="H1019" t="n">
         <v>0</v>
@@ -30355,7 +30355,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1034" t="n">
-        <v>1.75538575649261</v>
+        <v>1.75538563728333</v>
       </c>
       <c r="H1034" t="n">
         <v>13500</v>
@@ -30384,7 +30384,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.81111228466034</v>
+        <v>1.81111240386963</v>
       </c>
       <c r="H1035" t="n">
         <v>1500</v>
@@ -30616,7 +30616,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.78324902057648</v>
+        <v>1.78324890136719</v>
       </c>
       <c r="H1043" t="n">
         <v>4500</v>
@@ -30645,7 +30645,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1044" t="n">
-        <v>1.77396130561829</v>
+        <v>1.773961186409</v>
       </c>
       <c r="H1044" t="n">
         <v>3000</v>
@@ -30674,7 +30674,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1045" t="n">
-        <v>1.75538575649261</v>
+        <v>1.75538563728333</v>
       </c>
       <c r="H1045" t="n">
         <v>4500</v>
@@ -30703,7 +30703,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1046" t="n">
-        <v>1.77396130561829</v>
+        <v>1.773961186409</v>
       </c>
       <c r="H1046" t="n">
         <v>9000</v>
@@ -30732,7 +30732,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1047" t="n">
-        <v>1.77396130561829</v>
+        <v>1.773961186409</v>
       </c>
       <c r="H1047" t="n">
         <v>1500</v>
@@ -30819,7 +30819,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1050" t="n">
-        <v>1.75538575649261</v>
+        <v>1.75538563728333</v>
       </c>
       <c r="H1050" t="n">
         <v>1500</v>
@@ -30848,7 +30848,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1051" t="n">
-        <v>1.77396130561829</v>
+        <v>1.773961186409</v>
       </c>
       <c r="H1051" t="n">
         <v>4500</v>
@@ -31167,7 +31167,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1062" t="n">
-        <v>1.70894694328308</v>
+        <v>1.70894706249237</v>
       </c>
       <c r="H1062" t="n">
         <v>4500</v>
@@ -32153,7 +32153,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1096" t="n">
-        <v>1.60678172111511</v>
+        <v>1.60678160190582</v>
       </c>
       <c r="H1096" t="n">
         <v>10500</v>
@@ -32211,7 +32211,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1098" t="n">
-        <v>1.78324902057648</v>
+        <v>1.78324890136719</v>
       </c>
       <c r="H1098" t="n">
         <v>25500</v>
@@ -32240,7 +32240,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1099" t="n">
-        <v>1.77396130561829</v>
+        <v>1.773961186409</v>
       </c>
       <c r="H1099" t="n">
         <v>7500</v>
@@ -32269,7 +32269,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1100" t="n">
-        <v>1.75538575649261</v>
+        <v>1.75538563728333</v>
       </c>
       <c r="H1100" t="n">
         <v>6000</v>
@@ -32530,7 +32530,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1109" t="n">
-        <v>1.70894694328308</v>
+        <v>1.70894706249237</v>
       </c>
       <c r="H1109" t="n">
         <v>4500</v>
@@ -33168,7 +33168,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1131" t="n">
-        <v>1.70894694328308</v>
+        <v>1.70894706249237</v>
       </c>
       <c r="H1131" t="n">
         <v>1500</v>
@@ -33255,7 +33255,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1134" t="n">
-        <v>1.70894694328308</v>
+        <v>1.70894706249237</v>
       </c>
       <c r="H1134" t="n">
         <v>6000</v>
@@ -33284,7 +33284,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1135" t="n">
-        <v>1.70894694328308</v>
+        <v>1.70894706249237</v>
       </c>
       <c r="H1135" t="n">
         <v>0</v>
@@ -33951,7 +33951,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1158" t="n">
-        <v>1.65322041511536</v>
+        <v>1.65322029590607</v>
       </c>
       <c r="H1158" t="n">
         <v>3000</v>
@@ -34183,7 +34183,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1166" t="n">
-        <v>1.54176723957062</v>
+        <v>1.54176735877991</v>
       </c>
       <c r="H1166" t="n">
         <v>13500</v>
@@ -34212,7 +34212,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1167" t="n">
-        <v>1.54176723957062</v>
+        <v>1.54176735877991</v>
       </c>
       <c r="H1167" t="n">
         <v>0</v>
@@ -34241,7 +34241,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1168" t="n">
-        <v>1.54176723957062</v>
+        <v>1.54176735877991</v>
       </c>
       <c r="H1168" t="n">
         <v>0</v>

--- a/data/RETI.MI.xlsx
+++ b/data/RETI.MI.xlsx
@@ -456,7 +456,7 @@
         <v>0.899600028991699</v>
       </c>
       <c r="G3" t="n">
-        <v>0.768141031265259</v>
+        <v>0.768140971660614</v>
       </c>
       <c r="H3" t="n">
         <v>472500</v>
@@ -485,7 +485,7 @@
         <v>0.879899978637695</v>
       </c>
       <c r="G4" t="n">
-        <v>0.751319766044617</v>
+        <v>0.751319706439972</v>
       </c>
       <c r="H4" t="n">
         <v>75000</v>
@@ -688,7 +688,7 @@
         <v>0.84799998998642</v>
       </c>
       <c r="G11" t="n">
-        <v>0.724081218242645</v>
+        <v>0.72408127784729</v>
       </c>
       <c r="H11" t="n">
         <v>39000</v>
@@ -746,7 +746,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G13" t="n">
-        <v>0.691634237766266</v>
+        <v>0.691634178161621</v>
       </c>
       <c r="H13" t="n">
         <v>49500</v>
@@ -833,7 +833,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G16" t="n">
-        <v>0.666018128395081</v>
+        <v>0.666018187999725</v>
       </c>
       <c r="H16" t="n">
         <v>67500</v>
@@ -891,7 +891,7 @@
         <v>0.833999991416931</v>
       </c>
       <c r="G18" t="n">
-        <v>0.712127089500427</v>
+        <v>0.712127149105072</v>
       </c>
       <c r="H18" t="n">
         <v>579000</v>
@@ -949,7 +949,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G20" t="n">
-        <v>0.66772586107254</v>
+        <v>0.667725920677185</v>
       </c>
       <c r="H20" t="n">
         <v>72000</v>
@@ -1007,7 +1007,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G22" t="n">
-        <v>0.659187197685242</v>
+        <v>0.659187257289886</v>
       </c>
       <c r="H22" t="n">
         <v>24000</v>
@@ -1036,7 +1036,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G23" t="n">
-        <v>0.666018128395081</v>
+        <v>0.666018187999725</v>
       </c>
       <c r="H23" t="n">
         <v>39000</v>
@@ -1065,7 +1065,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G24" t="n">
-        <v>0.652356207370758</v>
+        <v>0.652356266975403</v>
       </c>
       <c r="H24" t="n">
         <v>10500</v>
@@ -1152,7 +1152,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G27" t="n">
-        <v>0.633571147918701</v>
+        <v>0.633571088314056</v>
       </c>
       <c r="H27" t="n">
         <v>43500</v>
@@ -1210,7 +1210,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G29" t="n">
-        <v>0.623324632644653</v>
+        <v>0.623324692249298</v>
       </c>
       <c r="H29" t="n">
         <v>46500</v>
@@ -1239,7 +1239,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G30" t="n">
-        <v>0.607955038547516</v>
+        <v>0.607955098152161</v>
       </c>
       <c r="H30" t="n">
         <v>19500</v>
@@ -1326,7 +1326,7 @@
         <v>0.722000002861023</v>
       </c>
       <c r="G33" t="n">
-        <v>0.616493761539459</v>
+        <v>0.616493701934814</v>
       </c>
       <c r="H33" t="n">
         <v>3000</v>
@@ -1413,7 +1413,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G36" t="n">
-        <v>0.563553810119629</v>
+        <v>0.563553869724274</v>
       </c>
       <c r="H36" t="n">
         <v>66000</v>
@@ -1500,7 +1500,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G39" t="n">
-        <v>0.525983572006226</v>
+        <v>0.525983512401581</v>
       </c>
       <c r="H39" t="n">
         <v>10500</v>
@@ -1529,7 +1529,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G40" t="n">
-        <v>0.546476423740387</v>
+        <v>0.546476483345032</v>
       </c>
       <c r="H40" t="n">
         <v>15000</v>
@@ -1587,7 +1587,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G42" t="n">
-        <v>0.604539632797241</v>
+        <v>0.604539573192596</v>
       </c>
       <c r="H42" t="n">
         <v>127500</v>
@@ -1616,7 +1616,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G43" t="n">
-        <v>0.623324632644653</v>
+        <v>0.623324692249298</v>
       </c>
       <c r="H43" t="n">
         <v>138000</v>
@@ -1645,7 +1645,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G44" t="n">
-        <v>0.604539632797241</v>
+        <v>0.604539573192596</v>
       </c>
       <c r="H44" t="n">
         <v>64500</v>
@@ -1674,7 +1674,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G45" t="n">
-        <v>0.618201434612274</v>
+        <v>0.618201494216919</v>
       </c>
       <c r="H45" t="n">
         <v>18000</v>
@@ -1732,7 +1732,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G47" t="n">
-        <v>0.607955038547516</v>
+        <v>0.607955098152161</v>
       </c>
       <c r="H47" t="n">
         <v>7500</v>
@@ -1964,7 +1964,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G55" t="n">
-        <v>0.677972376346588</v>
+        <v>0.677972316741943</v>
       </c>
       <c r="H55" t="n">
         <v>36000</v>
@@ -1993,7 +1993,7 @@
         <v>0.815999984741211</v>
       </c>
       <c r="G56" t="n">
-        <v>0.69675749540329</v>
+        <v>0.696757435798645</v>
       </c>
       <c r="H56" t="n">
         <v>28500</v>
@@ -2254,7 +2254,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G65" t="n">
-        <v>0.66772586107254</v>
+        <v>0.667725920677185</v>
       </c>
       <c r="H65" t="n">
         <v>10500</v>
@@ -2341,7 +2341,7 @@
         <v>0.815999984741211</v>
       </c>
       <c r="G68" t="n">
-        <v>0.69675749540329</v>
+        <v>0.696757435798645</v>
       </c>
       <c r="H68" t="n">
         <v>7500</v>
@@ -2370,7 +2370,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G69" t="n">
-        <v>0.69334203004837</v>
+        <v>0.693341970443726</v>
       </c>
       <c r="H69" t="n">
         <v>15000</v>
@@ -2399,7 +2399,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G70" t="n">
-        <v>0.677972376346588</v>
+        <v>0.677972316741943</v>
       </c>
       <c r="H70" t="n">
         <v>3000</v>
@@ -2428,7 +2428,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G71" t="n">
-        <v>0.677972376346588</v>
+        <v>0.677972316741943</v>
       </c>
       <c r="H71" t="n">
         <v>3000</v>
@@ -2457,7 +2457,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G72" t="n">
-        <v>0.69334203004837</v>
+        <v>0.693341970443726</v>
       </c>
       <c r="H72" t="n">
         <v>3000</v>
@@ -2515,7 +2515,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G74" t="n">
-        <v>0.691634237766266</v>
+        <v>0.691634178161621</v>
       </c>
       <c r="H74" t="n">
         <v>43500</v>
@@ -2544,7 +2544,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G75" t="n">
-        <v>0.700172901153564</v>
+        <v>0.700172960758209</v>
       </c>
       <c r="H75" t="n">
         <v>73500</v>
@@ -2573,7 +2573,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G76" t="n">
-        <v>0.707003831863403</v>
+        <v>0.707003891468048</v>
       </c>
       <c r="H76" t="n">
         <v>7500</v>
@@ -2602,7 +2602,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G77" t="n">
-        <v>0.700172901153564</v>
+        <v>0.700172960758209</v>
       </c>
       <c r="H77" t="n">
         <v>22500</v>
@@ -2631,7 +2631,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G78" t="n">
-        <v>0.700172901153564</v>
+        <v>0.700172960758209</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
@@ -2689,7 +2689,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G80" t="n">
-        <v>0.717250347137451</v>
+        <v>0.717250287532806</v>
       </c>
       <c r="H80" t="n">
         <v>28500</v>
@@ -2747,7 +2747,7 @@
         <v>0.833999991416931</v>
       </c>
       <c r="G82" t="n">
-        <v>0.712127089500427</v>
+        <v>0.712127149105072</v>
       </c>
       <c r="H82" t="n">
         <v>4500</v>
@@ -2776,7 +2776,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G83" t="n">
-        <v>0.715542614459991</v>
+        <v>0.715542674064636</v>
       </c>
       <c r="H83" t="n">
         <v>1500</v>
@@ -2805,7 +2805,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G84" t="n">
-        <v>0.717250347137451</v>
+        <v>0.717250287532806</v>
       </c>
       <c r="H84" t="n">
         <v>1500</v>
@@ -2834,7 +2834,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G85" t="n">
-        <v>0.715542614459991</v>
+        <v>0.715542674064636</v>
       </c>
       <c r="H85" t="n">
         <v>9000</v>
@@ -2863,7 +2863,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G86" t="n">
-        <v>0.700172901153564</v>
+        <v>0.700172960758209</v>
       </c>
       <c r="H86" t="n">
         <v>1500</v>
@@ -2921,7 +2921,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G88" t="n">
-        <v>0.700172901153564</v>
+        <v>0.700172960758209</v>
       </c>
       <c r="H88" t="n">
         <v>16500</v>
@@ -2950,7 +2950,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G89" t="n">
-        <v>0.684803247451782</v>
+        <v>0.684803187847137</v>
       </c>
       <c r="H89" t="n">
         <v>22500</v>
@@ -2979,7 +2979,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G90" t="n">
-        <v>0.684803247451782</v>
+        <v>0.684803187847137</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -3095,7 +3095,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G94" t="n">
-        <v>0.69846522808075</v>
+        <v>0.698465168476105</v>
       </c>
       <c r="H94" t="n">
         <v>19500</v>
@@ -3182,7 +3182,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G97" t="n">
-        <v>0.66772586107254</v>
+        <v>0.667725920677185</v>
       </c>
       <c r="H97" t="n">
         <v>9000</v>
@@ -3211,7 +3211,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G98" t="n">
-        <v>0.666018128395081</v>
+        <v>0.666018187999725</v>
       </c>
       <c r="H98" t="n">
         <v>18000</v>
@@ -3240,7 +3240,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G99" t="n">
-        <v>0.677972376346588</v>
+        <v>0.677972316741943</v>
       </c>
       <c r="H99" t="n">
         <v>7500</v>
@@ -3269,7 +3269,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G100" t="n">
-        <v>0.676264584064484</v>
+        <v>0.676264643669128</v>
       </c>
       <c r="H100" t="n">
         <v>7500</v>
@@ -3298,7 +3298,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G101" t="n">
-        <v>0.676264584064484</v>
+        <v>0.676264643669128</v>
       </c>
       <c r="H101" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G103" t="n">
-        <v>0.707003831863403</v>
+        <v>0.707003891468048</v>
       </c>
       <c r="H103" t="n">
         <v>22500</v>
@@ -3472,7 +3472,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G107" t="n">
-        <v>0.691634237766266</v>
+        <v>0.691634178161621</v>
       </c>
       <c r="H107" t="n">
         <v>42000</v>
@@ -3501,7 +3501,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G108" t="n">
-        <v>0.700172901153564</v>
+        <v>0.700172960758209</v>
       </c>
       <c r="H108" t="n">
         <v>55500</v>
@@ -3559,7 +3559,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G110" t="n">
-        <v>0.69846522808075</v>
+        <v>0.698465168476105</v>
       </c>
       <c r="H110" t="n">
         <v>6000</v>
@@ -3617,7 +3617,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G112" t="n">
-        <v>0.686511039733887</v>
+        <v>0.686511099338531</v>
       </c>
       <c r="H112" t="n">
         <v>40500</v>
@@ -3646,7 +3646,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G113" t="n">
-        <v>0.691634237766266</v>
+        <v>0.691634178161621</v>
       </c>
       <c r="H113" t="n">
         <v>4500</v>
@@ -3675,7 +3675,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G114" t="n">
-        <v>0.700172901153564</v>
+        <v>0.700172960758209</v>
       </c>
       <c r="H114" t="n">
         <v>21000</v>
@@ -3762,7 +3762,7 @@
         <v>0.842000007629395</v>
       </c>
       <c r="G117" t="n">
-        <v>0.718958020210266</v>
+        <v>0.718958079814911</v>
       </c>
       <c r="H117" t="n">
         <v>102000</v>
@@ -3791,7 +3791,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G118" t="n">
-        <v>0.717250347137451</v>
+        <v>0.717250287532806</v>
       </c>
       <c r="H118" t="n">
         <v>69000</v>
@@ -3820,7 +3820,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G119" t="n">
-        <v>0.715542614459991</v>
+        <v>0.715542674064636</v>
       </c>
       <c r="H119" t="n">
         <v>16500</v>
@@ -3849,7 +3849,7 @@
         <v>0.867999970912933</v>
       </c>
       <c r="G120" t="n">
-        <v>0.741158664226532</v>
+        <v>0.741158604621887</v>
       </c>
       <c r="H120" t="n">
         <v>139500</v>
@@ -3878,7 +3878,7 @@
         <v>0.867999970912933</v>
       </c>
       <c r="G121" t="n">
-        <v>0.741158664226532</v>
+        <v>0.741158604621887</v>
       </c>
       <c r="H121" t="n">
         <v>151500</v>
@@ -3907,7 +3907,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G122" t="n">
-        <v>0.858138799667358</v>
+        <v>0.858138859272003</v>
       </c>
       <c r="H122" t="n">
         <v>660000</v>
@@ -3936,7 +3936,7 @@
         <v>0.972000002861023</v>
       </c>
       <c r="G123" t="n">
-        <v>0.829961121082306</v>
+        <v>0.829961061477661</v>
       </c>
       <c r="H123" t="n">
         <v>922500</v>
@@ -3965,7 +3965,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G124" t="n">
-        <v>0.828253388404846</v>
+        <v>0.828253328800201</v>
       </c>
       <c r="H124" t="n">
         <v>213000</v>
@@ -4052,7 +4052,7 @@
         <v>1</v>
       </c>
       <c r="G127" t="n">
-        <v>0.853869438171387</v>
+        <v>0.853869378566742</v>
       </c>
       <c r="H127" t="n">
         <v>66000</v>
@@ -4081,7 +4081,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G128" t="n">
-        <v>0.862408101558685</v>
+        <v>0.86240816116333</v>
       </c>
       <c r="H128" t="n">
         <v>60000</v>
@@ -4110,7 +4110,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G129" t="n">
-        <v>0.862408101558685</v>
+        <v>0.86240816116333</v>
       </c>
       <c r="H129" t="n">
         <v>25500</v>
@@ -4139,7 +4139,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G130" t="n">
-        <v>0.862408101558685</v>
+        <v>0.86240816116333</v>
       </c>
       <c r="H130" t="n">
         <v>72000</v>
@@ -4168,7 +4168,7 @@
         <v>0.994000017642975</v>
       </c>
       <c r="G131" t="n">
-        <v>0.848746299743652</v>
+        <v>0.848746240139008</v>
       </c>
       <c r="H131" t="n">
         <v>60000</v>
@@ -4284,7 +4284,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G135" t="n">
-        <v>0.866677522659302</v>
+        <v>0.866677463054657</v>
       </c>
       <c r="H135" t="n">
         <v>15000</v>
@@ -4342,7 +4342,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G137" t="n">
-        <v>0.888024151325226</v>
+        <v>0.888024210929871</v>
       </c>
       <c r="H137" t="n">
         <v>33000</v>
@@ -4400,7 +4400,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G139" t="n">
-        <v>0.913640320301056</v>
+        <v>0.913640379905701</v>
       </c>
       <c r="H139" t="n">
         <v>4500</v>
@@ -4487,7 +4487,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G142" t="n">
-        <v>0.913640320301056</v>
+        <v>0.913640379905701</v>
       </c>
       <c r="H142" t="n">
         <v>42000</v>
@@ -4603,7 +4603,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G146" t="n">
-        <v>1.1356463432312</v>
+        <v>1.13564646244049</v>
       </c>
       <c r="H146" t="n">
         <v>342000</v>
@@ -4661,7 +4661,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G148" t="n">
-        <v>1.20395600795746</v>
+        <v>1.20395588874817</v>
       </c>
       <c r="H148" t="n">
         <v>210000</v>
@@ -4690,7 +4690,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G149" t="n">
-        <v>1.20395600795746</v>
+        <v>1.20395588874817</v>
       </c>
       <c r="H149" t="n">
         <v>172500</v>
@@ -4719,7 +4719,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G150" t="n">
-        <v>1.18637979030609</v>
+        <v>1.18637990951538</v>
       </c>
       <c r="H150" t="n">
         <v>103500</v>
@@ -4777,7 +4777,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G152" t="n">
-        <v>1.22153186798096</v>
+        <v>1.22153174877167</v>
       </c>
       <c r="H152" t="n">
         <v>57000</v>
@@ -4806,7 +4806,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G153" t="n">
-        <v>1.22153186798096</v>
+        <v>1.22153174877167</v>
       </c>
       <c r="H153" t="n">
         <v>157500</v>
@@ -4864,7 +4864,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G155" t="n">
-        <v>1.13804602622986</v>
+        <v>1.13804590702057</v>
       </c>
       <c r="H155" t="n">
         <v>30000</v>
@@ -4922,7 +4922,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G157" t="n">
-        <v>1.13365197181702</v>
+        <v>1.13365185260773</v>
       </c>
       <c r="H157" t="n">
         <v>46500</v>
@@ -5038,7 +5038,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G161" t="n">
-        <v>1.08971190452576</v>
+        <v>1.08971178531647</v>
       </c>
       <c r="H161" t="n">
         <v>136500</v>
@@ -5096,7 +5096,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G163" t="n">
-        <v>1.13365197181702</v>
+        <v>1.13365185260773</v>
       </c>
       <c r="H163" t="n">
         <v>21000</v>
@@ -5154,7 +5154,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G165" t="n">
-        <v>1.16880393028259</v>
+        <v>1.16880404949188</v>
       </c>
       <c r="H165" t="n">
         <v>52500</v>
@@ -5183,7 +5183,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G166" t="n">
-        <v>1.16001582145691</v>
+        <v>1.1600159406662</v>
       </c>
       <c r="H166" t="n">
         <v>49500</v>
@@ -5328,7 +5328,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G171" t="n">
-        <v>1.13804602622986</v>
+        <v>1.13804590702057</v>
       </c>
       <c r="H171" t="n">
         <v>9000</v>
@@ -5386,7 +5386,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G173" t="n">
-        <v>1.18637979030609</v>
+        <v>1.18637990951538</v>
       </c>
       <c r="H173" t="n">
         <v>85500</v>
@@ -5444,7 +5444,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G175" t="n">
-        <v>1.23031997680664</v>
+        <v>1.23031985759735</v>
       </c>
       <c r="H175" t="n">
         <v>234000</v>
@@ -5473,7 +5473,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G176" t="n">
-        <v>1.32259392738342</v>
+        <v>1.32259368896484</v>
       </c>
       <c r="H176" t="n">
         <v>226500</v>
@@ -5502,7 +5502,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G177" t="n">
-        <v>1.32259392738342</v>
+        <v>1.32259368896484</v>
       </c>
       <c r="H177" t="n">
         <v>208500</v>
@@ -5589,7 +5589,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G180" t="n">
-        <v>1.34895777702332</v>
+        <v>1.34895801544189</v>
       </c>
       <c r="H180" t="n">
         <v>9000</v>
@@ -5647,7 +5647,7 @@
         <v>1.5</v>
       </c>
       <c r="G182" t="n">
-        <v>1.31819987297058</v>
+        <v>1.31819975376129</v>
       </c>
       <c r="H182" t="n">
         <v>39000</v>
@@ -5676,7 +5676,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G183" t="n">
-        <v>1.28304779529572</v>
+        <v>1.283047914505</v>
       </c>
       <c r="H183" t="n">
         <v>180000</v>
@@ -5705,7 +5705,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G184" t="n">
-        <v>1.32259392738342</v>
+        <v>1.32259368896484</v>
       </c>
       <c r="H184" t="n">
         <v>30000</v>
@@ -5734,7 +5734,7 @@
         <v>1.5</v>
       </c>
       <c r="G185" t="n">
-        <v>1.31819987297058</v>
+        <v>1.31819975376129</v>
       </c>
       <c r="H185" t="n">
         <v>19500</v>
@@ -5763,7 +5763,7 @@
         <v>1.5</v>
       </c>
       <c r="G186" t="n">
-        <v>1.31819987297058</v>
+        <v>1.31819975376129</v>
       </c>
       <c r="H186" t="n">
         <v>31500</v>
@@ -5821,7 +5821,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G188" t="n">
-        <v>1.34895777702332</v>
+        <v>1.34895801544189</v>
       </c>
       <c r="H188" t="n">
         <v>36000</v>
@@ -5850,7 +5850,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G189" t="n">
-        <v>1.45001983642578</v>
+        <v>1.45001995563507</v>
       </c>
       <c r="H189" t="n">
         <v>148500</v>
@@ -5937,7 +5937,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G192" t="n">
-        <v>1.37971580028534</v>
+        <v>1.37971591949463</v>
       </c>
       <c r="H192" t="n">
         <v>87000</v>
@@ -5966,7 +5966,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G193" t="n">
-        <v>1.34895777702332</v>
+        <v>1.34895801544189</v>
       </c>
       <c r="H193" t="n">
         <v>34500</v>
@@ -5995,7 +5995,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G194" t="n">
-        <v>1.34016978740692</v>
+        <v>1.34016990661621</v>
       </c>
       <c r="H194" t="n">
         <v>85500</v>
@@ -6053,7 +6053,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G196" t="n">
-        <v>1.33138191699982</v>
+        <v>1.33138179779053</v>
       </c>
       <c r="H196" t="n">
         <v>66000</v>
@@ -6082,7 +6082,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G197" t="n">
-        <v>1.32259392738342</v>
+        <v>1.32259368896484</v>
       </c>
       <c r="H197" t="n">
         <v>43500</v>
@@ -6111,7 +6111,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G198" t="n">
-        <v>1.32698798179626</v>
+        <v>1.32698786258698</v>
       </c>
       <c r="H198" t="n">
         <v>13500</v>
@@ -6169,7 +6169,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G200" t="n">
-        <v>1.34895777702332</v>
+        <v>1.34895801544189</v>
       </c>
       <c r="H200" t="n">
         <v>22500</v>
@@ -6198,7 +6198,7 @@
         <v>1.5</v>
       </c>
       <c r="G201" t="n">
-        <v>1.31819987297058</v>
+        <v>1.31819975376129</v>
       </c>
       <c r="H201" t="n">
         <v>16500</v>
@@ -6227,7 +6227,7 @@
         <v>1.5</v>
       </c>
       <c r="G202" t="n">
-        <v>1.31819987297058</v>
+        <v>1.31819975376129</v>
       </c>
       <c r="H202" t="n">
         <v>3000</v>
@@ -6256,7 +6256,7 @@
         <v>1.5</v>
       </c>
       <c r="G203" t="n">
-        <v>1.31819987297058</v>
+        <v>1.31819975376129</v>
       </c>
       <c r="H203" t="n">
         <v>12000</v>
@@ -6285,7 +6285,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G204" t="n">
-        <v>1.33138191699982</v>
+        <v>1.33138179779053</v>
       </c>
       <c r="H204" t="n">
         <v>6000</v>
@@ -6401,7 +6401,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G208" t="n">
-        <v>1.35335183143616</v>
+        <v>1.35335195064545</v>
       </c>
       <c r="H208" t="n">
         <v>1500</v>
@@ -6430,7 +6430,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G209" t="n">
-        <v>1.35335183143616</v>
+        <v>1.35335195064545</v>
       </c>
       <c r="H209" t="n">
         <v>0</v>
@@ -6459,7 +6459,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G210" t="n">
-        <v>1.35335183143616</v>
+        <v>1.35335195064545</v>
       </c>
       <c r="H210" t="n">
         <v>0</v>
@@ -6575,7 +6575,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G214" t="n">
-        <v>1.34895777702332</v>
+        <v>1.34895801544189</v>
       </c>
       <c r="H214" t="n">
         <v>28500</v>
@@ -6604,7 +6604,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G215" t="n">
-        <v>1.32698798179626</v>
+        <v>1.32698786258698</v>
       </c>
       <c r="H215" t="n">
         <v>13500</v>
@@ -6633,7 +6633,7 @@
         <v>1.5</v>
       </c>
       <c r="G216" t="n">
-        <v>1.31819987297058</v>
+        <v>1.31819975376129</v>
       </c>
       <c r="H216" t="n">
         <v>15000</v>
@@ -6691,7 +6691,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G218" t="n">
-        <v>1.24789571762085</v>
+        <v>1.24789595603943</v>
       </c>
       <c r="H218" t="n">
         <v>33000</v>
@@ -6720,7 +6720,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G219" t="n">
-        <v>1.23031997680664</v>
+        <v>1.23031985759735</v>
       </c>
       <c r="H219" t="n">
         <v>70500</v>
@@ -6778,7 +6778,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G221" t="n">
-        <v>1.28744196891785</v>
+        <v>1.28744184970856</v>
       </c>
       <c r="H221" t="n">
         <v>15000</v>
@@ -6865,7 +6865,7 @@
         <v>1.5</v>
       </c>
       <c r="G224" t="n">
-        <v>1.31819987297058</v>
+        <v>1.31819975376129</v>
       </c>
       <c r="H224" t="n">
         <v>13500</v>
@@ -6894,7 +6894,7 @@
         <v>1.5</v>
       </c>
       <c r="G225" t="n">
-        <v>1.31819987297058</v>
+        <v>1.31819975376129</v>
       </c>
       <c r="H225" t="n">
         <v>0</v>
@@ -6952,7 +6952,7 @@
         <v>1.5</v>
       </c>
       <c r="G227" t="n">
-        <v>1.31819987297058</v>
+        <v>1.31819975376129</v>
       </c>
       <c r="H227" t="n">
         <v>13500</v>
@@ -7068,7 +7068,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G231" t="n">
-        <v>1.28304779529572</v>
+        <v>1.283047914505</v>
       </c>
       <c r="H231" t="n">
         <v>4500</v>
@@ -7126,7 +7126,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G233" t="n">
-        <v>1.34016978740692</v>
+        <v>1.34016990661621</v>
       </c>
       <c r="H233" t="n">
         <v>61500</v>
@@ -7213,7 +7213,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G236" t="n">
-        <v>1.34895777702332</v>
+        <v>1.34895801544189</v>
       </c>
       <c r="H236" t="n">
         <v>13500</v>
@@ -7300,7 +7300,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G239" t="n">
-        <v>1.34016978740692</v>
+        <v>1.34016990661621</v>
       </c>
       <c r="H239" t="n">
         <v>69000</v>
@@ -7329,7 +7329,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G240" t="n">
-        <v>1.74881184101105</v>
+        <v>1.74881172180176</v>
       </c>
       <c r="H240" t="n">
         <v>333000</v>
@@ -7358,7 +7358,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G241" t="n">
-        <v>2.24972772598267</v>
+        <v>2.24972796440125</v>
       </c>
       <c r="H241" t="n">
         <v>774000</v>
@@ -7387,7 +7387,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G242" t="n">
-        <v>2.08275580406189</v>
+        <v>2.08275556564331</v>
       </c>
       <c r="H242" t="n">
         <v>1374000</v>
@@ -7416,7 +7416,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G243" t="n">
-        <v>2.23215174674988</v>
+        <v>2.2321515083313</v>
       </c>
       <c r="H243" t="n">
         <v>702000</v>
@@ -7474,7 +7474,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G245" t="n">
-        <v>2.39912390708923</v>
+        <v>2.39912366867065</v>
       </c>
       <c r="H245" t="n">
         <v>546000</v>
@@ -7503,7 +7503,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G246" t="n">
-        <v>2.27609205245972</v>
+        <v>2.27609181404114</v>
       </c>
       <c r="H246" t="n">
         <v>229500</v>
@@ -7561,7 +7561,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G248" t="n">
-        <v>2.27609205245972</v>
+        <v>2.27609181404114</v>
       </c>
       <c r="H248" t="n">
         <v>240000</v>
@@ -7619,7 +7619,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G250" t="n">
-        <v>2.23215174674988</v>
+        <v>2.2321515083313</v>
       </c>
       <c r="H250" t="n">
         <v>102000</v>
@@ -7648,7 +7648,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G251" t="n">
-        <v>2.18821167945862</v>
+        <v>2.1882119178772</v>
       </c>
       <c r="H251" t="n">
         <v>40500</v>
@@ -7677,7 +7677,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G252" t="n">
-        <v>2.18821167945862</v>
+        <v>2.1882119178772</v>
       </c>
       <c r="H252" t="n">
         <v>36000</v>
@@ -7764,7 +7764,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G255" t="n">
-        <v>2.33760786056519</v>
+        <v>2.33760809898376</v>
       </c>
       <c r="H255" t="n">
         <v>108000</v>
@@ -7851,7 +7851,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G258" t="n">
-        <v>2.28487968444824</v>
+        <v>2.28487992286682</v>
       </c>
       <c r="H258" t="n">
         <v>138000</v>
@@ -7880,7 +7880,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G259" t="n">
-        <v>2.22336363792419</v>
+        <v>2.22336339950562</v>
       </c>
       <c r="H259" t="n">
         <v>60000</v>
@@ -7967,7 +7967,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G262" t="n">
-        <v>2.24972772598267</v>
+        <v>2.24972796440125</v>
       </c>
       <c r="H262" t="n">
         <v>33000</v>
@@ -8112,7 +8112,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G267" t="n">
-        <v>2.27609205245972</v>
+        <v>2.27609181404114</v>
       </c>
       <c r="H267" t="n">
         <v>61500</v>
@@ -8199,7 +8199,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G270" t="n">
-        <v>2.23215174674988</v>
+        <v>2.2321515083313</v>
       </c>
       <c r="H270" t="n">
         <v>97500</v>
@@ -8286,7 +8286,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G273" t="n">
-        <v>2.27609205245972</v>
+        <v>2.27609181404114</v>
       </c>
       <c r="H273" t="n">
         <v>94500</v>
@@ -8315,7 +8315,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G274" t="n">
-        <v>2.24972772598267</v>
+        <v>2.24972796440125</v>
       </c>
       <c r="H274" t="n">
         <v>45000</v>
@@ -8344,7 +8344,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G275" t="n">
-        <v>2.28487968444824</v>
+        <v>2.28487992286682</v>
       </c>
       <c r="H275" t="n">
         <v>18000</v>
@@ -8373,7 +8373,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G276" t="n">
-        <v>2.28487968444824</v>
+        <v>2.28487992286682</v>
       </c>
       <c r="H276" t="n">
         <v>6000</v>
@@ -8460,7 +8460,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G279" t="n">
-        <v>2.32003164291382</v>
+        <v>2.3200318813324</v>
       </c>
       <c r="H279" t="n">
         <v>10500</v>
@@ -8489,7 +8489,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G280" t="n">
-        <v>2.28487968444824</v>
+        <v>2.28487992286682</v>
       </c>
       <c r="H280" t="n">
         <v>16500</v>
@@ -8605,7 +8605,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G284" t="n">
-        <v>2.32003164291382</v>
+        <v>2.3200318813324</v>
       </c>
       <c r="H284" t="n">
         <v>18000</v>
@@ -8634,7 +8634,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G285" t="n">
-        <v>2.27609205245972</v>
+        <v>2.27609181404114</v>
       </c>
       <c r="H285" t="n">
         <v>24000</v>
@@ -8663,7 +8663,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G286" t="n">
-        <v>2.26730394363403</v>
+        <v>2.26730370521545</v>
       </c>
       <c r="H286" t="n">
         <v>28500</v>
@@ -8750,7 +8750,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G289" t="n">
-        <v>2.32003164291382</v>
+        <v>2.3200318813324</v>
       </c>
       <c r="H289" t="n">
         <v>87000</v>
@@ -8808,7 +8808,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G291" t="n">
-        <v>2.27609205245972</v>
+        <v>2.27609181404114</v>
       </c>
       <c r="H291" t="n">
         <v>18000</v>
@@ -8866,7 +8866,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G293" t="n">
-        <v>2.24972772598267</v>
+        <v>2.24972796440125</v>
       </c>
       <c r="H293" t="n">
         <v>1500</v>
@@ -8895,7 +8895,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G294" t="n">
-        <v>2.28487968444824</v>
+        <v>2.28487992286682</v>
       </c>
       <c r="H294" t="n">
         <v>1500</v>
@@ -8924,7 +8924,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G295" t="n">
-        <v>2.26730394363403</v>
+        <v>2.26730370521545</v>
       </c>
       <c r="H295" t="n">
         <v>30000</v>
@@ -8953,7 +8953,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G296" t="n">
-        <v>2.23215174674988</v>
+        <v>2.2321515083313</v>
       </c>
       <c r="H296" t="n">
         <v>7500</v>
@@ -9040,7 +9040,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G299" t="n">
-        <v>2.22336363792419</v>
+        <v>2.22336339950562</v>
       </c>
       <c r="H299" t="n">
         <v>4500</v>
@@ -9127,7 +9127,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G302" t="n">
-        <v>2.14427208900452</v>
+        <v>2.14427185058594</v>
       </c>
       <c r="H302" t="n">
         <v>31500</v>
@@ -9156,7 +9156,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G303" t="n">
-        <v>2.07396769523621</v>
+        <v>2.07396793365479</v>
       </c>
       <c r="H303" t="n">
         <v>58500</v>
@@ -9214,7 +9214,7 @@
         <v>2.25</v>
       </c>
       <c r="G305" t="n">
-        <v>1.97729969024658</v>
+        <v>1.97729980945587</v>
       </c>
       <c r="H305" t="n">
         <v>51000</v>
@@ -9243,7 +9243,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G306" t="n">
-        <v>1.99487566947937</v>
+        <v>1.99487578868866</v>
       </c>
       <c r="H306" t="n">
         <v>13500</v>
@@ -9272,7 +9272,7 @@
         <v>2.25</v>
       </c>
       <c r="G307" t="n">
-        <v>1.97729969024658</v>
+        <v>1.97729980945587</v>
       </c>
       <c r="H307" t="n">
         <v>13500</v>
@@ -9301,7 +9301,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G308" t="n">
-        <v>2.02123975753784</v>
+        <v>2.02123951911926</v>
       </c>
       <c r="H308" t="n">
         <v>12000</v>
@@ -9330,7 +9330,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G309" t="n">
-        <v>1.93335998058319</v>
+        <v>1.93335962295532</v>
       </c>
       <c r="H309" t="n">
         <v>18000</v>
@@ -9417,7 +9417,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G312" t="n">
-        <v>1.8279036283493</v>
+        <v>1.82790374755859</v>
       </c>
       <c r="H312" t="n">
         <v>37500</v>
@@ -9446,7 +9446,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G313" t="n">
-        <v>1.93335998058319</v>
+        <v>1.93335962295532</v>
       </c>
       <c r="H313" t="n">
         <v>18000</v>
@@ -9475,7 +9475,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G314" t="n">
-        <v>1.93335998058319</v>
+        <v>1.93335962295532</v>
       </c>
       <c r="H314" t="n">
         <v>6000</v>
@@ -9504,7 +9504,7 @@
         <v>2.25</v>
       </c>
       <c r="G315" t="n">
-        <v>1.97729969024658</v>
+        <v>1.97729980945587</v>
       </c>
       <c r="H315" t="n">
         <v>25500</v>
@@ -9533,7 +9533,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G316" t="n">
-        <v>2.08275580406189</v>
+        <v>2.08275556564331</v>
       </c>
       <c r="H316" t="n">
         <v>48000</v>
@@ -9562,7 +9562,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G317" t="n">
-        <v>2.07396769523621</v>
+        <v>2.07396793365479</v>
       </c>
       <c r="H317" t="n">
         <v>12000</v>
@@ -9620,7 +9620,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G319" t="n">
-        <v>2.12669563293457</v>
+        <v>2.12669587135315</v>
       </c>
       <c r="H319" t="n">
         <v>15000</v>
@@ -9649,7 +9649,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G320" t="n">
-        <v>2.14427208900452</v>
+        <v>2.14427185058594</v>
       </c>
       <c r="H320" t="n">
         <v>9000</v>
@@ -9678,7 +9678,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G321" t="n">
-        <v>2.14427208900452</v>
+        <v>2.14427185058594</v>
       </c>
       <c r="H321" t="n">
         <v>3000</v>
@@ -9823,7 +9823,7 @@
         <v>2.25</v>
       </c>
       <c r="G326" t="n">
-        <v>1.97729969024658</v>
+        <v>1.97729980945587</v>
       </c>
       <c r="H326" t="n">
         <v>48000</v>
@@ -9968,7 +9968,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G331" t="n">
-        <v>1.99487566947937</v>
+        <v>1.99487578868866</v>
       </c>
       <c r="H331" t="n">
         <v>12000</v>
@@ -9997,7 +9997,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G332" t="n">
-        <v>1.99487566947937</v>
+        <v>1.99487578868866</v>
       </c>
       <c r="H332" t="n">
         <v>7500</v>
@@ -10026,7 +10026,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G333" t="n">
-        <v>1.99487566947937</v>
+        <v>1.99487578868866</v>
       </c>
       <c r="H333" t="n">
         <v>6000</v>
@@ -10113,7 +10113,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G336" t="n">
-        <v>2.02123975753784</v>
+        <v>2.02123951911926</v>
       </c>
       <c r="H336" t="n">
         <v>10500</v>
@@ -10171,7 +10171,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G338" t="n">
-        <v>2.05639171600342</v>
+        <v>2.056391954422</v>
       </c>
       <c r="H338" t="n">
         <v>3000</v>
@@ -10200,7 +10200,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G339" t="n">
-        <v>2.08275580406189</v>
+        <v>2.08275556564331</v>
       </c>
       <c r="H339" t="n">
         <v>3000</v>
@@ -10345,7 +10345,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G344" t="n">
-        <v>1.9597235918045</v>
+        <v>1.95972394943237</v>
       </c>
       <c r="H344" t="n">
         <v>27000</v>
@@ -10432,7 +10432,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G347" t="n">
-        <v>1.96851170063019</v>
+        <v>1.96851181983948</v>
       </c>
       <c r="H347" t="n">
         <v>15000</v>
@@ -10461,7 +10461,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G348" t="n">
-        <v>1.93335998058319</v>
+        <v>1.93335962295532</v>
       </c>
       <c r="H348" t="n">
         <v>1500</v>
@@ -10490,7 +10490,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G349" t="n">
-        <v>1.90699577331543</v>
+        <v>1.90699589252472</v>
       </c>
       <c r="H349" t="n">
         <v>7500</v>
@@ -10519,7 +10519,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G350" t="n">
-        <v>1.90699577331543</v>
+        <v>1.90699589252472</v>
       </c>
       <c r="H350" t="n">
         <v>4500</v>
@@ -10577,7 +10577,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G352" t="n">
-        <v>1.81032764911652</v>
+        <v>1.81032776832581</v>
       </c>
       <c r="H352" t="n">
         <v>10500</v>
@@ -10664,7 +10664,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G355" t="n">
-        <v>1.92457187175751</v>
+        <v>1.9245719909668</v>
       </c>
       <c r="H355" t="n">
         <v>13500</v>
@@ -10722,7 +10722,7 @@
         <v>2.25</v>
       </c>
       <c r="G357" t="n">
-        <v>1.97729969024658</v>
+        <v>1.97729980945587</v>
       </c>
       <c r="H357" t="n">
         <v>7500</v>
@@ -10838,7 +10838,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G361" t="n">
-        <v>1.99487566947937</v>
+        <v>1.99487578868866</v>
       </c>
       <c r="H361" t="n">
         <v>15000</v>
@@ -10867,7 +10867,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G362" t="n">
-        <v>1.99487566947937</v>
+        <v>1.99487578868866</v>
       </c>
       <c r="H362" t="n">
         <v>6000</v>
@@ -10896,7 +10896,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G363" t="n">
-        <v>1.96851170063019</v>
+        <v>1.96851181983948</v>
       </c>
       <c r="H363" t="n">
         <v>3000</v>
@@ -10983,7 +10983,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G366" t="n">
-        <v>1.93335998058319</v>
+        <v>1.93335962295532</v>
       </c>
       <c r="H366" t="n">
         <v>13500</v>
@@ -11012,7 +11012,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G367" t="n">
-        <v>1.93335998058319</v>
+        <v>1.93335962295532</v>
       </c>
       <c r="H367" t="n">
         <v>1500</v>
@@ -11070,7 +11070,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G369" t="n">
-        <v>1.98608779907227</v>
+        <v>1.98608791828156</v>
       </c>
       <c r="H369" t="n">
         <v>25500</v>
@@ -11099,7 +11099,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G370" t="n">
-        <v>1.93335998058319</v>
+        <v>1.93335962295532</v>
       </c>
       <c r="H370" t="n">
         <v>6000</v>
@@ -11128,7 +11128,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G371" t="n">
-        <v>1.93335998058319</v>
+        <v>1.93335962295532</v>
       </c>
       <c r="H371" t="n">
         <v>1500</v>
@@ -11157,7 +11157,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G372" t="n">
-        <v>1.98608779907227</v>
+        <v>1.98608791828156</v>
       </c>
       <c r="H372" t="n">
         <v>7500</v>
@@ -11186,7 +11186,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G373" t="n">
-        <v>1.9509357213974</v>
+        <v>1.95093560218811</v>
       </c>
       <c r="H373" t="n">
         <v>3000</v>
@@ -11215,7 +11215,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G374" t="n">
-        <v>1.77517580986023</v>
+        <v>1.77517592906952</v>
       </c>
       <c r="H374" t="n">
         <v>52500</v>
@@ -11273,7 +11273,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G376" t="n">
-        <v>1.88063180446625</v>
+        <v>1.88063192367554</v>
       </c>
       <c r="H376" t="n">
         <v>9000</v>
@@ -11302,7 +11302,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G377" t="n">
-        <v>1.88063180446625</v>
+        <v>1.88063192367554</v>
       </c>
       <c r="H377" t="n">
         <v>3000</v>
@@ -11331,7 +11331,7 @@
         <v>2.25</v>
       </c>
       <c r="G378" t="n">
-        <v>1.97729969024658</v>
+        <v>1.97729980945587</v>
       </c>
       <c r="H378" t="n">
         <v>16500</v>
@@ -11360,7 +11360,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G379" t="n">
-        <v>1.93335998058319</v>
+        <v>1.93335962295532</v>
       </c>
       <c r="H379" t="n">
         <v>3000</v>
@@ -11389,7 +11389,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G380" t="n">
-        <v>1.62577974796295</v>
+        <v>1.62577986717224</v>
       </c>
       <c r="H380" t="n">
         <v>43500</v>
@@ -11447,7 +11447,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G382" t="n">
-        <v>1.80153965950012</v>
+        <v>1.80153977870941</v>
       </c>
       <c r="H382" t="n">
         <v>21000</v>
@@ -11476,7 +11476,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G383" t="n">
-        <v>1.86305558681488</v>
+        <v>1.86305582523346</v>
       </c>
       <c r="H383" t="n">
         <v>21000</v>
@@ -11505,7 +11505,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G384" t="n">
-        <v>1.86305558681488</v>
+        <v>1.86305582523346</v>
       </c>
       <c r="H384" t="n">
         <v>1500</v>
@@ -11534,7 +11534,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G385" t="n">
-        <v>1.88063180446625</v>
+        <v>1.88063192367554</v>
       </c>
       <c r="H385" t="n">
         <v>13500</v>
@@ -11563,7 +11563,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G386" t="n">
-        <v>1.99487566947937</v>
+        <v>1.99487578868866</v>
       </c>
       <c r="H386" t="n">
         <v>15000</v>
@@ -11621,7 +11621,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G388" t="n">
-        <v>1.99487566947937</v>
+        <v>1.99487578868866</v>
       </c>
       <c r="H388" t="n">
         <v>9000</v>
@@ -11650,7 +11650,7 @@
         <v>2.25</v>
       </c>
       <c r="G389" t="n">
-        <v>1.97729969024658</v>
+        <v>1.97729980945587</v>
       </c>
       <c r="H389" t="n">
         <v>6000</v>
@@ -11679,7 +11679,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G390" t="n">
-        <v>1.93335998058319</v>
+        <v>1.93335962295532</v>
       </c>
       <c r="H390" t="n">
         <v>1500</v>
@@ -11708,7 +11708,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G391" t="n">
-        <v>1.96851170063019</v>
+        <v>1.96851181983948</v>
       </c>
       <c r="H391" t="n">
         <v>9000</v>
@@ -11737,7 +11737,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G392" t="n">
-        <v>1.98608779907227</v>
+        <v>1.98608791828156</v>
       </c>
       <c r="H392" t="n">
         <v>6000</v>
@@ -11766,7 +11766,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G393" t="n">
-        <v>1.98608779907227</v>
+        <v>1.98608791828156</v>
       </c>
       <c r="H393" t="n">
         <v>0</v>
@@ -11795,7 +11795,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G394" t="n">
-        <v>1.92457187175751</v>
+        <v>1.9245719909668</v>
       </c>
       <c r="H394" t="n">
         <v>12000</v>
@@ -11824,7 +11824,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G395" t="n">
-        <v>1.99487566947937</v>
+        <v>1.99487578868866</v>
       </c>
       <c r="H395" t="n">
         <v>31500</v>
@@ -11911,7 +11911,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G398" t="n">
-        <v>2.05639171600342</v>
+        <v>2.056391954422</v>
       </c>
       <c r="H398" t="n">
         <v>10500</v>
@@ -11940,7 +11940,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G399" t="n">
-        <v>1.98608779907227</v>
+        <v>1.98608791828156</v>
       </c>
       <c r="H399" t="n">
         <v>6000</v>
@@ -11969,7 +11969,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G400" t="n">
-        <v>2.02123975753784</v>
+        <v>2.02123951911926</v>
       </c>
       <c r="H400" t="n">
         <v>10500</v>
@@ -12027,7 +12027,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G402" t="n">
-        <v>2.05639171600342</v>
+        <v>2.056391954422</v>
       </c>
       <c r="H402" t="n">
         <v>36000</v>
@@ -12056,7 +12056,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G403" t="n">
-        <v>1.93335998058319</v>
+        <v>1.93335962295532</v>
       </c>
       <c r="H403" t="n">
         <v>7500</v>
@@ -12085,7 +12085,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G404" t="n">
-        <v>1.96851170063019</v>
+        <v>1.96851181983948</v>
       </c>
       <c r="H404" t="n">
         <v>22500</v>
@@ -12114,7 +12114,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G405" t="n">
-        <v>1.98608779907227</v>
+        <v>1.98608791828156</v>
       </c>
       <c r="H405" t="n">
         <v>16500</v>
@@ -12143,7 +12143,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G406" t="n">
-        <v>1.98608779907227</v>
+        <v>1.98608791828156</v>
       </c>
       <c r="H406" t="n">
         <v>0</v>
@@ -12288,7 +12288,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G411" t="n">
-        <v>1.87184405326843</v>
+        <v>1.87184381484985</v>
       </c>
       <c r="H411" t="n">
         <v>4500</v>
@@ -12317,7 +12317,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G412" t="n">
-        <v>1.88063180446625</v>
+        <v>1.88063192367554</v>
       </c>
       <c r="H412" t="n">
         <v>9000</v>
@@ -12346,7 +12346,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G413" t="n">
-        <v>1.88063180446625</v>
+        <v>1.88063192367554</v>
       </c>
       <c r="H413" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G415" t="n">
-        <v>1.81911587715149</v>
+        <v>1.8191157579422</v>
       </c>
       <c r="H415" t="n">
         <v>4500</v>
@@ -12433,7 +12433,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G416" t="n">
-        <v>1.81911587715149</v>
+        <v>1.8191157579422</v>
       </c>
       <c r="H416" t="n">
         <v>0</v>
@@ -12462,7 +12462,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G417" t="n">
-        <v>1.86305558681488</v>
+        <v>1.86305582523346</v>
       </c>
       <c r="H417" t="n">
         <v>6000</v>
@@ -12491,7 +12491,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G418" t="n">
-        <v>1.81032764911652</v>
+        <v>1.81032776832581</v>
       </c>
       <c r="H418" t="n">
         <v>6000</v>
@@ -12607,7 +12607,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G422" t="n">
-        <v>1.80153965950012</v>
+        <v>1.80153977870941</v>
       </c>
       <c r="H422" t="n">
         <v>25500</v>
@@ -12636,7 +12636,7 @@
         <v>2</v>
       </c>
       <c r="G423" t="n">
-        <v>1.75759983062744</v>
+        <v>1.75759971141815</v>
       </c>
       <c r="H423" t="n">
         <v>25500</v>
@@ -12665,7 +12665,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G424" t="n">
-        <v>1.77517580986023</v>
+        <v>1.77517592906952</v>
       </c>
       <c r="H424" t="n">
         <v>7500</v>
@@ -12723,7 +12723,7 @@
         <v>2</v>
       </c>
       <c r="G426" t="n">
-        <v>1.75759983062744</v>
+        <v>1.75759971141815</v>
       </c>
       <c r="H426" t="n">
         <v>4500</v>
@@ -12752,7 +12752,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G427" t="n">
-        <v>1.76638782024384</v>
+        <v>1.76638793945312</v>
       </c>
       <c r="H427" t="n">
         <v>4500</v>
@@ -12781,7 +12781,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G428" t="n">
-        <v>1.76638782024384</v>
+        <v>1.76638793945312</v>
       </c>
       <c r="H428" t="n">
         <v>3000</v>
@@ -12810,7 +12810,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G429" t="n">
-        <v>1.76638782024384</v>
+        <v>1.76638793945312</v>
       </c>
       <c r="H429" t="n">
         <v>3000</v>
@@ -12839,7 +12839,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G430" t="n">
-        <v>1.76638782024384</v>
+        <v>1.76638793945312</v>
       </c>
       <c r="H430" t="n">
         <v>4500</v>
@@ -12897,7 +12897,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G432" t="n">
-        <v>1.77517580986023</v>
+        <v>1.77517592906952</v>
       </c>
       <c r="H432" t="n">
         <v>3000</v>
@@ -12926,7 +12926,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G433" t="n">
-        <v>1.86305558681488</v>
+        <v>1.86305582523346</v>
       </c>
       <c r="H433" t="n">
         <v>7500</v>
@@ -12955,7 +12955,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G434" t="n">
-        <v>1.86305558681488</v>
+        <v>1.86305582523346</v>
       </c>
       <c r="H434" t="n">
         <v>0</v>
@@ -12984,7 +12984,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G435" t="n">
-        <v>1.86305558681488</v>
+        <v>1.86305582523346</v>
       </c>
       <c r="H435" t="n">
         <v>3000</v>
@@ -13013,7 +13013,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G436" t="n">
-        <v>1.88063180446625</v>
+        <v>1.88063192367554</v>
       </c>
       <c r="H436" t="n">
         <v>3000</v>
@@ -13100,7 +13100,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G439" t="n">
-        <v>1.81911587715149</v>
+        <v>1.8191157579422</v>
       </c>
       <c r="H439" t="n">
         <v>6000</v>
@@ -13129,7 +13129,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G440" t="n">
-        <v>1.81911587715149</v>
+        <v>1.8191157579422</v>
       </c>
       <c r="H440" t="n">
         <v>0</v>
@@ -13158,7 +13158,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G441" t="n">
-        <v>1.88063180446625</v>
+        <v>1.88063192367554</v>
       </c>
       <c r="H441" t="n">
         <v>3000</v>
@@ -13187,7 +13187,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G442" t="n">
-        <v>1.88063180446625</v>
+        <v>1.88063192367554</v>
       </c>
       <c r="H442" t="n">
         <v>0</v>
@@ -13216,7 +13216,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G443" t="n">
-        <v>1.8279036283493</v>
+        <v>1.82790374755859</v>
       </c>
       <c r="H443" t="n">
         <v>4500</v>
@@ -13245,7 +13245,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G444" t="n">
-        <v>1.86305558681488</v>
+        <v>1.86305582523346</v>
       </c>
       <c r="H444" t="n">
         <v>1500</v>
@@ -13274,7 +13274,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G445" t="n">
-        <v>1.8279036283493</v>
+        <v>1.82790374755859</v>
       </c>
       <c r="H445" t="n">
         <v>1500</v>
@@ -13303,7 +13303,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G446" t="n">
-        <v>1.8279036283493</v>
+        <v>1.82790374755859</v>
       </c>
       <c r="H446" t="n">
         <v>0</v>
@@ -13332,7 +13332,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G447" t="n">
-        <v>1.76638782024384</v>
+        <v>1.76638793945312</v>
       </c>
       <c r="H447" t="n">
         <v>15000</v>
@@ -13419,7 +13419,7 @@
         <v>2</v>
       </c>
       <c r="G450" t="n">
-        <v>1.75759983062744</v>
+        <v>1.75759971141815</v>
       </c>
       <c r="H450" t="n">
         <v>10500</v>
@@ -13506,7 +13506,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G453" t="n">
-        <v>1.68729567527771</v>
+        <v>1.687295794487</v>
       </c>
       <c r="H453" t="n">
         <v>7500</v>
@@ -13535,7 +13535,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G454" t="n">
-        <v>1.63896191120148</v>
+        <v>1.63896179199219</v>
       </c>
       <c r="H454" t="n">
         <v>6000</v>
@@ -13796,7 +13796,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G463" t="n">
-        <v>1.66093182563782</v>
+        <v>1.66093194484711</v>
       </c>
       <c r="H463" t="n">
         <v>1500</v>
@@ -13825,7 +13825,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G464" t="n">
-        <v>1.66093182563782</v>
+        <v>1.66093194484711</v>
       </c>
       <c r="H464" t="n">
         <v>0</v>
@@ -13883,7 +13883,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G466" t="n">
-        <v>1.59941601753235</v>
+        <v>1.59941577911377</v>
       </c>
       <c r="H466" t="n">
         <v>6000</v>
@@ -13912,7 +13912,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G467" t="n">
-        <v>1.59502184391022</v>
+        <v>1.59502196311951</v>
       </c>
       <c r="H467" t="n">
         <v>3000</v>
@@ -13941,7 +13941,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G468" t="n">
-        <v>1.66971981525421</v>
+        <v>1.6697199344635</v>
       </c>
       <c r="H468" t="n">
         <v>4500</v>
@@ -13970,7 +13970,7 @@
         <v>1.875</v>
       </c>
       <c r="G469" t="n">
-        <v>1.64774990081787</v>
+        <v>1.64774978160858</v>
       </c>
       <c r="H469" t="n">
         <v>3000</v>
@@ -13999,7 +13999,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G470" t="n">
-        <v>1.66093182563782</v>
+        <v>1.66093194484711</v>
       </c>
       <c r="H470" t="n">
         <v>3000</v>
@@ -14028,7 +14028,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G471" t="n">
-        <v>1.59502184391022</v>
+        <v>1.59502196311951</v>
       </c>
       <c r="H471" t="n">
         <v>15000</v>
@@ -14057,7 +14057,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G472" t="n">
-        <v>1.64335584640503</v>
+        <v>1.64335572719574</v>
       </c>
       <c r="H472" t="n">
         <v>4500</v>
@@ -14086,7 +14086,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G473" t="n">
-        <v>1.64335584640503</v>
+        <v>1.64335572719574</v>
       </c>
       <c r="H473" t="n">
         <v>0</v>
@@ -14115,7 +14115,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G474" t="n">
-        <v>1.66971981525421</v>
+        <v>1.6697199344635</v>
       </c>
       <c r="H474" t="n">
         <v>3000</v>
@@ -14144,7 +14144,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G475" t="n">
-        <v>1.63456785678864</v>
+        <v>1.63456773757935</v>
       </c>
       <c r="H475" t="n">
         <v>3000</v>
@@ -14260,7 +14260,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G479" t="n">
-        <v>1.65653777122498</v>
+        <v>1.65653789043427</v>
       </c>
       <c r="H479" t="n">
         <v>4500</v>
@@ -14289,7 +14289,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G480" t="n">
-        <v>1.63017380237579</v>
+        <v>1.63017392158508</v>
       </c>
       <c r="H480" t="n">
         <v>3000</v>
@@ -14318,7 +14318,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G481" t="n">
-        <v>1.68729567527771</v>
+        <v>1.687295794487</v>
       </c>
       <c r="H481" t="n">
         <v>3000</v>
@@ -14376,7 +14376,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G483" t="n">
-        <v>1.64335584640503</v>
+        <v>1.64335572719574</v>
       </c>
       <c r="H483" t="n">
         <v>3000</v>
@@ -14405,7 +14405,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G484" t="n">
-        <v>1.74881184101105</v>
+        <v>1.74881172180176</v>
       </c>
       <c r="H484" t="n">
         <v>19500</v>
@@ -14434,7 +14434,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G485" t="n">
-        <v>1.81032764911652</v>
+        <v>1.81032776832581</v>
       </c>
       <c r="H485" t="n">
         <v>6000</v>
@@ -14463,7 +14463,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G486" t="n">
-        <v>1.87184405326843</v>
+        <v>1.87184381484985</v>
       </c>
       <c r="H486" t="n">
         <v>25500</v>
@@ -14492,7 +14492,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G487" t="n">
-        <v>1.93335998058319</v>
+        <v>1.93335962295532</v>
       </c>
       <c r="H487" t="n">
         <v>33000</v>
@@ -14521,7 +14521,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G488" t="n">
-        <v>1.92457187175751</v>
+        <v>1.9245719909668</v>
       </c>
       <c r="H488" t="n">
         <v>34500</v>
@@ -14637,7 +14637,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G492" t="n">
-        <v>1.99487566947937</v>
+        <v>1.99487578868866</v>
       </c>
       <c r="H492" t="n">
         <v>3000</v>
@@ -14666,7 +14666,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G493" t="n">
-        <v>2.02123975753784</v>
+        <v>2.02123951911926</v>
       </c>
       <c r="H493" t="n">
         <v>42000</v>
@@ -14695,7 +14695,7 @@
         <v>2.25</v>
       </c>
       <c r="G494" t="n">
-        <v>1.97729969024658</v>
+        <v>1.97729980945587</v>
       </c>
       <c r="H494" t="n">
         <v>4500</v>
@@ -14724,7 +14724,7 @@
         <v>2.25</v>
       </c>
       <c r="G495" t="n">
-        <v>1.97729969024658</v>
+        <v>1.97729980945587</v>
       </c>
       <c r="H495" t="n">
         <v>0</v>
@@ -14753,7 +14753,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G496" t="n">
-        <v>1.93335998058319</v>
+        <v>1.93335962295532</v>
       </c>
       <c r="H496" t="n">
         <v>6000</v>
@@ -14782,7 +14782,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G497" t="n">
-        <v>1.8279036283493</v>
+        <v>1.82790374755859</v>
       </c>
       <c r="H497" t="n">
         <v>21000</v>
@@ -14840,7 +14840,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G499" t="n">
-        <v>1.78396391868591</v>
+        <v>1.78396379947662</v>
       </c>
       <c r="H499" t="n">
         <v>12000</v>
@@ -14869,7 +14869,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G500" t="n">
-        <v>1.78396391868591</v>
+        <v>1.78396379947662</v>
       </c>
       <c r="H500" t="n">
         <v>3000</v>
@@ -14898,7 +14898,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G501" t="n">
-        <v>1.78396391868591</v>
+        <v>1.78396379947662</v>
       </c>
       <c r="H501" t="n">
         <v>0</v>
@@ -14927,7 +14927,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G502" t="n">
-        <v>1.74881184101105</v>
+        <v>1.74881172180176</v>
       </c>
       <c r="H502" t="n">
         <v>4500</v>
@@ -14956,7 +14956,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G503" t="n">
-        <v>1.74881184101105</v>
+        <v>1.74881172180176</v>
       </c>
       <c r="H503" t="n">
         <v>1500</v>
@@ -14985,7 +14985,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G504" t="n">
-        <v>1.74881184101105</v>
+        <v>1.74881172180176</v>
       </c>
       <c r="H504" t="n">
         <v>1500</v>
@@ -15014,7 +15014,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G505" t="n">
-        <v>1.77517580986023</v>
+        <v>1.77517592906952</v>
       </c>
       <c r="H505" t="n">
         <v>3000</v>
@@ -15043,7 +15043,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G506" t="n">
-        <v>1.77517580986023</v>
+        <v>1.77517592906952</v>
       </c>
       <c r="H506" t="n">
         <v>3000</v>
@@ -15072,7 +15072,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G507" t="n">
-        <v>1.78396391868591</v>
+        <v>1.78396379947662</v>
       </c>
       <c r="H507" t="n">
         <v>3000</v>
@@ -15101,7 +15101,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G508" t="n">
-        <v>1.78396391868591</v>
+        <v>1.78396379947662</v>
       </c>
       <c r="H508" t="n">
         <v>1500</v>
@@ -15130,7 +15130,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G509" t="n">
-        <v>1.78396391868591</v>
+        <v>1.78396379947662</v>
       </c>
       <c r="H509" t="n">
         <v>1500</v>
@@ -15159,7 +15159,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G510" t="n">
-        <v>1.77517580986023</v>
+        <v>1.77517592906952</v>
       </c>
       <c r="H510" t="n">
         <v>4500</v>
@@ -15217,7 +15217,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G512" t="n">
-        <v>1.78396391868591</v>
+        <v>1.78396379947662</v>
       </c>
       <c r="H512" t="n">
         <v>6000</v>
@@ -15246,7 +15246,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G513" t="n">
-        <v>1.81032764911652</v>
+        <v>1.81032776832581</v>
       </c>
       <c r="H513" t="n">
         <v>3000</v>
@@ -15275,7 +15275,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G514" t="n">
-        <v>1.78396391868591</v>
+        <v>1.78396379947662</v>
       </c>
       <c r="H514" t="n">
         <v>4500</v>
@@ -15304,7 +15304,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G515" t="n">
-        <v>1.78396391868591</v>
+        <v>1.78396379947662</v>
       </c>
       <c r="H515" t="n">
         <v>1500</v>
@@ -15333,7 +15333,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G516" t="n">
-        <v>1.71365988254547</v>
+        <v>1.71365976333618</v>
       </c>
       <c r="H516" t="n">
         <v>6000</v>
@@ -15362,7 +15362,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G517" t="n">
-        <v>1.71365988254547</v>
+        <v>1.71365976333618</v>
       </c>
       <c r="H517" t="n">
         <v>1500</v>
@@ -15391,7 +15391,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G518" t="n">
-        <v>1.71365988254547</v>
+        <v>1.71365976333618</v>
       </c>
       <c r="H518" t="n">
         <v>0</v>
@@ -15420,7 +15420,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G519" t="n">
-        <v>1.76638782024384</v>
+        <v>1.76638793945312</v>
       </c>
       <c r="H519" t="n">
         <v>3000</v>
@@ -15478,7 +15478,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G521" t="n">
-        <v>1.81032764911652</v>
+        <v>1.81032776832581</v>
       </c>
       <c r="H521" t="n">
         <v>4500</v>
@@ -15507,7 +15507,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G522" t="n">
-        <v>1.76638782024384</v>
+        <v>1.76638793945312</v>
       </c>
       <c r="H522" t="n">
         <v>9000</v>
@@ -15594,7 +15594,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G525" t="n">
-        <v>1.62577974796295</v>
+        <v>1.62577986717224</v>
       </c>
       <c r="H525" t="n">
         <v>6000</v>
@@ -15623,7 +15623,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G526" t="n">
-        <v>1.54229390621185</v>
+        <v>1.54229378700256</v>
       </c>
       <c r="H526" t="n">
         <v>19500</v>
@@ -15652,7 +15652,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G527" t="n">
-        <v>1.50274789333344</v>
+        <v>1.50274777412415</v>
       </c>
       <c r="H527" t="n">
         <v>25500</v>
@@ -15681,7 +15681,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G528" t="n">
-        <v>1.50274789333344</v>
+        <v>1.50274777412415</v>
       </c>
       <c r="H528" t="n">
         <v>9000</v>
@@ -15913,7 +15913,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G536" t="n">
-        <v>1.50274789333344</v>
+        <v>1.50274777412415</v>
       </c>
       <c r="H536" t="n">
         <v>6000</v>
@@ -15942,7 +15942,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G537" t="n">
-        <v>1.50274789333344</v>
+        <v>1.50274777412415</v>
       </c>
       <c r="H537" t="n">
         <v>0</v>
@@ -15971,7 +15971,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G538" t="n">
-        <v>1.55108177661896</v>
+        <v>1.55108189582825</v>
       </c>
       <c r="H538" t="n">
         <v>1500</v>
@@ -16000,7 +16000,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G539" t="n">
-        <v>1.55108177661896</v>
+        <v>1.55108189582825</v>
       </c>
       <c r="H539" t="n">
         <v>0</v>
@@ -16029,7 +16029,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G540" t="n">
-        <v>1.51153600215912</v>
+        <v>1.51153588294983</v>
       </c>
       <c r="H540" t="n">
         <v>7500</v>
@@ -16058,7 +16058,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G541" t="n">
-        <v>1.51153600215912</v>
+        <v>1.51153588294983</v>
       </c>
       <c r="H541" t="n">
         <v>0</v>
@@ -16087,7 +16087,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G542" t="n">
-        <v>1.51153600215912</v>
+        <v>1.51153588294983</v>
       </c>
       <c r="H542" t="n">
         <v>0</v>
@@ -16174,7 +16174,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G545" t="n">
-        <v>1.5642637014389</v>
+        <v>1.56426393985748</v>
       </c>
       <c r="H545" t="n">
         <v>4500</v>
@@ -16203,7 +16203,7 @@
         <v>1.875</v>
       </c>
       <c r="G546" t="n">
-        <v>1.64774990081787</v>
+        <v>1.64774978160858</v>
       </c>
       <c r="H546" t="n">
         <v>18000</v>
@@ -16232,7 +16232,7 @@
         <v>1.875</v>
       </c>
       <c r="G547" t="n">
-        <v>1.64774990081787</v>
+        <v>1.64774978160858</v>
       </c>
       <c r="H547" t="n">
         <v>0</v>
@@ -16435,7 +16435,7 @@
         <v>2</v>
       </c>
       <c r="G554" t="n">
-        <v>1.75759983062744</v>
+        <v>1.75759971141815</v>
       </c>
       <c r="H554" t="n">
         <v>1500</v>
@@ -16464,7 +16464,7 @@
         <v>2</v>
       </c>
       <c r="G555" t="n">
-        <v>1.75759983062744</v>
+        <v>1.75759971141815</v>
       </c>
       <c r="H555" t="n">
         <v>0</v>
@@ -16493,7 +16493,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G556" t="n">
-        <v>1.66971981525421</v>
+        <v>1.6697199344635</v>
       </c>
       <c r="H556" t="n">
         <v>6000</v>
@@ -16522,7 +16522,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G557" t="n">
-        <v>1.66971981525421</v>
+        <v>1.6697199344635</v>
       </c>
       <c r="H557" t="n">
         <v>3000</v>
@@ -16783,7 +16783,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G566" t="n">
-        <v>1.62577974796295</v>
+        <v>1.62577986717224</v>
       </c>
       <c r="H566" t="n">
         <v>4500</v>
@@ -16812,7 +16812,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G567" t="n">
-        <v>1.62577974796295</v>
+        <v>1.62577986717224</v>
       </c>
       <c r="H567" t="n">
         <v>0</v>
@@ -16841,7 +16841,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G568" t="n">
-        <v>1.62577974796295</v>
+        <v>1.62577986717224</v>
       </c>
       <c r="H568" t="n">
         <v>0</v>
@@ -16870,7 +16870,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G569" t="n">
-        <v>1.6038099527359</v>
+        <v>1.60380983352661</v>
       </c>
       <c r="H569" t="n">
         <v>4500</v>
@@ -16899,7 +16899,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G570" t="n">
-        <v>1.6038099527359</v>
+        <v>1.60380983352661</v>
       </c>
       <c r="H570" t="n">
         <v>0</v>
@@ -16928,7 +16928,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G571" t="n">
-        <v>1.66093182563782</v>
+        <v>1.66093194484711</v>
       </c>
       <c r="H571" t="n">
         <v>1500</v>
@@ -16986,7 +16986,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G573" t="n">
-        <v>1.66971981525421</v>
+        <v>1.6697199344635</v>
       </c>
       <c r="H573" t="n">
         <v>1500</v>
@@ -17015,7 +17015,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G574" t="n">
-        <v>1.66971981525421</v>
+        <v>1.6697199344635</v>
       </c>
       <c r="H574" t="n">
         <v>0</v>
@@ -17044,7 +17044,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G575" t="n">
-        <v>1.66971981525421</v>
+        <v>1.6697199344635</v>
       </c>
       <c r="H575" t="n">
         <v>0</v>
@@ -17073,7 +17073,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G576" t="n">
-        <v>1.66971981525421</v>
+        <v>1.6697199344635</v>
       </c>
       <c r="H576" t="n">
         <v>0</v>
@@ -17102,7 +17102,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G577" t="n">
-        <v>1.66971981525421</v>
+        <v>1.6697199344635</v>
       </c>
       <c r="H577" t="n">
         <v>0</v>
@@ -17218,7 +17218,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G581" t="n">
-        <v>1.68729567527771</v>
+        <v>1.687295794487</v>
       </c>
       <c r="H581" t="n">
         <v>1500</v>
@@ -17305,7 +17305,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G584" t="n">
-        <v>1.62577974796295</v>
+        <v>1.62577986717224</v>
       </c>
       <c r="H584" t="n">
         <v>1500</v>
@@ -17334,7 +17334,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G585" t="n">
-        <v>1.62577974796295</v>
+        <v>1.62577986717224</v>
       </c>
       <c r="H585" t="n">
         <v>0</v>
@@ -17363,7 +17363,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G586" t="n">
-        <v>1.62577974796295</v>
+        <v>1.62577986717224</v>
       </c>
       <c r="H586" t="n">
         <v>0</v>
@@ -17392,7 +17392,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G587" t="n">
-        <v>1.62577974796295</v>
+        <v>1.62577986717224</v>
       </c>
       <c r="H587" t="n">
         <v>1500</v>
@@ -17421,7 +17421,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G588" t="n">
-        <v>1.62577974796295</v>
+        <v>1.62577986717224</v>
       </c>
       <c r="H588" t="n">
         <v>0</v>
@@ -17450,7 +17450,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G589" t="n">
-        <v>1.62577974796295</v>
+        <v>1.62577986717224</v>
       </c>
       <c r="H589" t="n">
         <v>1500</v>
@@ -17479,7 +17479,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G590" t="n">
-        <v>1.65653777122498</v>
+        <v>1.65653789043427</v>
       </c>
       <c r="H590" t="n">
         <v>3000</v>
@@ -17508,7 +17508,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G591" t="n">
-        <v>1.58623373508453</v>
+        <v>1.58623385429382</v>
       </c>
       <c r="H591" t="n">
         <v>9000</v>
@@ -17566,7 +17566,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G593" t="n">
-        <v>1.55547571182251</v>
+        <v>1.55547595024109</v>
       </c>
       <c r="H593" t="n">
         <v>13500</v>
@@ -17595,7 +17595,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G594" t="n">
-        <v>1.55986976623535</v>
+        <v>1.55987000465393</v>
       </c>
       <c r="H594" t="n">
         <v>15000</v>
@@ -17624,7 +17624,7 @@
         <v>1.875</v>
       </c>
       <c r="G595" t="n">
-        <v>1.64774990081787</v>
+        <v>1.64774978160858</v>
       </c>
       <c r="H595" t="n">
         <v>7500</v>
@@ -17653,7 +17653,7 @@
         <v>1.875</v>
       </c>
       <c r="G596" t="n">
-        <v>1.64774990081787</v>
+        <v>1.64774978160858</v>
       </c>
       <c r="H596" t="n">
         <v>0</v>
@@ -17711,7 +17711,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G598" t="n">
-        <v>1.63896191120148</v>
+        <v>1.63896179199219</v>
       </c>
       <c r="H598" t="n">
         <v>1500</v>
@@ -17740,7 +17740,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G599" t="n">
-        <v>1.63896191120148</v>
+        <v>1.63896179199219</v>
       </c>
       <c r="H599" t="n">
         <v>0</v>
@@ -17769,7 +17769,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G600" t="n">
-        <v>1.59941601753235</v>
+        <v>1.59941577911377</v>
       </c>
       <c r="H600" t="n">
         <v>3000</v>
@@ -17798,7 +17798,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G601" t="n">
-        <v>1.59941601753235</v>
+        <v>1.59941577911377</v>
       </c>
       <c r="H601" t="n">
         <v>0</v>
@@ -17827,7 +17827,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G602" t="n">
-        <v>1.59941601753235</v>
+        <v>1.59941577911377</v>
       </c>
       <c r="H602" t="n">
         <v>0</v>
@@ -17885,7 +17885,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G604" t="n">
-        <v>1.6038099527359</v>
+        <v>1.60380983352661</v>
       </c>
       <c r="H604" t="n">
         <v>18000</v>
@@ -17914,7 +17914,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G605" t="n">
-        <v>1.6038099527359</v>
+        <v>1.60380983352661</v>
       </c>
       <c r="H605" t="n">
         <v>0</v>
@@ -17943,7 +17943,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G606" t="n">
-        <v>1.63896191120148</v>
+        <v>1.63896179199219</v>
       </c>
       <c r="H606" t="n">
         <v>3000</v>
@@ -18001,7 +18001,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G608" t="n">
-        <v>1.58183991909027</v>
+        <v>1.58183979988098</v>
       </c>
       <c r="H608" t="n">
         <v>12000</v>
@@ -18233,7 +18233,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G616" t="n">
-        <v>1.56865787506104</v>
+        <v>1.56865775585175</v>
       </c>
       <c r="H616" t="n">
         <v>7500</v>
@@ -18262,7 +18262,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G617" t="n">
-        <v>1.75320589542389</v>
+        <v>1.7532057762146</v>
       </c>
       <c r="H617" t="n">
         <v>114000</v>
@@ -18349,7 +18349,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G620" t="n">
-        <v>1.71805381774902</v>
+        <v>1.71805393695831</v>
       </c>
       <c r="H620" t="n">
         <v>1500</v>
@@ -18378,7 +18378,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G621" t="n">
-        <v>1.66971981525421</v>
+        <v>1.6697199344635</v>
       </c>
       <c r="H621" t="n">
         <v>7500</v>
@@ -18465,7 +18465,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G624" t="n">
-        <v>1.66971981525421</v>
+        <v>1.6697199344635</v>
       </c>
       <c r="H624" t="n">
         <v>4500</v>
@@ -18581,7 +18581,7 @@
         <v>2.25</v>
       </c>
       <c r="G628" t="n">
-        <v>1.97729969024658</v>
+        <v>1.97729980945587</v>
       </c>
       <c r="H628" t="n">
         <v>303000</v>
@@ -18610,7 +18610,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G629" t="n">
-        <v>1.88063180446625</v>
+        <v>1.88063192367554</v>
       </c>
       <c r="H629" t="n">
         <v>39000</v>
@@ -18668,7 +18668,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G631" t="n">
-        <v>1.81032764911652</v>
+        <v>1.81032776832581</v>
       </c>
       <c r="H631" t="n">
         <v>24000</v>
@@ -18697,7 +18697,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G632" t="n">
-        <v>1.86305558681488</v>
+        <v>1.86305582523346</v>
       </c>
       <c r="H632" t="n">
         <v>33000</v>
@@ -18726,7 +18726,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G633" t="n">
-        <v>1.81911587715149</v>
+        <v>1.8191157579422</v>
       </c>
       <c r="H633" t="n">
         <v>4500</v>
@@ -18755,7 +18755,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G634" t="n">
-        <v>1.81032764911652</v>
+        <v>1.81032776832581</v>
       </c>
       <c r="H634" t="n">
         <v>21000</v>
@@ -18813,7 +18813,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G636" t="n">
-        <v>1.71805381774902</v>
+        <v>1.71805393695831</v>
       </c>
       <c r="H636" t="n">
         <v>30000</v>
@@ -18842,7 +18842,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G637" t="n">
-        <v>1.71365988254547</v>
+        <v>1.71365976333618</v>
       </c>
       <c r="H637" t="n">
         <v>24000</v>
@@ -18900,7 +18900,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G639" t="n">
-        <v>1.64335584640503</v>
+        <v>1.64335572719574</v>
       </c>
       <c r="H639" t="n">
         <v>19500</v>
@@ -18958,7 +18958,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G641" t="n">
-        <v>1.62577974796295</v>
+        <v>1.62577986717224</v>
       </c>
       <c r="H641" t="n">
         <v>1500</v>
@@ -19045,7 +19045,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G644" t="n">
-        <v>1.66093182563782</v>
+        <v>1.66093194484711</v>
       </c>
       <c r="H644" t="n">
         <v>9000</v>
@@ -19074,7 +19074,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G645" t="n">
-        <v>1.66093182563782</v>
+        <v>1.66093194484711</v>
       </c>
       <c r="H645" t="n">
         <v>0</v>
@@ -19103,7 +19103,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G646" t="n">
-        <v>1.62138569355011</v>
+        <v>1.6213858127594</v>
       </c>
       <c r="H646" t="n">
         <v>6000</v>
@@ -19190,7 +19190,7 @@
         <v>2</v>
       </c>
       <c r="G649" t="n">
-        <v>1.75759983062744</v>
+        <v>1.75759971141815</v>
       </c>
       <c r="H649" t="n">
         <v>6000</v>
@@ -19219,7 +19219,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G650" t="n">
-        <v>1.74881184101105</v>
+        <v>1.74881172180176</v>
       </c>
       <c r="H650" t="n">
         <v>3000</v>
@@ -19248,7 +19248,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G651" t="n">
-        <v>1.71365988254547</v>
+        <v>1.71365976333618</v>
       </c>
       <c r="H651" t="n">
         <v>1500</v>
@@ -19393,7 +19393,7 @@
         <v>2</v>
       </c>
       <c r="G656" t="n">
-        <v>1.75759983062744</v>
+        <v>1.75759971141815</v>
       </c>
       <c r="H656" t="n">
         <v>1500</v>
@@ -19422,7 +19422,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G657" t="n">
-        <v>1.70487189292908</v>
+        <v>1.70487177371979</v>
       </c>
       <c r="H657" t="n">
         <v>10500</v>
@@ -19480,7 +19480,7 @@
         <v>2</v>
       </c>
       <c r="G659" t="n">
-        <v>1.75759983062744</v>
+        <v>1.75759971141815</v>
       </c>
       <c r="H659" t="n">
         <v>102000</v>
@@ -19567,7 +19567,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G662" t="n">
-        <v>1.70596218109131</v>
+        <v>1.7059623003006</v>
       </c>
       <c r="H662" t="n">
         <v>54000</v>
@@ -19596,7 +19596,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G663" t="n">
-        <v>1.70596218109131</v>
+        <v>1.7059623003006</v>
       </c>
       <c r="H663" t="n">
         <v>6000</v>
@@ -19683,7 +19683,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G666" t="n">
-        <v>1.73304092884064</v>
+        <v>1.73304104804993</v>
       </c>
       <c r="H666" t="n">
         <v>9000</v>
@@ -19712,7 +19712,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G667" t="n">
-        <v>1.70596218109131</v>
+        <v>1.7059623003006</v>
       </c>
       <c r="H667" t="n">
         <v>7500</v>
@@ -19770,7 +19770,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G669" t="n">
-        <v>1.66985726356506</v>
+        <v>1.66985738277435</v>
       </c>
       <c r="H669" t="n">
         <v>3000</v>
@@ -19828,7 +19828,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G671" t="n">
-        <v>1.63375222682953</v>
+        <v>1.63375210762024</v>
       </c>
       <c r="H671" t="n">
         <v>1500</v>
@@ -19857,7 +19857,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G672" t="n">
-        <v>1.63375222682953</v>
+        <v>1.63375210762024</v>
       </c>
       <c r="H672" t="n">
         <v>0</v>
@@ -20060,7 +20060,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G679" t="n">
-        <v>1.63375222682953</v>
+        <v>1.63375210762024</v>
       </c>
       <c r="H679" t="n">
         <v>1500</v>
@@ -20089,7 +20089,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G680" t="n">
-        <v>1.63375222682953</v>
+        <v>1.63375210762024</v>
       </c>
       <c r="H680" t="n">
         <v>0</v>
@@ -20118,7 +20118,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G681" t="n">
-        <v>1.62472605705261</v>
+        <v>1.62472593784332</v>
       </c>
       <c r="H681" t="n">
         <v>10500</v>
@@ -20147,7 +20147,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G682" t="n">
-        <v>1.62472605705261</v>
+        <v>1.62472593784332</v>
       </c>
       <c r="H682" t="n">
         <v>0</v>
@@ -20176,7 +20176,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G683" t="n">
-        <v>1.62472605705261</v>
+        <v>1.62472593784332</v>
       </c>
       <c r="H683" t="n">
         <v>0</v>
@@ -20205,7 +20205,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G684" t="n">
-        <v>1.5976470708847</v>
+        <v>1.59764719009399</v>
       </c>
       <c r="H684" t="n">
         <v>1500</v>
@@ -20437,7 +20437,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G692" t="n">
-        <v>1.61569976806641</v>
+        <v>1.61569964885712</v>
       </c>
       <c r="H692" t="n">
         <v>4500</v>
@@ -20466,7 +20466,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G693" t="n">
-        <v>1.61569976806641</v>
+        <v>1.61569964885712</v>
       </c>
       <c r="H693" t="n">
         <v>0</v>
@@ -20495,7 +20495,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G694" t="n">
-        <v>1.61569976806641</v>
+        <v>1.61569964885712</v>
       </c>
       <c r="H694" t="n">
         <v>0</v>
@@ -20524,7 +20524,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G695" t="n">
-        <v>1.56154215335846</v>
+        <v>1.56154227256775</v>
       </c>
       <c r="H695" t="n">
         <v>9000</v>
@@ -20611,7 +20611,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G698" t="n">
-        <v>1.56154215335846</v>
+        <v>1.56154227256775</v>
       </c>
       <c r="H698" t="n">
         <v>3000</v>
@@ -20698,7 +20698,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G701" t="n">
-        <v>1.5976470708847</v>
+        <v>1.59764719009399</v>
       </c>
       <c r="H701" t="n">
         <v>1500</v>
@@ -20727,7 +20727,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G702" t="n">
-        <v>1.5976470708847</v>
+        <v>1.59764719009399</v>
       </c>
       <c r="H702" t="n">
         <v>3000</v>
@@ -20756,7 +20756,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G703" t="n">
-        <v>1.5976470708847</v>
+        <v>1.59764719009399</v>
       </c>
       <c r="H703" t="n">
         <v>4500</v>
@@ -20785,7 +20785,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G704" t="n">
-        <v>1.5976470708847</v>
+        <v>1.59764719009399</v>
       </c>
       <c r="H704" t="n">
         <v>0</v>
@@ -20843,7 +20843,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G706" t="n">
-        <v>1.5976470708847</v>
+        <v>1.59764719009399</v>
       </c>
       <c r="H706" t="n">
         <v>7500</v>
@@ -20988,7 +20988,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G711" t="n">
-        <v>1.56154215335846</v>
+        <v>1.56154227256775</v>
       </c>
       <c r="H711" t="n">
         <v>4500</v>
@@ -21017,7 +21017,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G712" t="n">
-        <v>1.56154215335846</v>
+        <v>1.56154227256775</v>
       </c>
       <c r="H712" t="n">
         <v>0</v>
@@ -21046,7 +21046,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G713" t="n">
-        <v>1.56154215335846</v>
+        <v>1.56154227256775</v>
       </c>
       <c r="H713" t="n">
         <v>0</v>
@@ -21249,7 +21249,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G720" t="n">
-        <v>1.56154215335846</v>
+        <v>1.56154227256775</v>
       </c>
       <c r="H720" t="n">
         <v>1500</v>
@@ -21278,7 +21278,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G721" t="n">
-        <v>1.56154215335846</v>
+        <v>1.56154227256775</v>
       </c>
       <c r="H721" t="n">
         <v>0</v>
@@ -21307,7 +21307,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G722" t="n">
-        <v>1.56154215335846</v>
+        <v>1.56154227256775</v>
       </c>
       <c r="H722" t="n">
         <v>1500</v>
@@ -21336,7 +21336,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G723" t="n">
-        <v>1.56154215335846</v>
+        <v>1.56154227256775</v>
       </c>
       <c r="H723" t="n">
         <v>0</v>
@@ -21365,7 +21365,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G724" t="n">
-        <v>1.56154215335846</v>
+        <v>1.56154227256775</v>
       </c>
       <c r="H724" t="n">
         <v>0</v>
@@ -21626,7 +21626,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G733" t="n">
-        <v>1.55251598358154</v>
+        <v>1.55251586437225</v>
       </c>
       <c r="H733" t="n">
         <v>1500</v>
@@ -21655,7 +21655,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G734" t="n">
-        <v>1.55251598358154</v>
+        <v>1.55251586437225</v>
       </c>
       <c r="H734" t="n">
         <v>6000</v>
@@ -21684,7 +21684,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G735" t="n">
-        <v>1.55251598358154</v>
+        <v>1.55251586437225</v>
       </c>
       <c r="H735" t="n">
         <v>0</v>
@@ -21713,7 +21713,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G736" t="n">
-        <v>1.55251598358154</v>
+        <v>1.55251586437225</v>
       </c>
       <c r="H736" t="n">
         <v>0</v>
@@ -22264,7 +22264,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G755" t="n">
-        <v>1.44420087337494</v>
+        <v>1.44420075416565</v>
       </c>
       <c r="H755" t="n">
         <v>1500</v>
@@ -22322,7 +22322,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G757" t="n">
-        <v>1.56154215335846</v>
+        <v>1.56154227256775</v>
       </c>
       <c r="H757" t="n">
         <v>6000</v>
@@ -22351,7 +22351,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G758" t="n">
-        <v>1.56154215335846</v>
+        <v>1.56154227256775</v>
       </c>
       <c r="H758" t="n">
         <v>6000</v>
@@ -22583,7 +22583,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G766" t="n">
-        <v>1.48030579090118</v>
+        <v>1.48030591011047</v>
       </c>
       <c r="H766" t="n">
         <v>3000</v>
@@ -22960,7 +22960,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G779" t="n">
-        <v>1.48030579090118</v>
+        <v>1.48030591011047</v>
       </c>
       <c r="H779" t="n">
         <v>6000</v>
@@ -22989,7 +22989,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G780" t="n">
-        <v>1.45322704315186</v>
+        <v>1.45322716236115</v>
       </c>
       <c r="H780" t="n">
         <v>10500</v>
@@ -23221,7 +23221,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G788" t="n">
-        <v>1.48030579090118</v>
+        <v>1.48030591011047</v>
       </c>
       <c r="H788" t="n">
         <v>1500</v>
@@ -23250,7 +23250,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G789" t="n">
-        <v>1.48030579090118</v>
+        <v>1.48030591011047</v>
       </c>
       <c r="H789" t="n">
         <v>0</v>
@@ -23395,7 +23395,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G794" t="n">
-        <v>1.98577642440796</v>
+        <v>1.98577618598938</v>
       </c>
       <c r="H794" t="n">
         <v>370500</v>
@@ -23424,7 +23424,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G795" t="n">
-        <v>1.87746095657349</v>
+        <v>1.87746107578278</v>
       </c>
       <c r="H795" t="n">
         <v>319500</v>
@@ -23453,7 +23453,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G796" t="n">
-        <v>1.66985726356506</v>
+        <v>1.66985738277435</v>
       </c>
       <c r="H796" t="n">
         <v>94500</v>
@@ -23540,7 +23540,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G799" t="n">
-        <v>1.77817237377167</v>
+        <v>1.77817225456238</v>
       </c>
       <c r="H799" t="n">
         <v>24000</v>
@@ -23627,7 +23627,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G802" t="n">
-        <v>1.84135603904724</v>
+        <v>1.84135615825653</v>
       </c>
       <c r="H802" t="n">
         <v>37500</v>
@@ -23656,7 +23656,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G803" t="n">
-        <v>1.93161869049072</v>
+        <v>1.93161880970001</v>
       </c>
       <c r="H803" t="n">
         <v>73500</v>
@@ -23685,7 +23685,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G804" t="n">
-        <v>1.87746095657349</v>
+        <v>1.87746107578278</v>
       </c>
       <c r="H804" t="n">
         <v>46500</v>
@@ -23714,7 +23714,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G805" t="n">
-        <v>1.85940849781036</v>
+        <v>1.85940861701965</v>
       </c>
       <c r="H805" t="n">
         <v>4500</v>
@@ -23743,7 +23743,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G806" t="n">
-        <v>1.89551341533661</v>
+        <v>1.8955135345459</v>
       </c>
       <c r="H806" t="n">
         <v>9000</v>
@@ -23772,7 +23772,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G807" t="n">
-        <v>1.85940849781036</v>
+        <v>1.85940861701965</v>
       </c>
       <c r="H807" t="n">
         <v>7500</v>
@@ -23801,7 +23801,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G808" t="n">
-        <v>1.87746095657349</v>
+        <v>1.87746107578278</v>
       </c>
       <c r="H808" t="n">
         <v>10500</v>
@@ -23830,7 +23830,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G809" t="n">
-        <v>1.85940849781036</v>
+        <v>1.85940861701965</v>
       </c>
       <c r="H809" t="n">
         <v>1500</v>
@@ -23859,7 +23859,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G810" t="n">
-        <v>1.85940849781036</v>
+        <v>1.85940861701965</v>
       </c>
       <c r="H810" t="n">
         <v>1500</v>
@@ -23888,7 +23888,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G811" t="n">
-        <v>1.84135603904724</v>
+        <v>1.84135615825653</v>
       </c>
       <c r="H811" t="n">
         <v>6000</v>
@@ -23917,7 +23917,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G812" t="n">
-        <v>1.87746095657349</v>
+        <v>1.87746107578278</v>
       </c>
       <c r="H812" t="n">
         <v>6000</v>
@@ -23946,7 +23946,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G813" t="n">
-        <v>1.91356599330902</v>
+        <v>1.91356611251831</v>
       </c>
       <c r="H813" t="n">
         <v>3000</v>
@@ -23975,7 +23975,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G814" t="n">
-        <v>1.87746095657349</v>
+        <v>1.87746107578278</v>
       </c>
       <c r="H814" t="n">
         <v>7500</v>
@@ -24004,7 +24004,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G815" t="n">
-        <v>1.76011991500854</v>
+        <v>1.76011979579926</v>
       </c>
       <c r="H815" t="n">
         <v>79500</v>
@@ -24091,7 +24091,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G818" t="n">
-        <v>1.70596218109131</v>
+        <v>1.7059623003006</v>
       </c>
       <c r="H818" t="n">
         <v>55500</v>
@@ -24120,7 +24120,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G819" t="n">
-        <v>1.76914620399475</v>
+        <v>1.76914608478546</v>
       </c>
       <c r="H819" t="n">
         <v>12000</v>
@@ -24149,7 +24149,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G820" t="n">
-        <v>1.76914620399475</v>
+        <v>1.76914608478546</v>
       </c>
       <c r="H820" t="n">
         <v>0</v>
@@ -24178,7 +24178,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G821" t="n">
-        <v>1.73304092884064</v>
+        <v>1.73304104804993</v>
       </c>
       <c r="H821" t="n">
         <v>7500</v>
@@ -24207,7 +24207,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G822" t="n">
-        <v>1.77817237377167</v>
+        <v>1.77817225456238</v>
       </c>
       <c r="H822" t="n">
         <v>10500</v>
@@ -24236,7 +24236,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G823" t="n">
-        <v>1.84135603904724</v>
+        <v>1.84135615825653</v>
       </c>
       <c r="H823" t="n">
         <v>15000</v>
@@ -24294,7 +24294,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G825" t="n">
-        <v>1.76011991500854</v>
+        <v>1.76011979579926</v>
       </c>
       <c r="H825" t="n">
         <v>15000</v>
@@ -24352,7 +24352,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G827" t="n">
-        <v>1.73304092884064</v>
+        <v>1.73304104804993</v>
       </c>
       <c r="H827" t="n">
         <v>10500</v>
@@ -24497,7 +24497,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G832" t="n">
-        <v>1.77817237377167</v>
+        <v>1.77817225456238</v>
       </c>
       <c r="H832" t="n">
         <v>7500</v>
@@ -24526,7 +24526,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G833" t="n">
-        <v>1.74206733703613</v>
+        <v>1.74206721782684</v>
       </c>
       <c r="H833" t="n">
         <v>6000</v>
@@ -24555,7 +24555,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G834" t="n">
-        <v>1.73304092884064</v>
+        <v>1.73304104804993</v>
       </c>
       <c r="H834" t="n">
         <v>1500</v>
@@ -24584,7 +24584,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G835" t="n">
-        <v>1.76914620399475</v>
+        <v>1.76914608478546</v>
       </c>
       <c r="H835" t="n">
         <v>7500</v>
@@ -24613,7 +24613,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G836" t="n">
-        <v>1.76011991500854</v>
+        <v>1.76011979579926</v>
       </c>
       <c r="H836" t="n">
         <v>1500</v>
@@ -24642,7 +24642,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G837" t="n">
-        <v>1.77817237377167</v>
+        <v>1.77817225456238</v>
       </c>
       <c r="H837" t="n">
         <v>13500</v>
@@ -24671,7 +24671,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G838" t="n">
-        <v>1.74206733703613</v>
+        <v>1.74206721782684</v>
       </c>
       <c r="H838" t="n">
         <v>10500</v>
@@ -24700,7 +24700,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G839" t="n">
-        <v>1.74206733703613</v>
+        <v>1.74206721782684</v>
       </c>
       <c r="H839" t="n">
         <v>0</v>
@@ -24903,7 +24903,7 @@
         <v>2</v>
       </c>
       <c r="G846" t="n">
-        <v>1.805251121521</v>
+        <v>1.80525100231171</v>
       </c>
       <c r="H846" t="n">
         <v>24000</v>
@@ -24932,7 +24932,7 @@
         <v>2</v>
       </c>
       <c r="G847" t="n">
-        <v>1.805251121521</v>
+        <v>1.80525100231171</v>
       </c>
       <c r="H847" t="n">
         <v>0</v>
@@ -24961,7 +24961,7 @@
         <v>2</v>
       </c>
       <c r="G848" t="n">
-        <v>1.805251121521</v>
+        <v>1.80525100231171</v>
       </c>
       <c r="H848" t="n">
         <v>0</v>
@@ -25019,7 +25019,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G850" t="n">
-        <v>1.77817237377167</v>
+        <v>1.77817225456238</v>
       </c>
       <c r="H850" t="n">
         <v>4500</v>
@@ -25048,7 +25048,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G851" t="n">
-        <v>1.73304092884064</v>
+        <v>1.73304104804993</v>
       </c>
       <c r="H851" t="n">
         <v>16500</v>
@@ -25077,7 +25077,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G852" t="n">
-        <v>1.77817237377167</v>
+        <v>1.77817225456238</v>
       </c>
       <c r="H852" t="n">
         <v>10500</v>
@@ -25106,7 +25106,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G853" t="n">
-        <v>1.77817237377167</v>
+        <v>1.77817225456238</v>
       </c>
       <c r="H853" t="n">
         <v>3000</v>
@@ -25135,7 +25135,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G854" t="n">
-        <v>1.76914620399475</v>
+        <v>1.76914608478546</v>
       </c>
       <c r="H854" t="n">
         <v>1500</v>
@@ -25164,7 +25164,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G855" t="n">
-        <v>1.76011991500854</v>
+        <v>1.76011979579926</v>
       </c>
       <c r="H855" t="n">
         <v>10500</v>
@@ -25193,7 +25193,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G856" t="n">
-        <v>1.76011991500854</v>
+        <v>1.76011979579926</v>
       </c>
       <c r="H856" t="n">
         <v>1500</v>
@@ -25280,7 +25280,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G859" t="n">
-        <v>1.76011991500854</v>
+        <v>1.76011979579926</v>
       </c>
       <c r="H859" t="n">
         <v>1500</v>
@@ -25338,7 +25338,7 @@
         <v>2</v>
       </c>
       <c r="G861" t="n">
-        <v>1.805251121521</v>
+        <v>1.80525100231171</v>
       </c>
       <c r="H861" t="n">
         <v>4500</v>
@@ -25425,7 +25425,7 @@
         <v>2</v>
       </c>
       <c r="G864" t="n">
-        <v>1.805251121521</v>
+        <v>1.80525100231171</v>
       </c>
       <c r="H864" t="n">
         <v>9000</v>
@@ -25454,7 +25454,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G865" t="n">
-        <v>1.84135603904724</v>
+        <v>1.84135615825653</v>
       </c>
       <c r="H865" t="n">
         <v>48000</v>
@@ -25483,7 +25483,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G866" t="n">
-        <v>1.87746095657349</v>
+        <v>1.87746107578278</v>
       </c>
       <c r="H866" t="n">
         <v>7500</v>
@@ -25512,7 +25512,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G867" t="n">
-        <v>1.91356599330902</v>
+        <v>1.91356611251831</v>
       </c>
       <c r="H867" t="n">
         <v>21000</v>
@@ -25541,7 +25541,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G868" t="n">
-        <v>1.98577642440796</v>
+        <v>1.98577618598938</v>
       </c>
       <c r="H868" t="n">
         <v>57000</v>
@@ -25570,7 +25570,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G869" t="n">
-        <v>1.98577642440796</v>
+        <v>1.98577618598938</v>
       </c>
       <c r="H869" t="n">
         <v>42000</v>
@@ -25599,7 +25599,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G870" t="n">
-        <v>2.05798602104187</v>
+        <v>2.05798625946045</v>
       </c>
       <c r="H870" t="n">
         <v>60000</v>
@@ -25628,7 +25628,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G871" t="n">
-        <v>2.07603883743286</v>
+        <v>2.07603859901428</v>
       </c>
       <c r="H871" t="n">
         <v>30000</v>
@@ -25657,7 +25657,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G872" t="n">
-        <v>2.05798602104187</v>
+        <v>2.05798625946045</v>
       </c>
       <c r="H872" t="n">
         <v>43500</v>
@@ -25686,7 +25686,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G873" t="n">
-        <v>2.05798602104187</v>
+        <v>2.05798625946045</v>
       </c>
       <c r="H873" t="n">
         <v>30000</v>
@@ -25715,7 +25715,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G874" t="n">
-        <v>1.98577642440796</v>
+        <v>1.98577618598938</v>
       </c>
       <c r="H874" t="n">
         <v>33000</v>
@@ -25744,7 +25744,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G875" t="n">
-        <v>2.05798602104187</v>
+        <v>2.05798625946045</v>
       </c>
       <c r="H875" t="n">
         <v>10500</v>
@@ -25802,7 +25802,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G877" t="n">
-        <v>1.94967126846313</v>
+        <v>1.94967114925385</v>
       </c>
       <c r="H877" t="n">
         <v>10500</v>
@@ -25831,7 +25831,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G878" t="n">
-        <v>1.93161869049072</v>
+        <v>1.93161880970001</v>
       </c>
       <c r="H878" t="n">
         <v>12000</v>
@@ -25860,7 +25860,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G879" t="n">
-        <v>1.94967126846313</v>
+        <v>1.94967114925385</v>
       </c>
       <c r="H879" t="n">
         <v>22500</v>
@@ -25889,7 +25889,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G880" t="n">
-        <v>1.94967126846313</v>
+        <v>1.94967114925385</v>
       </c>
       <c r="H880" t="n">
         <v>1500</v>
@@ -25918,7 +25918,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G881" t="n">
-        <v>1.94967126846313</v>
+        <v>1.94967114925385</v>
       </c>
       <c r="H881" t="n">
         <v>9000</v>
@@ -25947,7 +25947,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G882" t="n">
-        <v>1.94967126846313</v>
+        <v>1.94967114925385</v>
       </c>
       <c r="H882" t="n">
         <v>7500</v>
@@ -25976,7 +25976,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G883" t="n">
-        <v>1.98577642440796</v>
+        <v>1.98577618598938</v>
       </c>
       <c r="H883" t="n">
         <v>13500</v>
@@ -26005,7 +26005,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G884" t="n">
-        <v>2.07603883743286</v>
+        <v>2.07603859901428</v>
       </c>
       <c r="H884" t="n">
         <v>45000</v>
@@ -26034,7 +26034,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G885" t="n">
-        <v>2.20240640640259</v>
+        <v>2.20240616798401</v>
       </c>
       <c r="H885" t="n">
         <v>234000</v>
@@ -26150,7 +26150,7 @@
         <v>2.5</v>
       </c>
       <c r="G889" t="n">
-        <v>2.25656390190125</v>
+        <v>2.25656414031982</v>
       </c>
       <c r="H889" t="n">
         <v>96000</v>
@@ -26179,7 +26179,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G890" t="n">
-        <v>2.20240640640259</v>
+        <v>2.20240616798401</v>
       </c>
       <c r="H890" t="n">
         <v>79500</v>
@@ -26237,7 +26237,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G892" t="n">
-        <v>2.07603883743286</v>
+        <v>2.07603859901428</v>
       </c>
       <c r="H892" t="n">
         <v>67500</v>
@@ -26266,7 +26266,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G893" t="n">
-        <v>2.07603883743286</v>
+        <v>2.07603859901428</v>
       </c>
       <c r="H893" t="n">
         <v>15000</v>
@@ -26295,7 +26295,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G894" t="n">
-        <v>2.0218813419342</v>
+        <v>2.02188110351562</v>
       </c>
       <c r="H894" t="n">
         <v>42000</v>
@@ -26324,7 +26324,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G895" t="n">
-        <v>1.85940849781036</v>
+        <v>1.85940861701965</v>
       </c>
       <c r="H895" t="n">
         <v>126000</v>
@@ -26353,7 +26353,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G896" t="n">
-        <v>1.94967126846313</v>
+        <v>1.94967114925385</v>
       </c>
       <c r="H896" t="n">
         <v>33000</v>
@@ -26382,7 +26382,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G897" t="n">
-        <v>1.91356599330902</v>
+        <v>1.91356611251831</v>
       </c>
       <c r="H897" t="n">
         <v>54000</v>
@@ -26411,7 +26411,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G898" t="n">
-        <v>1.87746095657349</v>
+        <v>1.87746107578278</v>
       </c>
       <c r="H898" t="n">
         <v>15000</v>
@@ -26440,7 +26440,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G899" t="n">
-        <v>1.85940849781036</v>
+        <v>1.85940861701965</v>
       </c>
       <c r="H899" t="n">
         <v>16500</v>
@@ -26469,7 +26469,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G900" t="n">
-        <v>1.87746095657349</v>
+        <v>1.87746107578278</v>
       </c>
       <c r="H900" t="n">
         <v>12000</v>
@@ -26498,7 +26498,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G901" t="n">
-        <v>1.85940849781036</v>
+        <v>1.85940861701965</v>
       </c>
       <c r="H901" t="n">
         <v>4500</v>
@@ -26527,7 +26527,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G902" t="n">
-        <v>1.93161869049072</v>
+        <v>1.93161880970001</v>
       </c>
       <c r="H902" t="n">
         <v>9000</v>
@@ -26556,7 +26556,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G903" t="n">
-        <v>1.91356599330902</v>
+        <v>1.91356611251831</v>
       </c>
       <c r="H903" t="n">
         <v>4500</v>
@@ -26585,7 +26585,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G904" t="n">
-        <v>1.93161869049072</v>
+        <v>1.93161880970001</v>
       </c>
       <c r="H904" t="n">
         <v>9000</v>
@@ -26614,7 +26614,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G905" t="n">
-        <v>1.94967126846313</v>
+        <v>1.94967114925385</v>
       </c>
       <c r="H905" t="n">
         <v>15000</v>
@@ -26643,7 +26643,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G906" t="n">
-        <v>1.91356599330902</v>
+        <v>1.91356611251831</v>
       </c>
       <c r="H906" t="n">
         <v>7500</v>
@@ -26672,7 +26672,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G907" t="n">
-        <v>1.93161869049072</v>
+        <v>1.93161880970001</v>
       </c>
       <c r="H907" t="n">
         <v>1500</v>
@@ -26701,7 +26701,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G908" t="n">
-        <v>1.93161869049072</v>
+        <v>1.93161880970001</v>
       </c>
       <c r="H908" t="n">
         <v>0</v>
@@ -26730,7 +26730,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G909" t="n">
-        <v>1.85940849781036</v>
+        <v>1.85940861701965</v>
       </c>
       <c r="H909" t="n">
         <v>111000</v>
@@ -26759,7 +26759,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G910" t="n">
-        <v>1.84135603904724</v>
+        <v>1.84135615825653</v>
       </c>
       <c r="H910" t="n">
         <v>21000</v>
@@ -26788,7 +26788,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G911" t="n">
-        <v>1.87746095657349</v>
+        <v>1.87746107578278</v>
       </c>
       <c r="H911" t="n">
         <v>9000</v>
@@ -26817,7 +26817,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G912" t="n">
-        <v>1.85940849781036</v>
+        <v>1.85940861701965</v>
       </c>
       <c r="H912" t="n">
         <v>15000</v>
@@ -26846,7 +26846,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G913" t="n">
-        <v>1.85940849781036</v>
+        <v>1.85940861701965</v>
       </c>
       <c r="H913" t="n">
         <v>6000</v>
@@ -26875,7 +26875,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G914" t="n">
-        <v>1.89551341533661</v>
+        <v>1.8955135345459</v>
       </c>
       <c r="H914" t="n">
         <v>7500</v>
@@ -26904,7 +26904,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G915" t="n">
-        <v>1.87746095657349</v>
+        <v>1.87746107578278</v>
       </c>
       <c r="H915" t="n">
         <v>10500</v>
@@ -26933,7 +26933,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G916" t="n">
-        <v>1.87746095657349</v>
+        <v>1.87746107578278</v>
       </c>
       <c r="H916" t="n">
         <v>1500</v>
@@ -26962,7 +26962,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G917" t="n">
-        <v>1.85940849781036</v>
+        <v>1.85940861701965</v>
       </c>
       <c r="H917" t="n">
         <v>13500</v>
@@ -27049,7 +27049,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G920" t="n">
-        <v>1.89470195770264</v>
+        <v>1.89470207691193</v>
       </c>
       <c r="H920" t="n">
         <v>4500</v>
@@ -27078,7 +27078,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G921" t="n">
-        <v>1.89470195770264</v>
+        <v>1.89470207691193</v>
       </c>
       <c r="H921" t="n">
         <v>0</v>
@@ -27107,7 +27107,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G922" t="n">
-        <v>1.89470195770264</v>
+        <v>1.89470207691193</v>
       </c>
       <c r="H922" t="n">
         <v>15000</v>
@@ -27136,7 +27136,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G923" t="n">
-        <v>1.82968783378601</v>
+        <v>1.82968771457672</v>
       </c>
       <c r="H923" t="n">
         <v>28500</v>
@@ -27165,7 +27165,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G924" t="n">
-        <v>1.773961186409</v>
+        <v>1.77396130561829</v>
       </c>
       <c r="H924" t="n">
         <v>147000</v>
@@ -27223,7 +27223,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G926" t="n">
-        <v>1.81111240386963</v>
+        <v>1.81111228466034</v>
       </c>
       <c r="H926" t="n">
         <v>6000</v>
@@ -27252,7 +27252,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G927" t="n">
-        <v>1.81111240386963</v>
+        <v>1.81111228466034</v>
       </c>
       <c r="H927" t="n">
         <v>4500</v>
@@ -27281,7 +27281,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G928" t="n">
-        <v>1.81111240386963</v>
+        <v>1.81111228466034</v>
       </c>
       <c r="H928" t="n">
         <v>1500</v>
@@ -27513,7 +27513,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G936" t="n">
-        <v>1.81111240386963</v>
+        <v>1.81111228466034</v>
       </c>
       <c r="H936" t="n">
         <v>7500</v>
@@ -27542,7 +27542,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G937" t="n">
-        <v>1.81111240386963</v>
+        <v>1.81111228466034</v>
       </c>
       <c r="H937" t="n">
         <v>1500</v>
@@ -27629,7 +27629,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G940" t="n">
-        <v>1.78324890136719</v>
+        <v>1.78324902057648</v>
       </c>
       <c r="H940" t="n">
         <v>3000</v>
@@ -27658,7 +27658,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G941" t="n">
-        <v>1.78324890136719</v>
+        <v>1.78324902057648</v>
       </c>
       <c r="H941" t="n">
         <v>6000</v>
@@ -27716,7 +27716,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G943" t="n">
-        <v>1.81111240386963</v>
+        <v>1.81111228466034</v>
       </c>
       <c r="H943" t="n">
         <v>3000</v>
@@ -27745,7 +27745,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G944" t="n">
-        <v>1.773961186409</v>
+        <v>1.77396130561829</v>
       </c>
       <c r="H944" t="n">
         <v>27000</v>
@@ -27774,7 +27774,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G945" t="n">
-        <v>1.773961186409</v>
+        <v>1.77396130561829</v>
       </c>
       <c r="H945" t="n">
         <v>3000</v>
@@ -27803,7 +27803,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G946" t="n">
-        <v>1.773961186409</v>
+        <v>1.77396130561829</v>
       </c>
       <c r="H946" t="n">
         <v>0</v>
@@ -27832,7 +27832,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G947" t="n">
-        <v>1.78324890136719</v>
+        <v>1.78324902057648</v>
       </c>
       <c r="H947" t="n">
         <v>4500</v>
@@ -27919,7 +27919,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G950" t="n">
-        <v>1.78324890136719</v>
+        <v>1.78324902057648</v>
       </c>
       <c r="H950" t="n">
         <v>6000</v>
@@ -27948,7 +27948,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G951" t="n">
-        <v>1.78324890136719</v>
+        <v>1.78324902057648</v>
       </c>
       <c r="H951" t="n">
         <v>1500</v>
@@ -28122,7 +28122,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G957" t="n">
-        <v>1.78324890136719</v>
+        <v>1.78324902057648</v>
       </c>
       <c r="H957" t="n">
         <v>3000</v>
@@ -28151,7 +28151,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G958" t="n">
-        <v>1.78324890136719</v>
+        <v>1.78324902057648</v>
       </c>
       <c r="H958" t="n">
         <v>1500</v>
@@ -28180,7 +28180,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G959" t="n">
-        <v>1.78324890136719</v>
+        <v>1.78324902057648</v>
       </c>
       <c r="H959" t="n">
         <v>1500</v>
@@ -28209,7 +28209,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G960" t="n">
-        <v>1.75538563728333</v>
+        <v>1.75538575649261</v>
       </c>
       <c r="H960" t="n">
         <v>9000</v>
@@ -28238,7 +28238,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G961" t="n">
-        <v>1.78324890136719</v>
+        <v>1.78324902057648</v>
       </c>
       <c r="H961" t="n">
         <v>4500</v>
@@ -28354,7 +28354,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G965" t="n">
-        <v>1.78324890136719</v>
+        <v>1.78324902057648</v>
       </c>
       <c r="H965" t="n">
         <v>13500</v>
@@ -28383,7 +28383,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G966" t="n">
-        <v>1.78324890136719</v>
+        <v>1.78324902057648</v>
       </c>
       <c r="H966" t="n">
         <v>4500</v>
@@ -28615,7 +28615,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G974" t="n">
-        <v>1.82040011882782</v>
+        <v>1.82039999961853</v>
       </c>
       <c r="H974" t="n">
         <v>13500</v>
@@ -28644,7 +28644,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G975" t="n">
-        <v>1.82040011882782</v>
+        <v>1.82039999961853</v>
       </c>
       <c r="H975" t="n">
         <v>0</v>
@@ -28673,7 +28673,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G976" t="n">
-        <v>1.82040011882782</v>
+        <v>1.82039999961853</v>
       </c>
       <c r="H976" t="n">
         <v>0</v>
@@ -28702,7 +28702,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G977" t="n">
-        <v>1.773961186409</v>
+        <v>1.77396130561829</v>
       </c>
       <c r="H977" t="n">
         <v>16500</v>
@@ -28818,7 +28818,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G981" t="n">
-        <v>1.78324890136719</v>
+        <v>1.78324902057648</v>
       </c>
       <c r="H981" t="n">
         <v>1500</v>
@@ -28847,7 +28847,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G982" t="n">
-        <v>1.78324890136719</v>
+        <v>1.78324902057648</v>
       </c>
       <c r="H982" t="n">
         <v>0</v>
@@ -28876,7 +28876,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G983" t="n">
-        <v>1.78324890136719</v>
+        <v>1.78324902057648</v>
       </c>
       <c r="H983" t="n">
         <v>0</v>
@@ -28934,7 +28934,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G985" t="n">
-        <v>1.78324890136719</v>
+        <v>1.78324902057648</v>
       </c>
       <c r="H985" t="n">
         <v>15000</v>
@@ -28992,7 +28992,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G987" t="n">
-        <v>1.81111240386963</v>
+        <v>1.81111228466034</v>
       </c>
       <c r="H987" t="n">
         <v>40500</v>
@@ -29021,7 +29021,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G988" t="n">
-        <v>1.82040011882782</v>
+        <v>1.82039999961853</v>
       </c>
       <c r="H988" t="n">
         <v>3000</v>
@@ -29050,7 +29050,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G989" t="n">
-        <v>1.78324890136719</v>
+        <v>1.78324902057648</v>
       </c>
       <c r="H989" t="n">
         <v>1500</v>
@@ -29137,7 +29137,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G992" t="n">
-        <v>1.75538563728333</v>
+        <v>1.75538575649261</v>
       </c>
       <c r="H992" t="n">
         <v>9000</v>
@@ -29166,7 +29166,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G993" t="n">
-        <v>1.75538563728333</v>
+        <v>1.75538575649261</v>
       </c>
       <c r="H993" t="n">
         <v>0</v>
@@ -29195,7 +29195,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G994" t="n">
-        <v>1.773961186409</v>
+        <v>1.77396130561829</v>
       </c>
       <c r="H994" t="n">
         <v>3000</v>
@@ -29224,7 +29224,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G995" t="n">
-        <v>1.773961186409</v>
+        <v>1.77396130561829</v>
       </c>
       <c r="H995" t="n">
         <v>0</v>
@@ -29630,7 +29630,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1009" t="n">
-        <v>1.773961186409</v>
+        <v>1.77396130561829</v>
       </c>
       <c r="H1009" t="n">
         <v>6000</v>
@@ -29659,7 +29659,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1010" t="n">
-        <v>1.773961186409</v>
+        <v>1.77396130561829</v>
       </c>
       <c r="H1010" t="n">
         <v>0</v>
@@ -29688,7 +29688,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.773961186409</v>
+        <v>1.77396130561829</v>
       </c>
       <c r="H1011" t="n">
         <v>0</v>
@@ -29746,7 +29746,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1013" t="n">
-        <v>1.773961186409</v>
+        <v>1.77396130561829</v>
       </c>
       <c r="H1013" t="n">
         <v>3000</v>
@@ -29862,7 +29862,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1017" t="n">
-        <v>1.773961186409</v>
+        <v>1.77396130561829</v>
       </c>
       <c r="H1017" t="n">
         <v>1500</v>
@@ -29891,7 +29891,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1018" t="n">
-        <v>1.773961186409</v>
+        <v>1.77396130561829</v>
       </c>
       <c r="H1018" t="n">
         <v>0</v>
@@ -29920,7 +29920,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1019" t="n">
-        <v>1.773961186409</v>
+        <v>1.77396130561829</v>
       </c>
       <c r="H1019" t="n">
         <v>0</v>
@@ -30355,7 +30355,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1034" t="n">
-        <v>1.75538563728333</v>
+        <v>1.75538575649261</v>
       </c>
       <c r="H1034" t="n">
         <v>13500</v>
@@ -30384,7 +30384,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.81111240386963</v>
+        <v>1.81111228466034</v>
       </c>
       <c r="H1035" t="n">
         <v>1500</v>
@@ -30616,7 +30616,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.78324890136719</v>
+        <v>1.78324902057648</v>
       </c>
       <c r="H1043" t="n">
         <v>4500</v>
@@ -30645,7 +30645,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1044" t="n">
-        <v>1.773961186409</v>
+        <v>1.77396130561829</v>
       </c>
       <c r="H1044" t="n">
         <v>3000</v>
@@ -30674,7 +30674,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1045" t="n">
-        <v>1.75538563728333</v>
+        <v>1.75538575649261</v>
       </c>
       <c r="H1045" t="n">
         <v>4500</v>
@@ -30703,7 +30703,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1046" t="n">
-        <v>1.773961186409</v>
+        <v>1.77396130561829</v>
       </c>
       <c r="H1046" t="n">
         <v>9000</v>
@@ -30732,7 +30732,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1047" t="n">
-        <v>1.773961186409</v>
+        <v>1.77396130561829</v>
       </c>
       <c r="H1047" t="n">
         <v>1500</v>
@@ -30819,7 +30819,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1050" t="n">
-        <v>1.75538563728333</v>
+        <v>1.75538575649261</v>
       </c>
       <c r="H1050" t="n">
         <v>1500</v>
@@ -30848,7 +30848,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1051" t="n">
-        <v>1.773961186409</v>
+        <v>1.77396130561829</v>
       </c>
       <c r="H1051" t="n">
         <v>4500</v>
@@ -31167,7 +31167,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1062" t="n">
-        <v>1.70894706249237</v>
+        <v>1.70894694328308</v>
       </c>
       <c r="H1062" t="n">
         <v>4500</v>
@@ -32153,7 +32153,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1096" t="n">
-        <v>1.60678160190582</v>
+        <v>1.60678172111511</v>
       </c>
       <c r="H1096" t="n">
         <v>10500</v>
@@ -32211,7 +32211,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1098" t="n">
-        <v>1.78324890136719</v>
+        <v>1.78324902057648</v>
       </c>
       <c r="H1098" t="n">
         <v>25500</v>
@@ -32240,7 +32240,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1099" t="n">
-        <v>1.773961186409</v>
+        <v>1.77396130561829</v>
       </c>
       <c r="H1099" t="n">
         <v>7500</v>
@@ -32269,7 +32269,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1100" t="n">
-        <v>1.75538563728333</v>
+        <v>1.75538575649261</v>
       </c>
       <c r="H1100" t="n">
         <v>6000</v>
@@ -32530,7 +32530,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1109" t="n">
-        <v>1.70894706249237</v>
+        <v>1.70894694328308</v>
       </c>
       <c r="H1109" t="n">
         <v>4500</v>
@@ -33168,7 +33168,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1131" t="n">
-        <v>1.70894706249237</v>
+        <v>1.70894694328308</v>
       </c>
       <c r="H1131" t="n">
         <v>1500</v>
@@ -33255,7 +33255,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1134" t="n">
-        <v>1.70894706249237</v>
+        <v>1.70894694328308</v>
       </c>
       <c r="H1134" t="n">
         <v>6000</v>
@@ -33284,7 +33284,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1135" t="n">
-        <v>1.70894706249237</v>
+        <v>1.70894694328308</v>
       </c>
       <c r="H1135" t="n">
         <v>0</v>
@@ -33951,7 +33951,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1158" t="n">
-        <v>1.65322029590607</v>
+        <v>1.65322041511536</v>
       </c>
       <c r="H1158" t="n">
         <v>3000</v>
@@ -34183,7 +34183,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1166" t="n">
-        <v>1.54176735877991</v>
+        <v>1.54176723957062</v>
       </c>
       <c r="H1166" t="n">
         <v>13500</v>
@@ -34212,7 +34212,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1167" t="n">
-        <v>1.54176735877991</v>
+        <v>1.54176723957062</v>
       </c>
       <c r="H1167" t="n">
         <v>0</v>
@@ -34241,7 +34241,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1168" t="n">
-        <v>1.54176735877991</v>
+        <v>1.54176723957062</v>
       </c>
       <c r="H1168" t="n">
         <v>0</v>
@@ -45586,6 +45586,64 @@
         <v>3000</v>
       </c>
       <c r="I1559" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1560">
+      <c r="A1560" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1560" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1560" t="n">
+        <v>1.52999997138977</v>
+      </c>
+      <c r="D1560" t="n">
+        <v>1.52999997138977</v>
+      </c>
+      <c r="E1560" t="n">
+        <v>1.52999997138977</v>
+      </c>
+      <c r="F1560" t="n">
+        <v>1.52999997138977</v>
+      </c>
+      <c r="G1560" t="n">
+        <v>1.52999997138977</v>
+      </c>
+      <c r="H1560" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1560" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1561">
+      <c r="A1561" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1561" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1561" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D1561" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E1561" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F1561" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G1561" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H1561" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I1561" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RETI.MI.xlsx
+++ b/data/RETI.MI.xlsx
@@ -485,7 +485,7 @@
         <v>0.879899978637695</v>
       </c>
       <c r="G4" t="n">
-        <v>0.751319706439972</v>
+        <v>0.751319646835327</v>
       </c>
       <c r="H4" t="n">
         <v>75000</v>
@@ -659,7 +659,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G10" t="n">
-        <v>0.722373604774475</v>
+        <v>0.72237354516983</v>
       </c>
       <c r="H10" t="n">
         <v>48000</v>
@@ -862,7 +862,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G17" t="n">
-        <v>0.654063999652863</v>
+        <v>0.654063940048218</v>
       </c>
       <c r="H17" t="n">
         <v>25500</v>
@@ -891,7 +891,7 @@
         <v>0.833999991416931</v>
       </c>
       <c r="G18" t="n">
-        <v>0.712127149105072</v>
+        <v>0.712127089500427</v>
       </c>
       <c r="H18" t="n">
         <v>579000</v>
@@ -978,7 +978,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G21" t="n">
-        <v>0.654063999652863</v>
+        <v>0.654063940048218</v>
       </c>
       <c r="H21" t="n">
         <v>132000</v>
@@ -1007,7 +1007,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G22" t="n">
-        <v>0.659187257289886</v>
+        <v>0.659187197685242</v>
       </c>
       <c r="H22" t="n">
         <v>24000</v>
@@ -1065,7 +1065,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G24" t="n">
-        <v>0.652356266975403</v>
+        <v>0.652356207370758</v>
       </c>
       <c r="H24" t="n">
         <v>10500</v>
@@ -1094,7 +1094,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G25" t="n">
-        <v>0.660894989967346</v>
+        <v>0.660894930362701</v>
       </c>
       <c r="H25" t="n">
         <v>12000</v>
@@ -1123,7 +1123,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G26" t="n">
-        <v>0.654063999652863</v>
+        <v>0.654063940048218</v>
       </c>
       <c r="H26" t="n">
         <v>27000</v>
@@ -1181,7 +1181,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G28" t="n">
-        <v>0.631863415241241</v>
+        <v>0.631863355636597</v>
       </c>
       <c r="H28" t="n">
         <v>33000</v>
@@ -1239,7 +1239,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G30" t="n">
-        <v>0.607955098152161</v>
+        <v>0.607955038547516</v>
       </c>
       <c r="H30" t="n">
         <v>19500</v>
@@ -1297,7 +1297,7 @@
         <v>0.73199999332428</v>
       </c>
       <c r="G32" t="n">
-        <v>0.625032424926758</v>
+        <v>0.625032484531403</v>
       </c>
       <c r="H32" t="n">
         <v>27000</v>
@@ -1326,7 +1326,7 @@
         <v>0.722000002861023</v>
       </c>
       <c r="G33" t="n">
-        <v>0.616493701934814</v>
+        <v>0.616493761539459</v>
       </c>
       <c r="H33" t="n">
         <v>3000</v>
@@ -1355,7 +1355,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G34" t="n">
-        <v>0.60966283082962</v>
+        <v>0.609662771224976</v>
       </c>
       <c r="H34" t="n">
         <v>13500</v>
@@ -1384,7 +1384,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G35" t="n">
-        <v>0.580631256103516</v>
+        <v>0.58063131570816</v>
       </c>
       <c r="H35" t="n">
         <v>12000</v>
@@ -1413,7 +1413,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G36" t="n">
-        <v>0.563553869724274</v>
+        <v>0.563553810119629</v>
       </c>
       <c r="H36" t="n">
         <v>66000</v>
@@ -1500,7 +1500,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G39" t="n">
-        <v>0.525983512401581</v>
+        <v>0.525983572006226</v>
       </c>
       <c r="H39" t="n">
         <v>10500</v>
@@ -1529,7 +1529,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G40" t="n">
-        <v>0.546476483345032</v>
+        <v>0.546476423740387</v>
       </c>
       <c r="H40" t="n">
         <v>15000</v>
@@ -1703,7 +1703,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G46" t="n">
-        <v>0.631863415241241</v>
+        <v>0.631863355636597</v>
       </c>
       <c r="H46" t="n">
         <v>6000</v>
@@ -1732,7 +1732,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G47" t="n">
-        <v>0.607955098152161</v>
+        <v>0.607955038547516</v>
       </c>
       <c r="H47" t="n">
         <v>7500</v>
@@ -1761,7 +1761,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G48" t="n">
-        <v>0.611370503902435</v>
+        <v>0.61137056350708</v>
       </c>
       <c r="H48" t="n">
         <v>21000</v>
@@ -1819,7 +1819,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G50" t="n">
-        <v>0.631863415241241</v>
+        <v>0.631863355636597</v>
       </c>
       <c r="H50" t="n">
         <v>12000</v>
@@ -1906,7 +1906,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G53" t="n">
-        <v>0.701880693435669</v>
+        <v>0.701880753040314</v>
       </c>
       <c r="H53" t="n">
         <v>70500</v>
@@ -1964,7 +1964,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G55" t="n">
-        <v>0.677972316741943</v>
+        <v>0.677972376346588</v>
       </c>
       <c r="H55" t="n">
         <v>36000</v>
@@ -2167,7 +2167,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G62" t="n">
-        <v>0.681387782096863</v>
+        <v>0.681387841701508</v>
       </c>
       <c r="H62" t="n">
         <v>16500</v>
@@ -2399,7 +2399,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G70" t="n">
-        <v>0.677972316741943</v>
+        <v>0.677972376346588</v>
       </c>
       <c r="H70" t="n">
         <v>3000</v>
@@ -2428,7 +2428,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G71" t="n">
-        <v>0.677972316741943</v>
+        <v>0.677972376346588</v>
       </c>
       <c r="H71" t="n">
         <v>3000</v>
@@ -2544,7 +2544,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G75" t="n">
-        <v>0.700172960758209</v>
+        <v>0.700172901153564</v>
       </c>
       <c r="H75" t="n">
         <v>73500</v>
@@ -2602,7 +2602,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G77" t="n">
-        <v>0.700172960758209</v>
+        <v>0.700172901153564</v>
       </c>
       <c r="H77" t="n">
         <v>22500</v>
@@ -2631,7 +2631,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G78" t="n">
-        <v>0.700172960758209</v>
+        <v>0.700172901153564</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
@@ -2689,7 +2689,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G80" t="n">
-        <v>0.717250287532806</v>
+        <v>0.717250347137451</v>
       </c>
       <c r="H80" t="n">
         <v>28500</v>
@@ -2718,7 +2718,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G81" t="n">
-        <v>0.708711624145508</v>
+        <v>0.708711683750153</v>
       </c>
       <c r="H81" t="n">
         <v>22500</v>
@@ -2747,7 +2747,7 @@
         <v>0.833999991416931</v>
       </c>
       <c r="G82" t="n">
-        <v>0.712127149105072</v>
+        <v>0.712127089500427</v>
       </c>
       <c r="H82" t="n">
         <v>4500</v>
@@ -2776,7 +2776,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G83" t="n">
-        <v>0.715542674064636</v>
+        <v>0.715542614459991</v>
       </c>
       <c r="H83" t="n">
         <v>1500</v>
@@ -2805,7 +2805,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G84" t="n">
-        <v>0.717250287532806</v>
+        <v>0.717250347137451</v>
       </c>
       <c r="H84" t="n">
         <v>1500</v>
@@ -2834,7 +2834,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G85" t="n">
-        <v>0.715542674064636</v>
+        <v>0.715542614459991</v>
       </c>
       <c r="H85" t="n">
         <v>9000</v>
@@ -2863,7 +2863,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G86" t="n">
-        <v>0.700172960758209</v>
+        <v>0.700172901153564</v>
       </c>
       <c r="H86" t="n">
         <v>1500</v>
@@ -2921,7 +2921,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G88" t="n">
-        <v>0.700172960758209</v>
+        <v>0.700172901153564</v>
       </c>
       <c r="H88" t="n">
         <v>16500</v>
@@ -2950,7 +2950,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G89" t="n">
-        <v>0.684803187847137</v>
+        <v>0.684803247451782</v>
       </c>
       <c r="H89" t="n">
         <v>22500</v>
@@ -2979,7 +2979,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G90" t="n">
-        <v>0.684803187847137</v>
+        <v>0.684803247451782</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -3008,7 +3008,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G91" t="n">
-        <v>0.701880693435669</v>
+        <v>0.701880753040314</v>
       </c>
       <c r="H91" t="n">
         <v>10500</v>
@@ -3037,7 +3037,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G92" t="n">
-        <v>0.701880693435669</v>
+        <v>0.701880753040314</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
@@ -3066,7 +3066,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G93" t="n">
-        <v>0.701880693435669</v>
+        <v>0.701880753040314</v>
       </c>
       <c r="H93" t="n">
         <v>1500</v>
@@ -3240,7 +3240,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G99" t="n">
-        <v>0.677972316741943</v>
+        <v>0.677972376346588</v>
       </c>
       <c r="H99" t="n">
         <v>7500</v>
@@ -3269,7 +3269,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G100" t="n">
-        <v>0.676264643669128</v>
+        <v>0.676264524459839</v>
       </c>
       <c r="H100" t="n">
         <v>7500</v>
@@ -3298,7 +3298,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G101" t="n">
-        <v>0.676264643669128</v>
+        <v>0.676264524459839</v>
       </c>
       <c r="H101" t="n">
         <v>0</v>
@@ -3501,7 +3501,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G108" t="n">
-        <v>0.700172960758209</v>
+        <v>0.700172901153564</v>
       </c>
       <c r="H108" t="n">
         <v>55500</v>
@@ -3617,7 +3617,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G112" t="n">
-        <v>0.686511099338531</v>
+        <v>0.686511039733887</v>
       </c>
       <c r="H112" t="n">
         <v>40500</v>
@@ -3675,7 +3675,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G114" t="n">
-        <v>0.700172960758209</v>
+        <v>0.700172901153564</v>
       </c>
       <c r="H114" t="n">
         <v>21000</v>
@@ -3762,7 +3762,7 @@
         <v>0.842000007629395</v>
       </c>
       <c r="G117" t="n">
-        <v>0.718958079814911</v>
+        <v>0.718958020210266</v>
       </c>
       <c r="H117" t="n">
         <v>102000</v>
@@ -3791,7 +3791,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G118" t="n">
-        <v>0.717250287532806</v>
+        <v>0.717250347137451</v>
       </c>
       <c r="H118" t="n">
         <v>69000</v>
@@ -3820,7 +3820,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G119" t="n">
-        <v>0.715542674064636</v>
+        <v>0.715542614459991</v>
       </c>
       <c r="H119" t="n">
         <v>16500</v>
@@ -3907,7 +3907,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G122" t="n">
-        <v>0.858138859272003</v>
+        <v>0.858138799667358</v>
       </c>
       <c r="H122" t="n">
         <v>660000</v>
@@ -3936,7 +3936,7 @@
         <v>0.972000002861023</v>
       </c>
       <c r="G123" t="n">
-        <v>0.829961061477661</v>
+        <v>0.829961180686951</v>
       </c>
       <c r="H123" t="n">
         <v>922500</v>
@@ -3965,7 +3965,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G124" t="n">
-        <v>0.828253328800201</v>
+        <v>0.828253448009491</v>
       </c>
       <c r="H124" t="n">
         <v>213000</v>
@@ -3994,7 +3994,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G125" t="n">
-        <v>0.836792051792145</v>
+        <v>0.83679211139679</v>
       </c>
       <c r="H125" t="n">
         <v>196500</v>
@@ -4023,7 +4023,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G126" t="n">
-        <v>0.836792051792145</v>
+        <v>0.83679211139679</v>
       </c>
       <c r="H126" t="n">
         <v>76500</v>
@@ -4081,7 +4081,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G128" t="n">
-        <v>0.86240816116333</v>
+        <v>0.862408101558685</v>
       </c>
       <c r="H128" t="n">
         <v>60000</v>
@@ -4110,7 +4110,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G129" t="n">
-        <v>0.86240816116333</v>
+        <v>0.862408101558685</v>
       </c>
       <c r="H129" t="n">
         <v>25500</v>
@@ -4139,7 +4139,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G130" t="n">
-        <v>0.86240816116333</v>
+        <v>0.862408101558685</v>
       </c>
       <c r="H130" t="n">
         <v>72000</v>
@@ -4197,7 +4197,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G132" t="n">
-        <v>0.845330774784088</v>
+        <v>0.845330715179443</v>
       </c>
       <c r="H132" t="n">
         <v>25500</v>
@@ -4342,7 +4342,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G137" t="n">
-        <v>0.888024210929871</v>
+        <v>0.888024151325226</v>
       </c>
       <c r="H137" t="n">
         <v>33000</v>
@@ -4371,7 +4371,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G138" t="n">
-        <v>0.892293512821198</v>
+        <v>0.892293572425842</v>
       </c>
       <c r="H138" t="n">
         <v>82500</v>
@@ -4400,7 +4400,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G139" t="n">
-        <v>0.913640379905701</v>
+        <v>0.913640260696411</v>
       </c>
       <c r="H139" t="n">
         <v>4500</v>
@@ -4429,7 +4429,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G140" t="n">
-        <v>0.922179043292999</v>
+        <v>0.922179102897644</v>
       </c>
       <c r="H140" t="n">
         <v>22500</v>
@@ -4458,7 +4458,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G141" t="n">
-        <v>0.922179043292999</v>
+        <v>0.922179102897644</v>
       </c>
       <c r="H141" t="n">
         <v>67500</v>
@@ -4487,7 +4487,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G142" t="n">
-        <v>0.913640379905701</v>
+        <v>0.913640260696411</v>
       </c>
       <c r="H142" t="n">
         <v>42000</v>
@@ -4516,7 +4516,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G143" t="n">
-        <v>0.930717766284943</v>
+        <v>0.930717825889587</v>
       </c>
       <c r="H143" t="n">
         <v>45000</v>
@@ -4574,7 +4574,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G145" t="n">
-        <v>1.11429965496063</v>
+        <v>1.11429953575134</v>
       </c>
       <c r="H145" t="n">
         <v>834000</v>
@@ -4603,7 +4603,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G146" t="n">
-        <v>1.13564646244049</v>
+        <v>1.13564622402191</v>
       </c>
       <c r="H146" t="n">
         <v>342000</v>
@@ -4661,7 +4661,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G148" t="n">
-        <v>1.20395588874817</v>
+        <v>1.20395600795746</v>
       </c>
       <c r="H148" t="n">
         <v>210000</v>
@@ -4690,7 +4690,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G149" t="n">
-        <v>1.20395588874817</v>
+        <v>1.20395600795746</v>
       </c>
       <c r="H149" t="n">
         <v>172500</v>
@@ -4777,7 +4777,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G152" t="n">
-        <v>1.22153174877167</v>
+        <v>1.22153186798096</v>
       </c>
       <c r="H152" t="n">
         <v>57000</v>
@@ -4806,7 +4806,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G153" t="n">
-        <v>1.22153174877167</v>
+        <v>1.22153186798096</v>
       </c>
       <c r="H153" t="n">
         <v>157500</v>
@@ -4893,7 +4893,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G156" t="n">
-        <v>1.14683389663696</v>
+        <v>1.14683377742767</v>
       </c>
       <c r="H156" t="n">
         <v>15000</v>
@@ -4980,7 +4980,7 @@
         <v>1.25499999523163</v>
       </c>
       <c r="G159" t="n">
-        <v>1.10289394855499</v>
+        <v>1.1028938293457</v>
       </c>
       <c r="H159" t="n">
         <v>19500</v>
@@ -5009,7 +5009,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G160" t="n">
-        <v>1.05455994606018</v>
+        <v>1.05455982685089</v>
       </c>
       <c r="H160" t="n">
         <v>49500</v>
@@ -5038,7 +5038,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G161" t="n">
-        <v>1.08971178531647</v>
+        <v>1.08971190452576</v>
       </c>
       <c r="H161" t="n">
         <v>136500</v>
@@ -5067,7 +5067,7 @@
         <v>1.25</v>
       </c>
       <c r="G162" t="n">
-        <v>1.09849989414215</v>
+        <v>1.09850001335144</v>
       </c>
       <c r="H162" t="n">
         <v>39000</v>
@@ -5154,7 +5154,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G165" t="n">
-        <v>1.16880404949188</v>
+        <v>1.16880393028259</v>
       </c>
       <c r="H165" t="n">
         <v>52500</v>
@@ -5241,7 +5241,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G168" t="n">
-        <v>1.14683389663696</v>
+        <v>1.14683377742767</v>
       </c>
       <c r="H168" t="n">
         <v>49500</v>
@@ -5270,7 +5270,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G169" t="n">
-        <v>1.12925791740417</v>
+        <v>1.12925803661346</v>
       </c>
       <c r="H169" t="n">
         <v>28500</v>
@@ -5299,7 +5299,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G170" t="n">
-        <v>1.14683389663696</v>
+        <v>1.14683377742767</v>
       </c>
       <c r="H170" t="n">
         <v>9000</v>
@@ -5473,7 +5473,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G176" t="n">
-        <v>1.32259368896484</v>
+        <v>1.32259380817413</v>
       </c>
       <c r="H176" t="n">
         <v>226500</v>
@@ -5502,7 +5502,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G177" t="n">
-        <v>1.32259368896484</v>
+        <v>1.32259380817413</v>
       </c>
       <c r="H177" t="n">
         <v>208500</v>
@@ -5560,7 +5560,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G179" t="n">
-        <v>1.33577585220337</v>
+        <v>1.33577597141266</v>
       </c>
       <c r="H179" t="n">
         <v>48000</v>
@@ -5589,7 +5589,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G180" t="n">
-        <v>1.34895801544189</v>
+        <v>1.34895777702332</v>
       </c>
       <c r="H180" t="n">
         <v>9000</v>
@@ -5618,7 +5618,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G181" t="n">
-        <v>1.33577585220337</v>
+        <v>1.33577597141266</v>
       </c>
       <c r="H181" t="n">
         <v>24000</v>
@@ -5676,7 +5676,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G183" t="n">
-        <v>1.283047914505</v>
+        <v>1.28304779529572</v>
       </c>
       <c r="H183" t="n">
         <v>180000</v>
@@ -5705,7 +5705,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G184" t="n">
-        <v>1.32259368896484</v>
+        <v>1.32259380817413</v>
       </c>
       <c r="H184" t="n">
         <v>30000</v>
@@ -5821,7 +5821,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G188" t="n">
-        <v>1.34895801544189</v>
+        <v>1.34895777702332</v>
       </c>
       <c r="H188" t="n">
         <v>36000</v>
@@ -5850,7 +5850,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G189" t="n">
-        <v>1.45001995563507</v>
+        <v>1.45001983642578</v>
       </c>
       <c r="H189" t="n">
         <v>148500</v>
@@ -5937,7 +5937,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G192" t="n">
-        <v>1.37971591949463</v>
+        <v>1.37971580028534</v>
       </c>
       <c r="H192" t="n">
         <v>87000</v>
@@ -5966,7 +5966,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G193" t="n">
-        <v>1.34895801544189</v>
+        <v>1.34895777702332</v>
       </c>
       <c r="H193" t="n">
         <v>34500</v>
@@ -6082,7 +6082,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G197" t="n">
-        <v>1.32259368896484</v>
+        <v>1.32259380817413</v>
       </c>
       <c r="H197" t="n">
         <v>43500</v>
@@ -6169,7 +6169,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G200" t="n">
-        <v>1.34895801544189</v>
+        <v>1.34895777702332</v>
       </c>
       <c r="H200" t="n">
         <v>22500</v>
@@ -6314,7 +6314,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G205" t="n">
-        <v>1.33577585220337</v>
+        <v>1.33577597141266</v>
       </c>
       <c r="H205" t="n">
         <v>4500</v>
@@ -6401,7 +6401,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G208" t="n">
-        <v>1.35335195064545</v>
+        <v>1.35335183143616</v>
       </c>
       <c r="H208" t="n">
         <v>1500</v>
@@ -6430,7 +6430,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G209" t="n">
-        <v>1.35335195064545</v>
+        <v>1.35335183143616</v>
       </c>
       <c r="H209" t="n">
         <v>0</v>
@@ -6459,7 +6459,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G210" t="n">
-        <v>1.35335195064545</v>
+        <v>1.35335183143616</v>
       </c>
       <c r="H210" t="n">
         <v>0</v>
@@ -6575,7 +6575,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G214" t="n">
-        <v>1.34895801544189</v>
+        <v>1.34895777702332</v>
       </c>
       <c r="H214" t="n">
         <v>28500</v>
@@ -6691,7 +6691,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G218" t="n">
-        <v>1.24789595603943</v>
+        <v>1.24789583683014</v>
       </c>
       <c r="H218" t="n">
         <v>33000</v>
@@ -7068,7 +7068,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G231" t="n">
-        <v>1.283047914505</v>
+        <v>1.28304779529572</v>
       </c>
       <c r="H231" t="n">
         <v>4500</v>
@@ -7213,7 +7213,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G236" t="n">
-        <v>1.34895801544189</v>
+        <v>1.34895777702332</v>
       </c>
       <c r="H236" t="n">
         <v>13500</v>
@@ -7329,7 +7329,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G240" t="n">
-        <v>1.74881172180176</v>
+        <v>1.74881196022034</v>
       </c>
       <c r="H240" t="n">
         <v>333000</v>
@@ -7358,7 +7358,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G241" t="n">
-        <v>2.24972796440125</v>
+        <v>2.24972772598267</v>
       </c>
       <c r="H241" t="n">
         <v>774000</v>
@@ -7474,7 +7474,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G245" t="n">
-        <v>2.39912366867065</v>
+        <v>2.39912390708923</v>
       </c>
       <c r="H245" t="n">
         <v>546000</v>
@@ -7590,7 +7590,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G249" t="n">
-        <v>2.20578789710999</v>
+        <v>2.20578765869141</v>
       </c>
       <c r="H249" t="n">
         <v>195000</v>
@@ -7764,7 +7764,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G255" t="n">
-        <v>2.33760809898376</v>
+        <v>2.33760786056519</v>
       </c>
       <c r="H255" t="n">
         <v>108000</v>
@@ -7851,7 +7851,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G258" t="n">
-        <v>2.28487992286682</v>
+        <v>2.28487968444824</v>
       </c>
       <c r="H258" t="n">
         <v>138000</v>
@@ -7880,7 +7880,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G259" t="n">
-        <v>2.22336339950562</v>
+        <v>2.22336363792419</v>
       </c>
       <c r="H259" t="n">
         <v>60000</v>
@@ -7909,7 +7909,7 @@
         <v>2.5</v>
       </c>
       <c r="G260" t="n">
-        <v>2.1969997882843</v>
+        <v>2.19700002670288</v>
       </c>
       <c r="H260" t="n">
         <v>85500</v>
@@ -7967,7 +7967,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G262" t="n">
-        <v>2.24972796440125</v>
+        <v>2.24972772598267</v>
       </c>
       <c r="H262" t="n">
         <v>33000</v>
@@ -7996,7 +7996,7 @@
         <v>2.5</v>
       </c>
       <c r="G263" t="n">
-        <v>2.1969997882843</v>
+        <v>2.19700002670288</v>
       </c>
       <c r="H263" t="n">
         <v>13500</v>
@@ -8025,7 +8025,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G264" t="n">
-        <v>2.20578789710999</v>
+        <v>2.20578765869141</v>
       </c>
       <c r="H264" t="n">
         <v>37500</v>
@@ -8170,7 +8170,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G269" t="n">
-        <v>2.31124377250671</v>
+        <v>2.31124401092529</v>
       </c>
       <c r="H269" t="n">
         <v>54000</v>
@@ -8228,7 +8228,7 @@
         <v>2.5</v>
       </c>
       <c r="G271" t="n">
-        <v>2.1969997882843</v>
+        <v>2.19700002670288</v>
       </c>
       <c r="H271" t="n">
         <v>36000</v>
@@ -8315,7 +8315,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G274" t="n">
-        <v>2.24972796440125</v>
+        <v>2.24972772598267</v>
       </c>
       <c r="H274" t="n">
         <v>45000</v>
@@ -8344,7 +8344,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G275" t="n">
-        <v>2.28487992286682</v>
+        <v>2.28487968444824</v>
       </c>
       <c r="H275" t="n">
         <v>18000</v>
@@ -8373,7 +8373,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G276" t="n">
-        <v>2.28487992286682</v>
+        <v>2.28487968444824</v>
       </c>
       <c r="H276" t="n">
         <v>6000</v>
@@ -8489,7 +8489,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G280" t="n">
-        <v>2.28487992286682</v>
+        <v>2.28487968444824</v>
       </c>
       <c r="H280" t="n">
         <v>16500</v>
@@ -8576,7 +8576,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G283" t="n">
-        <v>2.25851583480835</v>
+        <v>2.25851607322693</v>
       </c>
       <c r="H283" t="n">
         <v>12000</v>
@@ -8779,7 +8779,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G290" t="n">
-        <v>2.25851583480835</v>
+        <v>2.25851607322693</v>
       </c>
       <c r="H290" t="n">
         <v>63000</v>
@@ -8866,7 +8866,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G293" t="n">
-        <v>2.24972796440125</v>
+        <v>2.24972772598267</v>
       </c>
       <c r="H293" t="n">
         <v>1500</v>
@@ -8895,7 +8895,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G294" t="n">
-        <v>2.28487992286682</v>
+        <v>2.28487968444824</v>
       </c>
       <c r="H294" t="n">
         <v>1500</v>
@@ -9040,7 +9040,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G299" t="n">
-        <v>2.22336339950562</v>
+        <v>2.22336363792419</v>
       </c>
       <c r="H299" t="n">
         <v>4500</v>
@@ -9069,7 +9069,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G300" t="n">
-        <v>2.20578789710999</v>
+        <v>2.20578765869141</v>
       </c>
       <c r="H300" t="n">
         <v>24000</v>
@@ -9098,7 +9098,7 @@
         <v>2.5</v>
       </c>
       <c r="G301" t="n">
-        <v>2.1969997882843</v>
+        <v>2.19700002670288</v>
       </c>
       <c r="H301" t="n">
         <v>21000</v>
@@ -9127,7 +9127,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G302" t="n">
-        <v>2.14427185058594</v>
+        <v>2.14427208900452</v>
       </c>
       <c r="H302" t="n">
         <v>31500</v>
@@ -9243,7 +9243,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G306" t="n">
-        <v>1.99487578868866</v>
+        <v>1.99487566947937</v>
       </c>
       <c r="H306" t="n">
         <v>13500</v>
@@ -9330,7 +9330,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G309" t="n">
-        <v>1.93335962295532</v>
+        <v>1.93335998058319</v>
       </c>
       <c r="H309" t="n">
         <v>18000</v>
@@ -9446,7 +9446,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G313" t="n">
-        <v>1.93335962295532</v>
+        <v>1.93335998058319</v>
       </c>
       <c r="H313" t="n">
         <v>18000</v>
@@ -9475,7 +9475,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G314" t="n">
-        <v>1.93335962295532</v>
+        <v>1.93335998058319</v>
       </c>
       <c r="H314" t="n">
         <v>6000</v>
@@ -9591,7 +9591,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G318" t="n">
-        <v>2.09154391288757</v>
+        <v>2.09154367446899</v>
       </c>
       <c r="H318" t="n">
         <v>12000</v>
@@ -9649,7 +9649,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G320" t="n">
-        <v>2.14427185058594</v>
+        <v>2.14427208900452</v>
       </c>
       <c r="H320" t="n">
         <v>9000</v>
@@ -9678,7 +9678,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G321" t="n">
-        <v>2.14427185058594</v>
+        <v>2.14427208900452</v>
       </c>
       <c r="H321" t="n">
         <v>3000</v>
@@ -9968,7 +9968,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G331" t="n">
-        <v>1.99487578868866</v>
+        <v>1.99487566947937</v>
       </c>
       <c r="H331" t="n">
         <v>12000</v>
@@ -9997,7 +9997,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G332" t="n">
-        <v>1.99487578868866</v>
+        <v>1.99487566947937</v>
       </c>
       <c r="H332" t="n">
         <v>7500</v>
@@ -10026,7 +10026,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G333" t="n">
-        <v>1.99487578868866</v>
+        <v>1.99487566947937</v>
       </c>
       <c r="H333" t="n">
         <v>6000</v>
@@ -10142,7 +10142,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G337" t="n">
-        <v>2.10911989212036</v>
+        <v>2.10911965370178</v>
       </c>
       <c r="H337" t="n">
         <v>9000</v>
@@ -10171,7 +10171,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G338" t="n">
-        <v>2.056391954422</v>
+        <v>2.05639171600342</v>
       </c>
       <c r="H338" t="n">
         <v>3000</v>
@@ -10345,7 +10345,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G344" t="n">
-        <v>1.95972394943237</v>
+        <v>1.9597235918045</v>
       </c>
       <c r="H344" t="n">
         <v>27000</v>
@@ -10374,7 +10374,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G345" t="n">
-        <v>2.01245164871216</v>
+        <v>2.01245188713074</v>
       </c>
       <c r="H345" t="n">
         <v>4500</v>
@@ -10461,7 +10461,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G348" t="n">
-        <v>1.93335962295532</v>
+        <v>1.93335998058319</v>
       </c>
       <c r="H348" t="n">
         <v>1500</v>
@@ -10693,7 +10693,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G356" t="n">
-        <v>2.01245164871216</v>
+        <v>2.01245188713074</v>
       </c>
       <c r="H356" t="n">
         <v>19500</v>
@@ -10838,7 +10838,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G361" t="n">
-        <v>1.99487578868866</v>
+        <v>1.99487566947937</v>
       </c>
       <c r="H361" t="n">
         <v>15000</v>
@@ -10867,7 +10867,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G362" t="n">
-        <v>1.99487578868866</v>
+        <v>1.99487566947937</v>
       </c>
       <c r="H362" t="n">
         <v>6000</v>
@@ -10983,7 +10983,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G366" t="n">
-        <v>1.93335962295532</v>
+        <v>1.93335998058319</v>
       </c>
       <c r="H366" t="n">
         <v>13500</v>
@@ -11012,7 +11012,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G367" t="n">
-        <v>1.93335962295532</v>
+        <v>1.93335998058319</v>
       </c>
       <c r="H367" t="n">
         <v>1500</v>
@@ -11041,7 +11041,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G368" t="n">
-        <v>2.01245164871216</v>
+        <v>2.01245188713074</v>
       </c>
       <c r="H368" t="n">
         <v>4500</v>
@@ -11099,7 +11099,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G370" t="n">
-        <v>1.93335962295532</v>
+        <v>1.93335998058319</v>
       </c>
       <c r="H370" t="n">
         <v>6000</v>
@@ -11128,7 +11128,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G371" t="n">
-        <v>1.93335962295532</v>
+        <v>1.93335998058319</v>
       </c>
       <c r="H371" t="n">
         <v>1500</v>
@@ -11186,7 +11186,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G373" t="n">
-        <v>1.95093560218811</v>
+        <v>1.95093584060669</v>
       </c>
       <c r="H373" t="n">
         <v>3000</v>
@@ -11215,7 +11215,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G374" t="n">
-        <v>1.77517592906952</v>
+        <v>1.77517580986023</v>
       </c>
       <c r="H374" t="n">
         <v>52500</v>
@@ -11273,7 +11273,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G376" t="n">
-        <v>1.88063192367554</v>
+        <v>1.88063168525696</v>
       </c>
       <c r="H376" t="n">
         <v>9000</v>
@@ -11302,7 +11302,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G377" t="n">
-        <v>1.88063192367554</v>
+        <v>1.88063168525696</v>
       </c>
       <c r="H377" t="n">
         <v>3000</v>
@@ -11360,7 +11360,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G379" t="n">
-        <v>1.93335962295532</v>
+        <v>1.93335998058319</v>
       </c>
       <c r="H379" t="n">
         <v>3000</v>
@@ -11447,7 +11447,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G382" t="n">
-        <v>1.80153977870941</v>
+        <v>1.80153965950012</v>
       </c>
       <c r="H382" t="n">
         <v>21000</v>
@@ -11476,7 +11476,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G383" t="n">
-        <v>1.86305582523346</v>
+        <v>1.86305558681488</v>
       </c>
       <c r="H383" t="n">
         <v>21000</v>
@@ -11505,7 +11505,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G384" t="n">
-        <v>1.86305582523346</v>
+        <v>1.86305558681488</v>
       </c>
       <c r="H384" t="n">
         <v>1500</v>
@@ -11534,7 +11534,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G385" t="n">
-        <v>1.88063192367554</v>
+        <v>1.88063168525696</v>
       </c>
       <c r="H385" t="n">
         <v>13500</v>
@@ -11563,7 +11563,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G386" t="n">
-        <v>1.99487578868866</v>
+        <v>1.99487566947937</v>
       </c>
       <c r="H386" t="n">
         <v>15000</v>
@@ -11592,7 +11592,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G387" t="n">
-        <v>1.89820790290833</v>
+        <v>1.89820802211761</v>
       </c>
       <c r="H387" t="n">
         <v>28500</v>
@@ -11621,7 +11621,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G388" t="n">
-        <v>1.99487578868866</v>
+        <v>1.99487566947937</v>
       </c>
       <c r="H388" t="n">
         <v>9000</v>
@@ -11679,7 +11679,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G390" t="n">
-        <v>1.93335962295532</v>
+        <v>1.93335998058319</v>
       </c>
       <c r="H390" t="n">
         <v>1500</v>
@@ -11824,7 +11824,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G395" t="n">
-        <v>1.99487578868866</v>
+        <v>1.99487566947937</v>
       </c>
       <c r="H395" t="n">
         <v>31500</v>
@@ -11853,7 +11853,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G396" t="n">
-        <v>2.01245164871216</v>
+        <v>2.01245188713074</v>
       </c>
       <c r="H396" t="n">
         <v>12000</v>
@@ -11911,7 +11911,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G398" t="n">
-        <v>2.056391954422</v>
+        <v>2.05639171600342</v>
       </c>
       <c r="H398" t="n">
         <v>10500</v>
@@ -11998,7 +11998,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G401" t="n">
-        <v>2.01245164871216</v>
+        <v>2.01245188713074</v>
       </c>
       <c r="H401" t="n">
         <v>15000</v>
@@ -12027,7 +12027,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G402" t="n">
-        <v>2.056391954422</v>
+        <v>2.05639171600342</v>
       </c>
       <c r="H402" t="n">
         <v>36000</v>
@@ -12056,7 +12056,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G403" t="n">
-        <v>1.93335962295532</v>
+        <v>1.93335998058319</v>
       </c>
       <c r="H403" t="n">
         <v>7500</v>
@@ -12172,7 +12172,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G407" t="n">
-        <v>1.84547972679138</v>
+        <v>1.84547960758209</v>
       </c>
       <c r="H407" t="n">
         <v>64500</v>
@@ -12201,7 +12201,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G408" t="n">
-        <v>1.89820790290833</v>
+        <v>1.89820802211761</v>
       </c>
       <c r="H408" t="n">
         <v>6000</v>
@@ -12288,7 +12288,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G411" t="n">
-        <v>1.87184381484985</v>
+        <v>1.87184405326843</v>
       </c>
       <c r="H411" t="n">
         <v>4500</v>
@@ -12317,7 +12317,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G412" t="n">
-        <v>1.88063192367554</v>
+        <v>1.88063168525696</v>
       </c>
       <c r="H412" t="n">
         <v>9000</v>
@@ -12346,7 +12346,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G413" t="n">
-        <v>1.88063192367554</v>
+        <v>1.88063168525696</v>
       </c>
       <c r="H413" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G415" t="n">
-        <v>1.8191157579422</v>
+        <v>1.81911587715149</v>
       </c>
       <c r="H415" t="n">
         <v>4500</v>
@@ -12433,7 +12433,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G416" t="n">
-        <v>1.8191157579422</v>
+        <v>1.81911587715149</v>
       </c>
       <c r="H416" t="n">
         <v>0</v>
@@ -12462,7 +12462,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G417" t="n">
-        <v>1.86305582523346</v>
+        <v>1.86305558681488</v>
       </c>
       <c r="H417" t="n">
         <v>6000</v>
@@ -12549,7 +12549,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G420" t="n">
-        <v>1.89820790290833</v>
+        <v>1.89820802211761</v>
       </c>
       <c r="H420" t="n">
         <v>6000</v>
@@ -12607,7 +12607,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G422" t="n">
-        <v>1.80153977870941</v>
+        <v>1.80153965950012</v>
       </c>
       <c r="H422" t="n">
         <v>25500</v>
@@ -12665,7 +12665,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G424" t="n">
-        <v>1.77517592906952</v>
+        <v>1.77517580986023</v>
       </c>
       <c r="H424" t="n">
         <v>7500</v>
@@ -12752,7 +12752,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G427" t="n">
-        <v>1.76638793945312</v>
+        <v>1.76638782024384</v>
       </c>
       <c r="H427" t="n">
         <v>4500</v>
@@ -12781,7 +12781,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G428" t="n">
-        <v>1.76638793945312</v>
+        <v>1.76638782024384</v>
       </c>
       <c r="H428" t="n">
         <v>3000</v>
@@ -12810,7 +12810,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G429" t="n">
-        <v>1.76638793945312</v>
+        <v>1.76638782024384</v>
       </c>
       <c r="H429" t="n">
         <v>3000</v>
@@ -12839,7 +12839,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G430" t="n">
-        <v>1.76638793945312</v>
+        <v>1.76638782024384</v>
       </c>
       <c r="H430" t="n">
         <v>4500</v>
@@ -12868,7 +12868,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G431" t="n">
-        <v>1.84547972679138</v>
+        <v>1.84547960758209</v>
       </c>
       <c r="H431" t="n">
         <v>6000</v>
@@ -12897,7 +12897,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G432" t="n">
-        <v>1.77517592906952</v>
+        <v>1.77517580986023</v>
       </c>
       <c r="H432" t="n">
         <v>3000</v>
@@ -12926,7 +12926,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G433" t="n">
-        <v>1.86305582523346</v>
+        <v>1.86305558681488</v>
       </c>
       <c r="H433" t="n">
         <v>7500</v>
@@ -12955,7 +12955,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G434" t="n">
-        <v>1.86305582523346</v>
+        <v>1.86305558681488</v>
       </c>
       <c r="H434" t="n">
         <v>0</v>
@@ -12984,7 +12984,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G435" t="n">
-        <v>1.86305582523346</v>
+        <v>1.86305558681488</v>
       </c>
       <c r="H435" t="n">
         <v>3000</v>
@@ -13013,7 +13013,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G436" t="n">
-        <v>1.88063192367554</v>
+        <v>1.88063168525696</v>
       </c>
       <c r="H436" t="n">
         <v>3000</v>
@@ -13100,7 +13100,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G439" t="n">
-        <v>1.8191157579422</v>
+        <v>1.81911587715149</v>
       </c>
       <c r="H439" t="n">
         <v>6000</v>
@@ -13129,7 +13129,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G440" t="n">
-        <v>1.8191157579422</v>
+        <v>1.81911587715149</v>
       </c>
       <c r="H440" t="n">
         <v>0</v>
@@ -13158,7 +13158,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G441" t="n">
-        <v>1.88063192367554</v>
+        <v>1.88063168525696</v>
       </c>
       <c r="H441" t="n">
         <v>3000</v>
@@ -13187,7 +13187,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G442" t="n">
-        <v>1.88063192367554</v>
+        <v>1.88063168525696</v>
       </c>
       <c r="H442" t="n">
         <v>0</v>
@@ -13245,7 +13245,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G444" t="n">
-        <v>1.86305582523346</v>
+        <v>1.86305558681488</v>
       </c>
       <c r="H444" t="n">
         <v>1500</v>
@@ -13332,7 +13332,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G447" t="n">
-        <v>1.76638793945312</v>
+        <v>1.76638782024384</v>
       </c>
       <c r="H447" t="n">
         <v>15000</v>
@@ -13361,7 +13361,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G448" t="n">
-        <v>1.73562979698181</v>
+        <v>1.7356299161911</v>
       </c>
       <c r="H448" t="n">
         <v>3000</v>
@@ -13506,7 +13506,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G453" t="n">
-        <v>1.687295794487</v>
+        <v>1.68729567527771</v>
       </c>
       <c r="H453" t="n">
         <v>7500</v>
@@ -13535,7 +13535,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G454" t="n">
-        <v>1.63896179199219</v>
+        <v>1.63896191120148</v>
       </c>
       <c r="H454" t="n">
         <v>6000</v>
@@ -13796,7 +13796,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G463" t="n">
-        <v>1.66093194484711</v>
+        <v>1.66093182563782</v>
       </c>
       <c r="H463" t="n">
         <v>1500</v>
@@ -13825,7 +13825,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G464" t="n">
-        <v>1.66093194484711</v>
+        <v>1.66093182563782</v>
       </c>
       <c r="H464" t="n">
         <v>0</v>
@@ -13883,7 +13883,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G466" t="n">
-        <v>1.59941577911377</v>
+        <v>1.59941601753235</v>
       </c>
       <c r="H466" t="n">
         <v>6000</v>
@@ -13912,7 +13912,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G467" t="n">
-        <v>1.59502196311951</v>
+        <v>1.59502184391022</v>
       </c>
       <c r="H467" t="n">
         <v>3000</v>
@@ -13941,7 +13941,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G468" t="n">
-        <v>1.6697199344635</v>
+        <v>1.66971981525421</v>
       </c>
       <c r="H468" t="n">
         <v>4500</v>
@@ -13970,7 +13970,7 @@
         <v>1.875</v>
       </c>
       <c r="G469" t="n">
-        <v>1.64774978160858</v>
+        <v>1.64774990081787</v>
       </c>
       <c r="H469" t="n">
         <v>3000</v>
@@ -13999,7 +13999,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G470" t="n">
-        <v>1.66093194484711</v>
+        <v>1.66093182563782</v>
       </c>
       <c r="H470" t="n">
         <v>3000</v>
@@ -14028,7 +14028,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G471" t="n">
-        <v>1.59502196311951</v>
+        <v>1.59502184391022</v>
       </c>
       <c r="H471" t="n">
         <v>15000</v>
@@ -14057,7 +14057,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G472" t="n">
-        <v>1.64335572719574</v>
+        <v>1.64335584640503</v>
       </c>
       <c r="H472" t="n">
         <v>4500</v>
@@ -14086,7 +14086,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G473" t="n">
-        <v>1.64335572719574</v>
+        <v>1.64335584640503</v>
       </c>
       <c r="H473" t="n">
         <v>0</v>
@@ -14115,7 +14115,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G474" t="n">
-        <v>1.6697199344635</v>
+        <v>1.66971981525421</v>
       </c>
       <c r="H474" t="n">
         <v>3000</v>
@@ -14144,7 +14144,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G475" t="n">
-        <v>1.63456773757935</v>
+        <v>1.63456785678864</v>
       </c>
       <c r="H475" t="n">
         <v>3000</v>
@@ -14173,7 +14173,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G476" t="n">
-        <v>1.66532588005066</v>
+        <v>1.66532576084137</v>
       </c>
       <c r="H476" t="n">
         <v>1500</v>
@@ -14202,7 +14202,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G477" t="n">
-        <v>1.66532588005066</v>
+        <v>1.66532576084137</v>
       </c>
       <c r="H477" t="n">
         <v>0</v>
@@ -14231,7 +14231,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G478" t="n">
-        <v>1.66532588005066</v>
+        <v>1.66532576084137</v>
       </c>
       <c r="H478" t="n">
         <v>0</v>
@@ -14289,7 +14289,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G480" t="n">
-        <v>1.63017392158508</v>
+        <v>1.63017380237579</v>
       </c>
       <c r="H480" t="n">
         <v>3000</v>
@@ -14318,7 +14318,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G481" t="n">
-        <v>1.687295794487</v>
+        <v>1.68729567527771</v>
       </c>
       <c r="H481" t="n">
         <v>3000</v>
@@ -14376,7 +14376,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G483" t="n">
-        <v>1.64335572719574</v>
+        <v>1.64335584640503</v>
       </c>
       <c r="H483" t="n">
         <v>3000</v>
@@ -14405,7 +14405,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G484" t="n">
-        <v>1.74881172180176</v>
+        <v>1.74881196022034</v>
       </c>
       <c r="H484" t="n">
         <v>19500</v>
@@ -14463,7 +14463,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G486" t="n">
-        <v>1.87184381484985</v>
+        <v>1.87184405326843</v>
       </c>
       <c r="H486" t="n">
         <v>25500</v>
@@ -14492,7 +14492,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G487" t="n">
-        <v>1.93335962295532</v>
+        <v>1.93335998058319</v>
       </c>
       <c r="H487" t="n">
         <v>33000</v>
@@ -14637,7 +14637,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G492" t="n">
-        <v>1.99487578868866</v>
+        <v>1.99487566947937</v>
       </c>
       <c r="H492" t="n">
         <v>3000</v>
@@ -14753,7 +14753,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G496" t="n">
-        <v>1.93335962295532</v>
+        <v>1.93335998058319</v>
       </c>
       <c r="H496" t="n">
         <v>6000</v>
@@ -14811,7 +14811,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G498" t="n">
-        <v>1.73562979698181</v>
+        <v>1.7356299161911</v>
       </c>
       <c r="H498" t="n">
         <v>40500</v>
@@ -14927,7 +14927,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G502" t="n">
-        <v>1.74881172180176</v>
+        <v>1.74881196022034</v>
       </c>
       <c r="H502" t="n">
         <v>4500</v>
@@ -14956,7 +14956,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G503" t="n">
-        <v>1.74881172180176</v>
+        <v>1.74881196022034</v>
       </c>
       <c r="H503" t="n">
         <v>1500</v>
@@ -14985,7 +14985,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G504" t="n">
-        <v>1.74881172180176</v>
+        <v>1.74881196022034</v>
       </c>
       <c r="H504" t="n">
         <v>1500</v>
@@ -15014,7 +15014,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G505" t="n">
-        <v>1.77517592906952</v>
+        <v>1.77517580986023</v>
       </c>
       <c r="H505" t="n">
         <v>3000</v>
@@ -15043,7 +15043,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G506" t="n">
-        <v>1.77517592906952</v>
+        <v>1.77517580986023</v>
       </c>
       <c r="H506" t="n">
         <v>3000</v>
@@ -15159,7 +15159,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G510" t="n">
-        <v>1.77517592906952</v>
+        <v>1.77517580986023</v>
       </c>
       <c r="H510" t="n">
         <v>4500</v>
@@ -15333,7 +15333,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G516" t="n">
-        <v>1.71365976333618</v>
+        <v>1.71366000175476</v>
       </c>
       <c r="H516" t="n">
         <v>6000</v>
@@ -15362,7 +15362,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G517" t="n">
-        <v>1.71365976333618</v>
+        <v>1.71366000175476</v>
       </c>
       <c r="H517" t="n">
         <v>1500</v>
@@ -15391,7 +15391,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G518" t="n">
-        <v>1.71365976333618</v>
+        <v>1.71366000175476</v>
       </c>
       <c r="H518" t="n">
         <v>0</v>
@@ -15420,7 +15420,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G519" t="n">
-        <v>1.76638793945312</v>
+        <v>1.76638782024384</v>
       </c>
       <c r="H519" t="n">
         <v>3000</v>
@@ -15507,7 +15507,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G522" t="n">
-        <v>1.76638793945312</v>
+        <v>1.76638782024384</v>
       </c>
       <c r="H522" t="n">
         <v>9000</v>
@@ -15623,7 +15623,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G526" t="n">
-        <v>1.54229378700256</v>
+        <v>1.54229390621185</v>
       </c>
       <c r="H526" t="n">
         <v>19500</v>
@@ -15652,7 +15652,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G527" t="n">
-        <v>1.50274777412415</v>
+        <v>1.50274789333344</v>
       </c>
       <c r="H527" t="n">
         <v>25500</v>
@@ -15681,7 +15681,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G528" t="n">
-        <v>1.50274777412415</v>
+        <v>1.50274789333344</v>
       </c>
       <c r="H528" t="n">
         <v>9000</v>
@@ -15768,7 +15768,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G531" t="n">
-        <v>1.51592993736267</v>
+        <v>1.51592981815338</v>
       </c>
       <c r="H531" t="n">
         <v>1500</v>
@@ -15797,7 +15797,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G532" t="n">
-        <v>1.51592993736267</v>
+        <v>1.51592981815338</v>
       </c>
       <c r="H532" t="n">
         <v>0</v>
@@ -15826,7 +15826,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G533" t="n">
-        <v>1.51592993736267</v>
+        <v>1.51592981815338</v>
       </c>
       <c r="H533" t="n">
         <v>0</v>
@@ -15913,7 +15913,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G536" t="n">
-        <v>1.50274777412415</v>
+        <v>1.50274789333344</v>
       </c>
       <c r="H536" t="n">
         <v>6000</v>
@@ -15942,7 +15942,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G537" t="n">
-        <v>1.50274777412415</v>
+        <v>1.50274789333344</v>
       </c>
       <c r="H537" t="n">
         <v>0</v>
@@ -15971,7 +15971,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G538" t="n">
-        <v>1.55108189582825</v>
+        <v>1.55108177661896</v>
       </c>
       <c r="H538" t="n">
         <v>1500</v>
@@ -16000,7 +16000,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G539" t="n">
-        <v>1.55108189582825</v>
+        <v>1.55108177661896</v>
       </c>
       <c r="H539" t="n">
         <v>0</v>
@@ -16116,7 +16116,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G543" t="n">
-        <v>1.49395990371704</v>
+        <v>1.49395978450775</v>
       </c>
       <c r="H543" t="n">
         <v>1500</v>
@@ -16145,7 +16145,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G544" t="n">
-        <v>1.52911174297333</v>
+        <v>1.52911186218262</v>
       </c>
       <c r="H544" t="n">
         <v>1500</v>
@@ -16174,7 +16174,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G545" t="n">
-        <v>1.56426393985748</v>
+        <v>1.56426382064819</v>
       </c>
       <c r="H545" t="n">
         <v>4500</v>
@@ -16203,7 +16203,7 @@
         <v>1.875</v>
       </c>
       <c r="G546" t="n">
-        <v>1.64774978160858</v>
+        <v>1.64774990081787</v>
       </c>
       <c r="H546" t="n">
         <v>18000</v>
@@ -16232,7 +16232,7 @@
         <v>1.875</v>
       </c>
       <c r="G547" t="n">
-        <v>1.64774978160858</v>
+        <v>1.64774990081787</v>
       </c>
       <c r="H547" t="n">
         <v>0</v>
@@ -16493,7 +16493,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G556" t="n">
-        <v>1.6697199344635</v>
+        <v>1.66971981525421</v>
       </c>
       <c r="H556" t="n">
         <v>6000</v>
@@ -16522,7 +16522,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G557" t="n">
-        <v>1.6697199344635</v>
+        <v>1.66971981525421</v>
       </c>
       <c r="H557" t="n">
         <v>3000</v>
@@ -16928,7 +16928,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G571" t="n">
-        <v>1.66093194484711</v>
+        <v>1.66093182563782</v>
       </c>
       <c r="H571" t="n">
         <v>1500</v>
@@ -16986,7 +16986,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G573" t="n">
-        <v>1.6697199344635</v>
+        <v>1.66971981525421</v>
       </c>
       <c r="H573" t="n">
         <v>1500</v>
@@ -17015,7 +17015,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G574" t="n">
-        <v>1.6697199344635</v>
+        <v>1.66971981525421</v>
       </c>
       <c r="H574" t="n">
         <v>0</v>
@@ -17044,7 +17044,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G575" t="n">
-        <v>1.6697199344635</v>
+        <v>1.66971981525421</v>
       </c>
       <c r="H575" t="n">
         <v>0</v>
@@ -17073,7 +17073,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G576" t="n">
-        <v>1.6697199344635</v>
+        <v>1.66971981525421</v>
       </c>
       <c r="H576" t="n">
         <v>0</v>
@@ -17102,7 +17102,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G577" t="n">
-        <v>1.6697199344635</v>
+        <v>1.66971981525421</v>
       </c>
       <c r="H577" t="n">
         <v>0</v>
@@ -17218,7 +17218,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G581" t="n">
-        <v>1.687295794487</v>
+        <v>1.68729567527771</v>
       </c>
       <c r="H581" t="n">
         <v>1500</v>
@@ -17508,7 +17508,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G591" t="n">
-        <v>1.58623385429382</v>
+        <v>1.58623373508453</v>
       </c>
       <c r="H591" t="n">
         <v>9000</v>
@@ -17566,7 +17566,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G593" t="n">
-        <v>1.55547595024109</v>
+        <v>1.55547571182251</v>
       </c>
       <c r="H593" t="n">
         <v>13500</v>
@@ -17595,7 +17595,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G594" t="n">
-        <v>1.55987000465393</v>
+        <v>1.55986976623535</v>
       </c>
       <c r="H594" t="n">
         <v>15000</v>
@@ -17624,7 +17624,7 @@
         <v>1.875</v>
       </c>
       <c r="G595" t="n">
-        <v>1.64774978160858</v>
+        <v>1.64774990081787</v>
       </c>
       <c r="H595" t="n">
         <v>7500</v>
@@ -17653,7 +17653,7 @@
         <v>1.875</v>
       </c>
       <c r="G596" t="n">
-        <v>1.64774978160858</v>
+        <v>1.64774990081787</v>
       </c>
       <c r="H596" t="n">
         <v>0</v>
@@ -17711,7 +17711,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G598" t="n">
-        <v>1.63896179199219</v>
+        <v>1.63896191120148</v>
       </c>
       <c r="H598" t="n">
         <v>1500</v>
@@ -17740,7 +17740,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G599" t="n">
-        <v>1.63896179199219</v>
+        <v>1.63896191120148</v>
       </c>
       <c r="H599" t="n">
         <v>0</v>
@@ -17769,7 +17769,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G600" t="n">
-        <v>1.59941577911377</v>
+        <v>1.59941601753235</v>
       </c>
       <c r="H600" t="n">
         <v>3000</v>
@@ -17798,7 +17798,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G601" t="n">
-        <v>1.59941577911377</v>
+        <v>1.59941601753235</v>
       </c>
       <c r="H601" t="n">
         <v>0</v>
@@ -17827,7 +17827,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G602" t="n">
-        <v>1.59941577911377</v>
+        <v>1.59941601753235</v>
       </c>
       <c r="H602" t="n">
         <v>0</v>
@@ -17943,7 +17943,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G606" t="n">
-        <v>1.63896179199219</v>
+        <v>1.63896191120148</v>
       </c>
       <c r="H606" t="n">
         <v>3000</v>
@@ -18001,7 +18001,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G608" t="n">
-        <v>1.58183979988098</v>
+        <v>1.58183991909027</v>
       </c>
       <c r="H608" t="n">
         <v>12000</v>
@@ -18030,7 +18030,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G609" t="n">
-        <v>1.61259782314301</v>
+        <v>1.61259794235229</v>
       </c>
       <c r="H609" t="n">
         <v>1500</v>
@@ -18233,7 +18233,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G616" t="n">
-        <v>1.56865775585175</v>
+        <v>1.56865787506104</v>
       </c>
       <c r="H616" t="n">
         <v>7500</v>
@@ -18320,7 +18320,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G619" t="n">
-        <v>1.72244787216187</v>
+        <v>1.72244775295258</v>
       </c>
       <c r="H619" t="n">
         <v>10500</v>
@@ -18378,7 +18378,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G621" t="n">
-        <v>1.6697199344635</v>
+        <v>1.66971981525421</v>
       </c>
       <c r="H621" t="n">
         <v>7500</v>
@@ -18436,7 +18436,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G623" t="n">
-        <v>1.69608390331268</v>
+        <v>1.69608378410339</v>
       </c>
       <c r="H623" t="n">
         <v>1500</v>
@@ -18465,7 +18465,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G624" t="n">
-        <v>1.6697199344635</v>
+        <v>1.66971981525421</v>
       </c>
       <c r="H624" t="n">
         <v>4500</v>
@@ -18610,7 +18610,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G629" t="n">
-        <v>1.88063192367554</v>
+        <v>1.88063168525696</v>
       </c>
       <c r="H629" t="n">
         <v>39000</v>
@@ -18697,7 +18697,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G632" t="n">
-        <v>1.86305582523346</v>
+        <v>1.86305558681488</v>
       </c>
       <c r="H632" t="n">
         <v>33000</v>
@@ -18726,7 +18726,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G633" t="n">
-        <v>1.8191157579422</v>
+        <v>1.81911587715149</v>
       </c>
       <c r="H633" t="n">
         <v>4500</v>
@@ -18842,7 +18842,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G637" t="n">
-        <v>1.71365976333618</v>
+        <v>1.71366000175476</v>
       </c>
       <c r="H637" t="n">
         <v>24000</v>
@@ -18900,7 +18900,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G639" t="n">
-        <v>1.64335572719574</v>
+        <v>1.64335584640503</v>
       </c>
       <c r="H639" t="n">
         <v>19500</v>
@@ -19045,7 +19045,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G644" t="n">
-        <v>1.66093194484711</v>
+        <v>1.66093182563782</v>
       </c>
       <c r="H644" t="n">
         <v>9000</v>
@@ -19074,7 +19074,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G645" t="n">
-        <v>1.66093194484711</v>
+        <v>1.66093182563782</v>
       </c>
       <c r="H645" t="n">
         <v>0</v>
@@ -19132,7 +19132,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G647" t="n">
-        <v>1.66532588005066</v>
+        <v>1.66532576084137</v>
       </c>
       <c r="H647" t="n">
         <v>7500</v>
@@ -19161,7 +19161,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G648" t="n">
-        <v>1.69608390331268</v>
+        <v>1.69608378410339</v>
       </c>
       <c r="H648" t="n">
         <v>1500</v>
@@ -19219,7 +19219,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G650" t="n">
-        <v>1.74881172180176</v>
+        <v>1.74881196022034</v>
       </c>
       <c r="H650" t="n">
         <v>3000</v>
@@ -19248,7 +19248,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G651" t="n">
-        <v>1.71365976333618</v>
+        <v>1.71366000175476</v>
       </c>
       <c r="H651" t="n">
         <v>1500</v>
@@ -19422,7 +19422,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G657" t="n">
-        <v>1.70487177371979</v>
+        <v>1.70487201213837</v>
       </c>
       <c r="H657" t="n">
         <v>10500</v>
@@ -19538,7 +19538,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G661" t="n">
-        <v>1.78719854354858</v>
+        <v>1.78719866275787</v>
       </c>
       <c r="H661" t="n">
         <v>3000</v>
@@ -19567,7 +19567,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G662" t="n">
-        <v>1.7059623003006</v>
+        <v>1.70596218109131</v>
       </c>
       <c r="H662" t="n">
         <v>54000</v>
@@ -19596,7 +19596,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G663" t="n">
-        <v>1.7059623003006</v>
+        <v>1.70596218109131</v>
       </c>
       <c r="H663" t="n">
         <v>6000</v>
@@ -19654,7 +19654,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G665" t="n">
-        <v>1.67888355255127</v>
+        <v>1.67888343334198</v>
       </c>
       <c r="H665" t="n">
         <v>13500</v>
@@ -19683,7 +19683,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G666" t="n">
-        <v>1.73304104804993</v>
+        <v>1.73304092884064</v>
       </c>
       <c r="H666" t="n">
         <v>9000</v>
@@ -19712,7 +19712,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G667" t="n">
-        <v>1.7059623003006</v>
+        <v>1.70596218109131</v>
       </c>
       <c r="H667" t="n">
         <v>7500</v>
@@ -19741,7 +19741,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G668" t="n">
-        <v>1.67888355255127</v>
+        <v>1.67888343334198</v>
       </c>
       <c r="H668" t="n">
         <v>4500</v>
@@ -19770,7 +19770,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G669" t="n">
-        <v>1.66985738277435</v>
+        <v>1.66985726356506</v>
       </c>
       <c r="H669" t="n">
         <v>3000</v>
@@ -19828,7 +19828,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G671" t="n">
-        <v>1.63375210762024</v>
+        <v>1.63375222682953</v>
       </c>
       <c r="H671" t="n">
         <v>1500</v>
@@ -19857,7 +19857,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G672" t="n">
-        <v>1.63375210762024</v>
+        <v>1.63375222682953</v>
       </c>
       <c r="H672" t="n">
         <v>0</v>
@@ -19886,7 +19886,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G673" t="n">
-        <v>1.64277851581573</v>
+        <v>1.64277863502502</v>
       </c>
       <c r="H673" t="n">
         <v>4500</v>
@@ -19915,7 +19915,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G674" t="n">
-        <v>1.64277851581573</v>
+        <v>1.64277863502502</v>
       </c>
       <c r="H674" t="n">
         <v>0</v>
@@ -19944,7 +19944,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G675" t="n">
-        <v>1.64277851581573</v>
+        <v>1.64277863502502</v>
       </c>
       <c r="H675" t="n">
         <v>0</v>
@@ -19973,7 +19973,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G676" t="n">
-        <v>1.64277851581573</v>
+        <v>1.64277863502502</v>
       </c>
       <c r="H676" t="n">
         <v>0</v>
@@ -20002,7 +20002,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G677" t="n">
-        <v>1.60667335987091</v>
+        <v>1.6066734790802</v>
       </c>
       <c r="H677" t="n">
         <v>4500</v>
@@ -20031,7 +20031,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G678" t="n">
-        <v>1.60667335987091</v>
+        <v>1.6066734790802</v>
       </c>
       <c r="H678" t="n">
         <v>1500</v>
@@ -20060,7 +20060,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G679" t="n">
-        <v>1.63375210762024</v>
+        <v>1.63375222682953</v>
       </c>
       <c r="H679" t="n">
         <v>1500</v>
@@ -20089,7 +20089,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G680" t="n">
-        <v>1.63375210762024</v>
+        <v>1.63375222682953</v>
       </c>
       <c r="H680" t="n">
         <v>0</v>
@@ -20205,7 +20205,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G684" t="n">
-        <v>1.59764719009399</v>
+        <v>1.5976470708847</v>
       </c>
       <c r="H684" t="n">
         <v>1500</v>
@@ -20234,7 +20234,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G685" t="n">
-        <v>1.60667335987091</v>
+        <v>1.6066734790802</v>
       </c>
       <c r="H685" t="n">
         <v>7500</v>
@@ -20263,7 +20263,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G686" t="n">
-        <v>1.60667335987091</v>
+        <v>1.6066734790802</v>
       </c>
       <c r="H686" t="n">
         <v>0</v>
@@ -20292,7 +20292,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G687" t="n">
-        <v>1.60667335987091</v>
+        <v>1.6066734790802</v>
       </c>
       <c r="H687" t="n">
         <v>0</v>
@@ -20321,7 +20321,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G688" t="n">
-        <v>1.60667335987091</v>
+        <v>1.6066734790802</v>
       </c>
       <c r="H688" t="n">
         <v>4500</v>
@@ -20350,7 +20350,7 @@
         <v>1.75</v>
       </c>
       <c r="G689" t="n">
-        <v>1.57959473133087</v>
+        <v>1.57959461212158</v>
       </c>
       <c r="H689" t="n">
         <v>4500</v>
@@ -20379,7 +20379,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G690" t="n">
-        <v>1.60667335987091</v>
+        <v>1.6066734790802</v>
       </c>
       <c r="H690" t="n">
         <v>3000</v>
@@ -20408,7 +20408,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G691" t="n">
-        <v>1.60667335987091</v>
+        <v>1.6066734790802</v>
       </c>
       <c r="H691" t="n">
         <v>0</v>
@@ -20437,7 +20437,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G692" t="n">
-        <v>1.61569964885712</v>
+        <v>1.61569976806641</v>
       </c>
       <c r="H692" t="n">
         <v>4500</v>
@@ -20466,7 +20466,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G693" t="n">
-        <v>1.61569964885712</v>
+        <v>1.61569976806641</v>
       </c>
       <c r="H693" t="n">
         <v>0</v>
@@ -20495,7 +20495,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G694" t="n">
-        <v>1.61569964885712</v>
+        <v>1.61569976806641</v>
       </c>
       <c r="H694" t="n">
         <v>0</v>
@@ -20553,7 +20553,7 @@
         <v>1.75</v>
       </c>
       <c r="G696" t="n">
-        <v>1.57959473133087</v>
+        <v>1.57959461212158</v>
       </c>
       <c r="H696" t="n">
         <v>6000</v>
@@ -20698,7 +20698,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G701" t="n">
-        <v>1.59764719009399</v>
+        <v>1.5976470708847</v>
       </c>
       <c r="H701" t="n">
         <v>1500</v>
@@ -20727,7 +20727,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G702" t="n">
-        <v>1.59764719009399</v>
+        <v>1.5976470708847</v>
       </c>
       <c r="H702" t="n">
         <v>3000</v>
@@ -20756,7 +20756,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G703" t="n">
-        <v>1.59764719009399</v>
+        <v>1.5976470708847</v>
       </c>
       <c r="H703" t="n">
         <v>4500</v>
@@ -20785,7 +20785,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G704" t="n">
-        <v>1.59764719009399</v>
+        <v>1.5976470708847</v>
       </c>
       <c r="H704" t="n">
         <v>0</v>
@@ -20843,7 +20843,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G706" t="n">
-        <v>1.59764719009399</v>
+        <v>1.5976470708847</v>
       </c>
       <c r="H706" t="n">
         <v>7500</v>
@@ -20959,7 +20959,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G710" t="n">
-        <v>1.51641094684601</v>
+        <v>1.51641082763672</v>
       </c>
       <c r="H710" t="n">
         <v>13500</v>
@@ -21133,7 +21133,7 @@
         <v>1.75</v>
       </c>
       <c r="G716" t="n">
-        <v>1.57959473133087</v>
+        <v>1.57959461212158</v>
       </c>
       <c r="H716" t="n">
         <v>4500</v>
@@ -21162,7 +21162,7 @@
         <v>1.75</v>
       </c>
       <c r="G717" t="n">
-        <v>1.57959473133087</v>
+        <v>1.57959461212158</v>
       </c>
       <c r="H717" t="n">
         <v>0</v>
@@ -21510,7 +21510,7 @@
         <v>1.75</v>
       </c>
       <c r="G729" t="n">
-        <v>1.57959473133087</v>
+        <v>1.57959461212158</v>
       </c>
       <c r="H729" t="n">
         <v>1500</v>
@@ -21539,7 +21539,7 @@
         <v>1.75</v>
       </c>
       <c r="G730" t="n">
-        <v>1.57959473133087</v>
+        <v>1.57959461212158</v>
       </c>
       <c r="H730" t="n">
         <v>7500</v>
@@ -22264,7 +22264,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G755" t="n">
-        <v>1.44420075416565</v>
+        <v>1.44420087337494</v>
       </c>
       <c r="H755" t="n">
         <v>1500</v>
@@ -22293,7 +22293,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G756" t="n">
-        <v>1.51641094684601</v>
+        <v>1.51641082763672</v>
       </c>
       <c r="H756" t="n">
         <v>4500</v>
@@ -22554,7 +22554,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G765" t="n">
-        <v>1.51641094684601</v>
+        <v>1.51641082763672</v>
       </c>
       <c r="H765" t="n">
         <v>1500</v>
@@ -22641,7 +22641,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G768" t="n">
-        <v>1.51641094684601</v>
+        <v>1.51641082763672</v>
       </c>
       <c r="H768" t="n">
         <v>3000</v>
@@ -22699,7 +22699,7 @@
         <v>1.75</v>
       </c>
       <c r="G770" t="n">
-        <v>1.57959473133087</v>
+        <v>1.57959461212158</v>
       </c>
       <c r="H770" t="n">
         <v>6000</v>
@@ -22728,7 +22728,7 @@
         <v>1.75</v>
       </c>
       <c r="G771" t="n">
-        <v>1.57959473133087</v>
+        <v>1.57959461212158</v>
       </c>
       <c r="H771" t="n">
         <v>0</v>
@@ -22757,7 +22757,7 @@
         <v>1.75</v>
       </c>
       <c r="G772" t="n">
-        <v>1.57959473133087</v>
+        <v>1.57959461212158</v>
       </c>
       <c r="H772" t="n">
         <v>0</v>
@@ -22873,7 +22873,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G776" t="n">
-        <v>1.51641094684601</v>
+        <v>1.51641082763672</v>
       </c>
       <c r="H776" t="n">
         <v>3000</v>
@@ -22902,7 +22902,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G777" t="n">
-        <v>1.51641094684601</v>
+        <v>1.51641082763672</v>
       </c>
       <c r="H777" t="n">
         <v>0</v>
@@ -23134,7 +23134,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G785" t="n">
-        <v>1.51641094684601</v>
+        <v>1.51641082763672</v>
       </c>
       <c r="H785" t="n">
         <v>1500</v>
@@ -23163,7 +23163,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G786" t="n">
-        <v>1.51641094684601</v>
+        <v>1.51641082763672</v>
       </c>
       <c r="H786" t="n">
         <v>3000</v>
@@ -23192,7 +23192,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G787" t="n">
-        <v>1.51641094684601</v>
+        <v>1.51641082763672</v>
       </c>
       <c r="H787" t="n">
         <v>0</v>
@@ -23395,7 +23395,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G794" t="n">
-        <v>1.98577618598938</v>
+        <v>1.98577630519867</v>
       </c>
       <c r="H794" t="n">
         <v>370500</v>
@@ -23424,7 +23424,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G795" t="n">
-        <v>1.87746107578278</v>
+        <v>1.87746095657349</v>
       </c>
       <c r="H795" t="n">
         <v>319500</v>
@@ -23453,7 +23453,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G796" t="n">
-        <v>1.66985738277435</v>
+        <v>1.66985726356506</v>
       </c>
       <c r="H796" t="n">
         <v>94500</v>
@@ -23540,7 +23540,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G799" t="n">
-        <v>1.77817225456238</v>
+        <v>1.77817237377167</v>
       </c>
       <c r="H799" t="n">
         <v>24000</v>
@@ -23598,7 +23598,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G801" t="n">
-        <v>1.78719854354858</v>
+        <v>1.78719866275787</v>
       </c>
       <c r="H801" t="n">
         <v>30000</v>
@@ -23627,7 +23627,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G802" t="n">
-        <v>1.84135615825653</v>
+        <v>1.84135603904724</v>
       </c>
       <c r="H802" t="n">
         <v>37500</v>
@@ -23656,7 +23656,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G803" t="n">
-        <v>1.93161880970001</v>
+        <v>1.93161857128143</v>
       </c>
       <c r="H803" t="n">
         <v>73500</v>
@@ -23685,7 +23685,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G804" t="n">
-        <v>1.87746107578278</v>
+        <v>1.87746095657349</v>
       </c>
       <c r="H804" t="n">
         <v>46500</v>
@@ -23714,7 +23714,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G805" t="n">
-        <v>1.85940861701965</v>
+        <v>1.85940849781036</v>
       </c>
       <c r="H805" t="n">
         <v>4500</v>
@@ -23772,7 +23772,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G807" t="n">
-        <v>1.85940861701965</v>
+        <v>1.85940849781036</v>
       </c>
       <c r="H807" t="n">
         <v>7500</v>
@@ -23801,7 +23801,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G808" t="n">
-        <v>1.87746107578278</v>
+        <v>1.87746095657349</v>
       </c>
       <c r="H808" t="n">
         <v>10500</v>
@@ -23830,7 +23830,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G809" t="n">
-        <v>1.85940861701965</v>
+        <v>1.85940849781036</v>
       </c>
       <c r="H809" t="n">
         <v>1500</v>
@@ -23859,7 +23859,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G810" t="n">
-        <v>1.85940861701965</v>
+        <v>1.85940849781036</v>
       </c>
       <c r="H810" t="n">
         <v>1500</v>
@@ -23888,7 +23888,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G811" t="n">
-        <v>1.84135615825653</v>
+        <v>1.84135603904724</v>
       </c>
       <c r="H811" t="n">
         <v>6000</v>
@@ -23917,7 +23917,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G812" t="n">
-        <v>1.87746107578278</v>
+        <v>1.87746095657349</v>
       </c>
       <c r="H812" t="n">
         <v>6000</v>
@@ -23946,7 +23946,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G813" t="n">
-        <v>1.91356611251831</v>
+        <v>1.91356599330902</v>
       </c>
       <c r="H813" t="n">
         <v>3000</v>
@@ -23975,7 +23975,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G814" t="n">
-        <v>1.87746107578278</v>
+        <v>1.87746095657349</v>
       </c>
       <c r="H814" t="n">
         <v>7500</v>
@@ -24091,7 +24091,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G818" t="n">
-        <v>1.7059623003006</v>
+        <v>1.70596218109131</v>
       </c>
       <c r="H818" t="n">
         <v>55500</v>
@@ -24120,7 +24120,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G819" t="n">
-        <v>1.76914608478546</v>
+        <v>1.76914620399475</v>
       </c>
       <c r="H819" t="n">
         <v>12000</v>
@@ -24149,7 +24149,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G820" t="n">
-        <v>1.76914608478546</v>
+        <v>1.76914620399475</v>
       </c>
       <c r="H820" t="n">
         <v>0</v>
@@ -24178,7 +24178,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G821" t="n">
-        <v>1.73304104804993</v>
+        <v>1.73304092884064</v>
       </c>
       <c r="H821" t="n">
         <v>7500</v>
@@ -24207,7 +24207,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G822" t="n">
-        <v>1.77817225456238</v>
+        <v>1.77817237377167</v>
       </c>
       <c r="H822" t="n">
         <v>10500</v>
@@ -24236,7 +24236,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G823" t="n">
-        <v>1.84135615825653</v>
+        <v>1.84135603904724</v>
       </c>
       <c r="H823" t="n">
         <v>15000</v>
@@ -24352,7 +24352,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G827" t="n">
-        <v>1.73304104804993</v>
+        <v>1.73304092884064</v>
       </c>
       <c r="H827" t="n">
         <v>10500</v>
@@ -24497,7 +24497,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G832" t="n">
-        <v>1.77817225456238</v>
+        <v>1.77817237377167</v>
       </c>
       <c r="H832" t="n">
         <v>7500</v>
@@ -24526,7 +24526,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G833" t="n">
-        <v>1.74206721782684</v>
+        <v>1.74206733703613</v>
       </c>
       <c r="H833" t="n">
         <v>6000</v>
@@ -24555,7 +24555,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G834" t="n">
-        <v>1.73304104804993</v>
+        <v>1.73304092884064</v>
       </c>
       <c r="H834" t="n">
         <v>1500</v>
@@ -24584,7 +24584,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G835" t="n">
-        <v>1.76914608478546</v>
+        <v>1.76914620399475</v>
       </c>
       <c r="H835" t="n">
         <v>7500</v>
@@ -24642,7 +24642,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G837" t="n">
-        <v>1.77817225456238</v>
+        <v>1.77817237377167</v>
       </c>
       <c r="H837" t="n">
         <v>13500</v>
@@ -24671,7 +24671,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G838" t="n">
-        <v>1.74206721782684</v>
+        <v>1.74206733703613</v>
       </c>
       <c r="H838" t="n">
         <v>10500</v>
@@ -24700,7 +24700,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G839" t="n">
-        <v>1.74206721782684</v>
+        <v>1.74206733703613</v>
       </c>
       <c r="H839" t="n">
         <v>0</v>
@@ -24729,7 +24729,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G840" t="n">
-        <v>1.78719854354858</v>
+        <v>1.78719866275787</v>
       </c>
       <c r="H840" t="n">
         <v>15000</v>
@@ -24758,7 +24758,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G841" t="n">
-        <v>1.78719854354858</v>
+        <v>1.78719866275787</v>
       </c>
       <c r="H841" t="n">
         <v>1500</v>
@@ -25019,7 +25019,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G850" t="n">
-        <v>1.77817225456238</v>
+        <v>1.77817237377167</v>
       </c>
       <c r="H850" t="n">
         <v>4500</v>
@@ -25048,7 +25048,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G851" t="n">
-        <v>1.73304104804993</v>
+        <v>1.73304092884064</v>
       </c>
       <c r="H851" t="n">
         <v>16500</v>
@@ -25077,7 +25077,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G852" t="n">
-        <v>1.77817225456238</v>
+        <v>1.77817237377167</v>
       </c>
       <c r="H852" t="n">
         <v>10500</v>
@@ -25106,7 +25106,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G853" t="n">
-        <v>1.77817225456238</v>
+        <v>1.77817237377167</v>
       </c>
       <c r="H853" t="n">
         <v>3000</v>
@@ -25135,7 +25135,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G854" t="n">
-        <v>1.76914608478546</v>
+        <v>1.76914620399475</v>
       </c>
       <c r="H854" t="n">
         <v>1500</v>
@@ -25222,7 +25222,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G857" t="n">
-        <v>1.78719854354858</v>
+        <v>1.78719866275787</v>
       </c>
       <c r="H857" t="n">
         <v>6000</v>
@@ -25251,7 +25251,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G858" t="n">
-        <v>1.78719854354858</v>
+        <v>1.78719866275787</v>
       </c>
       <c r="H858" t="n">
         <v>0</v>
@@ -25309,7 +25309,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G860" t="n">
-        <v>1.78719854354858</v>
+        <v>1.78719866275787</v>
       </c>
       <c r="H860" t="n">
         <v>6000</v>
@@ -25367,7 +25367,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G862" t="n">
-        <v>1.78719854354858</v>
+        <v>1.78719866275787</v>
       </c>
       <c r="H862" t="n">
         <v>4500</v>
@@ -25454,7 +25454,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G865" t="n">
-        <v>1.84135615825653</v>
+        <v>1.84135603904724</v>
       </c>
       <c r="H865" t="n">
         <v>48000</v>
@@ -25483,7 +25483,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G866" t="n">
-        <v>1.87746107578278</v>
+        <v>1.87746095657349</v>
       </c>
       <c r="H866" t="n">
         <v>7500</v>
@@ -25512,7 +25512,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G867" t="n">
-        <v>1.91356611251831</v>
+        <v>1.91356599330902</v>
       </c>
       <c r="H867" t="n">
         <v>21000</v>
@@ -25541,7 +25541,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G868" t="n">
-        <v>1.98577618598938</v>
+        <v>1.98577630519867</v>
       </c>
       <c r="H868" t="n">
         <v>57000</v>
@@ -25570,7 +25570,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G869" t="n">
-        <v>1.98577618598938</v>
+        <v>1.98577630519867</v>
       </c>
       <c r="H869" t="n">
         <v>42000</v>
@@ -25715,7 +25715,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G874" t="n">
-        <v>1.98577618598938</v>
+        <v>1.98577630519867</v>
       </c>
       <c r="H874" t="n">
         <v>33000</v>
@@ -25802,7 +25802,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G877" t="n">
-        <v>1.94967114925385</v>
+        <v>1.94967126846313</v>
       </c>
       <c r="H877" t="n">
         <v>10500</v>
@@ -25831,7 +25831,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G878" t="n">
-        <v>1.93161880970001</v>
+        <v>1.93161857128143</v>
       </c>
       <c r="H878" t="n">
         <v>12000</v>
@@ -25860,7 +25860,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G879" t="n">
-        <v>1.94967114925385</v>
+        <v>1.94967126846313</v>
       </c>
       <c r="H879" t="n">
         <v>22500</v>
@@ -25889,7 +25889,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G880" t="n">
-        <v>1.94967114925385</v>
+        <v>1.94967126846313</v>
       </c>
       <c r="H880" t="n">
         <v>1500</v>
@@ -25918,7 +25918,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G881" t="n">
-        <v>1.94967114925385</v>
+        <v>1.94967126846313</v>
       </c>
       <c r="H881" t="n">
         <v>9000</v>
@@ -25947,7 +25947,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G882" t="n">
-        <v>1.94967114925385</v>
+        <v>1.94967126846313</v>
       </c>
       <c r="H882" t="n">
         <v>7500</v>
@@ -25976,7 +25976,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G883" t="n">
-        <v>1.98577618598938</v>
+        <v>1.98577630519867</v>
       </c>
       <c r="H883" t="n">
         <v>13500</v>
@@ -26034,7 +26034,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G885" t="n">
-        <v>2.20240616798401</v>
+        <v>2.20240640640259</v>
       </c>
       <c r="H885" t="n">
         <v>234000</v>
@@ -26063,7 +26063,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G886" t="n">
-        <v>2.16630148887634</v>
+        <v>2.16630125045776</v>
       </c>
       <c r="H886" t="n">
         <v>43500</v>
@@ -26092,7 +26092,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G887" t="n">
-        <v>2.16630148887634</v>
+        <v>2.16630125045776</v>
       </c>
       <c r="H887" t="n">
         <v>31500</v>
@@ -26121,7 +26121,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G888" t="n">
-        <v>2.16630148887634</v>
+        <v>2.16630125045776</v>
       </c>
       <c r="H888" t="n">
         <v>51000</v>
@@ -26150,7 +26150,7 @@
         <v>2.5</v>
       </c>
       <c r="G889" t="n">
-        <v>2.25656414031982</v>
+        <v>2.25656390190125</v>
       </c>
       <c r="H889" t="n">
         <v>96000</v>
@@ -26179,7 +26179,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G890" t="n">
-        <v>2.20240616798401</v>
+        <v>2.20240640640259</v>
       </c>
       <c r="H890" t="n">
         <v>79500</v>
@@ -26324,7 +26324,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G895" t="n">
-        <v>1.85940861701965</v>
+        <v>1.85940849781036</v>
       </c>
       <c r="H895" t="n">
         <v>126000</v>
@@ -26353,7 +26353,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G896" t="n">
-        <v>1.94967114925385</v>
+        <v>1.94967126846313</v>
       </c>
       <c r="H896" t="n">
         <v>33000</v>
@@ -26382,7 +26382,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G897" t="n">
-        <v>1.91356611251831</v>
+        <v>1.91356599330902</v>
       </c>
       <c r="H897" t="n">
         <v>54000</v>
@@ -26411,7 +26411,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G898" t="n">
-        <v>1.87746107578278</v>
+        <v>1.87746095657349</v>
       </c>
       <c r="H898" t="n">
         <v>15000</v>
@@ -26440,7 +26440,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G899" t="n">
-        <v>1.85940861701965</v>
+        <v>1.85940849781036</v>
       </c>
       <c r="H899" t="n">
         <v>16500</v>
@@ -26469,7 +26469,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G900" t="n">
-        <v>1.87746107578278</v>
+        <v>1.87746095657349</v>
       </c>
       <c r="H900" t="n">
         <v>12000</v>
@@ -26498,7 +26498,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G901" t="n">
-        <v>1.85940861701965</v>
+        <v>1.85940849781036</v>
       </c>
       <c r="H901" t="n">
         <v>4500</v>
@@ -26527,7 +26527,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G902" t="n">
-        <v>1.93161880970001</v>
+        <v>1.93161857128143</v>
       </c>
       <c r="H902" t="n">
         <v>9000</v>
@@ -26556,7 +26556,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G903" t="n">
-        <v>1.91356611251831</v>
+        <v>1.91356599330902</v>
       </c>
       <c r="H903" t="n">
         <v>4500</v>
@@ -26585,7 +26585,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G904" t="n">
-        <v>1.93161880970001</v>
+        <v>1.93161857128143</v>
       </c>
       <c r="H904" t="n">
         <v>9000</v>
@@ -26614,7 +26614,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G905" t="n">
-        <v>1.94967114925385</v>
+        <v>1.94967126846313</v>
       </c>
       <c r="H905" t="n">
         <v>15000</v>
@@ -26643,7 +26643,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G906" t="n">
-        <v>1.91356611251831</v>
+        <v>1.91356599330902</v>
       </c>
       <c r="H906" t="n">
         <v>7500</v>
@@ -26672,7 +26672,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G907" t="n">
-        <v>1.93161880970001</v>
+        <v>1.93161857128143</v>
       </c>
       <c r="H907" t="n">
         <v>1500</v>
@@ -26701,7 +26701,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G908" t="n">
-        <v>1.93161880970001</v>
+        <v>1.93161857128143</v>
       </c>
       <c r="H908" t="n">
         <v>0</v>
@@ -26730,7 +26730,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G909" t="n">
-        <v>1.85940861701965</v>
+        <v>1.85940849781036</v>
       </c>
       <c r="H909" t="n">
         <v>111000</v>
@@ -26759,7 +26759,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G910" t="n">
-        <v>1.84135615825653</v>
+        <v>1.84135603904724</v>
       </c>
       <c r="H910" t="n">
         <v>21000</v>
@@ -26788,7 +26788,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G911" t="n">
-        <v>1.87746107578278</v>
+        <v>1.87746095657349</v>
       </c>
       <c r="H911" t="n">
         <v>9000</v>
@@ -26817,7 +26817,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G912" t="n">
-        <v>1.85940861701965</v>
+        <v>1.85940849781036</v>
       </c>
       <c r="H912" t="n">
         <v>15000</v>
@@ -26846,7 +26846,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G913" t="n">
-        <v>1.85940861701965</v>
+        <v>1.85940849781036</v>
       </c>
       <c r="H913" t="n">
         <v>6000</v>
@@ -26904,7 +26904,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G915" t="n">
-        <v>1.87746107578278</v>
+        <v>1.87746095657349</v>
       </c>
       <c r="H915" t="n">
         <v>10500</v>
@@ -26933,7 +26933,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G916" t="n">
-        <v>1.87746107578278</v>
+        <v>1.87746095657349</v>
       </c>
       <c r="H916" t="n">
         <v>1500</v>
@@ -26962,7 +26962,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G917" t="n">
-        <v>1.85940861701965</v>
+        <v>1.85940849781036</v>
       </c>
       <c r="H917" t="n">
         <v>13500</v>
@@ -27049,7 +27049,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G920" t="n">
-        <v>1.89470207691193</v>
+        <v>1.89470195770264</v>
       </c>
       <c r="H920" t="n">
         <v>4500</v>
@@ -27078,7 +27078,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G921" t="n">
-        <v>1.89470207691193</v>
+        <v>1.89470195770264</v>
       </c>
       <c r="H921" t="n">
         <v>0</v>
@@ -27107,7 +27107,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G922" t="n">
-        <v>1.89470207691193</v>
+        <v>1.89470195770264</v>
       </c>
       <c r="H922" t="n">
         <v>15000</v>
@@ -27136,7 +27136,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G923" t="n">
-        <v>1.82968771457672</v>
+        <v>1.82968783378601</v>
       </c>
       <c r="H923" t="n">
         <v>28500</v>
@@ -27165,7 +27165,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G924" t="n">
-        <v>1.77396130561829</v>
+        <v>1.773961186409</v>
       </c>
       <c r="H924" t="n">
         <v>147000</v>
@@ -27223,7 +27223,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G926" t="n">
-        <v>1.81111228466034</v>
+        <v>1.81111240386963</v>
       </c>
       <c r="H926" t="n">
         <v>6000</v>
@@ -27252,7 +27252,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G927" t="n">
-        <v>1.81111228466034</v>
+        <v>1.81111240386963</v>
       </c>
       <c r="H927" t="n">
         <v>4500</v>
@@ -27281,7 +27281,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G928" t="n">
-        <v>1.81111228466034</v>
+        <v>1.81111240386963</v>
       </c>
       <c r="H928" t="n">
         <v>1500</v>
@@ -27513,7 +27513,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G936" t="n">
-        <v>1.81111228466034</v>
+        <v>1.81111240386963</v>
       </c>
       <c r="H936" t="n">
         <v>7500</v>
@@ -27542,7 +27542,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G937" t="n">
-        <v>1.81111228466034</v>
+        <v>1.81111240386963</v>
       </c>
       <c r="H937" t="n">
         <v>1500</v>
@@ -27629,7 +27629,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G940" t="n">
-        <v>1.78324902057648</v>
+        <v>1.78324890136719</v>
       </c>
       <c r="H940" t="n">
         <v>3000</v>
@@ -27658,7 +27658,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G941" t="n">
-        <v>1.78324902057648</v>
+        <v>1.78324890136719</v>
       </c>
       <c r="H941" t="n">
         <v>6000</v>
@@ -27716,7 +27716,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G943" t="n">
-        <v>1.81111228466034</v>
+        <v>1.81111240386963</v>
       </c>
       <c r="H943" t="n">
         <v>3000</v>
@@ -27745,7 +27745,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G944" t="n">
-        <v>1.77396130561829</v>
+        <v>1.773961186409</v>
       </c>
       <c r="H944" t="n">
         <v>27000</v>
@@ -27774,7 +27774,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G945" t="n">
-        <v>1.77396130561829</v>
+        <v>1.773961186409</v>
       </c>
       <c r="H945" t="n">
         <v>3000</v>
@@ -27803,7 +27803,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G946" t="n">
-        <v>1.77396130561829</v>
+        <v>1.773961186409</v>
       </c>
       <c r="H946" t="n">
         <v>0</v>
@@ -27832,7 +27832,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G947" t="n">
-        <v>1.78324902057648</v>
+        <v>1.78324890136719</v>
       </c>
       <c r="H947" t="n">
         <v>4500</v>
@@ -27919,7 +27919,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G950" t="n">
-        <v>1.78324902057648</v>
+        <v>1.78324890136719</v>
       </c>
       <c r="H950" t="n">
         <v>6000</v>
@@ -27948,7 +27948,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G951" t="n">
-        <v>1.78324902057648</v>
+        <v>1.78324890136719</v>
       </c>
       <c r="H951" t="n">
         <v>1500</v>
@@ -28122,7 +28122,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G957" t="n">
-        <v>1.78324902057648</v>
+        <v>1.78324890136719</v>
       </c>
       <c r="H957" t="n">
         <v>3000</v>
@@ -28151,7 +28151,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G958" t="n">
-        <v>1.78324902057648</v>
+        <v>1.78324890136719</v>
       </c>
       <c r="H958" t="n">
         <v>1500</v>
@@ -28180,7 +28180,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G959" t="n">
-        <v>1.78324902057648</v>
+        <v>1.78324890136719</v>
       </c>
       <c r="H959" t="n">
         <v>1500</v>
@@ -28209,7 +28209,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G960" t="n">
-        <v>1.75538575649261</v>
+        <v>1.75538563728333</v>
       </c>
       <c r="H960" t="n">
         <v>9000</v>
@@ -28238,7 +28238,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G961" t="n">
-        <v>1.78324902057648</v>
+        <v>1.78324890136719</v>
       </c>
       <c r="H961" t="n">
         <v>4500</v>
@@ -28354,7 +28354,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G965" t="n">
-        <v>1.78324902057648</v>
+        <v>1.78324890136719</v>
       </c>
       <c r="H965" t="n">
         <v>13500</v>
@@ -28383,7 +28383,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G966" t="n">
-        <v>1.78324902057648</v>
+        <v>1.78324890136719</v>
       </c>
       <c r="H966" t="n">
         <v>4500</v>
@@ -28615,7 +28615,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G974" t="n">
-        <v>1.82039999961853</v>
+        <v>1.82040011882782</v>
       </c>
       <c r="H974" t="n">
         <v>13500</v>
@@ -28644,7 +28644,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G975" t="n">
-        <v>1.82039999961853</v>
+        <v>1.82040011882782</v>
       </c>
       <c r="H975" t="n">
         <v>0</v>
@@ -28673,7 +28673,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G976" t="n">
-        <v>1.82039999961853</v>
+        <v>1.82040011882782</v>
       </c>
       <c r="H976" t="n">
         <v>0</v>
@@ -28702,7 +28702,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G977" t="n">
-        <v>1.77396130561829</v>
+        <v>1.773961186409</v>
       </c>
       <c r="H977" t="n">
         <v>16500</v>
@@ -28818,7 +28818,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G981" t="n">
-        <v>1.78324902057648</v>
+        <v>1.78324890136719</v>
       </c>
       <c r="H981" t="n">
         <v>1500</v>
@@ -28847,7 +28847,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G982" t="n">
-        <v>1.78324902057648</v>
+        <v>1.78324890136719</v>
       </c>
       <c r="H982" t="n">
         <v>0</v>
@@ -28876,7 +28876,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G983" t="n">
-        <v>1.78324902057648</v>
+        <v>1.78324890136719</v>
       </c>
       <c r="H983" t="n">
         <v>0</v>
@@ -28934,7 +28934,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G985" t="n">
-        <v>1.78324902057648</v>
+        <v>1.78324890136719</v>
       </c>
       <c r="H985" t="n">
         <v>15000</v>
@@ -28992,7 +28992,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G987" t="n">
-        <v>1.81111228466034</v>
+        <v>1.81111240386963</v>
       </c>
       <c r="H987" t="n">
         <v>40500</v>
@@ -29021,7 +29021,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G988" t="n">
-        <v>1.82039999961853</v>
+        <v>1.82040011882782</v>
       </c>
       <c r="H988" t="n">
         <v>3000</v>
@@ -29050,7 +29050,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G989" t="n">
-        <v>1.78324902057648</v>
+        <v>1.78324890136719</v>
       </c>
       <c r="H989" t="n">
         <v>1500</v>
@@ -29137,7 +29137,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G992" t="n">
-        <v>1.75538575649261</v>
+        <v>1.75538563728333</v>
       </c>
       <c r="H992" t="n">
         <v>9000</v>
@@ -29166,7 +29166,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G993" t="n">
-        <v>1.75538575649261</v>
+        <v>1.75538563728333</v>
       </c>
       <c r="H993" t="n">
         <v>0</v>
@@ -29195,7 +29195,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G994" t="n">
-        <v>1.77396130561829</v>
+        <v>1.773961186409</v>
       </c>
       <c r="H994" t="n">
         <v>3000</v>
@@ -29224,7 +29224,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G995" t="n">
-        <v>1.77396130561829</v>
+        <v>1.773961186409</v>
       </c>
       <c r="H995" t="n">
         <v>0</v>
@@ -29630,7 +29630,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1009" t="n">
-        <v>1.77396130561829</v>
+        <v>1.773961186409</v>
       </c>
       <c r="H1009" t="n">
         <v>6000</v>
@@ -29659,7 +29659,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1010" t="n">
-        <v>1.77396130561829</v>
+        <v>1.773961186409</v>
       </c>
       <c r="H1010" t="n">
         <v>0</v>
@@ -29688,7 +29688,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.77396130561829</v>
+        <v>1.773961186409</v>
       </c>
       <c r="H1011" t="n">
         <v>0</v>
@@ -29746,7 +29746,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1013" t="n">
-        <v>1.77396130561829</v>
+        <v>1.773961186409</v>
       </c>
       <c r="H1013" t="n">
         <v>3000</v>
@@ -29862,7 +29862,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1017" t="n">
-        <v>1.77396130561829</v>
+        <v>1.773961186409</v>
       </c>
       <c r="H1017" t="n">
         <v>1500</v>
@@ -29891,7 +29891,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1018" t="n">
-        <v>1.77396130561829</v>
+        <v>1.773961186409</v>
       </c>
       <c r="H1018" t="n">
         <v>0</v>
@@ -29920,7 +29920,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1019" t="n">
-        <v>1.77396130561829</v>
+        <v>1.773961186409</v>
       </c>
       <c r="H1019" t="n">
         <v>0</v>
@@ -30355,7 +30355,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1034" t="n">
-        <v>1.75538575649261</v>
+        <v>1.75538563728333</v>
       </c>
       <c r="H1034" t="n">
         <v>13500</v>
@@ -30384,7 +30384,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.81111228466034</v>
+        <v>1.81111240386963</v>
       </c>
       <c r="H1035" t="n">
         <v>1500</v>
@@ -30616,7 +30616,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.78324902057648</v>
+        <v>1.78324890136719</v>
       </c>
       <c r="H1043" t="n">
         <v>4500</v>
@@ -30645,7 +30645,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1044" t="n">
-        <v>1.77396130561829</v>
+        <v>1.773961186409</v>
       </c>
       <c r="H1044" t="n">
         <v>3000</v>
@@ -30674,7 +30674,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1045" t="n">
-        <v>1.75538575649261</v>
+        <v>1.75538563728333</v>
       </c>
       <c r="H1045" t="n">
         <v>4500</v>
@@ -30703,7 +30703,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1046" t="n">
-        <v>1.77396130561829</v>
+        <v>1.773961186409</v>
       </c>
       <c r="H1046" t="n">
         <v>9000</v>
@@ -30732,7 +30732,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1047" t="n">
-        <v>1.77396130561829</v>
+        <v>1.773961186409</v>
       </c>
       <c r="H1047" t="n">
         <v>1500</v>
@@ -30819,7 +30819,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1050" t="n">
-        <v>1.75538575649261</v>
+        <v>1.75538563728333</v>
       </c>
       <c r="H1050" t="n">
         <v>1500</v>
@@ -30848,7 +30848,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1051" t="n">
-        <v>1.77396130561829</v>
+        <v>1.773961186409</v>
       </c>
       <c r="H1051" t="n">
         <v>4500</v>
@@ -31167,7 +31167,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1062" t="n">
-        <v>1.70894694328308</v>
+        <v>1.70894706249237</v>
       </c>
       <c r="H1062" t="n">
         <v>4500</v>
@@ -32153,7 +32153,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1096" t="n">
-        <v>1.60678172111511</v>
+        <v>1.60678160190582</v>
       </c>
       <c r="H1096" t="n">
         <v>10500</v>
@@ -32211,7 +32211,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1098" t="n">
-        <v>1.78324902057648</v>
+        <v>1.78324890136719</v>
       </c>
       <c r="H1098" t="n">
         <v>25500</v>
@@ -32240,7 +32240,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1099" t="n">
-        <v>1.77396130561829</v>
+        <v>1.773961186409</v>
       </c>
       <c r="H1099" t="n">
         <v>7500</v>
@@ -32269,7 +32269,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1100" t="n">
-        <v>1.75538575649261</v>
+        <v>1.75538563728333</v>
       </c>
       <c r="H1100" t="n">
         <v>6000</v>
@@ -32530,7 +32530,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1109" t="n">
-        <v>1.70894694328308</v>
+        <v>1.70894706249237</v>
       </c>
       <c r="H1109" t="n">
         <v>4500</v>
@@ -33168,7 +33168,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1131" t="n">
-        <v>1.70894694328308</v>
+        <v>1.70894706249237</v>
       </c>
       <c r="H1131" t="n">
         <v>1500</v>
@@ -33255,7 +33255,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1134" t="n">
-        <v>1.70894694328308</v>
+        <v>1.70894706249237</v>
       </c>
       <c r="H1134" t="n">
         <v>6000</v>
@@ -33284,7 +33284,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1135" t="n">
-        <v>1.70894694328308</v>
+        <v>1.70894706249237</v>
       </c>
       <c r="H1135" t="n">
         <v>0</v>
@@ -33951,7 +33951,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1158" t="n">
-        <v>1.65322041511536</v>
+        <v>1.65322029590607</v>
       </c>
       <c r="H1158" t="n">
         <v>3000</v>
@@ -34183,7 +34183,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1166" t="n">
-        <v>1.54176723957062</v>
+        <v>1.54176735877991</v>
       </c>
       <c r="H1166" t="n">
         <v>13500</v>
@@ -34212,7 +34212,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1167" t="n">
-        <v>1.54176723957062</v>
+        <v>1.54176735877991</v>
       </c>
       <c r="H1167" t="n">
         <v>0</v>
@@ -34241,7 +34241,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1168" t="n">
-        <v>1.54176723957062</v>
+        <v>1.54176735877991</v>
       </c>
       <c r="H1168" t="n">
         <v>0</v>
@@ -45644,6 +45644,35 @@
         <v>1500</v>
       </c>
       <c r="I1561" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1562">
+      <c r="A1562" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1562" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1562" t="n">
+        <v>1.51999998092651</v>
+      </c>
+      <c r="D1562" t="n">
+        <v>1.55999994277954</v>
+      </c>
+      <c r="E1562" t="n">
+        <v>1.51999998092651</v>
+      </c>
+      <c r="F1562" t="n">
+        <v>1.55999994277954</v>
+      </c>
+      <c r="G1562" t="n">
+        <v>1.55999994277954</v>
+      </c>
+      <c r="H1562" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I1562" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RETI.MI.xlsx
+++ b/data/RETI.MI.xlsx
@@ -427,7 +427,7 @@
         <v>0.889900028705597</v>
       </c>
       <c r="G2" t="n">
-        <v>0.759858429431915</v>
+        <v>0.759858548641205</v>
       </c>
       <c r="H2" t="n">
         <v>856500</v>
@@ -514,7 +514,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G5" t="n">
-        <v>0.765067040920258</v>
+        <v>0.765066981315613</v>
       </c>
       <c r="H5" t="n">
         <v>37500</v>
@@ -543,7 +543,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G6" t="n">
-        <v>0.765067040920258</v>
+        <v>0.765066981315613</v>
       </c>
       <c r="H6" t="n">
         <v>33000</v>
@@ -601,7 +601,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G8" t="n">
-        <v>0.756528317928314</v>
+        <v>0.756528258323669</v>
       </c>
       <c r="H8" t="n">
         <v>63000</v>
@@ -630,7 +630,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G9" t="n">
-        <v>0.732620000839233</v>
+        <v>0.732619941234589</v>
       </c>
       <c r="H9" t="n">
         <v>118500</v>
@@ -659,7 +659,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G10" t="n">
-        <v>0.72237354516983</v>
+        <v>0.722373604774475</v>
       </c>
       <c r="H10" t="n">
         <v>48000</v>
@@ -746,7 +746,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G13" t="n">
-        <v>0.691634178161621</v>
+        <v>0.691634297370911</v>
       </c>
       <c r="H13" t="n">
         <v>49500</v>
@@ -833,7 +833,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G16" t="n">
-        <v>0.666018187999725</v>
+        <v>0.666018128395081</v>
       </c>
       <c r="H16" t="n">
         <v>67500</v>
@@ -862,7 +862,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G17" t="n">
-        <v>0.654063940048218</v>
+        <v>0.654063999652863</v>
       </c>
       <c r="H17" t="n">
         <v>25500</v>
@@ -978,7 +978,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G21" t="n">
-        <v>0.654063940048218</v>
+        <v>0.654063999652863</v>
       </c>
       <c r="H21" t="n">
         <v>132000</v>
@@ -1007,7 +1007,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G22" t="n">
-        <v>0.659187197685242</v>
+        <v>0.659187257289886</v>
       </c>
       <c r="H22" t="n">
         <v>24000</v>
@@ -1036,7 +1036,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G23" t="n">
-        <v>0.666018187999725</v>
+        <v>0.666018128395081</v>
       </c>
       <c r="H23" t="n">
         <v>39000</v>
@@ -1065,7 +1065,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G24" t="n">
-        <v>0.652356207370758</v>
+        <v>0.652356266975403</v>
       </c>
       <c r="H24" t="n">
         <v>10500</v>
@@ -1123,7 +1123,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G26" t="n">
-        <v>0.654063940048218</v>
+        <v>0.654063999652863</v>
       </c>
       <c r="H26" t="n">
         <v>27000</v>
@@ -1152,7 +1152,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G27" t="n">
-        <v>0.633571088314056</v>
+        <v>0.633571147918701</v>
       </c>
       <c r="H27" t="n">
         <v>43500</v>
@@ -1181,7 +1181,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G28" t="n">
-        <v>0.631863355636597</v>
+        <v>0.631863415241241</v>
       </c>
       <c r="H28" t="n">
         <v>33000</v>
@@ -1268,7 +1268,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G31" t="n">
-        <v>0.58746212720871</v>
+        <v>0.587462246417999</v>
       </c>
       <c r="H31" t="n">
         <v>78000</v>
@@ -1297,7 +1297,7 @@
         <v>0.73199999332428</v>
       </c>
       <c r="G32" t="n">
-        <v>0.625032484531403</v>
+        <v>0.625032424926758</v>
       </c>
       <c r="H32" t="n">
         <v>27000</v>
@@ -1326,7 +1326,7 @@
         <v>0.722000002861023</v>
       </c>
       <c r="G33" t="n">
-        <v>0.616493761539459</v>
+        <v>0.616493701934814</v>
       </c>
       <c r="H33" t="n">
         <v>3000</v>
@@ -1384,7 +1384,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G35" t="n">
-        <v>0.58063131570816</v>
+        <v>0.580631196498871</v>
       </c>
       <c r="H35" t="n">
         <v>12000</v>
@@ -1413,7 +1413,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G36" t="n">
-        <v>0.563553810119629</v>
+        <v>0.563553869724274</v>
       </c>
       <c r="H36" t="n">
         <v>66000</v>
@@ -1587,7 +1587,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G42" t="n">
-        <v>0.604539573192596</v>
+        <v>0.604539513587952</v>
       </c>
       <c r="H42" t="n">
         <v>127500</v>
@@ -1645,7 +1645,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G44" t="n">
-        <v>0.604539573192596</v>
+        <v>0.604539513587952</v>
       </c>
       <c r="H44" t="n">
         <v>64500</v>
@@ -1703,7 +1703,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G46" t="n">
-        <v>0.631863355636597</v>
+        <v>0.631863415241241</v>
       </c>
       <c r="H46" t="n">
         <v>6000</v>
@@ -1819,7 +1819,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G50" t="n">
-        <v>0.631863355636597</v>
+        <v>0.631863415241241</v>
       </c>
       <c r="H50" t="n">
         <v>12000</v>
@@ -1877,7 +1877,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G52" t="n">
-        <v>0.705296158790588</v>
+        <v>0.705296099185944</v>
       </c>
       <c r="H52" t="n">
         <v>157500</v>
@@ -1906,7 +1906,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G53" t="n">
-        <v>0.701880753040314</v>
+        <v>0.701880693435669</v>
       </c>
       <c r="H53" t="n">
         <v>70500</v>
@@ -1935,7 +1935,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G54" t="n">
-        <v>0.674556851387024</v>
+        <v>0.674556910991669</v>
       </c>
       <c r="H54" t="n">
         <v>115500</v>
@@ -1964,7 +1964,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G55" t="n">
-        <v>0.677972376346588</v>
+        <v>0.677972435951233</v>
       </c>
       <c r="H55" t="n">
         <v>36000</v>
@@ -2022,7 +2022,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G57" t="n">
-        <v>0.705296158790588</v>
+        <v>0.705296099185944</v>
       </c>
       <c r="H57" t="n">
         <v>25500</v>
@@ -2051,7 +2051,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G58" t="n">
-        <v>0.703588426113129</v>
+        <v>0.703588485717773</v>
       </c>
       <c r="H58" t="n">
         <v>12000</v>
@@ -2167,7 +2167,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G62" t="n">
-        <v>0.681387841701508</v>
+        <v>0.681387782096863</v>
       </c>
       <c r="H62" t="n">
         <v>16500</v>
@@ -2283,7 +2283,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G66" t="n">
-        <v>0.674556851387024</v>
+        <v>0.674556910991669</v>
       </c>
       <c r="H66" t="n">
         <v>10500</v>
@@ -2370,7 +2370,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G69" t="n">
-        <v>0.693341970443726</v>
+        <v>0.693341910839081</v>
       </c>
       <c r="H69" t="n">
         <v>15000</v>
@@ -2399,7 +2399,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G70" t="n">
-        <v>0.677972376346588</v>
+        <v>0.677972435951233</v>
       </c>
       <c r="H70" t="n">
         <v>3000</v>
@@ -2428,7 +2428,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G71" t="n">
-        <v>0.677972376346588</v>
+        <v>0.677972435951233</v>
       </c>
       <c r="H71" t="n">
         <v>3000</v>
@@ -2457,7 +2457,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G72" t="n">
-        <v>0.693341970443726</v>
+        <v>0.693341910839081</v>
       </c>
       <c r="H72" t="n">
         <v>3000</v>
@@ -2486,7 +2486,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G73" t="n">
-        <v>0.705296158790588</v>
+        <v>0.705296099185944</v>
       </c>
       <c r="H73" t="n">
         <v>19500</v>
@@ -2515,7 +2515,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G74" t="n">
-        <v>0.691634178161621</v>
+        <v>0.691634297370911</v>
       </c>
       <c r="H74" t="n">
         <v>43500</v>
@@ -2544,7 +2544,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G75" t="n">
-        <v>0.700172901153564</v>
+        <v>0.700172960758209</v>
       </c>
       <c r="H75" t="n">
         <v>73500</v>
@@ -2602,7 +2602,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G77" t="n">
-        <v>0.700172901153564</v>
+        <v>0.700172960758209</v>
       </c>
       <c r="H77" t="n">
         <v>22500</v>
@@ -2631,7 +2631,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G78" t="n">
-        <v>0.700172901153564</v>
+        <v>0.700172960758209</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
@@ -2660,7 +2660,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G79" t="n">
-        <v>0.705296158790588</v>
+        <v>0.705296099185944</v>
       </c>
       <c r="H79" t="n">
         <v>3000</v>
@@ -2689,7 +2689,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G80" t="n">
-        <v>0.717250347137451</v>
+        <v>0.717250287532806</v>
       </c>
       <c r="H80" t="n">
         <v>28500</v>
@@ -2718,7 +2718,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G81" t="n">
-        <v>0.708711683750153</v>
+        <v>0.708711624145508</v>
       </c>
       <c r="H81" t="n">
         <v>22500</v>
@@ -2805,7 +2805,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G84" t="n">
-        <v>0.717250347137451</v>
+        <v>0.717250287532806</v>
       </c>
       <c r="H84" t="n">
         <v>1500</v>
@@ -2863,7 +2863,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G86" t="n">
-        <v>0.700172901153564</v>
+        <v>0.700172960758209</v>
       </c>
       <c r="H86" t="n">
         <v>1500</v>
@@ -2921,7 +2921,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G88" t="n">
-        <v>0.700172901153564</v>
+        <v>0.700172960758209</v>
       </c>
       <c r="H88" t="n">
         <v>16500</v>
@@ -2950,7 +2950,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G89" t="n">
-        <v>0.684803247451782</v>
+        <v>0.684803307056427</v>
       </c>
       <c r="H89" t="n">
         <v>22500</v>
@@ -2979,7 +2979,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G90" t="n">
-        <v>0.684803247451782</v>
+        <v>0.684803307056427</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -3008,7 +3008,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G91" t="n">
-        <v>0.701880753040314</v>
+        <v>0.701880693435669</v>
       </c>
       <c r="H91" t="n">
         <v>10500</v>
@@ -3037,7 +3037,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G92" t="n">
-        <v>0.701880753040314</v>
+        <v>0.701880693435669</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
@@ -3066,7 +3066,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G93" t="n">
-        <v>0.701880753040314</v>
+        <v>0.701880693435669</v>
       </c>
       <c r="H93" t="n">
         <v>1500</v>
@@ -3095,7 +3095,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G94" t="n">
-        <v>0.698465168476105</v>
+        <v>0.69846522808075</v>
       </c>
       <c r="H94" t="n">
         <v>19500</v>
@@ -3153,7 +3153,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G96" t="n">
-        <v>0.674556851387024</v>
+        <v>0.674556910991669</v>
       </c>
       <c r="H96" t="n">
         <v>12000</v>
@@ -3211,7 +3211,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G98" t="n">
-        <v>0.666018187999725</v>
+        <v>0.666018128395081</v>
       </c>
       <c r="H98" t="n">
         <v>18000</v>
@@ -3240,7 +3240,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G99" t="n">
-        <v>0.677972376346588</v>
+        <v>0.677972435951233</v>
       </c>
       <c r="H99" t="n">
         <v>7500</v>
@@ -3269,7 +3269,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G100" t="n">
-        <v>0.676264524459839</v>
+        <v>0.676264643669128</v>
       </c>
       <c r="H100" t="n">
         <v>7500</v>
@@ -3298,7 +3298,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G101" t="n">
-        <v>0.676264524459839</v>
+        <v>0.676264643669128</v>
       </c>
       <c r="H101" t="n">
         <v>0</v>
@@ -3472,7 +3472,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G107" t="n">
-        <v>0.691634178161621</v>
+        <v>0.691634297370911</v>
       </c>
       <c r="H107" t="n">
         <v>42000</v>
@@ -3501,7 +3501,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G108" t="n">
-        <v>0.700172901153564</v>
+        <v>0.700172960758209</v>
       </c>
       <c r="H108" t="n">
         <v>55500</v>
@@ -3559,7 +3559,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G110" t="n">
-        <v>0.698465168476105</v>
+        <v>0.69846522808075</v>
       </c>
       <c r="H110" t="n">
         <v>6000</v>
@@ -3588,7 +3588,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G111" t="n">
-        <v>0.703588426113129</v>
+        <v>0.703588485717773</v>
       </c>
       <c r="H111" t="n">
         <v>24000</v>
@@ -3646,7 +3646,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G113" t="n">
-        <v>0.691634178161621</v>
+        <v>0.691634297370911</v>
       </c>
       <c r="H113" t="n">
         <v>4500</v>
@@ -3675,7 +3675,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G114" t="n">
-        <v>0.700172901153564</v>
+        <v>0.700172960758209</v>
       </c>
       <c r="H114" t="n">
         <v>21000</v>
@@ -3704,7 +3704,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G115" t="n">
-        <v>0.703588426113129</v>
+        <v>0.703588485717773</v>
       </c>
       <c r="H115" t="n">
         <v>7500</v>
@@ -3733,7 +3733,7 @@
         <v>0.86599999666214</v>
       </c>
       <c r="G116" t="n">
-        <v>0.739450931549072</v>
+        <v>0.739450871944427</v>
       </c>
       <c r="H116" t="n">
         <v>108000</v>
@@ -3762,7 +3762,7 @@
         <v>0.842000007629395</v>
       </c>
       <c r="G117" t="n">
-        <v>0.718958020210266</v>
+        <v>0.718958079814911</v>
       </c>
       <c r="H117" t="n">
         <v>102000</v>
@@ -3791,7 +3791,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G118" t="n">
-        <v>0.717250347137451</v>
+        <v>0.717250287532806</v>
       </c>
       <c r="H118" t="n">
         <v>69000</v>
@@ -3849,7 +3849,7 @@
         <v>0.867999970912933</v>
       </c>
       <c r="G120" t="n">
-        <v>0.741158604621887</v>
+        <v>0.741158664226532</v>
       </c>
       <c r="H120" t="n">
         <v>139500</v>
@@ -3878,7 +3878,7 @@
         <v>0.867999970912933</v>
       </c>
       <c r="G121" t="n">
-        <v>0.741158604621887</v>
+        <v>0.741158664226532</v>
       </c>
       <c r="H121" t="n">
         <v>151500</v>
@@ -3936,7 +3936,7 @@
         <v>0.972000002861023</v>
       </c>
       <c r="G123" t="n">
-        <v>0.829961180686951</v>
+        <v>0.829961121082306</v>
       </c>
       <c r="H123" t="n">
         <v>922500</v>
@@ -3965,7 +3965,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G124" t="n">
-        <v>0.828253448009491</v>
+        <v>0.828253388404846</v>
       </c>
       <c r="H124" t="n">
         <v>213000</v>
@@ -3994,7 +3994,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G125" t="n">
-        <v>0.83679211139679</v>
+        <v>0.836792051792145</v>
       </c>
       <c r="H125" t="n">
         <v>196500</v>
@@ -4023,7 +4023,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G126" t="n">
-        <v>0.83679211139679</v>
+        <v>0.836792051792145</v>
       </c>
       <c r="H126" t="n">
         <v>76500</v>
@@ -4197,7 +4197,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G132" t="n">
-        <v>0.845330715179443</v>
+        <v>0.845330774784088</v>
       </c>
       <c r="H132" t="n">
         <v>25500</v>
@@ -4284,7 +4284,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G135" t="n">
-        <v>0.866677463054657</v>
+        <v>0.866677403450012</v>
       </c>
       <c r="H135" t="n">
         <v>15000</v>
@@ -4313,7 +4313,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G136" t="n">
-        <v>0.900832295417786</v>
+        <v>0.900832235813141</v>
       </c>
       <c r="H136" t="n">
         <v>127500</v>
@@ -4342,7 +4342,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G137" t="n">
-        <v>0.888024151325226</v>
+        <v>0.888024210929871</v>
       </c>
       <c r="H137" t="n">
         <v>33000</v>
@@ -4400,7 +4400,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G139" t="n">
-        <v>0.913640260696411</v>
+        <v>0.913640379905701</v>
       </c>
       <c r="H139" t="n">
         <v>4500</v>
@@ -4429,7 +4429,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G140" t="n">
-        <v>0.922179102897644</v>
+        <v>0.922179043292999</v>
       </c>
       <c r="H140" t="n">
         <v>22500</v>
@@ -4458,7 +4458,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G141" t="n">
-        <v>0.922179102897644</v>
+        <v>0.922179043292999</v>
       </c>
       <c r="H141" t="n">
         <v>67500</v>
@@ -4487,7 +4487,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G142" t="n">
-        <v>0.913640260696411</v>
+        <v>0.913640379905701</v>
       </c>
       <c r="H142" t="n">
         <v>42000</v>
@@ -4516,7 +4516,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G143" t="n">
-        <v>0.930717825889587</v>
+        <v>0.930717706680298</v>
       </c>
       <c r="H143" t="n">
         <v>45000</v>
@@ -4545,7 +4545,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G144" t="n">
-        <v>1.17833983898163</v>
+        <v>1.17833971977234</v>
       </c>
       <c r="H144" t="n">
         <v>451500</v>
@@ -4574,7 +4574,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G145" t="n">
-        <v>1.11429953575134</v>
+        <v>1.11429965496063</v>
       </c>
       <c r="H145" t="n">
         <v>834000</v>
@@ -4603,7 +4603,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G146" t="n">
-        <v>1.13564622402191</v>
+        <v>1.13564646244049</v>
       </c>
       <c r="H146" t="n">
         <v>342000</v>
@@ -4632,7 +4632,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G147" t="n">
-        <v>1.20395600795746</v>
+        <v>1.20395588874817</v>
       </c>
       <c r="H147" t="n">
         <v>510000</v>
@@ -4661,7 +4661,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G148" t="n">
-        <v>1.20395600795746</v>
+        <v>1.20395588874817</v>
       </c>
       <c r="H148" t="n">
         <v>210000</v>
@@ -4690,7 +4690,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G149" t="n">
-        <v>1.20395600795746</v>
+        <v>1.20395588874817</v>
       </c>
       <c r="H149" t="n">
         <v>172500</v>
@@ -4864,7 +4864,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G155" t="n">
-        <v>1.13804590702057</v>
+        <v>1.13804578781128</v>
       </c>
       <c r="H155" t="n">
         <v>30000</v>
@@ -4893,7 +4893,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G156" t="n">
-        <v>1.14683377742767</v>
+        <v>1.14683389663696</v>
       </c>
       <c r="H156" t="n">
         <v>15000</v>
@@ -4980,7 +4980,7 @@
         <v>1.25499999523163</v>
       </c>
       <c r="G159" t="n">
-        <v>1.1028938293457</v>
+        <v>1.10289394855499</v>
       </c>
       <c r="H159" t="n">
         <v>19500</v>
@@ -5038,7 +5038,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G161" t="n">
-        <v>1.08971190452576</v>
+        <v>1.08971202373505</v>
       </c>
       <c r="H161" t="n">
         <v>136500</v>
@@ -5067,7 +5067,7 @@
         <v>1.25</v>
       </c>
       <c r="G162" t="n">
-        <v>1.09850001335144</v>
+        <v>1.09849989414215</v>
       </c>
       <c r="H162" t="n">
         <v>39000</v>
@@ -5241,7 +5241,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G168" t="n">
-        <v>1.14683377742767</v>
+        <v>1.14683389663696</v>
       </c>
       <c r="H168" t="n">
         <v>49500</v>
@@ -5270,7 +5270,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G169" t="n">
-        <v>1.12925803661346</v>
+        <v>1.12925791740417</v>
       </c>
       <c r="H169" t="n">
         <v>28500</v>
@@ -5299,7 +5299,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G170" t="n">
-        <v>1.14683377742767</v>
+        <v>1.14683389663696</v>
       </c>
       <c r="H170" t="n">
         <v>9000</v>
@@ -5328,7 +5328,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G171" t="n">
-        <v>1.13804590702057</v>
+        <v>1.13804578781128</v>
       </c>
       <c r="H171" t="n">
         <v>9000</v>
@@ -5415,7 +5415,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G174" t="n">
-        <v>1.18198585510254</v>
+        <v>1.18198597431183</v>
       </c>
       <c r="H174" t="n">
         <v>24000</v>
@@ -5531,7 +5531,7 @@
         <v>1.49500000476837</v>
       </c>
       <c r="G178" t="n">
-        <v>1.31380581855774</v>
+        <v>1.31380593776703</v>
       </c>
       <c r="H178" t="n">
         <v>75000</v>
@@ -5560,7 +5560,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G179" t="n">
-        <v>1.33577597141266</v>
+        <v>1.33577573299408</v>
       </c>
       <c r="H179" t="n">
         <v>48000</v>
@@ -5589,7 +5589,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G180" t="n">
-        <v>1.34895777702332</v>
+        <v>1.3489578962326</v>
       </c>
       <c r="H180" t="n">
         <v>9000</v>
@@ -5618,7 +5618,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G181" t="n">
-        <v>1.33577597141266</v>
+        <v>1.33577573299408</v>
       </c>
       <c r="H181" t="n">
         <v>24000</v>
@@ -5647,7 +5647,7 @@
         <v>1.5</v>
       </c>
       <c r="G182" t="n">
-        <v>1.31819975376129</v>
+        <v>1.31819987297058</v>
       </c>
       <c r="H182" t="n">
         <v>39000</v>
@@ -5676,7 +5676,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G183" t="n">
-        <v>1.28304779529572</v>
+        <v>1.283047914505</v>
       </c>
       <c r="H183" t="n">
         <v>180000</v>
@@ -5734,7 +5734,7 @@
         <v>1.5</v>
       </c>
       <c r="G185" t="n">
-        <v>1.31819975376129</v>
+        <v>1.31819987297058</v>
       </c>
       <c r="H185" t="n">
         <v>19500</v>
@@ -5763,7 +5763,7 @@
         <v>1.5</v>
       </c>
       <c r="G186" t="n">
-        <v>1.31819975376129</v>
+        <v>1.31819987297058</v>
       </c>
       <c r="H186" t="n">
         <v>31500</v>
@@ -5821,7 +5821,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G188" t="n">
-        <v>1.34895777702332</v>
+        <v>1.3489578962326</v>
       </c>
       <c r="H188" t="n">
         <v>36000</v>
@@ -5908,7 +5908,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G191" t="n">
-        <v>1.38410997390747</v>
+        <v>1.38410985469818</v>
       </c>
       <c r="H191" t="n">
         <v>34500</v>
@@ -5937,7 +5937,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G192" t="n">
-        <v>1.37971580028534</v>
+        <v>1.37971591949463</v>
       </c>
       <c r="H192" t="n">
         <v>87000</v>
@@ -5966,7 +5966,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G193" t="n">
-        <v>1.34895777702332</v>
+        <v>1.3489578962326</v>
       </c>
       <c r="H193" t="n">
         <v>34500</v>
@@ -5995,7 +5995,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G194" t="n">
-        <v>1.34016990661621</v>
+        <v>1.34016978740692</v>
       </c>
       <c r="H194" t="n">
         <v>85500</v>
@@ -6024,7 +6024,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G195" t="n">
-        <v>1.34456384181976</v>
+        <v>1.34456372261047</v>
       </c>
       <c r="H195" t="n">
         <v>18000</v>
@@ -6140,7 +6140,7 @@
         <v>1.49500000476837</v>
       </c>
       <c r="G199" t="n">
-        <v>1.31380581855774</v>
+        <v>1.31380593776703</v>
       </c>
       <c r="H199" t="n">
         <v>18000</v>
@@ -6169,7 +6169,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G200" t="n">
-        <v>1.34895777702332</v>
+        <v>1.3489578962326</v>
       </c>
       <c r="H200" t="n">
         <v>22500</v>
@@ -6198,7 +6198,7 @@
         <v>1.5</v>
       </c>
       <c r="G201" t="n">
-        <v>1.31819975376129</v>
+        <v>1.31819987297058</v>
       </c>
       <c r="H201" t="n">
         <v>16500</v>
@@ -6227,7 +6227,7 @@
         <v>1.5</v>
       </c>
       <c r="G202" t="n">
-        <v>1.31819975376129</v>
+        <v>1.31819987297058</v>
       </c>
       <c r="H202" t="n">
         <v>3000</v>
@@ -6256,7 +6256,7 @@
         <v>1.5</v>
       </c>
       <c r="G203" t="n">
-        <v>1.31819975376129</v>
+        <v>1.31819987297058</v>
       </c>
       <c r="H203" t="n">
         <v>12000</v>
@@ -6314,7 +6314,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G205" t="n">
-        <v>1.33577597141266</v>
+        <v>1.33577573299408</v>
       </c>
       <c r="H205" t="n">
         <v>4500</v>
@@ -6343,7 +6343,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G206" t="n">
-        <v>1.34456384181976</v>
+        <v>1.34456372261047</v>
       </c>
       <c r="H206" t="n">
         <v>18000</v>
@@ -6372,7 +6372,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G207" t="n">
-        <v>1.34456384181976</v>
+        <v>1.34456372261047</v>
       </c>
       <c r="H207" t="n">
         <v>4500</v>
@@ -6401,7 +6401,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G208" t="n">
-        <v>1.35335183143616</v>
+        <v>1.35335195064545</v>
       </c>
       <c r="H208" t="n">
         <v>1500</v>
@@ -6430,7 +6430,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G209" t="n">
-        <v>1.35335183143616</v>
+        <v>1.35335195064545</v>
       </c>
       <c r="H209" t="n">
         <v>0</v>
@@ -6459,7 +6459,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G210" t="n">
-        <v>1.35335183143616</v>
+        <v>1.35335195064545</v>
       </c>
       <c r="H210" t="n">
         <v>0</v>
@@ -6488,7 +6488,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G211" t="n">
-        <v>1.2918359041214</v>
+        <v>1.29183602333069</v>
       </c>
       <c r="H211" t="n">
         <v>45000</v>
@@ -6575,7 +6575,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G214" t="n">
-        <v>1.34895777702332</v>
+        <v>1.3489578962326</v>
       </c>
       <c r="H214" t="n">
         <v>28500</v>
@@ -6633,7 +6633,7 @@
         <v>1.5</v>
       </c>
       <c r="G216" t="n">
-        <v>1.31819975376129</v>
+        <v>1.31819987297058</v>
       </c>
       <c r="H216" t="n">
         <v>15000</v>
@@ -6807,7 +6807,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G222" t="n">
-        <v>1.2918359041214</v>
+        <v>1.29183602333069</v>
       </c>
       <c r="H222" t="n">
         <v>9000</v>
@@ -6865,7 +6865,7 @@
         <v>1.5</v>
       </c>
       <c r="G224" t="n">
-        <v>1.31819975376129</v>
+        <v>1.31819987297058</v>
       </c>
       <c r="H224" t="n">
         <v>13500</v>
@@ -6894,7 +6894,7 @@
         <v>1.5</v>
       </c>
       <c r="G225" t="n">
-        <v>1.31819975376129</v>
+        <v>1.31819987297058</v>
       </c>
       <c r="H225" t="n">
         <v>0</v>
@@ -6952,7 +6952,7 @@
         <v>1.5</v>
       </c>
       <c r="G227" t="n">
-        <v>1.31819975376129</v>
+        <v>1.31819987297058</v>
       </c>
       <c r="H227" t="n">
         <v>13500</v>
@@ -6981,7 +6981,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G228" t="n">
-        <v>1.2918359041214</v>
+        <v>1.29183602333069</v>
       </c>
       <c r="H228" t="n">
         <v>27000</v>
@@ -7010,7 +7010,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G229" t="n">
-        <v>1.27425992488861</v>
+        <v>1.27425980567932</v>
       </c>
       <c r="H229" t="n">
         <v>6000</v>
@@ -7068,7 +7068,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G231" t="n">
-        <v>1.28304779529572</v>
+        <v>1.283047914505</v>
       </c>
       <c r="H231" t="n">
         <v>4500</v>
@@ -7097,7 +7097,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G232" t="n">
-        <v>1.34456384181976</v>
+        <v>1.34456372261047</v>
       </c>
       <c r="H232" t="n">
         <v>45000</v>
@@ -7126,7 +7126,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G233" t="n">
-        <v>1.34016990661621</v>
+        <v>1.34016978740692</v>
       </c>
       <c r="H233" t="n">
         <v>61500</v>
@@ -7184,7 +7184,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G235" t="n">
-        <v>1.34456384181976</v>
+        <v>1.34456372261047</v>
       </c>
       <c r="H235" t="n">
         <v>13500</v>
@@ -7213,7 +7213,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G236" t="n">
-        <v>1.34895777702332</v>
+        <v>1.3489578962326</v>
       </c>
       <c r="H236" t="n">
         <v>13500</v>
@@ -7242,7 +7242,7 @@
         <v>1.49500000476837</v>
       </c>
       <c r="G237" t="n">
-        <v>1.31380581855774</v>
+        <v>1.31380593776703</v>
       </c>
       <c r="H237" t="n">
         <v>28500</v>
@@ -7271,7 +7271,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G238" t="n">
-        <v>1.3665337562561</v>
+        <v>1.36653387546539</v>
       </c>
       <c r="H238" t="n">
         <v>34500</v>
@@ -7300,7 +7300,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G239" t="n">
-        <v>1.34016990661621</v>
+        <v>1.34016978740692</v>
       </c>
       <c r="H239" t="n">
         <v>69000</v>
@@ -7329,7 +7329,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G240" t="n">
-        <v>1.74881196022034</v>
+        <v>1.74881184101105</v>
       </c>
       <c r="H240" t="n">
         <v>333000</v>
@@ -7358,7 +7358,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G241" t="n">
-        <v>2.24972772598267</v>
+        <v>2.24972748756409</v>
       </c>
       <c r="H241" t="n">
         <v>774000</v>
@@ -7416,7 +7416,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G243" t="n">
-        <v>2.2321515083313</v>
+        <v>2.23215174674988</v>
       </c>
       <c r="H243" t="n">
         <v>702000</v>
@@ -7445,7 +7445,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G244" t="n">
-        <v>2.52215576171875</v>
+        <v>2.52215552330017</v>
       </c>
       <c r="H244" t="n">
         <v>1464000</v>
@@ -7474,7 +7474,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G245" t="n">
-        <v>2.39912390708923</v>
+        <v>2.39912366867065</v>
       </c>
       <c r="H245" t="n">
         <v>546000</v>
@@ -7503,7 +7503,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G246" t="n">
-        <v>2.27609181404114</v>
+        <v>2.27609157562256</v>
       </c>
       <c r="H246" t="n">
         <v>229500</v>
@@ -7532,7 +7532,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G247" t="n">
-        <v>2.17063570022583</v>
+        <v>2.17063593864441</v>
       </c>
       <c r="H247" t="n">
         <v>265500</v>
@@ -7561,7 +7561,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G248" t="n">
-        <v>2.27609181404114</v>
+        <v>2.27609157562256</v>
       </c>
       <c r="H248" t="n">
         <v>240000</v>
@@ -7590,7 +7590,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G249" t="n">
-        <v>2.20578765869141</v>
+        <v>2.20578789710999</v>
       </c>
       <c r="H249" t="n">
         <v>195000</v>
@@ -7619,7 +7619,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G250" t="n">
-        <v>2.2321515083313</v>
+        <v>2.23215174674988</v>
       </c>
       <c r="H250" t="n">
         <v>102000</v>
@@ -7648,7 +7648,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G251" t="n">
-        <v>2.1882119178772</v>
+        <v>2.18821167945862</v>
       </c>
       <c r="H251" t="n">
         <v>40500</v>
@@ -7677,7 +7677,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G252" t="n">
-        <v>2.1882119178772</v>
+        <v>2.18821167945862</v>
       </c>
       <c r="H252" t="n">
         <v>36000</v>
@@ -7706,7 +7706,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G253" t="n">
-        <v>2.32881999015808</v>
+        <v>2.3288197517395</v>
       </c>
       <c r="H253" t="n">
         <v>237000</v>
@@ -7735,7 +7735,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G254" t="n">
-        <v>2.34639596939087</v>
+        <v>2.34639573097229</v>
       </c>
       <c r="H254" t="n">
         <v>139500</v>
@@ -7793,7 +7793,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G256" t="n">
-        <v>2.32881999015808</v>
+        <v>2.3288197517395</v>
       </c>
       <c r="H256" t="n">
         <v>75000</v>
@@ -7851,7 +7851,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G258" t="n">
-        <v>2.28487968444824</v>
+        <v>2.28487992286682</v>
       </c>
       <c r="H258" t="n">
         <v>138000</v>
@@ -7909,7 +7909,7 @@
         <v>2.5</v>
       </c>
       <c r="G260" t="n">
-        <v>2.19700002670288</v>
+        <v>2.1969997882843</v>
       </c>
       <c r="H260" t="n">
         <v>85500</v>
@@ -7967,7 +7967,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G262" t="n">
-        <v>2.24972772598267</v>
+        <v>2.24972748756409</v>
       </c>
       <c r="H262" t="n">
         <v>33000</v>
@@ -7996,7 +7996,7 @@
         <v>2.5</v>
       </c>
       <c r="G263" t="n">
-        <v>2.19700002670288</v>
+        <v>2.1969997882843</v>
       </c>
       <c r="H263" t="n">
         <v>13500</v>
@@ -8025,7 +8025,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G264" t="n">
-        <v>2.20578765869141</v>
+        <v>2.20578789710999</v>
       </c>
       <c r="H264" t="n">
         <v>37500</v>
@@ -8054,7 +8054,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G265" t="n">
-        <v>2.34639596939087</v>
+        <v>2.34639573097229</v>
       </c>
       <c r="H265" t="n">
         <v>46500</v>
@@ -8112,7 +8112,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G267" t="n">
-        <v>2.27609181404114</v>
+        <v>2.27609157562256</v>
       </c>
       <c r="H267" t="n">
         <v>61500</v>
@@ -8199,7 +8199,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G270" t="n">
-        <v>2.2321515083313</v>
+        <v>2.23215174674988</v>
       </c>
       <c r="H270" t="n">
         <v>97500</v>
@@ -8228,7 +8228,7 @@
         <v>2.5</v>
       </c>
       <c r="G271" t="n">
-        <v>2.19700002670288</v>
+        <v>2.1969997882843</v>
       </c>
       <c r="H271" t="n">
         <v>36000</v>
@@ -8257,7 +8257,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G272" t="n">
-        <v>2.17063570022583</v>
+        <v>2.17063593864441</v>
       </c>
       <c r="H272" t="n">
         <v>42000</v>
@@ -8286,7 +8286,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G273" t="n">
-        <v>2.27609181404114</v>
+        <v>2.27609157562256</v>
       </c>
       <c r="H273" t="n">
         <v>94500</v>
@@ -8315,7 +8315,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G274" t="n">
-        <v>2.24972772598267</v>
+        <v>2.24972748756409</v>
       </c>
       <c r="H274" t="n">
         <v>45000</v>
@@ -8344,7 +8344,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G275" t="n">
-        <v>2.28487968444824</v>
+        <v>2.28487992286682</v>
       </c>
       <c r="H275" t="n">
         <v>18000</v>
@@ -8373,7 +8373,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G276" t="n">
-        <v>2.28487968444824</v>
+        <v>2.28487992286682</v>
       </c>
       <c r="H276" t="n">
         <v>6000</v>
@@ -8431,7 +8431,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G278" t="n">
-        <v>2.32881999015808</v>
+        <v>2.3288197517395</v>
       </c>
       <c r="H278" t="n">
         <v>33000</v>
@@ -8489,7 +8489,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G280" t="n">
-        <v>2.28487968444824</v>
+        <v>2.28487992286682</v>
       </c>
       <c r="H280" t="n">
         <v>16500</v>
@@ -8518,7 +8518,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G281" t="n">
-        <v>2.32881999015808</v>
+        <v>2.3288197517395</v>
       </c>
       <c r="H281" t="n">
         <v>25500</v>
@@ -8576,7 +8576,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G283" t="n">
-        <v>2.25851607322693</v>
+        <v>2.25851583480835</v>
       </c>
       <c r="H283" t="n">
         <v>12000</v>
@@ -8634,7 +8634,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G285" t="n">
-        <v>2.27609181404114</v>
+        <v>2.27609157562256</v>
       </c>
       <c r="H285" t="n">
         <v>24000</v>
@@ -8779,7 +8779,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G290" t="n">
-        <v>2.25851607322693</v>
+        <v>2.25851583480835</v>
       </c>
       <c r="H290" t="n">
         <v>63000</v>
@@ -8808,7 +8808,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G291" t="n">
-        <v>2.27609181404114</v>
+        <v>2.27609157562256</v>
       </c>
       <c r="H291" t="n">
         <v>18000</v>
@@ -8866,7 +8866,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G293" t="n">
-        <v>2.24972772598267</v>
+        <v>2.24972748756409</v>
       </c>
       <c r="H293" t="n">
         <v>1500</v>
@@ -8895,7 +8895,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G294" t="n">
-        <v>2.28487968444824</v>
+        <v>2.28487992286682</v>
       </c>
       <c r="H294" t="n">
         <v>1500</v>
@@ -8953,7 +8953,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G296" t="n">
-        <v>2.2321515083313</v>
+        <v>2.23215174674988</v>
       </c>
       <c r="H296" t="n">
         <v>7500</v>
@@ -9069,7 +9069,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G300" t="n">
-        <v>2.20578765869141</v>
+        <v>2.20578789710999</v>
       </c>
       <c r="H300" t="n">
         <v>24000</v>
@@ -9098,7 +9098,7 @@
         <v>2.5</v>
       </c>
       <c r="G301" t="n">
-        <v>2.19700002670288</v>
+        <v>2.1969997882843</v>
       </c>
       <c r="H301" t="n">
         <v>21000</v>
@@ -9127,7 +9127,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G302" t="n">
-        <v>2.14427208900452</v>
+        <v>2.14427185058594</v>
       </c>
       <c r="H302" t="n">
         <v>31500</v>
@@ -9156,7 +9156,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G303" t="n">
-        <v>2.07396793365479</v>
+        <v>2.07396769523621</v>
       </c>
       <c r="H303" t="n">
         <v>58500</v>
@@ -9185,7 +9185,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G304" t="n">
-        <v>2.03881573677063</v>
+        <v>2.03881597518921</v>
       </c>
       <c r="H304" t="n">
         <v>51000</v>
@@ -9214,7 +9214,7 @@
         <v>2.25</v>
       </c>
       <c r="G305" t="n">
-        <v>1.97729980945587</v>
+        <v>1.97729969024658</v>
       </c>
       <c r="H305" t="n">
         <v>51000</v>
@@ -9243,7 +9243,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G306" t="n">
-        <v>1.99487566947937</v>
+        <v>1.99487555027008</v>
       </c>
       <c r="H306" t="n">
         <v>13500</v>
@@ -9272,7 +9272,7 @@
         <v>2.25</v>
       </c>
       <c r="G307" t="n">
-        <v>1.97729980945587</v>
+        <v>1.97729969024658</v>
       </c>
       <c r="H307" t="n">
         <v>13500</v>
@@ -9301,7 +9301,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G308" t="n">
-        <v>2.02123951911926</v>
+        <v>2.02123975753784</v>
       </c>
       <c r="H308" t="n">
         <v>12000</v>
@@ -9330,7 +9330,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G309" t="n">
-        <v>1.93335998058319</v>
+        <v>1.9333598613739</v>
       </c>
       <c r="H309" t="n">
         <v>18000</v>
@@ -9359,7 +9359,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G310" t="n">
-        <v>1.83669173717499</v>
+        <v>1.83669185638428</v>
       </c>
       <c r="H310" t="n">
         <v>82500</v>
@@ -9388,7 +9388,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G311" t="n">
-        <v>1.88941979408264</v>
+        <v>1.88941991329193</v>
       </c>
       <c r="H311" t="n">
         <v>34500</v>
@@ -9446,7 +9446,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G313" t="n">
-        <v>1.93335998058319</v>
+        <v>1.9333598613739</v>
       </c>
       <c r="H313" t="n">
         <v>18000</v>
@@ -9475,7 +9475,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G314" t="n">
-        <v>1.93335998058319</v>
+        <v>1.9333598613739</v>
       </c>
       <c r="H314" t="n">
         <v>6000</v>
@@ -9504,7 +9504,7 @@
         <v>2.25</v>
       </c>
       <c r="G315" t="n">
-        <v>1.97729980945587</v>
+        <v>1.97729969024658</v>
       </c>
       <c r="H315" t="n">
         <v>25500</v>
@@ -9562,7 +9562,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G317" t="n">
-        <v>2.07396793365479</v>
+        <v>2.07396769523621</v>
       </c>
       <c r="H317" t="n">
         <v>12000</v>
@@ -9591,7 +9591,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G318" t="n">
-        <v>2.09154367446899</v>
+        <v>2.09154391288757</v>
       </c>
       <c r="H318" t="n">
         <v>12000</v>
@@ -9649,7 +9649,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G320" t="n">
-        <v>2.14427208900452</v>
+        <v>2.14427185058594</v>
       </c>
       <c r="H320" t="n">
         <v>9000</v>
@@ -9678,7 +9678,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G321" t="n">
-        <v>2.14427208900452</v>
+        <v>2.14427185058594</v>
       </c>
       <c r="H321" t="n">
         <v>3000</v>
@@ -9707,7 +9707,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G322" t="n">
-        <v>2.10033202171326</v>
+        <v>2.10033178329468</v>
       </c>
       <c r="H322" t="n">
         <v>3000</v>
@@ -9736,7 +9736,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G323" t="n">
-        <v>2.10033202171326</v>
+        <v>2.10033178329468</v>
       </c>
       <c r="H323" t="n">
         <v>0</v>
@@ -9794,7 +9794,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G325" t="n">
-        <v>1.94214773178101</v>
+        <v>1.94214797019958</v>
       </c>
       <c r="H325" t="n">
         <v>7500</v>
@@ -9823,7 +9823,7 @@
         <v>2.25</v>
       </c>
       <c r="G326" t="n">
-        <v>1.97729980945587</v>
+        <v>1.97729969024658</v>
       </c>
       <c r="H326" t="n">
         <v>48000</v>
@@ -9852,7 +9852,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G327" t="n">
-        <v>1.9157840013504</v>
+        <v>1.91578388214111</v>
       </c>
       <c r="H327" t="n">
         <v>24000</v>
@@ -9881,7 +9881,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G328" t="n">
-        <v>1.88941979408264</v>
+        <v>1.88941991329193</v>
       </c>
       <c r="H328" t="n">
         <v>31500</v>
@@ -9939,7 +9939,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G330" t="n">
-        <v>2.03002786636353</v>
+        <v>2.03002762794495</v>
       </c>
       <c r="H330" t="n">
         <v>4500</v>
@@ -9968,7 +9968,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G331" t="n">
-        <v>1.99487566947937</v>
+        <v>1.99487555027008</v>
       </c>
       <c r="H331" t="n">
         <v>12000</v>
@@ -9997,7 +9997,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G332" t="n">
-        <v>1.99487566947937</v>
+        <v>1.99487555027008</v>
       </c>
       <c r="H332" t="n">
         <v>7500</v>
@@ -10026,7 +10026,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G333" t="n">
-        <v>1.99487566947937</v>
+        <v>1.99487555027008</v>
       </c>
       <c r="H333" t="n">
         <v>6000</v>
@@ -10055,7 +10055,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G334" t="n">
-        <v>2.03881573677063</v>
+        <v>2.03881597518921</v>
       </c>
       <c r="H334" t="n">
         <v>7500</v>
@@ -10113,7 +10113,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G336" t="n">
-        <v>2.02123951911926</v>
+        <v>2.02123975753784</v>
       </c>
       <c r="H336" t="n">
         <v>10500</v>
@@ -10229,7 +10229,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G340" t="n">
-        <v>2.03881573677063</v>
+        <v>2.03881597518921</v>
       </c>
       <c r="H340" t="n">
         <v>3000</v>
@@ -10345,7 +10345,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G344" t="n">
-        <v>1.9597235918045</v>
+        <v>1.95972394943237</v>
       </c>
       <c r="H344" t="n">
         <v>27000</v>
@@ -10432,7 +10432,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G347" t="n">
-        <v>1.96851181983948</v>
+        <v>1.96851170063019</v>
       </c>
       <c r="H347" t="n">
         <v>15000</v>
@@ -10461,7 +10461,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G348" t="n">
-        <v>1.93335998058319</v>
+        <v>1.9333598613739</v>
       </c>
       <c r="H348" t="n">
         <v>1500</v>
@@ -10490,7 +10490,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G349" t="n">
-        <v>1.90699589252472</v>
+        <v>1.90699577331543</v>
       </c>
       <c r="H349" t="n">
         <v>7500</v>
@@ -10519,7 +10519,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G350" t="n">
-        <v>1.90699589252472</v>
+        <v>1.90699577331543</v>
       </c>
       <c r="H350" t="n">
         <v>4500</v>
@@ -10548,7 +10548,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G351" t="n">
-        <v>1.83669173717499</v>
+        <v>1.83669185638428</v>
       </c>
       <c r="H351" t="n">
         <v>10500</v>
@@ -10577,7 +10577,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G352" t="n">
-        <v>1.81032776832581</v>
+        <v>1.81032752990723</v>
       </c>
       <c r="H352" t="n">
         <v>10500</v>
@@ -10606,7 +10606,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G353" t="n">
-        <v>1.88941979408264</v>
+        <v>1.88941991329193</v>
       </c>
       <c r="H353" t="n">
         <v>7500</v>
@@ -10635,7 +10635,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G354" t="n">
-        <v>1.85426783561707</v>
+        <v>1.85426771640778</v>
       </c>
       <c r="H354" t="n">
         <v>13500</v>
@@ -10722,7 +10722,7 @@
         <v>2.25</v>
       </c>
       <c r="G357" t="n">
-        <v>1.97729980945587</v>
+        <v>1.97729969024658</v>
       </c>
       <c r="H357" t="n">
         <v>7500</v>
@@ -10751,7 +10751,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G358" t="n">
-        <v>2.03881573677063</v>
+        <v>2.03881597518921</v>
       </c>
       <c r="H358" t="n">
         <v>10500</v>
@@ -10780,7 +10780,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G359" t="n">
-        <v>2.03002786636353</v>
+        <v>2.03002762794495</v>
       </c>
       <c r="H359" t="n">
         <v>7500</v>
@@ -10809,7 +10809,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G360" t="n">
-        <v>2.03002786636353</v>
+        <v>2.03002762794495</v>
       </c>
       <c r="H360" t="n">
         <v>0</v>
@@ -10838,7 +10838,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G361" t="n">
-        <v>1.99487566947937</v>
+        <v>1.99487555027008</v>
       </c>
       <c r="H361" t="n">
         <v>15000</v>
@@ -10867,7 +10867,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G362" t="n">
-        <v>1.99487566947937</v>
+        <v>1.99487555027008</v>
       </c>
       <c r="H362" t="n">
         <v>6000</v>
@@ -10896,7 +10896,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G363" t="n">
-        <v>1.96851181983948</v>
+        <v>1.96851170063019</v>
       </c>
       <c r="H363" t="n">
         <v>3000</v>
@@ -10983,7 +10983,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G366" t="n">
-        <v>1.93335998058319</v>
+        <v>1.9333598613739</v>
       </c>
       <c r="H366" t="n">
         <v>13500</v>
@@ -11012,7 +11012,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G367" t="n">
-        <v>1.93335998058319</v>
+        <v>1.9333598613739</v>
       </c>
       <c r="H367" t="n">
         <v>1500</v>
@@ -11070,7 +11070,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G369" t="n">
-        <v>1.98608791828156</v>
+        <v>1.98608779907227</v>
       </c>
       <c r="H369" t="n">
         <v>25500</v>
@@ -11099,7 +11099,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G370" t="n">
-        <v>1.93335998058319</v>
+        <v>1.9333598613739</v>
       </c>
       <c r="H370" t="n">
         <v>6000</v>
@@ -11128,7 +11128,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G371" t="n">
-        <v>1.93335998058319</v>
+        <v>1.9333598613739</v>
       </c>
       <c r="H371" t="n">
         <v>1500</v>
@@ -11157,7 +11157,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G372" t="n">
-        <v>1.98608791828156</v>
+        <v>1.98608779907227</v>
       </c>
       <c r="H372" t="n">
         <v>7500</v>
@@ -11244,7 +11244,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G375" t="n">
-        <v>1.85426783561707</v>
+        <v>1.85426771640778</v>
       </c>
       <c r="H375" t="n">
         <v>15000</v>
@@ -11273,7 +11273,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G376" t="n">
-        <v>1.88063168525696</v>
+        <v>1.88063192367554</v>
       </c>
       <c r="H376" t="n">
         <v>9000</v>
@@ -11302,7 +11302,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G377" t="n">
-        <v>1.88063168525696</v>
+        <v>1.88063192367554</v>
       </c>
       <c r="H377" t="n">
         <v>3000</v>
@@ -11331,7 +11331,7 @@
         <v>2.25</v>
       </c>
       <c r="G378" t="n">
-        <v>1.97729980945587</v>
+        <v>1.97729969024658</v>
       </c>
       <c r="H378" t="n">
         <v>16500</v>
@@ -11360,7 +11360,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G379" t="n">
-        <v>1.93335998058319</v>
+        <v>1.9333598613739</v>
       </c>
       <c r="H379" t="n">
         <v>3000</v>
@@ -11389,7 +11389,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G380" t="n">
-        <v>1.62577986717224</v>
+        <v>1.62577998638153</v>
       </c>
       <c r="H380" t="n">
         <v>43500</v>
@@ -11418,7 +11418,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G381" t="n">
-        <v>1.74002385139465</v>
+        <v>1.74002397060394</v>
       </c>
       <c r="H381" t="n">
         <v>34500</v>
@@ -11447,7 +11447,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G382" t="n">
-        <v>1.80153965950012</v>
+        <v>1.80153977870941</v>
       </c>
       <c r="H382" t="n">
         <v>21000</v>
@@ -11476,7 +11476,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G383" t="n">
-        <v>1.86305558681488</v>
+        <v>1.86305582523346</v>
       </c>
       <c r="H383" t="n">
         <v>21000</v>
@@ -11505,7 +11505,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G384" t="n">
-        <v>1.86305558681488</v>
+        <v>1.86305582523346</v>
       </c>
       <c r="H384" t="n">
         <v>1500</v>
@@ -11534,7 +11534,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G385" t="n">
-        <v>1.88063168525696</v>
+        <v>1.88063192367554</v>
       </c>
       <c r="H385" t="n">
         <v>13500</v>
@@ -11563,7 +11563,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G386" t="n">
-        <v>1.99487566947937</v>
+        <v>1.99487555027008</v>
       </c>
       <c r="H386" t="n">
         <v>15000</v>
@@ -11592,7 +11592,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G387" t="n">
-        <v>1.89820802211761</v>
+        <v>1.89820790290833</v>
       </c>
       <c r="H387" t="n">
         <v>28500</v>
@@ -11621,7 +11621,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G388" t="n">
-        <v>1.99487566947937</v>
+        <v>1.99487555027008</v>
       </c>
       <c r="H388" t="n">
         <v>9000</v>
@@ -11650,7 +11650,7 @@
         <v>2.25</v>
       </c>
       <c r="G389" t="n">
-        <v>1.97729980945587</v>
+        <v>1.97729969024658</v>
       </c>
       <c r="H389" t="n">
         <v>6000</v>
@@ -11679,7 +11679,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G390" t="n">
-        <v>1.93335998058319</v>
+        <v>1.9333598613739</v>
       </c>
       <c r="H390" t="n">
         <v>1500</v>
@@ -11708,7 +11708,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G391" t="n">
-        <v>1.96851181983948</v>
+        <v>1.96851170063019</v>
       </c>
       <c r="H391" t="n">
         <v>9000</v>
@@ -11737,7 +11737,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G392" t="n">
-        <v>1.98608791828156</v>
+        <v>1.98608779907227</v>
       </c>
       <c r="H392" t="n">
         <v>6000</v>
@@ -11766,7 +11766,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G393" t="n">
-        <v>1.98608791828156</v>
+        <v>1.98608779907227</v>
       </c>
       <c r="H393" t="n">
         <v>0</v>
@@ -11824,7 +11824,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G395" t="n">
-        <v>1.99487566947937</v>
+        <v>1.99487555027008</v>
       </c>
       <c r="H395" t="n">
         <v>31500</v>
@@ -11940,7 +11940,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G399" t="n">
-        <v>1.98608791828156</v>
+        <v>1.98608779907227</v>
       </c>
       <c r="H399" t="n">
         <v>6000</v>
@@ -11969,7 +11969,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G400" t="n">
-        <v>2.02123951911926</v>
+        <v>2.02123975753784</v>
       </c>
       <c r="H400" t="n">
         <v>10500</v>
@@ -12056,7 +12056,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G403" t="n">
-        <v>1.93335998058319</v>
+        <v>1.9333598613739</v>
       </c>
       <c r="H403" t="n">
         <v>7500</v>
@@ -12085,7 +12085,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G404" t="n">
-        <v>1.96851181983948</v>
+        <v>1.96851170063019</v>
       </c>
       <c r="H404" t="n">
         <v>22500</v>
@@ -12114,7 +12114,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G405" t="n">
-        <v>1.98608791828156</v>
+        <v>1.98608779907227</v>
       </c>
       <c r="H405" t="n">
         <v>16500</v>
@@ -12143,7 +12143,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G406" t="n">
-        <v>1.98608791828156</v>
+        <v>1.98608779907227</v>
       </c>
       <c r="H406" t="n">
         <v>0</v>
@@ -12172,7 +12172,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G407" t="n">
-        <v>1.84547960758209</v>
+        <v>1.84547984600067</v>
       </c>
       <c r="H407" t="n">
         <v>64500</v>
@@ -12201,7 +12201,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G408" t="n">
-        <v>1.89820802211761</v>
+        <v>1.89820790290833</v>
       </c>
       <c r="H408" t="n">
         <v>6000</v>
@@ -12230,7 +12230,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G409" t="n">
-        <v>1.88941979408264</v>
+        <v>1.88941991329193</v>
       </c>
       <c r="H409" t="n">
         <v>6000</v>
@@ -12259,7 +12259,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G410" t="n">
-        <v>1.88941979408264</v>
+        <v>1.88941991329193</v>
       </c>
       <c r="H410" t="n">
         <v>0</v>
@@ -12288,7 +12288,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G411" t="n">
-        <v>1.87184405326843</v>
+        <v>1.87184393405914</v>
       </c>
       <c r="H411" t="n">
         <v>4500</v>
@@ -12317,7 +12317,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G412" t="n">
-        <v>1.88063168525696</v>
+        <v>1.88063192367554</v>
       </c>
       <c r="H412" t="n">
         <v>9000</v>
@@ -12346,7 +12346,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G413" t="n">
-        <v>1.88063168525696</v>
+        <v>1.88063192367554</v>
       </c>
       <c r="H413" t="n">
         <v>0</v>
@@ -12375,7 +12375,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G414" t="n">
-        <v>1.83669173717499</v>
+        <v>1.83669185638428</v>
       </c>
       <c r="H414" t="n">
         <v>1500</v>
@@ -12462,7 +12462,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G417" t="n">
-        <v>1.86305558681488</v>
+        <v>1.86305582523346</v>
       </c>
       <c r="H417" t="n">
         <v>6000</v>
@@ -12491,7 +12491,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G418" t="n">
-        <v>1.81032776832581</v>
+        <v>1.81032752990723</v>
       </c>
       <c r="H418" t="n">
         <v>6000</v>
@@ -12520,7 +12520,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G419" t="n">
-        <v>1.9157840013504</v>
+        <v>1.91578388214111</v>
       </c>
       <c r="H419" t="n">
         <v>18000</v>
@@ -12549,7 +12549,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G420" t="n">
-        <v>1.89820802211761</v>
+        <v>1.89820790290833</v>
       </c>
       <c r="H420" t="n">
         <v>6000</v>
@@ -12578,7 +12578,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G421" t="n">
-        <v>1.9157840013504</v>
+        <v>1.91578388214111</v>
       </c>
       <c r="H421" t="n">
         <v>1500</v>
@@ -12607,7 +12607,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G422" t="n">
-        <v>1.80153965950012</v>
+        <v>1.80153977870941</v>
       </c>
       <c r="H422" t="n">
         <v>25500</v>
@@ -12694,7 +12694,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G425" t="n">
-        <v>1.74002385139465</v>
+        <v>1.74002397060394</v>
       </c>
       <c r="H425" t="n">
         <v>3000</v>
@@ -12752,7 +12752,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G427" t="n">
-        <v>1.76638782024384</v>
+        <v>1.76638793945312</v>
       </c>
       <c r="H427" t="n">
         <v>4500</v>
@@ -12781,7 +12781,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G428" t="n">
-        <v>1.76638782024384</v>
+        <v>1.76638793945312</v>
       </c>
       <c r="H428" t="n">
         <v>3000</v>
@@ -12810,7 +12810,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G429" t="n">
-        <v>1.76638782024384</v>
+        <v>1.76638793945312</v>
       </c>
       <c r="H429" t="n">
         <v>3000</v>
@@ -12839,7 +12839,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G430" t="n">
-        <v>1.76638782024384</v>
+        <v>1.76638793945312</v>
       </c>
       <c r="H430" t="n">
         <v>4500</v>
@@ -12868,7 +12868,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G431" t="n">
-        <v>1.84547960758209</v>
+        <v>1.84547984600067</v>
       </c>
       <c r="H431" t="n">
         <v>6000</v>
@@ -12926,7 +12926,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G433" t="n">
-        <v>1.86305558681488</v>
+        <v>1.86305582523346</v>
       </c>
       <c r="H433" t="n">
         <v>7500</v>
@@ -12955,7 +12955,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G434" t="n">
-        <v>1.86305558681488</v>
+        <v>1.86305582523346</v>
       </c>
       <c r="H434" t="n">
         <v>0</v>
@@ -12984,7 +12984,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G435" t="n">
-        <v>1.86305558681488</v>
+        <v>1.86305582523346</v>
       </c>
       <c r="H435" t="n">
         <v>3000</v>
@@ -13013,7 +13013,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G436" t="n">
-        <v>1.88063168525696</v>
+        <v>1.88063192367554</v>
       </c>
       <c r="H436" t="n">
         <v>3000</v>
@@ -13042,7 +13042,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G437" t="n">
-        <v>1.85426783561707</v>
+        <v>1.85426771640778</v>
       </c>
       <c r="H437" t="n">
         <v>4500</v>
@@ -13071,7 +13071,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G438" t="n">
-        <v>1.85426783561707</v>
+        <v>1.85426771640778</v>
       </c>
       <c r="H438" t="n">
         <v>0</v>
@@ -13158,7 +13158,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G441" t="n">
-        <v>1.88063168525696</v>
+        <v>1.88063192367554</v>
       </c>
       <c r="H441" t="n">
         <v>3000</v>
@@ -13187,7 +13187,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G442" t="n">
-        <v>1.88063168525696</v>
+        <v>1.88063192367554</v>
       </c>
       <c r="H442" t="n">
         <v>0</v>
@@ -13245,7 +13245,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G444" t="n">
-        <v>1.86305558681488</v>
+        <v>1.86305582523346</v>
       </c>
       <c r="H444" t="n">
         <v>1500</v>
@@ -13332,7 +13332,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G447" t="n">
-        <v>1.76638782024384</v>
+        <v>1.76638793945312</v>
       </c>
       <c r="H447" t="n">
         <v>15000</v>
@@ -13448,7 +13448,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G451" t="n">
-        <v>1.74002385139465</v>
+        <v>1.74002397060394</v>
       </c>
       <c r="H451" t="n">
         <v>4500</v>
@@ -13477,7 +13477,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G452" t="n">
-        <v>1.72684180736542</v>
+        <v>1.72684192657471</v>
       </c>
       <c r="H452" t="n">
         <v>3000</v>
@@ -13564,7 +13564,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G455" t="n">
-        <v>1.70926582813263</v>
+        <v>1.70926594734192</v>
       </c>
       <c r="H455" t="n">
         <v>9000</v>
@@ -13593,7 +13593,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G456" t="n">
-        <v>1.70926582813263</v>
+        <v>1.70926594734192</v>
       </c>
       <c r="H456" t="n">
         <v>0</v>
@@ -13622,7 +13622,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G457" t="n">
-        <v>1.70926582813263</v>
+        <v>1.70926594734192</v>
       </c>
       <c r="H457" t="n">
         <v>0</v>
@@ -13651,7 +13651,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G458" t="n">
-        <v>1.70926582813263</v>
+        <v>1.70926594734192</v>
       </c>
       <c r="H458" t="n">
         <v>0</v>
@@ -13680,7 +13680,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G459" t="n">
-        <v>1.70926582813263</v>
+        <v>1.70926594734192</v>
       </c>
       <c r="H459" t="n">
         <v>0</v>
@@ -13709,7 +13709,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G460" t="n">
-        <v>1.67411386966705</v>
+        <v>1.67411363124847</v>
       </c>
       <c r="H460" t="n">
         <v>1500</v>
@@ -13738,7 +13738,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G461" t="n">
-        <v>1.67411386966705</v>
+        <v>1.67411363124847</v>
       </c>
       <c r="H461" t="n">
         <v>6000</v>
@@ -13767,7 +13767,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G462" t="n">
-        <v>1.67411386966705</v>
+        <v>1.67411363124847</v>
       </c>
       <c r="H462" t="n">
         <v>1500</v>
@@ -13796,7 +13796,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G463" t="n">
-        <v>1.66093182563782</v>
+        <v>1.66093170642853</v>
       </c>
       <c r="H463" t="n">
         <v>1500</v>
@@ -13825,7 +13825,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G464" t="n">
-        <v>1.66093182563782</v>
+        <v>1.66093170642853</v>
       </c>
       <c r="H464" t="n">
         <v>0</v>
@@ -13883,7 +13883,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G466" t="n">
-        <v>1.59941601753235</v>
+        <v>1.59941589832306</v>
       </c>
       <c r="H466" t="n">
         <v>6000</v>
@@ -13970,7 +13970,7 @@
         <v>1.875</v>
       </c>
       <c r="G469" t="n">
-        <v>1.64774990081787</v>
+        <v>1.64774978160858</v>
       </c>
       <c r="H469" t="n">
         <v>3000</v>
@@ -13999,7 +13999,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G470" t="n">
-        <v>1.66093182563782</v>
+        <v>1.66093170642853</v>
       </c>
       <c r="H470" t="n">
         <v>3000</v>
@@ -14057,7 +14057,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G472" t="n">
-        <v>1.64335584640503</v>
+        <v>1.64335596561432</v>
       </c>
       <c r="H472" t="n">
         <v>4500</v>
@@ -14086,7 +14086,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G473" t="n">
-        <v>1.64335584640503</v>
+        <v>1.64335596561432</v>
       </c>
       <c r="H473" t="n">
         <v>0</v>
@@ -14289,7 +14289,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G480" t="n">
-        <v>1.63017380237579</v>
+        <v>1.63017404079437</v>
       </c>
       <c r="H480" t="n">
         <v>3000</v>
@@ -14347,7 +14347,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G482" t="n">
-        <v>1.67411386966705</v>
+        <v>1.67411363124847</v>
       </c>
       <c r="H482" t="n">
         <v>4500</v>
@@ -14376,7 +14376,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G483" t="n">
-        <v>1.64335584640503</v>
+        <v>1.64335596561432</v>
       </c>
       <c r="H483" t="n">
         <v>3000</v>
@@ -14405,7 +14405,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G484" t="n">
-        <v>1.74881196022034</v>
+        <v>1.74881184101105</v>
       </c>
       <c r="H484" t="n">
         <v>19500</v>
@@ -14434,7 +14434,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G485" t="n">
-        <v>1.81032776832581</v>
+        <v>1.81032752990723</v>
       </c>
       <c r="H485" t="n">
         <v>6000</v>
@@ -14463,7 +14463,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G486" t="n">
-        <v>1.87184405326843</v>
+        <v>1.87184393405914</v>
       </c>
       <c r="H486" t="n">
         <v>25500</v>
@@ -14492,7 +14492,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G487" t="n">
-        <v>1.93335998058319</v>
+        <v>1.9333598613739</v>
       </c>
       <c r="H487" t="n">
         <v>33000</v>
@@ -14579,7 +14579,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G490" t="n">
-        <v>2.03881573677063</v>
+        <v>2.03881597518921</v>
       </c>
       <c r="H490" t="n">
         <v>28500</v>
@@ -14608,7 +14608,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G491" t="n">
-        <v>2.03881573677063</v>
+        <v>2.03881597518921</v>
       </c>
       <c r="H491" t="n">
         <v>0</v>
@@ -14637,7 +14637,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G492" t="n">
-        <v>1.99487566947937</v>
+        <v>1.99487555027008</v>
       </c>
       <c r="H492" t="n">
         <v>3000</v>
@@ -14666,7 +14666,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G493" t="n">
-        <v>2.02123951911926</v>
+        <v>2.02123975753784</v>
       </c>
       <c r="H493" t="n">
         <v>42000</v>
@@ -14695,7 +14695,7 @@
         <v>2.25</v>
       </c>
       <c r="G494" t="n">
-        <v>1.97729980945587</v>
+        <v>1.97729969024658</v>
       </c>
       <c r="H494" t="n">
         <v>4500</v>
@@ -14724,7 +14724,7 @@
         <v>2.25</v>
       </c>
       <c r="G495" t="n">
-        <v>1.97729980945587</v>
+        <v>1.97729969024658</v>
       </c>
       <c r="H495" t="n">
         <v>0</v>
@@ -14753,7 +14753,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G496" t="n">
-        <v>1.93335998058319</v>
+        <v>1.9333598613739</v>
       </c>
       <c r="H496" t="n">
         <v>6000</v>
@@ -14840,7 +14840,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G499" t="n">
-        <v>1.78396379947662</v>
+        <v>1.78396368026733</v>
       </c>
       <c r="H499" t="n">
         <v>12000</v>
@@ -14869,7 +14869,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G500" t="n">
-        <v>1.78396379947662</v>
+        <v>1.78396368026733</v>
       </c>
       <c r="H500" t="n">
         <v>3000</v>
@@ -14898,7 +14898,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G501" t="n">
-        <v>1.78396379947662</v>
+        <v>1.78396368026733</v>
       </c>
       <c r="H501" t="n">
         <v>0</v>
@@ -14927,7 +14927,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G502" t="n">
-        <v>1.74881196022034</v>
+        <v>1.74881184101105</v>
       </c>
       <c r="H502" t="n">
         <v>4500</v>
@@ -14956,7 +14956,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G503" t="n">
-        <v>1.74881196022034</v>
+        <v>1.74881184101105</v>
       </c>
       <c r="H503" t="n">
         <v>1500</v>
@@ -14985,7 +14985,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G504" t="n">
-        <v>1.74881196022034</v>
+        <v>1.74881184101105</v>
       </c>
       <c r="H504" t="n">
         <v>1500</v>
@@ -15072,7 +15072,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G507" t="n">
-        <v>1.78396379947662</v>
+        <v>1.78396368026733</v>
       </c>
       <c r="H507" t="n">
         <v>3000</v>
@@ -15101,7 +15101,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G508" t="n">
-        <v>1.78396379947662</v>
+        <v>1.78396368026733</v>
       </c>
       <c r="H508" t="n">
         <v>1500</v>
@@ -15130,7 +15130,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G509" t="n">
-        <v>1.78396379947662</v>
+        <v>1.78396368026733</v>
       </c>
       <c r="H509" t="n">
         <v>1500</v>
@@ -15217,7 +15217,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G512" t="n">
-        <v>1.78396379947662</v>
+        <v>1.78396368026733</v>
       </c>
       <c r="H512" t="n">
         <v>6000</v>
@@ -15246,7 +15246,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G513" t="n">
-        <v>1.81032776832581</v>
+        <v>1.81032752990723</v>
       </c>
       <c r="H513" t="n">
         <v>3000</v>
@@ -15275,7 +15275,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G514" t="n">
-        <v>1.78396379947662</v>
+        <v>1.78396368026733</v>
       </c>
       <c r="H514" t="n">
         <v>4500</v>
@@ -15304,7 +15304,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G515" t="n">
-        <v>1.78396379947662</v>
+        <v>1.78396368026733</v>
       </c>
       <c r="H515" t="n">
         <v>1500</v>
@@ -15333,7 +15333,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G516" t="n">
-        <v>1.71366000175476</v>
+        <v>1.71365976333618</v>
       </c>
       <c r="H516" t="n">
         <v>6000</v>
@@ -15362,7 +15362,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G517" t="n">
-        <v>1.71366000175476</v>
+        <v>1.71365976333618</v>
       </c>
       <c r="H517" t="n">
         <v>1500</v>
@@ -15391,7 +15391,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G518" t="n">
-        <v>1.71366000175476</v>
+        <v>1.71365976333618</v>
       </c>
       <c r="H518" t="n">
         <v>0</v>
@@ -15420,7 +15420,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G519" t="n">
-        <v>1.76638782024384</v>
+        <v>1.76638793945312</v>
       </c>
       <c r="H519" t="n">
         <v>3000</v>
@@ -15449,7 +15449,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G520" t="n">
-        <v>1.79275178909302</v>
+        <v>1.79275190830231</v>
       </c>
       <c r="H520" t="n">
         <v>4500</v>
@@ -15478,7 +15478,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G521" t="n">
-        <v>1.81032776832581</v>
+        <v>1.81032752990723</v>
       </c>
       <c r="H521" t="n">
         <v>4500</v>
@@ -15507,7 +15507,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G522" t="n">
-        <v>1.76638782024384</v>
+        <v>1.76638793945312</v>
       </c>
       <c r="H522" t="n">
         <v>9000</v>
@@ -15565,7 +15565,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G524" t="n">
-        <v>1.70926582813263</v>
+        <v>1.70926594734192</v>
       </c>
       <c r="H524" t="n">
         <v>1500</v>
@@ -15594,7 +15594,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G525" t="n">
-        <v>1.62577986717224</v>
+        <v>1.62577998638153</v>
       </c>
       <c r="H525" t="n">
         <v>6000</v>
@@ -15623,7 +15623,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G526" t="n">
-        <v>1.54229390621185</v>
+        <v>1.54229378700256</v>
       </c>
       <c r="H526" t="n">
         <v>19500</v>
@@ -15739,7 +15739,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G530" t="n">
-        <v>1.48517191410065</v>
+        <v>1.48517179489136</v>
       </c>
       <c r="H530" t="n">
         <v>7500</v>
@@ -15768,7 +15768,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G531" t="n">
-        <v>1.51592981815338</v>
+        <v>1.51592993736267</v>
       </c>
       <c r="H531" t="n">
         <v>1500</v>
@@ -15797,7 +15797,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G532" t="n">
-        <v>1.51592981815338</v>
+        <v>1.51592993736267</v>
       </c>
       <c r="H532" t="n">
         <v>0</v>
@@ -15826,7 +15826,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G533" t="n">
-        <v>1.51592981815338</v>
+        <v>1.51592993736267</v>
       </c>
       <c r="H533" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G534" t="n">
-        <v>1.48517191410065</v>
+        <v>1.48517179489136</v>
       </c>
       <c r="H534" t="n">
         <v>1500</v>
@@ -15884,7 +15884,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G535" t="n">
-        <v>1.48517191410065</v>
+        <v>1.48517179489136</v>
       </c>
       <c r="H535" t="n">
         <v>0</v>
@@ -16116,7 +16116,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G543" t="n">
-        <v>1.49395978450775</v>
+        <v>1.49395990371704</v>
       </c>
       <c r="H543" t="n">
         <v>1500</v>
@@ -16203,7 +16203,7 @@
         <v>1.875</v>
       </c>
       <c r="G546" t="n">
-        <v>1.64774990081787</v>
+        <v>1.64774978160858</v>
       </c>
       <c r="H546" t="n">
         <v>18000</v>
@@ -16232,7 +16232,7 @@
         <v>1.875</v>
       </c>
       <c r="G547" t="n">
-        <v>1.64774990081787</v>
+        <v>1.64774978160858</v>
       </c>
       <c r="H547" t="n">
         <v>0</v>
@@ -16348,7 +16348,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G551" t="n">
-        <v>1.72684180736542</v>
+        <v>1.72684192657471</v>
       </c>
       <c r="H551" t="n">
         <v>1500</v>
@@ -16551,7 +16551,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G558" t="n">
-        <v>1.72684180736542</v>
+        <v>1.72684192657471</v>
       </c>
       <c r="H558" t="n">
         <v>13500</v>
@@ -16580,7 +16580,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G559" t="n">
-        <v>1.72684180736542</v>
+        <v>1.72684192657471</v>
       </c>
       <c r="H559" t="n">
         <v>0</v>
@@ -16783,7 +16783,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G566" t="n">
-        <v>1.62577986717224</v>
+        <v>1.62577998638153</v>
       </c>
       <c r="H566" t="n">
         <v>4500</v>
@@ -16812,7 +16812,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G567" t="n">
-        <v>1.62577986717224</v>
+        <v>1.62577998638153</v>
       </c>
       <c r="H567" t="n">
         <v>0</v>
@@ -16841,7 +16841,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G568" t="n">
-        <v>1.62577986717224</v>
+        <v>1.62577998638153</v>
       </c>
       <c r="H568" t="n">
         <v>0</v>
@@ -16928,7 +16928,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G571" t="n">
-        <v>1.66093182563782</v>
+        <v>1.66093170642853</v>
       </c>
       <c r="H571" t="n">
         <v>1500</v>
@@ -16957,7 +16957,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G572" t="n">
-        <v>1.67411386966705</v>
+        <v>1.67411363124847</v>
       </c>
       <c r="H572" t="n">
         <v>1500</v>
@@ -17305,7 +17305,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G584" t="n">
-        <v>1.62577986717224</v>
+        <v>1.62577998638153</v>
       </c>
       <c r="H584" t="n">
         <v>1500</v>
@@ -17334,7 +17334,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G585" t="n">
-        <v>1.62577986717224</v>
+        <v>1.62577998638153</v>
       </c>
       <c r="H585" t="n">
         <v>0</v>
@@ -17363,7 +17363,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G586" t="n">
-        <v>1.62577986717224</v>
+        <v>1.62577998638153</v>
       </c>
       <c r="H586" t="n">
         <v>0</v>
@@ -17392,7 +17392,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G587" t="n">
-        <v>1.62577986717224</v>
+        <v>1.62577998638153</v>
       </c>
       <c r="H587" t="n">
         <v>1500</v>
@@ -17421,7 +17421,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G588" t="n">
-        <v>1.62577986717224</v>
+        <v>1.62577998638153</v>
       </c>
       <c r="H588" t="n">
         <v>0</v>
@@ -17450,7 +17450,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G589" t="n">
-        <v>1.62577986717224</v>
+        <v>1.62577998638153</v>
       </c>
       <c r="H589" t="n">
         <v>1500</v>
@@ -17508,7 +17508,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G591" t="n">
-        <v>1.58623373508453</v>
+        <v>1.58623385429382</v>
       </c>
       <c r="H591" t="n">
         <v>9000</v>
@@ -17566,7 +17566,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G593" t="n">
-        <v>1.55547571182251</v>
+        <v>1.5554758310318</v>
       </c>
       <c r="H593" t="n">
         <v>13500</v>
@@ -17595,7 +17595,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G594" t="n">
-        <v>1.55986976623535</v>
+        <v>1.55986988544464</v>
       </c>
       <c r="H594" t="n">
         <v>15000</v>
@@ -17624,7 +17624,7 @@
         <v>1.875</v>
       </c>
       <c r="G595" t="n">
-        <v>1.64774990081787</v>
+        <v>1.64774978160858</v>
       </c>
       <c r="H595" t="n">
         <v>7500</v>
@@ -17653,7 +17653,7 @@
         <v>1.875</v>
       </c>
       <c r="G596" t="n">
-        <v>1.64774990081787</v>
+        <v>1.64774978160858</v>
       </c>
       <c r="H596" t="n">
         <v>0</v>
@@ -17769,7 +17769,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G600" t="n">
-        <v>1.59941601753235</v>
+        <v>1.59941589832306</v>
       </c>
       <c r="H600" t="n">
         <v>3000</v>
@@ -17798,7 +17798,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G601" t="n">
-        <v>1.59941601753235</v>
+        <v>1.59941589832306</v>
       </c>
       <c r="H601" t="n">
         <v>0</v>
@@ -17827,7 +17827,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G602" t="n">
-        <v>1.59941601753235</v>
+        <v>1.59941589832306</v>
       </c>
       <c r="H602" t="n">
         <v>0</v>
@@ -18001,7 +18001,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G608" t="n">
-        <v>1.58183991909027</v>
+        <v>1.58183979988098</v>
       </c>
       <c r="H608" t="n">
         <v>12000</v>
@@ -18030,7 +18030,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G609" t="n">
-        <v>1.61259794235229</v>
+        <v>1.61259782314301</v>
       </c>
       <c r="H609" t="n">
         <v>1500</v>
@@ -18117,7 +18117,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G612" t="n">
-        <v>1.60820388793945</v>
+        <v>1.60820376873016</v>
       </c>
       <c r="H612" t="n">
         <v>1500</v>
@@ -18262,7 +18262,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G617" t="n">
-        <v>1.7532057762146</v>
+        <v>1.75320589542389</v>
       </c>
       <c r="H617" t="n">
         <v>114000</v>
@@ -18320,7 +18320,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G619" t="n">
-        <v>1.72244775295258</v>
+        <v>1.72244787216187</v>
       </c>
       <c r="H619" t="n">
         <v>10500</v>
@@ -18349,7 +18349,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G620" t="n">
-        <v>1.71805393695831</v>
+        <v>1.71805381774902</v>
       </c>
       <c r="H620" t="n">
         <v>1500</v>
@@ -18436,7 +18436,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G623" t="n">
-        <v>1.69608378410339</v>
+        <v>1.69608390331268</v>
       </c>
       <c r="H623" t="n">
         <v>1500</v>
@@ -18494,7 +18494,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G625" t="n">
-        <v>1.70047783851624</v>
+        <v>1.70047771930695</v>
       </c>
       <c r="H625" t="n">
         <v>6000</v>
@@ -18523,7 +18523,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G626" t="n">
-        <v>1.70047783851624</v>
+        <v>1.70047771930695</v>
       </c>
       <c r="H626" t="n">
         <v>7500</v>
@@ -18581,7 +18581,7 @@
         <v>2.25</v>
       </c>
       <c r="G628" t="n">
-        <v>1.97729980945587</v>
+        <v>1.97729969024658</v>
       </c>
       <c r="H628" t="n">
         <v>303000</v>
@@ -18610,7 +18610,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G629" t="n">
-        <v>1.88063168525696</v>
+        <v>1.88063192367554</v>
       </c>
       <c r="H629" t="n">
         <v>39000</v>
@@ -18639,7 +18639,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G630" t="n">
-        <v>1.88941979408264</v>
+        <v>1.88941991329193</v>
       </c>
       <c r="H630" t="n">
         <v>19500</v>
@@ -18668,7 +18668,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G631" t="n">
-        <v>1.81032776832581</v>
+        <v>1.81032752990723</v>
       </c>
       <c r="H631" t="n">
         <v>24000</v>
@@ -18697,7 +18697,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G632" t="n">
-        <v>1.86305558681488</v>
+        <v>1.86305582523346</v>
       </c>
       <c r="H632" t="n">
         <v>33000</v>
@@ -18755,7 +18755,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G634" t="n">
-        <v>1.81032776832581</v>
+        <v>1.81032752990723</v>
       </c>
       <c r="H634" t="n">
         <v>21000</v>
@@ -18813,7 +18813,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G636" t="n">
-        <v>1.71805393695831</v>
+        <v>1.71805381774902</v>
       </c>
       <c r="H636" t="n">
         <v>30000</v>
@@ -18842,7 +18842,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G637" t="n">
-        <v>1.71366000175476</v>
+        <v>1.71365976333618</v>
       </c>
       <c r="H637" t="n">
         <v>24000</v>
@@ -18900,7 +18900,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G639" t="n">
-        <v>1.64335584640503</v>
+        <v>1.64335596561432</v>
       </c>
       <c r="H639" t="n">
         <v>19500</v>
@@ -18929,7 +18929,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G640" t="n">
-        <v>1.60820388793945</v>
+        <v>1.60820376873016</v>
       </c>
       <c r="H640" t="n">
         <v>33000</v>
@@ -18958,7 +18958,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G641" t="n">
-        <v>1.62577986717224</v>
+        <v>1.62577998638153</v>
       </c>
       <c r="H641" t="n">
         <v>1500</v>
@@ -19045,7 +19045,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G644" t="n">
-        <v>1.66093182563782</v>
+        <v>1.66093170642853</v>
       </c>
       <c r="H644" t="n">
         <v>9000</v>
@@ -19074,7 +19074,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G645" t="n">
-        <v>1.66093182563782</v>
+        <v>1.66093170642853</v>
       </c>
       <c r="H645" t="n">
         <v>0</v>
@@ -19161,7 +19161,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G648" t="n">
-        <v>1.69608378410339</v>
+        <v>1.69608390331268</v>
       </c>
       <c r="H648" t="n">
         <v>1500</v>
@@ -19219,7 +19219,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G650" t="n">
-        <v>1.74881196022034</v>
+        <v>1.74881184101105</v>
       </c>
       <c r="H650" t="n">
         <v>3000</v>
@@ -19248,7 +19248,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G651" t="n">
-        <v>1.71366000175476</v>
+        <v>1.71365976333618</v>
       </c>
       <c r="H651" t="n">
         <v>1500</v>
@@ -19335,7 +19335,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G654" t="n">
-        <v>1.74002385139465</v>
+        <v>1.74002397060394</v>
       </c>
       <c r="H654" t="n">
         <v>1500</v>
@@ -19364,7 +19364,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G655" t="n">
-        <v>1.74002385139465</v>
+        <v>1.74002397060394</v>
       </c>
       <c r="H655" t="n">
         <v>0</v>
@@ -19422,7 +19422,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G657" t="n">
-        <v>1.70487201213837</v>
+        <v>1.70487189292908</v>
       </c>
       <c r="H657" t="n">
         <v>10500</v>
@@ -19451,7 +19451,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G658" t="n">
-        <v>1.79275178909302</v>
+        <v>1.79275190830231</v>
       </c>
       <c r="H658" t="n">
         <v>108000</v>
@@ -19654,7 +19654,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G665" t="n">
-        <v>1.67888343334198</v>
+        <v>1.67888355255127</v>
       </c>
       <c r="H665" t="n">
         <v>13500</v>
@@ -19741,7 +19741,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G668" t="n">
-        <v>1.67888343334198</v>
+        <v>1.67888355255127</v>
       </c>
       <c r="H668" t="n">
         <v>4500</v>
@@ -19770,7 +19770,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G669" t="n">
-        <v>1.66985726356506</v>
+        <v>1.66985738277435</v>
       </c>
       <c r="H669" t="n">
         <v>3000</v>
@@ -19799,7 +19799,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G670" t="n">
-        <v>1.66083109378815</v>
+        <v>1.66083097457886</v>
       </c>
       <c r="H670" t="n">
         <v>30000</v>
@@ -19886,7 +19886,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G673" t="n">
-        <v>1.64277863502502</v>
+        <v>1.64277851581573</v>
       </c>
       <c r="H673" t="n">
         <v>4500</v>
@@ -19915,7 +19915,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G674" t="n">
-        <v>1.64277863502502</v>
+        <v>1.64277851581573</v>
       </c>
       <c r="H674" t="n">
         <v>0</v>
@@ -19944,7 +19944,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G675" t="n">
-        <v>1.64277863502502</v>
+        <v>1.64277851581573</v>
       </c>
       <c r="H675" t="n">
         <v>0</v>
@@ -19973,7 +19973,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G676" t="n">
-        <v>1.64277863502502</v>
+        <v>1.64277851581573</v>
       </c>
       <c r="H676" t="n">
         <v>0</v>
@@ -20205,7 +20205,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G684" t="n">
-        <v>1.5976470708847</v>
+        <v>1.59764719009399</v>
       </c>
       <c r="H684" t="n">
         <v>1500</v>
@@ -20698,7 +20698,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G701" t="n">
-        <v>1.5976470708847</v>
+        <v>1.59764719009399</v>
       </c>
       <c r="H701" t="n">
         <v>1500</v>
@@ -20727,7 +20727,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G702" t="n">
-        <v>1.5976470708847</v>
+        <v>1.59764719009399</v>
       </c>
       <c r="H702" t="n">
         <v>3000</v>
@@ -20756,7 +20756,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G703" t="n">
-        <v>1.5976470708847</v>
+        <v>1.59764719009399</v>
       </c>
       <c r="H703" t="n">
         <v>4500</v>
@@ -20785,7 +20785,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G704" t="n">
-        <v>1.5976470708847</v>
+        <v>1.59764719009399</v>
       </c>
       <c r="H704" t="n">
         <v>0</v>
@@ -20843,7 +20843,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G706" t="n">
-        <v>1.5976470708847</v>
+        <v>1.59764719009399</v>
       </c>
       <c r="H706" t="n">
         <v>7500</v>
@@ -21626,7 +21626,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G733" t="n">
-        <v>1.55251586437225</v>
+        <v>1.55251598358154</v>
       </c>
       <c r="H733" t="n">
         <v>1500</v>
@@ -21655,7 +21655,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G734" t="n">
-        <v>1.55251586437225</v>
+        <v>1.55251598358154</v>
       </c>
       <c r="H734" t="n">
         <v>6000</v>
@@ -21684,7 +21684,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G735" t="n">
-        <v>1.55251586437225</v>
+        <v>1.55251598358154</v>
       </c>
       <c r="H735" t="n">
         <v>0</v>
@@ -21713,7 +21713,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G736" t="n">
-        <v>1.55251586437225</v>
+        <v>1.55251598358154</v>
       </c>
       <c r="H736" t="n">
         <v>0</v>
@@ -21771,7 +21771,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G738" t="n">
-        <v>1.52543723583221</v>
+        <v>1.52543711662292</v>
       </c>
       <c r="H738" t="n">
         <v>7500</v>
@@ -21800,7 +21800,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G739" t="n">
-        <v>1.52543723583221</v>
+        <v>1.52543711662292</v>
       </c>
       <c r="H739" t="n">
         <v>0</v>
@@ -21829,7 +21829,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G740" t="n">
-        <v>1.52543723583221</v>
+        <v>1.52543711662292</v>
       </c>
       <c r="H740" t="n">
         <v>0</v>
@@ -22235,7 +22235,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G754" t="n">
-        <v>1.46225333213806</v>
+        <v>1.46225345134735</v>
       </c>
       <c r="H754" t="n">
         <v>15000</v>
@@ -22612,7 +22612,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G767" t="n">
-        <v>1.48933219909668</v>
+        <v>1.48933207988739</v>
       </c>
       <c r="H767" t="n">
         <v>15000</v>
@@ -22844,7 +22844,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G775" t="n">
-        <v>1.48933219909668</v>
+        <v>1.48933207988739</v>
       </c>
       <c r="H775" t="n">
         <v>3000</v>
@@ -22931,7 +22931,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G778" t="n">
-        <v>1.48933219909668</v>
+        <v>1.48933207988739</v>
       </c>
       <c r="H778" t="n">
         <v>4500</v>
@@ -23076,7 +23076,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G783" t="n">
-        <v>1.46225333213806</v>
+        <v>1.46225345134735</v>
       </c>
       <c r="H783" t="n">
         <v>15000</v>
@@ -23424,7 +23424,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G795" t="n">
-        <v>1.87746095657349</v>
+        <v>1.87746107578278</v>
       </c>
       <c r="H795" t="n">
         <v>319500</v>
@@ -23453,7 +23453,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G796" t="n">
-        <v>1.66985726356506</v>
+        <v>1.66985738277435</v>
       </c>
       <c r="H796" t="n">
         <v>94500</v>
@@ -23627,7 +23627,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G802" t="n">
-        <v>1.84135603904724</v>
+        <v>1.84135615825653</v>
       </c>
       <c r="H802" t="n">
         <v>37500</v>
@@ -23656,7 +23656,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G803" t="n">
-        <v>1.93161857128143</v>
+        <v>1.93161880970001</v>
       </c>
       <c r="H803" t="n">
         <v>73500</v>
@@ -23685,7 +23685,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G804" t="n">
-        <v>1.87746095657349</v>
+        <v>1.87746107578278</v>
       </c>
       <c r="H804" t="n">
         <v>46500</v>
@@ -23714,7 +23714,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G805" t="n">
-        <v>1.85940849781036</v>
+        <v>1.85940837860107</v>
       </c>
       <c r="H805" t="n">
         <v>4500</v>
@@ -23743,7 +23743,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G806" t="n">
-        <v>1.8955135345459</v>
+        <v>1.89551365375519</v>
       </c>
       <c r="H806" t="n">
         <v>9000</v>
@@ -23772,7 +23772,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G807" t="n">
-        <v>1.85940849781036</v>
+        <v>1.85940837860107</v>
       </c>
       <c r="H807" t="n">
         <v>7500</v>
@@ -23801,7 +23801,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G808" t="n">
-        <v>1.87746095657349</v>
+        <v>1.87746107578278</v>
       </c>
       <c r="H808" t="n">
         <v>10500</v>
@@ -23830,7 +23830,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G809" t="n">
-        <v>1.85940849781036</v>
+        <v>1.85940837860107</v>
       </c>
       <c r="H809" t="n">
         <v>1500</v>
@@ -23859,7 +23859,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G810" t="n">
-        <v>1.85940849781036</v>
+        <v>1.85940837860107</v>
       </c>
       <c r="H810" t="n">
         <v>1500</v>
@@ -23888,7 +23888,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G811" t="n">
-        <v>1.84135603904724</v>
+        <v>1.84135615825653</v>
       </c>
       <c r="H811" t="n">
         <v>6000</v>
@@ -23917,7 +23917,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G812" t="n">
-        <v>1.87746095657349</v>
+        <v>1.87746107578278</v>
       </c>
       <c r="H812" t="n">
         <v>6000</v>
@@ -23946,7 +23946,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G813" t="n">
-        <v>1.91356599330902</v>
+        <v>1.91356611251831</v>
       </c>
       <c r="H813" t="n">
         <v>3000</v>
@@ -23975,7 +23975,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G814" t="n">
-        <v>1.87746095657349</v>
+        <v>1.87746107578278</v>
       </c>
       <c r="H814" t="n">
         <v>7500</v>
@@ -24120,7 +24120,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G819" t="n">
-        <v>1.76914620399475</v>
+        <v>1.76914608478546</v>
       </c>
       <c r="H819" t="n">
         <v>12000</v>
@@ -24149,7 +24149,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G820" t="n">
-        <v>1.76914620399475</v>
+        <v>1.76914608478546</v>
       </c>
       <c r="H820" t="n">
         <v>0</v>
@@ -24236,7 +24236,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G823" t="n">
-        <v>1.84135603904724</v>
+        <v>1.84135615825653</v>
       </c>
       <c r="H823" t="n">
         <v>15000</v>
@@ -24584,7 +24584,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G835" t="n">
-        <v>1.76914620399475</v>
+        <v>1.76914608478546</v>
       </c>
       <c r="H835" t="n">
         <v>7500</v>
@@ -25135,7 +25135,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G854" t="n">
-        <v>1.76914620399475</v>
+        <v>1.76914608478546</v>
       </c>
       <c r="H854" t="n">
         <v>1500</v>
@@ -25454,7 +25454,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G865" t="n">
-        <v>1.84135603904724</v>
+        <v>1.84135615825653</v>
       </c>
       <c r="H865" t="n">
         <v>48000</v>
@@ -25483,7 +25483,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G866" t="n">
-        <v>1.87746095657349</v>
+        <v>1.87746107578278</v>
       </c>
       <c r="H866" t="n">
         <v>7500</v>
@@ -25512,7 +25512,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G867" t="n">
-        <v>1.91356599330902</v>
+        <v>1.91356611251831</v>
       </c>
       <c r="H867" t="n">
         <v>21000</v>
@@ -25831,7 +25831,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G878" t="n">
-        <v>1.93161857128143</v>
+        <v>1.93161880970001</v>
       </c>
       <c r="H878" t="n">
         <v>12000</v>
@@ -26324,7 +26324,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G895" t="n">
-        <v>1.85940849781036</v>
+        <v>1.85940837860107</v>
       </c>
       <c r="H895" t="n">
         <v>126000</v>
@@ -26382,7 +26382,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G897" t="n">
-        <v>1.91356599330902</v>
+        <v>1.91356611251831</v>
       </c>
       <c r="H897" t="n">
         <v>54000</v>
@@ -26411,7 +26411,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G898" t="n">
-        <v>1.87746095657349</v>
+        <v>1.87746107578278</v>
       </c>
       <c r="H898" t="n">
         <v>15000</v>
@@ -26440,7 +26440,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G899" t="n">
-        <v>1.85940849781036</v>
+        <v>1.85940837860107</v>
       </c>
       <c r="H899" t="n">
         <v>16500</v>
@@ -26469,7 +26469,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G900" t="n">
-        <v>1.87746095657349</v>
+        <v>1.87746107578278</v>
       </c>
       <c r="H900" t="n">
         <v>12000</v>
@@ -26498,7 +26498,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G901" t="n">
-        <v>1.85940849781036</v>
+        <v>1.85940837860107</v>
       </c>
       <c r="H901" t="n">
         <v>4500</v>
@@ -26527,7 +26527,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G902" t="n">
-        <v>1.93161857128143</v>
+        <v>1.93161880970001</v>
       </c>
       <c r="H902" t="n">
         <v>9000</v>
@@ -26556,7 +26556,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G903" t="n">
-        <v>1.91356599330902</v>
+        <v>1.91356611251831</v>
       </c>
       <c r="H903" t="n">
         <v>4500</v>
@@ -26585,7 +26585,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G904" t="n">
-        <v>1.93161857128143</v>
+        <v>1.93161880970001</v>
       </c>
       <c r="H904" t="n">
         <v>9000</v>
@@ -26643,7 +26643,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G906" t="n">
-        <v>1.91356599330902</v>
+        <v>1.91356611251831</v>
       </c>
       <c r="H906" t="n">
         <v>7500</v>
@@ -26672,7 +26672,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G907" t="n">
-        <v>1.93161857128143</v>
+        <v>1.93161880970001</v>
       </c>
       <c r="H907" t="n">
         <v>1500</v>
@@ -26701,7 +26701,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G908" t="n">
-        <v>1.93161857128143</v>
+        <v>1.93161880970001</v>
       </c>
       <c r="H908" t="n">
         <v>0</v>
@@ -26730,7 +26730,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G909" t="n">
-        <v>1.85940849781036</v>
+        <v>1.85940837860107</v>
       </c>
       <c r="H909" t="n">
         <v>111000</v>
@@ -26759,7 +26759,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G910" t="n">
-        <v>1.84135603904724</v>
+        <v>1.84135615825653</v>
       </c>
       <c r="H910" t="n">
         <v>21000</v>
@@ -26788,7 +26788,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G911" t="n">
-        <v>1.87746095657349</v>
+        <v>1.87746107578278</v>
       </c>
       <c r="H911" t="n">
         <v>9000</v>
@@ -26817,7 +26817,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G912" t="n">
-        <v>1.85940849781036</v>
+        <v>1.85940837860107</v>
       </c>
       <c r="H912" t="n">
         <v>15000</v>
@@ -26846,7 +26846,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G913" t="n">
-        <v>1.85940849781036</v>
+        <v>1.85940837860107</v>
       </c>
       <c r="H913" t="n">
         <v>6000</v>
@@ -26875,7 +26875,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G914" t="n">
-        <v>1.8955135345459</v>
+        <v>1.89551365375519</v>
       </c>
       <c r="H914" t="n">
         <v>7500</v>
@@ -26904,7 +26904,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G915" t="n">
-        <v>1.87746095657349</v>
+        <v>1.87746107578278</v>
       </c>
       <c r="H915" t="n">
         <v>10500</v>
@@ -26933,7 +26933,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G916" t="n">
-        <v>1.87746095657349</v>
+        <v>1.87746107578278</v>
       </c>
       <c r="H916" t="n">
         <v>1500</v>
@@ -26962,7 +26962,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G917" t="n">
-        <v>1.85940849781036</v>
+        <v>1.85940837860107</v>
       </c>
       <c r="H917" t="n">
         <v>13500</v>
@@ -45673,6 +45673,35 @@
         <v>6000</v>
       </c>
       <c r="I1562" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1563">
+      <c r="A1563" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1563" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C1563" t="n">
+        <v>1.51999998092651</v>
+      </c>
+      <c r="D1563" t="n">
+        <v>1.51999998092651</v>
+      </c>
+      <c r="E1563" t="n">
+        <v>1.51999998092651</v>
+      </c>
+      <c r="F1563" t="n">
+        <v>1.51999998092651</v>
+      </c>
+      <c r="G1563" t="n">
+        <v>1.51999998092651</v>
+      </c>
+      <c r="H1563" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I1563" t="s">
         <v>9</v>
       </c>
     </row>
